--- a/data/trending_momentum_stocks.xlsx
+++ b/data/trending_momentum_stocks.xlsx
@@ -461,2809 +461,2805 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NKIND</t>
+          <t>KALANA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>64.31999999999999</v>
+        <v>19.6</v>
       </c>
       <c r="C2" t="n">
-        <v>73.98999999999999</v>
+        <v>23.5</v>
       </c>
       <c r="D2" t="n">
-        <v>15.03</v>
+        <v>19.9</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>67.98999999999999</v>
+        <v>23.5</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>-8.109999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PRATHAM</t>
+          <t>WEWIN</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>131.85</v>
+        <v>43.55</v>
       </c>
       <c r="C3" t="n">
-        <v>150.5</v>
+        <v>47.7</v>
       </c>
       <c r="D3" t="n">
-        <v>14.14</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>139.8</v>
+        <v>45.19</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>-7.11</v>
+        <v>-5.26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>XTGLOBAL</t>
+          <t>DCMFINSERV</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33.63</v>
+        <v>4.38</v>
       </c>
       <c r="C4" t="n">
-        <v>37.9</v>
+        <v>4.7</v>
       </c>
       <c r="D4" t="n">
-        <v>12.7</v>
+        <v>7.31</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>38.87</v>
+        <v>4.15</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>2.56</v>
+        <v>-11.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MFML</t>
+          <t>3PLAND</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.11</v>
+        <v>32.68</v>
       </c>
       <c r="C5" t="n">
-        <v>25.98</v>
+        <v>34.89</v>
       </c>
       <c r="D5" t="n">
-        <v>12.42</v>
+        <v>6.76</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>23.99</v>
+        <v>32.3</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>-7.66</v>
+        <v>-7.42</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TARMAT</t>
+          <t>LIBAS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>64.89</v>
+        <v>10.04</v>
       </c>
       <c r="C6" t="n">
-        <v>72.75</v>
+        <v>10.7</v>
       </c>
       <c r="D6" t="n">
-        <v>12.11</v>
+        <v>6.57</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>70.76000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>-2.74</v>
+        <v>-4.67</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KABRAEXTRU</t>
+          <t>DTIL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>251.07</v>
+        <v>139</v>
       </c>
       <c r="C7" t="n">
-        <v>273</v>
+        <v>147</v>
       </c>
       <c r="D7" t="n">
-        <v>8.73</v>
+        <v>5.76</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>260.41</v>
+        <v>136</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>-4.61</v>
+        <v>-7.48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RVHL</t>
+          <t>MONEYBOXX</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>39.67</v>
+        <v>63.4</v>
       </c>
       <c r="C8" t="n">
-        <v>42.99</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>8.369999999999999</v>
+        <v>5.66</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>40.71</v>
+        <v>63.01</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>-5.3</v>
+        <v>-5.94</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UMESLTD</t>
+          <t>KAYA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.14</v>
+        <v>323.7</v>
       </c>
       <c r="C9" t="n">
-        <v>4.44</v>
+        <v>340</v>
       </c>
       <c r="D9" t="n">
-        <v>7.25</v>
+        <v>5.04</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>4.27</v>
+        <v>321.55</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>-3.83</v>
+        <v>-5.43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BSHSL</t>
+          <t>NEUEON</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>88.75</v>
+        <v>10.8</v>
       </c>
       <c r="C10" t="n">
-        <v>95</v>
+        <v>11.34</v>
       </c>
       <c r="D10" t="n">
-        <v>7.04</v>
+        <v>5</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>89.91</v>
+        <v>11.34</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>-5.36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MOHITIND</t>
+          <t>SETUINFRA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24.67</v>
+        <v>0.4</v>
       </c>
       <c r="C11" t="n">
-        <v>26.39</v>
+        <v>0.42</v>
       </c>
       <c r="D11" t="n">
-        <v>6.97</v>
+        <v>5</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>25.89</v>
+        <v>0.42</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>-1.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>OSWALSEEDS</t>
+          <t>UNITEDPOLY</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.09</v>
+        <v>24.66</v>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>25.89</v>
       </c>
       <c r="D12" t="n">
-        <v>6.95</v>
+        <v>4.99</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>12.95</v>
+        <v>23.9</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>-7.5</v>
+        <v>-7.69</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TFL</t>
+          <t>ROLLT</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13.59</v>
+        <v>1.41</v>
       </c>
       <c r="C13" t="n">
-        <v>14.49</v>
+        <v>1.48</v>
       </c>
       <c r="D13" t="n">
-        <v>6.62</v>
+        <v>4.96</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>13.22</v>
+        <v>1.48</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>-8.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SUPREME</t>
+          <t>SETCO</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>55.45</v>
+        <v>16.92</v>
       </c>
       <c r="C14" t="n">
-        <v>59.1</v>
+        <v>17.76</v>
       </c>
       <c r="D14" t="n">
-        <v>6.58</v>
+        <v>4.96</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>55.69</v>
+        <v>17.76</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>-5.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ELGIRUBCO</t>
+          <t>EUROTEXIND</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>40.37</v>
+        <v>12.91</v>
       </c>
       <c r="C15" t="n">
-        <v>42.94</v>
+        <v>13.55</v>
       </c>
       <c r="D15" t="n">
-        <v>6.37</v>
+        <v>4.96</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>41</v>
+        <v>13.4</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>-4.52</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DHARAN</t>
+          <t>TOUCHWOOD</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.16</v>
+        <v>73.89</v>
       </c>
       <c r="C16" t="n">
-        <v>0.17</v>
+        <v>77.55</v>
       </c>
       <c r="D16" t="n">
-        <v>6.25</v>
+        <v>4.95</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.17</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>-8.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RETAIL</t>
+          <t>PALREDTEC</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>23.4</v>
+        <v>32.55</v>
       </c>
       <c r="C17" t="n">
-        <v>24.8</v>
+        <v>34.14</v>
       </c>
       <c r="D17" t="n">
-        <v>5.98</v>
+        <v>4.88</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>24.25</v>
+        <v>33.52</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>-2.22</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SURYALAXMI</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>58.52</v>
+        <v>6.67</v>
       </c>
       <c r="C18" t="n">
-        <v>62</v>
+        <v>6.99</v>
       </c>
       <c r="D18" t="n">
-        <v>5.95</v>
+        <v>4.8</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>60</v>
+        <v>6.42</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>-3.23</v>
+        <v>-8.15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RHL</t>
+          <t>DCMSIL</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>192.47</v>
+        <v>63.67</v>
       </c>
       <c r="C19" t="n">
-        <v>203.9</v>
+        <v>66.7</v>
       </c>
       <c r="D19" t="n">
-        <v>5.94</v>
+        <v>4.76</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>192.41</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>-5.64</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RADAAN</t>
+          <t>ORTEL</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.12</v>
+        <v>1.51</v>
       </c>
       <c r="C20" t="n">
-        <v>3.3</v>
+        <v>1.58</v>
       </c>
       <c r="D20" t="n">
-        <v>5.77</v>
+        <v>4.64</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>3.1</v>
+        <v>1.58</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>-6.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FOSECOIND</t>
+          <t>BLUECOAST</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4731</v>
+        <v>21.33</v>
       </c>
       <c r="C21" t="n">
-        <v>4989.9</v>
+        <v>22.3</v>
       </c>
       <c r="D21" t="n">
-        <v>5.47</v>
+        <v>4.55</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>5315.1</v>
+        <v>21.21</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>6.52</v>
+        <v>-4.89</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COUNCODOS</t>
+          <t>DHARIWAL</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5.13</v>
+        <v>41.8</v>
       </c>
       <c r="C22" t="n">
-        <v>5.4</v>
+        <v>43.7</v>
       </c>
       <c r="D22" t="n">
-        <v>5.26</v>
+        <v>4.55</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>5.21</v>
+        <v>43.85</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>-3.52</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SILKFLEX</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>133.05</v>
+        <v>483.9</v>
       </c>
       <c r="C23" t="n">
-        <v>139.7</v>
+        <v>503</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>139</v>
+        <v>479</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>-0.5</v>
+        <v>-4.77</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HMT</t>
+          <t>EFACTOR</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>58.05</v>
+        <v>234.95</v>
       </c>
       <c r="C24" t="n">
-        <v>60.95</v>
+        <v>244</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>60.95</v>
+        <v>230</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>-5.74</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>OMKARCHEM</t>
+          <t>GTECJAINX</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.8</v>
+        <v>19.24</v>
       </c>
       <c r="C25" t="n">
-        <v>5.04</v>
+        <v>19.9</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>3.43</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>4.7</v>
+        <v>19.39</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>-6.75</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DCMSIL</t>
+          <t>DHARARAIL</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>60.64</v>
+        <v>119</v>
       </c>
       <c r="C26" t="n">
-        <v>63.67</v>
+        <v>122.9</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>3.28</v>
       </c>
       <c r="E26" t="b">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>63.67</v>
+        <v>116.75</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>UNITEDPOLY</t>
+          <t>VAISHALI</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>23.49</v>
+        <v>6.97</v>
       </c>
       <c r="C27" t="n">
-        <v>24.66</v>
+        <v>7.19</v>
       </c>
       <c r="D27" t="n">
-        <v>4.98</v>
+        <v>3.16</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>24.66</v>
+        <v>6.88</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>-4.31</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SECURKLOUD</t>
+          <t>VLEGOV</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>22.27</v>
+        <v>15.6</v>
       </c>
       <c r="C28" t="n">
-        <v>23.37</v>
+        <v>16.09</v>
       </c>
       <c r="D28" t="n">
-        <v>4.94</v>
+        <v>3.14</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>22.7</v>
+        <v>16.08</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>-2.87</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FILATFASH</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.21</v>
+        <v>279.7</v>
       </c>
       <c r="C29" t="n">
-        <v>0.22</v>
+        <v>288</v>
       </c>
       <c r="D29" t="n">
-        <v>4.76</v>
+        <v>2.97</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0.22</v>
+        <v>279.85</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SHRENIK</t>
+          <t>GJL</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.42</v>
+        <v>163.4</v>
       </c>
       <c r="C30" t="n">
-        <v>0.44</v>
+        <v>168</v>
       </c>
       <c r="D30" t="n">
-        <v>4.76</v>
+        <v>2.82</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0.44</v>
+        <v>171.55</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TECHLABS</t>
+          <t>GPECO</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>185.75</v>
+        <v>355</v>
       </c>
       <c r="C31" t="n">
-        <v>194.55</v>
+        <v>365</v>
       </c>
       <c r="D31" t="n">
-        <v>4.74</v>
+        <v>2.82</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>192</v>
+        <v>339</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>-1.31</v>
+        <v>-7.12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GJL</t>
+          <t>MITCON</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>155.65</v>
+        <v>58.5</v>
       </c>
       <c r="C32" t="n">
-        <v>163</v>
+        <v>60</v>
       </c>
       <c r="D32" t="n">
-        <v>4.72</v>
+        <v>2.56</v>
       </c>
       <c r="E32" t="b">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>163.4</v>
+        <v>58.01</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>0.25</v>
+        <v>-3.32</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ORTINGLOBE</t>
+          <t>FLFL</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>16.38</v>
+        <v>1.2</v>
       </c>
       <c r="C33" t="n">
-        <v>17.15</v>
+        <v>1.23</v>
       </c>
       <c r="D33" t="n">
-        <v>4.7</v>
+        <v>2.5</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>16.8</v>
+        <v>1.24</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>-2.04</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CROWN</t>
+          <t>BANKA</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>120.49</v>
+        <v>57.64</v>
       </c>
       <c r="C34" t="n">
-        <v>126</v>
+        <v>58.99</v>
       </c>
       <c r="D34" t="n">
-        <v>4.57</v>
+        <v>2.34</v>
       </c>
       <c r="E34" t="b">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>122.95</v>
+        <v>56.8</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>-2.42</v>
+        <v>-3.71</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DHRUV</t>
+          <t>FEL</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>27.24</v>
+        <v>0.43</v>
       </c>
       <c r="C35" t="n">
-        <v>28.48</v>
+        <v>0.44</v>
       </c>
       <c r="D35" t="n">
-        <v>4.55</v>
+        <v>2.33</v>
       </c>
       <c r="E35" t="b">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>27.41</v>
+        <v>0.44</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>-3.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TEJASNET</t>
+          <t>RPPL</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>371.05</v>
+        <v>16.6</v>
       </c>
       <c r="C36" t="n">
-        <v>387.8</v>
+        <v>16.95</v>
       </c>
       <c r="D36" t="n">
-        <v>4.51</v>
+        <v>2.11</v>
       </c>
       <c r="E36" t="b">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>407</v>
+        <v>16.42</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>4.95</v>
+        <v>-3.13</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>NDLVENTURE</t>
+          <t>MANCREDIT</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>113</v>
+        <v>168.55</v>
       </c>
       <c r="C37" t="n">
-        <v>118.06</v>
+        <v>171.99</v>
       </c>
       <c r="D37" t="n">
-        <v>4.48</v>
+        <v>2.04</v>
       </c>
       <c r="E37" t="b">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>115.66</v>
+        <v>167.64</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>-2.03</v>
+        <v>-2.53</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ROLLT</t>
+          <t>VHLTD</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.35</v>
+        <v>147</v>
       </c>
       <c r="C38" t="n">
-        <v>1.41</v>
+        <v>149.9</v>
       </c>
       <c r="D38" t="n">
-        <v>4.44</v>
+        <v>1.97</v>
       </c>
       <c r="E38" t="b">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>1.41</v>
+        <v>147</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SUVIDHAA</t>
+          <t>RAJRILTD</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.97</v>
+        <v>22.93</v>
       </c>
       <c r="C39" t="n">
-        <v>3.1</v>
+        <v>23.38</v>
       </c>
       <c r="D39" t="n">
-        <v>4.38</v>
+        <v>1.96</v>
       </c>
       <c r="E39" t="b">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>2.99</v>
+        <v>22.48</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>-3.55</v>
+        <v>-3.85</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BALKRISHNA</t>
+          <t>SANCO</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>16.28</v>
+        <v>2.21</v>
       </c>
       <c r="C40" t="n">
-        <v>16.99</v>
+        <v>2.25</v>
       </c>
       <c r="D40" t="n">
-        <v>4.36</v>
+        <v>1.81</v>
       </c>
       <c r="E40" t="b">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>16.07</v>
+        <v>2.21</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>-5.41</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TNTELE</t>
+          <t>BAFNAPH</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>8.82</v>
+        <v>106.15</v>
       </c>
       <c r="C41" t="n">
-        <v>9.199999999999999</v>
+        <v>108</v>
       </c>
       <c r="D41" t="n">
-        <v>4.31</v>
+        <v>1.74</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>8.890000000000001</v>
+        <v>108</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>-3.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>LASA</t>
+          <t>HINDOILEXP</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>7.85</v>
+        <v>130.88</v>
       </c>
       <c r="C42" t="n">
-        <v>8.18</v>
+        <v>133</v>
       </c>
       <c r="D42" t="n">
-        <v>4.2</v>
+        <v>1.62</v>
       </c>
       <c r="E42" t="b">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>7.7</v>
+        <v>136.77</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>-5.87</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CREATIVEYE</t>
+          <t>KEEPLEARN</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>6.67</v>
+        <v>1.96</v>
       </c>
       <c r="C43" t="n">
-        <v>6.95</v>
+        <v>1.99</v>
       </c>
       <c r="D43" t="n">
-        <v>4.2</v>
+        <v>1.53</v>
       </c>
       <c r="E43" t="b">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>6.5</v>
+        <v>1.97</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>-6.47</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TCIFINANCE</t>
+          <t>CEDAAR</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>16.03</v>
+        <v>30</v>
       </c>
       <c r="C44" t="n">
-        <v>16.69</v>
+        <v>30.45</v>
       </c>
       <c r="D44" t="n">
-        <v>4.12</v>
+        <v>1.5</v>
       </c>
       <c r="E44" t="b">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>15.57</v>
+        <v>29.2</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>-6.71</v>
+        <v>-4.11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PRAKASHSTL</t>
+          <t>HEXATRADEX</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4.41</v>
+        <v>160.11</v>
       </c>
       <c r="C45" t="n">
-        <v>4.59</v>
+        <v>162.5</v>
       </c>
       <c r="D45" t="n">
-        <v>4.08</v>
+        <v>1.49</v>
       </c>
       <c r="E45" t="b">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>4.44</v>
+        <v>160</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>-3.27</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ADROITINFO</t>
+          <t>SOUTHWEST</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>10.03</v>
+        <v>182.2</v>
       </c>
       <c r="C46" t="n">
-        <v>10.42</v>
+        <v>184.9</v>
       </c>
       <c r="D46" t="n">
-        <v>3.89</v>
+        <v>1.48</v>
       </c>
       <c r="E46" t="b">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>10.2</v>
+        <v>184.5</v>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>-2.11</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PRUDMOULI</t>
+          <t>LAKPRE</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>17.33</v>
+        <v>4.97</v>
       </c>
       <c r="C47" t="n">
-        <v>17.99</v>
+        <v>5.04</v>
       </c>
       <c r="D47" t="n">
-        <v>3.81</v>
+        <v>1.41</v>
       </c>
       <c r="E47" t="b">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>17.49</v>
+        <v>5.15</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>-2.78</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>RUCHINFRA</t>
+          <t>BALAXI</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>5.78</v>
+        <v>19.73</v>
       </c>
       <c r="C48" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D48" t="n">
-        <v>3.81</v>
+        <v>1.37</v>
       </c>
       <c r="E48" t="b">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>5.75</v>
+        <v>18.98</v>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>-4.17</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CUDML</t>
+          <t>IL&amp;FSTRANS</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>102.1</v>
+        <v>2.45</v>
       </c>
       <c r="C49" t="n">
-        <v>105.95</v>
+        <v>2.48</v>
       </c>
       <c r="D49" t="n">
-        <v>3.77</v>
+        <v>1.22</v>
       </c>
       <c r="E49" t="b">
         <v>0</v>
       </c>
-      <c r="F49" t="n">
-        <v>104</v>
-      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
-      <c r="H49" t="n">
-        <v>-1.84</v>
-      </c>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SHRADHA</t>
+          <t>ALPA</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>38.1</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="C50" t="n">
-        <v>39.5</v>
+        <v>66.8</v>
       </c>
       <c r="D50" t="n">
-        <v>3.67</v>
+        <v>1.2</v>
       </c>
       <c r="E50" t="b">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>38.12</v>
+        <v>64.5</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>-3.49</v>
+        <v>-3.44</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DIGIKORE</t>
+          <t>DJML</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>84.5</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="C51" t="n">
-        <v>87.59999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="D51" t="n">
-        <v>3.67</v>
+        <v>1.09</v>
       </c>
       <c r="E51" t="b">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>83</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>-5.25</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SETCO</t>
+          <t>PGHL</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>16.12</v>
+        <v>4900.5</v>
       </c>
       <c r="C52" t="n">
-        <v>16.7</v>
+        <v>4949</v>
       </c>
       <c r="D52" t="n">
-        <v>3.6</v>
+        <v>0.99</v>
       </c>
       <c r="E52" t="b">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>16.92</v>
+        <v>4946.5</v>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>1.32</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>GOLDTECH</t>
+          <t>DURLAX</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>39.39</v>
+        <v>48.25</v>
       </c>
       <c r="C53" t="n">
-        <v>40.79</v>
+        <v>48.7</v>
       </c>
       <c r="D53" t="n">
-        <v>3.55</v>
+        <v>0.93</v>
       </c>
       <c r="E53" t="b">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>39.59</v>
+        <v>45.3</v>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>-2.94</v>
+        <v>-6.98</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SHEMAROO</t>
+          <t>BLBLIMITED</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>104.31</v>
+        <v>17.74</v>
       </c>
       <c r="C54" t="n">
-        <v>107.99</v>
+        <v>17.9</v>
       </c>
       <c r="D54" t="n">
-        <v>3.53</v>
+        <v>0.9</v>
       </c>
       <c r="E54" t="b">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>102.14</v>
+        <v>17.11</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>-5.42</v>
+        <v>-4.41</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>USK</t>
+          <t>NGIL</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>28.57</v>
+        <v>25.78</v>
       </c>
       <c r="C55" t="n">
-        <v>29.57</v>
+        <v>25.99</v>
       </c>
       <c r="D55" t="n">
-        <v>3.5</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>29.01</v>
+        <v>25.4</v>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>-1.89</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MTEDUCARE</t>
+          <t>HILTON</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1.44</v>
+        <v>17.82</v>
       </c>
       <c r="C56" t="n">
-        <v>1.49</v>
+        <v>17.96</v>
       </c>
       <c r="D56" t="n">
-        <v>3.47</v>
+        <v>0.79</v>
       </c>
       <c r="E56" t="b">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>1.47</v>
+        <v>17.4</v>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>-1.34</v>
+        <v>-3.12</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BYKE</t>
+          <t>MODIRUBBER</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>43.5</v>
+        <v>117.12</v>
       </c>
       <c r="C57" t="n">
-        <v>44.99</v>
+        <v>117.99</v>
       </c>
       <c r="D57" t="n">
-        <v>3.43</v>
+        <v>0.74</v>
       </c>
       <c r="E57" t="b">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>43.33</v>
+        <v>112.49</v>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>-3.69</v>
+        <v>-4.66</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>VHLTD</t>
+          <t>MTEDUCARE</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>147.85</v>
+        <v>1.38</v>
       </c>
       <c r="C58" t="n">
-        <v>152.9</v>
+        <v>1.39</v>
       </c>
       <c r="D58" t="n">
-        <v>3.42</v>
+        <v>0.72</v>
       </c>
       <c r="E58" t="b">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>148.79</v>
+        <v>1.39</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>-2.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>GFLLIMITED</t>
+          <t>ASPINWALL</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>45.89</v>
+        <v>215.57</v>
       </c>
       <c r="C59" t="n">
-        <v>47.43</v>
+        <v>217</v>
       </c>
       <c r="D59" t="n">
-        <v>3.36</v>
+        <v>0.66</v>
       </c>
       <c r="E59" t="b">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>46</v>
+        <v>212</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>-3.01</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PREMIER</t>
+          <t>ORTINGLOBE</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2.99</v>
+        <v>17.19</v>
       </c>
       <c r="C60" t="n">
-        <v>3.09</v>
+        <v>17.3</v>
       </c>
       <c r="D60" t="n">
-        <v>3.34</v>
+        <v>0.64</v>
       </c>
       <c r="E60" t="b">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>16.5</v>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>-2.91</v>
+        <v>-4.62</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TECILCHEM</t>
+          <t>HBSL</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>13.54</v>
+        <v>55.66</v>
       </c>
       <c r="C61" t="n">
-        <v>13.99</v>
+        <v>56</v>
       </c>
       <c r="D61" t="n">
-        <v>3.32</v>
+        <v>0.61</v>
       </c>
       <c r="E61" t="b">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>13.01</v>
+        <v>54.57</v>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>-7.01</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SEMAC</t>
+          <t>ELGNZ</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>240.06</v>
+        <v>67.8</v>
       </c>
       <c r="C62" t="n">
-        <v>248</v>
+        <v>68.2</v>
       </c>
       <c r="D62" t="n">
-        <v>3.31</v>
+        <v>0.59</v>
       </c>
       <c r="E62" t="b">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>243</v>
+        <v>67</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>-2.02</v>
+        <v>-1.76</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>STEELCITY</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>6.77</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="C63" t="n">
-        <v>6.99</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D63" t="n">
-        <v>3.25</v>
+        <v>0.57</v>
       </c>
       <c r="E63" t="b">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>6.6</v>
+        <v>87.98</v>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>-5.58</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DAMODARIND</t>
+          <t>VISASTEEL</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>25.19</v>
+        <v>38.29</v>
       </c>
       <c r="C64" t="n">
-        <v>25.99</v>
+        <v>38.48</v>
       </c>
       <c r="D64" t="n">
-        <v>3.18</v>
+        <v>0.5</v>
       </c>
       <c r="E64" t="b">
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>25.54</v>
+        <v>37.89</v>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>-1.73</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>NEPHROCARE</t>
+          <t>SPLPETRO</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>72.7</v>
+        <v>716.8</v>
       </c>
       <c r="C65" t="n">
-        <v>75</v>
+        <v>720.3</v>
       </c>
       <c r="D65" t="n">
-        <v>3.16</v>
+        <v>0.49</v>
       </c>
       <c r="E65" t="b">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>76.34999999999999</v>
+        <v>707.85</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>1.8</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BALUFORGE</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>489.4</v>
+        <v>603.8</v>
       </c>
       <c r="C66" t="n">
-        <v>504.7</v>
+        <v>606</v>
       </c>
       <c r="D66" t="n">
-        <v>3.13</v>
+        <v>0.36</v>
       </c>
       <c r="E66" t="b">
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>496.65</v>
+        <v>618.65</v>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>-1.6</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MANGALAM</t>
+          <t>EMBDL</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>29.97</v>
+        <v>60.41</v>
       </c>
       <c r="C67" t="n">
-        <v>30.9</v>
+        <v>60.6</v>
       </c>
       <c r="D67" t="n">
-        <v>3.1</v>
+        <v>0.31</v>
       </c>
       <c r="E67" t="b">
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>29.47</v>
+        <v>60.1</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>-4.63</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ESFL</t>
+          <t>BILVYAPAR</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>128</v>
+        <v>6.79</v>
       </c>
       <c r="C68" t="n">
-        <v>131.95</v>
+        <v>6.81</v>
       </c>
       <c r="D68" t="n">
-        <v>3.09</v>
+        <v>0.29</v>
       </c>
       <c r="E68" t="b">
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>134.4</v>
+        <v>7.05</v>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>1.86</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>LAOPALA</t>
+          <t>INDIGRID</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>203.9</v>
+        <v>166.27</v>
       </c>
       <c r="C69" t="n">
-        <v>210.2</v>
+        <v>166.7</v>
       </c>
       <c r="D69" t="n">
-        <v>3.09</v>
+        <v>0.26</v>
       </c>
       <c r="E69" t="b">
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>207.8</v>
+        <v>166.09</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>-1.14</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MITTAL</t>
+          <t>ABCOTS</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.99</v>
+        <v>409.05</v>
       </c>
       <c r="C70" t="n">
-        <v>1.02</v>
+        <v>409.9</v>
       </c>
       <c r="D70" t="n">
-        <v>3.03</v>
+        <v>0.21</v>
       </c>
       <c r="E70" t="b">
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>1.01</v>
+        <v>407.65</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>-0.98</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PRIZOR</t>
+          <t>GOLDENTOBC</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>349.45</v>
+        <v>29.84</v>
       </c>
       <c r="C71" t="n">
-        <v>360</v>
+        <v>29.9</v>
       </c>
       <c r="D71" t="n">
-        <v>3.02</v>
+        <v>0.2</v>
       </c>
       <c r="E71" t="b">
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>352.2</v>
+        <v>29.31</v>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>-2.17</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>IMPEXFERRO</t>
+          <t>SAURASHCEM</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1.69</v>
+        <v>65.54000000000001</v>
       </c>
       <c r="C72" t="n">
-        <v>1.74</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="D72" t="n">
-        <v>2.96</v>
+        <v>0.17</v>
       </c>
       <c r="E72" t="b">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>1.65</v>
+        <v>64.78</v>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>-5.17</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STEL</t>
+          <t>GHCL</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>505</v>
+        <v>479.2</v>
       </c>
       <c r="C73" t="n">
-        <v>519.9</v>
+        <v>480</v>
       </c>
       <c r="D73" t="n">
-        <v>2.95</v>
+        <v>0.17</v>
       </c>
       <c r="E73" t="b">
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>500.4</v>
+        <v>470.6</v>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>-3.75</v>
+        <v>-1.96</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DANGEE</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>3.06</v>
+        <v>514.65</v>
       </c>
       <c r="C74" t="n">
-        <v>3.15</v>
+        <v>515</v>
       </c>
       <c r="D74" t="n">
-        <v>2.94</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E74" t="b">
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>3.1</v>
+        <v>523</v>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>-1.59</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SGL</t>
+          <t>VSTTILLERS</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>13.1</v>
+        <v>5776</v>
       </c>
       <c r="C75" t="n">
-        <v>13.48</v>
+        <v>5779.5</v>
       </c>
       <c r="D75" t="n">
-        <v>2.9</v>
+        <v>0.06</v>
       </c>
       <c r="E75" t="b">
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>12.43</v>
+        <v>5711</v>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>-7.79</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>ORIENTLTD</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1289.1</v>
+        <v>64.87</v>
       </c>
       <c r="C76" t="n">
-        <v>1326.3</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="D76" t="n">
-        <v>2.89</v>
+        <v>0.05</v>
       </c>
       <c r="E76" t="b">
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>1305.1</v>
+        <v>64.27</v>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>-1.6</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SITINET</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.35</v>
+        <v>3353.5</v>
       </c>
       <c r="C77" t="n">
-        <v>0.36</v>
+        <v>3354.9</v>
       </c>
       <c r="D77" t="n">
-        <v>2.86</v>
+        <v>0.04</v>
       </c>
       <c r="E77" t="b">
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>0.35</v>
+        <v>3423.8</v>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>-2.78</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>JAIPURKURT</t>
+          <t>ZODIACLOTH</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>35.04</v>
+        <v>80.5</v>
       </c>
       <c r="C78" t="n">
-        <v>36</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="D78" t="n">
-        <v>2.74</v>
+        <v>0.01</v>
       </c>
       <c r="E78" t="b">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>35.65</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>-0.97</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>TRANSWORLD</t>
+          <t>RADAAN</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>141.18</v>
+        <v>3.12</v>
       </c>
       <c r="C79" t="n">
-        <v>145</v>
+        <v>3.12</v>
       </c>
       <c r="D79" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="E79" t="b">
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>142.09</v>
+        <v>2.98</v>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>-2.01</v>
+        <v>-4.49</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SUMEETINDS</t>
+          <t>ALLDIGI</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>26.24</v>
+        <v>823.55</v>
       </c>
       <c r="C80" t="n">
-        <v>26.95</v>
+        <v>823.55</v>
       </c>
       <c r="D80" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="E80" t="b">
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>26.66</v>
+        <v>824.1</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>-1.08</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>NRAIL</t>
+          <t>TRIGYN</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>439.15</v>
+        <v>52.11</v>
       </c>
       <c r="C81" t="n">
-        <v>451</v>
+        <v>52.11</v>
       </c>
       <c r="D81" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="E81" t="b">
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>450.4</v>
+        <v>51.4</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>-0.13</v>
+        <v>-1.36</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AHCL</t>
+          <t>IMPEXFERRO</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>108.19</v>
+        <v>1.7</v>
       </c>
       <c r="C82" t="n">
-        <v>111.11</v>
+        <v>1.7</v>
       </c>
       <c r="D82" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="E82" t="b">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>108.07</v>
+        <v>1.67</v>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>-2.74</v>
+        <v>-1.76</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BAGFILMS</t>
+          <t>ARCHIES</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>5.2</v>
+        <v>15.82</v>
       </c>
       <c r="C83" t="n">
-        <v>5.34</v>
+        <v>15.82</v>
       </c>
       <c r="D83" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="E83" t="b">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>5.25</v>
+        <v>14.95</v>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>-1.69</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>NOIDATOLL</t>
+          <t>PRAKASHSTL</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>3.77</v>
+        <v>4.37</v>
       </c>
       <c r="C84" t="n">
-        <v>3.87</v>
+        <v>4.37</v>
       </c>
       <c r="D84" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="E84" t="b">
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>3.83</v>
+        <v>4.39</v>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>-1.03</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>KRITIKA</t>
+          <t>AILIMITED</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>6.04</v>
+        <v>36.55</v>
       </c>
       <c r="C85" t="n">
-        <v>6.2</v>
+        <v>36.55</v>
       </c>
       <c r="D85" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="E85" t="b">
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>6.06</v>
+        <v>38.35</v>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>-2.26</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>PREMIER</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>7.58</v>
+        <v>2.99</v>
       </c>
       <c r="C86" t="n">
-        <v>7.78</v>
+        <v>2.99</v>
       </c>
       <c r="D86" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="E86" t="b">
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>7.55</v>
+        <v>2.85</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>-2.96</v>
+        <v>-4.68</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PYRAMID</t>
+          <t>TIL</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>148.13</v>
+        <v>208.98</v>
       </c>
       <c r="C87" t="n">
-        <v>151.99</v>
+        <v>208.98</v>
       </c>
       <c r="D87" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="E87" t="b">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>149.52</v>
+        <v>213.79</v>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>-1.63</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ISHANCH</t>
+          <t>RELCHEMQ</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>60.23</v>
+        <v>122.33</v>
       </c>
       <c r="C88" t="n">
-        <v>61.8</v>
+        <v>122.33</v>
       </c>
       <c r="D88" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="E88" t="b">
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>60</v>
+        <v>118.61</v>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>-2.91</v>
+        <v>-3.04</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>HAVISHA</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1.53</v>
+        <v>55.99</v>
       </c>
       <c r="C89" t="n">
-        <v>1.57</v>
+        <v>55.99</v>
       </c>
       <c r="D89" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="E89" t="b">
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>1.57</v>
+        <v>55.06</v>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>VARDHACRLC</t>
+          <t>BANG</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>33.97</v>
+        <v>41.52</v>
       </c>
       <c r="C90" t="n">
-        <v>34.85</v>
+        <v>41.52</v>
       </c>
       <c r="D90" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="E90" t="b">
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>34.75</v>
+        <v>41.99</v>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>-0.29</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>UNIVASTU</t>
+          <t>HALEOSLABS</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>66.79000000000001</v>
+        <v>1260.3</v>
       </c>
       <c r="C91" t="n">
-        <v>68.5</v>
+        <v>1260.3</v>
       </c>
       <c r="D91" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="E91" t="b">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>66.45999999999999</v>
+        <v>1246</v>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>-2.98</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>OMAXE</t>
+          <t>AHLEAST</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>78.8</v>
+        <v>160.77</v>
       </c>
       <c r="C92" t="n">
-        <v>80.8</v>
+        <v>160.77</v>
       </c>
       <c r="D92" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="E92" t="b">
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>78.76000000000001</v>
+        <v>158.01</v>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
-        <v>-2.52</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SUMIT</t>
+          <t>LPDC</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>38.92</v>
+        <v>6.08</v>
       </c>
       <c r="C93" t="n">
-        <v>39.9</v>
+        <v>6.08</v>
       </c>
       <c r="D93" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="E93" t="b">
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>38.94</v>
+        <v>6.06</v>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
-        <v>-2.41</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DBOL</t>
+          <t>UNIDT</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>101.44</v>
+        <v>174.67</v>
       </c>
       <c r="C94" t="n">
-        <v>103.99</v>
+        <v>174.67</v>
       </c>
       <c r="D94" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="E94" t="b">
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>102.7</v>
+        <v>172.56</v>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>-1.24</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>SAHANA</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>2261.5</v>
+        <v>1008.85</v>
       </c>
       <c r="C95" t="n">
-        <v>2318</v>
+        <v>1008.85</v>
       </c>
       <c r="D95" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="E95" t="b">
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>2299</v>
+        <v>992</v>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>-0.82</v>
+        <v>-1.67</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>TREEHOUSE</t>
+          <t>SGIL</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>10.11</v>
+        <v>522.4</v>
       </c>
       <c r="C96" t="n">
-        <v>10.36</v>
+        <v>522.4</v>
       </c>
       <c r="D96" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="E96" t="b">
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>10.04</v>
+        <v>521.85</v>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>-3.09</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BLUECOAST</t>
+          <t>SAFARI</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>22.31</v>
+        <v>1797.2</v>
       </c>
       <c r="C97" t="n">
-        <v>22.86</v>
+        <v>1797.2</v>
       </c>
       <c r="D97" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="E97" t="b">
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>21.99</v>
+        <v>1781.5</v>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>-3.81</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ICDSLTD</t>
+          <t>ISHAN</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>41.47</v>
+        <v>0.65</v>
       </c>
       <c r="C98" t="n">
-        <v>42.49</v>
+        <v>0.65</v>
       </c>
       <c r="D98" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="E98" t="b">
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>41.01</v>
+        <v>0.6</v>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>-3.48</v>
+        <v>-7.69</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AVROIND</t>
+          <t>TSFINV</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>132.72</v>
+        <v>402.15</v>
       </c>
       <c r="C99" t="n">
-        <v>135.99</v>
+        <v>402.15</v>
       </c>
       <c r="D99" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="E99" t="b">
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>138.56</v>
+        <v>394.1</v>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
-        <v>1.89</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SADBHIN</t>
+          <t>SHRIRAMPPS</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>3.27</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="C100" t="n">
-        <v>3.35</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="D100" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="E100" t="b">
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>3.27</v>
+        <v>78.2</v>
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>-2.39</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>KOTARISUG</t>
+          <t>DELTAMAGNT</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>24.58</v>
+        <v>61.04</v>
       </c>
       <c r="C101" t="n">
-        <v>25.18</v>
+        <v>61.04</v>
       </c>
       <c r="D101" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="E101" t="b">
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>24.93</v>
+        <v>58.41</v>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>-0.99</v>
+        <v>-4.31</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ELDEHSG</t>
+          <t>MITTAL</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>894.35</v>
+        <v>1</v>
       </c>
       <c r="C102" t="n">
-        <v>916</v>
+        <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="E102" t="b">
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>900</v>
+        <v>0.92</v>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>-1.75</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ACEINTEG</t>
+          <t>MADHUCON</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>18.7</v>
+        <v>4.73</v>
       </c>
       <c r="C103" t="n">
-        <v>19.15</v>
+        <v>4.73</v>
       </c>
       <c r="D103" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="E103" t="b">
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>19.14</v>
+        <v>4.63</v>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>-0.05</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MOKSH</t>
+          <t>USK</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>12.53</v>
+        <v>28.67</v>
       </c>
       <c r="C104" t="n">
-        <v>12.83</v>
+        <v>28.67</v>
       </c>
       <c r="D104" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="E104" t="b">
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>12.32</v>
+        <v>27.4</v>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
-        <v>-3.98</v>
+        <v>-4.43</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>VIJIFIN</t>
+          <t>ZENITHSTL</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>2.09</v>
+        <v>5.68</v>
       </c>
       <c r="C105" t="n">
-        <v>2.14</v>
+        <v>5.68</v>
       </c>
       <c r="D105" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="E105" t="b">
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>2.13</v>
+        <v>5.59</v>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>-0.47</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>FEL</t>
+          <t>RUCHINFRA</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.43</v>
+        <v>5.74</v>
       </c>
       <c r="C106" t="n">
-        <v>0.44</v>
+        <v>5.74</v>
       </c>
       <c r="D106" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="E106" t="b">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>0.43</v>
+        <v>5.57</v>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
-        <v>-2.27</v>
+        <v>-2.96</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AKSHAR</t>
+          <t>GOLDTECH</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.43</v>
+        <v>39.8</v>
       </c>
       <c r="C107" t="n">
-        <v>0.44</v>
+        <v>39.8</v>
       </c>
       <c r="D107" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="E107" t="b">
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>0.44</v>
+        <v>39.53</v>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>0</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>NAVKARURB</t>
+          <t>OILCOUNTUB</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1.29</v>
+        <v>47.36</v>
       </c>
       <c r="C108" t="n">
-        <v>1.32</v>
+        <v>47.36</v>
       </c>
       <c r="D108" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="E108" t="b">
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>1.3</v>
+        <v>47.49</v>
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
-        <v>-1.52</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SPORTKING</t>
+          <t>FMNL</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>116.33</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="C109" t="n">
-        <v>119</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D109" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="E109" t="b">
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>116.37</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>-2.21</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="110">
@@ -3276,2386 +3272,2386 @@
         <v>0.87</v>
       </c>
       <c r="C110" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="D110" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="E110" t="b">
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
-        <v>-2.25</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SHIVAMAUTO</t>
+          <t>DICIND</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>20.04</v>
+        <v>526</v>
       </c>
       <c r="C111" t="n">
-        <v>20.5</v>
+        <v>526</v>
       </c>
       <c r="D111" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="E111" t="b">
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>19.62</v>
+        <v>540.05</v>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>-4.29</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>3PLAND</t>
+          <t>AFSL</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>33.68</v>
+        <v>201</v>
       </c>
       <c r="C112" t="n">
-        <v>34.45</v>
+        <v>201</v>
       </c>
       <c r="D112" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="E112" t="b">
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>33.3</v>
+        <v>201.49</v>
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
-        <v>-3.34</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DENORA</t>
+          <t>LYPSAGEMS</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>672.1</v>
+        <v>5.22</v>
       </c>
       <c r="C113" t="n">
-        <v>687.5</v>
+        <v>5.22</v>
       </c>
       <c r="D113" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="E113" t="b">
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>708</v>
+        <v>5.23</v>
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>2.98</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MUNJALSHOW</t>
+          <t>UNIINFO</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>128.9</v>
+        <v>14.04</v>
       </c>
       <c r="C114" t="n">
-        <v>131.8</v>
+        <v>14.04</v>
       </c>
       <c r="D114" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="E114" t="b">
         <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>130</v>
+        <v>13.93</v>
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
-        <v>-1.37</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ESSARSHPNG</t>
+          <t>ANKITMETAL</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>25.91</v>
+        <v>1.66</v>
       </c>
       <c r="C115" t="n">
-        <v>26.49</v>
+        <v>1.66</v>
       </c>
       <c r="D115" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="E115" t="b">
         <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>25.78</v>
+        <v>1.63</v>
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>-2.68</v>
+        <v>-1.81</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>HTMEDIA</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>3697.6</v>
+        <v>21.82</v>
       </c>
       <c r="C116" t="n">
-        <v>3780</v>
+        <v>21.82</v>
       </c>
       <c r="D116" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="E116" t="b">
         <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>3718.7</v>
+        <v>21.47</v>
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
-        <v>-1.62</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BORANA</t>
+          <t>GLOBALVECT</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>402.3</v>
+        <v>163.21</v>
       </c>
       <c r="C117" t="n">
-        <v>411</v>
+        <v>163.21</v>
       </c>
       <c r="D117" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="E117" t="b">
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>401.9</v>
+        <v>159.49</v>
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>-2.21</v>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>FILATFASH</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1361.8</v>
+        <v>0.22</v>
       </c>
       <c r="C118" t="n">
-        <v>1391</v>
+        <v>0.22</v>
       </c>
       <c r="D118" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="E118" t="b">
         <v>0</v>
       </c>
       <c r="F118" t="n">
-        <v>1371.8</v>
+        <v>0.22</v>
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
-        <v>-1.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>PILITA</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>8.48</v>
+        <v>1.01</v>
       </c>
       <c r="C119" t="n">
-        <v>8.66</v>
+        <v>1.01</v>
       </c>
       <c r="D119" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="E119" t="b">
         <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>8.6</v>
+        <v>0.99</v>
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>AARNAV</t>
+          <t>MARUSHIKA</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>27.47</v>
+        <v>103.15</v>
       </c>
       <c r="C120" t="n">
-        <v>28.05</v>
+        <v>103.15</v>
       </c>
       <c r="D120" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="E120" t="b">
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>27.32</v>
+        <v>101</v>
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
-        <v>-2.6</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>GODAVARIB</t>
+          <t>ONECAP-RE</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>283.55</v>
+        <v>0.2</v>
       </c>
       <c r="C121" t="n">
-        <v>289.5</v>
+        <v>0.2</v>
       </c>
       <c r="D121" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="E121" t="b">
         <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>303.7</v>
+        <v>0.18</v>
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
-        <v>4.91</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>JKIPL</t>
+          <t>TECHLABS</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>65.54000000000001</v>
+        <v>195</v>
       </c>
       <c r="C122" t="n">
-        <v>66.90000000000001</v>
+        <v>195</v>
       </c>
       <c r="D122" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="E122" t="b">
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>65.02</v>
+        <v>203</v>
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
-        <v>-2.81</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>INDRAMEDCO</t>
+          <t>SAHAJ</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>401.7</v>
+        <v>4.85</v>
       </c>
       <c r="C123" t="n">
-        <v>410</v>
+        <v>4.85</v>
       </c>
       <c r="D123" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="E123" t="b">
         <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>405.1</v>
+        <v>4.85</v>
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>RAJMET</t>
+          <t>SPCENET</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>3.86</v>
+        <v>5.03</v>
       </c>
       <c r="C124" t="n">
-        <v>3.94</v>
+        <v>5.03</v>
       </c>
       <c r="D124" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="E124" t="b">
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>3.85</v>
+        <v>4.98</v>
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
-        <v>-2.28</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>AHLADA</t>
+          <t>GAYAPROJ</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>45.07</v>
+        <v>12.7</v>
       </c>
       <c r="C125" t="n">
-        <v>46</v>
+        <v>12.7</v>
       </c>
       <c r="D125" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="E125" t="b">
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>45.31</v>
+        <v>12.7</v>
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>VAISHALI</t>
+          <t>VINYLINDIA</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>7.3</v>
+        <v>209.89</v>
       </c>
       <c r="C126" t="n">
-        <v>7.45</v>
+        <v>209.89</v>
       </c>
       <c r="D126" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="E126" t="b">
         <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>7.17</v>
+        <v>207.28</v>
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
-        <v>-3.76</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SHEKHAWATI</t>
+          <t>BHADORA</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>12.72</v>
+        <v>64.45</v>
       </c>
       <c r="C127" t="n">
-        <v>12.98</v>
+        <v>64.45</v>
       </c>
       <c r="D127" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="E127" t="b">
         <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>12.69</v>
+        <v>63</v>
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
-        <v>-2.23</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>THELEELA</t>
+          <t>VIVIMEDLAB</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>441</v>
+        <v>7.57</v>
       </c>
       <c r="C128" t="n">
-        <v>450</v>
+        <v>7.57</v>
       </c>
       <c r="D128" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="E128" t="b">
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>434.55</v>
+        <v>7.26</v>
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
-        <v>-3.43</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>EXXARO</t>
+          <t>GICL</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>7.83</v>
+        <v>48.4</v>
       </c>
       <c r="C129" t="n">
-        <v>7.99</v>
+        <v>48.4</v>
       </c>
       <c r="D129" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="E129" t="b">
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>8.220000000000001</v>
+        <v>48.2</v>
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
-        <v>2.88</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>PREMIERPOL</t>
+          <t>TARAPUR</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>52.43</v>
+        <v>25.34</v>
       </c>
       <c r="C130" t="n">
-        <v>53.49</v>
+        <v>25.34</v>
       </c>
       <c r="D130" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="E130" t="b">
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>52</v>
+        <v>24.52</v>
       </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
-        <v>-2.79</v>
+        <v>-3.24</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CAPACITE</t>
+          <t>DHARAN</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>248.05</v>
+        <v>0.17</v>
       </c>
       <c r="C131" t="n">
-        <v>253</v>
+        <v>0.17</v>
       </c>
       <c r="D131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E131" t="b">
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>246</v>
+        <v>0.18</v>
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
-        <v>-2.77</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>THOMASCOTT</t>
+          <t>ENSER</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>312.75</v>
+        <v>12</v>
       </c>
       <c r="C132" t="n">
-        <v>319</v>
+        <v>12</v>
       </c>
       <c r="D132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E132" t="b">
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>312.2</v>
+        <v>12</v>
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
-        <v>-2.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ROML</t>
+          <t>PRAXIS</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>43.67</v>
+        <v>7.79</v>
       </c>
       <c r="C133" t="n">
-        <v>44.54</v>
+        <v>7.79</v>
       </c>
       <c r="D133" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="E133" t="b">
         <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>43.21</v>
+        <v>7.56</v>
       </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
-        <v>-2.99</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>CIFL</t>
+          <t>FINBUD</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>31.13</v>
+        <v>105</v>
       </c>
       <c r="C134" t="n">
-        <v>31.75</v>
+        <v>105</v>
       </c>
       <c r="D134" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="E134" t="b">
         <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>30.42</v>
+        <v>110.9</v>
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
-        <v>-4.19</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>VIVIMEDLAB</t>
+          <t>UMESLTD</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>7.52</v>
+        <v>4.1</v>
       </c>
       <c r="C135" t="n">
-        <v>7.67</v>
+        <v>4.1</v>
       </c>
       <c r="D135" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="E135" t="b">
         <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>7.67</v>
+        <v>4.02</v>
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
-        <v>0</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>VHL</t>
+          <t>MYMUDRA</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>3332.5</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="C136" t="n">
-        <v>3398.9</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D136" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="E136" t="b">
         <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>3329</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
-        <v>-2.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>LATTEYS</t>
+          <t>SYSTMTXC</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>22.2</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="C137" t="n">
-        <v>22.64</v>
+        <v>75.45</v>
       </c>
       <c r="D137" t="n">
-        <v>1.98</v>
+        <v>-0.01</v>
       </c>
       <c r="E137" t="b">
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>22.15</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
-        <v>-2.16</v>
+        <v>-3.15</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ODIGMA</t>
+          <t>TCC</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>26.24</v>
+        <v>447.1</v>
       </c>
       <c r="C138" t="n">
-        <v>26.76</v>
+        <v>447</v>
       </c>
       <c r="D138" t="n">
-        <v>1.98</v>
+        <v>-0.02</v>
       </c>
       <c r="E138" t="b">
         <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>26</v>
+        <v>435</v>
       </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
-        <v>-2.84</v>
+        <v>-2.68</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>CELEBRITY</t>
+          <t>RVHL</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>8.140000000000001</v>
+        <v>41.51</v>
       </c>
       <c r="C139" t="n">
-        <v>8.300000000000001</v>
+        <v>41.5</v>
       </c>
       <c r="D139" t="n">
-        <v>1.97</v>
+        <v>-0.02</v>
       </c>
       <c r="E139" t="b">
         <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>8.15</v>
+        <v>40.05</v>
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
-        <v>-1.81</v>
+        <v>-3.49</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>BFUTILITIE</t>
+          <t>SMARTWORKS</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>495.15</v>
+        <v>410.05</v>
       </c>
       <c r="C140" t="n">
-        <v>504.9</v>
+        <v>409.9</v>
       </c>
       <c r="D140" t="n">
-        <v>1.97</v>
+        <v>-0.04</v>
       </c>
       <c r="E140" t="b">
         <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>505</v>
+        <v>396.45</v>
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
-        <v>0.02</v>
+        <v>-3.28</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>CEINSYS</t>
+          <t>DPABHUSHAN</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>987.8</v>
+        <v>1186.2</v>
       </c>
       <c r="C141" t="n">
-        <v>1007</v>
+        <v>1185.7</v>
       </c>
       <c r="D141" t="n">
-        <v>1.94</v>
+        <v>-0.04</v>
       </c>
       <c r="E141" t="b">
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>979.5</v>
+        <v>1158.6</v>
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
-        <v>-2.73</v>
+        <v>-2.29</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>TPLPLASTEH</t>
+          <t>CAPITALSFB</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>68.43000000000001</v>
+        <v>262.1</v>
       </c>
       <c r="C142" t="n">
-        <v>69.75</v>
+        <v>262</v>
       </c>
       <c r="D142" t="n">
-        <v>1.93</v>
+        <v>-0.04</v>
       </c>
       <c r="E142" t="b">
         <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>68.12</v>
+        <v>262.8</v>
       </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
-        <v>-2.34</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>LYPSAGEMS</t>
+          <t>STANLEY</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>5.21</v>
+        <v>162.07</v>
       </c>
       <c r="C143" t="n">
-        <v>5.31</v>
+        <v>162</v>
       </c>
       <c r="D143" t="n">
-        <v>1.92</v>
+        <v>-0.04</v>
       </c>
       <c r="E143" t="b">
         <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>5.18</v>
+        <v>158.2</v>
       </c>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
-        <v>-2.45</v>
+        <v>-2.35</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>STEELXIND</t>
+          <t>RKDL</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>8.33</v>
+        <v>19.09</v>
       </c>
       <c r="C144" t="n">
-        <v>8.49</v>
+        <v>19.08</v>
       </c>
       <c r="D144" t="n">
-        <v>1.92</v>
+        <v>-0.05</v>
       </c>
       <c r="E144" t="b">
         <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>8.69</v>
+        <v>18.93</v>
       </c>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
-        <v>2.36</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>LTM</t>
+          <t>JINDRILL</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>4504</v>
+        <v>445.3</v>
       </c>
       <c r="C145" t="n">
-        <v>4590</v>
+        <v>445.05</v>
       </c>
       <c r="D145" t="n">
-        <v>1.91</v>
+        <v>-0.06</v>
       </c>
       <c r="E145" t="b">
         <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>4545</v>
+        <v>477.4</v>
       </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
-        <v>-0.98</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SANGINITA</t>
+          <t>SGL</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>14.96</v>
+        <v>12.58</v>
       </c>
       <c r="C146" t="n">
-        <v>15.24</v>
+        <v>12.57</v>
       </c>
       <c r="D146" t="n">
-        <v>1.87</v>
+        <v>-0.08</v>
       </c>
       <c r="E146" t="b">
         <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>14.24</v>
+        <v>11.69</v>
       </c>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
-        <v>-6.56</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>PLAZACABLE</t>
+          <t>KRISHIVAL</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>37.99</v>
+        <v>313.25</v>
       </c>
       <c r="C147" t="n">
-        <v>38.7</v>
+        <v>313</v>
       </c>
       <c r="D147" t="n">
-        <v>1.87</v>
+        <v>-0.08</v>
       </c>
       <c r="E147" t="b">
         <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>38.12</v>
+        <v>315</v>
       </c>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
-        <v>-1.5</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ORICONENT</t>
+          <t>VINEETLAB</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>67.75</v>
+        <v>29.53</v>
       </c>
       <c r="C148" t="n">
-        <v>69</v>
+        <v>29.5</v>
       </c>
       <c r="D148" t="n">
-        <v>1.85</v>
+        <v>-0.1</v>
       </c>
       <c r="E148" t="b">
         <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>67.98</v>
+        <v>30</v>
       </c>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
-        <v>-1.48</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SIGIND</t>
+          <t>RAMANEWS</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>46.15</v>
+        <v>35.54</v>
       </c>
       <c r="C149" t="n">
-        <v>47</v>
+        <v>35.5</v>
       </c>
       <c r="D149" t="n">
-        <v>1.84</v>
+        <v>-0.11</v>
       </c>
       <c r="E149" t="b">
         <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>46.4</v>
+        <v>34.21</v>
       </c>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
-        <v>-1.28</v>
+        <v>-3.63</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>CAPTRUST</t>
+          <t>DGCONTENT</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>13.12</v>
+        <v>27.68</v>
       </c>
       <c r="C150" t="n">
-        <v>13.36</v>
+        <v>27.65</v>
       </c>
       <c r="D150" t="n">
-        <v>1.83</v>
+        <v>-0.11</v>
       </c>
       <c r="E150" t="b">
         <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>12.56</v>
+        <v>28</v>
       </c>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
-        <v>-5.99</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>PARASPETRO</t>
+          <t>PREMEXPLN</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>2.23</v>
+        <v>537.65</v>
       </c>
       <c r="C151" t="n">
-        <v>2.27</v>
+        <v>537</v>
       </c>
       <c r="D151" t="n">
-        <v>1.79</v>
+        <v>-0.12</v>
       </c>
       <c r="E151" t="b">
         <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>2.22</v>
+        <v>543.95</v>
       </c>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
-        <v>-2.2</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>VIVIDHA</t>
+          <t>SHANTIGEAR</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5600000000000001</v>
+        <v>450.1</v>
       </c>
       <c r="C152" t="n">
-        <v>0.57</v>
+        <v>449.5</v>
       </c>
       <c r="D152" t="n">
-        <v>1.79</v>
+        <v>-0.13</v>
       </c>
       <c r="E152" t="b">
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>0.55</v>
+        <v>451.4</v>
       </c>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="n">
-        <v>-3.51</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>ANANTAM</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>1373.5</v>
+        <v>102.53</v>
       </c>
       <c r="C153" t="n">
-        <v>1398</v>
+        <v>102.4</v>
       </c>
       <c r="D153" t="n">
-        <v>1.78</v>
+        <v>-0.13</v>
       </c>
       <c r="E153" t="b">
         <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>1392.4</v>
+        <v>102.75</v>
       </c>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="n">
-        <v>-0.4</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ANSALAPI</t>
+          <t>BALAJITELE</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>3.93</v>
+        <v>108.14</v>
       </c>
       <c r="C154" t="n">
-        <v>4</v>
+        <v>108</v>
       </c>
       <c r="D154" t="n">
-        <v>1.78</v>
+        <v>-0.13</v>
       </c>
       <c r="E154" t="b">
         <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>4</v>
+        <v>101.54</v>
       </c>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="n">
-        <v>0</v>
+        <v>-5.98</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>RAJRILTD</t>
+          <t>GSS</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>22.49</v>
+        <v>13.49</v>
       </c>
       <c r="C155" t="n">
-        <v>22.89</v>
+        <v>13.47</v>
       </c>
       <c r="D155" t="n">
-        <v>1.78</v>
+        <v>-0.15</v>
       </c>
       <c r="E155" t="b">
         <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>22.93</v>
+        <v>13.54</v>
       </c>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="n">
-        <v>0.17</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SBGLP</t>
+          <t>AKSHOPTFBR</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>29.32</v>
+        <v>4.86</v>
       </c>
       <c r="C156" t="n">
-        <v>29.84</v>
+        <v>4.85</v>
       </c>
       <c r="D156" t="n">
-        <v>1.77</v>
+        <v>-0.21</v>
       </c>
       <c r="E156" t="b">
         <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>29.44</v>
+        <v>4.75</v>
       </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="n">
-        <v>-1.34</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>KAJARIACER</t>
+          <t>TIJARIA</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>962.3</v>
+        <v>4.62</v>
       </c>
       <c r="C157" t="n">
-        <v>979.35</v>
+        <v>4.61</v>
       </c>
       <c r="D157" t="n">
-        <v>1.77</v>
+        <v>-0.22</v>
       </c>
       <c r="E157" t="b">
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>969.7</v>
+        <v>4.58</v>
       </c>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="n">
-        <v>-0.99</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>KWIL</t>
+          <t>NIRAJISPAT</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>25.94</v>
+        <v>284.73</v>
       </c>
       <c r="C158" t="n">
-        <v>26.39</v>
+        <v>284</v>
       </c>
       <c r="D158" t="n">
-        <v>1.73</v>
+        <v>-0.26</v>
       </c>
       <c r="E158" t="b">
         <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>26.15</v>
+        <v>270.6</v>
       </c>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="n">
-        <v>-0.91</v>
+        <v>-4.72</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>SAMBHAAV</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>14.99</v>
+        <v>7.51</v>
       </c>
       <c r="C159" t="n">
-        <v>15.25</v>
+        <v>7.49</v>
       </c>
       <c r="D159" t="n">
-        <v>1.73</v>
+        <v>-0.27</v>
       </c>
       <c r="E159" t="b">
         <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>14.72</v>
+        <v>7.14</v>
       </c>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="n">
-        <v>-3.48</v>
+        <v>-4.67</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>VISHWARAJ</t>
+          <t>PARAS</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>5.78</v>
+        <v>637.8</v>
       </c>
       <c r="C160" t="n">
-        <v>5.88</v>
+        <v>636</v>
       </c>
       <c r="D160" t="n">
-        <v>1.73</v>
+        <v>-0.28</v>
       </c>
       <c r="E160" t="b">
         <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>5.84</v>
+        <v>716.9</v>
       </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="n">
-        <v>-0.68</v>
+        <v>12.72</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>TPHQ</t>
+          <t>AGARIND</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.58</v>
+        <v>551</v>
       </c>
       <c r="C161" t="n">
-        <v>0.59</v>
+        <v>549.4</v>
       </c>
       <c r="D161" t="n">
-        <v>1.72</v>
+        <v>-0.29</v>
       </c>
       <c r="E161" t="b">
         <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>0.58</v>
+        <v>536</v>
       </c>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="n">
-        <v>-1.69</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>TIMETECHNO</t>
+          <t>GRMOVER</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>187.65</v>
+        <v>160.67</v>
       </c>
       <c r="C162" t="n">
-        <v>190.85</v>
+        <v>160.2</v>
       </c>
       <c r="D162" t="n">
-        <v>1.71</v>
+        <v>-0.29</v>
       </c>
       <c r="E162" t="b">
         <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>184.35</v>
+        <v>159.31</v>
       </c>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="n">
-        <v>-3.41</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>NIBL</t>
+          <t>SWARAJ</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>31.75</v>
+        <v>303.25</v>
       </c>
       <c r="C163" t="n">
-        <v>32.29</v>
+        <v>302.25</v>
       </c>
       <c r="D163" t="n">
-        <v>1.7</v>
+        <v>-0.33</v>
       </c>
       <c r="E163" t="b">
         <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>32.27</v>
+        <v>301.6</v>
       </c>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="n">
-        <v>-0.06</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>TEXINFRA</t>
+          <t>SUVIDHAA</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>95.18000000000001</v>
+        <v>3</v>
       </c>
       <c r="C164" t="n">
-        <v>96.8</v>
+        <v>2.99</v>
       </c>
       <c r="D164" t="n">
-        <v>1.7</v>
+        <v>-0.33</v>
       </c>
       <c r="E164" t="b">
         <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>93.86</v>
+        <v>2.97</v>
       </c>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="n">
-        <v>-3.04</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>LORDSCHLO</t>
+          <t>ELLEN</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>127.86</v>
+        <v>229.25</v>
       </c>
       <c r="C165" t="n">
-        <v>130</v>
+        <v>228.49</v>
       </c>
       <c r="D165" t="n">
-        <v>1.67</v>
+        <v>-0.33</v>
       </c>
       <c r="E165" t="b">
         <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>124.83</v>
+        <v>226.62</v>
       </c>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="n">
-        <v>-3.98</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>GUJTHEM</t>
+          <t>FLEXITUFF</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>313.2</v>
+        <v>8.73</v>
       </c>
       <c r="C166" t="n">
-        <v>318.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D166" t="n">
-        <v>1.66</v>
+        <v>-0.34</v>
       </c>
       <c r="E166" t="b">
         <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>305</v>
+        <v>8.5</v>
       </c>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="n">
-        <v>-4.21</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ZENITHSTL</t>
+          <t>DENORA</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>5.41</v>
+        <v>703.55</v>
       </c>
       <c r="C167" t="n">
-        <v>5.5</v>
+        <v>701.1</v>
       </c>
       <c r="D167" t="n">
-        <v>1.66</v>
+        <v>-0.35</v>
       </c>
       <c r="E167" t="b">
         <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>5.68</v>
+        <v>684.05</v>
       </c>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="n">
-        <v>3.27</v>
+        <v>-2.43</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>BSL</t>
+          <t>CROWN</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>130.69</v>
+        <v>120.44</v>
       </c>
       <c r="C168" t="n">
-        <v>132.85</v>
+        <v>120</v>
       </c>
       <c r="D168" t="n">
-        <v>1.65</v>
+        <v>-0.37</v>
       </c>
       <c r="E168" t="b">
         <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>129.02</v>
+        <v>116.99</v>
       </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="n">
-        <v>-2.88</v>
+        <v>-2.51</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>21STCENMGM</t>
+          <t>KOKUYOCMLN</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>36.49</v>
+        <v>82.31</v>
       </c>
       <c r="C169" t="n">
-        <v>37.09</v>
+        <v>82</v>
       </c>
       <c r="D169" t="n">
-        <v>1.64</v>
+        <v>-0.38</v>
       </c>
       <c r="E169" t="b">
         <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>36.99</v>
+        <v>80.75</v>
       </c>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="n">
-        <v>-0.27</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>AVONMORE</t>
+          <t>INDUSINVIT</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>14.76</v>
+        <v>124.8</v>
       </c>
       <c r="C170" t="n">
-        <v>15</v>
+        <v>124.3</v>
       </c>
       <c r="D170" t="n">
-        <v>1.63</v>
+        <v>-0.4</v>
       </c>
       <c r="E170" t="b">
         <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>14.99</v>
+        <v>124.75</v>
       </c>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>KNAGRI</t>
+          <t>NIPPOBATRY</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>171.21</v>
+        <v>336.45</v>
       </c>
       <c r="C171" t="n">
-        <v>174</v>
+        <v>335.1</v>
       </c>
       <c r="D171" t="n">
-        <v>1.63</v>
+        <v>-0.4</v>
       </c>
       <c r="E171" t="b">
         <v>0</v>
       </c>
       <c r="F171" t="n">
-        <v>179.77</v>
+        <v>319</v>
       </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="n">
-        <v>3.32</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ORIENTBELL</t>
+          <t>AHLADA</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>308.95</v>
+        <v>45.15</v>
       </c>
       <c r="C172" t="n">
-        <v>314</v>
+        <v>44.97</v>
       </c>
       <c r="D172" t="n">
-        <v>1.63</v>
+        <v>-0.4</v>
       </c>
       <c r="E172" t="b">
         <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>305.55</v>
+        <v>44.05</v>
       </c>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="n">
-        <v>-2.69</v>
+        <v>-2.05</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>GVPTECH</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>437.9</v>
+        <v>6.98</v>
       </c>
       <c r="C173" t="n">
-        <v>444.95</v>
+        <v>6.95</v>
       </c>
       <c r="D173" t="n">
-        <v>1.61</v>
+        <v>-0.43</v>
       </c>
       <c r="E173" t="b">
         <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>430</v>
+        <v>6.87</v>
       </c>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="n">
-        <v>-3.36</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>LYKALABS</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>6.89</v>
+        <v>62.35</v>
       </c>
       <c r="C174" t="n">
-        <v>7</v>
+        <v>62.08</v>
       </c>
       <c r="D174" t="n">
-        <v>1.6</v>
+        <v>-0.43</v>
       </c>
       <c r="E174" t="b">
         <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>6.95</v>
+        <v>61.73</v>
       </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="n">
-        <v>-0.71</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ARCHIES</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>15.62</v>
+        <v>2037.2</v>
       </c>
       <c r="C175" t="n">
-        <v>15.87</v>
+        <v>2028</v>
       </c>
       <c r="D175" t="n">
-        <v>1.6</v>
+        <v>-0.45</v>
       </c>
       <c r="E175" t="b">
         <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>15.5</v>
+        <v>2002.7</v>
       </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="n">
-        <v>-2.33</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>KCPSUGIND</t>
+          <t>EDELWEISS</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>22.58</v>
+        <v>114.42</v>
       </c>
       <c r="C176" t="n">
-        <v>22.94</v>
+        <v>113.9</v>
       </c>
       <c r="D176" t="n">
-        <v>1.59</v>
+        <v>-0.45</v>
       </c>
       <c r="E176" t="b">
         <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>23.02</v>
+        <v>114.35</v>
       </c>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>KMSUGAR</t>
+          <t>AKASH</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>24.58</v>
+        <v>26.12</v>
       </c>
       <c r="C177" t="n">
-        <v>24.97</v>
+        <v>26</v>
       </c>
       <c r="D177" t="n">
-        <v>1.59</v>
+        <v>-0.46</v>
       </c>
       <c r="E177" t="b">
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>25</v>
+        <v>25.3</v>
       </c>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="n">
-        <v>0.12</v>
+        <v>-2.69</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>CYBERTECH</t>
+          <t>SELMC</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>116.18</v>
+        <v>29.93</v>
       </c>
       <c r="C178" t="n">
-        <v>118</v>
+        <v>29.79</v>
       </c>
       <c r="D178" t="n">
-        <v>1.57</v>
+        <v>-0.47</v>
       </c>
       <c r="E178" t="b">
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>115.08</v>
+        <v>29.45</v>
       </c>
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="n">
-        <v>-2.47</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ASAHISONG</t>
+          <t>MEDIASSIST</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>215.23</v>
+        <v>370.7</v>
       </c>
       <c r="C179" t="n">
-        <v>218.6</v>
+        <v>368.95</v>
       </c>
       <c r="D179" t="n">
-        <v>1.57</v>
+        <v>-0.47</v>
       </c>
       <c r="E179" t="b">
         <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>212.34</v>
+        <v>358.1</v>
       </c>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="n">
-        <v>-2.86</v>
+        <v>-2.94</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>GTL</t>
+          <t>BIRLANU</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>7.04</v>
+        <v>1507.5</v>
       </c>
       <c r="C180" t="n">
-        <v>7.15</v>
+        <v>1500.1</v>
       </c>
       <c r="D180" t="n">
-        <v>1.56</v>
+        <v>-0.49</v>
       </c>
       <c r="E180" t="b">
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>7.07</v>
+        <v>1491.9</v>
       </c>
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="n">
-        <v>-1.12</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>LINC</t>
+          <t>RKEC</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>108.31</v>
+        <v>43.15</v>
       </c>
       <c r="C181" t="n">
-        <v>110</v>
+        <v>42.94</v>
       </c>
       <c r="D181" t="n">
-        <v>1.56</v>
+        <v>-0.49</v>
       </c>
       <c r="E181" t="b">
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>107.99</v>
+        <v>42.21</v>
       </c>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="n">
-        <v>-1.83</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>IZMO</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>772</v>
+        <v>566.3</v>
       </c>
       <c r="C182" t="n">
-        <v>784</v>
+        <v>563.5</v>
       </c>
       <c r="D182" t="n">
-        <v>1.55</v>
+        <v>-0.49</v>
       </c>
       <c r="E182" t="b">
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>769.9</v>
+        <v>579.85</v>
       </c>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="n">
-        <v>-1.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>MGEL</t>
+          <t>TRANSWORLD</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>11.01</v>
+        <v>139.17</v>
       </c>
       <c r="C183" t="n">
-        <v>11.18</v>
+        <v>138.48</v>
       </c>
       <c r="D183" t="n">
-        <v>1.54</v>
+        <v>-0.5</v>
       </c>
       <c r="E183" t="b">
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>11.1</v>
+        <v>135.5</v>
       </c>
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="n">
-        <v>-0.72</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>TIRUPATIFL</t>
+          <t>KABRAEXTRU</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>36.93</v>
+        <v>256.1</v>
       </c>
       <c r="C184" t="n">
-        <v>37.5</v>
+        <v>254.8</v>
       </c>
       <c r="D184" t="n">
-        <v>1.54</v>
+        <v>-0.51</v>
       </c>
       <c r="E184" t="b">
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>36.87</v>
+        <v>251.15</v>
       </c>
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="n">
-        <v>-1.68</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>NETWORK18</t>
+          <t>WELINV</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>33.39</v>
+        <v>1281.4</v>
       </c>
       <c r="C185" t="n">
-        <v>33.9</v>
+        <v>1274.7</v>
       </c>
       <c r="D185" t="n">
-        <v>1.53</v>
+        <v>-0.52</v>
       </c>
       <c r="E185" t="b">
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>33.42</v>
+        <v>1276.4</v>
       </c>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="n">
-        <v>-1.42</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>KEEPLEARN</t>
+          <t>NOIDATOLL</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>1.97</v>
+        <v>3.74</v>
       </c>
       <c r="C186" t="n">
-        <v>2</v>
+        <v>3.72</v>
       </c>
       <c r="D186" t="n">
-        <v>1.52</v>
+        <v>-0.53</v>
       </c>
       <c r="E186" t="b">
         <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>2</v>
+        <v>3.76</v>
       </c>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>AYMSYNTEX</t>
+          <t>ICDSLTD</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>199.27</v>
+        <v>41.1</v>
       </c>
       <c r="C187" t="n">
-        <v>202.3</v>
+        <v>40.88</v>
       </c>
       <c r="D187" t="n">
-        <v>1.52</v>
+        <v>-0.54</v>
       </c>
       <c r="E187" t="b">
         <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>197.29</v>
+        <v>40.5</v>
       </c>
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="n">
-        <v>-2.48</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>AKI</t>
+          <t>LGHL</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>5.27</v>
+        <v>286.95</v>
       </c>
       <c r="C188" t="n">
-        <v>5.35</v>
+        <v>285.4</v>
       </c>
       <c r="D188" t="n">
-        <v>1.52</v>
+        <v>-0.54</v>
       </c>
       <c r="E188" t="b">
         <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>5.15</v>
+        <v>277</v>
       </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="n">
-        <v>-3.74</v>
+        <v>-2.94</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>BASML</t>
+          <t>UCAL</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>23.04</v>
+        <v>108.59</v>
       </c>
       <c r="C189" t="n">
-        <v>23.39</v>
+        <v>108</v>
       </c>
       <c r="D189" t="n">
-        <v>1.52</v>
+        <v>-0.54</v>
       </c>
       <c r="E189" t="b">
         <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>23.11</v>
+        <v>106.73</v>
       </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="n">
-        <v>-1.2</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>RADHIKAJWE</t>
+          <t>ICRA</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>66.34</v>
+        <v>5531</v>
       </c>
       <c r="C190" t="n">
-        <v>67.34999999999999</v>
+        <v>5500</v>
       </c>
       <c r="D190" t="n">
-        <v>1.52</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E190" t="b">
         <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>65.79000000000001</v>
+        <v>5534.5</v>
       </c>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="n">
-        <v>-2.32</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>LIKHITHA</t>
+          <t>CCCL</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>151.81</v>
+        <v>15.99</v>
       </c>
       <c r="C191" t="n">
-        <v>154.1</v>
+        <v>15.9</v>
       </c>
       <c r="D191" t="n">
-        <v>1.51</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E191" t="b">
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>151.5</v>
+        <v>16.39</v>
       </c>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="n">
-        <v>-1.69</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>GKSL</t>
+          <t>ALLETEC</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>111.17</v>
+        <v>157.4</v>
       </c>
       <c r="C192" t="n">
-        <v>112.85</v>
+        <v>156.5</v>
       </c>
       <c r="D192" t="n">
-        <v>1.51</v>
+        <v>-0.57</v>
       </c>
       <c r="E192" t="b">
         <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>114.31</v>
+        <v>153.95</v>
       </c>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="n">
-        <v>1.29</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>LGHL</t>
+          <t>IRBINVIT</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>285.65</v>
+        <v>61.86</v>
       </c>
       <c r="C193" t="n">
-        <v>289.95</v>
+        <v>61.5</v>
       </c>
       <c r="D193" t="n">
-        <v>1.51</v>
+        <v>-0.58</v>
       </c>
       <c r="E193" t="b">
         <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>282.45</v>
+        <v>61.67</v>
       </c>
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="n">
-        <v>-2.59</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>BLUSPRING</t>
+          <t>SAILIFE</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>52.9</v>
+        <v>998.25</v>
       </c>
       <c r="C194" t="n">
-        <v>53.7</v>
+        <v>992.5</v>
       </c>
       <c r="D194" t="n">
-        <v>1.51</v>
+        <v>-0.58</v>
       </c>
       <c r="E194" t="b">
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>52.12</v>
+        <v>1000.9</v>
       </c>
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="n">
-        <v>-2.94</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>DIFFNKG</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>265.74</v>
+        <v>444.7</v>
       </c>
       <c r="C195" t="n">
-        <v>269.75</v>
+        <v>442.1</v>
       </c>
       <c r="D195" t="n">
-        <v>1.51</v>
+        <v>-0.58</v>
       </c>
       <c r="E195" t="b">
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>271.79</v>
+        <v>453.75</v>
       </c>
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="n">
-        <v>0.76</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>NELCAST</t>
+          <t>BALKRISHNA</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>111.56</v>
+        <v>16.82</v>
       </c>
       <c r="C196" t="n">
-        <v>113.25</v>
+        <v>16.72</v>
       </c>
       <c r="D196" t="n">
-        <v>1.51</v>
+        <v>-0.59</v>
       </c>
       <c r="E196" t="b">
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>110.48</v>
+        <v>16.1</v>
       </c>
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="n">
-        <v>-2.45</v>
+        <v>-3.71</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>UNIPARTS</t>
+          <t>FOODSIN</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>465.95</v>
+        <v>58.3</v>
       </c>
       <c r="C197" t="n">
-        <v>473</v>
+        <v>57.95</v>
       </c>
       <c r="D197" t="n">
-        <v>1.51</v>
+        <v>-0.6</v>
       </c>
       <c r="E197" t="b">
         <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>462.6</v>
+        <v>57.26</v>
       </c>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="n">
-        <v>-2.2</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>BAJAJHCARE</t>
+          <t>CAPINVIT</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>331.8</v>
+        <v>70</v>
       </c>
       <c r="C198" t="n">
-        <v>336.8</v>
+        <v>69.58</v>
       </c>
       <c r="D198" t="n">
-        <v>1.51</v>
+        <v>-0.6</v>
       </c>
       <c r="E198" t="b">
         <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>330.75</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="n">
-        <v>-1.8</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SUNDROP</t>
+          <t>NAGREEKEXP</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>655.25</v>
+        <v>25.2</v>
       </c>
       <c r="C199" t="n">
-        <v>665.1</v>
+        <v>25.05</v>
       </c>
       <c r="D199" t="n">
-        <v>1.5</v>
+        <v>-0.6</v>
       </c>
       <c r="E199" t="b">
         <v>0</v>
       </c>
       <c r="F199" t="n">
-        <v>653.9</v>
+        <v>24.5</v>
       </c>
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="n">
-        <v>-1.68</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>XELPMOC</t>
+          <t>DEEPINDS</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>133</v>
+        <v>347.1</v>
       </c>
       <c r="C200" t="n">
-        <v>135</v>
+        <v>345</v>
       </c>
       <c r="D200" t="n">
-        <v>1.5</v>
+        <v>-0.61</v>
       </c>
       <c r="E200" t="b">
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>132.26</v>
+        <v>364.2</v>
       </c>
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="n">
-        <v>-2.03</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>DODLA</t>
+          <t>TAINWALCHM</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>1156.6</v>
+        <v>209.18</v>
       </c>
       <c r="C201" t="n">
-        <v>1173.9</v>
+        <v>207.9</v>
       </c>
       <c r="D201" t="n">
-        <v>1.5</v>
+        <v>-0.61</v>
       </c>
       <c r="E201" t="b">
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>1158.9</v>
+        <v>199.01</v>
       </c>
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="n">
-        <v>-1.28</v>
+        <v>-4.28</v>
       </c>
     </row>
   </sheetData>

--- a/data/trending_momentum_stocks.xlsx
+++ b/data/trending_momentum_stocks.xlsx
@@ -503,11 +503,11 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>45.19</v>
+        <v>43.98</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>-5.26</v>
+        <v>-7.8</v>
       </c>
     </row>
     <row r="4">
@@ -529,11 +529,11 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>4.15</v>
+        <v>4.18</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>-11.7</v>
+        <v>-11.06</v>
       </c>
     </row>
     <row r="5">
@@ -555,11 +555,11 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>32.3</v>
+        <v>31.4</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>-7.42</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="6">
@@ -581,11 +581,11 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>-4.67</v>
+        <v>-5.61</v>
       </c>
     </row>
     <row r="7">
@@ -607,11 +607,11 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>-7.48</v>
+        <v>-8.84</v>
       </c>
     </row>
     <row r="8">
@@ -633,11 +633,11 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>63.01</v>
+        <v>62.13</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>-5.94</v>
+        <v>-7.25</v>
       </c>
     </row>
     <row r="9">
@@ -659,24 +659,24 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>321.55</v>
+        <v>312.05</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>-5.43</v>
+        <v>-8.220000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NEUEON</t>
+          <t>SETUINFRA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10.8</v>
+        <v>0.4</v>
       </c>
       <c r="C10" t="n">
-        <v>11.34</v>
+        <v>0.42</v>
       </c>
       <c r="D10" t="n">
         <v>5</v>
@@ -685,7 +685,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>11.34</v>
+        <v>0.42</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
@@ -695,14 +695,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SETUINFRA</t>
+          <t>NEUEON</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4</v>
+        <v>10.8</v>
       </c>
       <c r="C11" t="n">
-        <v>0.42</v>
+        <v>11.34</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -711,7 +711,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.42</v>
+        <v>11.34</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
@@ -737,24 +737,24 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>23.9</v>
+        <v>24.77</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>-7.69</v>
+        <v>-4.33</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ROLLT</t>
+          <t>SETCO</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.41</v>
+        <v>16.92</v>
       </c>
       <c r="C13" t="n">
-        <v>1.48</v>
+        <v>17.76</v>
       </c>
       <c r="D13" t="n">
         <v>4.96</v>
@@ -763,7 +763,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1.48</v>
+        <v>17.76</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
@@ -773,14 +773,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SETCO</t>
+          <t>EUROTEXIND</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16.92</v>
+        <v>12.91</v>
       </c>
       <c r="C14" t="n">
-        <v>17.76</v>
+        <v>13.55</v>
       </c>
       <c r="D14" t="n">
         <v>4.96</v>
@@ -789,24 +789,24 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>17.76</v>
+        <v>13</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-4.06</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EUROTEXIND</t>
+          <t>ROLLT</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12.91</v>
+        <v>1.41</v>
       </c>
       <c r="C15" t="n">
-        <v>13.55</v>
+        <v>1.48</v>
       </c>
       <c r="D15" t="n">
         <v>4.96</v>
@@ -815,11 +815,11 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>13.4</v>
+        <v>1.35</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>-1.11</v>
+        <v>-8.779999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -841,11 +841,11 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>70.95999999999999</v>
+        <v>71.16</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>-8.5</v>
+        <v>-8.24</v>
       </c>
     </row>
     <row r="17">
@@ -867,11 +867,11 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>33.52</v>
+        <v>32.34</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>-1.82</v>
+        <v>-5.27</v>
       </c>
     </row>
     <row r="18">
@@ -893,11 +893,11 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>6.42</v>
+        <v>6.39</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>-8.15</v>
+        <v>-8.58</v>
       </c>
     </row>
     <row r="19">
@@ -945,24 +945,24 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BLUECOAST</t>
+          <t>DHARIWAL</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21.33</v>
+        <v>41.8</v>
       </c>
       <c r="C21" t="n">
-        <v>22.3</v>
+        <v>43.7</v>
       </c>
       <c r="D21" t="n">
         <v>4.55</v>
@@ -971,24 +971,24 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>21.21</v>
+        <v>43.85</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>-4.89</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DHARIWAL</t>
+          <t>BLUECOAST</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>41.8</v>
+        <v>21.33</v>
       </c>
       <c r="C22" t="n">
-        <v>43.7</v>
+        <v>22.3</v>
       </c>
       <c r="D22" t="n">
         <v>4.55</v>
@@ -997,11 +997,11 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>43.85</v>
+        <v>20.27</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.34</v>
+        <v>-9.1</v>
       </c>
     </row>
     <row r="23">
@@ -1023,11 +1023,11 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>479</v>
+        <v>484.7</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>-4.77</v>
+        <v>-3.64</v>
       </c>
     </row>
     <row r="24">
@@ -1049,11 +1049,11 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>-5.74</v>
+        <v>-4.92</v>
       </c>
     </row>
     <row r="25">
@@ -1075,11 +1075,11 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>19.39</v>
+        <v>19.37</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>-2.56</v>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="26">
@@ -1101,11 +1101,11 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>116.75</v>
+        <v>117.1</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>-5</v>
+        <v>-4.72</v>
       </c>
     </row>
     <row r="27">
@@ -1127,11 +1127,11 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>6.88</v>
+        <v>6.72</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>-4.31</v>
+        <v>-6.54</v>
       </c>
     </row>
     <row r="28">
@@ -1153,11 +1153,11 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>16.08</v>
+        <v>16.05</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>-0.06</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="29">
@@ -1179,24 +1179,24 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>279.85</v>
+        <v>281.45</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>-2.83</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GJL</t>
+          <t>GPECO</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>163.4</v>
+        <v>355</v>
       </c>
       <c r="C30" t="n">
-        <v>168</v>
+        <v>365</v>
       </c>
       <c r="D30" t="n">
         <v>2.82</v>
@@ -1205,24 +1205,24 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>171.55</v>
+        <v>331</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>2.11</v>
+        <v>-9.32</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GPECO</t>
+          <t>GJL</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>355</v>
+        <v>163.4</v>
       </c>
       <c r="C31" t="n">
-        <v>365</v>
+        <v>168</v>
       </c>
       <c r="D31" t="n">
         <v>2.82</v>
@@ -1231,11 +1231,11 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>339</v>
+        <v>171.55</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>-7.12</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="32">
@@ -1257,11 +1257,11 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>58.01</v>
+        <v>55.26</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>-3.32</v>
+        <v>-7.9</v>
       </c>
     </row>
     <row r="33">
@@ -1309,11 +1309,11 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>56.8</v>
+        <v>56.02</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>-3.71</v>
+        <v>-5.03</v>
       </c>
     </row>
     <row r="35">
@@ -1335,11 +1335,11 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="36">
@@ -1361,11 +1361,11 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>16.42</v>
+        <v>15.42</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>-3.13</v>
+        <v>-9.029999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -1387,11 +1387,11 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>167.64</v>
+        <v>166.3</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>-2.53</v>
+        <v>-3.31</v>
       </c>
     </row>
     <row r="38">
@@ -1413,11 +1413,11 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>-1.93</v>
+        <v>-3.94</v>
       </c>
     </row>
     <row r="39">
@@ -1465,11 +1465,11 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>-1.78</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="41">
@@ -1491,11 +1491,11 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>108</v>
+        <v>108.29</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="42">
@@ -1517,11 +1517,11 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>136.77</v>
+        <v>136.79</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="43">
@@ -1543,11 +1543,11 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>-1.01</v>
+        <v>-2.01</v>
       </c>
     </row>
     <row r="44">
@@ -1569,11 +1569,11 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>29.2</v>
+        <v>28.5</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>-4.11</v>
+        <v>-6.4</v>
       </c>
     </row>
     <row r="45">
@@ -1621,11 +1621,11 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>184.5</v>
+        <v>183</v>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>-0.22</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="47">
@@ -1647,11 +1647,11 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>5.15</v>
+        <v>5.21</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>2.18</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="48">
@@ -1673,11 +1673,11 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>18.98</v>
+        <v>19</v>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>-5.1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="49">
@@ -1721,11 +1721,11 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>64.5</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>-3.44</v>
+        <v>-4.04</v>
       </c>
     </row>
     <row r="51">
@@ -1747,11 +1747,11 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>89.90000000000001</v>
+        <v>89</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>-1.75</v>
+        <v>-2.73</v>
       </c>
     </row>
     <row r="52">
@@ -1773,11 +1773,11 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>4946.5</v>
+        <v>4980.1</v>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>-0.05</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="53">
@@ -1799,11 +1799,11 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>45.3</v>
+        <v>44.8</v>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>-6.98</v>
+        <v>-8.01</v>
       </c>
     </row>
     <row r="54">
@@ -1825,11 +1825,11 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>17.11</v>
+        <v>17.1</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>-4.41</v>
+        <v>-4.47</v>
       </c>
     </row>
     <row r="55">
@@ -1851,11 +1851,11 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>25.4</v>
+        <v>24.75</v>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>-2.27</v>
+        <v>-4.77</v>
       </c>
     </row>
     <row r="56">
@@ -1877,11 +1877,11 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>17.4</v>
+        <v>17.68</v>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>-3.12</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="57">
@@ -1903,11 +1903,11 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>112.49</v>
+        <v>112</v>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>-4.66</v>
+        <v>-5.08</v>
       </c>
     </row>
     <row r="58">
@@ -1929,11 +1929,11 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="59">
@@ -1955,11 +1955,11 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>212</v>
+        <v>211.9</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>-2.3</v>
+        <v>-2.35</v>
       </c>
     </row>
     <row r="60">
@@ -1981,11 +1981,11 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>16.5</v>
+        <v>16.37</v>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>-4.62</v>
+        <v>-5.38</v>
       </c>
     </row>
     <row r="61">
@@ -2007,11 +2007,11 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>54.57</v>
+        <v>52.88</v>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>-2.55</v>
+        <v>-5.57</v>
       </c>
     </row>
     <row r="62">
@@ -2033,11 +2033,11 @@
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>-1.76</v>
+        <v>-4.69</v>
       </c>
     </row>
     <row r="63">
@@ -2059,11 +2059,11 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>87.98</v>
+        <v>88.84999999999999</v>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>0.09</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="64">
@@ -2085,11 +2085,11 @@
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>37.89</v>
+        <v>37.42</v>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>-1.53</v>
+        <v>-2.75</v>
       </c>
     </row>
     <row r="65">
@@ -2111,11 +2111,11 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>707.85</v>
+        <v>675</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>-1.73</v>
+        <v>-6.29</v>
       </c>
     </row>
     <row r="66">
@@ -2137,11 +2137,11 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>618.65</v>
+        <v>617</v>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>2.09</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="67">
@@ -2163,11 +2163,11 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>60.1</v>
+        <v>59.1</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>-0.83</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="68">
@@ -2189,11 +2189,11 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>7.05</v>
+        <v>6.51</v>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>3.52</v>
+        <v>-4.41</v>
       </c>
     </row>
     <row r="69">
@@ -2215,11 +2215,11 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>166.09</v>
+        <v>166.75</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>-0.37</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="70">
@@ -2241,11 +2241,11 @@
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>407.65</v>
+        <v>411</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>-0.55</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="71">
@@ -2267,11 +2267,11 @@
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>29.31</v>
+        <v>28.35</v>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>-1.97</v>
+        <v>-5.18</v>
       </c>
     </row>
     <row r="72">
@@ -2293,11 +2293,11 @@
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>64.78</v>
+        <v>63</v>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>-1.33</v>
+        <v>-4.04</v>
       </c>
     </row>
     <row r="73">
@@ -2319,11 +2319,11 @@
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>470.6</v>
+        <v>471.4</v>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>-1.96</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="74">
@@ -2345,11 +2345,11 @@
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>523</v>
+        <v>532.2</v>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>1.55</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="75">
@@ -2371,11 +2371,11 @@
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>5711</v>
+        <v>5648.5</v>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>-1.19</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="76">
@@ -2397,11 +2397,11 @@
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>64.27</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>-0.97</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="77">
@@ -2423,11 +2423,11 @@
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>3423.8</v>
+        <v>3466</v>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>2.05</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="78">
@@ -2449,24 +2449,24 @@
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>78.90000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>-2</v>
+        <v>-3.24</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>RADAAN</t>
+          <t>BHADORA</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>3.12</v>
+        <v>64.45</v>
       </c>
       <c r="C79" t="n">
-        <v>3.12</v>
+        <v>64.45</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
@@ -2475,24 +2475,24 @@
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>2.98</v>
+        <v>61.1</v>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>-4.49</v>
+        <v>-5.2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ALLDIGI</t>
+          <t>VINYLINDIA</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>823.55</v>
+        <v>209.89</v>
       </c>
       <c r="C80" t="n">
-        <v>823.55</v>
+        <v>209.89</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
@@ -2501,24 +2501,24 @@
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>824.1</v>
+        <v>205</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>0.07000000000000001</v>
+        <v>-2.33</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TRIGYN</t>
+          <t>HTMEDIA</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>52.11</v>
+        <v>21.82</v>
       </c>
       <c r="C81" t="n">
-        <v>52.11</v>
+        <v>21.82</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
@@ -2527,24 +2527,24 @@
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>51.4</v>
+        <v>20.7</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>-1.36</v>
+        <v>-5.13</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>IMPEXFERRO</t>
+          <t>UMESLTD</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="C82" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
@@ -2553,24 +2553,24 @@
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>1.67</v>
+        <v>4.05</v>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>-1.76</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ARCHIES</t>
+          <t>FILATFASH</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>15.82</v>
+        <v>0.22</v>
       </c>
       <c r="C83" t="n">
-        <v>15.82</v>
+        <v>0.22</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
@@ -2579,24 +2579,24 @@
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>14.95</v>
+        <v>0.21</v>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>-5.5</v>
+        <v>-4.55</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>PRAKASHSTL</t>
+          <t>GAYAPROJ</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>4.37</v>
+        <v>12.7</v>
       </c>
       <c r="C84" t="n">
-        <v>4.37</v>
+        <v>12.7</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
@@ -2605,24 +2605,24 @@
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>4.39</v>
+        <v>12.7</v>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>0.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AILIMITED</t>
+          <t>SPCENET</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>36.55</v>
+        <v>5.03</v>
       </c>
       <c r="C85" t="n">
-        <v>36.55</v>
+        <v>5.03</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
@@ -2631,24 +2631,24 @@
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>38.35</v>
+        <v>4.89</v>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>4.92</v>
+        <v>-2.78</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>PREMIER</t>
+          <t>HALEOSLABS</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2.99</v>
+        <v>1260.3</v>
       </c>
       <c r="C86" t="n">
-        <v>2.99</v>
+        <v>1260.3</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
@@ -2657,24 +2657,24 @@
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>2.85</v>
+        <v>1251</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>-4.68</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TIL</t>
+          <t>TECHLABS</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>208.98</v>
+        <v>195</v>
       </c>
       <c r="C87" t="n">
-        <v>208.98</v>
+        <v>195</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
@@ -2683,24 +2683,24 @@
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>213.79</v>
+        <v>199.9</v>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>2.3</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>RELCHEMQ</t>
+          <t>ONECAP-RE</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>122.33</v>
+        <v>0.2</v>
       </c>
       <c r="C88" t="n">
-        <v>122.33</v>
+        <v>0.2</v>
       </c>
       <c r="D88" t="n">
         <v>0</v>
@@ -2709,24 +2709,24 @@
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>118.61</v>
+        <v>0.18</v>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>-3.04</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>MARUSHIKA</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>55.99</v>
+        <v>103.15</v>
       </c>
       <c r="C89" t="n">
-        <v>55.99</v>
+        <v>103.15</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
@@ -2735,24 +2735,24 @@
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>55.06</v>
+        <v>101.5</v>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>-1.66</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BANG</t>
+          <t>IMPEXFERRO</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>41.52</v>
+        <v>1.7</v>
       </c>
       <c r="C90" t="n">
-        <v>41.52</v>
+        <v>1.7</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
@@ -2761,24 +2761,24 @@
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>41.99</v>
+        <v>1.69</v>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>1.13</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>HALEOSLABS</t>
+          <t>GOLDTECH</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1260.3</v>
+        <v>39.8</v>
       </c>
       <c r="C91" t="n">
-        <v>1260.3</v>
+        <v>39.8</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
@@ -2787,24 +2787,24 @@
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>1246</v>
+        <v>39</v>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>-1.13</v>
+        <v>-2.01</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AHLEAST</t>
+          <t>ANTGRAPHIC</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>160.77</v>
+        <v>0.87</v>
       </c>
       <c r="C92" t="n">
-        <v>160.77</v>
+        <v>0.87</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
@@ -2813,24 +2813,24 @@
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>158.01</v>
+        <v>0.86</v>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
-        <v>-1.72</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>LPDC</t>
+          <t>FMNL</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>6.08</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="C93" t="n">
-        <v>6.08</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D93" t="n">
         <v>0</v>
@@ -2839,24 +2839,24 @@
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>6.06</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
-        <v>-0.33</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>UNIDT</t>
+          <t>PRAKASHSTL</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>174.67</v>
+        <v>4.37</v>
       </c>
       <c r="C94" t="n">
-        <v>174.67</v>
+        <v>4.37</v>
       </c>
       <c r="D94" t="n">
         <v>0</v>
@@ -2865,24 +2865,24 @@
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>172.56</v>
+        <v>4.18</v>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>-1.21</v>
+        <v>-4.35</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SAHANA</t>
+          <t>ARCHIES</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1008.85</v>
+        <v>15.82</v>
       </c>
       <c r="C95" t="n">
-        <v>1008.85</v>
+        <v>15.82</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
@@ -2891,24 +2891,24 @@
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>992</v>
+        <v>15.03</v>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>-1.67</v>
+        <v>-4.99</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SGIL</t>
+          <t>UNIDT</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>522.4</v>
+        <v>174.67</v>
       </c>
       <c r="C96" t="n">
-        <v>522.4</v>
+        <v>174.67</v>
       </c>
       <c r="D96" t="n">
         <v>0</v>
@@ -2917,24 +2917,24 @@
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>521.85</v>
+        <v>171.99</v>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>-0.11</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SAFARI</t>
+          <t>SAHANA</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1797.2</v>
+        <v>1008.85</v>
       </c>
       <c r="C97" t="n">
-        <v>1797.2</v>
+        <v>1008.85</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
@@ -2943,24 +2943,24 @@
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>1781.5</v>
+        <v>1001</v>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>-0.87</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ISHAN</t>
+          <t>MYMUDRA</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.65</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="C98" t="n">
-        <v>0.65</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D98" t="n">
         <v>0</v>
@@ -2969,24 +2969,24 @@
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>0.6</v>
+        <v>75</v>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>-7.69</v>
+        <v>-2.72</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>TSFINV</t>
+          <t>GLOBALVECT</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>402.15</v>
+        <v>163.21</v>
       </c>
       <c r="C99" t="n">
-        <v>402.15</v>
+        <v>163.21</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
@@ -2995,24 +2995,24 @@
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>394.1</v>
+        <v>155.42</v>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
-        <v>-2</v>
+        <v>-4.77</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SHRIRAMPPS</t>
+          <t>ANKITMETAL</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>79.34999999999999</v>
+        <v>1.66</v>
       </c>
       <c r="C100" t="n">
-        <v>79.34999999999999</v>
+        <v>1.66</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
@@ -3021,24 +3021,24 @@
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>78.2</v>
+        <v>1.72</v>
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>-1.45</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>DELTAMAGNT</t>
+          <t>TSFINV</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>61.04</v>
+        <v>402.15</v>
       </c>
       <c r="C101" t="n">
-        <v>61.04</v>
+        <v>402.15</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
@@ -3047,24 +3047,24 @@
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>58.41</v>
+        <v>380.1</v>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>-4.31</v>
+        <v>-5.48</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MITTAL</t>
+          <t>UNIINFO</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1</v>
+        <v>14.04</v>
       </c>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>14.04</v>
       </c>
       <c r="D102" t="n">
         <v>0</v>
@@ -3073,24 +3073,24 @@
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>0.92</v>
+        <v>13.94</v>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>-8</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MADHUCON</t>
+          <t>RADAAN</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>4.73</v>
+        <v>3.12</v>
       </c>
       <c r="C103" t="n">
-        <v>4.73</v>
+        <v>3.12</v>
       </c>
       <c r="D103" t="n">
         <v>0</v>
@@ -3099,24 +3099,24 @@
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>4.63</v>
+        <v>3.05</v>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>-2.11</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>USK</t>
+          <t>FINBUD</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>28.67</v>
+        <v>105</v>
       </c>
       <c r="C104" t="n">
-        <v>28.67</v>
+        <v>105</v>
       </c>
       <c r="D104" t="n">
         <v>0</v>
@@ -3125,24 +3125,24 @@
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>27.4</v>
+        <v>100.6</v>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
-        <v>-4.43</v>
+        <v>-4.19</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ZENITHSTL</t>
+          <t>PRAXIS</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>5.68</v>
+        <v>7.79</v>
       </c>
       <c r="C105" t="n">
-        <v>5.68</v>
+        <v>7.79</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
@@ -3151,24 +3151,24 @@
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>5.59</v>
+        <v>7.41</v>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>-1.58</v>
+        <v>-4.88</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>RUCHINFRA</t>
+          <t>LYPSAGEMS</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>5.74</v>
+        <v>5.22</v>
       </c>
       <c r="C106" t="n">
-        <v>5.74</v>
+        <v>5.22</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
@@ -3177,24 +3177,24 @@
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>5.57</v>
+        <v>5.1</v>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
-        <v>-2.96</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>GOLDTECH</t>
+          <t>TRIGYN</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>39.8</v>
+        <v>52.11</v>
       </c>
       <c r="C107" t="n">
-        <v>39.8</v>
+        <v>52.11</v>
       </c>
       <c r="D107" t="n">
         <v>0</v>
@@ -3203,24 +3203,24 @@
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>39.53</v>
+        <v>51.25</v>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>-0.68</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>OILCOUNTUB</t>
+          <t>AILIMITED</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>47.36</v>
+        <v>36.55</v>
       </c>
       <c r="C108" t="n">
-        <v>47.36</v>
+        <v>36.55</v>
       </c>
       <c r="D108" t="n">
         <v>0</v>
@@ -3229,24 +3229,24 @@
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>47.49</v>
+        <v>38.35</v>
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
-        <v>0.27</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>FMNL</t>
+          <t>ENSER</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>8.300000000000001</v>
+        <v>12</v>
       </c>
       <c r="C109" t="n">
-        <v>8.300000000000001</v>
+        <v>12</v>
       </c>
       <c r="D109" t="n">
         <v>0</v>
@@ -3255,24 +3255,24 @@
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>8.220000000000001</v>
+        <v>12</v>
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>-0.96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ANTGRAPHIC</t>
+          <t>TARAPUR</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.87</v>
+        <v>25.34</v>
       </c>
       <c r="C110" t="n">
-        <v>0.87</v>
+        <v>25.34</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
@@ -3281,24 +3281,24 @@
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>0.85</v>
+        <v>25.15</v>
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
-        <v>-2.3</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>DICIND</t>
+          <t>GICL</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>526</v>
+        <v>48.4</v>
       </c>
       <c r="C111" t="n">
-        <v>526</v>
+        <v>48.4</v>
       </c>
       <c r="D111" t="n">
         <v>0</v>
@@ -3307,24 +3307,24 @@
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>540.05</v>
+        <v>47.8</v>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>2.67</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>AFSL</t>
+          <t>VIVIMEDLAB</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>201</v>
+        <v>7.57</v>
       </c>
       <c r="C112" t="n">
-        <v>201</v>
+        <v>7.57</v>
       </c>
       <c r="D112" t="n">
         <v>0</v>
@@ -3333,24 +3333,24 @@
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>201.49</v>
+        <v>7.2</v>
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
-        <v>0.24</v>
+        <v>-4.89</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>LYPSAGEMS</t>
+          <t>SAHAJ</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>5.22</v>
+        <v>4.85</v>
       </c>
       <c r="C113" t="n">
-        <v>5.22</v>
+        <v>4.85</v>
       </c>
       <c r="D113" t="n">
         <v>0</v>
@@ -3359,24 +3359,24 @@
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>5.23</v>
+        <v>4.65</v>
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>0.19</v>
+        <v>-4.12</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>UNIINFO</t>
+          <t>DHARAN</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>14.04</v>
+        <v>0.17</v>
       </c>
       <c r="C114" t="n">
-        <v>14.04</v>
+        <v>0.17</v>
       </c>
       <c r="D114" t="n">
         <v>0</v>
@@ -3385,24 +3385,24 @@
         <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>13.93</v>
+        <v>0.18</v>
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
-        <v>-0.78</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ANKITMETAL</t>
+          <t>SGIL</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1.66</v>
+        <v>522.4</v>
       </c>
       <c r="C115" t="n">
-        <v>1.66</v>
+        <v>522.4</v>
       </c>
       <c r="D115" t="n">
         <v>0</v>
@@ -3411,24 +3411,24 @@
         <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>1.63</v>
+        <v>513.25</v>
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>-1.81</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>HTMEDIA</t>
+          <t>SAFARI</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>21.82</v>
+        <v>1797.2</v>
       </c>
       <c r="C116" t="n">
-        <v>21.82</v>
+        <v>1797.2</v>
       </c>
       <c r="D116" t="n">
         <v>0</v>
@@ -3437,24 +3437,24 @@
         <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>21.47</v>
+        <v>1741.8</v>
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
-        <v>-1.6</v>
+        <v>-3.08</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>GLOBALVECT</t>
+          <t>ISHAN</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>163.21</v>
+        <v>0.65</v>
       </c>
       <c r="C117" t="n">
-        <v>163.21</v>
+        <v>0.65</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
@@ -3463,24 +3463,24 @@
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>159.49</v>
+        <v>0.6</v>
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>-2.28</v>
+        <v>-7.69</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>FILATFASH</t>
+          <t>SHRIRAMPPS</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.22</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="C118" t="n">
-        <v>0.22</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="D118" t="n">
         <v>0</v>
@@ -3489,24 +3489,24 @@
         <v>0</v>
       </c>
       <c r="F118" t="n">
-        <v>0.22</v>
+        <v>78</v>
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
-        <v>0</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MEP</t>
+          <t>DELTAMAGNT</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1.01</v>
+        <v>61.04</v>
       </c>
       <c r="C119" t="n">
-        <v>1.01</v>
+        <v>61.04</v>
       </c>
       <c r="D119" t="n">
         <v>0</v>
@@ -3515,24 +3515,24 @@
         <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>0.99</v>
+        <v>57.98</v>
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
-        <v>-1.98</v>
+        <v>-5.01</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MARUSHIKA</t>
+          <t>PREMIER</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>103.15</v>
+        <v>2.99</v>
       </c>
       <c r="C120" t="n">
-        <v>103.15</v>
+        <v>2.99</v>
       </c>
       <c r="D120" t="n">
         <v>0</v>
@@ -3541,24 +3541,24 @@
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>101</v>
+        <v>2.87</v>
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
-        <v>-2.08</v>
+        <v>-4.01</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ONECAP-RE</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.2</v>
+        <v>1.01</v>
       </c>
       <c r="C121" t="n">
-        <v>0.2</v>
+        <v>1.01</v>
       </c>
       <c r="D121" t="n">
         <v>0</v>
@@ -3567,24 +3567,24 @@
         <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>0.18</v>
+        <v>0.99</v>
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
-        <v>-10</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>TECHLABS</t>
+          <t>RELCHEMQ</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>195</v>
+        <v>122.33</v>
       </c>
       <c r="C122" t="n">
-        <v>195</v>
+        <v>122.33</v>
       </c>
       <c r="D122" t="n">
         <v>0</v>
@@ -3593,24 +3593,24 @@
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>203</v>
+        <v>118.03</v>
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
-        <v>4.1</v>
+        <v>-3.52</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SAHAJ</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>4.85</v>
+        <v>55.99</v>
       </c>
       <c r="C123" t="n">
-        <v>4.85</v>
+        <v>55.99</v>
       </c>
       <c r="D123" t="n">
         <v>0</v>
@@ -3619,24 +3619,24 @@
         <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>4.85</v>
+        <v>55.07</v>
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>0</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SPCENET</t>
+          <t>BANG</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>5.03</v>
+        <v>41.52</v>
       </c>
       <c r="C124" t="n">
-        <v>5.03</v>
+        <v>41.52</v>
       </c>
       <c r="D124" t="n">
         <v>0</v>
@@ -3645,24 +3645,24 @@
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>4.98</v>
+        <v>40.06</v>
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
-        <v>-0.99</v>
+        <v>-3.52</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GAYAPROJ</t>
+          <t>ZENITHSTL</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>12.7</v>
+        <v>5.68</v>
       </c>
       <c r="C125" t="n">
-        <v>12.7</v>
+        <v>5.68</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
@@ -3671,24 +3671,24 @@
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>12.7</v>
+        <v>5.83</v>
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>VINYLINDIA</t>
+          <t>AHLEAST</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>209.89</v>
+        <v>160.77</v>
       </c>
       <c r="C126" t="n">
-        <v>209.89</v>
+        <v>160.77</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
@@ -3697,24 +3697,24 @@
         <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>207.28</v>
+        <v>160.65</v>
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
-        <v>-1.24</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BHADORA</t>
+          <t>LPDC</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>64.45</v>
+        <v>6.08</v>
       </c>
       <c r="C127" t="n">
-        <v>64.45</v>
+        <v>6.08</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
@@ -3723,24 +3723,24 @@
         <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>63</v>
+        <v>5.83</v>
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
-        <v>-2.25</v>
+        <v>-4.11</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>VIVIMEDLAB</t>
+          <t>ALLDIGI</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>7.57</v>
+        <v>823.55</v>
       </c>
       <c r="C128" t="n">
-        <v>7.57</v>
+        <v>823.55</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
@@ -3749,24 +3749,24 @@
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>7.26</v>
+        <v>803.05</v>
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
-        <v>-4.1</v>
+        <v>-2.49</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>GICL</t>
+          <t>AFSL</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>48.4</v>
+        <v>201</v>
       </c>
       <c r="C129" t="n">
-        <v>48.4</v>
+        <v>201</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
@@ -3775,24 +3775,24 @@
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>48.2</v>
+        <v>201</v>
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
-        <v>-0.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>TARAPUR</t>
+          <t>OILCOUNTUB</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>25.34</v>
+        <v>47.36</v>
       </c>
       <c r="C130" t="n">
-        <v>25.34</v>
+        <v>47.36</v>
       </c>
       <c r="D130" t="n">
         <v>0</v>
@@ -3801,24 +3801,24 @@
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>24.52</v>
+        <v>47.8</v>
       </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
-        <v>-3.24</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>DHARAN</t>
+          <t>RUCHINFRA</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.17</v>
+        <v>5.74</v>
       </c>
       <c r="C131" t="n">
-        <v>0.17</v>
+        <v>5.74</v>
       </c>
       <c r="D131" t="n">
         <v>0</v>
@@ -3827,24 +3827,24 @@
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>0.18</v>
+        <v>5.73</v>
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
-        <v>5.88</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ENSER</t>
+          <t>MADHUCON</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>12</v>
+        <v>4.73</v>
       </c>
       <c r="C132" t="n">
-        <v>12</v>
+        <v>4.73</v>
       </c>
       <c r="D132" t="n">
         <v>0</v>
@@ -3853,24 +3853,24 @@
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>12</v>
+        <v>4.5</v>
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
-        <v>0</v>
+        <v>-4.86</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>PRAXIS</t>
+          <t>USK</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>7.79</v>
+        <v>28.67</v>
       </c>
       <c r="C133" t="n">
-        <v>7.79</v>
+        <v>28.67</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
@@ -3879,24 +3879,24 @@
         <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>7.56</v>
+        <v>27.77</v>
       </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
-        <v>-2.95</v>
+        <v>-3.14</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>FINBUD</t>
+          <t>MITTAL</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="C134" t="n">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
@@ -3905,24 +3905,24 @@
         <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>110.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
-        <v>5.62</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>UMESLTD</t>
+          <t>TIL</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>4.1</v>
+        <v>208.98</v>
       </c>
       <c r="C135" t="n">
-        <v>4.1</v>
+        <v>208.98</v>
       </c>
       <c r="D135" t="n">
         <v>0</v>
@@ -3931,24 +3931,24 @@
         <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>4.02</v>
+        <v>213</v>
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
-        <v>-1.95</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MYMUDRA</t>
+          <t>DICIND</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>77.09999999999999</v>
+        <v>526</v>
       </c>
       <c r="C136" t="n">
-        <v>77.09999999999999</v>
+        <v>526</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
@@ -3957,11 +3957,11 @@
         <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>77.09999999999999</v>
+        <v>521.5</v>
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
-        <v>0</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="137">
@@ -3983,24 +3983,24 @@
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>73.06999999999999</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
-        <v>-3.15</v>
+        <v>-4.29</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>TCC</t>
+          <t>RVHL</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>447.1</v>
+        <v>41.51</v>
       </c>
       <c r="C138" t="n">
-        <v>447</v>
+        <v>41.5</v>
       </c>
       <c r="D138" t="n">
         <v>-0.02</v>
@@ -4009,24 +4009,24 @@
         <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>435</v>
+        <v>38.32</v>
       </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
-        <v>-2.68</v>
+        <v>-7.66</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>RVHL</t>
+          <t>TCC</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>41.51</v>
+        <v>447.1</v>
       </c>
       <c r="C139" t="n">
-        <v>41.5</v>
+        <v>447</v>
       </c>
       <c r="D139" t="n">
         <v>-0.02</v>
@@ -4035,24 +4035,24 @@
         <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>40.05</v>
+        <v>428.35</v>
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
-        <v>-3.49</v>
+        <v>-4.17</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SMARTWORKS</t>
+          <t>DPABHUSHAN</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>410.05</v>
+        <v>1186.2</v>
       </c>
       <c r="C140" t="n">
-        <v>409.9</v>
+        <v>1185.7</v>
       </c>
       <c r="D140" t="n">
         <v>-0.04</v>
@@ -4061,24 +4061,24 @@
         <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>396.45</v>
+        <v>1158.9</v>
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
-        <v>-3.28</v>
+        <v>-2.26</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>DPABHUSHAN</t>
+          <t>SMARTWORKS</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1186.2</v>
+        <v>410.05</v>
       </c>
       <c r="C141" t="n">
-        <v>1185.7</v>
+        <v>409.9</v>
       </c>
       <c r="D141" t="n">
         <v>-0.04</v>
@@ -4087,24 +4087,24 @@
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>1158.6</v>
+        <v>395</v>
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
-        <v>-2.29</v>
+        <v>-3.64</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>CAPITALSFB</t>
+          <t>STANLEY</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>262.1</v>
+        <v>162.07</v>
       </c>
       <c r="C142" t="n">
-        <v>262</v>
+        <v>162</v>
       </c>
       <c r="D142" t="n">
         <v>-0.04</v>
@@ -4113,24 +4113,24 @@
         <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>262.8</v>
+        <v>155.8</v>
       </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
-        <v>0.31</v>
+        <v>-3.83</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>STANLEY</t>
+          <t>CAPITALSFB</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>162.07</v>
+        <v>262.1</v>
       </c>
       <c r="C143" t="n">
-        <v>162</v>
+        <v>262</v>
       </c>
       <c r="D143" t="n">
         <v>-0.04</v>
@@ -4139,11 +4139,11 @@
         <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>158.2</v>
+        <v>258.55</v>
       </c>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
-        <v>-2.35</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="144">
@@ -4165,11 +4165,11 @@
         <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>18.93</v>
+        <v>17.7</v>
       </c>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
-        <v>-0.79</v>
+        <v>-7.23</v>
       </c>
     </row>
     <row r="145">
@@ -4191,24 +4191,24 @@
         <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>477.4</v>
+        <v>518</v>
       </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
-        <v>7.27</v>
+        <v>16.39</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SGL</t>
+          <t>KRISHIVAL</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>12.58</v>
+        <v>313.25</v>
       </c>
       <c r="C146" t="n">
-        <v>12.57</v>
+        <v>313</v>
       </c>
       <c r="D146" t="n">
         <v>-0.08</v>
@@ -4217,24 +4217,24 @@
         <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>11.69</v>
+        <v>321.5</v>
       </c>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
-        <v>-7</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>KRISHIVAL</t>
+          <t>SGL</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>313.25</v>
+        <v>12.58</v>
       </c>
       <c r="C147" t="n">
-        <v>313</v>
+        <v>12.57</v>
       </c>
       <c r="D147" t="n">
         <v>-0.08</v>
@@ -4243,11 +4243,11 @@
         <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>315</v>
+        <v>12</v>
       </c>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
-        <v>0.64</v>
+        <v>-4.53</v>
       </c>
     </row>
     <row r="148">
@@ -4269,11 +4269,11 @@
         <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>30</v>
+        <v>29.5</v>
       </c>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -4295,11 +4295,11 @@
         <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>34.21</v>
+        <v>32.98</v>
       </c>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
-        <v>-3.63</v>
+        <v>-7.1</v>
       </c>
     </row>
     <row r="150">
@@ -4321,11 +4321,11 @@
         <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>28</v>
+        <v>26.51</v>
       </c>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
-        <v>1.27</v>
+        <v>-4.12</v>
       </c>
     </row>
     <row r="151">
@@ -4347,24 +4347,24 @@
         <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>543.95</v>
+        <v>516.55</v>
       </c>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
-        <v>1.29</v>
+        <v>-3.81</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SHANTIGEAR</t>
+          <t>ANANTAM</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>450.1</v>
+        <v>102.53</v>
       </c>
       <c r="C152" t="n">
-        <v>449.5</v>
+        <v>102.4</v>
       </c>
       <c r="D152" t="n">
         <v>-0.13</v>
@@ -4373,24 +4373,24 @@
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>451.4</v>
+        <v>102.81</v>
       </c>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ANANTAM</t>
+          <t>BALAJITELE</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>102.53</v>
+        <v>108.14</v>
       </c>
       <c r="C153" t="n">
-        <v>102.4</v>
+        <v>108</v>
       </c>
       <c r="D153" t="n">
         <v>-0.13</v>
@@ -4399,24 +4399,24 @@
         <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>102.75</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="n">
-        <v>0.34</v>
+        <v>-8.890000000000001</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BALAJITELE</t>
+          <t>SHANTIGEAR</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>108.14</v>
+        <v>450.1</v>
       </c>
       <c r="C154" t="n">
-        <v>108</v>
+        <v>449.5</v>
       </c>
       <c r="D154" t="n">
         <v>-0.13</v>
@@ -4425,11 +4425,11 @@
         <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>101.54</v>
+        <v>450.2</v>
       </c>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="n">
-        <v>-5.98</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="155">
@@ -4451,11 +4451,11 @@
         <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>13.54</v>
+        <v>13.6</v>
       </c>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="n">
-        <v>0.52</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="156">
@@ -4477,11 +4477,11 @@
         <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>4.75</v>
+        <v>4.54</v>
       </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="n">
-        <v>-2.06</v>
+        <v>-6.39</v>
       </c>
     </row>
     <row r="157">
@@ -4503,11 +4503,11 @@
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>4.58</v>
+        <v>4.39</v>
       </c>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="n">
-        <v>-0.65</v>
+        <v>-4.77</v>
       </c>
     </row>
     <row r="158">
@@ -4529,11 +4529,11 @@
         <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>270.6</v>
+        <v>279.55</v>
       </c>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="n">
-        <v>-4.72</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="159">
@@ -4581,11 +4581,11 @@
         <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>716.9</v>
+        <v>657</v>
       </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="n">
-        <v>12.72</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="161">
@@ -4607,11 +4607,11 @@
         <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>536</v>
+        <v>525.1</v>
       </c>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="n">
-        <v>-2.44</v>
+        <v>-4.42</v>
       </c>
     </row>
     <row r="162">
@@ -4633,24 +4633,24 @@
         <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>159.31</v>
+        <v>160</v>
       </c>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>SWARAJ</t>
+          <t>ELLEN</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>303.25</v>
+        <v>229.25</v>
       </c>
       <c r="C163" t="n">
-        <v>302.25</v>
+        <v>228.49</v>
       </c>
       <c r="D163" t="n">
         <v>-0.33</v>
@@ -4659,24 +4659,24 @@
         <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>301.6</v>
+        <v>225.85</v>
       </c>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="n">
-        <v>-0.22</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SUVIDHAA</t>
+          <t>SWARAJ</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>3</v>
+        <v>303.25</v>
       </c>
       <c r="C164" t="n">
-        <v>2.99</v>
+        <v>302.25</v>
       </c>
       <c r="D164" t="n">
         <v>-0.33</v>
@@ -4685,24 +4685,24 @@
         <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>2.97</v>
+        <v>302</v>
       </c>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="n">
-        <v>-0.67</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>SUVIDHAA</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>229.25</v>
+        <v>3</v>
       </c>
       <c r="C165" t="n">
-        <v>228.49</v>
+        <v>2.99</v>
       </c>
       <c r="D165" t="n">
         <v>-0.33</v>
@@ -4711,11 +4711,11 @@
         <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>226.62</v>
+        <v>2.93</v>
       </c>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="n">
-        <v>-0.82</v>
+        <v>-2.01</v>
       </c>
     </row>
     <row r="166">
@@ -4737,11 +4737,11 @@
         <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>8.5</v>
+        <v>8.44</v>
       </c>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="n">
-        <v>-2.3</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="167">
@@ -4763,11 +4763,11 @@
         <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>684.05</v>
+        <v>681.1</v>
       </c>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="n">
-        <v>-2.43</v>
+        <v>-2.85</v>
       </c>
     </row>
     <row r="168">
@@ -4789,11 +4789,11 @@
         <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>116.99</v>
+        <v>115.9</v>
       </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="n">
-        <v>-2.51</v>
+        <v>-3.42</v>
       </c>
     </row>
     <row r="169">
@@ -4815,11 +4815,11 @@
         <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>80.75</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="n">
-        <v>-1.52</v>
+        <v>-3.37</v>
       </c>
     </row>
     <row r="170">
@@ -4841,11 +4841,11 @@
         <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>124.75</v>
+        <v>126.98</v>
       </c>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="n">
-        <v>0.36</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="171">
@@ -4867,11 +4867,11 @@
         <v>0</v>
       </c>
       <c r="F171" t="n">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="n">
-        <v>-4.8</v>
+        <v>-6.6</v>
       </c>
     </row>
     <row r="172">
@@ -4893,11 +4893,11 @@
         <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>44.05</v>
+        <v>44</v>
       </c>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="n">
-        <v>-2.05</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="173">
@@ -4919,11 +4919,11 @@
         <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>6.87</v>
+        <v>6.7</v>
       </c>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="n">
-        <v>-1.15</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="174">
@@ -4945,24 +4945,24 @@
         <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>61.73</v>
+        <v>60.64</v>
       </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>EDELWEISS</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>2037.2</v>
+        <v>114.42</v>
       </c>
       <c r="C175" t="n">
-        <v>2028</v>
+        <v>113.9</v>
       </c>
       <c r="D175" t="n">
         <v>-0.45</v>
@@ -4971,24 +4971,24 @@
         <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>2002.7</v>
+        <v>112.54</v>
       </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="n">
-        <v>-1.25</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>EDELWEISS</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>114.42</v>
+        <v>2037.2</v>
       </c>
       <c r="C176" t="n">
-        <v>113.9</v>
+        <v>2028</v>
       </c>
       <c r="D176" t="n">
         <v>-0.45</v>
@@ -4997,11 +4997,11 @@
         <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>114.35</v>
+        <v>2031.4</v>
       </c>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="n">
-        <v>0.4</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="177">
@@ -5023,24 +5023,24 @@
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>25.3</v>
+        <v>25</v>
       </c>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="n">
-        <v>-2.69</v>
+        <v>-3.85</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SELMC</t>
+          <t>MEDIASSIST</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>29.93</v>
+        <v>370.7</v>
       </c>
       <c r="C178" t="n">
-        <v>29.79</v>
+        <v>368.95</v>
       </c>
       <c r="D178" t="n">
         <v>-0.47</v>
@@ -5049,24 +5049,24 @@
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>29.45</v>
+        <v>361.9</v>
       </c>
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="n">
-        <v>-1.14</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>MEDIASSIST</t>
+          <t>SELMC</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>370.7</v>
+        <v>29.93</v>
       </c>
       <c r="C179" t="n">
-        <v>368.95</v>
+        <v>29.79</v>
       </c>
       <c r="D179" t="n">
         <v>-0.47</v>
@@ -5075,11 +5075,11 @@
         <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>358.1</v>
+        <v>28.5</v>
       </c>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="n">
-        <v>-2.94</v>
+        <v>-4.33</v>
       </c>
     </row>
     <row r="180">
@@ -5101,24 +5101,24 @@
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>1491.9</v>
+        <v>1514</v>
       </c>
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="n">
-        <v>-0.55</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>RKEC</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>43.15</v>
+        <v>566.3</v>
       </c>
       <c r="C181" t="n">
-        <v>42.94</v>
+        <v>563.5</v>
       </c>
       <c r="D181" t="n">
         <v>-0.49</v>
@@ -5127,24 +5127,24 @@
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>42.21</v>
+        <v>576</v>
       </c>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="n">
-        <v>-1.7</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>RKEC</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>566.3</v>
+        <v>43.15</v>
       </c>
       <c r="C182" t="n">
-        <v>563.5</v>
+        <v>42.94</v>
       </c>
       <c r="D182" t="n">
         <v>-0.49</v>
@@ -5153,11 +5153,11 @@
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>579.85</v>
+        <v>42.57</v>
       </c>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="n">
-        <v>2.9</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="183">
@@ -5179,11 +5179,11 @@
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>135.5</v>
+        <v>131.08</v>
       </c>
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="n">
-        <v>-2.15</v>
+        <v>-5.34</v>
       </c>
     </row>
     <row r="184">
@@ -5205,11 +5205,11 @@
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>251.15</v>
+        <v>244</v>
       </c>
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="n">
-        <v>-1.43</v>
+        <v>-4.24</v>
       </c>
     </row>
     <row r="185">
@@ -5231,11 +5231,11 @@
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>1276.4</v>
+        <v>1274</v>
       </c>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="n">
-        <v>0.13</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="186">
@@ -5257,24 +5257,24 @@
         <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>3.76</v>
+        <v>3.61</v>
       </c>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="n">
-        <v>1.08</v>
+        <v>-2.96</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ICDSLTD</t>
+          <t>UCAL</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>41.1</v>
+        <v>108.59</v>
       </c>
       <c r="C187" t="n">
-        <v>40.88</v>
+        <v>108</v>
       </c>
       <c r="D187" t="n">
         <v>-0.54</v>
@@ -5283,11 +5283,11 @@
         <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>40.5</v>
+        <v>101.99</v>
       </c>
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="n">
-        <v>-0.93</v>
+        <v>-5.56</v>
       </c>
     </row>
     <row r="188">
@@ -5309,24 +5309,24 @@
         <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="n">
-        <v>-2.94</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>UCAL</t>
+          <t>ICDSLTD</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>108.59</v>
+        <v>41.1</v>
       </c>
       <c r="C189" t="n">
-        <v>108</v>
+        <v>40.88</v>
       </c>
       <c r="D189" t="n">
         <v>-0.54</v>
@@ -5335,24 +5335,24 @@
         <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>106.73</v>
+        <v>39.05</v>
       </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="n">
-        <v>-1.18</v>
+        <v>-4.48</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ICRA</t>
+          <t>CCCL</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>5531</v>
+        <v>15.99</v>
       </c>
       <c r="C190" t="n">
-        <v>5500</v>
+        <v>15.9</v>
       </c>
       <c r="D190" t="n">
         <v>-0.5600000000000001</v>
@@ -5361,24 +5361,24 @@
         <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>5534.5</v>
+        <v>15.4</v>
       </c>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="n">
-        <v>0.63</v>
+        <v>-3.14</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>CCCL</t>
+          <t>ICRA</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>15.99</v>
+        <v>5531</v>
       </c>
       <c r="C191" t="n">
-        <v>15.9</v>
+        <v>5500</v>
       </c>
       <c r="D191" t="n">
         <v>-0.5600000000000001</v>
@@ -5387,11 +5387,11 @@
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>16.39</v>
+        <v>5712.5</v>
       </c>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="n">
-        <v>3.08</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="192">
@@ -5413,24 +5413,24 @@
         <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>153.95</v>
+        <v>153.5</v>
       </c>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="n">
-        <v>-1.63</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>IRBINVIT</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>61.86</v>
+        <v>444.7</v>
       </c>
       <c r="C193" t="n">
-        <v>61.5</v>
+        <v>442.1</v>
       </c>
       <c r="D193" t="n">
         <v>-0.58</v>
@@ -5439,11 +5439,11 @@
         <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>61.67</v>
+        <v>454.15</v>
       </c>
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="n">
-        <v>0.28</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="194">
@@ -5465,24 +5465,24 @@
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>1000.9</v>
+        <v>999</v>
       </c>
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="n">
-        <v>0.85</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>IRBINVIT</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>444.7</v>
+        <v>61.86</v>
       </c>
       <c r="C195" t="n">
-        <v>442.1</v>
+        <v>61.5</v>
       </c>
       <c r="D195" t="n">
         <v>-0.58</v>
@@ -5491,11 +5491,11 @@
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>453.75</v>
+        <v>61.38</v>
       </c>
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="n">
-        <v>2.64</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="196">
@@ -5517,24 +5517,24 @@
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>16.1</v>
+        <v>16.3</v>
       </c>
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="n">
-        <v>-3.71</v>
+        <v>-2.51</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>FOODSIN</t>
+          <t>CAPINVIT</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>58.3</v>
+        <v>70</v>
       </c>
       <c r="C197" t="n">
-        <v>57.95</v>
+        <v>69.58</v>
       </c>
       <c r="D197" t="n">
         <v>-0.6</v>
@@ -5543,24 +5543,24 @@
         <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>57.26</v>
+        <v>69.8</v>
       </c>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="n">
-        <v>-1.19</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>CAPINVIT</t>
+          <t>FOODSIN</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>70</v>
+        <v>58.3</v>
       </c>
       <c r="C198" t="n">
-        <v>69.58</v>
+        <v>57.95</v>
       </c>
       <c r="D198" t="n">
         <v>-0.6</v>
@@ -5569,11 +5569,11 @@
         <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>69.59999999999999</v>
+        <v>57.23</v>
       </c>
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="n">
-        <v>0.03</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="199">
@@ -5595,11 +5595,11 @@
         <v>0</v>
       </c>
       <c r="F199" t="n">
-        <v>24.5</v>
+        <v>24.97</v>
       </c>
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="n">
-        <v>-2.2</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="200">
@@ -5621,24 +5621,24 @@
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>364.2</v>
+        <v>366.6</v>
       </c>
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="n">
-        <v>5.57</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>TAINWALCHM</t>
+          <t>SUNDROP</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>209.18</v>
+        <v>646.45</v>
       </c>
       <c r="C201" t="n">
-        <v>207.9</v>
+        <v>642.5</v>
       </c>
       <c r="D201" t="n">
         <v>-0.61</v>
@@ -5647,11 +5647,11 @@
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>199.01</v>
+        <v>632.2</v>
       </c>
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="n">
-        <v>-4.28</v>
+        <v>-1.6</v>
       </c>
     </row>
   </sheetData>

--- a/data/trending_momentum_stocks.xlsx
+++ b/data/trending_momentum_stocks.xlsx
@@ -461,3815 +461,3815 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KALANA</t>
+          <t>TECILCHEM</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.6</v>
+        <v>12.69</v>
       </c>
       <c r="C2" t="n">
-        <v>23.5</v>
+        <v>14.75</v>
       </c>
       <c r="D2" t="n">
-        <v>19.9</v>
+        <v>16.23</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>23.5</v>
+        <v>13.21</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-10.44</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WEWIN</t>
+          <t>SAHYADRI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>43.55</v>
+        <v>242.05</v>
       </c>
       <c r="C3" t="n">
-        <v>47.7</v>
+        <v>276.85</v>
       </c>
       <c r="D3" t="n">
-        <v>9.529999999999999</v>
+        <v>14.38</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>43.98</v>
+        <v>251.5</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>-7.8</v>
+        <v>-9.16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DCMFINSERV</t>
+          <t>KALANA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.38</v>
+        <v>23.5</v>
       </c>
       <c r="C4" t="n">
-        <v>4.7</v>
+        <v>25.85</v>
       </c>
       <c r="D4" t="n">
-        <v>7.31</v>
+        <v>10</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>4.18</v>
+        <v>25.55</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>-11.06</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3PLAND</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.68</v>
+        <v>111.83</v>
       </c>
       <c r="C5" t="n">
-        <v>34.89</v>
+        <v>123</v>
       </c>
       <c r="D5" t="n">
-        <v>6.76</v>
+        <v>9.99</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>31.4</v>
+        <v>114.92</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>-10</v>
+        <v>-6.57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LIBAS</t>
+          <t>EUROBOND</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.04</v>
+        <v>161.46</v>
       </c>
       <c r="C6" t="n">
-        <v>10.7</v>
+        <v>177</v>
       </c>
       <c r="D6" t="n">
-        <v>6.57</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>10.1</v>
+        <v>162.5</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>-5.61</v>
+        <v>-8.19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DTIL</t>
+          <t>INFOMEDIA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>139</v>
+        <v>5.08</v>
       </c>
       <c r="C7" t="n">
-        <v>147</v>
+        <v>5.5</v>
       </c>
       <c r="D7" t="n">
-        <v>5.76</v>
+        <v>8.27</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>134</v>
+        <v>5.2</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>-8.84</v>
+        <v>-5.45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MONEYBOXX</t>
+          <t>AAKASH</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>63.4</v>
+        <v>8.33</v>
       </c>
       <c r="C8" t="n">
-        <v>66.98999999999999</v>
+        <v>8.99</v>
       </c>
       <c r="D8" t="n">
-        <v>5.66</v>
+        <v>7.92</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>62.13</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>-7.25</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KAYA</t>
+          <t>TOUCHWOOD</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>323.7</v>
+        <v>71.3</v>
       </c>
       <c r="C9" t="n">
-        <v>340</v>
+        <v>76.92</v>
       </c>
       <c r="D9" t="n">
-        <v>5.04</v>
+        <v>7.88</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>312.05</v>
+        <v>73.22</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>-8.220000000000001</v>
+        <v>-4.81</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SETUINFRA</t>
+          <t>APCL</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4</v>
+        <v>124.33</v>
       </c>
       <c r="C10" t="n">
-        <v>0.42</v>
+        <v>132.95</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>6.93</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.42</v>
+        <v>122.86</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>-7.59</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NEUEON</t>
+          <t>CREATIVEYE</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10.8</v>
+        <v>6.3</v>
       </c>
       <c r="C11" t="n">
-        <v>11.34</v>
+        <v>6.73</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>6.83</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>11.34</v>
+        <v>6.16</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-8.470000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UNITEDPOLY</t>
+          <t>MFML</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24.66</v>
+        <v>21.64</v>
       </c>
       <c r="C12" t="n">
-        <v>25.89</v>
+        <v>23.1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.99</v>
+        <v>6.75</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>24.77</v>
+        <v>21.22</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>-4.33</v>
+        <v>-8.140000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SETCO</t>
+          <t>WELINV</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16.92</v>
+        <v>1268.2</v>
       </c>
       <c r="C13" t="n">
-        <v>17.76</v>
+        <v>1350</v>
       </c>
       <c r="D13" t="n">
-        <v>4.96</v>
+        <v>6.45</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>17.76</v>
+        <v>1289</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>-4.52</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EUROTEXIND</t>
+          <t>ACEINTEG</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12.91</v>
+        <v>17.45</v>
       </c>
       <c r="C14" t="n">
-        <v>13.55</v>
+        <v>18.4</v>
       </c>
       <c r="D14" t="n">
-        <v>4.96</v>
+        <v>5.44</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>13</v>
+        <v>16.65</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>-4.06</v>
+        <v>-9.51</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ROLLT</t>
+          <t>KHANDSE</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.41</v>
+        <v>16.77</v>
       </c>
       <c r="C15" t="n">
-        <v>1.48</v>
+        <v>17.66</v>
       </c>
       <c r="D15" t="n">
-        <v>4.96</v>
+        <v>5.31</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.35</v>
+        <v>16.02</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>-8.779999999999999</v>
+        <v>-9.289999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TOUCHWOOD</t>
+          <t>JINDRILL</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>73.89</v>
+        <v>522.15</v>
       </c>
       <c r="C16" t="n">
-        <v>77.55</v>
+        <v>549</v>
       </c>
       <c r="D16" t="n">
-        <v>4.95</v>
+        <v>5.14</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>71.16</v>
+        <v>594.95</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>-8.24</v>
+        <v>8.369999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PALREDTEC</t>
+          <t>SETCO</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32.55</v>
+        <v>17.76</v>
       </c>
       <c r="C17" t="n">
-        <v>34.14</v>
+        <v>18.64</v>
       </c>
       <c r="D17" t="n">
-        <v>4.88</v>
+        <v>4.95</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>32.34</v>
+        <v>17.73</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>-5.27</v>
+        <v>-4.88</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>NEUEON</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6.67</v>
+        <v>11.34</v>
       </c>
       <c r="C18" t="n">
-        <v>6.99</v>
+        <v>11.9</v>
       </c>
       <c r="D18" t="n">
-        <v>4.8</v>
+        <v>4.94</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>6.39</v>
+        <v>11.9</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>-8.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DCMSIL</t>
+          <t>DHARIWAL</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>63.67</v>
+        <v>43.85</v>
       </c>
       <c r="C19" t="n">
-        <v>66.7</v>
+        <v>46</v>
       </c>
       <c r="D19" t="n">
-        <v>4.76</v>
+        <v>4.9</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>66.84999999999999</v>
+        <v>46</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ORTEL</t>
+          <t>PREMIER</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.51</v>
+        <v>2.87</v>
       </c>
       <c r="C20" t="n">
-        <v>1.58</v>
+        <v>3.01</v>
       </c>
       <c r="D20" t="n">
-        <v>4.64</v>
+        <v>4.88</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1.57</v>
+        <v>3.01</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DHARIWAL</t>
+          <t>LOYALTEX</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>41.8</v>
+        <v>213.66</v>
       </c>
       <c r="C21" t="n">
-        <v>43.7</v>
+        <v>223.99</v>
       </c>
       <c r="D21" t="n">
-        <v>4.55</v>
+        <v>4.83</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>43.85</v>
+        <v>217</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.34</v>
+        <v>-3.12</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BLUECOAST</t>
+          <t>AIROLAM</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21.33</v>
+        <v>89.13</v>
       </c>
       <c r="C22" t="n">
-        <v>22.3</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>4.55</v>
+        <v>4.73</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>20.27</v>
+        <v>90.5</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>-9.1</v>
+        <v>-3.05</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>COMPUSOFT</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>483.9</v>
+        <v>13.71</v>
       </c>
       <c r="C23" t="n">
-        <v>503</v>
+        <v>14.35</v>
       </c>
       <c r="D23" t="n">
-        <v>3.95</v>
+        <v>4.67</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>484.7</v>
+        <v>13.32</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>-3.64</v>
+        <v>-7.18</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EFACTOR</t>
+          <t>TREEHOUSE</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>234.95</v>
+        <v>9.01</v>
       </c>
       <c r="C24" t="n">
-        <v>244</v>
+        <v>9.43</v>
       </c>
       <c r="D24" t="n">
-        <v>3.85</v>
+        <v>4.66</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>232</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>-4.92</v>
+        <v>-5.83</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GTECJAINX</t>
+          <t>OMKARCHEM</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.24</v>
+        <v>4.52</v>
       </c>
       <c r="C25" t="n">
-        <v>19.9</v>
+        <v>4.73</v>
       </c>
       <c r="D25" t="n">
-        <v>3.43</v>
+        <v>4.65</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>19.37</v>
+        <v>4.31</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>-2.66</v>
+        <v>-8.880000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DHARARAIL</t>
+          <t>BLUECOAST</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>119</v>
+        <v>20.75</v>
       </c>
       <c r="C26" t="n">
-        <v>122.9</v>
+        <v>21.7</v>
       </c>
       <c r="D26" t="n">
-        <v>3.28</v>
+        <v>4.58</v>
       </c>
       <c r="E26" t="b">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>117.1</v>
+        <v>20.39</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>-4.72</v>
+        <v>-6.04</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>VAISHALI</t>
+          <t>SHIVATEX</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.97</v>
+        <v>152.08</v>
       </c>
       <c r="C27" t="n">
-        <v>7.19</v>
+        <v>159.02</v>
       </c>
       <c r="D27" t="n">
-        <v>3.16</v>
+        <v>4.56</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>6.72</v>
+        <v>153.59</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>-6.54</v>
+        <v>-3.41</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>VLEGOV</t>
+          <t>PARAS</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>15.6</v>
+        <v>670.85</v>
       </c>
       <c r="C28" t="n">
-        <v>16.09</v>
+        <v>701</v>
       </c>
       <c r="D28" t="n">
-        <v>3.14</v>
+        <v>4.49</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>16.05</v>
+        <v>736.1</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>-0.25</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>AGROPHOS</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>279.7</v>
+        <v>32.53</v>
       </c>
       <c r="C29" t="n">
-        <v>288</v>
+        <v>33.99</v>
       </c>
       <c r="D29" t="n">
-        <v>2.97</v>
+        <v>4.49</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>281.45</v>
+        <v>32.12</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>-2.27</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GPECO</t>
+          <t>SOCL</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>355</v>
+        <v>27.85</v>
       </c>
       <c r="C30" t="n">
-        <v>365</v>
+        <v>29.1</v>
       </c>
       <c r="D30" t="n">
-        <v>2.82</v>
+        <v>4.49</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>331</v>
+        <v>29.2</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>-9.32</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GJL</t>
+          <t>ORTEL</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>163.4</v>
+        <v>1.57</v>
       </c>
       <c r="C31" t="n">
-        <v>168</v>
+        <v>1.64</v>
       </c>
       <c r="D31" t="n">
-        <v>2.82</v>
+        <v>4.46</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>171.55</v>
+        <v>1.57</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>2.11</v>
+        <v>-4.27</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MITCON</t>
+          <t>SELMC</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>58.5</v>
+        <v>28.73</v>
       </c>
       <c r="C32" t="n">
-        <v>60</v>
+        <v>29.98</v>
       </c>
       <c r="D32" t="n">
-        <v>2.56</v>
+        <v>4.35</v>
       </c>
       <c r="E32" t="b">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>55.26</v>
+        <v>27.33</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>-7.9</v>
+        <v>-8.84</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FLFL</t>
+          <t>ACCPL</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.2</v>
+        <v>68.05</v>
       </c>
       <c r="C33" t="n">
-        <v>1.23</v>
+        <v>70.95</v>
       </c>
       <c r="D33" t="n">
-        <v>2.5</v>
+        <v>4.26</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>1.24</v>
+        <v>70.95</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BANKA</t>
+          <t>SUNDRMBRAK</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>57.64</v>
+        <v>584.15</v>
       </c>
       <c r="C34" t="n">
-        <v>58.99</v>
+        <v>607.7</v>
       </c>
       <c r="D34" t="n">
-        <v>2.34</v>
+        <v>4.03</v>
       </c>
       <c r="E34" t="b">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>56.02</v>
+        <v>589.8</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>-5.03</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FEL</t>
+          <t>VETO</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.43</v>
+        <v>100.94</v>
       </c>
       <c r="C35" t="n">
-        <v>0.44</v>
+        <v>105</v>
       </c>
       <c r="D35" t="n">
-        <v>2.33</v>
+        <v>4.02</v>
       </c>
       <c r="E35" t="b">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0.43</v>
+        <v>100.28</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>-2.27</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RPPL</t>
+          <t>MAHAPEXLTD</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>16.6</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>16.95</v>
+        <v>90</v>
       </c>
       <c r="D36" t="n">
-        <v>2.11</v>
+        <v>3.79</v>
       </c>
       <c r="E36" t="b">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>15.42</v>
+        <v>87</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>-9.029999999999999</v>
+        <v>-3.33</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MANCREDIT</t>
+          <t>CTE</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>168.55</v>
+        <v>27.34</v>
       </c>
       <c r="C37" t="n">
-        <v>171.99</v>
+        <v>28.33</v>
       </c>
       <c r="D37" t="n">
-        <v>2.04</v>
+        <v>3.62</v>
       </c>
       <c r="E37" t="b">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>166.3</v>
+        <v>27.25</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>-3.31</v>
+        <v>-3.81</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>VHLTD</t>
+          <t>DHRUV</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>147</v>
+        <v>30.48</v>
       </c>
       <c r="C38" t="n">
-        <v>149.9</v>
+        <v>31.55</v>
       </c>
       <c r="D38" t="n">
-        <v>1.97</v>
+        <v>3.51</v>
       </c>
       <c r="E38" t="b">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>144</v>
+        <v>31.67</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>-3.94</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>RAJRILTD</t>
+          <t>RSSOFTWARE</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>22.93</v>
+        <v>33.52</v>
       </c>
       <c r="C39" t="n">
-        <v>23.38</v>
+        <v>34.68</v>
       </c>
       <c r="D39" t="n">
-        <v>1.96</v>
+        <v>3.46</v>
       </c>
       <c r="E39" t="b">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>22.48</v>
+        <v>34.96</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>-3.85</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SANCO</t>
+          <t>AKASH</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.21</v>
+        <v>25.06</v>
       </c>
       <c r="C40" t="n">
-        <v>2.25</v>
+        <v>25.9</v>
       </c>
       <c r="D40" t="n">
-        <v>1.81</v>
+        <v>3.35</v>
       </c>
       <c r="E40" t="b">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>2.24</v>
+        <v>24.21</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>-0.44</v>
+        <v>-6.53</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BAFNAPH</t>
+          <t>KNAGRI</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>106.15</v>
+        <v>188.75</v>
       </c>
       <c r="C41" t="n">
-        <v>108</v>
+        <v>194.99</v>
       </c>
       <c r="D41" t="n">
-        <v>1.74</v>
+        <v>3.31</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>108.29</v>
+        <v>184.68</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>0.27</v>
+        <v>-5.29</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HINDOILEXP</t>
+          <t>GTL</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>130.88</v>
+        <v>6.99</v>
       </c>
       <c r="C42" t="n">
-        <v>133</v>
+        <v>7.22</v>
       </c>
       <c r="D42" t="n">
-        <v>1.62</v>
+        <v>3.29</v>
       </c>
       <c r="E42" t="b">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>136.79</v>
+        <v>6.95</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>2.85</v>
+        <v>-3.74</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>KEEPLEARN</t>
+          <t>PRABHA</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.96</v>
+        <v>169.21</v>
       </c>
       <c r="C43" t="n">
-        <v>1.99</v>
+        <v>174.7</v>
       </c>
       <c r="D43" t="n">
-        <v>1.53</v>
+        <v>3.24</v>
       </c>
       <c r="E43" t="b">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>1.95</v>
+        <v>167.84</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>-2.01</v>
+        <v>-3.93</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CEDAAR</t>
+          <t>MAHESHWARI</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>30</v>
+        <v>41.5</v>
       </c>
       <c r="C44" t="n">
-        <v>30.45</v>
+        <v>42.75</v>
       </c>
       <c r="D44" t="n">
-        <v>1.5</v>
+        <v>3.01</v>
       </c>
       <c r="E44" t="b">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>28.5</v>
+        <v>39.67</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>-6.4</v>
+        <v>-7.2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HEXATRADEX</t>
+          <t>LIBAS</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>160.11</v>
+        <v>10.08</v>
       </c>
       <c r="C45" t="n">
-        <v>162.5</v>
+        <v>10.38</v>
       </c>
       <c r="D45" t="n">
-        <v>1.49</v>
+        <v>2.98</v>
       </c>
       <c r="E45" t="b">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>160</v>
+        <v>10.14</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>-1.54</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SOUTHWEST</t>
+          <t>ROML</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>182.2</v>
+        <v>41.75</v>
       </c>
       <c r="C46" t="n">
-        <v>184.9</v>
+        <v>42.99</v>
       </c>
       <c r="D46" t="n">
-        <v>1.48</v>
+        <v>2.97</v>
       </c>
       <c r="E46" t="b">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>183</v>
+        <v>41.51</v>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>-1.03</v>
+        <v>-3.44</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>LAKPRE</t>
+          <t>VHL</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4.97</v>
+        <v>3106.8</v>
       </c>
       <c r="C47" t="n">
-        <v>5.04</v>
+        <v>3197</v>
       </c>
       <c r="D47" t="n">
-        <v>1.41</v>
+        <v>2.9</v>
       </c>
       <c r="E47" t="b">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>5.21</v>
+        <v>3111.5</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>3.37</v>
+        <v>-2.67</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BALAXI</t>
+          <t>IDEAFORGE</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>19.73</v>
+        <v>441.3</v>
       </c>
       <c r="C48" t="n">
-        <v>20</v>
+        <v>454</v>
       </c>
       <c r="D48" t="n">
-        <v>1.37</v>
+        <v>2.88</v>
       </c>
       <c r="E48" t="b">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>19</v>
+        <v>458.65</v>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>-5</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>IL&amp;FSTRANS</t>
+          <t>ESSARSHPNG</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2.45</v>
+        <v>24.3</v>
       </c>
       <c r="C49" t="n">
-        <v>2.48</v>
+        <v>25</v>
       </c>
       <c r="D49" t="n">
-        <v>1.22</v>
+        <v>2.88</v>
       </c>
       <c r="E49" t="b">
         <v>0</v>
       </c>
-      <c r="F49" t="inlineStr"/>
+      <c r="F49" t="n">
+        <v>23.78</v>
+      </c>
       <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="H49" t="n">
+        <v>-4.88</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ALPA</t>
+          <t>MANOMAY</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>66.01000000000001</v>
+        <v>216.85</v>
       </c>
       <c r="C50" t="n">
-        <v>66.8</v>
+        <v>222.99</v>
       </c>
       <c r="D50" t="n">
-        <v>1.2</v>
+        <v>2.83</v>
       </c>
       <c r="E50" t="b">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>64.09999999999999</v>
+        <v>217</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>-4.04</v>
+        <v>-2.69</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DJML</t>
+          <t>GVPTECH</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>90.51000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="C51" t="n">
-        <v>91.5</v>
+        <v>6.99</v>
       </c>
       <c r="D51" t="n">
-        <v>1.09</v>
+        <v>2.79</v>
       </c>
       <c r="E51" t="b">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>89</v>
+        <v>6.57</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>-2.73</v>
+        <v>-6.01</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PGHL</t>
+          <t>NITIRAJ</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4900.5</v>
+        <v>207.35</v>
       </c>
       <c r="C52" t="n">
-        <v>4949</v>
+        <v>212.95</v>
       </c>
       <c r="D52" t="n">
-        <v>0.99</v>
+        <v>2.7</v>
       </c>
       <c r="E52" t="b">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>4980.1</v>
+        <v>202.05</v>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>0.63</v>
+        <v>-5.12</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DURLAX</t>
+          <t>ORTINGLOBE</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>48.25</v>
+        <v>16.37</v>
       </c>
       <c r="C53" t="n">
-        <v>48.7</v>
+        <v>16.8</v>
       </c>
       <c r="D53" t="n">
-        <v>0.93</v>
+        <v>2.63</v>
       </c>
       <c r="E53" t="b">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>44.8</v>
+        <v>15.75</v>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>-8.01</v>
+        <v>-6.25</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BLBLIMITED</t>
+          <t>DJML</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>17.74</v>
+        <v>88.55</v>
       </c>
       <c r="C54" t="n">
-        <v>17.9</v>
+        <v>90.87</v>
       </c>
       <c r="D54" t="n">
-        <v>0.9</v>
+        <v>2.62</v>
       </c>
       <c r="E54" t="b">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>17.1</v>
+        <v>88.43000000000001</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>-4.47</v>
+        <v>-2.69</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NGIL</t>
+          <t>DIGJAMLMTD</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>25.78</v>
+        <v>45.82</v>
       </c>
       <c r="C55" t="n">
-        <v>25.99</v>
+        <v>46.99</v>
       </c>
       <c r="D55" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.55</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>24.75</v>
+        <v>42.99</v>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>-4.77</v>
+        <v>-8.51</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>HILTON</t>
+          <t>TTKHLTCARE</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>17.82</v>
+        <v>892.8</v>
       </c>
       <c r="C56" t="n">
-        <v>17.96</v>
+        <v>915</v>
       </c>
       <c r="D56" t="n">
-        <v>0.79</v>
+        <v>2.49</v>
       </c>
       <c r="E56" t="b">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>17.68</v>
+        <v>897.9</v>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>-1.56</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MODIRUBBER</t>
+          <t>SAURASHCEM</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>117.12</v>
+        <v>63.29</v>
       </c>
       <c r="C57" t="n">
-        <v>117.99</v>
+        <v>64.8</v>
       </c>
       <c r="D57" t="n">
-        <v>0.74</v>
+        <v>2.39</v>
       </c>
       <c r="E57" t="b">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>112</v>
+        <v>63.45</v>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>-5.08</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MTEDUCARE</t>
+          <t>ABAN</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1.38</v>
+        <v>19.27</v>
       </c>
       <c r="C58" t="n">
-        <v>1.39</v>
+        <v>19.73</v>
       </c>
       <c r="D58" t="n">
-        <v>0.72</v>
+        <v>2.39</v>
       </c>
       <c r="E58" t="b">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>1.44</v>
+        <v>20.18</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>3.6</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ASPINWALL</t>
+          <t>DSFCL</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>215.57</v>
+        <v>33.19</v>
       </c>
       <c r="C59" t="n">
-        <v>217</v>
+        <v>33.98</v>
       </c>
       <c r="D59" t="n">
-        <v>0.66</v>
+        <v>2.38</v>
       </c>
       <c r="E59" t="b">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>211.9</v>
+        <v>29.42</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>-2.35</v>
+        <v>-13.42</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ORTINGLOBE</t>
+          <t>CORDSCABLE</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>17.19</v>
+        <v>167.26</v>
       </c>
       <c r="C60" t="n">
-        <v>17.3</v>
+        <v>170.95</v>
       </c>
       <c r="D60" t="n">
-        <v>0.64</v>
+        <v>2.21</v>
       </c>
       <c r="E60" t="b">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>16.37</v>
+        <v>165.95</v>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>-5.38</v>
+        <v>-2.92</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>HBSL</t>
+          <t>VAISHALI</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>55.66</v>
+        <v>6.79</v>
       </c>
       <c r="C61" t="n">
-        <v>56</v>
+        <v>6.94</v>
       </c>
       <c r="D61" t="n">
-        <v>0.61</v>
+        <v>2.21</v>
       </c>
       <c r="E61" t="b">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>52.88</v>
+        <v>6.82</v>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>-5.57</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ELGNZ</t>
+          <t>PRUDMOULI</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>67.8</v>
+        <v>17.61</v>
       </c>
       <c r="C62" t="n">
-        <v>68.2</v>
+        <v>17.98</v>
       </c>
       <c r="D62" t="n">
-        <v>0.59</v>
+        <v>2.1</v>
       </c>
       <c r="E62" t="b">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>65</v>
+        <v>16.18</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>-4.69</v>
+        <v>-10.01</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STEELCITY</t>
+          <t>DAMODARIND</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>87.40000000000001</v>
+        <v>24.38</v>
       </c>
       <c r="C63" t="n">
-        <v>87.90000000000001</v>
+        <v>24.89</v>
       </c>
       <c r="D63" t="n">
-        <v>0.57</v>
+        <v>2.09</v>
       </c>
       <c r="E63" t="b">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>88.84999999999999</v>
+        <v>23.9</v>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>1.08</v>
+        <v>-3.98</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>VISASTEEL</t>
+          <t>SADBHIN</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>38.29</v>
+        <v>3.38</v>
       </c>
       <c r="C64" t="n">
-        <v>38.48</v>
+        <v>3.45</v>
       </c>
       <c r="D64" t="n">
-        <v>0.5</v>
+        <v>2.07</v>
       </c>
       <c r="E64" t="b">
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>37.42</v>
+        <v>3.22</v>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>-2.75</v>
+        <v>-6.67</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SPLPETRO</t>
+          <t>UNIINFO</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>716.8</v>
+        <v>13.84</v>
       </c>
       <c r="C65" t="n">
-        <v>720.3</v>
+        <v>14.12</v>
       </c>
       <c r="D65" t="n">
-        <v>0.49</v>
+        <v>2.02</v>
       </c>
       <c r="E65" t="b">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>675</v>
+        <v>13.04</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>-6.29</v>
+        <v>-7.65</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>RADAAN</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>603.8</v>
+        <v>2.99</v>
       </c>
       <c r="C66" t="n">
-        <v>606</v>
+        <v>3.05</v>
       </c>
       <c r="D66" t="n">
-        <v>0.36</v>
+        <v>2.01</v>
       </c>
       <c r="E66" t="b">
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>617</v>
+        <v>2.97</v>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>1.82</v>
+        <v>-2.62</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>EMBDL</t>
+          <t>STARPAPER</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>60.41</v>
+        <v>136.66</v>
       </c>
       <c r="C67" t="n">
-        <v>60.6</v>
+        <v>139.39</v>
       </c>
       <c r="D67" t="n">
-        <v>0.31</v>
+        <v>2</v>
       </c>
       <c r="E67" t="b">
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>59.1</v>
+        <v>136.7</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>-2.48</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BILVYAPAR</t>
+          <t>EMKAY</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>6.79</v>
+        <v>226.29</v>
       </c>
       <c r="C68" t="n">
-        <v>6.81</v>
+        <v>230.8</v>
       </c>
       <c r="D68" t="n">
-        <v>0.29</v>
+        <v>1.99</v>
       </c>
       <c r="E68" t="b">
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>6.51</v>
+        <v>227.52</v>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>-4.41</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>INDIGRID</t>
+          <t>DBOL</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>166.27</v>
+        <v>100.01</v>
       </c>
       <c r="C69" t="n">
-        <v>166.7</v>
+        <v>102</v>
       </c>
       <c r="D69" t="n">
-        <v>0.26</v>
+        <v>1.99</v>
       </c>
       <c r="E69" t="b">
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>166.75</v>
+        <v>103.98</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>0.03</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ABCOTS</t>
+          <t>OILCOUNTUB</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>409.05</v>
+        <v>47.57</v>
       </c>
       <c r="C70" t="n">
-        <v>409.9</v>
+        <v>48.51</v>
       </c>
       <c r="D70" t="n">
-        <v>0.21</v>
+        <v>1.98</v>
       </c>
       <c r="E70" t="b">
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>411</v>
+        <v>50.83</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>0.27</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>GOLDENTOBC</t>
+          <t>RKDL</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>29.84</v>
+        <v>17.65</v>
       </c>
       <c r="C71" t="n">
-        <v>29.9</v>
+        <v>18</v>
       </c>
       <c r="D71" t="n">
-        <v>0.2</v>
+        <v>1.98</v>
       </c>
       <c r="E71" t="b">
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>28.35</v>
+        <v>17.6</v>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>-5.18</v>
+        <v>-2.22</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SAURASHCEM</t>
+          <t>LATTEYS</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>65.54000000000001</v>
+        <v>21.18</v>
       </c>
       <c r="C72" t="n">
-        <v>65.65000000000001</v>
+        <v>21.6</v>
       </c>
       <c r="D72" t="n">
-        <v>0.17</v>
+        <v>1.98</v>
       </c>
       <c r="E72" t="b">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>63</v>
+        <v>20.31</v>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>-4.04</v>
+        <v>-5.97</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>GHCL</t>
+          <t>MCL</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>479.2</v>
+        <v>66.67</v>
       </c>
       <c r="C73" t="n">
-        <v>480</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="D73" t="n">
-        <v>0.17</v>
+        <v>1.98</v>
       </c>
       <c r="E73" t="b">
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>471.4</v>
+        <v>70</v>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>-1.79</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>GOLDENTOBC</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>514.65</v>
+        <v>28.44</v>
       </c>
       <c r="C74" t="n">
-        <v>515</v>
+        <v>29</v>
       </c>
       <c r="D74" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.97</v>
       </c>
       <c r="E74" t="b">
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>532.2</v>
+        <v>28.99</v>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>3.34</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>VSTTILLERS</t>
+          <t>SAMPANN</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>5776</v>
+        <v>28.61</v>
       </c>
       <c r="C75" t="n">
-        <v>5779.5</v>
+        <v>29.17</v>
       </c>
       <c r="D75" t="n">
-        <v>0.06</v>
+        <v>1.96</v>
       </c>
       <c r="E75" t="b">
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>5648.5</v>
+        <v>27.98</v>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>-2.27</v>
+        <v>-4.08</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ORIENTLTD</t>
+          <t>HINDOILEXP</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>64.87</v>
+        <v>136.64</v>
       </c>
       <c r="C76" t="n">
-        <v>64.90000000000001</v>
+        <v>139.31</v>
       </c>
       <c r="D76" t="n">
-        <v>0.05</v>
+        <v>1.95</v>
       </c>
       <c r="E76" t="b">
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>64.59999999999999</v>
+        <v>140.16</v>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>-0.46</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>SICALLOG</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>3353.5</v>
+        <v>66.23</v>
       </c>
       <c r="C77" t="n">
-        <v>3354.9</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="D77" t="n">
-        <v>0.04</v>
+        <v>1.93</v>
       </c>
       <c r="E77" t="b">
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>3466</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>3.31</v>
+        <v>-5.05</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ZODIACLOTH</t>
+          <t>HMVL</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>80.5</v>
+        <v>66.72</v>
       </c>
       <c r="C78" t="n">
-        <v>80.51000000000001</v>
+        <v>68</v>
       </c>
       <c r="D78" t="n">
-        <v>0.01</v>
+        <v>1.92</v>
       </c>
       <c r="E78" t="b">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>77.90000000000001</v>
+        <v>67.69</v>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>-3.24</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BHADORA</t>
+          <t>INNOVANA</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>64.45</v>
+        <v>392.55</v>
       </c>
       <c r="C79" t="n">
-        <v>64.45</v>
+        <v>400</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="E79" t="b">
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>61.1</v>
+        <v>384.9</v>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>-5.2</v>
+        <v>-3.78</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>VINYLINDIA</t>
+          <t>LYKALABS</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>209.89</v>
+        <v>60.69</v>
       </c>
       <c r="C80" t="n">
-        <v>209.89</v>
+        <v>61.8</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="E80" t="b">
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>205</v>
+        <v>60.64</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>-2.33</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>HTMEDIA</t>
+          <t>IMPEXFERRO</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>21.82</v>
+        <v>1.71</v>
       </c>
       <c r="C81" t="n">
-        <v>21.82</v>
+        <v>1.74</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="E81" t="b">
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>20.7</v>
+        <v>1.67</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>-5.13</v>
+        <v>-4.02</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>UMESLTD</t>
+          <t>USK</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>4.1</v>
+        <v>27.51</v>
       </c>
       <c r="C82" t="n">
-        <v>4.1</v>
+        <v>27.99</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="E82" t="b">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>4.05</v>
+        <v>27.65</v>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>-1.22</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FILATFASH</t>
+          <t>WINSOME</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.22</v>
+        <v>1.74</v>
       </c>
       <c r="C83" t="n">
-        <v>0.22</v>
+        <v>1.77</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="E83" t="b">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>0.21</v>
+        <v>1.77</v>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>-4.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>GAYAPROJ</t>
+          <t>ANSALAPI</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>12.7</v>
+        <v>4.07</v>
       </c>
       <c r="C84" t="n">
-        <v>12.7</v>
+        <v>4.14</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="E84" t="b">
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>12.7</v>
+        <v>4.15</v>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SPCENET</t>
+          <t>PANACEABIO</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>5.03</v>
+        <v>326.4</v>
       </c>
       <c r="C85" t="n">
-        <v>5.03</v>
+        <v>332</v>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="E85" t="b">
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>4.89</v>
+        <v>323.6</v>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>-2.78</v>
+        <v>-2.53</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>HALEOSLABS</t>
+          <t>ARCHIES</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1260.3</v>
+        <v>14.7</v>
       </c>
       <c r="C86" t="n">
-        <v>1260.3</v>
+        <v>14.95</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="E86" t="b">
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>1251</v>
+        <v>14.55</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>-0.74</v>
+        <v>-2.68</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TECHLABS</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>195</v>
+        <v>282.2</v>
       </c>
       <c r="C87" t="n">
-        <v>195</v>
+        <v>287</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="E87" t="b">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>199.9</v>
+        <v>281.6</v>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>2.51</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ONECAP-RE</t>
+          <t>IL&amp;FSTRANS</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.2</v>
+        <v>2.35</v>
       </c>
       <c r="C88" t="n">
-        <v>0.2</v>
+        <v>2.39</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="E88" t="b">
         <v>0</v>
       </c>
-      <c r="F88" t="n">
-        <v>0.18</v>
-      </c>
+      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
-      <c r="H88" t="n">
-        <v>-10</v>
-      </c>
+      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MARUSHIKA</t>
+          <t>ADVANIHOTR</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>103.15</v>
+        <v>54.07</v>
       </c>
       <c r="C89" t="n">
-        <v>103.15</v>
+        <v>54.98</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="E89" t="b">
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>101.5</v>
+        <v>53.28</v>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>-1.6</v>
+        <v>-3.09</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>IMPEXFERRO</t>
+          <t>HMT</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1.7</v>
+        <v>63.93</v>
       </c>
       <c r="C90" t="n">
-        <v>1.7</v>
+        <v>65</v>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="E90" t="b">
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>1.69</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>-0.59</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>GOLDTECH</t>
+          <t>DEVIT</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>39.8</v>
+        <v>24.08</v>
       </c>
       <c r="C91" t="n">
-        <v>39.8</v>
+        <v>24.48</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="E91" t="b">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>39</v>
+        <v>27.25</v>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>-2.01</v>
+        <v>11.32</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ANTGRAPHIC</t>
+          <t>BEDMUTHA</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.87</v>
+        <v>132.51</v>
       </c>
       <c r="C92" t="n">
-        <v>0.87</v>
+        <v>134.7</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="E92" t="b">
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>0.86</v>
+        <v>131.2</v>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
-        <v>-1.15</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FMNL</t>
+          <t>KRISHIVAL</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>8.300000000000001</v>
+        <v>315.15</v>
       </c>
       <c r="C93" t="n">
-        <v>8.300000000000001</v>
+        <v>320</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="E93" t="b">
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>8.640000000000001</v>
+        <v>319.5</v>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
-        <v>4.1</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PRAKASHSTL</t>
+          <t>KOTHARIPRO</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>4.37</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="C94" t="n">
-        <v>4.37</v>
+        <v>65.7</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="E94" t="b">
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>4.18</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>-4.35</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ARCHIES</t>
+          <t>STEL</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>15.82</v>
+        <v>510.2</v>
       </c>
       <c r="C95" t="n">
-        <v>15.82</v>
+        <v>518</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="E95" t="b">
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>15.03</v>
+        <v>502.3</v>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>-4.99</v>
+        <v>-3.03</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>UNIDT</t>
+          <t>DBSTOCKBRO</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>174.67</v>
+        <v>24.89</v>
       </c>
       <c r="C96" t="n">
-        <v>174.67</v>
+        <v>25.25</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="E96" t="b">
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>171.99</v>
+        <v>24.8</v>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>-1.53</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SAHANA</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1008.85</v>
+        <v>488.05</v>
       </c>
       <c r="C97" t="n">
-        <v>1008.85</v>
+        <v>495.05</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="E97" t="b">
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>1001</v>
+        <v>492.85</v>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>-0.78</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MYMUDRA</t>
+          <t>URAVIDEF</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>77.09999999999999</v>
+        <v>140.86</v>
       </c>
       <c r="C98" t="n">
-        <v>77.09999999999999</v>
+        <v>142.79</v>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="E98" t="b">
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>75</v>
+        <v>139.97</v>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>-2.72</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>GLOBALVECT</t>
+          <t>CORALFINAC</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>163.21</v>
+        <v>33.04</v>
       </c>
       <c r="C99" t="n">
-        <v>163.21</v>
+        <v>33.49</v>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="E99" t="b">
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>155.42</v>
+        <v>32.54</v>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
-        <v>-4.77</v>
+        <v>-2.84</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ANKITMETAL</t>
+          <t>MBAPL</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1.66</v>
+        <v>450.25</v>
       </c>
       <c r="C100" t="n">
-        <v>1.66</v>
+        <v>456.35</v>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="E100" t="b">
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>1.72</v>
+        <v>456.2</v>
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>3.61</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>TSFINV</t>
+          <t>TIL</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>402.15</v>
+        <v>213.03</v>
       </c>
       <c r="C101" t="n">
-        <v>402.15</v>
+        <v>215.89</v>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="E101" t="b">
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>380.1</v>
+        <v>210.32</v>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>-5.48</v>
+        <v>-2.58</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>UNIINFO</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>14.04</v>
+        <v>453.95</v>
       </c>
       <c r="C102" t="n">
-        <v>14.04</v>
+        <v>460</v>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="E102" t="b">
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>13.94</v>
+        <v>456</v>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>-0.71</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>RADAAN</t>
+          <t>KRISHNADEF</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>3.12</v>
+        <v>1126.1</v>
       </c>
       <c r="C103" t="n">
-        <v>3.12</v>
+        <v>1140</v>
       </c>
       <c r="D103" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="E103" t="b">
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>3.05</v>
+        <v>1151.2</v>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>-2.24</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>FINBUD</t>
+          <t>TICL</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>105</v>
+        <v>26.47</v>
       </c>
       <c r="C104" t="n">
-        <v>105</v>
+        <v>26.79</v>
       </c>
       <c r="D104" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="E104" t="b">
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>100.6</v>
+        <v>25.63</v>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
-        <v>-4.19</v>
+        <v>-4.33</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>PRAXIS</t>
+          <t>VIDHIING</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>7.79</v>
+        <v>302.4</v>
       </c>
       <c r="C105" t="n">
-        <v>7.79</v>
+        <v>306</v>
       </c>
       <c r="D105" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="E105" t="b">
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>7.41</v>
+        <v>300.05</v>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>-4.88</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>LYPSAGEMS</t>
+          <t>GNA</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>5.22</v>
+        <v>428.85</v>
       </c>
       <c r="C106" t="n">
-        <v>5.22</v>
+        <v>433.95</v>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="E106" t="b">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>5.1</v>
+        <v>423.6</v>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
-        <v>-2.3</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>TRIGYN</t>
+          <t>SHRIRAMPPS</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>52.11</v>
+        <v>76.45</v>
       </c>
       <c r="C107" t="n">
-        <v>52.11</v>
+        <v>77.3</v>
       </c>
       <c r="D107" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="E107" t="b">
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>51.25</v>
+        <v>74.52</v>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>-1.65</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AILIMITED</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>36.55</v>
+        <v>0.99</v>
       </c>
       <c r="C108" t="n">
-        <v>36.55</v>
+        <v>1</v>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="E108" t="b">
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>38.35</v>
+        <v>1</v>
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
-        <v>4.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ENSER</t>
+          <t>INTENTECH</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>12</v>
+        <v>97.77</v>
       </c>
       <c r="C109" t="n">
-        <v>12</v>
+        <v>98.75</v>
       </c>
       <c r="D109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E109" t="b">
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>12</v>
+        <v>96.51000000000001</v>
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>0</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>TARAPUR</t>
+          <t>SWANDEF</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>25.34</v>
+        <v>1781.4</v>
       </c>
       <c r="C110" t="n">
-        <v>25.34</v>
+        <v>1799.3</v>
       </c>
       <c r="D110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E110" t="b">
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>25.15</v>
+        <v>1750</v>
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
-        <v>-0.75</v>
+        <v>-2.74</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>GICL</t>
+          <t>ASTRAMICRO</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>48.4</v>
+        <v>982.4</v>
       </c>
       <c r="C111" t="n">
-        <v>48.4</v>
+        <v>992.15</v>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="E111" t="b">
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>47.8</v>
+        <v>999</v>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>-1.24</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>VIVIMEDLAB</t>
+          <t>SOLARINDS</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>7.57</v>
+        <v>13989</v>
       </c>
       <c r="C112" t="n">
-        <v>7.57</v>
+        <v>14124</v>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="E112" t="b">
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>7.2</v>
+        <v>14338</v>
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
-        <v>-4.89</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SAHAJ</t>
+          <t>VIJIFIN</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>4.85</v>
+        <v>2.07</v>
       </c>
       <c r="C113" t="n">
-        <v>4.85</v>
+        <v>2.09</v>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="E113" t="b">
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>4.65</v>
+        <v>2.05</v>
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>-4.12</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>DHARAN</t>
+          <t>ORIENTCER</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.17</v>
+        <v>37.1</v>
       </c>
       <c r="C114" t="n">
-        <v>0.17</v>
+        <v>37.45</v>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E114" t="b">
         <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>0.18</v>
+        <v>36.43</v>
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
-        <v>5.88</v>
+        <v>-2.72</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SGIL</t>
+          <t>MIRZAINT</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>522.4</v>
+        <v>32.99</v>
       </c>
       <c r="C115" t="n">
-        <v>522.4</v>
+        <v>33.29</v>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="E115" t="b">
         <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>513.25</v>
+        <v>32.68</v>
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>-1.75</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SAFARI</t>
+          <t>MANAKSTEEL</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>1797.2</v>
+        <v>55.5</v>
       </c>
       <c r="C116" t="n">
-        <v>1797.2</v>
+        <v>56</v>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="E116" t="b">
         <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>1741.8</v>
+        <v>55.13</v>
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
-        <v>-3.08</v>
+        <v>-1.55</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ISHAN</t>
+          <t>LASA</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.65</v>
+        <v>7.78</v>
       </c>
       <c r="C117" t="n">
-        <v>0.65</v>
+        <v>7.85</v>
       </c>
       <c r="D117" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="E117" t="b">
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>0.6</v>
+        <v>7.43</v>
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>-7.69</v>
+        <v>-5.35</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SHRIRAMPPS</t>
+          <t>FLFL</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>79.34999999999999</v>
+        <v>1.24</v>
       </c>
       <c r="C118" t="n">
-        <v>79.34999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="D118" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E118" t="b">
         <v>0</v>
       </c>
       <c r="F118" t="n">
-        <v>78</v>
+        <v>1.3</v>
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
-        <v>-1.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>DELTAMAGNT</t>
+          <t>EIFFL</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>61.04</v>
+        <v>230.14</v>
       </c>
       <c r="C119" t="n">
-        <v>61.04</v>
+        <v>231.91</v>
       </c>
       <c r="D119" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="E119" t="b">
         <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>57.98</v>
+        <v>232.32</v>
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
-        <v>-5.01</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>PREMIER</t>
+          <t>EMAMIPAP</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>2.99</v>
+        <v>81.37</v>
       </c>
       <c r="C120" t="n">
-        <v>2.99</v>
+        <v>82</v>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="E120" t="b">
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>2.87</v>
+        <v>81</v>
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
-        <v>-4.01</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MEP</t>
+          <t>SUNDARAM</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="C121" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="D121" t="n">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="E121" t="b">
         <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>0.99</v>
+        <v>1.34</v>
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
-        <v>-1.98</v>
+        <v>-2.19</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>RELCHEMQ</t>
+          <t>IMPAL</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>122.33</v>
+        <v>1024.5</v>
       </c>
       <c r="C122" t="n">
-        <v>122.33</v>
+        <v>1032</v>
       </c>
       <c r="D122" t="n">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="E122" t="b">
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>118.03</v>
+        <v>1029.9</v>
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
-        <v>-3.52</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>JAYKAY</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>55.99</v>
+        <v>145.19</v>
       </c>
       <c r="C123" t="n">
-        <v>55.99</v>
+        <v>146.2</v>
       </c>
       <c r="D123" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="E123" t="b">
         <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>55.07</v>
+        <v>143.77</v>
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>-1.64</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>BANG</t>
+          <t>MVKAGRO</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>41.52</v>
+        <v>553.15</v>
       </c>
       <c r="C124" t="n">
-        <v>41.52</v>
+        <v>557</v>
       </c>
       <c r="D124" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="E124" t="b">
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>40.06</v>
+        <v>542.5</v>
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
-        <v>-3.52</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ZENITHSTL</t>
+          <t>ANANTAM</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>5.68</v>
+        <v>102.61</v>
       </c>
       <c r="C125" t="n">
-        <v>5.68</v>
+        <v>103.31</v>
       </c>
       <c r="D125" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="E125" t="b">
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>5.83</v>
+        <v>102.8</v>
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>2.64</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>AHLEAST</t>
+          <t>ESFL</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>160.77</v>
+        <v>141.1</v>
       </c>
       <c r="C126" t="n">
-        <v>160.77</v>
+        <v>142</v>
       </c>
       <c r="D126" t="n">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="E126" t="b">
         <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>160.65</v>
+        <v>148.15</v>
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
-        <v>-0.07000000000000001</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>LPDC</t>
+          <t>SAWALIYA</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>6.08</v>
+        <v>304.05</v>
       </c>
       <c r="C127" t="n">
-        <v>6.08</v>
+        <v>305.95</v>
       </c>
       <c r="D127" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="E127" t="b">
         <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>5.83</v>
+        <v>305</v>
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
-        <v>-4.11</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ALLDIGI</t>
+          <t>INDUSINVIT</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>823.55</v>
+        <v>126.69</v>
       </c>
       <c r="C128" t="n">
-        <v>823.55</v>
+        <v>127.46</v>
       </c>
       <c r="D128" t="n">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="E128" t="b">
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>803.05</v>
+        <v>125.01</v>
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
-        <v>-2.49</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>AFSL</t>
+          <t>ARROWGREEN</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>201</v>
+        <v>396.2</v>
       </c>
       <c r="C129" t="n">
-        <v>201</v>
+        <v>398.6</v>
       </c>
       <c r="D129" t="n">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="E129" t="b">
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>201</v>
+        <v>398.05</v>
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>OILCOUNTUB</t>
+          <t>DICIND</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>47.36</v>
+        <v>526.85</v>
       </c>
       <c r="C130" t="n">
-        <v>47.36</v>
+        <v>530</v>
       </c>
       <c r="D130" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E130" t="b">
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>47.8</v>
+        <v>510.05</v>
       </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
-        <v>0.93</v>
+        <v>-3.76</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>RUCHINFRA</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>5.74</v>
+        <v>362.85</v>
       </c>
       <c r="C131" t="n">
-        <v>5.74</v>
+        <v>365</v>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="E131" t="b">
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>5.73</v>
+        <v>360.2</v>
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
-        <v>-0.17</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>MADHUCON</t>
+          <t>VARDHACRLC</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>4.73</v>
+        <v>33.79</v>
       </c>
       <c r="C132" t="n">
-        <v>4.73</v>
+        <v>33.99</v>
       </c>
       <c r="D132" t="n">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="E132" t="b">
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>4.5</v>
+        <v>33.47</v>
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
-        <v>-4.86</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>USK</t>
+          <t>BROOKS</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>28.67</v>
+        <v>62.63</v>
       </c>
       <c r="C133" t="n">
-        <v>28.67</v>
+        <v>63</v>
       </c>
       <c r="D133" t="n">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="E133" t="b">
         <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>27.77</v>
+        <v>62.73</v>
       </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
-        <v>-3.14</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MITTAL</t>
+          <t>BOSCH-HCIL</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>1</v>
+        <v>1367.5</v>
       </c>
       <c r="C134" t="n">
-        <v>1</v>
+        <v>1375.5</v>
       </c>
       <c r="D134" t="n">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="E134" t="b">
         <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>0.9399999999999999</v>
+        <v>1354.1</v>
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
-        <v>-6</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>TIL</t>
+          <t>REPRO</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>208.98</v>
+        <v>382.55</v>
       </c>
       <c r="C135" t="n">
-        <v>208.98</v>
+        <v>384.75</v>
       </c>
       <c r="D135" t="n">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="E135" t="b">
         <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>213</v>
+        <v>381.45</v>
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
-        <v>1.92</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>DICIND</t>
+          <t>JLHL</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>526</v>
+        <v>1273.3</v>
       </c>
       <c r="C136" t="n">
-        <v>526</v>
+        <v>1280</v>
       </c>
       <c r="D136" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="E136" t="b">
         <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>521.5</v>
+        <v>1255.9</v>
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
-        <v>-0.86</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SYSTMTXC</t>
+          <t>ASIANHOTNR</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>75.45999999999999</v>
+        <v>278.55</v>
       </c>
       <c r="C137" t="n">
-        <v>75.45</v>
+        <v>280</v>
       </c>
       <c r="D137" t="n">
-        <v>-0.01</v>
+        <v>0.52</v>
       </c>
       <c r="E137" t="b">
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>72.20999999999999</v>
+        <v>269</v>
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
-        <v>-4.29</v>
+        <v>-3.93</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>RVHL</t>
+          <t>HITECHGEAR</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>41.51</v>
+        <v>620.85</v>
       </c>
       <c r="C138" t="n">
-        <v>41.5</v>
+        <v>624</v>
       </c>
       <c r="D138" t="n">
-        <v>-0.02</v>
+        <v>0.51</v>
       </c>
       <c r="E138" t="b">
         <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>38.32</v>
+        <v>612.5</v>
       </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
-        <v>-7.66</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>TCC</t>
+          <t>IRISDOREME</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>447.1</v>
+        <v>31.5</v>
       </c>
       <c r="C139" t="n">
-        <v>447</v>
+        <v>31.66</v>
       </c>
       <c r="D139" t="n">
-        <v>-0.02</v>
+        <v>0.51</v>
       </c>
       <c r="E139" t="b">
         <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>428.35</v>
+        <v>31.62</v>
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
-        <v>-4.17</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>DPABHUSHAN</t>
+          <t>INDOUS</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1186.2</v>
+        <v>140.71</v>
       </c>
       <c r="C140" t="n">
-        <v>1185.7</v>
+        <v>141.41</v>
       </c>
       <c r="D140" t="n">
-        <v>-0.04</v>
+        <v>0.5</v>
       </c>
       <c r="E140" t="b">
         <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>1158.9</v>
+        <v>132.23</v>
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
-        <v>-2.26</v>
+        <v>-6.49</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>SMARTWORKS</t>
+          <t>AYMSYNTEX</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>410.05</v>
+        <v>200.56</v>
       </c>
       <c r="C141" t="n">
-        <v>409.9</v>
+        <v>201.57</v>
       </c>
       <c r="D141" t="n">
-        <v>-0.04</v>
+        <v>0.5</v>
       </c>
       <c r="E141" t="b">
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>395</v>
+        <v>201</v>
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
-        <v>-3.64</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>STANLEY</t>
+          <t>CHEMPLASTS</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>162.07</v>
+        <v>238.48</v>
       </c>
       <c r="C142" t="n">
-        <v>162</v>
+        <v>239.68</v>
       </c>
       <c r="D142" t="n">
-        <v>-0.04</v>
+        <v>0.5</v>
       </c>
       <c r="E142" t="b">
         <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>155.8</v>
+        <v>226.41</v>
       </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
-        <v>-3.83</v>
+        <v>-5.54</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>CAPITALSFB</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>262.1</v>
+        <v>3951.6</v>
       </c>
       <c r="C143" t="n">
-        <v>262</v>
+        <v>3971.3</v>
       </c>
       <c r="D143" t="n">
-        <v>-0.04</v>
+        <v>0.5</v>
       </c>
       <c r="E143" t="b">
         <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>258.55</v>
+        <v>3902.4</v>
       </c>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
-        <v>-1.32</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>RKDL</t>
+          <t>BDL</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>19.09</v>
+        <v>1268</v>
       </c>
       <c r="C144" t="n">
-        <v>19.08</v>
+        <v>1274.2</v>
       </c>
       <c r="D144" t="n">
-        <v>-0.05</v>
+        <v>0.49</v>
       </c>
       <c r="E144" t="b">
         <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>17.7</v>
+        <v>1284.4</v>
       </c>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
-        <v>-7.23</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>JINDRILL</t>
+          <t>TARAPUR</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>445.3</v>
+        <v>24.99</v>
       </c>
       <c r="C145" t="n">
-        <v>445.05</v>
+        <v>25.11</v>
       </c>
       <c r="D145" t="n">
-        <v>-0.06</v>
+        <v>0.48</v>
       </c>
       <c r="E145" t="b">
         <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>518</v>
+        <v>24.84</v>
       </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
-        <v>16.39</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>KRISHIVAL</t>
+          <t>PARASPETRO</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>313.25</v>
+        <v>2.07</v>
       </c>
       <c r="C146" t="n">
-        <v>313</v>
+        <v>2.08</v>
       </c>
       <c r="D146" t="n">
-        <v>-0.08</v>
+        <v>0.48</v>
       </c>
       <c r="E146" t="b">
         <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>321.5</v>
+        <v>2.09</v>
       </c>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
-        <v>2.72</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>SGL</t>
+          <t>PTL</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>12.58</v>
+        <v>38.07</v>
       </c>
       <c r="C147" t="n">
-        <v>12.57</v>
+        <v>38.25</v>
       </c>
       <c r="D147" t="n">
-        <v>-0.08</v>
+        <v>0.47</v>
       </c>
       <c r="E147" t="b">
         <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>12</v>
+        <v>37.78</v>
       </c>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
-        <v>-4.53</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>VINEETLAB</t>
+          <t>AKG</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>29.53</v>
+        <v>10.65</v>
       </c>
       <c r="C148" t="n">
-        <v>29.5</v>
+        <v>10.7</v>
       </c>
       <c r="D148" t="n">
-        <v>-0.1</v>
+        <v>0.47</v>
       </c>
       <c r="E148" t="b">
         <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>29.5</v>
+        <v>10.7</v>
       </c>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
@@ -4279,1379 +4279,1379 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>RAMANEWS</t>
+          <t>CHEMCON</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>35.54</v>
+        <v>159.27</v>
       </c>
       <c r="C149" t="n">
-        <v>35.5</v>
+        <v>160</v>
       </c>
       <c r="D149" t="n">
-        <v>-0.11</v>
+        <v>0.46</v>
       </c>
       <c r="E149" t="b">
         <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>32.98</v>
+        <v>158.1</v>
       </c>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
-        <v>-7.1</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>DGCONTENT</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>27.68</v>
+        <v>2613.5</v>
       </c>
       <c r="C150" t="n">
-        <v>27.65</v>
+        <v>2625</v>
       </c>
       <c r="D150" t="n">
-        <v>-0.11</v>
+        <v>0.44</v>
       </c>
       <c r="E150" t="b">
         <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>26.51</v>
+        <v>2599.9</v>
       </c>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
-        <v>-4.12</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>PREMEXPLN</t>
+          <t>VLEGOV</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>537.65</v>
+        <v>15.92</v>
       </c>
       <c r="C151" t="n">
-        <v>537</v>
+        <v>15.99</v>
       </c>
       <c r="D151" t="n">
-        <v>-0.12</v>
+        <v>0.44</v>
       </c>
       <c r="E151" t="b">
         <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>516.55</v>
+        <v>15.5</v>
       </c>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
-        <v>-3.81</v>
+        <v>-3.06</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ANANTAM</t>
+          <t>KRITINUT</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>102.53</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="C152" t="n">
-        <v>102.4</v>
+        <v>67</v>
       </c>
       <c r="D152" t="n">
-        <v>-0.13</v>
+        <v>0.43</v>
       </c>
       <c r="E152" t="b">
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>102.81</v>
+        <v>67.02</v>
       </c>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="n">
-        <v>0.4</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BALAJITELE</t>
+          <t>CONFIPET</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>108.14</v>
+        <v>30.37</v>
       </c>
       <c r="C153" t="n">
-        <v>108</v>
+        <v>30.5</v>
       </c>
       <c r="D153" t="n">
-        <v>-0.13</v>
+        <v>0.43</v>
       </c>
       <c r="E153" t="b">
         <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>98.40000000000001</v>
+        <v>30.16</v>
       </c>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="n">
-        <v>-8.890000000000001</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SHANTIGEAR</t>
+          <t>AXISCADES</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>450.1</v>
+        <v>1433.2</v>
       </c>
       <c r="C154" t="n">
-        <v>449.5</v>
+        <v>1439.4</v>
       </c>
       <c r="D154" t="n">
-        <v>-0.13</v>
+        <v>0.43</v>
       </c>
       <c r="E154" t="b">
         <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>450.2</v>
+        <v>1493.8</v>
       </c>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="n">
-        <v>0.16</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>GSS</t>
+          <t>IRBINVIT</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>13.49</v>
+        <v>61.32</v>
       </c>
       <c r="C155" t="n">
-        <v>13.47</v>
+        <v>61.58</v>
       </c>
       <c r="D155" t="n">
-        <v>-0.15</v>
+        <v>0.42</v>
       </c>
       <c r="E155" t="b">
         <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>13.6</v>
+        <v>61.07</v>
       </c>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="n">
-        <v>0.97</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>AKSHOPTFBR</t>
+          <t>PIGL</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>4.86</v>
+        <v>105.06</v>
       </c>
       <c r="C156" t="n">
-        <v>4.85</v>
+        <v>105.5</v>
       </c>
       <c r="D156" t="n">
-        <v>-0.21</v>
+        <v>0.42</v>
       </c>
       <c r="E156" t="b">
         <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>4.54</v>
+        <v>107.99</v>
       </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="n">
-        <v>-6.39</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>TIJARIA</t>
+          <t>SHAH</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>4.62</v>
+        <v>4.86</v>
       </c>
       <c r="C157" t="n">
-        <v>4.61</v>
+        <v>4.88</v>
       </c>
       <c r="D157" t="n">
-        <v>-0.22</v>
+        <v>0.41</v>
       </c>
       <c r="E157" t="b">
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>4.39</v>
+        <v>4.79</v>
       </c>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="n">
-        <v>-4.77</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>NIRAJISPAT</t>
+          <t>VERTOZ</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>284.73</v>
+        <v>45.01</v>
       </c>
       <c r="C158" t="n">
-        <v>284</v>
+        <v>45.19</v>
       </c>
       <c r="D158" t="n">
-        <v>-0.26</v>
+        <v>0.4</v>
       </c>
       <c r="E158" t="b">
         <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>279.55</v>
+        <v>44.06</v>
       </c>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="n">
-        <v>-1.57</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>SAMBHAAV</t>
+          <t>LAKPRE</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>7.51</v>
+        <v>5.2</v>
       </c>
       <c r="C159" t="n">
-        <v>7.49</v>
+        <v>5.22</v>
       </c>
       <c r="D159" t="n">
-        <v>-0.27</v>
+        <v>0.38</v>
       </c>
       <c r="E159" t="b">
         <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>7.14</v>
+        <v>5.1</v>
       </c>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="n">
-        <v>-4.67</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>637.8</v>
+        <v>779.15</v>
       </c>
       <c r="C160" t="n">
-        <v>636</v>
+        <v>782.1</v>
       </c>
       <c r="D160" t="n">
-        <v>-0.28</v>
+        <v>0.38</v>
       </c>
       <c r="E160" t="b">
         <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>657</v>
+        <v>776.25</v>
       </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="n">
-        <v>3.3</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>AGARIND</t>
+          <t>STEELCITY</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>551</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="C161" t="n">
-        <v>549.4</v>
+        <v>88</v>
       </c>
       <c r="D161" t="n">
-        <v>-0.29</v>
+        <v>0.36</v>
       </c>
       <c r="E161" t="b">
         <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>525.1</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="n">
-        <v>-4.42</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>GRMOVER</t>
+          <t>GLOBAL</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>160.67</v>
+        <v>97.61</v>
       </c>
       <c r="C162" t="n">
-        <v>160.2</v>
+        <v>97.95</v>
       </c>
       <c r="D162" t="n">
-        <v>-0.29</v>
+        <v>0.35</v>
       </c>
       <c r="E162" t="b">
         <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>160</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="n">
-        <v>-0.12</v>
+        <v>-2.43</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>DEEPINDS</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>229.25</v>
+        <v>366.8</v>
       </c>
       <c r="C163" t="n">
-        <v>228.49</v>
+        <v>368.1</v>
       </c>
       <c r="D163" t="n">
-        <v>-0.33</v>
+        <v>0.35</v>
       </c>
       <c r="E163" t="b">
         <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>225.85</v>
+        <v>365.7</v>
       </c>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="n">
-        <v>-1.16</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SWARAJ</t>
+          <t>GRMOVER</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>303.25</v>
+        <v>158.96</v>
       </c>
       <c r="C164" t="n">
-        <v>302.25</v>
+        <v>159.5</v>
       </c>
       <c r="D164" t="n">
-        <v>-0.33</v>
+        <v>0.34</v>
       </c>
       <c r="E164" t="b">
         <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>302</v>
+        <v>156.43</v>
       </c>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="n">
-        <v>-0.08</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SUVIDHAA</t>
+          <t>POKARNA</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>3</v>
+        <v>891.95</v>
       </c>
       <c r="C165" t="n">
-        <v>2.99</v>
+        <v>895</v>
       </c>
       <c r="D165" t="n">
-        <v>-0.33</v>
+        <v>0.34</v>
       </c>
       <c r="E165" t="b">
         <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>2.93</v>
+        <v>886.15</v>
       </c>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="n">
-        <v>-2.01</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>FLEXITUFF</t>
+          <t>JAYAGROGN</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>8.73</v>
+        <v>173.94</v>
       </c>
       <c r="C166" t="n">
-        <v>8.699999999999999</v>
+        <v>174.5</v>
       </c>
       <c r="D166" t="n">
-        <v>-0.34</v>
+        <v>0.32</v>
       </c>
       <c r="E166" t="b">
         <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>8.44</v>
+        <v>171.83</v>
       </c>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="n">
-        <v>-2.99</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>DENORA</t>
+          <t>KALPATARU</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>703.55</v>
+        <v>314</v>
       </c>
       <c r="C167" t="n">
-        <v>701.1</v>
+        <v>315</v>
       </c>
       <c r="D167" t="n">
-        <v>-0.35</v>
+        <v>0.32</v>
       </c>
       <c r="E167" t="b">
         <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>681.1</v>
+        <v>307.8</v>
       </c>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="n">
-        <v>-2.85</v>
+        <v>-2.29</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CROWN</t>
+          <t>NEWJAISA</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>120.44</v>
+        <v>16.4</v>
       </c>
       <c r="C168" t="n">
-        <v>120</v>
+        <v>16.45</v>
       </c>
       <c r="D168" t="n">
-        <v>-0.37</v>
+        <v>0.3</v>
       </c>
       <c r="E168" t="b">
         <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>115.9</v>
+        <v>17.05</v>
       </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="n">
-        <v>-3.42</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>KOKUYOCMLN</t>
+          <t>GANDHITUBE</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>82.31</v>
+        <v>847.7</v>
       </c>
       <c r="C169" t="n">
-        <v>82</v>
+        <v>850</v>
       </c>
       <c r="D169" t="n">
-        <v>-0.38</v>
+        <v>0.27</v>
       </c>
       <c r="E169" t="b">
         <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>79.23999999999999</v>
+        <v>842.9</v>
       </c>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="n">
-        <v>-3.37</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>INDUSINVIT</t>
+          <t>CHETANA</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>124.8</v>
+        <v>38.35</v>
       </c>
       <c r="C170" t="n">
-        <v>124.3</v>
+        <v>38.45</v>
       </c>
       <c r="D170" t="n">
-        <v>-0.4</v>
+        <v>0.26</v>
       </c>
       <c r="E170" t="b">
         <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>126.98</v>
+        <v>38.45</v>
       </c>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>NIPPOBATRY</t>
+          <t>MANAKCOAT</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>336.45</v>
+        <v>117.71</v>
       </c>
       <c r="C171" t="n">
-        <v>335.1</v>
+        <v>118</v>
       </c>
       <c r="D171" t="n">
-        <v>-0.4</v>
+        <v>0.25</v>
       </c>
       <c r="E171" t="b">
         <v>0</v>
       </c>
       <c r="F171" t="n">
-        <v>313</v>
+        <v>117</v>
       </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="n">
-        <v>-6.6</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>AHLADA</t>
+          <t>FMGOETZE</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>45.15</v>
+        <v>393.25</v>
       </c>
       <c r="C172" t="n">
-        <v>44.97</v>
+        <v>394.25</v>
       </c>
       <c r="D172" t="n">
-        <v>-0.4</v>
+        <v>0.25</v>
       </c>
       <c r="E172" t="b">
         <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>44</v>
+        <v>387.15</v>
       </c>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="n">
-        <v>-2.16</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>GVPTECH</t>
+          <t>CALSOFT</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>6.98</v>
+        <v>11.96</v>
       </c>
       <c r="C173" t="n">
-        <v>6.95</v>
+        <v>11.99</v>
       </c>
       <c r="D173" t="n">
-        <v>-0.43</v>
+        <v>0.25</v>
       </c>
       <c r="E173" t="b">
         <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>6.7</v>
+        <v>12</v>
       </c>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="n">
-        <v>-3.6</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>LYKALABS</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>62.35</v>
+        <v>538.15</v>
       </c>
       <c r="C174" t="n">
-        <v>62.08</v>
+        <v>539.5</v>
       </c>
       <c r="D174" t="n">
-        <v>-0.43</v>
+        <v>0.25</v>
       </c>
       <c r="E174" t="b">
         <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>60.64</v>
+        <v>550.75</v>
       </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="n">
-        <v>-2.32</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>EDELWEISS</t>
+          <t>NELCO</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>114.42</v>
+        <v>601.55</v>
       </c>
       <c r="C175" t="n">
-        <v>113.9</v>
+        <v>603</v>
       </c>
       <c r="D175" t="n">
-        <v>-0.45</v>
+        <v>0.24</v>
       </c>
       <c r="E175" t="b">
         <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>112.54</v>
+        <v>600.45</v>
       </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="n">
-        <v>-1.19</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>2037.2</v>
+        <v>1288.9</v>
       </c>
       <c r="C176" t="n">
-        <v>2028</v>
+        <v>1292</v>
       </c>
       <c r="D176" t="n">
-        <v>-0.45</v>
+        <v>0.24</v>
       </c>
       <c r="E176" t="b">
         <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>2031.4</v>
+        <v>1306.2</v>
       </c>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="n">
-        <v>0.17</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>AKASH</t>
+          <t>AXITA</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>26.12</v>
+        <v>8.5</v>
       </c>
       <c r="C177" t="n">
-        <v>26</v>
+        <v>8.52</v>
       </c>
       <c r="D177" t="n">
-        <v>-0.46</v>
+        <v>0.24</v>
       </c>
       <c r="E177" t="b">
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>25</v>
+        <v>8.5</v>
       </c>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="n">
-        <v>-3.85</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>MEDIASSIST</t>
+          <t>CAPITALSFB</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>370.7</v>
+        <v>259.8</v>
       </c>
       <c r="C178" t="n">
-        <v>368.95</v>
+        <v>260.4</v>
       </c>
       <c r="D178" t="n">
-        <v>-0.47</v>
+        <v>0.23</v>
       </c>
       <c r="E178" t="b">
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>361.9</v>
+        <v>258.8</v>
       </c>
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="n">
-        <v>-1.91</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SELMC</t>
+          <t>VINEETLAB</t>
         </is>
       </c>
       <c r="B179" t="n">
         <v>29.93</v>
       </c>
       <c r="C179" t="n">
-        <v>29.79</v>
+        <v>30</v>
       </c>
       <c r="D179" t="n">
-        <v>-0.47</v>
+        <v>0.23</v>
       </c>
       <c r="E179" t="b">
         <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>28.5</v>
+        <v>29.3</v>
       </c>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="n">
-        <v>-4.33</v>
+        <v>-2.33</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>BIRLANU</t>
+          <t>DRONE</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>1507.5</v>
+        <v>47.4</v>
       </c>
       <c r="C180" t="n">
-        <v>1500.1</v>
+        <v>47.5</v>
       </c>
       <c r="D180" t="n">
-        <v>-0.49</v>
+        <v>0.21</v>
       </c>
       <c r="E180" t="b">
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>1514</v>
+        <v>46.85</v>
       </c>
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="n">
-        <v>0.93</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>INDOTHAI</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>566.3</v>
+        <v>258.3</v>
       </c>
       <c r="C181" t="n">
-        <v>563.5</v>
+        <v>258.85</v>
       </c>
       <c r="D181" t="n">
-        <v>-0.49</v>
+        <v>0.21</v>
       </c>
       <c r="E181" t="b">
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>576</v>
+        <v>259</v>
       </c>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="n">
-        <v>2.22</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>RKEC</t>
+          <t>VINDHYATEL</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>43.15</v>
+        <v>1024.5</v>
       </c>
       <c r="C182" t="n">
-        <v>42.94</v>
+        <v>1026.5</v>
       </c>
       <c r="D182" t="n">
-        <v>-0.49</v>
+        <v>0.2</v>
       </c>
       <c r="E182" t="b">
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>42.57</v>
+        <v>1011.9</v>
       </c>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="n">
-        <v>-0.86</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>TRANSWORLD</t>
+          <t>C2C</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>139.17</v>
+        <v>337.9</v>
       </c>
       <c r="C183" t="n">
-        <v>138.48</v>
+        <v>338.55</v>
       </c>
       <c r="D183" t="n">
-        <v>-0.5</v>
+        <v>0.19</v>
       </c>
       <c r="E183" t="b">
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>131.08</v>
+        <v>338</v>
       </c>
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="n">
-        <v>-5.34</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>KABRAEXTRU</t>
+          <t>SPECIALITY</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>256.1</v>
+        <v>99.22</v>
       </c>
       <c r="C184" t="n">
-        <v>254.8</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="D184" t="n">
-        <v>-0.51</v>
+        <v>0.18</v>
       </c>
       <c r="E184" t="b">
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>244</v>
+        <v>97.8</v>
       </c>
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="n">
-        <v>-4.24</v>
+        <v>-1.61</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>WELINV</t>
+          <t>VIPCLOTHNG</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>1281.4</v>
+        <v>19.71</v>
       </c>
       <c r="C185" t="n">
-        <v>1274.7</v>
+        <v>19.74</v>
       </c>
       <c r="D185" t="n">
-        <v>-0.52</v>
+        <v>0.15</v>
       </c>
       <c r="E185" t="b">
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>1274</v>
+        <v>19.69</v>
       </c>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="n">
-        <v>-0.05</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>NOIDATOLL</t>
+          <t>SPMLINFRA</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>3.74</v>
+        <v>165.77</v>
       </c>
       <c r="C186" t="n">
-        <v>3.72</v>
+        <v>165.99</v>
       </c>
       <c r="D186" t="n">
-        <v>-0.53</v>
+        <v>0.13</v>
       </c>
       <c r="E186" t="b">
         <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>3.61</v>
+        <v>176.11</v>
       </c>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="n">
-        <v>-2.96</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>UCAL</t>
+          <t>IGPL</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>108.59</v>
+        <v>347.45</v>
       </c>
       <c r="C187" t="n">
-        <v>108</v>
+        <v>347.85</v>
       </c>
       <c r="D187" t="n">
-        <v>-0.54</v>
+        <v>0.12</v>
       </c>
       <c r="E187" t="b">
         <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>101.99</v>
+        <v>335.6</v>
       </c>
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="n">
-        <v>-5.56</v>
+        <v>-3.52</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>LGHL</t>
+          <t>SIGMA</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>286.95</v>
+        <v>40.55</v>
       </c>
       <c r="C188" t="n">
-        <v>285.4</v>
+        <v>40.6</v>
       </c>
       <c r="D188" t="n">
-        <v>-0.54</v>
+        <v>0.12</v>
       </c>
       <c r="E188" t="b">
         <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>285</v>
+        <v>39.86</v>
       </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="n">
-        <v>-0.14</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ICDSLTD</t>
+          <t>MARKOLINES</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>41.1</v>
+        <v>159.71</v>
       </c>
       <c r="C189" t="n">
-        <v>40.88</v>
+        <v>159.88</v>
       </c>
       <c r="D189" t="n">
-        <v>-0.54</v>
+        <v>0.11</v>
       </c>
       <c r="E189" t="b">
         <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>39.05</v>
+        <v>159.08</v>
       </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="n">
-        <v>-4.48</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>CCCL</t>
+          <t>RAMAPHO</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>15.99</v>
+        <v>124.88</v>
       </c>
       <c r="C190" t="n">
-        <v>15.9</v>
+        <v>125</v>
       </c>
       <c r="D190" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="E190" t="b">
         <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>15.4</v>
+        <v>122.73</v>
       </c>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="n">
-        <v>-3.14</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ICRA</t>
+          <t>SECURKLOUD</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>5531</v>
+        <v>20.98</v>
       </c>
       <c r="C191" t="n">
-        <v>5500</v>
+        <v>21</v>
       </c>
       <c r="D191" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="E191" t="b">
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>5712.5</v>
+        <v>22</v>
       </c>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="n">
-        <v>3.86</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ALLETEC</t>
+          <t>SHREEJISPG</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>157.4</v>
+        <v>390.3</v>
       </c>
       <c r="C192" t="n">
-        <v>156.5</v>
+        <v>390.6</v>
       </c>
       <c r="D192" t="n">
-        <v>-0.57</v>
+        <v>0.08</v>
       </c>
       <c r="E192" t="b">
         <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>153.5</v>
+        <v>384.8</v>
       </c>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="n">
-        <v>-1.92</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>E2E</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>444.7</v>
+        <v>2457</v>
       </c>
       <c r="C193" t="n">
-        <v>442.1</v>
+        <v>2458.7</v>
       </c>
       <c r="D193" t="n">
-        <v>-0.58</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E193" t="b">
         <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>454.15</v>
+        <v>2350</v>
       </c>
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="n">
-        <v>2.73</v>
+        <v>-4.42</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SAILIFE</t>
+          <t>SAGCEM</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>998.25</v>
+        <v>189.89</v>
       </c>
       <c r="C194" t="n">
-        <v>992.5</v>
+        <v>190</v>
       </c>
       <c r="D194" t="n">
-        <v>-0.58</v>
+        <v>0.06</v>
       </c>
       <c r="E194" t="b">
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>999</v>
+        <v>183.95</v>
       </c>
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="n">
-        <v>0.65</v>
+        <v>-3.18</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>IRBINVIT</t>
+          <t>ZUARIIND</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>61.86</v>
+        <v>256.65</v>
       </c>
       <c r="C195" t="n">
-        <v>61.5</v>
+        <v>256.8</v>
       </c>
       <c r="D195" t="n">
-        <v>-0.58</v>
+        <v>0.06</v>
       </c>
       <c r="E195" t="b">
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>61.38</v>
+        <v>251.6</v>
       </c>
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="n">
-        <v>-0.2</v>
+        <v>-2.02</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>BALKRISHNA</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>16.82</v>
+        <v>1024.9</v>
       </c>
       <c r="C196" t="n">
-        <v>16.72</v>
+        <v>1025.4</v>
       </c>
       <c r="D196" t="n">
-        <v>-0.59</v>
+        <v>0.05</v>
       </c>
       <c r="E196" t="b">
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>16.3</v>
+        <v>1009</v>
       </c>
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="n">
-        <v>-2.51</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>CAPINVIT</t>
+          <t>MOLDTECH</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>70</v>
+        <v>129.12</v>
       </c>
       <c r="C197" t="n">
-        <v>69.58</v>
+        <v>129.19</v>
       </c>
       <c r="D197" t="n">
-        <v>-0.6</v>
+        <v>0.05</v>
       </c>
       <c r="E197" t="b">
         <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>69.8</v>
+        <v>125.1</v>
       </c>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="n">
-        <v>0.32</v>
+        <v>-3.17</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>FOODSIN</t>
+          <t>EVERESTIND</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>58.3</v>
+        <v>405.8</v>
       </c>
       <c r="C198" t="n">
-        <v>57.95</v>
+        <v>406</v>
       </c>
       <c r="D198" t="n">
-        <v>-0.6</v>
+        <v>0.05</v>
       </c>
       <c r="E198" t="b">
         <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>57.23</v>
+        <v>399.8</v>
       </c>
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="n">
-        <v>-1.24</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>NAGREEKEXP</t>
+          <t>LEMERITE</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>25.2</v>
+        <v>448.65</v>
       </c>
       <c r="C199" t="n">
-        <v>25.05</v>
+        <v>448.8</v>
       </c>
       <c r="D199" t="n">
-        <v>-0.6</v>
+        <v>0.03</v>
       </c>
       <c r="E199" t="b">
         <v>0</v>
       </c>
       <c r="F199" t="n">
-        <v>24.97</v>
+        <v>447.15</v>
       </c>
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="n">
-        <v>-0.32</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>DEEPINDS</t>
+          <t>GENCON</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>347.1</v>
+        <v>45.39</v>
       </c>
       <c r="C200" t="n">
-        <v>345</v>
+        <v>45.4</v>
       </c>
       <c r="D200" t="n">
-        <v>-0.61</v>
+        <v>0.02</v>
       </c>
       <c r="E200" t="b">
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>366.6</v>
+        <v>43.7</v>
       </c>
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="n">
-        <v>6.26</v>
+        <v>-3.74</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SUNDROP</t>
+          <t>BODALCHEM</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>646.45</v>
+        <v>46.39</v>
       </c>
       <c r="C201" t="n">
-        <v>642.5</v>
+        <v>46.4</v>
       </c>
       <c r="D201" t="n">
-        <v>-0.61</v>
+        <v>0.02</v>
       </c>
       <c r="E201" t="b">
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>632.2</v>
+        <v>44.67</v>
       </c>
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="n">
-        <v>-1.6</v>
+        <v>-3.73</v>
       </c>
     </row>
   </sheetData>

--- a/data/trending_momentum_stocks.xlsx
+++ b/data/trending_momentum_stocks.xlsx
@@ -461,465 +461,465 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TECILCHEM</t>
+          <t>UMESLTD</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12.69</v>
+        <v>3.94</v>
       </c>
       <c r="C2" t="n">
-        <v>14.75</v>
+        <v>4.55</v>
       </c>
       <c r="D2" t="n">
-        <v>16.23</v>
+        <v>15.48</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>13.21</v>
+        <v>4.23</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>-10.44</v>
+        <v>-7.03</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SAHYADRI</t>
+          <t>ELGIRUBCO</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>242.05</v>
+        <v>38.25</v>
       </c>
       <c r="C3" t="n">
-        <v>276.85</v>
+        <v>43.4</v>
       </c>
       <c r="D3" t="n">
-        <v>14.38</v>
+        <v>13.46</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>251.5</v>
+        <v>45.9</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>-9.16</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KALANA</t>
+          <t>RUBYMILLS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.5</v>
+        <v>203.88</v>
       </c>
       <c r="C4" t="n">
-        <v>25.85</v>
+        <v>230.02</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>12.82</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>25.55</v>
+        <v>223.15</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>-1.16</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>UMAEXPORTS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>111.83</v>
+        <v>24.78</v>
       </c>
       <c r="C5" t="n">
-        <v>123</v>
+        <v>27.5</v>
       </c>
       <c r="D5" t="n">
-        <v>9.99</v>
+        <v>10.98</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>114.92</v>
+        <v>25.94</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>-6.57</v>
+        <v>-5.67</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EUROBOND</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>161.46</v>
+        <v>6.91</v>
       </c>
       <c r="C6" t="n">
-        <v>177</v>
+        <v>7.65</v>
       </c>
       <c r="D6" t="n">
-        <v>9.619999999999999</v>
+        <v>10.71</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>162.5</v>
+        <v>7.14</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>-8.19</v>
+        <v>-6.67</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>INFOMEDIA</t>
+          <t>RKDL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.08</v>
+        <v>16.83</v>
       </c>
       <c r="C7" t="n">
-        <v>5.5</v>
+        <v>18.49</v>
       </c>
       <c r="D7" t="n">
-        <v>8.27</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>5.2</v>
+        <v>18.21</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>-5.45</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AAKASH</t>
+          <t>UNIINFO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.33</v>
+        <v>12.84</v>
       </c>
       <c r="C8" t="n">
-        <v>8.99</v>
+        <v>14.05</v>
       </c>
       <c r="D8" t="n">
-        <v>7.92</v>
+        <v>9.42</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>9.210000000000001</v>
+        <v>13.38</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>2.45</v>
+        <v>-4.77</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TOUCHWOOD</t>
+          <t>AAKASH</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>71.3</v>
+        <v>9.92</v>
       </c>
       <c r="C9" t="n">
-        <v>76.92</v>
+        <v>10.8</v>
       </c>
       <c r="D9" t="n">
-        <v>7.88</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>73.22</v>
+        <v>11.24</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>-4.81</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>APCL</t>
+          <t>KHFM</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>124.33</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
-        <v>132.95</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>6.93</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>122.86</v>
+        <v>60</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>-7.59</v>
+        <v>-10.98</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CREATIVEYE</t>
+          <t>TECHD</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.3</v>
+        <v>500.75</v>
       </c>
       <c r="C11" t="n">
-        <v>6.73</v>
+        <v>544</v>
       </c>
       <c r="D11" t="n">
-        <v>6.83</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>6.16</v>
+        <v>529.8</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>-8.470000000000001</v>
+        <v>-2.61</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MFML</t>
+          <t>PRUDMOULI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21.64</v>
+        <v>16.53</v>
       </c>
       <c r="C12" t="n">
-        <v>23.1</v>
+        <v>17.94</v>
       </c>
       <c r="D12" t="n">
-        <v>6.75</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>21.22</v>
+        <v>16.49</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>-8.140000000000001</v>
+        <v>-8.08</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WELINV</t>
+          <t>MFML</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1268.2</v>
+        <v>21.1</v>
       </c>
       <c r="C13" t="n">
-        <v>1350</v>
+        <v>22.78</v>
       </c>
       <c r="D13" t="n">
-        <v>6.45</v>
+        <v>7.96</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1289</v>
+        <v>22.09</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>-4.52</v>
+        <v>-3.03</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ACEINTEG</t>
+          <t>BELLACASA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17.45</v>
+        <v>265.25</v>
       </c>
       <c r="C14" t="n">
-        <v>18.4</v>
+        <v>285</v>
       </c>
       <c r="D14" t="n">
-        <v>5.44</v>
+        <v>7.45</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>16.65</v>
+        <v>265.35</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>-9.51</v>
+        <v>-6.89</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KHANDSE</t>
+          <t>TECILCHEM</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16.77</v>
+        <v>13.04</v>
       </c>
       <c r="C15" t="n">
-        <v>17.66</v>
+        <v>14</v>
       </c>
       <c r="D15" t="n">
-        <v>5.31</v>
+        <v>7.36</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>16.02</v>
+        <v>13.15</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>-9.289999999999999</v>
+        <v>-6.07</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JINDRILL</t>
+          <t>SUMIT</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>522.15</v>
+        <v>37.31</v>
       </c>
       <c r="C16" t="n">
-        <v>549</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>5.14</v>
+        <v>7.21</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>594.95</v>
+        <v>37.63</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>8.369999999999999</v>
+        <v>-5.92</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SETCO</t>
+          <t>KRITIKA</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17.76</v>
+        <v>5.45</v>
       </c>
       <c r="C17" t="n">
-        <v>18.64</v>
+        <v>5.83</v>
       </c>
       <c r="D17" t="n">
-        <v>4.95</v>
+        <v>6.97</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>17.73</v>
+        <v>5.84</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>-4.88</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NEUEON</t>
+          <t>KAMOPAINTS</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>11.34</v>
+        <v>4.2</v>
       </c>
       <c r="C18" t="n">
-        <v>11.9</v>
+        <v>4.48</v>
       </c>
       <c r="D18" t="n">
-        <v>4.94</v>
+        <v>6.67</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>11.9</v>
+        <v>4.21</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-6.03</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DHARIWAL</t>
+          <t>GATECHDVR</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>43.85</v>
+        <v>0.45</v>
       </c>
       <c r="C19" t="n">
-        <v>46</v>
+        <v>0.48</v>
       </c>
       <c r="D19" t="n">
-        <v>4.9</v>
+        <v>6.67</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>46</v>
+        <v>0.48</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
@@ -929,4729 +929,4729 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PREMIER</t>
+          <t>PARSVNATH</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.87</v>
+        <v>6.95</v>
       </c>
       <c r="C20" t="n">
-        <v>3.01</v>
+        <v>7.4</v>
       </c>
       <c r="D20" t="n">
-        <v>4.88</v>
+        <v>6.47</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>3.01</v>
+        <v>7.05</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>-4.73</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LOYALTEX</t>
+          <t>CTE</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>213.66</v>
+        <v>27.33</v>
       </c>
       <c r="C21" t="n">
-        <v>223.99</v>
+        <v>28.98</v>
       </c>
       <c r="D21" t="n">
-        <v>4.83</v>
+        <v>6.04</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>217</v>
+        <v>27.9</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>-3.12</v>
+        <v>-3.73</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AIROLAM</t>
+          <t>HEADSUP</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>89.13</v>
+        <v>7.55</v>
       </c>
       <c r="C22" t="n">
-        <v>93.34999999999999</v>
+        <v>8</v>
       </c>
       <c r="D22" t="n">
-        <v>4.73</v>
+        <v>5.96</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>90.5</v>
+        <v>7.5</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>-3.05</v>
+        <v>-6.25</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>COMPUSOFT</t>
+          <t>TAC</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13.71</v>
+        <v>432.2</v>
       </c>
       <c r="C23" t="n">
-        <v>14.35</v>
+        <v>457.9</v>
       </c>
       <c r="D23" t="n">
-        <v>4.67</v>
+        <v>5.95</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>13.32</v>
+        <v>457</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>-7.18</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TREEHOUSE</t>
+          <t>SHIVATEX</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9.01</v>
+        <v>149.16</v>
       </c>
       <c r="C24" t="n">
-        <v>9.43</v>
+        <v>158</v>
       </c>
       <c r="D24" t="n">
-        <v>4.66</v>
+        <v>5.93</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>8.880000000000001</v>
+        <v>151.3</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>-5.83</v>
+        <v>-4.24</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>OMKARCHEM</t>
+          <t>ZODIACLOTH</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.52</v>
+        <v>74.62</v>
       </c>
       <c r="C25" t="n">
-        <v>4.73</v>
+        <v>78.97</v>
       </c>
       <c r="D25" t="n">
-        <v>4.65</v>
+        <v>5.83</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>4.31</v>
+        <v>75.14</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>-8.880000000000001</v>
+        <v>-4.85</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BLUECOAST</t>
+          <t>RVHL</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>20.75</v>
+        <v>36.3</v>
       </c>
       <c r="C26" t="n">
-        <v>21.7</v>
+        <v>38.39</v>
       </c>
       <c r="D26" t="n">
-        <v>4.58</v>
+        <v>5.76</v>
       </c>
       <c r="E26" t="b">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>20.39</v>
+        <v>38</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>-6.04</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SHIVATEX</t>
+          <t>RELIABLE</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>152.08</v>
+        <v>128.8</v>
       </c>
       <c r="C27" t="n">
-        <v>159.02</v>
+        <v>136</v>
       </c>
       <c r="D27" t="n">
-        <v>4.56</v>
+        <v>5.59</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>153.59</v>
+        <v>125.89</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>-3.41</v>
+        <v>-7.43</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>UNIENTER</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>670.85</v>
+        <v>101.17</v>
       </c>
       <c r="C28" t="n">
-        <v>701</v>
+        <v>106.81</v>
       </c>
       <c r="D28" t="n">
-        <v>4.49</v>
+        <v>5.57</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>736.1</v>
+        <v>107.95</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>5.01</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AGROPHOS</t>
+          <t>NIRAJ</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>32.53</v>
+        <v>28.3</v>
       </c>
       <c r="C29" t="n">
-        <v>33.99</v>
+        <v>29.85</v>
       </c>
       <c r="D29" t="n">
-        <v>4.49</v>
+        <v>5.48</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>32.12</v>
+        <v>29.09</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>-5.5</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SOCL</t>
+          <t>RAMKY</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>27.85</v>
+        <v>430.5</v>
       </c>
       <c r="C30" t="n">
-        <v>29.1</v>
+        <v>454</v>
       </c>
       <c r="D30" t="n">
-        <v>4.49</v>
+        <v>5.46</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>29.2</v>
+        <v>483.3</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>0.34</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ORTEL</t>
+          <t>OSWALSEEDS</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.57</v>
+        <v>11.75</v>
       </c>
       <c r="C31" t="n">
-        <v>1.64</v>
+        <v>12.39</v>
       </c>
       <c r="D31" t="n">
-        <v>4.46</v>
+        <v>5.45</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>1.57</v>
+        <v>12.87</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>-4.27</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SELMC</t>
+          <t>SGL</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>28.73</v>
+        <v>11.19</v>
       </c>
       <c r="C32" t="n">
-        <v>29.98</v>
+        <v>11.8</v>
       </c>
       <c r="D32" t="n">
-        <v>4.35</v>
+        <v>5.45</v>
       </c>
       <c r="E32" t="b">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>27.33</v>
+        <v>11.53</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>-8.84</v>
+        <v>-2.29</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ACCPL</t>
+          <t>HMVL</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>68.05</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="C33" t="n">
-        <v>70.95</v>
+        <v>69.7</v>
       </c>
       <c r="D33" t="n">
-        <v>4.26</v>
+        <v>5.45</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>70.95</v>
+        <v>66.55</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>-4.52</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SUNDRMBRAK</t>
+          <t>RADIOCITY</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>584.15</v>
+        <v>5.87</v>
       </c>
       <c r="C34" t="n">
-        <v>607.7</v>
+        <v>6.19</v>
       </c>
       <c r="D34" t="n">
-        <v>4.03</v>
+        <v>5.45</v>
       </c>
       <c r="E34" t="b">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>589.8</v>
+        <v>5.9</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>-2.95</v>
+        <v>-4.68</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>VETO</t>
+          <t>KRIDHANINF</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>100.94</v>
+        <v>2.39</v>
       </c>
       <c r="C35" t="n">
-        <v>105</v>
+        <v>2.52</v>
       </c>
       <c r="D35" t="n">
-        <v>4.02</v>
+        <v>5.44</v>
       </c>
       <c r="E35" t="b">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>100.28</v>
+        <v>2.5</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>-4.5</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MAHAPEXLTD</t>
+          <t>PROZONER</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>86.70999999999999</v>
+        <v>45.47</v>
       </c>
       <c r="C36" t="n">
-        <v>90</v>
+        <v>47.9</v>
       </c>
       <c r="D36" t="n">
-        <v>3.79</v>
+        <v>5.34</v>
       </c>
       <c r="E36" t="b">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>87</v>
+        <v>45.37</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>-3.33</v>
+        <v>-5.28</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CTE</t>
+          <t>DHRUV</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>27.34</v>
+        <v>31.14</v>
       </c>
       <c r="C37" t="n">
-        <v>28.33</v>
+        <v>32.8</v>
       </c>
       <c r="D37" t="n">
-        <v>3.62</v>
+        <v>5.33</v>
       </c>
       <c r="E37" t="b">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>27.25</v>
+        <v>31.1</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>-3.81</v>
+        <v>-5.18</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DHRUV</t>
+          <t>ESSARSHPNG</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>30.48</v>
+        <v>23.55</v>
       </c>
       <c r="C38" t="n">
-        <v>31.55</v>
+        <v>24.8</v>
       </c>
       <c r="D38" t="n">
-        <v>3.51</v>
+        <v>5.31</v>
       </c>
       <c r="E38" t="b">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>31.67</v>
+        <v>26.31</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>0.38</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>RSSOFTWARE</t>
+          <t>KALANA</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>33.52</v>
+        <v>25.85</v>
       </c>
       <c r="C39" t="n">
-        <v>34.68</v>
+        <v>27.2</v>
       </c>
       <c r="D39" t="n">
-        <v>3.46</v>
+        <v>5.22</v>
       </c>
       <c r="E39" t="b">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>34.96</v>
+        <v>27.5</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AKASH</t>
+          <t>NIBL</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>25.06</v>
+        <v>30.87</v>
       </c>
       <c r="C40" t="n">
-        <v>25.9</v>
+        <v>32.45</v>
       </c>
       <c r="D40" t="n">
-        <v>3.35</v>
+        <v>5.12</v>
       </c>
       <c r="E40" t="b">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>24.21</v>
+        <v>30.62</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>-6.53</v>
+        <v>-5.64</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>KNAGRI</t>
+          <t>BAGFILMS</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>188.75</v>
+        <v>4.74</v>
       </c>
       <c r="C41" t="n">
-        <v>194.99</v>
+        <v>4.98</v>
       </c>
       <c r="D41" t="n">
-        <v>3.31</v>
+        <v>5.06</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>184.68</v>
+        <v>4.85</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>-5.29</v>
+        <v>-2.61</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GTL</t>
+          <t>BEARDSELL</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>6.99</v>
+        <v>24.76</v>
       </c>
       <c r="C42" t="n">
-        <v>7.22</v>
+        <v>26</v>
       </c>
       <c r="D42" t="n">
-        <v>3.29</v>
+        <v>5.01</v>
       </c>
       <c r="E42" t="b">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>6.95</v>
+        <v>24.8</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>-3.74</v>
+        <v>-4.62</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PRABHA</t>
+          <t>MANGALAM</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>169.21</v>
+        <v>29.27</v>
       </c>
       <c r="C43" t="n">
-        <v>174.7</v>
+        <v>30.73</v>
       </c>
       <c r="D43" t="n">
-        <v>3.24</v>
+        <v>4.99</v>
       </c>
       <c r="E43" t="b">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>167.84</v>
+        <v>30.73</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>-3.93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MAHESHWARI</t>
+          <t>ESFL</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>41.5</v>
+        <v>148.15</v>
       </c>
       <c r="C44" t="n">
-        <v>42.75</v>
+        <v>155.55</v>
       </c>
       <c r="D44" t="n">
-        <v>3.01</v>
+        <v>4.99</v>
       </c>
       <c r="E44" t="b">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>39.67</v>
+        <v>155.55</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>-7.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LIBAS</t>
+          <t>ESCONET</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>10.08</v>
+        <v>121.25</v>
       </c>
       <c r="C45" t="n">
-        <v>10.38</v>
+        <v>127.25</v>
       </c>
       <c r="D45" t="n">
-        <v>2.98</v>
+        <v>4.95</v>
       </c>
       <c r="E45" t="b">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>10.14</v>
+        <v>122.05</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>-2.31</v>
+        <v>-4.09</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ROML</t>
+          <t>NEWJAISA</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>41.75</v>
+        <v>17.2</v>
       </c>
       <c r="C46" t="n">
-        <v>42.99</v>
+        <v>18.05</v>
       </c>
       <c r="D46" t="n">
-        <v>2.97</v>
+        <v>4.94</v>
       </c>
       <c r="E46" t="b">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>41.51</v>
+        <v>17.85</v>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>-3.44</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>VHL</t>
+          <t>SUVIDHAA</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3106.8</v>
+        <v>2.84</v>
       </c>
       <c r="C47" t="n">
-        <v>3197</v>
+        <v>2.98</v>
       </c>
       <c r="D47" t="n">
-        <v>2.9</v>
+        <v>4.93</v>
       </c>
       <c r="E47" t="b">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>3111.5</v>
+        <v>2.99</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>-2.67</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>IDEAFORGE</t>
+          <t>VIVIMEDLAB</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>441.3</v>
+        <v>6.93</v>
       </c>
       <c r="C48" t="n">
-        <v>454</v>
+        <v>7.27</v>
       </c>
       <c r="D48" t="n">
-        <v>2.88</v>
+        <v>4.91</v>
       </c>
       <c r="E48" t="b">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>458.65</v>
+        <v>7.09</v>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>1.02</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ESSARSHPNG</t>
+          <t>ALKALI</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>24.3</v>
+        <v>58.15</v>
       </c>
       <c r="C49" t="n">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="D49" t="n">
-        <v>2.88</v>
+        <v>4.9</v>
       </c>
       <c r="E49" t="b">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>23.78</v>
+        <v>59.9</v>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>-4.88</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MANOMAY</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>216.85</v>
+        <v>293.7</v>
       </c>
       <c r="C50" t="n">
-        <v>222.99</v>
+        <v>308</v>
       </c>
       <c r="D50" t="n">
-        <v>2.83</v>
+        <v>4.87</v>
       </c>
       <c r="E50" t="b">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>217</v>
+        <v>295</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>-2.69</v>
+        <v>-4.22</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GVPTECH</t>
+          <t>GKWLIMITED</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>6.8</v>
+        <v>1609.7</v>
       </c>
       <c r="C51" t="n">
-        <v>6.99</v>
+        <v>1688</v>
       </c>
       <c r="D51" t="n">
-        <v>2.79</v>
+        <v>4.86</v>
       </c>
       <c r="E51" t="b">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>6.57</v>
+        <v>1609.9</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>-6.01</v>
+        <v>-4.63</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NITIRAJ</t>
+          <t>ANKITMETAL</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>207.35</v>
+        <v>1.67</v>
       </c>
       <c r="C52" t="n">
-        <v>212.95</v>
+        <v>1.75</v>
       </c>
       <c r="D52" t="n">
-        <v>2.7</v>
+        <v>4.79</v>
       </c>
       <c r="E52" t="b">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>202.05</v>
+        <v>1.73</v>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>-5.12</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ORTINGLOBE</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>16.37</v>
+        <v>23.28</v>
       </c>
       <c r="C53" t="n">
-        <v>16.8</v>
+        <v>24.39</v>
       </c>
       <c r="D53" t="n">
-        <v>2.63</v>
+        <v>4.77</v>
       </c>
       <c r="E53" t="b">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>15.75</v>
+        <v>23.75</v>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>-6.25</v>
+        <v>-2.62</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DJML</t>
+          <t>FILATFASH</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>88.55</v>
+        <v>0.21</v>
       </c>
       <c r="C54" t="n">
-        <v>90.87</v>
+        <v>0.22</v>
       </c>
       <c r="D54" t="n">
-        <v>2.62</v>
+        <v>4.76</v>
       </c>
       <c r="E54" t="b">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>88.43000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>-2.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DIGJAMLMTD</t>
+          <t>NURECA</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>45.82</v>
+        <v>272.05</v>
       </c>
       <c r="C55" t="n">
-        <v>46.99</v>
+        <v>285</v>
       </c>
       <c r="D55" t="n">
-        <v>2.55</v>
+        <v>4.76</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>42.99</v>
+        <v>270.6</v>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>-8.51</v>
+        <v>-5.05</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TTKHLTCARE</t>
+          <t>BALAJEE</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>892.8</v>
+        <v>26.01</v>
       </c>
       <c r="C56" t="n">
-        <v>915</v>
+        <v>27.24</v>
       </c>
       <c r="D56" t="n">
-        <v>2.49</v>
+        <v>4.73</v>
       </c>
       <c r="E56" t="b">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>897.9</v>
+        <v>26.1</v>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>-1.87</v>
+        <v>-4.19</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SAURASHCEM</t>
+          <t>RANASUG</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>63.29</v>
+        <v>11.83</v>
       </c>
       <c r="C57" t="n">
-        <v>64.8</v>
+        <v>12.39</v>
       </c>
       <c r="D57" t="n">
-        <v>2.39</v>
+        <v>4.73</v>
       </c>
       <c r="E57" t="b">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>63.45</v>
+        <v>11.98</v>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>-2.08</v>
+        <v>-3.31</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ABAN</t>
+          <t>JINDRILL</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>19.27</v>
+        <v>598.3</v>
       </c>
       <c r="C58" t="n">
-        <v>19.73</v>
+        <v>626.5</v>
       </c>
       <c r="D58" t="n">
-        <v>2.39</v>
+        <v>4.71</v>
       </c>
       <c r="E58" t="b">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>20.18</v>
+        <v>624.6</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>2.28</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DSFCL</t>
+          <t>GLOBALVECT</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>33.19</v>
+        <v>157.35</v>
       </c>
       <c r="C59" t="n">
-        <v>33.98</v>
+        <v>164.75</v>
       </c>
       <c r="D59" t="n">
-        <v>2.38</v>
+        <v>4.7</v>
       </c>
       <c r="E59" t="b">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>29.42</v>
+        <v>157.7</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>-13.42</v>
+        <v>-4.28</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CORDSCABLE</t>
+          <t>MCL</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>167.26</v>
+        <v>70</v>
       </c>
       <c r="C60" t="n">
-        <v>170.95</v>
+        <v>73.28</v>
       </c>
       <c r="D60" t="n">
-        <v>2.21</v>
+        <v>4.69</v>
       </c>
       <c r="E60" t="b">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>165.95</v>
+        <v>68.8</v>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>-2.92</v>
+        <v>-6.11</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>VAISHALI</t>
+          <t>GAYAHWS</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>6.79</v>
+        <v>2.14</v>
       </c>
       <c r="C61" t="n">
-        <v>6.94</v>
+        <v>2.24</v>
       </c>
       <c r="D61" t="n">
-        <v>2.21</v>
+        <v>4.67</v>
       </c>
       <c r="E61" t="b">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>6.82</v>
+        <v>2.23</v>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>-1.73</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PRUDMOULI</t>
+          <t>HMT</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>17.61</v>
+        <v>66.98</v>
       </c>
       <c r="C62" t="n">
-        <v>17.98</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="D62" t="n">
-        <v>2.1</v>
+        <v>4.66</v>
       </c>
       <c r="E62" t="b">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>16.18</v>
+        <v>69.75</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>-10.01</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DAMODARIND</t>
+          <t>ASHIMASYN</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>24.38</v>
+        <v>13.79</v>
       </c>
       <c r="C63" t="n">
-        <v>24.89</v>
+        <v>14.43</v>
       </c>
       <c r="D63" t="n">
-        <v>2.09</v>
+        <v>4.64</v>
       </c>
       <c r="E63" t="b">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>23.9</v>
+        <v>14.42</v>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>-3.98</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SADBHIN</t>
+          <t>KOHINOOR</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3.38</v>
+        <v>23.99</v>
       </c>
       <c r="C64" t="n">
-        <v>3.45</v>
+        <v>25.1</v>
       </c>
       <c r="D64" t="n">
-        <v>2.07</v>
+        <v>4.63</v>
       </c>
       <c r="E64" t="b">
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>3.22</v>
+        <v>24.85</v>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>-6.67</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>UNIINFO</t>
+          <t>GOLDSTAR</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>13.84</v>
+        <v>8.65</v>
       </c>
       <c r="C65" t="n">
-        <v>14.12</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="D65" t="n">
-        <v>2.02</v>
+        <v>4.62</v>
       </c>
       <c r="E65" t="b">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>13.04</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>-7.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>RADAAN</t>
+          <t>AARON</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2.99</v>
+        <v>140.9</v>
       </c>
       <c r="C66" t="n">
-        <v>3.05</v>
+        <v>147.4</v>
       </c>
       <c r="D66" t="n">
-        <v>2.01</v>
+        <v>4.61</v>
       </c>
       <c r="E66" t="b">
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>2.97</v>
+        <v>148.88</v>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>-2.62</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STARPAPER</t>
+          <t>GLOBALE</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>136.66</v>
+        <v>10.52</v>
       </c>
       <c r="C67" t="n">
-        <v>139.39</v>
+        <v>11</v>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>4.56</v>
       </c>
       <c r="E67" t="b">
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>136.7</v>
+        <v>10.31</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>-1.93</v>
+        <v>-6.27</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>EMKAY</t>
+          <t>PRIMO</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>226.29</v>
+        <v>18.09</v>
       </c>
       <c r="C68" t="n">
-        <v>230.8</v>
+        <v>18.9</v>
       </c>
       <c r="D68" t="n">
-        <v>1.99</v>
+        <v>4.48</v>
       </c>
       <c r="E68" t="b">
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>227.52</v>
+        <v>18.19</v>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>-1.42</v>
+        <v>-3.76</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DBOL</t>
+          <t>GATECH</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>100.01</v>
+        <v>0.45</v>
       </c>
       <c r="C69" t="n">
-        <v>102</v>
+        <v>0.47</v>
       </c>
       <c r="D69" t="n">
-        <v>1.99</v>
+        <v>4.44</v>
       </c>
       <c r="E69" t="b">
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>103.98</v>
+        <v>0.47</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>OILCOUNTUB</t>
+          <t>GFLLIMITED</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>47.57</v>
+        <v>43.46</v>
       </c>
       <c r="C70" t="n">
-        <v>48.51</v>
+        <v>45.38</v>
       </c>
       <c r="D70" t="n">
-        <v>1.98</v>
+        <v>4.42</v>
       </c>
       <c r="E70" t="b">
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>50.83</v>
+        <v>44.57</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>4.78</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>RKDL</t>
+          <t>ASIANTILES</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>17.65</v>
+        <v>66.09</v>
       </c>
       <c r="C71" t="n">
-        <v>18</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="D71" t="n">
-        <v>1.98</v>
+        <v>4.39</v>
       </c>
       <c r="E71" t="b">
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>17.6</v>
+        <v>66.68000000000001</v>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>-2.22</v>
+        <v>-3.35</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>LATTEYS</t>
+          <t>MOTOGENFIN</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>21.18</v>
+        <v>20.13</v>
       </c>
       <c r="C72" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="D72" t="n">
-        <v>1.98</v>
+        <v>4.32</v>
       </c>
       <c r="E72" t="b">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>20.31</v>
+        <v>20.61</v>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>-5.97</v>
+        <v>-1.86</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MCL</t>
+          <t>PILITA</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>66.67</v>
+        <v>7.71</v>
       </c>
       <c r="C73" t="n">
-        <v>67.98999999999999</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="D73" t="n">
-        <v>1.98</v>
+        <v>4.28</v>
       </c>
       <c r="E73" t="b">
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>70</v>
+        <v>7.96</v>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>2.96</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>GOLDENTOBC</t>
+          <t>CYBERTECH</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>28.44</v>
+        <v>103.67</v>
       </c>
       <c r="C74" t="n">
-        <v>29</v>
+        <v>108</v>
       </c>
       <c r="D74" t="n">
-        <v>1.97</v>
+        <v>4.18</v>
       </c>
       <c r="E74" t="b">
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>28.99</v>
+        <v>105</v>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>-0.03</v>
+        <v>-2.78</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SAMPANN</t>
+          <t>CLEDUCATE</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>28.61</v>
+        <v>41.86</v>
       </c>
       <c r="C75" t="n">
-        <v>29.17</v>
+        <v>43.59</v>
       </c>
       <c r="D75" t="n">
-        <v>1.96</v>
+        <v>4.13</v>
       </c>
       <c r="E75" t="b">
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>27.98</v>
+        <v>44.4</v>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>-4.08</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>HINDOILEXP</t>
+          <t>GINNIFILA</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>136.64</v>
+        <v>36.89</v>
       </c>
       <c r="C76" t="n">
-        <v>139.31</v>
+        <v>38.4</v>
       </c>
       <c r="D76" t="n">
-        <v>1.95</v>
+        <v>4.09</v>
       </c>
       <c r="E76" t="b">
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>140.16</v>
+        <v>37.19</v>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>0.61</v>
+        <v>-3.15</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SICALLOG</t>
+          <t>ASTRON</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>66.23</v>
+        <v>3.95</v>
       </c>
       <c r="C77" t="n">
-        <v>67.51000000000001</v>
+        <v>4.11</v>
       </c>
       <c r="D77" t="n">
-        <v>1.93</v>
+        <v>4.05</v>
       </c>
       <c r="E77" t="b">
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>64.09999999999999</v>
+        <v>4.09</v>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>-5.05</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>HMVL</t>
+          <t>KSHITIJPOL</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>66.72</v>
+        <v>2.5</v>
       </c>
       <c r="C78" t="n">
-        <v>68</v>
+        <v>2.6</v>
       </c>
       <c r="D78" t="n">
-        <v>1.92</v>
+        <v>4</v>
       </c>
       <c r="E78" t="b">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>67.69</v>
+        <v>2.48</v>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>-0.46</v>
+        <v>-4.62</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>INNOVANA</t>
+          <t>OILCOUNTUB</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>392.55</v>
+        <v>47.71</v>
       </c>
       <c r="C79" t="n">
-        <v>400</v>
+        <v>49.6</v>
       </c>
       <c r="D79" t="n">
-        <v>1.9</v>
+        <v>3.96</v>
       </c>
       <c r="E79" t="b">
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>384.9</v>
+        <v>47.08</v>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>-3.78</v>
+        <v>-5.08</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>LYKALABS</t>
+          <t>CPEDU</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>60.69</v>
+        <v>180.8</v>
       </c>
       <c r="C80" t="n">
-        <v>61.8</v>
+        <v>187.95</v>
       </c>
       <c r="D80" t="n">
-        <v>1.83</v>
+        <v>3.95</v>
       </c>
       <c r="E80" t="b">
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>60.64</v>
+        <v>184.6</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>-1.88</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>IMPEXFERRO</t>
+          <t>ABCOTS</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1.71</v>
+        <v>388.35</v>
       </c>
       <c r="C81" t="n">
-        <v>1.74</v>
+        <v>403.6</v>
       </c>
       <c r="D81" t="n">
-        <v>1.75</v>
+        <v>3.93</v>
       </c>
       <c r="E81" t="b">
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>1.67</v>
+        <v>413.7</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>-4.02</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>USK</t>
+          <t>ORCHASP</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>27.51</v>
+        <v>2.56</v>
       </c>
       <c r="C82" t="n">
-        <v>27.99</v>
+        <v>2.66</v>
       </c>
       <c r="D82" t="n">
-        <v>1.74</v>
+        <v>3.91</v>
       </c>
       <c r="E82" t="b">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>27.65</v>
+        <v>2.38</v>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>-1.21</v>
+        <v>-10.53</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>WINSOME</t>
+          <t>SAMPANN</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1.74</v>
+        <v>27.8</v>
       </c>
       <c r="C83" t="n">
-        <v>1.77</v>
+        <v>28.88</v>
       </c>
       <c r="D83" t="n">
-        <v>1.72</v>
+        <v>3.88</v>
       </c>
       <c r="E83" t="b">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>1.77</v>
+        <v>28.08</v>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ANSALAPI</t>
+          <t>SAMBHAAV</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>4.07</v>
+        <v>6.98</v>
       </c>
       <c r="C84" t="n">
-        <v>4.14</v>
+        <v>7.25</v>
       </c>
       <c r="D84" t="n">
-        <v>1.72</v>
+        <v>3.87</v>
       </c>
       <c r="E84" t="b">
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>4.15</v>
+        <v>7.15</v>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>0.24</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PANACEABIO</t>
+          <t>BTML</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>326.4</v>
+        <v>7.26</v>
       </c>
       <c r="C85" t="n">
-        <v>332</v>
+        <v>7.54</v>
       </c>
       <c r="D85" t="n">
-        <v>1.72</v>
+        <v>3.86</v>
       </c>
       <c r="E85" t="b">
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>323.6</v>
+        <v>7.41</v>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>-2.53</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ARCHIES</t>
+          <t>SILGO</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>14.7</v>
+        <v>69.36</v>
       </c>
       <c r="C86" t="n">
-        <v>14.95</v>
+        <v>72</v>
       </c>
       <c r="D86" t="n">
-        <v>1.7</v>
+        <v>3.81</v>
       </c>
       <c r="E86" t="b">
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>14.55</v>
+        <v>73.34</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>-2.68</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>TREL</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>282.2</v>
+        <v>23.89</v>
       </c>
       <c r="C87" t="n">
-        <v>287</v>
+        <v>24.8</v>
       </c>
       <c r="D87" t="n">
-        <v>1.7</v>
+        <v>3.81</v>
       </c>
       <c r="E87" t="b">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>281.6</v>
+        <v>24.18</v>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>-1.88</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>IL&amp;FSTRANS</t>
+          <t>UEL</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>2.35</v>
+        <v>161.83</v>
       </c>
       <c r="C88" t="n">
-        <v>2.39</v>
+        <v>167.99</v>
       </c>
       <c r="D88" t="n">
-        <v>1.7</v>
+        <v>3.81</v>
       </c>
       <c r="E88" t="b">
         <v>0</v>
       </c>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" t="n">
+        <v>169.92</v>
+      </c>
       <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="H88" t="n">
+        <v>1.15</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ADVANIHOTR</t>
+          <t>AURUM</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>54.07</v>
+        <v>165.64</v>
       </c>
       <c r="C89" t="n">
-        <v>54.98</v>
+        <v>171.9</v>
       </c>
       <c r="D89" t="n">
-        <v>1.68</v>
+        <v>3.78</v>
       </c>
       <c r="E89" t="b">
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>53.28</v>
+        <v>164.31</v>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>-3.09</v>
+        <v>-4.42</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>HMT</t>
+          <t>INDOWIND</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>63.93</v>
+        <v>8.76</v>
       </c>
       <c r="C90" t="n">
-        <v>65</v>
+        <v>9.09</v>
       </c>
       <c r="D90" t="n">
-        <v>1.67</v>
+        <v>3.77</v>
       </c>
       <c r="E90" t="b">
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>66.18000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>1.82</v>
+        <v>-2.53</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DEVIT</t>
+          <t>JALAN</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>24.08</v>
+        <v>2.65</v>
       </c>
       <c r="C91" t="n">
-        <v>24.48</v>
+        <v>2.75</v>
       </c>
       <c r="D91" t="n">
-        <v>1.66</v>
+        <v>3.77</v>
       </c>
       <c r="E91" t="b">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>27.25</v>
+        <v>2.75</v>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>11.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BEDMUTHA</t>
+          <t>SMLT</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>132.51</v>
+        <v>73.25</v>
       </c>
       <c r="C92" t="n">
-        <v>134.7</v>
+        <v>75.98</v>
       </c>
       <c r="D92" t="n">
-        <v>1.65</v>
+        <v>3.73</v>
       </c>
       <c r="E92" t="b">
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>131.2</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
-        <v>-2.6</v>
+        <v>-2.26</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>KRISHIVAL</t>
+          <t>ISFT</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>315.15</v>
+        <v>69.41</v>
       </c>
       <c r="C93" t="n">
-        <v>320</v>
+        <v>72</v>
       </c>
       <c r="D93" t="n">
-        <v>1.54</v>
+        <v>3.73</v>
       </c>
       <c r="E93" t="b">
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>319.5</v>
+        <v>69.66</v>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
-        <v>-0.16</v>
+        <v>-3.25</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>KOTHARIPRO</t>
+          <t>MAZDA</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>64.70999999999999</v>
+        <v>192.76</v>
       </c>
       <c r="C94" t="n">
-        <v>65.7</v>
+        <v>199.9</v>
       </c>
       <c r="D94" t="n">
-        <v>1.53</v>
+        <v>3.7</v>
       </c>
       <c r="E94" t="b">
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>65.29000000000001</v>
+        <v>196.6</v>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>-0.62</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STEL</t>
+          <t>KRITINUT</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>510.2</v>
+        <v>67.37</v>
       </c>
       <c r="C95" t="n">
-        <v>518</v>
+        <v>69.8</v>
       </c>
       <c r="D95" t="n">
-        <v>1.53</v>
+        <v>3.61</v>
       </c>
       <c r="E95" t="b">
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>502.3</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>-3.03</v>
+        <v>-2.79</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DBSTOCKBRO</t>
+          <t>KHAITANLTD</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>24.89</v>
+        <v>93.62</v>
       </c>
       <c r="C96" t="n">
-        <v>25.25</v>
+        <v>96.98999999999999</v>
       </c>
       <c r="D96" t="n">
-        <v>1.45</v>
+        <v>3.6</v>
       </c>
       <c r="E96" t="b">
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>24.8</v>
+        <v>95</v>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>-1.78</v>
+        <v>-2.05</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>RELTD</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>488.05</v>
+        <v>137.07</v>
       </c>
       <c r="C97" t="n">
-        <v>495.05</v>
+        <v>142</v>
       </c>
       <c r="D97" t="n">
-        <v>1.43</v>
+        <v>3.6</v>
       </c>
       <c r="E97" t="b">
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>492.85</v>
+        <v>137.4</v>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>-0.44</v>
+        <v>-3.24</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>URAVIDEF</t>
+          <t>SETCO</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>140.86</v>
+        <v>17.96</v>
       </c>
       <c r="C98" t="n">
-        <v>142.79</v>
+        <v>18.6</v>
       </c>
       <c r="D98" t="n">
-        <v>1.37</v>
+        <v>3.56</v>
       </c>
       <c r="E98" t="b">
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>139.97</v>
+        <v>17.71</v>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>-1.97</v>
+        <v>-4.78</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CORALFINAC</t>
+          <t>GJL</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>33.04</v>
+        <v>180.1</v>
       </c>
       <c r="C99" t="n">
-        <v>33.49</v>
+        <v>186.5</v>
       </c>
       <c r="D99" t="n">
-        <v>1.36</v>
+        <v>3.55</v>
       </c>
       <c r="E99" t="b">
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>32.54</v>
+        <v>189.1</v>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
-        <v>-2.84</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MBAPL</t>
+          <t>MOTISONS</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>450.25</v>
+        <v>14.33</v>
       </c>
       <c r="C100" t="n">
-        <v>456.35</v>
+        <v>14.83</v>
       </c>
       <c r="D100" t="n">
-        <v>1.35</v>
+        <v>3.49</v>
       </c>
       <c r="E100" t="b">
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>456.2</v>
+        <v>14.61</v>
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>-0.03</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>TIL</t>
+          <t>PRAENG</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>213.03</v>
+        <v>21.73</v>
       </c>
       <c r="C101" t="n">
-        <v>215.89</v>
+        <v>22.48</v>
       </c>
       <c r="D101" t="n">
-        <v>1.34</v>
+        <v>3.45</v>
       </c>
       <c r="E101" t="b">
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>210.32</v>
+        <v>21.72</v>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>-2.58</v>
+        <v>-3.38</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>KAPSTON</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>453.95</v>
+        <v>393.5</v>
       </c>
       <c r="C102" t="n">
-        <v>460</v>
+        <v>407</v>
       </c>
       <c r="D102" t="n">
-        <v>1.33</v>
+        <v>3.43</v>
       </c>
       <c r="E102" t="b">
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>456</v>
+        <v>402.05</v>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>-0.87</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>KRISHNADEF</t>
+          <t>GEECEE</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1126.1</v>
+        <v>285.25</v>
       </c>
       <c r="C103" t="n">
-        <v>1140</v>
+        <v>295</v>
       </c>
       <c r="D103" t="n">
-        <v>1.23</v>
+        <v>3.42</v>
       </c>
       <c r="E103" t="b">
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>1151.2</v>
+        <v>286.8</v>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>0.98</v>
+        <v>-2.78</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>TICL</t>
+          <t>DSFCL</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>26.47</v>
+        <v>29.5</v>
       </c>
       <c r="C104" t="n">
-        <v>26.79</v>
+        <v>30.5</v>
       </c>
       <c r="D104" t="n">
-        <v>1.21</v>
+        <v>3.39</v>
       </c>
       <c r="E104" t="b">
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>25.63</v>
+        <v>29.68</v>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
-        <v>-4.33</v>
+        <v>-2.69</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>VIDHIING</t>
+          <t>NOIDATOLL</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>302.4</v>
+        <v>3.56</v>
       </c>
       <c r="C105" t="n">
-        <v>306</v>
+        <v>3.68</v>
       </c>
       <c r="D105" t="n">
-        <v>1.19</v>
+        <v>3.37</v>
       </c>
       <c r="E105" t="b">
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>300.05</v>
+        <v>3.84</v>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>-1.94</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>GNA</t>
+          <t>EPACKPEB</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>428.85</v>
+        <v>167.87</v>
       </c>
       <c r="C106" t="n">
-        <v>433.95</v>
+        <v>173.5</v>
       </c>
       <c r="D106" t="n">
-        <v>1.19</v>
+        <v>3.35</v>
       </c>
       <c r="E106" t="b">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>423.6</v>
+        <v>168.01</v>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
-        <v>-2.39</v>
+        <v>-3.16</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SHRIRAMPPS</t>
+          <t>DCMNVL</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>76.45</v>
+        <v>131.12</v>
       </c>
       <c r="C107" t="n">
-        <v>77.3</v>
+        <v>135.5</v>
       </c>
       <c r="D107" t="n">
-        <v>1.11</v>
+        <v>3.34</v>
       </c>
       <c r="E107" t="b">
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>74.52</v>
+        <v>129.1</v>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>-3.6</v>
+        <v>-4.72</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MEP</t>
+          <t>PARAS</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.99</v>
+        <v>721.05</v>
       </c>
       <c r="C108" t="n">
-        <v>1</v>
+        <v>745</v>
       </c>
       <c r="D108" t="n">
-        <v>1.01</v>
+        <v>3.32</v>
       </c>
       <c r="E108" t="b">
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>1</v>
+        <v>726.1</v>
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>-2.54</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>INTENTECH</t>
+          <t>K2INFRA</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>97.77</v>
+        <v>50.2</v>
       </c>
       <c r="C109" t="n">
-        <v>98.75</v>
+        <v>51.85</v>
       </c>
       <c r="D109" t="n">
-        <v>1</v>
+        <v>3.29</v>
       </c>
       <c r="E109" t="b">
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>96.51000000000001</v>
+        <v>51.85</v>
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>-2.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SWANDEF</t>
+          <t>CALSOFT</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1781.4</v>
+        <v>12.87</v>
       </c>
       <c r="C110" t="n">
-        <v>1799.3</v>
+        <v>13.29</v>
       </c>
       <c r="D110" t="n">
-        <v>1</v>
+        <v>3.26</v>
       </c>
       <c r="E110" t="b">
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>1750</v>
+        <v>13.28</v>
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
-        <v>-2.74</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ASTRAMICRO</t>
+          <t>MANOMAY</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>982.4</v>
+        <v>212.14</v>
       </c>
       <c r="C111" t="n">
-        <v>992.15</v>
+        <v>219</v>
       </c>
       <c r="D111" t="n">
-        <v>0.99</v>
+        <v>3.23</v>
       </c>
       <c r="E111" t="b">
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>999</v>
+        <v>217.9</v>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SOLARINDS</t>
+          <t>BIRLAMONEY</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>13989</v>
+        <v>128.51</v>
       </c>
       <c r="C112" t="n">
-        <v>14124</v>
+        <v>132.65</v>
       </c>
       <c r="D112" t="n">
-        <v>0.97</v>
+        <v>3.22</v>
       </c>
       <c r="E112" t="b">
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>14338</v>
+        <v>129.42</v>
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
-        <v>1.52</v>
+        <v>-2.43</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>VIJIFIN</t>
+          <t>ABAN</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>2.07</v>
+        <v>20.23</v>
       </c>
       <c r="C113" t="n">
-        <v>2.09</v>
+        <v>20.88</v>
       </c>
       <c r="D113" t="n">
-        <v>0.97</v>
+        <v>3.21</v>
       </c>
       <c r="E113" t="b">
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>2.05</v>
+        <v>21.24</v>
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>-1.91</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ORIENTCER</t>
+          <t>BAIDFIN</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>37.1</v>
+        <v>11</v>
       </c>
       <c r="C114" t="n">
-        <v>37.45</v>
+        <v>11.35</v>
       </c>
       <c r="D114" t="n">
-        <v>0.9399999999999999</v>
+        <v>3.18</v>
       </c>
       <c r="E114" t="b">
         <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>36.43</v>
+        <v>11.16</v>
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
-        <v>-2.72</v>
+        <v>-1.67</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MIRZAINT</t>
+          <t>MOSCHIP</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>32.99</v>
+        <v>172.26</v>
       </c>
       <c r="C115" t="n">
-        <v>33.29</v>
+        <v>177.7</v>
       </c>
       <c r="D115" t="n">
-        <v>0.91</v>
+        <v>3.16</v>
       </c>
       <c r="E115" t="b">
         <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>32.68</v>
+        <v>173.18</v>
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>-1.83</v>
+        <v>-2.54</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MANAKSTEEL</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>55.5</v>
+        <v>2626.9</v>
       </c>
       <c r="C116" t="n">
-        <v>56</v>
+        <v>2710</v>
       </c>
       <c r="D116" t="n">
-        <v>0.9</v>
+        <v>3.16</v>
       </c>
       <c r="E116" t="b">
         <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>55.13</v>
+        <v>2726</v>
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
-        <v>-1.55</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>LASA</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>7.78</v>
+        <v>1841.8</v>
       </c>
       <c r="C117" t="n">
-        <v>7.85</v>
+        <v>1900</v>
       </c>
       <c r="D117" t="n">
-        <v>0.9</v>
+        <v>3.16</v>
       </c>
       <c r="E117" t="b">
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>7.43</v>
+        <v>1891</v>
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>-5.35</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>FLFL</t>
+          <t>SAKHTISUG</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1.24</v>
+        <v>16.85</v>
       </c>
       <c r="C118" t="n">
-        <v>1.25</v>
+        <v>17.38</v>
       </c>
       <c r="D118" t="n">
-        <v>0.8100000000000001</v>
+        <v>3.15</v>
       </c>
       <c r="E118" t="b">
         <v>0</v>
       </c>
       <c r="F118" t="n">
-        <v>1.3</v>
+        <v>16.88</v>
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
-        <v>4</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>EIFFL</t>
+          <t>JAYBARMARU</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>230.14</v>
+        <v>97.63</v>
       </c>
       <c r="C119" t="n">
-        <v>231.91</v>
+        <v>100.7</v>
       </c>
       <c r="D119" t="n">
-        <v>0.77</v>
+        <v>3.14</v>
       </c>
       <c r="E119" t="b">
         <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>232.32</v>
+        <v>96</v>
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
-        <v>0.18</v>
+        <v>-4.67</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>EMAMIPAP</t>
+          <t>VASWANI</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>81.37</v>
+        <v>53.33</v>
       </c>
       <c r="C120" t="n">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="D120" t="n">
-        <v>0.77</v>
+        <v>3.13</v>
       </c>
       <c r="E120" t="b">
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>81</v>
+        <v>54.28</v>
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
-        <v>-1.22</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SUNDARAM</t>
+          <t>SREEL</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1.36</v>
+        <v>198.6</v>
       </c>
       <c r="C121" t="n">
-        <v>1.37</v>
+        <v>204.8</v>
       </c>
       <c r="D121" t="n">
-        <v>0.74</v>
+        <v>3.12</v>
       </c>
       <c r="E121" t="b">
         <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>1.34</v>
+        <v>202.41</v>
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
-        <v>-2.19</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>IMPAL</t>
+          <t>BHARATSE</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1024.5</v>
+        <v>174.63</v>
       </c>
       <c r="C122" t="n">
-        <v>1032</v>
+        <v>180</v>
       </c>
       <c r="D122" t="n">
-        <v>0.73</v>
+        <v>3.08</v>
       </c>
       <c r="E122" t="b">
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>1029.9</v>
+        <v>174.22</v>
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
-        <v>-0.2</v>
+        <v>-3.21</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>JAYKAY</t>
+          <t>PRITIKAUTO</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>145.19</v>
+        <v>12.01</v>
       </c>
       <c r="C123" t="n">
-        <v>146.2</v>
+        <v>12.38</v>
       </c>
       <c r="D123" t="n">
-        <v>0.7</v>
+        <v>3.08</v>
       </c>
       <c r="E123" t="b">
         <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>143.77</v>
+        <v>12.33</v>
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>-1.66</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MVKAGRO</t>
+          <t>ACCURACY</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>553.15</v>
+        <v>4.22</v>
       </c>
       <c r="C124" t="n">
-        <v>557</v>
+        <v>4.35</v>
       </c>
       <c r="D124" t="n">
-        <v>0.7</v>
+        <v>3.08</v>
       </c>
       <c r="E124" t="b">
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>542.5</v>
+        <v>4.49</v>
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
-        <v>-2.6</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ANANTAM</t>
+          <t>GSS</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>102.61</v>
+        <v>13.14</v>
       </c>
       <c r="C125" t="n">
-        <v>103.31</v>
+        <v>13.54</v>
       </c>
       <c r="D125" t="n">
-        <v>0.68</v>
+        <v>3.04</v>
       </c>
       <c r="E125" t="b">
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>102.8</v>
+        <v>13.24</v>
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>-0.49</v>
+        <v>-2.22</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ESFL</t>
+          <t>NITCO</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>141.1</v>
+        <v>68.87</v>
       </c>
       <c r="C126" t="n">
-        <v>142</v>
+        <v>70.95</v>
       </c>
       <c r="D126" t="n">
-        <v>0.64</v>
+        <v>3.02</v>
       </c>
       <c r="E126" t="b">
         <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>148.15</v>
+        <v>67.61</v>
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
-        <v>4.33</v>
+        <v>-4.71</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SAWALIYA</t>
+          <t>CHEMBONDCH</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>304.05</v>
+        <v>142.53</v>
       </c>
       <c r="C127" t="n">
-        <v>305.95</v>
+        <v>146.8</v>
       </c>
       <c r="D127" t="n">
-        <v>0.62</v>
+        <v>3</v>
       </c>
       <c r="E127" t="b">
         <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>305</v>
+        <v>140.48</v>
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
-        <v>-0.31</v>
+        <v>-4.31</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>INDUSINVIT</t>
+          <t>ELECTHERM</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>126.69</v>
+        <v>662.2</v>
       </c>
       <c r="C128" t="n">
-        <v>127.46</v>
+        <v>682</v>
       </c>
       <c r="D128" t="n">
-        <v>0.61</v>
+        <v>2.99</v>
       </c>
       <c r="E128" t="b">
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>125.01</v>
+        <v>661.95</v>
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
-        <v>-1.92</v>
+        <v>-2.94</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ARROWGREEN</t>
+          <t>DANGEE</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>396.2</v>
+        <v>3.01</v>
       </c>
       <c r="C129" t="n">
-        <v>398.6</v>
+        <v>3.1</v>
       </c>
       <c r="D129" t="n">
-        <v>0.61</v>
+        <v>2.99</v>
       </c>
       <c r="E129" t="b">
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>398.05</v>
+        <v>3.07</v>
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
-        <v>-0.14</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>DICIND</t>
+          <t>DCM</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>526.85</v>
+        <v>69.81</v>
       </c>
       <c r="C130" t="n">
-        <v>530</v>
+        <v>71.89</v>
       </c>
       <c r="D130" t="n">
-        <v>0.6</v>
+        <v>2.98</v>
       </c>
       <c r="E130" t="b">
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>510.05</v>
+        <v>69.63</v>
       </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
-        <v>-3.76</v>
+        <v>-3.14</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>VEEDOL</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>362.85</v>
+        <v>1320.5</v>
       </c>
       <c r="C131" t="n">
-        <v>365</v>
+        <v>1359.7</v>
       </c>
       <c r="D131" t="n">
-        <v>0.59</v>
+        <v>2.97</v>
       </c>
       <c r="E131" t="b">
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>360.2</v>
+        <v>1312.4</v>
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
-        <v>-1.32</v>
+        <v>-3.48</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>VARDHACRLC</t>
+          <t>KHANDSE</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>33.79</v>
+        <v>16.89</v>
       </c>
       <c r="C132" t="n">
-        <v>33.99</v>
+        <v>17.39</v>
       </c>
       <c r="D132" t="n">
-        <v>0.59</v>
+        <v>2.96</v>
       </c>
       <c r="E132" t="b">
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>33.47</v>
+        <v>17.21</v>
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
-        <v>-1.53</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BROOKS</t>
+          <t>MOKSH</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>62.63</v>
+        <v>11.9</v>
       </c>
       <c r="C133" t="n">
-        <v>63</v>
+        <v>12.25</v>
       </c>
       <c r="D133" t="n">
-        <v>0.59</v>
+        <v>2.94</v>
       </c>
       <c r="E133" t="b">
         <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>62.73</v>
+        <v>12.27</v>
       </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
-        <v>-0.43</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>BOSCH-HCIL</t>
+          <t>SITINET</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>1367.5</v>
+        <v>0.34</v>
       </c>
       <c r="C134" t="n">
-        <v>1375.5</v>
+        <v>0.35</v>
       </c>
       <c r="D134" t="n">
-        <v>0.59</v>
+        <v>2.94</v>
       </c>
       <c r="E134" t="b">
         <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>1354.1</v>
+        <v>0.33</v>
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
-        <v>-1.56</v>
+        <v>-5.71</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>REPRO</t>
+          <t>NSIL</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>382.55</v>
+        <v>5635</v>
       </c>
       <c r="C135" t="n">
-        <v>384.75</v>
+        <v>5800</v>
       </c>
       <c r="D135" t="n">
-        <v>0.58</v>
+        <v>2.93</v>
       </c>
       <c r="E135" t="b">
         <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>381.45</v>
+        <v>5670</v>
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
-        <v>-0.86</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>JLHL</t>
+          <t>DAMODARIND</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>1273.3</v>
+        <v>24</v>
       </c>
       <c r="C136" t="n">
-        <v>1280</v>
+        <v>24.7</v>
       </c>
       <c r="D136" t="n">
-        <v>0.53</v>
+        <v>2.92</v>
       </c>
       <c r="E136" t="b">
         <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>1255.9</v>
+        <v>24.64</v>
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
-        <v>-1.88</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ASIANHOTNR</t>
+          <t>GARUDA</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>278.55</v>
+        <v>163.8</v>
       </c>
       <c r="C137" t="n">
-        <v>280</v>
+        <v>168.59</v>
       </c>
       <c r="D137" t="n">
-        <v>0.52</v>
+        <v>2.92</v>
       </c>
       <c r="E137" t="b">
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>269</v>
+        <v>164.07</v>
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
-        <v>-3.93</v>
+        <v>-2.68</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>HITECHGEAR</t>
+          <t>INFOMEDIA</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>620.85</v>
+        <v>5.13</v>
       </c>
       <c r="C138" t="n">
-        <v>624</v>
+        <v>5.28</v>
       </c>
       <c r="D138" t="n">
-        <v>0.51</v>
+        <v>2.92</v>
       </c>
       <c r="E138" t="b">
         <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>612.5</v>
+        <v>5.35</v>
       </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
-        <v>-1.84</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>IRISDOREME</t>
+          <t>TERASOFT</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>31.5</v>
+        <v>357.6</v>
       </c>
       <c r="C139" t="n">
-        <v>31.66</v>
+        <v>368</v>
       </c>
       <c r="D139" t="n">
-        <v>0.51</v>
+        <v>2.91</v>
       </c>
       <c r="E139" t="b">
         <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>31.62</v>
+        <v>362.8</v>
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
-        <v>-0.13</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>INDOUS</t>
+          <t>DEVIT</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>140.71</v>
+        <v>27.41</v>
       </c>
       <c r="C140" t="n">
-        <v>141.41</v>
+        <v>28.2</v>
       </c>
       <c r="D140" t="n">
-        <v>0.5</v>
+        <v>2.88</v>
       </c>
       <c r="E140" t="b">
         <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>132.23</v>
+        <v>26.55</v>
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
-        <v>-6.49</v>
+        <v>-5.85</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>AYMSYNTEX</t>
+          <t>FAIRCHEMOR</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>200.56</v>
+        <v>563</v>
       </c>
       <c r="C141" t="n">
-        <v>201.57</v>
+        <v>579</v>
       </c>
       <c r="D141" t="n">
-        <v>0.5</v>
+        <v>2.84</v>
       </c>
       <c r="E141" t="b">
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>201</v>
+        <v>562.5</v>
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
-        <v>-0.28</v>
+        <v>-2.85</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>CHEMPLASTS</t>
+          <t>PREMIERPOL</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>238.48</v>
+        <v>57.37</v>
       </c>
       <c r="C142" t="n">
-        <v>239.68</v>
+        <v>59</v>
       </c>
       <c r="D142" t="n">
-        <v>0.5</v>
+        <v>2.84</v>
       </c>
       <c r="E142" t="b">
         <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>226.41</v>
+        <v>55.3</v>
       </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
-        <v>-5.54</v>
+        <v>-6.27</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>HILTON</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>3951.6</v>
+        <v>17.04</v>
       </c>
       <c r="C143" t="n">
-        <v>3971.3</v>
+        <v>17.52</v>
       </c>
       <c r="D143" t="n">
-        <v>0.5</v>
+        <v>2.82</v>
       </c>
       <c r="E143" t="b">
         <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>3902.4</v>
+        <v>17.2</v>
       </c>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
-        <v>-1.73</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BDL</t>
+          <t>GLOBE</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>1268</v>
+        <v>2.5</v>
       </c>
       <c r="C144" t="n">
-        <v>1274.2</v>
+        <v>2.57</v>
       </c>
       <c r="D144" t="n">
-        <v>0.49</v>
+        <v>2.8</v>
       </c>
       <c r="E144" t="b">
         <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>1284.4</v>
+        <v>2.57</v>
       </c>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>TARAPUR</t>
+          <t>RADHIKAJWE</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>24.99</v>
+        <v>60.26</v>
       </c>
       <c r="C145" t="n">
-        <v>25.11</v>
+        <v>61.95</v>
       </c>
       <c r="D145" t="n">
-        <v>0.48</v>
+        <v>2.8</v>
       </c>
       <c r="E145" t="b">
         <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>24.84</v>
+        <v>60.05</v>
       </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
-        <v>-1.08</v>
+        <v>-3.07</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>PARASPETRO</t>
+          <t>DICIND</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>2.07</v>
+        <v>510.65</v>
       </c>
       <c r="C146" t="n">
-        <v>2.08</v>
+        <v>524.9</v>
       </c>
       <c r="D146" t="n">
-        <v>0.48</v>
+        <v>2.79</v>
       </c>
       <c r="E146" t="b">
         <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>2.09</v>
+        <v>517.85</v>
       </c>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
-        <v>0.48</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>PTL</t>
+          <t>HINDOILEXP</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>38.07</v>
+        <v>148.86</v>
       </c>
       <c r="C147" t="n">
-        <v>38.25</v>
+        <v>153</v>
       </c>
       <c r="D147" t="n">
-        <v>0.47</v>
+        <v>2.78</v>
       </c>
       <c r="E147" t="b">
         <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>37.78</v>
+        <v>156.08</v>
       </c>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
-        <v>-1.23</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>AKG</t>
+          <t>CHEMBOND</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>10.65</v>
+        <v>139.43</v>
       </c>
       <c r="C148" t="n">
-        <v>10.7</v>
+        <v>143.25</v>
       </c>
       <c r="D148" t="n">
-        <v>0.47</v>
+        <v>2.74</v>
       </c>
       <c r="E148" t="b">
         <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>10.7</v>
+        <v>141.01</v>
       </c>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
-        <v>0</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CHEMCON</t>
+          <t>RAMANEWS</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>159.27</v>
+        <v>33.87</v>
       </c>
       <c r="C149" t="n">
-        <v>160</v>
+        <v>34.79</v>
       </c>
       <c r="D149" t="n">
-        <v>0.46</v>
+        <v>2.72</v>
       </c>
       <c r="E149" t="b">
         <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>158.1</v>
+        <v>33.86</v>
       </c>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
-        <v>-1.19</v>
+        <v>-2.67</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>SHREERAMA</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>2613.5</v>
+        <v>50.62</v>
       </c>
       <c r="C150" t="n">
-        <v>2625</v>
+        <v>51.99</v>
       </c>
       <c r="D150" t="n">
-        <v>0.44</v>
+        <v>2.71</v>
       </c>
       <c r="E150" t="b">
         <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>2599.9</v>
+        <v>49.78</v>
       </c>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
-        <v>-0.96</v>
+        <v>-4.25</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>VLEGOV</t>
+          <t>AKSHAR</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>15.92</v>
+        <v>0.37</v>
       </c>
       <c r="C151" t="n">
-        <v>15.99</v>
+        <v>0.38</v>
       </c>
       <c r="D151" t="n">
-        <v>0.44</v>
+        <v>2.7</v>
       </c>
       <c r="E151" t="b">
         <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>15.5</v>
+        <v>0.38</v>
       </c>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
-        <v>-3.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>KRITINUT</t>
+          <t>SEPC</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>66.70999999999999</v>
+        <v>7.09</v>
       </c>
       <c r="C152" t="n">
-        <v>67</v>
+        <v>7.28</v>
       </c>
       <c r="D152" t="n">
-        <v>0.43</v>
+        <v>2.68</v>
       </c>
       <c r="E152" t="b">
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>67.02</v>
+        <v>6.98</v>
       </c>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="n">
-        <v>0.03</v>
+        <v>-4.12</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CONFIPET</t>
+          <t>SIGMAADV</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>30.37</v>
+        <v>157.81</v>
       </c>
       <c r="C153" t="n">
-        <v>30.5</v>
+        <v>162</v>
       </c>
       <c r="D153" t="n">
-        <v>0.43</v>
+        <v>2.66</v>
       </c>
       <c r="E153" t="b">
         <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>30.16</v>
+        <v>160.36</v>
       </c>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="n">
-        <v>-1.11</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>AXISCADES</t>
+          <t>VISAKAIND</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>1433.2</v>
+        <v>59.43</v>
       </c>
       <c r="C154" t="n">
-        <v>1439.4</v>
+        <v>61</v>
       </c>
       <c r="D154" t="n">
-        <v>0.43</v>
+        <v>2.64</v>
       </c>
       <c r="E154" t="b">
         <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>1493.8</v>
+        <v>59.73</v>
       </c>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="n">
-        <v>3.78</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>IRBINVIT</t>
+          <t>DCMSRIND</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>61.32</v>
+        <v>36.78</v>
       </c>
       <c r="C155" t="n">
-        <v>61.58</v>
+        <v>37.75</v>
       </c>
       <c r="D155" t="n">
-        <v>0.42</v>
+        <v>2.64</v>
       </c>
       <c r="E155" t="b">
         <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>61.07</v>
+        <v>36.92</v>
       </c>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="n">
-        <v>-0.83</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>PIGL</t>
+          <t>TAINWALCHM</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>105.06</v>
+        <v>199.63</v>
       </c>
       <c r="C156" t="n">
-        <v>105.5</v>
+        <v>204.9</v>
       </c>
       <c r="D156" t="n">
-        <v>0.42</v>
+        <v>2.64</v>
       </c>
       <c r="E156" t="b">
         <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>107.99</v>
+        <v>205.5</v>
       </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="n">
-        <v>2.36</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SHAH</t>
+          <t>CCCL</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>4.86</v>
+        <v>15.58</v>
       </c>
       <c r="C157" t="n">
-        <v>4.88</v>
+        <v>15.99</v>
       </c>
       <c r="D157" t="n">
-        <v>0.41</v>
+        <v>2.63</v>
       </c>
       <c r="E157" t="b">
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>4.79</v>
+        <v>15.4</v>
       </c>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="n">
-        <v>-1.84</v>
+        <v>-3.69</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>VERTOZ</t>
+          <t>ASMS</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>45.01</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="C158" t="n">
-        <v>45.19</v>
+        <v>9.35</v>
       </c>
       <c r="D158" t="n">
-        <v>0.4</v>
+        <v>2.63</v>
       </c>
       <c r="E158" t="b">
         <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>44.06</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="n">
-        <v>-2.5</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>LAKPRE</t>
+          <t>BAJAJHIND</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>5.2</v>
+        <v>17.21</v>
       </c>
       <c r="C159" t="n">
-        <v>5.22</v>
+        <v>17.66</v>
       </c>
       <c r="D159" t="n">
-        <v>0.38</v>
+        <v>2.61</v>
       </c>
       <c r="E159" t="b">
         <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>5.1</v>
+        <v>16.89</v>
       </c>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="n">
-        <v>-2.3</v>
+        <v>-4.36</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>HEXATRADEX</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>779.15</v>
+        <v>159.4</v>
       </c>
       <c r="C160" t="n">
-        <v>782.1</v>
+        <v>163.55</v>
       </c>
       <c r="D160" t="n">
-        <v>0.38</v>
+        <v>2.6</v>
       </c>
       <c r="E160" t="b">
         <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>776.25</v>
+        <v>160</v>
       </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="n">
-        <v>-0.75</v>
+        <v>-2.17</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>STEELCITY</t>
+          <t>CHAMUNDA</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>87.68000000000001</v>
+        <v>47.3</v>
       </c>
       <c r="C161" t="n">
-        <v>88</v>
+        <v>48.5</v>
       </c>
       <c r="D161" t="n">
-        <v>0.36</v>
+        <v>2.54</v>
       </c>
       <c r="E161" t="b">
         <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>88.79000000000001</v>
+        <v>48.5</v>
       </c>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>GLOBAL</t>
+          <t>PASUPTAC</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>97.61</v>
+        <v>49.73</v>
       </c>
       <c r="C162" t="n">
-        <v>97.95</v>
+        <v>50.99</v>
       </c>
       <c r="D162" t="n">
-        <v>0.35</v>
+        <v>2.53</v>
       </c>
       <c r="E162" t="b">
         <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>95.56999999999999</v>
+        <v>49.25</v>
       </c>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="n">
-        <v>-2.43</v>
+        <v>-3.41</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>DEEPINDS</t>
+          <t>SHRENIK</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>366.8</v>
+        <v>0.4</v>
       </c>
       <c r="C163" t="n">
-        <v>368.1</v>
+        <v>0.41</v>
       </c>
       <c r="D163" t="n">
-        <v>0.35</v>
+        <v>2.5</v>
       </c>
       <c r="E163" t="b">
         <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>365.7</v>
+        <v>0.4</v>
       </c>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="n">
-        <v>-0.65</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>GRMOVER</t>
+          <t>JMA</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>158.96</v>
+        <v>85.86</v>
       </c>
       <c r="C164" t="n">
-        <v>159.5</v>
+        <v>88</v>
       </c>
       <c r="D164" t="n">
-        <v>0.34</v>
+        <v>2.49</v>
       </c>
       <c r="E164" t="b">
         <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>156.43</v>
+        <v>87</v>
       </c>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="n">
-        <v>-1.92</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>POKARNA</t>
+          <t>SPENCERS</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>891.95</v>
+        <v>31.46</v>
       </c>
       <c r="C165" t="n">
-        <v>895</v>
+        <v>32.24</v>
       </c>
       <c r="D165" t="n">
-        <v>0.34</v>
+        <v>2.48</v>
       </c>
       <c r="E165" t="b">
         <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>886.15</v>
+        <v>31.53</v>
       </c>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="n">
-        <v>-0.99</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>JAYAGROGN</t>
+          <t>FLFL</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>173.94</v>
+        <v>1.21</v>
       </c>
       <c r="C166" t="n">
-        <v>174.5</v>
+        <v>1.24</v>
       </c>
       <c r="D166" t="n">
-        <v>0.32</v>
+        <v>2.48</v>
       </c>
       <c r="E166" t="b">
         <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>171.83</v>
+        <v>1.25</v>
       </c>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="n">
-        <v>-1.53</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>KALPATARU</t>
+          <t>STEL</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>314</v>
+        <v>517.1</v>
       </c>
       <c r="C167" t="n">
-        <v>315</v>
+        <v>529.9</v>
       </c>
       <c r="D167" t="n">
-        <v>0.32</v>
+        <v>2.48</v>
       </c>
       <c r="E167" t="b">
         <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>307.8</v>
+        <v>518.05</v>
       </c>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="n">
-        <v>-2.29</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>NEWJAISA</t>
+          <t>BODALCHEM</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>16.4</v>
+        <v>44.89</v>
       </c>
       <c r="C168" t="n">
-        <v>16.45</v>
+        <v>46</v>
       </c>
       <c r="D168" t="n">
-        <v>0.3</v>
+        <v>2.47</v>
       </c>
       <c r="E168" t="b">
         <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>17.05</v>
+        <v>44.85</v>
       </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="n">
-        <v>3.65</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>GANDHITUBE</t>
+          <t>GEEKAYWIRE</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>847.7</v>
+        <v>24.28</v>
       </c>
       <c r="C169" t="n">
-        <v>850</v>
+        <v>24.88</v>
       </c>
       <c r="D169" t="n">
-        <v>0.27</v>
+        <v>2.47</v>
       </c>
       <c r="E169" t="b">
         <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>842.9</v>
+        <v>23.98</v>
       </c>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="n">
-        <v>-0.84</v>
+        <v>-3.62</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CHETANA</t>
+          <t>GVPIL</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>38.35</v>
+        <v>437.25</v>
       </c>
       <c r="C170" t="n">
-        <v>38.45</v>
+        <v>448</v>
       </c>
       <c r="D170" t="n">
-        <v>0.26</v>
+        <v>2.46</v>
       </c>
       <c r="E170" t="b">
         <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>38.45</v>
+        <v>445</v>
       </c>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="n">
-        <v>0</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>MANAKCOAT</t>
+          <t>CROWN</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>117.71</v>
+        <v>121.91</v>
       </c>
       <c r="C171" t="n">
-        <v>118</v>
+        <v>124.91</v>
       </c>
       <c r="D171" t="n">
-        <v>0.25</v>
+        <v>2.46</v>
       </c>
       <c r="E171" t="b">
         <v>0</v>
       </c>
       <c r="F171" t="n">
-        <v>117</v>
+        <v>129.16</v>
       </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="n">
-        <v>-0.85</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>FMGOETZE</t>
+          <t>NIPPOBATRY</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>393.25</v>
+        <v>302.6</v>
       </c>
       <c r="C172" t="n">
-        <v>394.25</v>
+        <v>310</v>
       </c>
       <c r="D172" t="n">
-        <v>0.25</v>
+        <v>2.45</v>
       </c>
       <c r="E172" t="b">
         <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>387.15</v>
+        <v>315</v>
       </c>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="n">
-        <v>-1.8</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>CALSOFT</t>
+          <t>SEYAIND</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>11.96</v>
+        <v>10.67</v>
       </c>
       <c r="C173" t="n">
-        <v>11.99</v>
+        <v>10.93</v>
       </c>
       <c r="D173" t="n">
-        <v>0.25</v>
+        <v>2.44</v>
       </c>
       <c r="E173" t="b">
         <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>12</v>
+        <v>10.41</v>
       </c>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="n">
-        <v>0.08</v>
+        <v>-4.76</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>DPSCLTD</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>538.15</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="C174" t="n">
-        <v>539.5</v>
+        <v>8.85</v>
       </c>
       <c r="D174" t="n">
-        <v>0.25</v>
+        <v>2.43</v>
       </c>
       <c r="E174" t="b">
         <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>550.75</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="n">
-        <v>2.09</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>NELCO</t>
+          <t>HARDWYN</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>601.55</v>
+        <v>16.98</v>
       </c>
       <c r="C175" t="n">
-        <v>603</v>
+        <v>17.39</v>
       </c>
       <c r="D175" t="n">
-        <v>0.24</v>
+        <v>2.41</v>
       </c>
       <c r="E175" t="b">
         <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>600.45</v>
+        <v>16.97</v>
       </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="n">
-        <v>-0.42</v>
+        <v>-2.42</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>GVPTECH</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>1288.9</v>
+        <v>6.64</v>
       </c>
       <c r="C176" t="n">
-        <v>1292</v>
+        <v>6.8</v>
       </c>
       <c r="D176" t="n">
-        <v>0.24</v>
+        <v>2.41</v>
       </c>
       <c r="E176" t="b">
         <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>1306.2</v>
+        <v>6.9</v>
       </c>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="n">
-        <v>1.1</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>AXITA</t>
+          <t>BALMLAWRIE</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>8.5</v>
+        <v>170.33</v>
       </c>
       <c r="C177" t="n">
-        <v>8.52</v>
+        <v>174.4</v>
       </c>
       <c r="D177" t="n">
-        <v>0.24</v>
+        <v>2.39</v>
       </c>
       <c r="E177" t="b">
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>8.5</v>
+        <v>173.96</v>
       </c>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="n">
-        <v>-0.23</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>CAPITALSFB</t>
+          <t>FEL</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>259.8</v>
+        <v>0.42</v>
       </c>
       <c r="C178" t="n">
-        <v>260.4</v>
+        <v>0.43</v>
       </c>
       <c r="D178" t="n">
-        <v>0.23</v>
+        <v>2.38</v>
       </c>
       <c r="E178" t="b">
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>258.8</v>
+        <v>0.42</v>
       </c>
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="n">
-        <v>-0.61</v>
+        <v>-2.33</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>VINEETLAB</t>
+          <t>KILITCH</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>29.93</v>
+        <v>312.55</v>
       </c>
       <c r="C179" t="n">
-        <v>30</v>
+        <v>319.9</v>
       </c>
       <c r="D179" t="n">
-        <v>0.23</v>
+        <v>2.35</v>
       </c>
       <c r="E179" t="b">
         <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>29.3</v>
+        <v>319.95</v>
       </c>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="n">
-        <v>-2.33</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>DRONE</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>47.4</v>
+        <v>3604.8</v>
       </c>
       <c r="C180" t="n">
-        <v>47.5</v>
+        <v>3688.6</v>
       </c>
       <c r="D180" t="n">
-        <v>0.21</v>
+        <v>2.32</v>
       </c>
       <c r="E180" t="b">
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>46.85</v>
+        <v>3543.7</v>
       </c>
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="n">
-        <v>-1.37</v>
+        <v>-3.93</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>INDOTHAI</t>
+          <t>MAHASTEEL</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>258.3</v>
+        <v>762.35</v>
       </c>
       <c r="C181" t="n">
-        <v>258.85</v>
+        <v>780</v>
       </c>
       <c r="D181" t="n">
-        <v>0.21</v>
+        <v>2.32</v>
       </c>
       <c r="E181" t="b">
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>259</v>
+        <v>759</v>
       </c>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="n">
-        <v>0.06</v>
+        <v>-2.69</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>VINDHYATEL</t>
+          <t>RACLGEAR</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>1024.5</v>
+        <v>1368.4</v>
       </c>
       <c r="C182" t="n">
-        <v>1026.5</v>
+        <v>1400</v>
       </c>
       <c r="D182" t="n">
-        <v>0.2</v>
+        <v>2.31</v>
       </c>
       <c r="E182" t="b">
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>1011.9</v>
+        <v>1474.4</v>
       </c>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="n">
-        <v>-1.42</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>C2C</t>
+          <t>DHAMPURSUG</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>337.9</v>
+        <v>129.02</v>
       </c>
       <c r="C183" t="n">
-        <v>338.55</v>
+        <v>132</v>
       </c>
       <c r="D183" t="n">
-        <v>0.19</v>
+        <v>2.31</v>
       </c>
       <c r="E183" t="b">
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>338</v>
+        <v>127.65</v>
       </c>
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="n">
-        <v>-0.16</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>SPECIALITY</t>
+          <t>JYOTISTRUC</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>99.22</v>
+        <v>11.24</v>
       </c>
       <c r="C184" t="n">
-        <v>99.40000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="D184" t="n">
-        <v>0.18</v>
+        <v>2.31</v>
       </c>
       <c r="E184" t="b">
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>97.8</v>
+        <v>11.13</v>
       </c>
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="n">
-        <v>-1.61</v>
+        <v>-3.22</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>VIPCLOTHNG</t>
+          <t>MURUDCERA</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>19.71</v>
+        <v>30.79</v>
       </c>
       <c r="C185" t="n">
-        <v>19.74</v>
+        <v>31.5</v>
       </c>
       <c r="D185" t="n">
-        <v>0.15</v>
+        <v>2.31</v>
       </c>
       <c r="E185" t="b">
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>19.69</v>
+        <v>31.24</v>
       </c>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="n">
-        <v>-0.25</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>SPMLINFRA</t>
+          <t>SERVOTECH</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>165.77</v>
+        <v>67.25</v>
       </c>
       <c r="C186" t="n">
-        <v>165.99</v>
+        <v>68.8</v>
       </c>
       <c r="D186" t="n">
-        <v>0.13</v>
+        <v>2.3</v>
       </c>
       <c r="E186" t="b">
         <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>176.11</v>
+        <v>67.58</v>
       </c>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="n">
-        <v>6.1</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>IGPL</t>
+          <t>SCHAND</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>347.45</v>
+        <v>152.22</v>
       </c>
       <c r="C187" t="n">
-        <v>347.85</v>
+        <v>155.68</v>
       </c>
       <c r="D187" t="n">
-        <v>0.12</v>
+        <v>2.27</v>
       </c>
       <c r="E187" t="b">
         <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>335.6</v>
+        <v>149.48</v>
       </c>
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="n">
-        <v>-3.52</v>
+        <v>-3.98</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SIGMA</t>
+          <t>ZAGGLE</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>40.55</v>
+        <v>215.63</v>
       </c>
       <c r="C188" t="n">
-        <v>40.6</v>
+        <v>220.5</v>
       </c>
       <c r="D188" t="n">
-        <v>0.12</v>
+        <v>2.26</v>
       </c>
       <c r="E188" t="b">
         <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>39.86</v>
+        <v>216.7</v>
       </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="n">
-        <v>-1.82</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>MARKOLINES</t>
+          <t>PVSL</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>159.71</v>
+        <v>87.91</v>
       </c>
       <c r="C189" t="n">
-        <v>159.88</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D189" t="n">
-        <v>0.11</v>
+        <v>2.26</v>
       </c>
       <c r="E189" t="b">
         <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>159.08</v>
+        <v>88.84</v>
       </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="n">
-        <v>-0.5</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>RAMAPHO</t>
+          <t>OSIAHYPER</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>124.88</v>
+        <v>8.02</v>
       </c>
       <c r="C190" t="n">
-        <v>125</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D190" t="n">
-        <v>0.1</v>
+        <v>2.24</v>
       </c>
       <c r="E190" t="b">
         <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>122.73</v>
+        <v>8.08</v>
       </c>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="n">
-        <v>-1.82</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>SECURKLOUD</t>
+          <t>ARFIN</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>20.98</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="C191" t="n">
-        <v>21</v>
+        <v>75.5</v>
       </c>
       <c r="D191" t="n">
-        <v>0.1</v>
+        <v>2.23</v>
       </c>
       <c r="E191" t="b">
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>22</v>
+        <v>74.98</v>
       </c>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="n">
-        <v>4.76</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SHREEJISPG</t>
+          <t>J&amp;KBANK</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>390.3</v>
+        <v>116.24</v>
       </c>
       <c r="C192" t="n">
-        <v>390.6</v>
+        <v>118.8</v>
       </c>
       <c r="D192" t="n">
-        <v>0.08</v>
+        <v>2.2</v>
       </c>
       <c r="E192" t="b">
         <v>0</v>
       </c>
-      <c r="F192" t="n">
-        <v>384.8</v>
-      </c>
+      <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr"/>
-      <c r="H192" t="n">
-        <v>-1.48</v>
-      </c>
+      <c r="H192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>SANCO</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>2457</v>
+        <v>2.28</v>
       </c>
       <c r="C193" t="n">
-        <v>2458.7</v>
+        <v>2.33</v>
       </c>
       <c r="D193" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.19</v>
       </c>
       <c r="E193" t="b">
         <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>2350</v>
+        <v>2.3</v>
       </c>
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="n">
-        <v>-4.42</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SAGCEM</t>
+          <t>VIKASLIFE</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>189.89</v>
+        <v>1.37</v>
       </c>
       <c r="C194" t="n">
-        <v>190</v>
+        <v>1.4</v>
       </c>
       <c r="D194" t="n">
-        <v>0.06</v>
+        <v>2.19</v>
       </c>
       <c r="E194" t="b">
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>183.95</v>
+        <v>1.37</v>
       </c>
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="n">
-        <v>-3.18</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ZUARIIND</t>
+          <t>SUTLEJTEX</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>256.65</v>
+        <v>29.85</v>
       </c>
       <c r="C195" t="n">
-        <v>256.8</v>
+        <v>30.5</v>
       </c>
       <c r="D195" t="n">
-        <v>0.06</v>
+        <v>2.18</v>
       </c>
       <c r="E195" t="b">
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>251.6</v>
+        <v>30.48</v>
       </c>
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="n">
-        <v>-2.02</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>VPRPL</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>1024.9</v>
+        <v>41.4</v>
       </c>
       <c r="C196" t="n">
-        <v>1025.4</v>
+        <v>42.29</v>
       </c>
       <c r="D196" t="n">
-        <v>0.05</v>
+        <v>2.15</v>
       </c>
       <c r="E196" t="b">
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>1009</v>
+        <v>41.6</v>
       </c>
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="n">
-        <v>-1.6</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>MOLDTECH</t>
+          <t>RAMCOIND</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>129.12</v>
+        <v>278.9</v>
       </c>
       <c r="C197" t="n">
-        <v>129.19</v>
+        <v>284.9</v>
       </c>
       <c r="D197" t="n">
-        <v>0.05</v>
+        <v>2.15</v>
       </c>
       <c r="E197" t="b">
         <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>125.1</v>
+        <v>276.55</v>
       </c>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="n">
-        <v>-3.17</v>
+        <v>-2.93</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>EVERESTIND</t>
+          <t>LLOYDSENGG</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>405.8</v>
+        <v>43.96</v>
       </c>
       <c r="C198" t="n">
-        <v>406</v>
+        <v>44.9</v>
       </c>
       <c r="D198" t="n">
-        <v>0.05</v>
+        <v>2.14</v>
       </c>
       <c r="E198" t="b">
         <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>399.8</v>
+        <v>44.03</v>
       </c>
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="n">
-        <v>-1.53</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>LEMERITE</t>
+          <t>MEDIASSIST</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>448.65</v>
+        <v>340.5</v>
       </c>
       <c r="C199" t="n">
-        <v>448.8</v>
+        <v>347.8</v>
       </c>
       <c r="D199" t="n">
-        <v>0.03</v>
+        <v>2.14</v>
       </c>
       <c r="E199" t="b">
         <v>0</v>
       </c>
       <c r="F199" t="n">
-        <v>447.15</v>
+        <v>334.15</v>
       </c>
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="n">
-        <v>-0.37</v>
+        <v>-3.92</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>GENCON</t>
+          <t>MIRCELECTR</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>45.39</v>
+        <v>27.66</v>
       </c>
       <c r="C200" t="n">
-        <v>45.4</v>
+        <v>28.25</v>
       </c>
       <c r="D200" t="n">
-        <v>0.02</v>
+        <v>2.13</v>
       </c>
       <c r="E200" t="b">
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>43.7</v>
+        <v>26.98</v>
       </c>
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="n">
-        <v>-3.74</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>BODALCHEM</t>
+          <t>BHANDARI</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>46.39</v>
+        <v>2.82</v>
       </c>
       <c r="C201" t="n">
-        <v>46.4</v>
+        <v>2.88</v>
       </c>
       <c r="D201" t="n">
-        <v>0.02</v>
+        <v>2.13</v>
       </c>
       <c r="E201" t="b">
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>44.67</v>
+        <v>2.74</v>
       </c>
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="n">
-        <v>-3.73</v>
+        <v>-4.86</v>
       </c>
     </row>
   </sheetData>

--- a/data/trending_momentum_stocks.xlsx
+++ b/data/trending_momentum_stocks.xlsx
@@ -461,465 +461,465 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>UMESLTD</t>
+          <t>MODTHREAD</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.94</v>
+        <v>43.39</v>
       </c>
       <c r="C2" t="n">
-        <v>4.55</v>
+        <v>48.69</v>
       </c>
       <c r="D2" t="n">
-        <v>15.48</v>
+        <v>12.21</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>4.23</v>
+        <v>52.06</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>-7.03</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ELGIRUBCO</t>
+          <t>GLOBALE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38.25</v>
+        <v>10.7</v>
       </c>
       <c r="C3" t="n">
-        <v>43.4</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>13.46</v>
+        <v>12.15</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>45.9</v>
+        <v>11.06</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>5.76</v>
+        <v>-7.83</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RUBYMILLS</t>
+          <t>CENTEXT</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>203.88</v>
+        <v>20.72</v>
       </c>
       <c r="C4" t="n">
-        <v>230.02</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>12.82</v>
+        <v>11</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>223.15</v>
+        <v>21.96</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>-2.99</v>
+        <v>-4.52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UMAEXPORTS</t>
+          <t>RETAIL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.78</v>
+        <v>21.46</v>
       </c>
       <c r="C5" t="n">
-        <v>27.5</v>
+        <v>22.8</v>
       </c>
       <c r="D5" t="n">
-        <v>10.98</v>
+        <v>6.24</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>25.94</v>
+        <v>22.48</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>-5.67</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MAGNUM</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.91</v>
+        <v>20.26</v>
       </c>
       <c r="C6" t="n">
-        <v>7.65</v>
+        <v>21.5</v>
       </c>
       <c r="D6" t="n">
-        <v>10.71</v>
+        <v>6.12</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>7.14</v>
+        <v>20.5</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>-6.67</v>
+        <v>-4.65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RKDL</t>
+          <t>ACEINTEG</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.83</v>
+        <v>16.71</v>
       </c>
       <c r="C7" t="n">
-        <v>18.49</v>
+        <v>17.7</v>
       </c>
       <c r="D7" t="n">
-        <v>9.859999999999999</v>
+        <v>5.92</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>18.21</v>
+        <v>17.58</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>-1.51</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UNIINFO</t>
+          <t>JHS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12.84</v>
+        <v>8.94</v>
       </c>
       <c r="C8" t="n">
-        <v>14.05</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>9.42</v>
+        <v>5.7</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>13.38</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>-4.77</v>
+        <v>-3.39</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AAKASH</t>
+          <t>LATTEYS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.92</v>
+        <v>20.42</v>
       </c>
       <c r="C9" t="n">
-        <v>10.8</v>
+        <v>21.5</v>
       </c>
       <c r="D9" t="n">
-        <v>8.869999999999999</v>
+        <v>5.29</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>11.24</v>
+        <v>20.72</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>4.07</v>
+        <v>-3.63</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KHFM</t>
+          <t>AAKASH</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>11.9</v>
       </c>
       <c r="C10" t="n">
-        <v>67.40000000000001</v>
+        <v>12.52</v>
       </c>
       <c r="D10" t="n">
-        <v>8.710000000000001</v>
+        <v>5.21</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>60</v>
+        <v>10.53</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>-10.98</v>
+        <v>-15.89</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TECHD</t>
+          <t>ORKLAINDIA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>500.75</v>
+        <v>557.45</v>
       </c>
       <c r="C11" t="n">
-        <v>544</v>
+        <v>586.3</v>
       </c>
       <c r="D11" t="n">
-        <v>8.640000000000001</v>
+        <v>5.18</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>529.8</v>
+        <v>595.5</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>-2.61</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PRUDMOULI</t>
+          <t>SPENCERS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16.53</v>
+        <v>31.62</v>
       </c>
       <c r="C12" t="n">
-        <v>17.94</v>
+        <v>33.25</v>
       </c>
       <c r="D12" t="n">
-        <v>8.529999999999999</v>
+        <v>5.15</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>16.49</v>
+        <v>31.77</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>-8.08</v>
+        <v>-4.45</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MFML</t>
+          <t>HALDER</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21.1</v>
+        <v>254.15</v>
       </c>
       <c r="C13" t="n">
-        <v>22.78</v>
+        <v>266.85</v>
       </c>
       <c r="D13" t="n">
-        <v>7.96</v>
+        <v>5</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>22.09</v>
+        <v>264</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>-3.03</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BELLACASA</t>
+          <t>SETUINFRA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>265.25</v>
+        <v>0.4</v>
       </c>
       <c r="C14" t="n">
-        <v>285</v>
+        <v>0.42</v>
       </c>
       <c r="D14" t="n">
-        <v>7.45</v>
+        <v>5</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>265.35</v>
+        <v>0.42</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>-6.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TECILCHEM</t>
+          <t>GJL</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13.04</v>
+        <v>189.1</v>
       </c>
       <c r="C15" t="n">
-        <v>14</v>
+        <v>198.55</v>
       </c>
       <c r="D15" t="n">
-        <v>7.36</v>
+        <v>5</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>13.15</v>
+        <v>198.55</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>-6.07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SUMIT</t>
+          <t>YAAP</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>37.31</v>
+        <v>133.35</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>140</v>
       </c>
       <c r="D16" t="n">
-        <v>7.21</v>
+        <v>4.99</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>37.63</v>
+        <v>140</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>-5.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>KRITIKA</t>
+          <t>MANGALAM</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.45</v>
+        <v>30.73</v>
       </c>
       <c r="C17" t="n">
-        <v>5.83</v>
+        <v>32.26</v>
       </c>
       <c r="D17" t="n">
-        <v>6.97</v>
+        <v>4.98</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>5.84</v>
+        <v>32.26</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KAMOPAINTS</t>
+          <t>ESFL</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.2</v>
+        <v>155.55</v>
       </c>
       <c r="C18" t="n">
-        <v>4.48</v>
+        <v>163.3</v>
       </c>
       <c r="D18" t="n">
-        <v>6.67</v>
+        <v>4.98</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>4.21</v>
+        <v>163.3</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>-6.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GATECHDVR</t>
+          <t>GOLDSTAR</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.45</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>0.48</v>
+        <v>9.5</v>
       </c>
       <c r="D19" t="n">
-        <v>6.67</v>
+        <v>4.97</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.48</v>
+        <v>9.5</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
@@ -929,933 +929,929 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>FLFL</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.95</v>
+        <v>1.22</v>
       </c>
       <c r="C20" t="n">
-        <v>7.4</v>
+        <v>1.28</v>
       </c>
       <c r="D20" t="n">
-        <v>6.47</v>
+        <v>4.92</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>7.05</v>
+        <v>1.26</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>-4.73</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CTE</t>
+          <t>SOCL</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>27.33</v>
+        <v>30.65</v>
       </c>
       <c r="C21" t="n">
-        <v>28.98</v>
+        <v>32.15</v>
       </c>
       <c r="D21" t="n">
-        <v>6.04</v>
+        <v>4.89</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>27.9</v>
+        <v>30.8</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>-3.73</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HEADSUP</t>
+          <t>ESSENTIA</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7.55</v>
+        <v>1.46</v>
       </c>
       <c r="C22" t="n">
-        <v>8</v>
+        <v>1.53</v>
       </c>
       <c r="D22" t="n">
-        <v>5.96</v>
+        <v>4.79</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>-6.25</v>
+        <v>-1.96</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TAC</t>
+          <t>SURANASOL</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>432.2</v>
+        <v>21.67</v>
       </c>
       <c r="C23" t="n">
-        <v>457.9</v>
+        <v>22.7</v>
       </c>
       <c r="D23" t="n">
-        <v>5.95</v>
+        <v>4.75</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>457</v>
+        <v>22.4</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>-0.2</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SHIVATEX</t>
+          <t>CTE</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>149.16</v>
+        <v>26.17</v>
       </c>
       <c r="C24" t="n">
-        <v>158</v>
+        <v>27.4</v>
       </c>
       <c r="D24" t="n">
-        <v>5.93</v>
+        <v>4.7</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>151.3</v>
+        <v>27.46</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>-4.24</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ZODIACLOTH</t>
+          <t>TERASOFT</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>74.62</v>
+        <v>375.45</v>
       </c>
       <c r="C25" t="n">
-        <v>78.97</v>
+        <v>393</v>
       </c>
       <c r="D25" t="n">
-        <v>5.83</v>
+        <v>4.67</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>75.14</v>
+        <v>380.05</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>-4.85</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RVHL</t>
+          <t>S&amp;SPOWER</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>36.3</v>
+        <v>315.3</v>
       </c>
       <c r="C26" t="n">
-        <v>38.39</v>
+        <v>330</v>
       </c>
       <c r="D26" t="n">
-        <v>5.76</v>
+        <v>4.66</v>
       </c>
       <c r="E26" t="b">
         <v>0</v>
       </c>
-      <c r="F26" t="n">
-        <v>38</v>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="n">
-        <v>-1.02</v>
-      </c>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>RELIABLE</t>
+          <t>CREATIVEYE</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>128.8</v>
+        <v>6.88</v>
       </c>
       <c r="C27" t="n">
-        <v>136</v>
+        <v>7.2</v>
       </c>
       <c r="D27" t="n">
-        <v>5.59</v>
+        <v>4.65</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>125.89</v>
+        <v>6.66</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>-7.43</v>
+        <v>-7.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>UNIENTER</t>
+          <t>AMJLAND</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>101.17</v>
+        <v>39.19</v>
       </c>
       <c r="C28" t="n">
-        <v>106.81</v>
+        <v>41</v>
       </c>
       <c r="D28" t="n">
-        <v>5.57</v>
+        <v>4.62</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>107.95</v>
+        <v>39.65</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>1.07</v>
+        <v>-3.29</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NIRAJ</t>
+          <t>SANCO</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>28.3</v>
+        <v>2.17</v>
       </c>
       <c r="C29" t="n">
-        <v>29.85</v>
+        <v>2.27</v>
       </c>
       <c r="D29" t="n">
-        <v>5.48</v>
+        <v>4.61</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>29.09</v>
+        <v>2.17</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>-2.55</v>
+        <v>-4.41</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>RAMKY</t>
+          <t>TREJHARA</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>430.5</v>
+        <v>178.6</v>
       </c>
       <c r="C30" t="n">
-        <v>454</v>
+        <v>186.75</v>
       </c>
       <c r="D30" t="n">
-        <v>5.46</v>
+        <v>4.56</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>483.3</v>
+        <v>179</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>6.45</v>
+        <v>-4.15</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>OSWALSEEDS</t>
+          <t>ELGIRUBCO</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>11.75</v>
+        <v>45.9</v>
       </c>
       <c r="C31" t="n">
-        <v>12.39</v>
+        <v>47.96</v>
       </c>
       <c r="D31" t="n">
-        <v>5.45</v>
+        <v>4.49</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>12.87</v>
+        <v>45.95</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>3.87</v>
+        <v>-4.19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SGL</t>
+          <t>BAFNAPH</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>11.19</v>
+        <v>109.18</v>
       </c>
       <c r="C32" t="n">
-        <v>11.8</v>
+        <v>113.98</v>
       </c>
       <c r="D32" t="n">
-        <v>5.45</v>
+        <v>4.4</v>
       </c>
       <c r="E32" t="b">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>11.53</v>
+        <v>110.5</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>-2.29</v>
+        <v>-3.05</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>HMVL</t>
+          <t>JINDALPOLY</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>66.09999999999999</v>
+        <v>738</v>
       </c>
       <c r="C33" t="n">
-        <v>69.7</v>
+        <v>770</v>
       </c>
       <c r="D33" t="n">
-        <v>5.45</v>
+        <v>4.34</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>66.55</v>
+        <v>754</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>-4.52</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RADIOCITY</t>
+          <t>KRIDHANINF</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>5.87</v>
+        <v>2.59</v>
       </c>
       <c r="C34" t="n">
-        <v>6.19</v>
+        <v>2.7</v>
       </c>
       <c r="D34" t="n">
-        <v>5.45</v>
+        <v>4.25</v>
       </c>
       <c r="E34" t="b">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>5.9</v>
+        <v>2.84</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>-4.68</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>KRIDHANINF</t>
+          <t>ALANKIT</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.39</v>
+        <v>7.91</v>
       </c>
       <c r="C35" t="n">
-        <v>2.52</v>
+        <v>8.24</v>
       </c>
       <c r="D35" t="n">
-        <v>5.44</v>
+        <v>4.17</v>
       </c>
       <c r="E35" t="b">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>2.5</v>
+        <v>8.02</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>-0.79</v>
+        <v>-2.67</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PROZONER</t>
+          <t>ZEELEARN</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>45.47</v>
+        <v>5.55</v>
       </c>
       <c r="C36" t="n">
-        <v>47.9</v>
+        <v>5.78</v>
       </c>
       <c r="D36" t="n">
-        <v>5.34</v>
+        <v>4.14</v>
       </c>
       <c r="E36" t="b">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>45.37</v>
+        <v>5.63</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>-5.28</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DHRUV</t>
+          <t>XELPMOC</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>31.14</v>
+        <v>121.98</v>
       </c>
       <c r="C37" t="n">
-        <v>32.8</v>
+        <v>126.95</v>
       </c>
       <c r="D37" t="n">
-        <v>5.33</v>
+        <v>4.07</v>
       </c>
       <c r="E37" t="b">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>31.1</v>
+        <v>124.06</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>-5.18</v>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ESSARSHPNG</t>
+          <t>ABAN</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>23.55</v>
+        <v>21.24</v>
       </c>
       <c r="C38" t="n">
-        <v>24.8</v>
+        <v>22.1</v>
       </c>
       <c r="D38" t="n">
-        <v>5.31</v>
+        <v>4.05</v>
       </c>
       <c r="E38" t="b">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>26.31</v>
+        <v>22.3</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>6.09</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>KALANA</t>
+          <t>HMVL</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>25.85</v>
+        <v>67.38</v>
       </c>
       <c r="C39" t="n">
-        <v>27.2</v>
+        <v>70</v>
       </c>
       <c r="D39" t="n">
-        <v>5.22</v>
+        <v>3.89</v>
       </c>
       <c r="E39" t="b">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>27.5</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>1.1</v>
+        <v>-2.87</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NIBL</t>
+          <t>ALMONDZ</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>30.87</v>
+        <v>14.4</v>
       </c>
       <c r="C40" t="n">
-        <v>32.45</v>
+        <v>14.95</v>
       </c>
       <c r="D40" t="n">
-        <v>5.12</v>
+        <v>3.82</v>
       </c>
       <c r="E40" t="b">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>30.62</v>
+        <v>15.12</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>-5.64</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BAGFILMS</t>
+          <t>ALKALI</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4.74</v>
+        <v>59.78</v>
       </c>
       <c r="C41" t="n">
-        <v>4.98</v>
+        <v>62</v>
       </c>
       <c r="D41" t="n">
-        <v>5.06</v>
+        <v>3.71</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>4.85</v>
+        <v>61.25</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>-2.61</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BEARDSELL</t>
+          <t>RILINFRA</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>24.76</v>
+        <v>33.65</v>
       </c>
       <c r="C42" t="n">
-        <v>26</v>
+        <v>34.9</v>
       </c>
       <c r="D42" t="n">
-        <v>5.01</v>
+        <v>3.71</v>
       </c>
       <c r="E42" t="b">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>24.8</v>
+        <v>34</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>-4.62</v>
+        <v>-2.58</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MANGALAM</t>
+          <t>RUBFILA</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>29.27</v>
+        <v>64.53</v>
       </c>
       <c r="C43" t="n">
-        <v>30.73</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>4.99</v>
+        <v>3.67</v>
       </c>
       <c r="E43" t="b">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>30.73</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>-3.48</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ESFL</t>
+          <t>NAVKARURB</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>148.15</v>
+        <v>1.1</v>
       </c>
       <c r="C44" t="n">
-        <v>155.55</v>
+        <v>1.14</v>
       </c>
       <c r="D44" t="n">
-        <v>4.99</v>
+        <v>3.64</v>
       </c>
       <c r="E44" t="b">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>155.55</v>
+        <v>1.12</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ESCONET</t>
+          <t>GAYAHWS</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>121.25</v>
+        <v>2.24</v>
       </c>
       <c r="C45" t="n">
-        <v>127.25</v>
+        <v>2.32</v>
       </c>
       <c r="D45" t="n">
-        <v>4.95</v>
+        <v>3.57</v>
       </c>
       <c r="E45" t="b">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>122.05</v>
+        <v>2.3</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>-4.09</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NEWJAISA</t>
+          <t>UMESLTD</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>17.2</v>
+        <v>4.21</v>
       </c>
       <c r="C46" t="n">
-        <v>18.05</v>
+        <v>4.36</v>
       </c>
       <c r="D46" t="n">
-        <v>4.94</v>
+        <v>3.56</v>
       </c>
       <c r="E46" t="b">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>17.85</v>
+        <v>4.23</v>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>-1.11</v>
+        <v>-2.98</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SUVIDHAA</t>
+          <t>CYBERMEDIA</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.84</v>
+        <v>14.46</v>
       </c>
       <c r="C47" t="n">
-        <v>2.98</v>
+        <v>14.97</v>
       </c>
       <c r="D47" t="n">
-        <v>4.93</v>
+        <v>3.53</v>
       </c>
       <c r="E47" t="b">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>2.99</v>
+        <v>14.01</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>0.34</v>
+        <v>-6.41</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>VIVIMEDLAB</t>
+          <t>MANOMAY</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>6.93</v>
+        <v>215.9</v>
       </c>
       <c r="C48" t="n">
-        <v>7.27</v>
+        <v>223.5</v>
       </c>
       <c r="D48" t="n">
-        <v>4.91</v>
+        <v>3.52</v>
       </c>
       <c r="E48" t="b">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>7.09</v>
+        <v>214.01</v>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>-2.48</v>
+        <v>-4.25</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ALKALI</t>
+          <t>SHREYANIND</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>58.15</v>
+        <v>149.65</v>
       </c>
       <c r="C49" t="n">
-        <v>61</v>
+        <v>154.9</v>
       </c>
       <c r="D49" t="n">
-        <v>4.9</v>
+        <v>3.51</v>
       </c>
       <c r="E49" t="b">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>59.9</v>
+        <v>151</v>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>-1.8</v>
+        <v>-2.52</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MASTER</t>
+          <t>DCXINDIA</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>293.7</v>
+        <v>177.75</v>
       </c>
       <c r="C50" t="n">
-        <v>308</v>
+        <v>183.98</v>
       </c>
       <c r="D50" t="n">
-        <v>4.87</v>
+        <v>3.5</v>
       </c>
       <c r="E50" t="b">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>295</v>
+        <v>196.27</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>-4.22</v>
+        <v>6.68</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GKWLIMITED</t>
+          <t>BESTAGRO</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1609.7</v>
+        <v>15.42</v>
       </c>
       <c r="C51" t="n">
-        <v>1688</v>
+        <v>15.96</v>
       </c>
       <c r="D51" t="n">
-        <v>4.86</v>
+        <v>3.5</v>
       </c>
       <c r="E51" t="b">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>1609.9</v>
+        <v>16.19</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>-4.63</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ANKITMETAL</t>
+          <t>KIRLOSBROS</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.67</v>
+        <v>1493.9</v>
       </c>
       <c r="C52" t="n">
-        <v>1.75</v>
+        <v>1546.2</v>
       </c>
       <c r="D52" t="n">
-        <v>4.79</v>
+        <v>3.5</v>
       </c>
       <c r="E52" t="b">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>1.73</v>
+        <v>1605.8</v>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>-1.14</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>GSS</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>23.28</v>
+        <v>12.97</v>
       </c>
       <c r="C53" t="n">
-        <v>24.39</v>
+        <v>13.42</v>
       </c>
       <c r="D53" t="n">
-        <v>4.77</v>
+        <v>3.47</v>
       </c>
       <c r="E53" t="b">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>23.75</v>
+        <v>12.86</v>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>-2.62</v>
+        <v>-4.17</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FILATFASH</t>
+          <t>HAVISHA</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.21</v>
+        <v>1.45</v>
       </c>
       <c r="C54" t="n">
-        <v>0.22</v>
+        <v>1.5</v>
       </c>
       <c r="D54" t="n">
-        <v>4.76</v>
+        <v>3.45</v>
       </c>
       <c r="E54" t="b">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0.22</v>
+        <v>1.49</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NURECA</t>
+          <t>RANASUG</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>272.05</v>
+        <v>11.87</v>
       </c>
       <c r="C55" t="n">
-        <v>285</v>
+        <v>12.28</v>
       </c>
       <c r="D55" t="n">
-        <v>4.76</v>
+        <v>3.45</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>270.6</v>
+        <v>11.66</v>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
@@ -1865,3793 +1861,3797 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BALAJEE</t>
+          <t>DEEDEV</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>26.01</v>
+        <v>276.5</v>
       </c>
       <c r="C56" t="n">
-        <v>27.24</v>
+        <v>285.95</v>
       </c>
       <c r="D56" t="n">
-        <v>4.73</v>
+        <v>3.42</v>
       </c>
       <c r="E56" t="b">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>26.1</v>
+        <v>285.8</v>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>-4.19</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>RANASUG</t>
+          <t>MARC</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>11.83</v>
+        <v>61.95</v>
       </c>
       <c r="C57" t="n">
-        <v>12.39</v>
+        <v>64</v>
       </c>
       <c r="D57" t="n">
-        <v>4.73</v>
+        <v>3.31</v>
       </c>
       <c r="E57" t="b">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>11.98</v>
+        <v>63.85</v>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>-3.31</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>JINDRILL</t>
+          <t>PRITI</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>598.3</v>
+        <v>40.57</v>
       </c>
       <c r="C58" t="n">
-        <v>626.5</v>
+        <v>41.9</v>
       </c>
       <c r="D58" t="n">
-        <v>4.71</v>
+        <v>3.28</v>
       </c>
       <c r="E58" t="b">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>624.6</v>
+        <v>40.23</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>-0.3</v>
+        <v>-3.99</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>GLOBALVECT</t>
+          <t>ARCHIES</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>157.35</v>
+        <v>14.47</v>
       </c>
       <c r="C59" t="n">
-        <v>164.75</v>
+        <v>14.94</v>
       </c>
       <c r="D59" t="n">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="E59" t="b">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>157.7</v>
+        <v>14.85</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>-4.28</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MCL</t>
+          <t>SWANDEF</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>70</v>
+        <v>1937.2</v>
       </c>
       <c r="C60" t="n">
-        <v>73.28</v>
+        <v>1999.9</v>
       </c>
       <c r="D60" t="n">
-        <v>4.69</v>
+        <v>3.24</v>
       </c>
       <c r="E60" t="b">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>68.8</v>
+        <v>2018</v>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>-6.11</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>GAYAHWS</t>
+          <t>RVTH</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2.14</v>
+        <v>619</v>
       </c>
       <c r="C61" t="n">
-        <v>2.24</v>
+        <v>638.9</v>
       </c>
       <c r="D61" t="n">
-        <v>4.67</v>
+        <v>3.21</v>
       </c>
       <c r="E61" t="b">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>2.23</v>
+        <v>620</v>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>-0.45</v>
+        <v>-2.96</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>HMT</t>
+          <t>USK</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>66.98</v>
+        <v>27.22</v>
       </c>
       <c r="C62" t="n">
-        <v>70.09999999999999</v>
+        <v>28.09</v>
       </c>
       <c r="D62" t="n">
-        <v>4.66</v>
+        <v>3.2</v>
       </c>
       <c r="E62" t="b">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>69.75</v>
+        <v>26.85</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>-0.5</v>
+        <v>-4.41</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ASHIMASYN</t>
+          <t>AAATECH</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>13.79</v>
+        <v>91.02</v>
       </c>
       <c r="C63" t="n">
-        <v>14.43</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="D63" t="n">
-        <v>4.64</v>
+        <v>3.16</v>
       </c>
       <c r="E63" t="b">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>14.42</v>
+        <v>92.3</v>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>KOHINOOR</t>
+          <t>DSFCL</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>23.99</v>
+        <v>30.05</v>
       </c>
       <c r="C64" t="n">
-        <v>25.1</v>
+        <v>31</v>
       </c>
       <c r="D64" t="n">
-        <v>4.63</v>
+        <v>3.16</v>
       </c>
       <c r="E64" t="b">
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>24.85</v>
+        <v>29.25</v>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>-1</v>
+        <v>-5.65</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>GOLDSTAR</t>
+          <t>OSIAHYPER</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>8.65</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="C65" t="n">
-        <v>9.050000000000001</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="D65" t="n">
-        <v>4.62</v>
+        <v>3.08</v>
       </c>
       <c r="E65" t="b">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>9.050000000000001</v>
+        <v>8.01</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AARON</t>
+          <t>KAMOPAINTS</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>140.9</v>
+        <v>4.26</v>
       </c>
       <c r="C66" t="n">
-        <v>147.4</v>
+        <v>4.39</v>
       </c>
       <c r="D66" t="n">
-        <v>4.61</v>
+        <v>3.05</v>
       </c>
       <c r="E66" t="b">
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>148.88</v>
+        <v>4.22</v>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>1</v>
+        <v>-3.87</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>GLOBALE</t>
+          <t>DEVIT</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>10.52</v>
+        <v>26.18</v>
       </c>
       <c r="C67" t="n">
-        <v>11</v>
+        <v>26.97</v>
       </c>
       <c r="D67" t="n">
-        <v>4.56</v>
+        <v>3.02</v>
       </c>
       <c r="E67" t="b">
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>10.31</v>
+        <v>26.45</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>-6.27</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PRIMO</t>
+          <t>KOTYARK</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>18.09</v>
+        <v>278.35</v>
       </c>
       <c r="C68" t="n">
-        <v>18.9</v>
+        <v>286.75</v>
       </c>
       <c r="D68" t="n">
-        <v>4.48</v>
+        <v>3.02</v>
       </c>
       <c r="E68" t="b">
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>18.19</v>
+        <v>278.9</v>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>-3.76</v>
+        <v>-2.74</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>GATECH</t>
+          <t>LTFOODS</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.45</v>
+        <v>430.15</v>
       </c>
       <c r="C69" t="n">
-        <v>0.47</v>
+        <v>443</v>
       </c>
       <c r="D69" t="n">
-        <v>4.44</v>
+        <v>2.99</v>
       </c>
       <c r="E69" t="b">
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>0.47</v>
+        <v>445.85</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GFLLIMITED</t>
+          <t>LYPSAGEMS</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>43.46</v>
+        <v>5.05</v>
       </c>
       <c r="C70" t="n">
-        <v>45.38</v>
+        <v>5.2</v>
       </c>
       <c r="D70" t="n">
-        <v>4.42</v>
+        <v>2.97</v>
       </c>
       <c r="E70" t="b">
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>44.57</v>
+        <v>5.19</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>-1.78</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ASIANTILES</t>
+          <t>ESAFSFB</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>66.09</v>
+        <v>26.04</v>
       </c>
       <c r="C71" t="n">
-        <v>68.98999999999999</v>
+        <v>26.78</v>
       </c>
       <c r="D71" t="n">
-        <v>4.39</v>
+        <v>2.84</v>
       </c>
       <c r="E71" t="b">
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>66.68000000000001</v>
+        <v>26</v>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>-3.35</v>
+        <v>-2.91</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MOTOGENFIN</t>
+          <t>HYBRIDFIN</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>20.13</v>
+        <v>18.66</v>
       </c>
       <c r="C72" t="n">
-        <v>21</v>
+        <v>19.18</v>
       </c>
       <c r="D72" t="n">
-        <v>4.32</v>
+        <v>2.79</v>
       </c>
       <c r="E72" t="b">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>20.61</v>
+        <v>20.14</v>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>-1.86</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PILITA</t>
+          <t>VHLTD</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>7.71</v>
+        <v>143.99</v>
       </c>
       <c r="C73" t="n">
-        <v>8.039999999999999</v>
+        <v>148</v>
       </c>
       <c r="D73" t="n">
-        <v>4.28</v>
+        <v>2.78</v>
       </c>
       <c r="E73" t="b">
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>7.96</v>
+        <v>148.01</v>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>-1</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CYBERTECH</t>
+          <t>FRACTAL</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>103.67</v>
+        <v>759.15</v>
       </c>
       <c r="C74" t="n">
-        <v>108</v>
+        <v>780</v>
       </c>
       <c r="D74" t="n">
-        <v>4.18</v>
+        <v>2.75</v>
       </c>
       <c r="E74" t="b">
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>105</v>
+        <v>818.8</v>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>-2.78</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CLEDUCATE</t>
+          <t>AKSHAR</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>41.86</v>
+        <v>0.37</v>
       </c>
       <c r="C75" t="n">
-        <v>43.59</v>
+        <v>0.38</v>
       </c>
       <c r="D75" t="n">
-        <v>4.13</v>
+        <v>2.7</v>
       </c>
       <c r="E75" t="b">
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>44.4</v>
+        <v>0.38</v>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GINNIFILA</t>
+          <t>FINKURVE</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>36.89</v>
+        <v>66.91</v>
       </c>
       <c r="C76" t="n">
-        <v>38.4</v>
+        <v>68.7</v>
       </c>
       <c r="D76" t="n">
-        <v>4.09</v>
+        <v>2.68</v>
       </c>
       <c r="E76" t="b">
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>37.19</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>-3.15</v>
+        <v>-1.85</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ASTRON</t>
+          <t>SHAH</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>3.95</v>
+        <v>4.86</v>
       </c>
       <c r="C77" t="n">
-        <v>4.11</v>
+        <v>4.99</v>
       </c>
       <c r="D77" t="n">
-        <v>4.05</v>
+        <v>2.67</v>
       </c>
       <c r="E77" t="b">
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>4.09</v>
+        <v>4.9</v>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>-0.49</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>KSHITIJPOL</t>
+          <t>SONAMLTD</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2.5</v>
+        <v>51.23</v>
       </c>
       <c r="C78" t="n">
-        <v>2.6</v>
+        <v>52.6</v>
       </c>
       <c r="D78" t="n">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="E78" t="b">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>2.48</v>
+        <v>51.21</v>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>-4.62</v>
+        <v>-2.64</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>OILCOUNTUB</t>
+          <t>MCLOUD</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>47.71</v>
+        <v>23.34</v>
       </c>
       <c r="C79" t="n">
-        <v>49.6</v>
+        <v>23.96</v>
       </c>
       <c r="D79" t="n">
-        <v>3.96</v>
+        <v>2.66</v>
       </c>
       <c r="E79" t="b">
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>47.08</v>
+        <v>23.65</v>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>-5.08</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CPEDU</t>
+          <t>LANCORHOL</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>180.8</v>
+        <v>22.96</v>
       </c>
       <c r="C80" t="n">
-        <v>187.95</v>
+        <v>23.57</v>
       </c>
       <c r="D80" t="n">
-        <v>3.95</v>
+        <v>2.66</v>
       </c>
       <c r="E80" t="b">
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>184.6</v>
+        <v>23.57</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>-1.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ABCOTS</t>
+          <t>ALPA</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>388.35</v>
+        <v>63.23</v>
       </c>
       <c r="C81" t="n">
-        <v>403.6</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="D81" t="n">
-        <v>3.93</v>
+        <v>2.64</v>
       </c>
       <c r="E81" t="b">
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>413.7</v>
+        <v>63.59</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>2.5</v>
+        <v>-2.02</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ORCHASP</t>
+          <t>NITIRAJ</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2.56</v>
+        <v>204.57</v>
       </c>
       <c r="C82" t="n">
-        <v>2.66</v>
+        <v>209.95</v>
       </c>
       <c r="D82" t="n">
-        <v>3.91</v>
+        <v>2.63</v>
       </c>
       <c r="E82" t="b">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>2.38</v>
+        <v>205</v>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>-10.53</v>
+        <v>-2.36</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SAMPANN</t>
+          <t>DRCSYSTEMS</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>27.8</v>
+        <v>14.07</v>
       </c>
       <c r="C83" t="n">
-        <v>28.88</v>
+        <v>14.44</v>
       </c>
       <c r="D83" t="n">
-        <v>3.88</v>
+        <v>2.63</v>
       </c>
       <c r="E83" t="b">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>28.08</v>
+        <v>14.39</v>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>-2.77</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SAMBHAAV</t>
+          <t>AARON</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>6.98</v>
+        <v>148.13</v>
       </c>
       <c r="C84" t="n">
-        <v>7.25</v>
+        <v>152</v>
       </c>
       <c r="D84" t="n">
-        <v>3.87</v>
+        <v>2.61</v>
       </c>
       <c r="E84" t="b">
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>7.15</v>
+        <v>151.2</v>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>-1.38</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BTML</t>
+          <t>UNITEDPOLY</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>7.26</v>
+        <v>24.29</v>
       </c>
       <c r="C85" t="n">
-        <v>7.54</v>
+        <v>24.9</v>
       </c>
       <c r="D85" t="n">
-        <v>3.86</v>
+        <v>2.51</v>
       </c>
       <c r="E85" t="b">
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>7.41</v>
+        <v>25.49</v>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>-1.72</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SILGO</t>
+          <t>ANTGRAPHIC</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>69.36</v>
+        <v>0.8</v>
       </c>
       <c r="C86" t="n">
-        <v>72</v>
+        <v>0.82</v>
       </c>
       <c r="D86" t="n">
-        <v>3.81</v>
+        <v>2.5</v>
       </c>
       <c r="E86" t="b">
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>73.34</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>1.86</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TREL</t>
+          <t>HILTON</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>23.89</v>
+        <v>16.97</v>
       </c>
       <c r="C87" t="n">
-        <v>24.8</v>
+        <v>17.39</v>
       </c>
       <c r="D87" t="n">
-        <v>3.81</v>
+        <v>2.47</v>
       </c>
       <c r="E87" t="b">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>24.18</v>
+        <v>17.18</v>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>-2.5</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>UEL</t>
+          <t>ACCURACY</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>161.83</v>
+        <v>4.47</v>
       </c>
       <c r="C88" t="n">
-        <v>167.99</v>
+        <v>4.58</v>
       </c>
       <c r="D88" t="n">
-        <v>3.81</v>
+        <v>2.46</v>
       </c>
       <c r="E88" t="b">
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>169.92</v>
+        <v>4.61</v>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>1.15</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AURUM</t>
+          <t>OILCOUNTUB</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>165.64</v>
+        <v>46.26</v>
       </c>
       <c r="C89" t="n">
-        <v>171.9</v>
+        <v>47.4</v>
       </c>
       <c r="D89" t="n">
-        <v>3.78</v>
+        <v>2.46</v>
       </c>
       <c r="E89" t="b">
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>164.31</v>
+        <v>46.23</v>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>-4.42</v>
+        <v>-2.47</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>INDOWIND</t>
+          <t>RHFL</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>8.76</v>
+        <v>2.04</v>
       </c>
       <c r="C90" t="n">
-        <v>9.09</v>
+        <v>2.09</v>
       </c>
       <c r="D90" t="n">
-        <v>3.77</v>
+        <v>2.45</v>
       </c>
       <c r="E90" t="b">
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>8.859999999999999</v>
+        <v>2.14</v>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>-2.53</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>JALAN</t>
+          <t>SHRENIK</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>2.65</v>
+        <v>0.41</v>
       </c>
       <c r="C91" t="n">
-        <v>2.75</v>
+        <v>0.42</v>
       </c>
       <c r="D91" t="n">
-        <v>3.77</v>
+        <v>2.44</v>
       </c>
       <c r="E91" t="b">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>2.75</v>
+        <v>0.43</v>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SMLT</t>
+          <t>MRPL</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>73.25</v>
+        <v>196.24</v>
       </c>
       <c r="C92" t="n">
-        <v>75.98</v>
+        <v>200.99</v>
       </c>
       <c r="D92" t="n">
-        <v>3.73</v>
+        <v>2.42</v>
       </c>
       <c r="E92" t="b">
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>74.26000000000001</v>
+        <v>203.35</v>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
-        <v>-2.26</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ISFT</t>
+          <t>CHEMFAB</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>69.41</v>
+        <v>375.35</v>
       </c>
       <c r="C93" t="n">
-        <v>72</v>
+        <v>384.45</v>
       </c>
       <c r="D93" t="n">
-        <v>3.73</v>
+        <v>2.42</v>
       </c>
       <c r="E93" t="b">
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>69.66</v>
+        <v>383.9</v>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
-        <v>-3.25</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MAZDA</t>
+          <t>CCCL</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>192.76</v>
+        <v>15.33</v>
       </c>
       <c r="C94" t="n">
-        <v>199.9</v>
+        <v>15.7</v>
       </c>
       <c r="D94" t="n">
-        <v>3.7</v>
+        <v>2.41</v>
       </c>
       <c r="E94" t="b">
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>196.6</v>
+        <v>15.39</v>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>-1.65</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>KRITINUT</t>
+          <t>CHENNPETRO</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>67.37</v>
+        <v>991.5</v>
       </c>
       <c r="C95" t="n">
-        <v>69.8</v>
+        <v>1015</v>
       </c>
       <c r="D95" t="n">
-        <v>3.61</v>
+        <v>2.37</v>
       </c>
       <c r="E95" t="b">
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>67.84999999999999</v>
+        <v>1003.3</v>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>-2.79</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>KHAITANLTD</t>
+          <t>KAKATCEM</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>93.62</v>
+        <v>108.05</v>
       </c>
       <c r="C96" t="n">
-        <v>96.98999999999999</v>
+        <v>110.6</v>
       </c>
       <c r="D96" t="n">
-        <v>3.6</v>
+        <v>2.36</v>
       </c>
       <c r="E96" t="b">
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>-2.05</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>RELTD</t>
+          <t>GOKUL</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>137.07</v>
+        <v>39.91</v>
       </c>
       <c r="C97" t="n">
-        <v>142</v>
+        <v>40.85</v>
       </c>
       <c r="D97" t="n">
-        <v>3.6</v>
+        <v>2.36</v>
       </c>
       <c r="E97" t="b">
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>137.4</v>
+        <v>39.5</v>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>-3.24</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SETCO</t>
+          <t>SSEGL</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>17.96</v>
+        <v>347.35</v>
       </c>
       <c r="C98" t="n">
-        <v>18.6</v>
+        <v>355.5</v>
       </c>
       <c r="D98" t="n">
-        <v>3.56</v>
+        <v>2.35</v>
       </c>
       <c r="E98" t="b">
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>17.71</v>
+        <v>355.9</v>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>-4.78</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>GJL</t>
+          <t>TEXMOPIPES</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>180.1</v>
+        <v>43.19</v>
       </c>
       <c r="C99" t="n">
-        <v>186.5</v>
+        <v>44.19</v>
       </c>
       <c r="D99" t="n">
-        <v>3.55</v>
+        <v>2.32</v>
       </c>
       <c r="E99" t="b">
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>189.1</v>
+        <v>43.53</v>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
-        <v>1.39</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MOTISONS</t>
+          <t>UFO</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>14.33</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="C100" t="n">
-        <v>14.83</v>
+        <v>69.89</v>
       </c>
       <c r="D100" t="n">
-        <v>3.49</v>
+        <v>2.3</v>
       </c>
       <c r="E100" t="b">
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>14.61</v>
+        <v>69.2</v>
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>-1.48</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>PRAENG</t>
+          <t>AKG</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>21.73</v>
+        <v>10.95</v>
       </c>
       <c r="C101" t="n">
-        <v>22.48</v>
+        <v>11.2</v>
       </c>
       <c r="D101" t="n">
-        <v>3.45</v>
+        <v>2.28</v>
       </c>
       <c r="E101" t="b">
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>21.72</v>
+        <v>10.92</v>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>-3.38</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>KAPSTON</t>
+          <t>RAMKY</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>393.5</v>
+        <v>481.7</v>
       </c>
       <c r="C102" t="n">
-        <v>407</v>
+        <v>492.7</v>
       </c>
       <c r="D102" t="n">
-        <v>3.43</v>
+        <v>2.28</v>
       </c>
       <c r="E102" t="b">
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>402.05</v>
+        <v>493.35</v>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>-1.22</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>GEECEE</t>
+          <t>THOMASCOTT</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>285.25</v>
+        <v>272.8</v>
       </c>
       <c r="C103" t="n">
-        <v>295</v>
+        <v>279</v>
       </c>
       <c r="D103" t="n">
-        <v>3.42</v>
+        <v>2.27</v>
       </c>
       <c r="E103" t="b">
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>286.8</v>
+        <v>273.75</v>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>-2.78</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DSFCL</t>
+          <t>CYBERTECH</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>29.5</v>
+        <v>103.67</v>
       </c>
       <c r="C104" t="n">
-        <v>30.5</v>
+        <v>106</v>
       </c>
       <c r="D104" t="n">
-        <v>3.39</v>
+        <v>2.25</v>
       </c>
       <c r="E104" t="b">
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>29.68</v>
+        <v>107.96</v>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
-        <v>-2.69</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>NOIDATOLL</t>
+          <t>HCL-INSYS</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>3.56</v>
+        <v>12.42</v>
       </c>
       <c r="C105" t="n">
-        <v>3.68</v>
+        <v>12.7</v>
       </c>
       <c r="D105" t="n">
-        <v>3.37</v>
+        <v>2.25</v>
       </c>
       <c r="E105" t="b">
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>3.84</v>
+        <v>12.57</v>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>4.35</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>EPACKPEB</t>
+          <t>UEL</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>167.87</v>
+        <v>169.92</v>
       </c>
       <c r="C106" t="n">
-        <v>173.5</v>
+        <v>173.7</v>
       </c>
       <c r="D106" t="n">
-        <v>3.35</v>
+        <v>2.22</v>
       </c>
       <c r="E106" t="b">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>168.01</v>
+        <v>178.41</v>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
-        <v>-3.16</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>DCMNVL</t>
+          <t>BSL</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>131.12</v>
+        <v>122</v>
       </c>
       <c r="C107" t="n">
-        <v>135.5</v>
+        <v>124.7</v>
       </c>
       <c r="D107" t="n">
-        <v>3.34</v>
+        <v>2.21</v>
       </c>
       <c r="E107" t="b">
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>129.1</v>
+        <v>129.3</v>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>-4.72</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>KANORICHEM</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>721.05</v>
+        <v>65.97</v>
       </c>
       <c r="C108" t="n">
-        <v>745</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="D108" t="n">
-        <v>3.32</v>
+        <v>2.17</v>
       </c>
       <c r="E108" t="b">
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>726.1</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
-        <v>-2.54</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>K2INFRA</t>
+          <t>ADVANIHOTR</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>50.2</v>
+        <v>53.77</v>
       </c>
       <c r="C109" t="n">
-        <v>51.85</v>
+        <v>54.93</v>
       </c>
       <c r="D109" t="n">
-        <v>3.29</v>
+        <v>2.16</v>
       </c>
       <c r="E109" t="b">
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>51.85</v>
+        <v>53.65</v>
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>0</v>
+        <v>-2.33</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CALSOFT</t>
+          <t>HINDCON</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>12.87</v>
+        <v>19.08</v>
       </c>
       <c r="C110" t="n">
-        <v>13.29</v>
+        <v>19.49</v>
       </c>
       <c r="D110" t="n">
-        <v>3.26</v>
+        <v>2.15</v>
       </c>
       <c r="E110" t="b">
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>13.28</v>
+        <v>19.18</v>
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
-        <v>-0.08</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MANOMAY</t>
+          <t>KUANTUM</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>212.14</v>
+        <v>84.11</v>
       </c>
       <c r="C111" t="n">
-        <v>219</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="D111" t="n">
-        <v>3.23</v>
+        <v>2.13</v>
       </c>
       <c r="E111" t="b">
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>217.9</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>-0.5</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BIRLAMONEY</t>
+          <t>GATECH</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>128.51</v>
+        <v>0.47</v>
       </c>
       <c r="C112" t="n">
-        <v>132.65</v>
+        <v>0.48</v>
       </c>
       <c r="D112" t="n">
-        <v>3.22</v>
+        <v>2.13</v>
       </c>
       <c r="E112" t="b">
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>129.42</v>
+        <v>0.48</v>
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
-        <v>-2.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ABAN</t>
+          <t>AQYLON</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>20.23</v>
+        <v>113.8</v>
       </c>
       <c r="C113" t="n">
-        <v>20.88</v>
+        <v>116.2</v>
       </c>
       <c r="D113" t="n">
-        <v>3.21</v>
+        <v>2.11</v>
       </c>
       <c r="E113" t="b">
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>21.24</v>
+        <v>119.4</v>
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>1.72</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>BAIDFIN</t>
+          <t>NIBE</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>11</v>
+        <v>979.8</v>
       </c>
       <c r="C114" t="n">
-        <v>11.35</v>
+        <v>1000</v>
       </c>
       <c r="D114" t="n">
-        <v>3.18</v>
+        <v>2.06</v>
       </c>
       <c r="E114" t="b">
         <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>11.16</v>
+        <v>1030.2</v>
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
-        <v>-1.67</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MOSCHIP</t>
+          <t>MTEDUCARE</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>172.26</v>
+        <v>1.46</v>
       </c>
       <c r="C115" t="n">
-        <v>177.7</v>
+        <v>1.49</v>
       </c>
       <c r="D115" t="n">
-        <v>3.16</v>
+        <v>2.05</v>
       </c>
       <c r="E115" t="b">
         <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>173.18</v>
+        <v>1.51</v>
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>-2.54</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>MKPL</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>2626.9</v>
+        <v>4.9</v>
       </c>
       <c r="C116" t="n">
-        <v>2710</v>
+        <v>5</v>
       </c>
       <c r="D116" t="n">
-        <v>3.16</v>
+        <v>2.04</v>
       </c>
       <c r="E116" t="b">
         <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>2726</v>
+        <v>5.01</v>
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
-        <v>0.59</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>OCCLLTD</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1841.8</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="C117" t="n">
-        <v>1900</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="D117" t="n">
-        <v>3.16</v>
+        <v>2.03</v>
       </c>
       <c r="E117" t="b">
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>1891</v>
+        <v>83.14</v>
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>-0.47</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SAKHTISUG</t>
+          <t>LEMERITE</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>16.85</v>
+        <v>450.25</v>
       </c>
       <c r="C118" t="n">
-        <v>17.38</v>
+        <v>459.3</v>
       </c>
       <c r="D118" t="n">
-        <v>3.15</v>
+        <v>2.01</v>
       </c>
       <c r="E118" t="b">
         <v>0</v>
       </c>
       <c r="F118" t="n">
-        <v>16.88</v>
+        <v>449.6</v>
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
-        <v>-2.88</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>JAYBARMARU</t>
+          <t>KRITIKA</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>97.63</v>
+        <v>5.96</v>
       </c>
       <c r="C119" t="n">
-        <v>100.7</v>
+        <v>6.08</v>
       </c>
       <c r="D119" t="n">
-        <v>3.14</v>
+        <v>2.01</v>
       </c>
       <c r="E119" t="b">
         <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>96</v>
+        <v>5.93</v>
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
-        <v>-4.67</v>
+        <v>-2.47</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>VASWANI</t>
+          <t>PREMIER</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>53.33</v>
+        <v>2.99</v>
       </c>
       <c r="C120" t="n">
-        <v>55</v>
+        <v>3.05</v>
       </c>
       <c r="D120" t="n">
-        <v>3.13</v>
+        <v>2.01</v>
       </c>
       <c r="E120" t="b">
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>54.28</v>
+        <v>2.91</v>
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
-        <v>-1.31</v>
+        <v>-4.59</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SREEL</t>
+          <t>SIKKO</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>198.6</v>
+        <v>4.54</v>
       </c>
       <c r="C121" t="n">
-        <v>204.8</v>
+        <v>4.63</v>
       </c>
       <c r="D121" t="n">
-        <v>3.12</v>
+        <v>1.98</v>
       </c>
       <c r="E121" t="b">
         <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>202.41</v>
+        <v>4.66</v>
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
-        <v>-1.17</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>BHARATSE</t>
+          <t>COMPUSOFT</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>174.63</v>
+        <v>13.16</v>
       </c>
       <c r="C122" t="n">
-        <v>180</v>
+        <v>13.42</v>
       </c>
       <c r="D122" t="n">
-        <v>3.08</v>
+        <v>1.98</v>
       </c>
       <c r="E122" t="b">
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>174.22</v>
+        <v>13.15</v>
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
-        <v>-3.21</v>
+        <v>-2.01</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>PRITIKAUTO</t>
+          <t>MADHAV</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>12.01</v>
+        <v>35.27</v>
       </c>
       <c r="C123" t="n">
-        <v>12.38</v>
+        <v>35.97</v>
       </c>
       <c r="D123" t="n">
-        <v>3.08</v>
+        <v>1.98</v>
       </c>
       <c r="E123" t="b">
         <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>12.33</v>
+        <v>35.91</v>
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>-0.4</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ACCURACY</t>
+          <t>ROSSELLIND</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>4.22</v>
+        <v>44.95</v>
       </c>
       <c r="C124" t="n">
-        <v>4.35</v>
+        <v>45.84</v>
       </c>
       <c r="D124" t="n">
-        <v>3.08</v>
+        <v>1.98</v>
       </c>
       <c r="E124" t="b">
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>4.49</v>
+        <v>45.58</v>
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
-        <v>3.22</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GSS</t>
+          <t>OSWALGREEN</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>13.14</v>
+        <v>25</v>
       </c>
       <c r="C125" t="n">
-        <v>13.54</v>
+        <v>25.49</v>
       </c>
       <c r="D125" t="n">
-        <v>3.04</v>
+        <v>1.96</v>
       </c>
       <c r="E125" t="b">
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>13.24</v>
+        <v>24.99</v>
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>-2.22</v>
+        <v>-1.96</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>NITCO</t>
+          <t>GOLDENTOBC</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>68.87</v>
+        <v>29.01</v>
       </c>
       <c r="C126" t="n">
-        <v>70.95</v>
+        <v>29.58</v>
       </c>
       <c r="D126" t="n">
-        <v>3.02</v>
+        <v>1.96</v>
       </c>
       <c r="E126" t="b">
         <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>67.61</v>
+        <v>29.3</v>
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
-        <v>-4.71</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CHEMBONDCH</t>
+          <t>VARDMNPOLY</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>142.53</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="C127" t="n">
-        <v>146.8</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="D127" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="E127" t="b">
         <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>140.48</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
-        <v>-4.31</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ELECTHERM</t>
+          <t>MUKTAARTS</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>662.2</v>
+        <v>53.76</v>
       </c>
       <c r="C128" t="n">
-        <v>682</v>
+        <v>54.8</v>
       </c>
       <c r="D128" t="n">
-        <v>2.99</v>
+        <v>1.93</v>
       </c>
       <c r="E128" t="b">
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>661.95</v>
+        <v>52.78</v>
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
-        <v>-2.94</v>
+        <v>-3.69</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>DANGEE</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>3.01</v>
+        <v>6.28</v>
       </c>
       <c r="C129" t="n">
-        <v>3.1</v>
+        <v>6.4</v>
       </c>
       <c r="D129" t="n">
-        <v>2.99</v>
+        <v>1.91</v>
       </c>
       <c r="E129" t="b">
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>3.07</v>
+        <v>6.44</v>
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
-        <v>-0.97</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>DCM</t>
+          <t>TARACHAND</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>69.81</v>
+        <v>59.86</v>
       </c>
       <c r="C130" t="n">
-        <v>71.89</v>
+        <v>61</v>
       </c>
       <c r="D130" t="n">
-        <v>2.98</v>
+        <v>1.9</v>
       </c>
       <c r="E130" t="b">
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>69.63</v>
+        <v>59.98</v>
       </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
-        <v>-3.14</v>
+        <v>-1.67</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>VEEDOL</t>
+          <t>CHAMUNDA</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1320.5</v>
+        <v>47.5</v>
       </c>
       <c r="C131" t="n">
-        <v>1359.7</v>
+        <v>48.4</v>
       </c>
       <c r="D131" t="n">
-        <v>2.97</v>
+        <v>1.89</v>
       </c>
       <c r="E131" t="b">
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>1312.4</v>
+        <v>47</v>
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
-        <v>-3.48</v>
+        <v>-2.89</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>KHANDSE</t>
+          <t>GML</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>16.89</v>
+        <v>16</v>
       </c>
       <c r="C132" t="n">
-        <v>17.39</v>
+        <v>16.3</v>
       </c>
       <c r="D132" t="n">
-        <v>2.96</v>
+        <v>1.88</v>
       </c>
       <c r="E132" t="b">
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>17.21</v>
+        <v>16.3</v>
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
-        <v>-1.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MOKSH</t>
+          <t>NIBL</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>11.9</v>
+        <v>30.82</v>
       </c>
       <c r="C133" t="n">
-        <v>12.25</v>
+        <v>31.4</v>
       </c>
       <c r="D133" t="n">
-        <v>2.94</v>
+        <v>1.88</v>
       </c>
       <c r="E133" t="b">
         <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>12.27</v>
+        <v>31.21</v>
       </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
-        <v>0.16</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SITINET</t>
+          <t>A2ZINFRA</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.34</v>
+        <v>16.54</v>
       </c>
       <c r="C134" t="n">
-        <v>0.35</v>
+        <v>16.85</v>
       </c>
       <c r="D134" t="n">
-        <v>2.94</v>
+        <v>1.87</v>
       </c>
       <c r="E134" t="b">
         <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>0.33</v>
+        <v>16.75</v>
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
-        <v>-5.71</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>NSIL</t>
+          <t>BAGFILMS</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>5635</v>
+        <v>4.87</v>
       </c>
       <c r="C135" t="n">
-        <v>5800</v>
+        <v>4.96</v>
       </c>
       <c r="D135" t="n">
-        <v>2.93</v>
+        <v>1.85</v>
       </c>
       <c r="E135" t="b">
         <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>5670</v>
+        <v>5.06</v>
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
-        <v>-2.24</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>DAMODARIND</t>
+          <t>PARASPETRO</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>24</v>
+        <v>2.16</v>
       </c>
       <c r="C136" t="n">
-        <v>24.7</v>
+        <v>2.2</v>
       </c>
       <c r="D136" t="n">
-        <v>2.92</v>
+        <v>1.85</v>
       </c>
       <c r="E136" t="b">
         <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>24.64</v>
+        <v>2.19</v>
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
-        <v>-0.24</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>GARUDA</t>
+          <t>SUKHJITS</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>163.8</v>
+        <v>187.53</v>
       </c>
       <c r="C137" t="n">
-        <v>168.59</v>
+        <v>190.96</v>
       </c>
       <c r="D137" t="n">
-        <v>2.92</v>
+        <v>1.83</v>
       </c>
       <c r="E137" t="b">
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>164.07</v>
+        <v>190.56</v>
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
-        <v>-2.68</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>INFOMEDIA</t>
+          <t>RUDRA</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>5.13</v>
+        <v>17.63</v>
       </c>
       <c r="C138" t="n">
-        <v>5.28</v>
+        <v>17.95</v>
       </c>
       <c r="D138" t="n">
-        <v>2.92</v>
+        <v>1.82</v>
       </c>
       <c r="E138" t="b">
         <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>5.35</v>
+        <v>17.8</v>
       </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
-        <v>1.33</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>TERASOFT</t>
+          <t>SHIVAMILLS</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>357.6</v>
+        <v>55</v>
       </c>
       <c r="C139" t="n">
-        <v>368</v>
+        <v>56</v>
       </c>
       <c r="D139" t="n">
-        <v>2.91</v>
+        <v>1.82</v>
       </c>
       <c r="E139" t="b">
         <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>362.8</v>
+        <v>53.9</v>
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
-        <v>-1.41</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>DEVIT</t>
+          <t>CUPID</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>27.41</v>
+        <v>405.5</v>
       </c>
       <c r="C140" t="n">
-        <v>28.2</v>
+        <v>412.85</v>
       </c>
       <c r="D140" t="n">
-        <v>2.88</v>
+        <v>1.81</v>
       </c>
       <c r="E140" t="b">
         <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>26.55</v>
+        <v>407.2</v>
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
-        <v>-5.85</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>FAIRCHEMOR</t>
+          <t>LOKESHMACH</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>563</v>
+        <v>196.47</v>
       </c>
       <c r="C141" t="n">
-        <v>579</v>
+        <v>200</v>
       </c>
       <c r="D141" t="n">
-        <v>2.84</v>
+        <v>1.8</v>
       </c>
       <c r="E141" t="b">
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>562.5</v>
+        <v>219.58</v>
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
-        <v>-2.85</v>
+        <v>9.789999999999999</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>PREMIERPOL</t>
+          <t>GTL</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>57.37</v>
+        <v>6.9</v>
       </c>
       <c r="C142" t="n">
-        <v>59</v>
+        <v>7.02</v>
       </c>
       <c r="D142" t="n">
-        <v>2.84</v>
+        <v>1.74</v>
       </c>
       <c r="E142" t="b">
         <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>55.3</v>
+        <v>6.99</v>
       </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
-        <v>-6.27</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>HILTON</t>
+          <t>OMAXAUTO</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>17.04</v>
+        <v>103.22</v>
       </c>
       <c r="C143" t="n">
-        <v>17.52</v>
+        <v>105</v>
       </c>
       <c r="D143" t="n">
-        <v>2.82</v>
+        <v>1.72</v>
       </c>
       <c r="E143" t="b">
         <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>17.2</v>
+        <v>104.23</v>
       </c>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
-        <v>-1.83</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>GLOBE</t>
+          <t>COROMANDEL</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>2.5</v>
+        <v>2063.5</v>
       </c>
       <c r="C144" t="n">
-        <v>2.57</v>
+        <v>2099</v>
       </c>
       <c r="D144" t="n">
-        <v>2.8</v>
+        <v>1.72</v>
       </c>
       <c r="E144" t="b">
         <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>2.57</v>
+        <v>2019.1</v>
       </c>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
-        <v>0</v>
+        <v>-3.81</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>RADHIKAJWE</t>
+          <t>KCEIL</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>60.26</v>
+        <v>122.9</v>
       </c>
       <c r="C145" t="n">
-        <v>61.95</v>
+        <v>125</v>
       </c>
       <c r="D145" t="n">
-        <v>2.8</v>
+        <v>1.71</v>
       </c>
       <c r="E145" t="b">
         <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>60.05</v>
+        <v>120.15</v>
       </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
-        <v>-3.07</v>
+        <v>-3.88</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>DICIND</t>
+          <t>SANATHAN</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>510.65</v>
+        <v>411.5</v>
       </c>
       <c r="C146" t="n">
-        <v>524.9</v>
+        <v>418.45</v>
       </c>
       <c r="D146" t="n">
-        <v>2.79</v>
+        <v>1.69</v>
       </c>
       <c r="E146" t="b">
         <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>517.85</v>
+        <v>412.05</v>
       </c>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
-        <v>-1.34</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>HINDOILEXP</t>
+          <t>RSSOFTWARE</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>148.86</v>
+        <v>33.45</v>
       </c>
       <c r="C147" t="n">
-        <v>153</v>
+        <v>34</v>
       </c>
       <c r="D147" t="n">
-        <v>2.78</v>
+        <v>1.64</v>
       </c>
       <c r="E147" t="b">
         <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>156.08</v>
+        <v>33.2</v>
       </c>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
-        <v>2.01</v>
+        <v>-2.35</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CHEMBOND</t>
+          <t>GINNIFILA</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>139.43</v>
+        <v>35.05</v>
       </c>
       <c r="C148" t="n">
-        <v>143.25</v>
+        <v>35.62</v>
       </c>
       <c r="D148" t="n">
-        <v>2.74</v>
+        <v>1.63</v>
       </c>
       <c r="E148" t="b">
         <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>141.01</v>
+        <v>34.87</v>
       </c>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
-        <v>-1.56</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>RAMANEWS</t>
+          <t>GOLDTECH</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>33.87</v>
+        <v>39.37</v>
       </c>
       <c r="C149" t="n">
-        <v>34.79</v>
+        <v>40</v>
       </c>
       <c r="D149" t="n">
-        <v>2.72</v>
+        <v>1.6</v>
       </c>
       <c r="E149" t="b">
         <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>33.86</v>
+        <v>39.45</v>
       </c>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
-        <v>-2.67</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SHREERAMA</t>
+          <t>OMAXE</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>50.62</v>
+        <v>78.56</v>
       </c>
       <c r="C150" t="n">
-        <v>51.99</v>
+        <v>79.8</v>
       </c>
       <c r="D150" t="n">
-        <v>2.71</v>
+        <v>1.58</v>
       </c>
       <c r="E150" t="b">
         <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>49.78</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
-        <v>-4.25</v>
+        <v>-3.52</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>AKSHAR</t>
+          <t>NAGAFERT</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.37</v>
+        <v>4.43</v>
       </c>
       <c r="C151" t="n">
-        <v>0.38</v>
+        <v>4.5</v>
       </c>
       <c r="D151" t="n">
-        <v>2.7</v>
+        <v>1.58</v>
       </c>
       <c r="E151" t="b">
         <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>0.38</v>
+        <v>4.45</v>
       </c>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
-        <v>0</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SEPC</t>
+          <t>SREEL</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>7.09</v>
+        <v>198.68</v>
       </c>
       <c r="C152" t="n">
-        <v>7.28</v>
+        <v>201.8</v>
       </c>
       <c r="D152" t="n">
-        <v>2.68</v>
+        <v>1.57</v>
       </c>
       <c r="E152" t="b">
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>6.98</v>
+        <v>203.97</v>
       </c>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="n">
-        <v>-4.12</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SIGMAADV</t>
+          <t>PRITIKAUTO</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>157.81</v>
+        <v>12.09</v>
       </c>
       <c r="C153" t="n">
-        <v>162</v>
+        <v>12.28</v>
       </c>
       <c r="D153" t="n">
-        <v>2.66</v>
+        <v>1.57</v>
       </c>
       <c r="E153" t="b">
         <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>160.36</v>
+        <v>12.29</v>
       </c>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="n">
-        <v>-1.01</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>VISAKAIND</t>
+          <t>VCL</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>59.43</v>
+        <v>1.94</v>
       </c>
       <c r="C154" t="n">
-        <v>61</v>
+        <v>1.97</v>
       </c>
       <c r="D154" t="n">
-        <v>2.64</v>
+        <v>1.55</v>
       </c>
       <c r="E154" t="b">
         <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>59.73</v>
+        <v>2</v>
       </c>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="n">
-        <v>-2.08</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>DCMSRIND</t>
+          <t>SETL</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>36.78</v>
+        <v>118.87</v>
       </c>
       <c r="C155" t="n">
-        <v>37.75</v>
+        <v>120.7</v>
       </c>
       <c r="D155" t="n">
-        <v>2.64</v>
+        <v>1.54</v>
       </c>
       <c r="E155" t="b">
         <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>36.92</v>
+        <v>120.26</v>
       </c>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="n">
-        <v>-2.2</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>TAINWALCHM</t>
+          <t>BHARATGEAR</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>199.63</v>
+        <v>102.42</v>
       </c>
       <c r="C156" t="n">
-        <v>204.9</v>
+        <v>104</v>
       </c>
       <c r="D156" t="n">
-        <v>2.64</v>
+        <v>1.54</v>
       </c>
       <c r="E156" t="b">
         <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>205.5</v>
+        <v>101.05</v>
       </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="n">
-        <v>0.29</v>
+        <v>-2.84</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>CCCL</t>
+          <t>LPDC</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>15.58</v>
+        <v>5.89</v>
       </c>
       <c r="C157" t="n">
-        <v>15.99</v>
+        <v>5.98</v>
       </c>
       <c r="D157" t="n">
-        <v>2.63</v>
+        <v>1.53</v>
       </c>
       <c r="E157" t="b">
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>15.4</v>
+        <v>5.96</v>
       </c>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="n">
-        <v>-3.69</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ASMS</t>
+          <t>CIFL</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>9.109999999999999</v>
+        <v>30.04</v>
       </c>
       <c r="C158" t="n">
-        <v>9.35</v>
+        <v>30.5</v>
       </c>
       <c r="D158" t="n">
-        <v>2.63</v>
+        <v>1.53</v>
       </c>
       <c r="E158" t="b">
         <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>9.279999999999999</v>
+        <v>30.03</v>
       </c>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="n">
-        <v>-0.75</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>BAJAJHIND</t>
+          <t>CROWN</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>17.21</v>
+        <v>122.63</v>
       </c>
       <c r="C159" t="n">
-        <v>17.66</v>
+        <v>124.49</v>
       </c>
       <c r="D159" t="n">
-        <v>2.61</v>
+        <v>1.52</v>
       </c>
       <c r="E159" t="b">
         <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>16.89</v>
+        <v>122.42</v>
       </c>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="n">
-        <v>-4.36</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>HEXATRADEX</t>
+          <t>ZIMLAB</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>159.4</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="C160" t="n">
-        <v>163.55</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="D160" t="n">
-        <v>2.6</v>
+        <v>1.52</v>
       </c>
       <c r="E160" t="b">
         <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>160</v>
+        <v>67.78</v>
       </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="n">
-        <v>-2.17</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>CHAMUNDA</t>
+          <t>JAYBARMARU</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>47.3</v>
+        <v>96.78</v>
       </c>
       <c r="C161" t="n">
-        <v>48.5</v>
+        <v>98.25</v>
       </c>
       <c r="D161" t="n">
-        <v>2.54</v>
+        <v>1.52</v>
       </c>
       <c r="E161" t="b">
         <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>48.5</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="n">
-        <v>0</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>PASUPTAC</t>
+          <t>PRABHA</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>49.73</v>
+        <v>167.47</v>
       </c>
       <c r="C162" t="n">
-        <v>50.99</v>
+        <v>170</v>
       </c>
       <c r="D162" t="n">
-        <v>2.53</v>
+        <v>1.51</v>
       </c>
       <c r="E162" t="b">
         <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>49.25</v>
+        <v>165.02</v>
       </c>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="n">
-        <v>-3.41</v>
+        <v>-2.93</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>SHRENIK</t>
+          <t>TINNARUBR</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.4</v>
+        <v>654.75</v>
       </c>
       <c r="C163" t="n">
-        <v>0.41</v>
+        <v>664.55</v>
       </c>
       <c r="D163" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="E163" t="b">
         <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>0.4</v>
+        <v>661.5</v>
       </c>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="n">
-        <v>-2.44</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>JMA</t>
+          <t>LINC</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>85.86</v>
+        <v>106.11</v>
       </c>
       <c r="C164" t="n">
-        <v>88</v>
+        <v>107.7</v>
       </c>
       <c r="D164" t="n">
-        <v>2.49</v>
+        <v>1.5</v>
       </c>
       <c r="E164" t="b">
         <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>87</v>
+        <v>104.92</v>
       </c>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="n">
-        <v>-1.14</v>
+        <v>-2.58</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SPENCERS</t>
+          <t>SAMHI</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>31.46</v>
+        <v>151.72</v>
       </c>
       <c r="C165" t="n">
-        <v>32.24</v>
+        <v>154</v>
       </c>
       <c r="D165" t="n">
-        <v>2.48</v>
+        <v>1.5</v>
       </c>
       <c r="E165" t="b">
         <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>31.53</v>
+        <v>148.8</v>
       </c>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="n">
-        <v>-2.2</v>
+        <v>-3.38</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>FLFL</t>
+          <t>SILINV</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>1.21</v>
+        <v>414</v>
       </c>
       <c r="C166" t="n">
-        <v>1.24</v>
+        <v>420.2</v>
       </c>
       <c r="D166" t="n">
-        <v>2.48</v>
+        <v>1.5</v>
       </c>
       <c r="E166" t="b">
         <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>1.25</v>
+        <v>419</v>
       </c>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>STEL</t>
+          <t>PANACEABIO</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>517.1</v>
+        <v>320.7</v>
       </c>
       <c r="C167" t="n">
-        <v>529.9</v>
+        <v>325.5</v>
       </c>
       <c r="D167" t="n">
-        <v>2.48</v>
+        <v>1.5</v>
       </c>
       <c r="E167" t="b">
         <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>518.05</v>
+        <v>326.3</v>
       </c>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="n">
-        <v>-2.24</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>BODALCHEM</t>
+          <t>DNAMEDIA</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>44.89</v>
+        <v>3.33</v>
       </c>
       <c r="C168" t="n">
-        <v>46</v>
+        <v>3.38</v>
       </c>
       <c r="D168" t="n">
-        <v>2.47</v>
+        <v>1.5</v>
       </c>
       <c r="E168" t="b">
         <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>44.85</v>
+        <v>3.45</v>
       </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="n">
-        <v>-2.5</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>GEEKAYWIRE</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>24.28</v>
+        <v>55.96</v>
       </c>
       <c r="C169" t="n">
-        <v>24.88</v>
+        <v>56.8</v>
       </c>
       <c r="D169" t="n">
-        <v>2.47</v>
+        <v>1.5</v>
       </c>
       <c r="E169" t="b">
         <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>23.98</v>
+        <v>56.92</v>
       </c>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="n">
-        <v>-3.62</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>GVPIL</t>
+          <t>BLBLIMITED</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>437.25</v>
+        <v>17.61</v>
       </c>
       <c r="C170" t="n">
-        <v>448</v>
+        <v>17.87</v>
       </c>
       <c r="D170" t="n">
-        <v>2.46</v>
+        <v>1.48</v>
       </c>
       <c r="E170" t="b">
         <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>445</v>
+        <v>17.92</v>
       </c>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="n">
-        <v>-0.67</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>CROWN</t>
+          <t>HPIL</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>121.91</v>
+        <v>123.29</v>
       </c>
       <c r="C171" t="n">
-        <v>124.91</v>
+        <v>125.1</v>
       </c>
       <c r="D171" t="n">
-        <v>2.46</v>
+        <v>1.47</v>
       </c>
       <c r="E171" t="b">
         <v>0</v>
       </c>
       <c r="F171" t="n">
-        <v>129.16</v>
+        <v>121.01</v>
       </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="n">
-        <v>3.4</v>
+        <v>-3.27</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>NIPPOBATRY</t>
+          <t>MAHAPEXLTD</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>302.6</v>
+        <v>87.70999999999999</v>
       </c>
       <c r="C172" t="n">
-        <v>310</v>
+        <v>89</v>
       </c>
       <c r="D172" t="n">
-        <v>2.45</v>
+        <v>1.47</v>
       </c>
       <c r="E172" t="b">
         <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>315</v>
+        <v>105.25</v>
       </c>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="n">
-        <v>1.61</v>
+        <v>18.26</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>SEYAIND</t>
+          <t>KREBSBIO</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>10.67</v>
+        <v>53.22</v>
       </c>
       <c r="C173" t="n">
-        <v>10.93</v>
+        <v>54</v>
       </c>
       <c r="D173" t="n">
-        <v>2.44</v>
+        <v>1.47</v>
       </c>
       <c r="E173" t="b">
         <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>10.41</v>
+        <v>53.01</v>
       </c>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="n">
-        <v>-4.76</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>DPSCLTD</t>
+          <t>BIRLACABLE</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>8.640000000000001</v>
+        <v>142.61</v>
       </c>
       <c r="C174" t="n">
-        <v>8.85</v>
+        <v>144.7</v>
       </c>
       <c r="D174" t="n">
-        <v>2.43</v>
+        <v>1.47</v>
       </c>
       <c r="E174" t="b">
         <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>8.890000000000001</v>
+        <v>142.65</v>
       </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="n">
-        <v>0.45</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>HARDWYN</t>
+          <t>TREL</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>16.98</v>
+        <v>24.44</v>
       </c>
       <c r="C175" t="n">
-        <v>17.39</v>
+        <v>24.8</v>
       </c>
       <c r="D175" t="n">
-        <v>2.41</v>
+        <v>1.47</v>
       </c>
       <c r="E175" t="b">
         <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>16.97</v>
+        <v>24.34</v>
       </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="n">
-        <v>-2.42</v>
+        <v>-1.85</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>GVPTECH</t>
+          <t>BIRLAMONEY</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>6.64</v>
+        <v>127.75</v>
       </c>
       <c r="C176" t="n">
-        <v>6.8</v>
+        <v>129.6</v>
       </c>
       <c r="D176" t="n">
-        <v>2.41</v>
+        <v>1.45</v>
       </c>
       <c r="E176" t="b">
         <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>6.9</v>
+        <v>128.28</v>
       </c>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="n">
-        <v>1.47</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>BALMLAWRIE</t>
+          <t>SIRCA</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>170.33</v>
+        <v>452.95</v>
       </c>
       <c r="C177" t="n">
-        <v>174.4</v>
+        <v>459.5</v>
       </c>
       <c r="D177" t="n">
-        <v>2.39</v>
+        <v>1.45</v>
       </c>
       <c r="E177" t="b">
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>173.96</v>
+        <v>455</v>
       </c>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="n">
-        <v>-0.25</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>FEL</t>
+          <t>RAMASTEEL</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.42</v>
+        <v>6.19</v>
       </c>
       <c r="C178" t="n">
-        <v>0.43</v>
+        <v>6.28</v>
       </c>
       <c r="D178" t="n">
-        <v>2.38</v>
+        <v>1.45</v>
       </c>
       <c r="E178" t="b">
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>0.42</v>
+        <v>6.38</v>
       </c>
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="n">
-        <v>-2.33</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>KILITCH</t>
+          <t>HILINFRA</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>312.55</v>
+        <v>52.21</v>
       </c>
       <c r="C179" t="n">
-        <v>319.9</v>
+        <v>52.96</v>
       </c>
       <c r="D179" t="n">
-        <v>2.35</v>
+        <v>1.44</v>
       </c>
       <c r="E179" t="b">
         <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>319.95</v>
+        <v>51.66</v>
       </c>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="n">
-        <v>0.02</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>PAKKA</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>3604.8</v>
+        <v>84.81</v>
       </c>
       <c r="C180" t="n">
-        <v>3688.6</v>
+        <v>86</v>
       </c>
       <c r="D180" t="n">
-        <v>2.32</v>
+        <v>1.4</v>
       </c>
       <c r="E180" t="b">
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>3543.7</v>
+        <v>83.7</v>
       </c>
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="n">
-        <v>-3.93</v>
+        <v>-2.67</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>MAHASTEEL</t>
+          <t>RADIANTCMS</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>762.35</v>
+        <v>36.99</v>
       </c>
       <c r="C181" t="n">
-        <v>780</v>
+        <v>37.5</v>
       </c>
       <c r="D181" t="n">
-        <v>2.32</v>
+        <v>1.38</v>
       </c>
       <c r="E181" t="b">
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>759</v>
+        <v>36.94</v>
       </c>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="n">
-        <v>-2.69</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>RACLGEAR</t>
+          <t>AXITA</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>1368.4</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="C182" t="n">
-        <v>1400</v>
+        <v>8.83</v>
       </c>
       <c r="D182" t="n">
-        <v>2.31</v>
+        <v>1.38</v>
       </c>
       <c r="E182" t="b">
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>1474.4</v>
+        <v>8.85</v>
       </c>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="n">
-        <v>5.31</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>DHAMPURSUG</t>
+          <t>BIOFILCHEM</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>129.02</v>
+        <v>30.56</v>
       </c>
       <c r="C183" t="n">
-        <v>132</v>
+        <v>30.98</v>
       </c>
       <c r="D183" t="n">
-        <v>2.31</v>
+        <v>1.37</v>
       </c>
       <c r="E183" t="b">
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>127.65</v>
+        <v>30.62</v>
       </c>
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="n">
-        <v>-3.3</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>JYOTISTRUC</t>
+          <t>CAPILLARY</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>11.24</v>
+        <v>512.8</v>
       </c>
       <c r="C184" t="n">
-        <v>11.5</v>
+        <v>519.8</v>
       </c>
       <c r="D184" t="n">
-        <v>2.31</v>
+        <v>1.37</v>
       </c>
       <c r="E184" t="b">
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>11.13</v>
+        <v>520.5</v>
       </c>
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="n">
-        <v>-3.22</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>MURUDCERA</t>
+          <t>BHARATSE</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>30.79</v>
+        <v>179.46</v>
       </c>
       <c r="C185" t="n">
-        <v>31.5</v>
+        <v>181.88</v>
       </c>
       <c r="D185" t="n">
-        <v>2.31</v>
+        <v>1.35</v>
       </c>
       <c r="E185" t="b">
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>31.24</v>
+        <v>182.55</v>
       </c>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="n">
-        <v>-0.83</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>SERVOTECH</t>
+          <t>OSWALAGRO</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>67.25</v>
+        <v>44.31</v>
       </c>
       <c r="C186" t="n">
-        <v>68.8</v>
+        <v>44.9</v>
       </c>
       <c r="D186" t="n">
-        <v>2.3</v>
+        <v>1.33</v>
       </c>
       <c r="E186" t="b">
         <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>67.58</v>
+        <v>45.23</v>
       </c>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="n">
-        <v>-1.77</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>SCHAND</t>
+          <t>BLUESTONE</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>152.22</v>
+        <v>448.25</v>
       </c>
       <c r="C187" t="n">
-        <v>155.68</v>
+        <v>454.2</v>
       </c>
       <c r="D187" t="n">
-        <v>2.27</v>
+        <v>1.33</v>
       </c>
       <c r="E187" t="b">
         <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>149.48</v>
+        <v>442.25</v>
       </c>
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="n">
-        <v>-3.98</v>
+        <v>-2.63</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ZAGGLE</t>
+          <t>PREMIERPOL</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>215.63</v>
+        <v>58.72</v>
       </c>
       <c r="C188" t="n">
-        <v>220.5</v>
+        <v>59.5</v>
       </c>
       <c r="D188" t="n">
-        <v>2.26</v>
+        <v>1.33</v>
       </c>
       <c r="E188" t="b">
         <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>216.7</v>
+        <v>58</v>
       </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="n">
-        <v>-1.72</v>
+        <v>-2.52</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>PVSL</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>87.91</v>
+        <v>2352.5</v>
       </c>
       <c r="C189" t="n">
-        <v>89.90000000000001</v>
+        <v>2383.3</v>
       </c>
       <c r="D189" t="n">
-        <v>2.26</v>
+        <v>1.31</v>
       </c>
       <c r="E189" t="b">
         <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>88.84</v>
+        <v>2509.3</v>
       </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="n">
-        <v>-1.18</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>OSIAHYPER</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>8.02</v>
+        <v>276.35</v>
       </c>
       <c r="C190" t="n">
-        <v>8.199999999999999</v>
+        <v>279.95</v>
       </c>
       <c r="D190" t="n">
-        <v>2.24</v>
+        <v>1.3</v>
       </c>
       <c r="E190" t="b">
         <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>8.08</v>
+        <v>272.4</v>
       </c>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="n">
-        <v>-1.46</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ARFIN</t>
+          <t>HPAL</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>73.84999999999999</v>
+        <v>34.53</v>
       </c>
       <c r="C191" t="n">
-        <v>75.5</v>
+        <v>34.98</v>
       </c>
       <c r="D191" t="n">
-        <v>2.23</v>
+        <v>1.3</v>
       </c>
       <c r="E191" t="b">
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>74.98</v>
+        <v>34.63</v>
       </c>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>J&amp;KBANK</t>
+          <t>SUBEXLTD</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>116.24</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="C192" t="n">
-        <v>118.8</v>
+        <v>8.65</v>
       </c>
       <c r="D192" t="n">
-        <v>2.2</v>
+        <v>1.29</v>
       </c>
       <c r="E192" t="b">
         <v>0</v>
       </c>
-      <c r="F192" t="inlineStr"/>
+      <c r="F192" t="n">
+        <v>8.66</v>
+      </c>
       <c r="G192" t="inlineStr"/>
-      <c r="H192" t="inlineStr"/>
+      <c r="H192" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SANCO</t>
+          <t>RCOM</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>2.28</v>
+        <v>0.78</v>
       </c>
       <c r="C193" t="n">
-        <v>2.33</v>
+        <v>0.79</v>
       </c>
       <c r="D193" t="n">
-        <v>2.19</v>
+        <v>1.28</v>
       </c>
       <c r="E193" t="b">
         <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>2.3</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="n">
-        <v>-1.29</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>VIKASLIFE</t>
+          <t>JTLIND</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>1.37</v>
+        <v>53.34</v>
       </c>
       <c r="C194" t="n">
-        <v>1.4</v>
+        <v>54</v>
       </c>
       <c r="D194" t="n">
-        <v>2.19</v>
+        <v>1.24</v>
       </c>
       <c r="E194" t="b">
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>1.37</v>
+        <v>53.4</v>
       </c>
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="n">
-        <v>-2.14</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SUTLEJTEX</t>
+          <t>MSPL</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>29.85</v>
+        <v>31.41</v>
       </c>
       <c r="C195" t="n">
-        <v>30.5</v>
+        <v>31.8</v>
       </c>
       <c r="D195" t="n">
-        <v>2.18</v>
+        <v>1.24</v>
       </c>
       <c r="E195" t="b">
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>30.48</v>
+        <v>31.84</v>
       </c>
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>VPRPL</t>
+          <t>VIMTALABS</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>41.4</v>
+        <v>439</v>
       </c>
       <c r="C196" t="n">
-        <v>42.29</v>
+        <v>444.4</v>
       </c>
       <c r="D196" t="n">
-        <v>2.15</v>
+        <v>1.23</v>
       </c>
       <c r="E196" t="b">
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>41.6</v>
+        <v>440</v>
       </c>
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="n">
-        <v>-1.63</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>RAMCOIND</t>
+          <t>RITCO</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>278.9</v>
+        <v>204</v>
       </c>
       <c r="C197" t="n">
-        <v>284.9</v>
+        <v>206.5</v>
       </c>
       <c r="D197" t="n">
-        <v>2.15</v>
+        <v>1.23</v>
       </c>
       <c r="E197" t="b">
         <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>276.55</v>
+        <v>202.25</v>
       </c>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="n">
-        <v>-2.93</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>LLOYDSENGG</t>
+          <t>MAHASTEEL</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>43.96</v>
+        <v>778.5</v>
       </c>
       <c r="C198" t="n">
-        <v>44.9</v>
+        <v>788</v>
       </c>
       <c r="D198" t="n">
-        <v>2.14</v>
+        <v>1.22</v>
       </c>
       <c r="E198" t="b">
         <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>44.03</v>
+        <v>754.7</v>
       </c>
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="n">
-        <v>-1.94</v>
+        <v>-4.23</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>MEDIASSIST</t>
+          <t>SUMMITSEC</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>340.5</v>
+        <v>1580.3</v>
       </c>
       <c r="C199" t="n">
-        <v>347.8</v>
+        <v>1599.5</v>
       </c>
       <c r="D199" t="n">
-        <v>2.14</v>
+        <v>1.21</v>
       </c>
       <c r="E199" t="b">
         <v>0</v>
       </c>
       <c r="F199" t="n">
-        <v>334.15</v>
+        <v>1587.6</v>
       </c>
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="n">
-        <v>-3.92</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>MIRCELECTR</t>
+          <t>TTKHLTCARE</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>27.66</v>
+        <v>860.9</v>
       </c>
       <c r="C200" t="n">
-        <v>28.25</v>
+        <v>871.2</v>
       </c>
       <c r="D200" t="n">
-        <v>2.13</v>
+        <v>1.2</v>
       </c>
       <c r="E200" t="b">
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>26.98</v>
+        <v>880</v>
       </c>
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="n">
-        <v>-4.5</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>BHANDARI</t>
+          <t>ASIANTILES</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>2.82</v>
+        <v>68.19</v>
       </c>
       <c r="C201" t="n">
-        <v>2.88</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="D201" t="n">
-        <v>2.13</v>
+        <v>1.17</v>
       </c>
       <c r="E201" t="b">
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>2.74</v>
+        <v>67.62</v>
       </c>
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="n">
-        <v>-4.86</v>
+        <v>-1.99</v>
       </c>
     </row>
   </sheetData>

--- a/data/trending_momentum_stocks.xlsx
+++ b/data/trending_momentum_stocks.xlsx
@@ -461,274 +461,274 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MODTHREAD</t>
+          <t>LOKESHMACH</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43.39</v>
+        <v>205.61</v>
       </c>
       <c r="C2" t="n">
-        <v>48.69</v>
+        <v>232</v>
       </c>
       <c r="D2" t="n">
-        <v>12.21</v>
+        <v>12.83</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>52.06</v>
+        <v>209.14</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>6.92</v>
+        <v>-9.85</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GLOBALE</t>
+          <t>MAHAPEXLTD</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.7</v>
+        <v>105.25</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>117.89</v>
       </c>
       <c r="D3" t="n">
-        <v>12.15</v>
+        <v>12.01</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>11.06</v>
+        <v>109.06</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>-7.83</v>
+        <v>-7.49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CENTEXT</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20.72</v>
+        <v>593.3</v>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>647.95</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>21.96</v>
+        <v>625.95</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>-4.52</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RETAIL</t>
+          <t>WEALTH</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.46</v>
+        <v>950.3</v>
       </c>
       <c r="C5" t="n">
-        <v>22.8</v>
+        <v>1034</v>
       </c>
       <c r="D5" t="n">
-        <v>6.24</v>
+        <v>8.81</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>22.48</v>
+        <v>941.15</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>-1.4</v>
+        <v>-8.98</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MAGNUM</t>
+          <t>ARENTERP</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.26</v>
+        <v>41.45</v>
       </c>
       <c r="C6" t="n">
-        <v>21.5</v>
+        <v>44.99</v>
       </c>
       <c r="D6" t="n">
-        <v>6.12</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>20.5</v>
+        <v>40.2</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>-4.65</v>
+        <v>-10.65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ACEINTEG</t>
+          <t>HINDOILEXP</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.71</v>
+        <v>156.47</v>
       </c>
       <c r="C7" t="n">
-        <v>17.7</v>
+        <v>169</v>
       </c>
       <c r="D7" t="n">
-        <v>5.92</v>
+        <v>8.01</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>17.58</v>
+        <v>166.46</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>-0.68</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JHS</t>
+          <t>ABCOTS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.94</v>
+        <v>410.4</v>
       </c>
       <c r="C8" t="n">
-        <v>9.449999999999999</v>
+        <v>435</v>
       </c>
       <c r="D8" t="n">
-        <v>5.7</v>
+        <v>5.99</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>9.130000000000001</v>
+        <v>411.6</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>-3.39</v>
+        <v>-5.38</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LATTEYS</t>
+          <t>EUROBOND</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20.42</v>
+        <v>161.26</v>
       </c>
       <c r="C9" t="n">
-        <v>21.5</v>
+        <v>170.75</v>
       </c>
       <c r="D9" t="n">
-        <v>5.29</v>
+        <v>5.88</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>20.72</v>
+        <v>156</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>-3.63</v>
+        <v>-8.640000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AAKASH</t>
+          <t>BYKE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11.9</v>
+        <v>41.09</v>
       </c>
       <c r="C10" t="n">
-        <v>12.52</v>
+        <v>43.38</v>
       </c>
       <c r="D10" t="n">
-        <v>5.21</v>
+        <v>5.57</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>10.53</v>
+        <v>38.59</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>-15.89</v>
+        <v>-11.04</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ORKLAINDIA</t>
+          <t>KRIDHANINF</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>557.45</v>
+        <v>2.84</v>
       </c>
       <c r="C11" t="n">
-        <v>586.3</v>
+        <v>2.99</v>
       </c>
       <c r="D11" t="n">
-        <v>5.18</v>
+        <v>5.28</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>595.5</v>
+        <v>2.89</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>1.57</v>
+        <v>-3.34</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SPENCERS</t>
+          <t>KHANDSE</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31.62</v>
+        <v>17.87</v>
       </c>
       <c r="C12" t="n">
-        <v>33.25</v>
+        <v>18.79</v>
       </c>
       <c r="D12" t="n">
         <v>5.15</v>
@@ -737,24 +737,24 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>31.77</v>
+        <v>17.9</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>-4.45</v>
+        <v>-4.74</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HALDER</t>
+          <t>SANWARIA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>254.15</v>
+        <v>0.2</v>
       </c>
       <c r="C13" t="n">
-        <v>266.85</v>
+        <v>0.21</v>
       </c>
       <c r="D13" t="n">
         <v>5</v>
@@ -763,59 +763,59 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>264</v>
+        <v>0.21</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>-1.07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SETUINFRA</t>
+          <t>ESFL</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4</v>
+        <v>163.3</v>
       </c>
       <c r="C14" t="n">
-        <v>0.42</v>
+        <v>171.45</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.42</v>
+        <v>157.2</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-8.31</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GJL</t>
+          <t>NEUEON</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>189.1</v>
+        <v>13.11</v>
       </c>
       <c r="C15" t="n">
-        <v>198.55</v>
+        <v>13.76</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>4.96</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>198.55</v>
+        <v>13.76</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
@@ -825,49 +825,49 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>YAAP</t>
+          <t>SHANTI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>133.35</v>
+        <v>6.67</v>
       </c>
       <c r="C16" t="n">
-        <v>140</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>4.99</v>
+        <v>4.95</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>140</v>
+        <v>6.6</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>-5.71</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MANGALAM</t>
+          <t>RCOM</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>32.26</v>
+        <v>0.85</v>
       </c>
       <c r="D17" t="n">
-        <v>4.98</v>
+        <v>4.94</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>32.26</v>
+        <v>0.85</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
@@ -877,49 +877,49 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ESFL</t>
+          <t>MAGNUM</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>155.55</v>
+        <v>20.54</v>
       </c>
       <c r="C18" t="n">
-        <v>163.3</v>
+        <v>21.55</v>
       </c>
       <c r="D18" t="n">
-        <v>4.98</v>
+        <v>4.92</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>163.3</v>
+        <v>19.95</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-7.42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GOLDSTAR</t>
+          <t>AFIL</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9.050000000000001</v>
+        <v>7.52</v>
       </c>
       <c r="C19" t="n">
-        <v>9.5</v>
+        <v>7.89</v>
       </c>
       <c r="D19" t="n">
-        <v>4.97</v>
+        <v>4.92</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>9.5</v>
+        <v>7.89</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
@@ -929,478 +929,482 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FLFL</t>
+          <t>AUSOMENT</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.22</v>
+        <v>98.94</v>
       </c>
       <c r="C20" t="n">
-        <v>1.28</v>
+        <v>103.76</v>
       </c>
       <c r="D20" t="n">
-        <v>4.92</v>
+        <v>4.87</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1.26</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>-1.56</v>
+        <v>-8.35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SOCL</t>
+          <t>STYL</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>30.65</v>
+        <v>238.26</v>
       </c>
       <c r="C21" t="n">
-        <v>32.15</v>
+        <v>249.8</v>
       </c>
       <c r="D21" t="n">
-        <v>4.89</v>
+        <v>4.84</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>30.8</v>
+        <v>252.15</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>-4.2</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ESSENTIA</t>
+          <t>INSPIRISYS</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.46</v>
+        <v>83</v>
       </c>
       <c r="C22" t="n">
-        <v>1.53</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>4.79</v>
+        <v>4.81</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5</v>
+        <v>83.7</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>-1.96</v>
+        <v>-3.78</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SURANASOL</t>
+          <t>FELDVR</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>21.67</v>
+        <v>2.92</v>
       </c>
       <c r="C23" t="n">
-        <v>22.7</v>
+        <v>3.06</v>
       </c>
       <c r="D23" t="n">
-        <v>4.75</v>
+        <v>4.79</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>22.4</v>
+        <v>2.98</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>-1.32</v>
+        <v>-2.61</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CTE</t>
+          <t>SHIVAMAUTO</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>26.17</v>
+        <v>18.37</v>
       </c>
       <c r="C24" t="n">
-        <v>27.4</v>
+        <v>19.24</v>
       </c>
       <c r="D24" t="n">
-        <v>4.7</v>
+        <v>4.74</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>27.46</v>
+        <v>17.8</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>0.22</v>
+        <v>-7.48</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TERASOFT</t>
+          <t>RADIOCITY</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>375.45</v>
+        <v>5.91</v>
       </c>
       <c r="C25" t="n">
-        <v>393</v>
+        <v>6.19</v>
       </c>
       <c r="D25" t="n">
-        <v>4.67</v>
+        <v>4.74</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>380.05</v>
+        <v>5.8</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>-3.3</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S&amp;SPOWER</t>
+          <t>GOLDSTAR</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>315.3</v>
+        <v>9.5</v>
       </c>
       <c r="C26" t="n">
-        <v>330</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>4.66</v>
+        <v>4.74</v>
       </c>
       <c r="E26" t="b">
         <v>0</v>
       </c>
-      <c r="F26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>9.25</v>
+      </c>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="n">
+        <v>-7.04</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CREATIVEYE</t>
+          <t>REPL</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.88</v>
+        <v>82.11</v>
       </c>
       <c r="C27" t="n">
-        <v>7.2</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>4.65</v>
+        <v>4.73</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>6.66</v>
+        <v>76.73</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>-7.5</v>
+        <v>-10.77</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AMJLAND</t>
+          <t>BRANDMAN</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>39.19</v>
+        <v>155.65</v>
       </c>
       <c r="C28" t="n">
-        <v>41</v>
+        <v>163</v>
       </c>
       <c r="D28" t="n">
-        <v>4.62</v>
+        <v>4.72</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>39.65</v>
+        <v>153</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>-3.29</v>
+        <v>-6.13</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SANCO</t>
+          <t>TECHLABS</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.17</v>
+        <v>213.45</v>
       </c>
       <c r="C29" t="n">
-        <v>2.27</v>
+        <v>223.4</v>
       </c>
       <c r="D29" t="n">
-        <v>4.61</v>
+        <v>4.66</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>2.17</v>
+        <v>218</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>-4.41</v>
+        <v>-2.42</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TREJHARA</t>
+          <t>VCL</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>178.6</v>
+        <v>1.93</v>
       </c>
       <c r="C30" t="n">
-        <v>186.75</v>
+        <v>2.02</v>
       </c>
       <c r="D30" t="n">
-        <v>4.56</v>
+        <v>4.66</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>179</v>
+        <v>1.92</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>-4.15</v>
+        <v>-4.95</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ELGIRUBCO</t>
+          <t>GUJRAFFIA</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>45.9</v>
+        <v>39.08</v>
       </c>
       <c r="C31" t="n">
-        <v>47.96</v>
+        <v>40.89</v>
       </c>
       <c r="D31" t="n">
-        <v>4.49</v>
+        <v>4.63</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>45.95</v>
+        <v>40.68</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>-4.19</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BAFNAPH</t>
+          <t>SUMIT</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>109.18</v>
+        <v>37.48</v>
       </c>
       <c r="C32" t="n">
-        <v>113.98</v>
+        <v>39.2</v>
       </c>
       <c r="D32" t="n">
-        <v>4.4</v>
+        <v>4.59</v>
       </c>
       <c r="E32" t="b">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>110.5</v>
+        <v>36.75</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>-3.05</v>
+        <v>-6.25</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>JINDALPOLY</t>
+          <t>VIJIFIN</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>738</v>
+        <v>2.19</v>
       </c>
       <c r="C33" t="n">
-        <v>770</v>
+        <v>2.29</v>
       </c>
       <c r="D33" t="n">
-        <v>4.34</v>
+        <v>4.57</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>754</v>
+        <v>2.17</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>-2.08</v>
+        <v>-5.24</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>KRIDHANINF</t>
+          <t>ZENITHSTL</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.59</v>
+        <v>5.59</v>
       </c>
       <c r="C34" t="n">
-        <v>2.7</v>
+        <v>5.84</v>
       </c>
       <c r="D34" t="n">
-        <v>4.25</v>
+        <v>4.47</v>
       </c>
       <c r="E34" t="b">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>2.84</v>
+        <v>5.5</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>5.19</v>
+        <v>-5.82</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ALANKIT</t>
+          <t>RSYSTEMS</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>7.91</v>
+        <v>258.5</v>
       </c>
       <c r="C35" t="n">
-        <v>8.24</v>
+        <v>269.9</v>
       </c>
       <c r="D35" t="n">
-        <v>4.17</v>
+        <v>4.41</v>
       </c>
       <c r="E35" t="b">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>8.02</v>
+        <v>287.9</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>-2.67</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ZEELEARN</t>
+          <t>AAKASH</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>5.55</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>5.78</v>
+        <v>10.2</v>
       </c>
       <c r="D36" t="n">
-        <v>4.14</v>
+        <v>4.19</v>
       </c>
       <c r="E36" t="b">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>5.63</v>
+        <v>10.97</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>-2.6</v>
+        <v>7.55</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>XELPMOC</t>
+          <t>DCXINDIA</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>121.98</v>
+        <v>190.98</v>
       </c>
       <c r="C37" t="n">
-        <v>126.95</v>
+        <v>198.97</v>
       </c>
       <c r="D37" t="n">
-        <v>4.07</v>
+        <v>4.18</v>
       </c>
       <c r="E37" t="b">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>124.06</v>
+        <v>195.82</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>-2.28</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ABAN</t>
+          <t>LANCORHOL</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>21.24</v>
+        <v>22.96</v>
       </c>
       <c r="C38" t="n">
-        <v>22.1</v>
+        <v>23.89</v>
       </c>
       <c r="D38" t="n">
         <v>4.05</v>
@@ -1409,362 +1413,358 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>22.3</v>
+        <v>21.82</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>0.9</v>
+        <v>-8.66</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HMVL</t>
+          <t>WORTHPERI</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>67.38</v>
+        <v>132.69</v>
       </c>
       <c r="C39" t="n">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="D39" t="n">
-        <v>3.89</v>
+        <v>4</v>
       </c>
       <c r="E39" t="b">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>67.98999999999999</v>
+        <v>126.95</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>-2.87</v>
+        <v>-8.01</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ALMONDZ</t>
+          <t>MAHASTEEL</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>14.4</v>
+        <v>830.8</v>
       </c>
       <c r="C40" t="n">
-        <v>14.95</v>
+        <v>863.95</v>
       </c>
       <c r="D40" t="n">
-        <v>3.82</v>
+        <v>3.99</v>
       </c>
       <c r="E40" t="b">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>15.12</v>
+        <v>855.9</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>1.14</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ALKALI</t>
+          <t>TIJARIA</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>59.78</v>
+        <v>4.77</v>
       </c>
       <c r="C41" t="n">
-        <v>62</v>
+        <v>4.96</v>
       </c>
       <c r="D41" t="n">
-        <v>3.71</v>
+        <v>3.98</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>61.25</v>
+        <v>4.72</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>-1.21</v>
+        <v>-4.84</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>RILINFRA</t>
+          <t>NITIRAJ</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>33.65</v>
+        <v>213.7</v>
       </c>
       <c r="C42" t="n">
-        <v>34.9</v>
+        <v>222</v>
       </c>
       <c r="D42" t="n">
-        <v>3.71</v>
+        <v>3.88</v>
       </c>
       <c r="E42" t="b">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>34</v>
+        <v>208.55</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>-2.58</v>
+        <v>-6.06</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>RUBFILA</t>
+          <t>SWANDEF</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>64.53</v>
+        <v>2022.5</v>
       </c>
       <c r="C43" t="n">
-        <v>66.90000000000001</v>
+        <v>2100</v>
       </c>
       <c r="D43" t="n">
-        <v>3.67</v>
+        <v>3.83</v>
       </c>
       <c r="E43" t="b">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>64.56999999999999</v>
+        <v>2000</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>-3.48</v>
+        <v>-4.76</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>NAVKARURB</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.1</v>
+        <v>484.5</v>
       </c>
       <c r="C44" t="n">
-        <v>1.14</v>
+        <v>503</v>
       </c>
       <c r="D44" t="n">
-        <v>3.64</v>
+        <v>3.82</v>
       </c>
       <c r="E44" t="b">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>1.12</v>
+        <v>472.55</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>-1.75</v>
+        <v>-6.05</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GAYAHWS</t>
+          <t>PARASPETRO</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="C45" t="n">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="D45" t="n">
-        <v>3.57</v>
+        <v>3.81</v>
       </c>
       <c r="E45" t="b">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>-0.86</v>
+        <v>-2.29</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>UMESLTD</t>
+          <t>S&amp;SPOWER</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4.21</v>
+        <v>331.05</v>
       </c>
       <c r="C46" t="n">
-        <v>4.36</v>
+        <v>343.25</v>
       </c>
       <c r="D46" t="n">
-        <v>3.56</v>
+        <v>3.69</v>
       </c>
       <c r="E46" t="b">
         <v>0</v>
       </c>
-      <c r="F46" t="n">
-        <v>4.23</v>
-      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" t="n">
-        <v>-2.98</v>
-      </c>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CYBERMEDIA</t>
+          <t>MADHUCON</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>14.46</v>
+        <v>4.39</v>
       </c>
       <c r="C47" t="n">
-        <v>14.97</v>
+        <v>4.55</v>
       </c>
       <c r="D47" t="n">
-        <v>3.53</v>
+        <v>3.64</v>
       </c>
       <c r="E47" t="b">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>14.01</v>
+        <v>4.37</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>-6.41</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MANOMAY</t>
+          <t>TICL</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>215.9</v>
+        <v>24.61</v>
       </c>
       <c r="C48" t="n">
-        <v>223.5</v>
+        <v>25.5</v>
       </c>
       <c r="D48" t="n">
-        <v>3.52</v>
+        <v>3.62</v>
       </c>
       <c r="E48" t="b">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>214.01</v>
+        <v>24.4</v>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>-4.25</v>
+        <v>-4.31</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SHREYANIND</t>
+          <t>SELMC</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>149.65</v>
+        <v>30.39</v>
       </c>
       <c r="C49" t="n">
-        <v>154.9</v>
+        <v>31.49</v>
       </c>
       <c r="D49" t="n">
-        <v>3.51</v>
+        <v>3.62</v>
       </c>
       <c r="E49" t="b">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>151</v>
+        <v>29.11</v>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>-2.52</v>
+        <v>-7.56</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DCXINDIA</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>177.75</v>
+        <v>278.95</v>
       </c>
       <c r="C50" t="n">
-        <v>183.98</v>
+        <v>289</v>
       </c>
       <c r="D50" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="E50" t="b">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>196.27</v>
+        <v>273.85</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>6.68</v>
+        <v>-5.24</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BESTAGRO</t>
+          <t>VINEETLAB</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>15.42</v>
+        <v>30.4</v>
       </c>
       <c r="C51" t="n">
-        <v>15.96</v>
+        <v>31.49</v>
       </c>
       <c r="D51" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="E51" t="b">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>16.19</v>
+        <v>28.83</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>1.44</v>
+        <v>-8.449999999999999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>KIRLOSBROS</t>
+          <t>ASHIMASYN</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1493.9</v>
+        <v>14.01</v>
       </c>
       <c r="C52" t="n">
-        <v>1546.2</v>
+        <v>14.5</v>
       </c>
       <c r="D52" t="n">
         <v>3.5</v>
@@ -1773,3885 +1773,3881 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>1605.8</v>
+        <v>14.3</v>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>3.85</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>GSS</t>
+          <t>JWL</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>12.97</v>
+        <v>298.6</v>
       </c>
       <c r="C53" t="n">
-        <v>13.42</v>
+        <v>309</v>
       </c>
       <c r="D53" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="E53" t="b">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>12.86</v>
+        <v>291.4</v>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>-4.17</v>
+        <v>-5.7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>HAVISHA</t>
+          <t>SIGIND</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1.45</v>
+        <v>45.45</v>
       </c>
       <c r="C54" t="n">
-        <v>1.5</v>
+        <v>46.98</v>
       </c>
       <c r="D54" t="n">
-        <v>3.45</v>
+        <v>3.37</v>
       </c>
       <c r="E54" t="b">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>1.49</v>
+        <v>44.55</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>-0.67</v>
+        <v>-5.17</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>RANASUG</t>
+          <t>PRAKASHSTL</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>11.87</v>
+        <v>4.15</v>
       </c>
       <c r="C55" t="n">
-        <v>12.28</v>
+        <v>4.29</v>
       </c>
       <c r="D55" t="n">
-        <v>3.45</v>
+        <v>3.37</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>11.66</v>
+        <v>4.08</v>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>-5.05</v>
+        <v>-4.9</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DEEDEV</t>
+          <t>MODTHREAD</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>276.5</v>
+        <v>52.06</v>
       </c>
       <c r="C56" t="n">
-        <v>285.95</v>
+        <v>53.62</v>
       </c>
       <c r="D56" t="n">
-        <v>3.42</v>
+        <v>3</v>
       </c>
       <c r="E56" t="b">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>285.8</v>
+        <v>51.74</v>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>-0.05</v>
+        <v>-3.51</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MARC</t>
+          <t>MAITREYA</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>61.95</v>
+        <v>219.05</v>
       </c>
       <c r="C57" t="n">
-        <v>64</v>
+        <v>225.5</v>
       </c>
       <c r="D57" t="n">
-        <v>3.31</v>
+        <v>2.94</v>
       </c>
       <c r="E57" t="b">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>63.85</v>
+        <v>217.95</v>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>-0.23</v>
+        <v>-3.35</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PRITI</t>
+          <t>HCL-INSYS</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>40.57</v>
+        <v>12.51</v>
       </c>
       <c r="C58" t="n">
-        <v>41.9</v>
+        <v>12.87</v>
       </c>
       <c r="D58" t="n">
-        <v>3.28</v>
+        <v>2.88</v>
       </c>
       <c r="E58" t="b">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>40.23</v>
+        <v>12.32</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>-3.99</v>
+        <v>-4.27</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ARCHIES</t>
+          <t>NOIDATOLL</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>14.47</v>
+        <v>3.87</v>
       </c>
       <c r="C59" t="n">
-        <v>14.94</v>
+        <v>3.98</v>
       </c>
       <c r="D59" t="n">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="E59" t="b">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>14.85</v>
+        <v>3.66</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>-0.6</v>
+        <v>-8.039999999999999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SWANDEF</t>
+          <t>GVPTECH</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1937.2</v>
+        <v>6.52</v>
       </c>
       <c r="C60" t="n">
-        <v>1999.9</v>
+        <v>6.7</v>
       </c>
       <c r="D60" t="n">
-        <v>3.24</v>
+        <v>2.76</v>
       </c>
       <c r="E60" t="b">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>2018</v>
+        <v>6.27</v>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>0.91</v>
+        <v>-6.42</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>RVTH</t>
+          <t>TREJHARA</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>619</v>
+        <v>175.21</v>
       </c>
       <c r="C61" t="n">
-        <v>638.9</v>
+        <v>179.98</v>
       </c>
       <c r="D61" t="n">
-        <v>3.21</v>
+        <v>2.72</v>
       </c>
       <c r="E61" t="b">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>620</v>
+        <v>170</v>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>-2.96</v>
+        <v>-5.55</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>USK</t>
+          <t>ABAN</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>27.22</v>
+        <v>22.3</v>
       </c>
       <c r="C62" t="n">
-        <v>28.09</v>
+        <v>22.9</v>
       </c>
       <c r="D62" t="n">
-        <v>3.2</v>
+        <v>2.69</v>
       </c>
       <c r="E62" t="b">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>26.85</v>
+        <v>23.41</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>-4.41</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AAATECH</t>
+          <t>STEL</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>91.02</v>
+        <v>524.65</v>
       </c>
       <c r="C63" t="n">
-        <v>93.90000000000001</v>
+        <v>538.7</v>
       </c>
       <c r="D63" t="n">
-        <v>3.16</v>
+        <v>2.68</v>
       </c>
       <c r="E63" t="b">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>92.3</v>
+        <v>534.8</v>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>-1.7</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DSFCL</t>
+          <t>TVVISION</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>30.05</v>
+        <v>5.65</v>
       </c>
       <c r="C64" t="n">
-        <v>31</v>
+        <v>5.8</v>
       </c>
       <c r="D64" t="n">
-        <v>3.16</v>
+        <v>2.65</v>
       </c>
       <c r="E64" t="b">
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>29.25</v>
+        <v>5.64</v>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>-5.65</v>
+        <v>-2.76</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>OSIAHYPER</t>
+          <t>VHLTD</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>8.119999999999999</v>
+        <v>149.09</v>
       </c>
       <c r="C65" t="n">
-        <v>8.369999999999999</v>
+        <v>153</v>
       </c>
       <c r="D65" t="n">
-        <v>3.08</v>
+        <v>2.62</v>
       </c>
       <c r="E65" t="b">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>8.01</v>
+        <v>146</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>-4.3</v>
+        <v>-4.58</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>KAMOPAINTS</t>
+          <t>SIKKO</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>4.26</v>
+        <v>4.63</v>
       </c>
       <c r="C66" t="n">
-        <v>4.39</v>
+        <v>4.75</v>
       </c>
       <c r="D66" t="n">
-        <v>3.05</v>
+        <v>2.59</v>
       </c>
       <c r="E66" t="b">
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>4.22</v>
+        <v>4.56</v>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>-3.87</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DEVIT</t>
+          <t>SAURASHCEM</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>26.18</v>
+        <v>62.59</v>
       </c>
       <c r="C67" t="n">
-        <v>26.97</v>
+        <v>64.2</v>
       </c>
       <c r="D67" t="n">
-        <v>3.02</v>
+        <v>2.57</v>
       </c>
       <c r="E67" t="b">
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>26.45</v>
+        <v>60.15</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>-1.93</v>
+        <v>-6.31</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>KOTYARK</t>
+          <t>JINDRILL</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>278.35</v>
+        <v>542.2</v>
       </c>
       <c r="C68" t="n">
-        <v>286.75</v>
+        <v>556</v>
       </c>
       <c r="D68" t="n">
-        <v>3.02</v>
+        <v>2.55</v>
       </c>
       <c r="E68" t="b">
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>278.9</v>
+        <v>565.9</v>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>-2.74</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>LTFOODS</t>
+          <t>ASIANHOTNR</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>430.15</v>
+        <v>292.65</v>
       </c>
       <c r="C69" t="n">
-        <v>443</v>
+        <v>299.95</v>
       </c>
       <c r="D69" t="n">
-        <v>2.99</v>
+        <v>2.49</v>
       </c>
       <c r="E69" t="b">
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>445.85</v>
+        <v>289.05</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>0.64</v>
+        <v>-3.63</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>LYPSAGEMS</t>
+          <t>ORCHASP</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>5.05</v>
+        <v>2.43</v>
       </c>
       <c r="C70" t="n">
-        <v>5.2</v>
+        <v>2.49</v>
       </c>
       <c r="D70" t="n">
-        <v>2.97</v>
+        <v>2.47</v>
       </c>
       <c r="E70" t="b">
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>5.19</v>
+        <v>2.33</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>-0.19</v>
+        <v>-6.43</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ESAFSFB</t>
+          <t>EMUDHRA</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>26.04</v>
+        <v>413.6</v>
       </c>
       <c r="C71" t="n">
-        <v>26.78</v>
+        <v>423.7</v>
       </c>
       <c r="D71" t="n">
-        <v>2.84</v>
+        <v>2.44</v>
       </c>
       <c r="E71" t="b">
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>26</v>
+        <v>408.3</v>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>-2.91</v>
+        <v>-3.63</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>HYBRIDFIN</t>
+          <t>BLUECOAST</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>18.66</v>
+        <v>20.93</v>
       </c>
       <c r="C72" t="n">
-        <v>19.18</v>
+        <v>21.44</v>
       </c>
       <c r="D72" t="n">
-        <v>2.79</v>
+        <v>2.44</v>
       </c>
       <c r="E72" t="b">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>20.14</v>
+        <v>20.5</v>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>5.01</v>
+        <v>-4.38</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>VHLTD</t>
+          <t>FEL</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>143.99</v>
+        <v>0.42</v>
       </c>
       <c r="C73" t="n">
-        <v>148</v>
+        <v>0.43</v>
       </c>
       <c r="D73" t="n">
-        <v>2.78</v>
+        <v>2.38</v>
       </c>
       <c r="E73" t="b">
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>148.01</v>
+        <v>0.41</v>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>0.01</v>
+        <v>-4.65</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FRACTAL</t>
+          <t>SIGMAADV</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>759.15</v>
+        <v>160.13</v>
       </c>
       <c r="C74" t="n">
-        <v>780</v>
+        <v>163.9</v>
       </c>
       <c r="D74" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="E74" t="b">
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>818.8</v>
+        <v>154.43</v>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>4.97</v>
+        <v>-5.78</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AKSHAR</t>
+          <t>DNAMEDIA</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.37</v>
+        <v>3.41</v>
       </c>
       <c r="C75" t="n">
-        <v>0.38</v>
+        <v>3.49</v>
       </c>
       <c r="D75" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="E75" t="b">
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>0.38</v>
+        <v>3.36</v>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>-3.72</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FINKURVE</t>
+          <t>IITL</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>66.91</v>
+        <v>131.93</v>
       </c>
       <c r="C76" t="n">
-        <v>68.7</v>
+        <v>134.93</v>
       </c>
       <c r="D76" t="n">
-        <v>2.68</v>
+        <v>2.27</v>
       </c>
       <c r="E76" t="b">
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>67.43000000000001</v>
+        <v>123.48</v>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>-1.85</v>
+        <v>-8.49</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SHAH</t>
+          <t>GATECH</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>4.86</v>
+        <v>0.46</v>
       </c>
       <c r="C77" t="n">
-        <v>4.99</v>
+        <v>0.47</v>
       </c>
       <c r="D77" t="n">
-        <v>2.67</v>
+        <v>2.17</v>
       </c>
       <c r="E77" t="b">
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>4.9</v>
+        <v>0.46</v>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>-1.8</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SONAMLTD</t>
+          <t>ZEELEARN</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>51.23</v>
+        <v>5.57</v>
       </c>
       <c r="C78" t="n">
-        <v>52.6</v>
+        <v>5.69</v>
       </c>
       <c r="D78" t="n">
-        <v>2.67</v>
+        <v>2.15</v>
       </c>
       <c r="E78" t="b">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>51.21</v>
+        <v>5.4</v>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>-2.64</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MCLOUD</t>
+          <t>GATECHDVR</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>23.34</v>
+        <v>0.47</v>
       </c>
       <c r="C79" t="n">
-        <v>23.96</v>
+        <v>0.48</v>
       </c>
       <c r="D79" t="n">
-        <v>2.66</v>
+        <v>2.13</v>
       </c>
       <c r="E79" t="b">
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>23.65</v>
+        <v>0.43</v>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>-1.29</v>
+        <v>-10.42</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>LANCORHOL</t>
+          <t>AVONMORE</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>22.96</v>
+        <v>14.1</v>
       </c>
       <c r="C80" t="n">
-        <v>23.57</v>
+        <v>14.4</v>
       </c>
       <c r="D80" t="n">
-        <v>2.66</v>
+        <v>2.13</v>
       </c>
       <c r="E80" t="b">
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>23.57</v>
+        <v>13.88</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>-3.61</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ALPA</t>
+          <t>BGLOBAL</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>63.23</v>
+        <v>2.84</v>
       </c>
       <c r="C81" t="n">
-        <v>64.90000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="D81" t="n">
-        <v>2.64</v>
+        <v>2.11</v>
       </c>
       <c r="E81" t="b">
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>63.59</v>
+        <v>2.92</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>-2.02</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>NITIRAJ</t>
+          <t>RAJMET</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>204.57</v>
+        <v>3.81</v>
       </c>
       <c r="C82" t="n">
-        <v>209.95</v>
+        <v>3.89</v>
       </c>
       <c r="D82" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="E82" t="b">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>205</v>
+        <v>3.76</v>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>-2.36</v>
+        <v>-3.34</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DRCSYSTEMS</t>
+          <t>KAUSHALYA</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>14.07</v>
+        <v>842.4</v>
       </c>
       <c r="C83" t="n">
-        <v>14.44</v>
+        <v>860</v>
       </c>
       <c r="D83" t="n">
-        <v>2.63</v>
+        <v>2.09</v>
       </c>
       <c r="E83" t="b">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>14.39</v>
+        <v>829</v>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>-0.35</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AARON</t>
+          <t>MTEDUCARE</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>148.13</v>
+        <v>1.47</v>
       </c>
       <c r="C84" t="n">
-        <v>152</v>
+        <v>1.5</v>
       </c>
       <c r="D84" t="n">
-        <v>2.61</v>
+        <v>2.04</v>
       </c>
       <c r="E84" t="b">
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>151.2</v>
+        <v>1.47</v>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>-0.53</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>UNITEDPOLY</t>
+          <t>ORTEL</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>24.29</v>
+        <v>1.48</v>
       </c>
       <c r="C85" t="n">
-        <v>24.9</v>
+        <v>1.51</v>
       </c>
       <c r="D85" t="n">
-        <v>2.51</v>
+        <v>2.03</v>
       </c>
       <c r="E85" t="b">
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>25.49</v>
+        <v>1.5</v>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>2.37</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ANTGRAPHIC</t>
+          <t>ROML</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.8</v>
+        <v>44.98</v>
       </c>
       <c r="C86" t="n">
-        <v>0.82</v>
+        <v>45.89</v>
       </c>
       <c r="D86" t="n">
-        <v>2.5</v>
+        <v>2.02</v>
       </c>
       <c r="E86" t="b">
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>0.8100000000000001</v>
+        <v>44.41</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>-1.22</v>
+        <v>-3.23</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>HILTON</t>
+          <t>DICIND</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>16.97</v>
+        <v>524.45</v>
       </c>
       <c r="C87" t="n">
-        <v>17.39</v>
+        <v>535</v>
       </c>
       <c r="D87" t="n">
-        <v>2.47</v>
+        <v>2.01</v>
       </c>
       <c r="E87" t="b">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>17.18</v>
+        <v>519.7</v>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>-1.21</v>
+        <v>-2.86</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ACCURACY</t>
+          <t>SBGLP</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>4.47</v>
+        <v>28.36</v>
       </c>
       <c r="C88" t="n">
-        <v>4.58</v>
+        <v>28.93</v>
       </c>
       <c r="D88" t="n">
-        <v>2.46</v>
+        <v>2.01</v>
       </c>
       <c r="E88" t="b">
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>4.61</v>
+        <v>27.72</v>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>0.66</v>
+        <v>-4.18</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>OILCOUNTUB</t>
+          <t>PARAS</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>46.26</v>
+        <v>749.35</v>
       </c>
       <c r="C89" t="n">
-        <v>47.4</v>
+        <v>764.35</v>
       </c>
       <c r="D89" t="n">
-        <v>2.46</v>
+        <v>2</v>
       </c>
       <c r="E89" t="b">
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>46.23</v>
+        <v>717.15</v>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>-2.47</v>
+        <v>-6.18</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>RHFL</t>
+          <t>JMA</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2.04</v>
+        <v>84.67</v>
       </c>
       <c r="C90" t="n">
-        <v>2.09</v>
+        <v>86.36</v>
       </c>
       <c r="D90" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="E90" t="b">
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>2.14</v>
+        <v>84</v>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>2.39</v>
+        <v>-2.73</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SHRENIK</t>
+          <t>RAJRILTD</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.41</v>
+        <v>22.84</v>
       </c>
       <c r="C91" t="n">
-        <v>0.42</v>
+        <v>23.29</v>
       </c>
       <c r="D91" t="n">
-        <v>2.44</v>
+        <v>1.97</v>
       </c>
       <c r="E91" t="b">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>0.43</v>
+        <v>22.4</v>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>2.38</v>
+        <v>-3.82</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MRPL</t>
+          <t>SMARTLINK</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>196.24</v>
+        <v>120.14</v>
       </c>
       <c r="C92" t="n">
-        <v>200.99</v>
+        <v>122.5</v>
       </c>
       <c r="D92" t="n">
-        <v>2.42</v>
+        <v>1.96</v>
       </c>
       <c r="E92" t="b">
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>203.35</v>
+        <v>117.2</v>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
-        <v>1.17</v>
+        <v>-4.33</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CHEMFAB</t>
+          <t>SOLARA</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>375.35</v>
+        <v>459.05</v>
       </c>
       <c r="C93" t="n">
-        <v>384.45</v>
+        <v>467.95</v>
       </c>
       <c r="D93" t="n">
-        <v>2.42</v>
+        <v>1.94</v>
       </c>
       <c r="E93" t="b">
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>383.9</v>
+        <v>444.3</v>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
-        <v>-0.14</v>
+        <v>-5.05</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CCCL</t>
+          <t>SURANASOL</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>15.33</v>
+        <v>22.26</v>
       </c>
       <c r="C94" t="n">
-        <v>15.7</v>
+        <v>22.69</v>
       </c>
       <c r="D94" t="n">
-        <v>2.41</v>
+        <v>1.93</v>
       </c>
       <c r="E94" t="b">
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>15.39</v>
+        <v>21.23</v>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>-1.97</v>
+        <v>-6.43</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CHENNPETRO</t>
+          <t>SCPL</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>991.5</v>
+        <v>325.75</v>
       </c>
       <c r="C95" t="n">
-        <v>1015</v>
+        <v>332</v>
       </c>
       <c r="D95" t="n">
-        <v>2.37</v>
+        <v>1.92</v>
       </c>
       <c r="E95" t="b">
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>1003.3</v>
+        <v>318.9</v>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>-1.15</v>
+        <v>-3.95</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>KAKATCEM</t>
+          <t>VIVIDHA</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>108.05</v>
+        <v>0.52</v>
       </c>
       <c r="C96" t="n">
-        <v>110.6</v>
+        <v>0.53</v>
       </c>
       <c r="D96" t="n">
-        <v>2.36</v>
+        <v>1.92</v>
       </c>
       <c r="E96" t="b">
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>109</v>
+        <v>0.54</v>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>-1.45</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>GOKUL</t>
+          <t>GSS</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>39.91</v>
+        <v>13.09</v>
       </c>
       <c r="C97" t="n">
-        <v>40.85</v>
+        <v>13.34</v>
       </c>
       <c r="D97" t="n">
-        <v>2.36</v>
+        <v>1.91</v>
       </c>
       <c r="E97" t="b">
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>39.5</v>
+        <v>13</v>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>-3.3</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SSEGL</t>
+          <t>SADBHIN</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>347.35</v>
+        <v>3.18</v>
       </c>
       <c r="C98" t="n">
-        <v>355.5</v>
+        <v>3.24</v>
       </c>
       <c r="D98" t="n">
-        <v>2.35</v>
+        <v>1.89</v>
       </c>
       <c r="E98" t="b">
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>355.9</v>
+        <v>3.17</v>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>0.11</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>TEXMOPIPES</t>
+          <t>VISASTEEL</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>43.19</v>
+        <v>36.2</v>
       </c>
       <c r="C99" t="n">
-        <v>44.19</v>
+        <v>36.88</v>
       </c>
       <c r="D99" t="n">
-        <v>2.32</v>
+        <v>1.88</v>
       </c>
       <c r="E99" t="b">
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>43.53</v>
+        <v>34.8</v>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
-        <v>-1.49</v>
+        <v>-5.64</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>UFO</t>
+          <t>RUDRA</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>68.31999999999999</v>
+        <v>17.76</v>
       </c>
       <c r="C100" t="n">
-        <v>69.89</v>
+        <v>18.09</v>
       </c>
       <c r="D100" t="n">
-        <v>2.3</v>
+        <v>1.86</v>
       </c>
       <c r="E100" t="b">
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>69.2</v>
+        <v>16.98</v>
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>-0.99</v>
+        <v>-6.14</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AKG</t>
+          <t>TPHQ</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>10.95</v>
+        <v>0.55</v>
       </c>
       <c r="C101" t="n">
-        <v>11.2</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D101" t="n">
-        <v>2.28</v>
+        <v>1.82</v>
       </c>
       <c r="E101" t="b">
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>10.92</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>RAMKY</t>
+          <t>AMJLAND</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>481.7</v>
+        <v>38.42</v>
       </c>
       <c r="C102" t="n">
-        <v>492.7</v>
+        <v>39.1</v>
       </c>
       <c r="D102" t="n">
-        <v>2.28</v>
+        <v>1.77</v>
       </c>
       <c r="E102" t="b">
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>493.35</v>
+        <v>38.44</v>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>0.13</v>
+        <v>-1.69</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>THOMASCOTT</t>
+          <t>RKDL</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>272.8</v>
+        <v>20.55</v>
       </c>
       <c r="C103" t="n">
-        <v>279</v>
+        <v>20.9</v>
       </c>
       <c r="D103" t="n">
-        <v>2.27</v>
+        <v>1.7</v>
       </c>
       <c r="E103" t="b">
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>273.75</v>
+        <v>19.48</v>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>-1.88</v>
+        <v>-6.79</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CYBERTECH</t>
+          <t>DPEL</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>103.67</v>
+        <v>290.1</v>
       </c>
       <c r="C104" t="n">
-        <v>106</v>
+        <v>295</v>
       </c>
       <c r="D104" t="n">
-        <v>2.25</v>
+        <v>1.69</v>
       </c>
       <c r="E104" t="b">
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>107.96</v>
+        <v>276.25</v>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
-        <v>1.85</v>
+        <v>-6.36</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>HCL-INSYS</t>
+          <t>MHLXMIRU</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>12.42</v>
+        <v>170.07</v>
       </c>
       <c r="C105" t="n">
-        <v>12.7</v>
+        <v>172.9</v>
       </c>
       <c r="D105" t="n">
-        <v>2.25</v>
+        <v>1.66</v>
       </c>
       <c r="E105" t="b">
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>12.57</v>
+        <v>169.99</v>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>-1.02</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>UEL</t>
+          <t>DANGEE</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>169.92</v>
+        <v>3.02</v>
       </c>
       <c r="C106" t="n">
-        <v>173.7</v>
+        <v>3.07</v>
       </c>
       <c r="D106" t="n">
-        <v>2.22</v>
+        <v>1.66</v>
       </c>
       <c r="E106" t="b">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>178.41</v>
+        <v>3.01</v>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
-        <v>2.71</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>BSL</t>
+          <t>SPCENET</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>122</v>
+        <v>4.28</v>
       </c>
       <c r="C107" t="n">
-        <v>124.7</v>
+        <v>4.35</v>
       </c>
       <c r="D107" t="n">
-        <v>2.21</v>
+        <v>1.64</v>
       </c>
       <c r="E107" t="b">
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>129.3</v>
+        <v>4.09</v>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>3.69</v>
+        <v>-5.98</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>KANORICHEM</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>65.97</v>
+        <v>131.99</v>
       </c>
       <c r="C108" t="n">
-        <v>67.40000000000001</v>
+        <v>134.01</v>
       </c>
       <c r="D108" t="n">
-        <v>2.17</v>
+        <v>1.53</v>
       </c>
       <c r="E108" t="b">
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>66.34999999999999</v>
+        <v>127.15</v>
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
-        <v>-1.56</v>
+        <v>-5.12</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ADVANIHOTR</t>
+          <t>KOHINOOR</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>53.77</v>
+        <v>25.61</v>
       </c>
       <c r="C109" t="n">
-        <v>54.93</v>
+        <v>26</v>
       </c>
       <c r="D109" t="n">
-        <v>2.16</v>
+        <v>1.52</v>
       </c>
       <c r="E109" t="b">
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>53.65</v>
+        <v>24.89</v>
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>-2.33</v>
+        <v>-4.27</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>HINDCON</t>
+          <t>OMINFRAL</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>19.08</v>
+        <v>80.29000000000001</v>
       </c>
       <c r="C110" t="n">
-        <v>19.49</v>
+        <v>81.5</v>
       </c>
       <c r="D110" t="n">
-        <v>2.15</v>
+        <v>1.51</v>
       </c>
       <c r="E110" t="b">
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>19.18</v>
+        <v>77.45</v>
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
-        <v>-1.59</v>
+        <v>-4.97</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>KUANTUM</t>
+          <t>AIRAN</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>84.11</v>
+        <v>16.01</v>
       </c>
       <c r="C111" t="n">
-        <v>85.90000000000001</v>
+        <v>16.25</v>
       </c>
       <c r="D111" t="n">
-        <v>2.13</v>
+        <v>1.5</v>
       </c>
       <c r="E111" t="b">
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>84.65000000000001</v>
+        <v>15.55</v>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>-1.46</v>
+        <v>-4.31</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>GATECH</t>
+          <t>GVKPIL</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.47</v>
+        <v>2.69</v>
       </c>
       <c r="C112" t="n">
-        <v>0.48</v>
+        <v>2.73</v>
       </c>
       <c r="D112" t="n">
-        <v>2.13</v>
+        <v>1.49</v>
       </c>
       <c r="E112" t="b">
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>0.48</v>
+        <v>2.64</v>
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
-        <v>0</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AQYLON</t>
+          <t>NELCAST</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>113.8</v>
+        <v>114.59</v>
       </c>
       <c r="C113" t="n">
-        <v>116.2</v>
+        <v>116.3</v>
       </c>
       <c r="D113" t="n">
-        <v>2.11</v>
+        <v>1.49</v>
       </c>
       <c r="E113" t="b">
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>119.4</v>
+        <v>111.67</v>
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>2.75</v>
+        <v>-3.98</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>NIBE</t>
+          <t>MBLINFRA</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>979.8</v>
+        <v>25.61</v>
       </c>
       <c r="C114" t="n">
-        <v>1000</v>
+        <v>25.99</v>
       </c>
       <c r="D114" t="n">
-        <v>2.06</v>
+        <v>1.48</v>
       </c>
       <c r="E114" t="b">
         <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>1030.2</v>
+        <v>24.6</v>
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
-        <v>3.02</v>
+        <v>-5.35</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MTEDUCARE</t>
+          <t>KRITINUT</t>
         </is>
       </c>
       <c r="B115" t="n">
+        <v>65.05</v>
+      </c>
+      <c r="C115" t="n">
+        <v>66</v>
+      </c>
+      <c r="D115" t="n">
         <v>1.46</v>
       </c>
-      <c r="C115" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="D115" t="n">
-        <v>2.05</v>
-      </c>
       <c r="E115" t="b">
         <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>1.51</v>
+        <v>61.5</v>
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>1.34</v>
+        <v>-6.82</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MKPL</t>
+          <t>SURANAT&amp;P</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>4.9</v>
+        <v>17.24</v>
       </c>
       <c r="C116" t="n">
-        <v>5</v>
+        <v>17.49</v>
       </c>
       <c r="D116" t="n">
-        <v>2.04</v>
+        <v>1.45</v>
       </c>
       <c r="E116" t="b">
         <v>0</v>
       </c>
-      <c r="F116" t="n">
-        <v>5.01</v>
-      </c>
+      <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
-      <c r="H116" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>OCCLLTD</t>
+          <t>COUNCODOS</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>82.43000000000001</v>
+        <v>4.91</v>
       </c>
       <c r="C117" t="n">
-        <v>84.09999999999999</v>
+        <v>4.98</v>
       </c>
       <c r="D117" t="n">
-        <v>2.03</v>
+        <v>1.43</v>
       </c>
       <c r="E117" t="b">
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>83.14</v>
+        <v>4.9</v>
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>-1.14</v>
+        <v>-1.61</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>LEMERITE</t>
+          <t>HINDCOMPOS</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>450.25</v>
+        <v>414.05</v>
       </c>
       <c r="C118" t="n">
-        <v>459.3</v>
+        <v>419.9</v>
       </c>
       <c r="D118" t="n">
-        <v>2.01</v>
+        <v>1.41</v>
       </c>
       <c r="E118" t="b">
         <v>0</v>
       </c>
       <c r="F118" t="n">
-        <v>449.6</v>
+        <v>403.95</v>
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
-        <v>-2.11</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>KRITIKA</t>
+          <t>KDL</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>5.96</v>
+        <v>120.1</v>
       </c>
       <c r="C119" t="n">
-        <v>6.08</v>
+        <v>121.7</v>
       </c>
       <c r="D119" t="n">
-        <v>2.01</v>
+        <v>1.33</v>
       </c>
       <c r="E119" t="b">
         <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>5.93</v>
+        <v>122.5</v>
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
-        <v>-2.47</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>PREMIER</t>
+          <t>SPLPETRO</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>2.99</v>
+        <v>669.2</v>
       </c>
       <c r="C120" t="n">
-        <v>3.05</v>
+        <v>678</v>
       </c>
       <c r="D120" t="n">
-        <v>2.01</v>
+        <v>1.32</v>
       </c>
       <c r="E120" t="b">
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>2.91</v>
+        <v>662.4</v>
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
-        <v>-4.59</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SIKKO</t>
+          <t>DRONE</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>4.54</v>
+        <v>47.35</v>
       </c>
       <c r="C121" t="n">
-        <v>4.63</v>
+        <v>47.95</v>
       </c>
       <c r="D121" t="n">
-        <v>1.98</v>
+        <v>1.27</v>
       </c>
       <c r="E121" t="b">
         <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>4.66</v>
+        <v>46.25</v>
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
-        <v>0.65</v>
+        <v>-3.55</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>COMPUSOFT</t>
+          <t>RSSOFTWARE</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>13.16</v>
+        <v>32.49</v>
       </c>
       <c r="C122" t="n">
-        <v>13.42</v>
+        <v>32.9</v>
       </c>
       <c r="D122" t="n">
-        <v>1.98</v>
+        <v>1.26</v>
       </c>
       <c r="E122" t="b">
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>13.15</v>
+        <v>31.82</v>
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
-        <v>-2.01</v>
+        <v>-3.28</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MADHAV</t>
+          <t>AXITA</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>35.27</v>
+        <v>8.85</v>
       </c>
       <c r="C123" t="n">
-        <v>35.97</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="D123" t="n">
-        <v>1.98</v>
+        <v>1.24</v>
       </c>
       <c r="E123" t="b">
         <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>35.91</v>
+        <v>8.65</v>
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>-0.17</v>
+        <v>-3.46</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ROSSELLIND</t>
+          <t>CHENNPETRO</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>44.95</v>
+        <v>1007.5</v>
       </c>
       <c r="C124" t="n">
-        <v>45.84</v>
+        <v>1020</v>
       </c>
       <c r="D124" t="n">
-        <v>1.98</v>
+        <v>1.24</v>
       </c>
       <c r="E124" t="b">
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>45.58</v>
+        <v>948.85</v>
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
-        <v>-0.57</v>
+        <v>-6.98</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>OSWALGREEN</t>
+          <t>ANTGRAPHIC</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>25</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="C125" t="n">
-        <v>25.49</v>
+        <v>0.82</v>
       </c>
       <c r="D125" t="n">
-        <v>1.96</v>
+        <v>1.23</v>
       </c>
       <c r="E125" t="b">
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>24.99</v>
+        <v>0.79</v>
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>-1.96</v>
+        <v>-3.66</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>GOLDENTOBC</t>
+          <t>UNITEDPOLY</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>29.01</v>
+        <v>25.5</v>
       </c>
       <c r="C126" t="n">
-        <v>29.58</v>
+        <v>25.8</v>
       </c>
       <c r="D126" t="n">
-        <v>1.96</v>
+        <v>1.18</v>
       </c>
       <c r="E126" t="b">
         <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>29.3</v>
+        <v>24.9</v>
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
-        <v>-0.95</v>
+        <v>-3.49</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>VARDMNPOLY</t>
+          <t>INDUSINVIT</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>8.199999999999999</v>
+        <v>123.21</v>
       </c>
       <c r="C127" t="n">
-        <v>8.359999999999999</v>
+        <v>124.67</v>
       </c>
       <c r="D127" t="n">
-        <v>1.95</v>
+        <v>1.18</v>
       </c>
       <c r="E127" t="b">
         <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>8.609999999999999</v>
+        <v>121.78</v>
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
-        <v>2.99</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>MUKTAARTS</t>
+          <t>SUMEETINDS</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>53.76</v>
+        <v>30.64</v>
       </c>
       <c r="C128" t="n">
-        <v>54.8</v>
+        <v>31</v>
       </c>
       <c r="D128" t="n">
-        <v>1.93</v>
+        <v>1.17</v>
       </c>
       <c r="E128" t="b">
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>52.78</v>
+        <v>29.61</v>
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
-        <v>-3.69</v>
+        <v>-4.48</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>LASA</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>6.28</v>
+        <v>7.89</v>
       </c>
       <c r="C129" t="n">
-        <v>6.4</v>
+        <v>7.98</v>
       </c>
       <c r="D129" t="n">
-        <v>1.91</v>
+        <v>1.14</v>
       </c>
       <c r="E129" t="b">
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>6.44</v>
+        <v>7.74</v>
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
-        <v>0.63</v>
+        <v>-3.01</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>TARACHAND</t>
+          <t>ALPHAGEO</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>59.86</v>
+        <v>202.75</v>
       </c>
       <c r="C130" t="n">
-        <v>61</v>
+        <v>205</v>
       </c>
       <c r="D130" t="n">
-        <v>1.9</v>
+        <v>1.11</v>
       </c>
       <c r="E130" t="b">
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>59.98</v>
+        <v>208</v>
       </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
-        <v>-1.67</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CHAMUNDA</t>
+          <t>EFACTOR</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>47.5</v>
+        <v>225.5</v>
       </c>
       <c r="C131" t="n">
-        <v>48.4</v>
+        <v>228</v>
       </c>
       <c r="D131" t="n">
-        <v>1.89</v>
+        <v>1.11</v>
       </c>
       <c r="E131" t="b">
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>47</v>
+        <v>220</v>
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
-        <v>-2.89</v>
+        <v>-3.51</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>GML</t>
+          <t>ASMS</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>16</v>
+        <v>9.02</v>
       </c>
       <c r="C132" t="n">
-        <v>16.3</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="D132" t="n">
-        <v>1.88</v>
+        <v>1.11</v>
       </c>
       <c r="E132" t="b">
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>16.3</v>
+        <v>8.76</v>
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
-        <v>0</v>
+        <v>-3.95</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>NIBL</t>
+          <t>ISHANCH</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>30.82</v>
+        <v>57.79</v>
       </c>
       <c r="C133" t="n">
-        <v>31.4</v>
+        <v>58.4</v>
       </c>
       <c r="D133" t="n">
-        <v>1.88</v>
+        <v>1.06</v>
       </c>
       <c r="E133" t="b">
         <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>31.21</v>
+        <v>56.99</v>
       </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
-        <v>-0.61</v>
+        <v>-2.41</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A2ZINFRA</t>
+          <t>ASIANENE</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>16.54</v>
+        <v>285.5</v>
       </c>
       <c r="C134" t="n">
-        <v>16.85</v>
+        <v>288.5</v>
       </c>
       <c r="D134" t="n">
-        <v>1.87</v>
+        <v>1.05</v>
       </c>
       <c r="E134" t="b">
         <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>16.75</v>
+        <v>273.55</v>
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
-        <v>-0.59</v>
+        <v>-5.18</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BAGFILMS</t>
+          <t>SETCO</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>4.87</v>
+        <v>18.24</v>
       </c>
       <c r="C135" t="n">
-        <v>4.96</v>
+        <v>18.43</v>
       </c>
       <c r="D135" t="n">
-        <v>1.85</v>
+        <v>1.04</v>
       </c>
       <c r="E135" t="b">
         <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>5.06</v>
+        <v>17.45</v>
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
-        <v>2.02</v>
+        <v>-5.32</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>PARASPETRO</t>
+          <t>OSWALSEEDS</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>2.16</v>
+        <v>12.62</v>
       </c>
       <c r="C136" t="n">
-        <v>2.2</v>
+        <v>12.75</v>
       </c>
       <c r="D136" t="n">
-        <v>1.85</v>
+        <v>1.03</v>
       </c>
       <c r="E136" t="b">
         <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>2.19</v>
+        <v>12.58</v>
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
-        <v>-0.45</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SUKHJITS</t>
+          <t>RUSHIL</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>187.53</v>
+        <v>16.47</v>
       </c>
       <c r="C137" t="n">
-        <v>190.96</v>
+        <v>16.64</v>
       </c>
       <c r="D137" t="n">
-        <v>1.83</v>
+        <v>1.03</v>
       </c>
       <c r="E137" t="b">
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>190.56</v>
+        <v>16.2</v>
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
-        <v>-0.21</v>
+        <v>-2.64</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>RUDRA</t>
+          <t>BONLON</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>17.63</v>
+        <v>38.6</v>
       </c>
       <c r="C138" t="n">
-        <v>17.95</v>
+        <v>38.99</v>
       </c>
       <c r="D138" t="n">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="E138" t="b">
         <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>17.8</v>
+        <v>37.97</v>
       </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
-        <v>-0.84</v>
+        <v>-2.62</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SHIVAMILLS</t>
+          <t>TRIGYN</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>55</v>
+        <v>48.51</v>
       </c>
       <c r="C139" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D139" t="n">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="E139" t="b">
         <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>53.9</v>
+        <v>46.71</v>
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
-        <v>-3.75</v>
+        <v>-4.67</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>CUPID</t>
+          <t>KRITIKA</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>405.5</v>
+        <v>5.99</v>
       </c>
       <c r="C140" t="n">
-        <v>412.85</v>
+        <v>6.05</v>
       </c>
       <c r="D140" t="n">
-        <v>1.81</v>
+        <v>1</v>
       </c>
       <c r="E140" t="b">
         <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>407.2</v>
+        <v>6.25</v>
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
-        <v>-1.37</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>LOKESHMACH</t>
+          <t>KAYTEX</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>196.47</v>
+        <v>84.05</v>
       </c>
       <c r="C141" t="n">
-        <v>200</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="D141" t="n">
-        <v>1.8</v>
+        <v>0.95</v>
       </c>
       <c r="E141" t="b">
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>219.58</v>
+        <v>81</v>
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
-        <v>9.789999999999999</v>
+        <v>-4.54</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>GTL</t>
+          <t>OILCOUNTUB</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>6.9</v>
+        <v>46.81</v>
       </c>
       <c r="C142" t="n">
-        <v>7.02</v>
+        <v>47.25</v>
       </c>
       <c r="D142" t="n">
-        <v>1.74</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E142" t="b">
         <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>6.99</v>
+        <v>47</v>
       </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
-        <v>-0.43</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>OMAXAUTO</t>
+          <t>LXCHEM</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>103.22</v>
+        <v>113.72</v>
       </c>
       <c r="C143" t="n">
-        <v>105</v>
+        <v>114.78</v>
       </c>
       <c r="D143" t="n">
-        <v>1.72</v>
+        <v>0.93</v>
       </c>
       <c r="E143" t="b">
         <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>104.23</v>
+        <v>112.52</v>
       </c>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
-        <v>-0.73</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>COROMANDEL</t>
+          <t>CAPTRUST</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>2063.5</v>
+        <v>11.9</v>
       </c>
       <c r="C144" t="n">
-        <v>2099</v>
+        <v>12.01</v>
       </c>
       <c r="D144" t="n">
-        <v>1.72</v>
+        <v>0.92</v>
       </c>
       <c r="E144" t="b">
         <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>2019.1</v>
+        <v>12.3</v>
       </c>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
-        <v>-3.81</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>KCEIL</t>
+          <t>NAGAFERT</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>122.9</v>
+        <v>4.34</v>
       </c>
       <c r="C145" t="n">
-        <v>125</v>
+        <v>4.38</v>
       </c>
       <c r="D145" t="n">
-        <v>1.71</v>
+        <v>0.92</v>
       </c>
       <c r="E145" t="b">
         <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>120.15</v>
+        <v>4.19</v>
       </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
-        <v>-3.88</v>
+        <v>-4.34</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SANATHAN</t>
+          <t>MAXIND</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>411.5</v>
+        <v>148.64</v>
       </c>
       <c r="C146" t="n">
-        <v>418.45</v>
+        <v>150</v>
       </c>
       <c r="D146" t="n">
-        <v>1.69</v>
+        <v>0.91</v>
       </c>
       <c r="E146" t="b">
         <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>412.05</v>
+        <v>142.96</v>
       </c>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
-        <v>-1.53</v>
+        <v>-4.69</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>RSSOFTWARE</t>
+          <t>MIDWESTLTD</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>33.45</v>
+        <v>1126.7</v>
       </c>
       <c r="C147" t="n">
-        <v>34</v>
+        <v>1136.9</v>
       </c>
       <c r="D147" t="n">
-        <v>1.64</v>
+        <v>0.91</v>
       </c>
       <c r="E147" t="b">
         <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>33.2</v>
+        <v>1076</v>
       </c>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
-        <v>-2.35</v>
+        <v>-5.36</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>GINNIFILA</t>
+          <t>ANANTAM</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>35.05</v>
+        <v>102.97</v>
       </c>
       <c r="C148" t="n">
-        <v>35.62</v>
+        <v>103.9</v>
       </c>
       <c r="D148" t="n">
-        <v>1.63</v>
+        <v>0.9</v>
       </c>
       <c r="E148" t="b">
         <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>34.87</v>
+        <v>102.22</v>
       </c>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
-        <v>-2.11</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>GOLDTECH</t>
+          <t>VAISHALI</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>39.37</v>
+        <v>6.74</v>
       </c>
       <c r="C149" t="n">
-        <v>40</v>
+        <v>6.8</v>
       </c>
       <c r="D149" t="n">
-        <v>1.6</v>
+        <v>0.89</v>
       </c>
       <c r="E149" t="b">
         <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>39.45</v>
+        <v>6.55</v>
       </c>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
-        <v>-1.37</v>
+        <v>-3.68</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>OMAXE</t>
+          <t>INA</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>78.56</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="C150" t="n">
-        <v>79.8</v>
+        <v>97</v>
       </c>
       <c r="D150" t="n">
-        <v>1.58</v>
+        <v>0.88</v>
       </c>
       <c r="E150" t="b">
         <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>76.98999999999999</v>
+        <v>95.20999999999999</v>
       </c>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
-        <v>-3.52</v>
+        <v>-1.85</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>NAGAFERT</t>
+          <t>UMAEXPORTS</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>4.43</v>
+        <v>22.8</v>
       </c>
       <c r="C151" t="n">
-        <v>4.5</v>
+        <v>23</v>
       </c>
       <c r="D151" t="n">
-        <v>1.58</v>
+        <v>0.88</v>
       </c>
       <c r="E151" t="b">
         <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>4.45</v>
+        <v>22.77</v>
       </c>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
-        <v>-1.11</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SREEL</t>
+          <t>GLOBALVECT</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>198.68</v>
+        <v>156.69</v>
       </c>
       <c r="C152" t="n">
-        <v>201.8</v>
+        <v>158</v>
       </c>
       <c r="D152" t="n">
-        <v>1.57</v>
+        <v>0.84</v>
       </c>
       <c r="E152" t="b">
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>203.97</v>
+        <v>155.63</v>
       </c>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="n">
-        <v>1.08</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>PRITIKAUTO</t>
+          <t>ANSALAPI</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>12.09</v>
+        <v>3.87</v>
       </c>
       <c r="C153" t="n">
-        <v>12.28</v>
+        <v>3.9</v>
       </c>
       <c r="D153" t="n">
-        <v>1.57</v>
+        <v>0.78</v>
       </c>
       <c r="E153" t="b">
         <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>12.29</v>
+        <v>3.8</v>
       </c>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="n">
-        <v>0.08</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>VCL</t>
+          <t>MRPL</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>1.94</v>
+        <v>206.55</v>
       </c>
       <c r="C154" t="n">
-        <v>1.97</v>
+        <v>208.1</v>
       </c>
       <c r="D154" t="n">
-        <v>1.55</v>
+        <v>0.75</v>
       </c>
       <c r="E154" t="b">
         <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>2</v>
+        <v>191.04</v>
       </c>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="n">
-        <v>1.52</v>
+        <v>-8.199999999999999</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SETL</t>
+          <t>BALPHARMA</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>118.87</v>
+        <v>72.47</v>
       </c>
       <c r="C155" t="n">
-        <v>120.7</v>
+        <v>73</v>
       </c>
       <c r="D155" t="n">
-        <v>1.54</v>
+        <v>0.73</v>
       </c>
       <c r="E155" t="b">
         <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>120.26</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="n">
-        <v>-0.36</v>
+        <v>-6.84</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>BHARATGEAR</t>
+          <t>DEEPINDS</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>102.42</v>
+        <v>337.7</v>
       </c>
       <c r="C156" t="n">
-        <v>104</v>
+        <v>340</v>
       </c>
       <c r="D156" t="n">
-        <v>1.54</v>
+        <v>0.68</v>
       </c>
       <c r="E156" t="b">
         <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>101.05</v>
+        <v>354</v>
       </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="n">
-        <v>-2.84</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>LPDC</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>5.89</v>
+        <v>2471.9</v>
       </c>
       <c r="C157" t="n">
-        <v>5.98</v>
+        <v>2488.4</v>
       </c>
       <c r="D157" t="n">
-        <v>1.53</v>
+        <v>0.67</v>
       </c>
       <c r="E157" t="b">
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>5.96</v>
+        <v>2367.3</v>
       </c>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="n">
-        <v>-0.33</v>
+        <v>-4.87</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>CIFL</t>
+          <t>SOLARINDS</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>30.04</v>
+        <v>15152</v>
       </c>
       <c r="C158" t="n">
-        <v>30.5</v>
+        <v>15250</v>
       </c>
       <c r="D158" t="n">
-        <v>1.53</v>
+        <v>0.65</v>
       </c>
       <c r="E158" t="b">
         <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>30.03</v>
+        <v>14748</v>
       </c>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="n">
-        <v>-1.54</v>
+        <v>-3.29</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CROWN</t>
+          <t>ALANKIT</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>122.63</v>
+        <v>7.95</v>
       </c>
       <c r="C159" t="n">
-        <v>124.49</v>
+        <v>8</v>
       </c>
       <c r="D159" t="n">
-        <v>1.52</v>
+        <v>0.63</v>
       </c>
       <c r="E159" t="b">
         <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>122.42</v>
+        <v>7.72</v>
       </c>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="n">
-        <v>-1.66</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ZIMLAB</t>
+          <t>GFLLIMITED</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>67.95999999999999</v>
+        <v>43.03</v>
       </c>
       <c r="C160" t="n">
-        <v>68.98999999999999</v>
+        <v>43.3</v>
       </c>
       <c r="D160" t="n">
-        <v>1.52</v>
+        <v>0.63</v>
       </c>
       <c r="E160" t="b">
         <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>67.78</v>
+        <v>41.62</v>
       </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="n">
-        <v>-1.75</v>
+        <v>-3.88</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>JAYBARMARU</t>
+          <t>VINDHYATEL</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>96.78</v>
+        <v>1003.8</v>
       </c>
       <c r="C161" t="n">
-        <v>98.25</v>
+        <v>1009.9</v>
       </c>
       <c r="D161" t="n">
-        <v>1.52</v>
+        <v>0.61</v>
       </c>
       <c r="E161" t="b">
         <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>98.01000000000001</v>
+        <v>998</v>
       </c>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="n">
-        <v>-0.24</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>PRABHA</t>
+          <t>CONFIPET</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>167.47</v>
+        <v>29.73</v>
       </c>
       <c r="C162" t="n">
-        <v>170</v>
+        <v>29.91</v>
       </c>
       <c r="D162" t="n">
-        <v>1.51</v>
+        <v>0.61</v>
       </c>
       <c r="E162" t="b">
         <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>165.02</v>
+        <v>28.74</v>
       </c>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="n">
-        <v>-2.93</v>
+        <v>-3.91</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>TINNARUBR</t>
+          <t>SURYODAY</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>654.75</v>
+        <v>129.25</v>
       </c>
       <c r="C163" t="n">
-        <v>664.55</v>
+        <v>130</v>
       </c>
       <c r="D163" t="n">
-        <v>1.5</v>
+        <v>0.58</v>
       </c>
       <c r="E163" t="b">
         <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>661.5</v>
+        <v>129.11</v>
       </c>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="n">
-        <v>-0.46</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>LINC</t>
+          <t>GULFPETRO</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>106.11</v>
+        <v>31.04</v>
       </c>
       <c r="C164" t="n">
-        <v>107.7</v>
+        <v>31.2</v>
       </c>
       <c r="D164" t="n">
-        <v>1.5</v>
+        <v>0.52</v>
       </c>
       <c r="E164" t="b">
         <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>104.92</v>
+        <v>30.85</v>
       </c>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="n">
-        <v>-2.58</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SAMHI</t>
+          <t>ONWARDTEC</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>151.72</v>
+        <v>250.2</v>
       </c>
       <c r="C165" t="n">
-        <v>154</v>
+        <v>251.5</v>
       </c>
       <c r="D165" t="n">
-        <v>1.5</v>
+        <v>0.52</v>
       </c>
       <c r="E165" t="b">
         <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>148.8</v>
+        <v>240.25</v>
       </c>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="n">
-        <v>-3.38</v>
+        <v>-4.47</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SILINV</t>
+          <t>SHREYANIND</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>414</v>
+        <v>150.12</v>
       </c>
       <c r="C166" t="n">
-        <v>420.2</v>
+        <v>150.9</v>
       </c>
       <c r="D166" t="n">
-        <v>1.5</v>
+        <v>0.52</v>
       </c>
       <c r="E166" t="b">
         <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>419</v>
+        <v>148.75</v>
       </c>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="n">
-        <v>-0.29</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>PANACEABIO</t>
+          <t>LEMERITE</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>320.7</v>
+        <v>443.9</v>
       </c>
       <c r="C167" t="n">
-        <v>325.5</v>
+        <v>446.15</v>
       </c>
       <c r="D167" t="n">
-        <v>1.5</v>
+        <v>0.51</v>
       </c>
       <c r="E167" t="b">
         <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>326.3</v>
+        <v>443.65</v>
       </c>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="n">
-        <v>0.25</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>DNAMEDIA</t>
+          <t>CSLFINANCE</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>3.33</v>
+        <v>246.7</v>
       </c>
       <c r="C168" t="n">
-        <v>3.38</v>
+        <v>247.95</v>
       </c>
       <c r="D168" t="n">
-        <v>1.5</v>
+        <v>0.51</v>
       </c>
       <c r="E168" t="b">
         <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>3.45</v>
+        <v>244.9</v>
       </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="n">
-        <v>2.07</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>VENUSREM</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>55.96</v>
+        <v>704.85</v>
       </c>
       <c r="C169" t="n">
-        <v>56.8</v>
+        <v>708.35</v>
       </c>
       <c r="D169" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="E169" t="b">
         <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>56.92</v>
+        <v>690</v>
       </c>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="n">
-        <v>0.21</v>
+        <v>-2.59</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>BLBLIMITED</t>
+          <t>ROSSELLIND</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>17.61</v>
+        <v>46.17</v>
       </c>
       <c r="C170" t="n">
-        <v>17.87</v>
+        <v>46.4</v>
       </c>
       <c r="D170" t="n">
-        <v>1.48</v>
+        <v>0.5</v>
       </c>
       <c r="E170" t="b">
         <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>17.92</v>
+        <v>45.27</v>
       </c>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="n">
-        <v>0.28</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>HPIL</t>
+          <t>SMCGLOBAL</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>123.29</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="C171" t="n">
-        <v>125.1</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D171" t="n">
-        <v>1.47</v>
+        <v>0.5</v>
       </c>
       <c r="E171" t="b">
         <v>0</v>
       </c>
       <c r="F171" t="n">
-        <v>121.01</v>
+        <v>68.5</v>
       </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="n">
-        <v>-3.27</v>
+        <v>-4.99</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>MAHAPEXLTD</t>
+          <t>KHAITANLTD</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>87.70999999999999</v>
+        <v>95.83</v>
       </c>
       <c r="C172" t="n">
-        <v>89</v>
+        <v>96.3</v>
       </c>
       <c r="D172" t="n">
-        <v>1.47</v>
+        <v>0.49</v>
       </c>
       <c r="E172" t="b">
         <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>105.25</v>
+        <v>91.05</v>
       </c>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="n">
-        <v>18.26</v>
+        <v>-5.45</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>KREBSBIO</t>
+          <t>FOODSIN</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>53.22</v>
+        <v>52.59</v>
       </c>
       <c r="C173" t="n">
-        <v>54</v>
+        <v>52.85</v>
       </c>
       <c r="D173" t="n">
-        <v>1.47</v>
+        <v>0.49</v>
       </c>
       <c r="E173" t="b">
         <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>53.01</v>
+        <v>51.58</v>
       </c>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="n">
-        <v>-1.83</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>BIRLACABLE</t>
+          <t>EMAMIREAL</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>142.61</v>
+        <v>61.23</v>
       </c>
       <c r="C174" t="n">
-        <v>144.7</v>
+        <v>61.53</v>
       </c>
       <c r="D174" t="n">
-        <v>1.47</v>
+        <v>0.49</v>
       </c>
       <c r="E174" t="b">
         <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>142.65</v>
+        <v>61.22</v>
       </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="n">
-        <v>-1.42</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>TREL</t>
+          <t>SINDHUTRAD</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>24.44</v>
+        <v>25.12</v>
       </c>
       <c r="C175" t="n">
-        <v>24.8</v>
+        <v>25.24</v>
       </c>
       <c r="D175" t="n">
-        <v>1.47</v>
+        <v>0.48</v>
       </c>
       <c r="E175" t="b">
         <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>24.34</v>
+        <v>24.08</v>
       </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="n">
-        <v>-1.85</v>
+        <v>-4.6</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>BIRLAMONEY</t>
+          <t>SOLEX</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>127.75</v>
+        <v>869.25</v>
       </c>
       <c r="C176" t="n">
-        <v>129.6</v>
+        <v>873.45</v>
       </c>
       <c r="D176" t="n">
-        <v>1.45</v>
+        <v>0.48</v>
       </c>
       <c r="E176" t="b">
         <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>128.28</v>
+        <v>843.25</v>
       </c>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="n">
-        <v>-1.02</v>
+        <v>-3.46</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SIRCA</t>
+          <t>SILLYMONKS</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>452.95</v>
+        <v>17.41</v>
       </c>
       <c r="C177" t="n">
-        <v>459.5</v>
+        <v>17.49</v>
       </c>
       <c r="D177" t="n">
-        <v>1.45</v>
+        <v>0.46</v>
       </c>
       <c r="E177" t="b">
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>455</v>
+        <v>16.65</v>
       </c>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="n">
-        <v>-0.98</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>RAMASTEEL</t>
+          <t>PUSHPA</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>6.19</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="C178" t="n">
-        <v>6.28</v>
+        <v>89</v>
       </c>
       <c r="D178" t="n">
-        <v>1.45</v>
+        <v>0.45</v>
       </c>
       <c r="E178" t="b">
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>6.38</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="n">
-        <v>1.59</v>
+        <v>-8.82</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>HILINFRA</t>
+          <t>INDOWIND</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>52.21</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="C179" t="n">
-        <v>52.96</v>
+        <v>8.99</v>
       </c>
       <c r="D179" t="n">
-        <v>1.44</v>
+        <v>0.45</v>
       </c>
       <c r="E179" t="b">
         <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>51.66</v>
+        <v>8.75</v>
       </c>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="n">
-        <v>-2.45</v>
+        <v>-2.67</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>PAKKA</t>
+          <t>PRAXIS</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>84.81</v>
+        <v>6.62</v>
       </c>
       <c r="C180" t="n">
-        <v>86</v>
+        <v>6.65</v>
       </c>
       <c r="D180" t="n">
-        <v>1.4</v>
+        <v>0.45</v>
       </c>
       <c r="E180" t="b">
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>83.7</v>
+        <v>6.4</v>
       </c>
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="n">
-        <v>-2.67</v>
+        <v>-3.76</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>RADIANTCMS</t>
+          <t>SESHAPAPER</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>36.99</v>
+        <v>259.55</v>
       </c>
       <c r="C181" t="n">
-        <v>37.5</v>
+        <v>260.7</v>
       </c>
       <c r="D181" t="n">
-        <v>1.38</v>
+        <v>0.44</v>
       </c>
       <c r="E181" t="b">
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>36.94</v>
+        <v>257.05</v>
       </c>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="n">
-        <v>-1.49</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>AXITA</t>
+          <t>HESTERBIO</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>8.710000000000001</v>
+        <v>1474.1</v>
       </c>
       <c r="C182" t="n">
-        <v>8.83</v>
+        <v>1480.1</v>
       </c>
       <c r="D182" t="n">
-        <v>1.38</v>
+        <v>0.41</v>
       </c>
       <c r="E182" t="b">
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>8.85</v>
+        <v>1445.6</v>
       </c>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="n">
-        <v>0.23</v>
+        <v>-2.33</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>BIOFILCHEM</t>
+          <t>RVHL</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>30.56</v>
+        <v>38.99</v>
       </c>
       <c r="C183" t="n">
-        <v>30.98</v>
+        <v>39.15</v>
       </c>
       <c r="D183" t="n">
-        <v>1.37</v>
+        <v>0.41</v>
       </c>
       <c r="E183" t="b">
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>30.62</v>
+        <v>38.43</v>
       </c>
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="n">
-        <v>-1.16</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>CAPILLARY</t>
+          <t>ALPA</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>512.8</v>
+        <v>63.45</v>
       </c>
       <c r="C184" t="n">
-        <v>519.8</v>
+        <v>63.7</v>
       </c>
       <c r="D184" t="n">
-        <v>1.37</v>
+        <v>0.39</v>
       </c>
       <c r="E184" t="b">
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>520.5</v>
+        <v>61.65</v>
       </c>
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="n">
-        <v>0.13</v>
+        <v>-3.22</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>BHARATSE</t>
+          <t>DOLPHIN</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>179.46</v>
+        <v>444.3</v>
       </c>
       <c r="C185" t="n">
-        <v>181.88</v>
+        <v>446</v>
       </c>
       <c r="D185" t="n">
-        <v>1.35</v>
+        <v>0.38</v>
       </c>
       <c r="E185" t="b">
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>182.55</v>
+        <v>440.5</v>
       </c>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="n">
-        <v>0.37</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>OSWALAGRO</t>
+          <t>TEXMOPIPES</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>44.31</v>
+        <v>43.69</v>
       </c>
       <c r="C186" t="n">
-        <v>44.9</v>
+        <v>43.85</v>
       </c>
       <c r="D186" t="n">
-        <v>1.33</v>
+        <v>0.37</v>
       </c>
       <c r="E186" t="b">
         <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>45.23</v>
+        <v>41.93</v>
       </c>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="n">
-        <v>0.73</v>
+        <v>-4.38</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>BLUESTONE</t>
+          <t>ASHOKAMET</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>448.25</v>
+        <v>14.03</v>
       </c>
       <c r="C187" t="n">
-        <v>454.2</v>
+        <v>14.08</v>
       </c>
       <c r="D187" t="n">
-        <v>1.33</v>
+        <v>0.36</v>
       </c>
       <c r="E187" t="b">
         <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>442.25</v>
+        <v>14.16</v>
       </c>
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="n">
-        <v>-2.63</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>PREMIERPOL</t>
+          <t>PTL</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>58.72</v>
+        <v>38.12</v>
       </c>
       <c r="C188" t="n">
-        <v>59.5</v>
+        <v>38.25</v>
       </c>
       <c r="D188" t="n">
-        <v>1.33</v>
+        <v>0.34</v>
       </c>
       <c r="E188" t="b">
         <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>58</v>
+        <v>37.12</v>
       </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="n">
-        <v>-2.52</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>DUCON</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>2352.5</v>
+        <v>3.04</v>
       </c>
       <c r="C189" t="n">
-        <v>2383.3</v>
+        <v>3.05</v>
       </c>
       <c r="D189" t="n">
-        <v>1.31</v>
+        <v>0.33</v>
       </c>
       <c r="E189" t="b">
         <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>2509.3</v>
+        <v>2.95</v>
       </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="n">
-        <v>5.29</v>
+        <v>-3.28</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>276.35</v>
+        <v>468.45</v>
       </c>
       <c r="C190" t="n">
-        <v>279.95</v>
+        <v>470</v>
       </c>
       <c r="D190" t="n">
-        <v>1.3</v>
+        <v>0.33</v>
       </c>
       <c r="E190" t="b">
         <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>272.4</v>
+        <v>451.1</v>
       </c>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="n">
-        <v>-2.7</v>
+        <v>-4.02</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>HPAL</t>
+          <t>IFBAGRO</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>34.53</v>
+        <v>767.2</v>
       </c>
       <c r="C191" t="n">
-        <v>34.98</v>
+        <v>769.7</v>
       </c>
       <c r="D191" t="n">
-        <v>1.3</v>
+        <v>0.33</v>
       </c>
       <c r="E191" t="b">
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>34.63</v>
+        <v>728.85</v>
       </c>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="n">
-        <v>-1</v>
+        <v>-5.31</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SUBEXLTD</t>
+          <t>CENTRUM</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>8.539999999999999</v>
+        <v>22.47</v>
       </c>
       <c r="C192" t="n">
-        <v>8.65</v>
+        <v>22.54</v>
       </c>
       <c r="D192" t="n">
-        <v>1.29</v>
+        <v>0.31</v>
       </c>
       <c r="E192" t="b">
         <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>8.66</v>
+        <v>21.47</v>
       </c>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="n">
-        <v>0.12</v>
+        <v>-4.75</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>RCOM</t>
+          <t>KAMATHOTEL</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.78</v>
+        <v>183.91</v>
       </c>
       <c r="C193" t="n">
-        <v>0.79</v>
+        <v>184.47</v>
       </c>
       <c r="D193" t="n">
-        <v>1.28</v>
+        <v>0.3</v>
       </c>
       <c r="E193" t="b">
         <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>0.8100000000000001</v>
+        <v>180.45</v>
       </c>
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="n">
-        <v>2.53</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>JTLIND</t>
+          <t>BAJAJINDEF</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>53.34</v>
+        <v>229.69</v>
       </c>
       <c r="C194" t="n">
-        <v>54</v>
+        <v>230.37</v>
       </c>
       <c r="D194" t="n">
-        <v>1.24</v>
+        <v>0.3</v>
       </c>
       <c r="E194" t="b">
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>53.4</v>
+        <v>219.7</v>
       </c>
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="n">
-        <v>-1.11</v>
+        <v>-4.63</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>MSPL</t>
+          <t>KIRLOSENG</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>31.41</v>
+        <v>1510.5</v>
       </c>
       <c r="C195" t="n">
-        <v>31.8</v>
+        <v>1515</v>
       </c>
       <c r="D195" t="n">
-        <v>1.24</v>
+        <v>0.3</v>
       </c>
       <c r="E195" t="b">
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>31.84</v>
+        <v>1474.6</v>
       </c>
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="n">
-        <v>0.13</v>
+        <v>-2.67</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>VIMTALABS</t>
+          <t>UNIDT</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>439</v>
+        <v>179.85</v>
       </c>
       <c r="C196" t="n">
-        <v>444.4</v>
+        <v>180.38</v>
       </c>
       <c r="D196" t="n">
-        <v>1.23</v>
+        <v>0.29</v>
       </c>
       <c r="E196" t="b">
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>440</v>
+        <v>183.72</v>
       </c>
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="n">
-        <v>-0.99</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>RITCO</t>
+          <t>GGBL</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>204</v>
+        <v>283.2</v>
       </c>
       <c r="C197" t="n">
-        <v>206.5</v>
+        <v>284</v>
       </c>
       <c r="D197" t="n">
-        <v>1.23</v>
+        <v>0.28</v>
       </c>
       <c r="E197" t="b">
         <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>202.25</v>
+        <v>274.9</v>
       </c>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="n">
-        <v>-2.06</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>MAHASTEEL</t>
+          <t>LIBERTSHOE</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>778.5</v>
+        <v>224.4</v>
       </c>
       <c r="C198" t="n">
-        <v>788</v>
+        <v>225</v>
       </c>
       <c r="D198" t="n">
-        <v>1.22</v>
+        <v>0.27</v>
       </c>
       <c r="E198" t="b">
         <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>754.7</v>
+        <v>219.26</v>
       </c>
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="n">
-        <v>-4.23</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SUMMITSEC</t>
+          <t>BRNL</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>1580.3</v>
+        <v>18.4</v>
       </c>
       <c r="C199" t="n">
-        <v>1599.5</v>
+        <v>18.45</v>
       </c>
       <c r="D199" t="n">
-        <v>1.21</v>
+        <v>0.27</v>
       </c>
       <c r="E199" t="b">
         <v>0</v>
       </c>
       <c r="F199" t="n">
-        <v>1587.6</v>
+        <v>18</v>
       </c>
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="n">
-        <v>-0.74</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>TTKHLTCARE</t>
+          <t>SAGCEM</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>860.9</v>
+        <v>186</v>
       </c>
       <c r="C200" t="n">
-        <v>871.2</v>
+        <v>186.49</v>
       </c>
       <c r="D200" t="n">
-        <v>1.2</v>
+        <v>0.26</v>
       </c>
       <c r="E200" t="b">
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>880</v>
+        <v>179.11</v>
       </c>
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="n">
-        <v>1.01</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ASIANTILES</t>
+          <t>MANAKSTEEL</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>68.19</v>
+        <v>56.96</v>
       </c>
       <c r="C201" t="n">
-        <v>68.98999999999999</v>
+        <v>57.1</v>
       </c>
       <c r="D201" t="n">
-        <v>1.17</v>
+        <v>0.25</v>
       </c>
       <c r="E201" t="b">
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>67.62</v>
+        <v>54.52</v>
       </c>
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="n">
-        <v>-1.99</v>
+        <v>-4.52</v>
       </c>
     </row>
   </sheetData>

--- a/data/trending_momentum_stocks.xlsx
+++ b/data/trending_momentum_stocks.xlsx
@@ -461,5193 +461,5193 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LOKESHMACH</t>
+          <t>HILTON-RE2</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>205.61</v>
+        <v>0.2</v>
       </c>
       <c r="C2" t="n">
-        <v>232</v>
+        <v>0.23</v>
       </c>
       <c r="D2" t="n">
-        <v>12.83</v>
+        <v>15</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>209.14</v>
+        <v>0.16</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>-9.85</v>
+        <v>-30.43</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MAHAPEXLTD</t>
+          <t>3PLAND</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>105.25</v>
+        <v>30.31</v>
       </c>
       <c r="C3" t="n">
-        <v>117.89</v>
+        <v>33.99</v>
       </c>
       <c r="D3" t="n">
-        <v>12.01</v>
+        <v>12.14</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>109.06</v>
+        <v>30.85</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>-7.49</v>
+        <v>-9.24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>SUPERSPIN</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>593.3</v>
+        <v>5.22</v>
       </c>
       <c r="C4" t="n">
-        <v>647.95</v>
+        <v>5.8</v>
       </c>
       <c r="D4" t="n">
-        <v>9.210000000000001</v>
+        <v>11.11</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>625.95</v>
+        <v>5.67</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>-3.4</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WEALTH</t>
+          <t>CROWN</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>950.3</v>
+        <v>117.54</v>
       </c>
       <c r="C5" t="n">
-        <v>1034</v>
+        <v>128.2</v>
       </c>
       <c r="D5" t="n">
-        <v>8.81</v>
+        <v>9.07</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>941.15</v>
+        <v>120.98</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>-8.98</v>
+        <v>-5.63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARENTERP</t>
+          <t>SECURKLOUD</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>41.45</v>
+        <v>20.05</v>
       </c>
       <c r="C6" t="n">
-        <v>44.99</v>
+        <v>21.8</v>
       </c>
       <c r="D6" t="n">
-        <v>8.539999999999999</v>
+        <v>8.73</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>40.2</v>
+        <v>21.69</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>-10.65</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HINDOILEXP</t>
+          <t>INFOMEDIA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>156.47</v>
+        <v>5.24</v>
       </c>
       <c r="C7" t="n">
-        <v>169</v>
+        <v>5.69</v>
       </c>
       <c r="D7" t="n">
-        <v>8.01</v>
+        <v>8.59</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>166.46</v>
+        <v>5.07</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>-1.5</v>
+        <v>-10.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ABCOTS</t>
+          <t>GEECEE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>410.4</v>
+        <v>260.8</v>
       </c>
       <c r="C8" t="n">
-        <v>435</v>
+        <v>283</v>
       </c>
       <c r="D8" t="n">
-        <v>5.99</v>
+        <v>8.51</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>411.6</v>
+        <v>286.35</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>-5.38</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EUROBOND</t>
+          <t>AKSHARCHEM</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>161.26</v>
+        <v>191.16</v>
       </c>
       <c r="C9" t="n">
-        <v>170.75</v>
+        <v>207.3</v>
       </c>
       <c r="D9" t="n">
-        <v>5.88</v>
+        <v>8.44</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>156</v>
+        <v>193.24</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>-8.640000000000001</v>
+        <v>-6.78</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BYKE</t>
+          <t>RSYSTEMS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>41.09</v>
+        <v>298.1</v>
       </c>
       <c r="C10" t="n">
-        <v>43.38</v>
+        <v>322.65</v>
       </c>
       <c r="D10" t="n">
-        <v>5.57</v>
+        <v>8.24</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>38.59</v>
+        <v>332.55</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>-11.04</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KRIDHANINF</t>
+          <t>NOIDATOLL</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.84</v>
+        <v>3.61</v>
       </c>
       <c r="C11" t="n">
-        <v>2.99</v>
+        <v>3.9</v>
       </c>
       <c r="D11" t="n">
-        <v>5.28</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2.89</v>
+        <v>3.63</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>-3.34</v>
+        <v>-6.92</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KHANDSE</t>
+          <t>PALASHSECU</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17.87</v>
+        <v>86.22</v>
       </c>
       <c r="C12" t="n">
-        <v>18.79</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>5.15</v>
+        <v>7.86</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>17.9</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>-4.74</v>
+        <v>-4.19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SANWARIA</t>
+          <t>NECCLTD</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>0.21</v>
+        <v>13.99</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>7.62</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.21</v>
+        <v>14.14</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ESFL</t>
+          <t>ARVSMART</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>163.3</v>
+        <v>501.35</v>
       </c>
       <c r="C14" t="n">
-        <v>171.45</v>
+        <v>538.5</v>
       </c>
       <c r="D14" t="n">
-        <v>4.99</v>
+        <v>7.41</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>157.2</v>
+        <v>569</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>-8.31</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NEUEON</t>
+          <t>BIOFILCHEM</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13.11</v>
+        <v>30.1</v>
       </c>
       <c r="C15" t="n">
-        <v>13.76</v>
+        <v>32.25</v>
       </c>
       <c r="D15" t="n">
-        <v>4.96</v>
+        <v>7.14</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>13.76</v>
+        <v>30.97</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>-3.97</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SHANTI</t>
+          <t>JAGSNPHARM</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6.67</v>
+        <v>168.27</v>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>180</v>
       </c>
       <c r="D16" t="n">
-        <v>4.95</v>
+        <v>6.97</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>6.6</v>
+        <v>185.43</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>-5.71</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RCOM</t>
+          <t>MEDICO</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8100000000000001</v>
+        <v>40.25</v>
       </c>
       <c r="C17" t="n">
-        <v>0.85</v>
+        <v>43</v>
       </c>
       <c r="D17" t="n">
-        <v>4.94</v>
+        <v>6.83</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.85</v>
+        <v>40.92</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-4.84</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MAGNUM</t>
+          <t>MITCON</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20.54</v>
+        <v>53.24</v>
       </c>
       <c r="C18" t="n">
-        <v>21.55</v>
+        <v>56.8</v>
       </c>
       <c r="D18" t="n">
-        <v>4.92</v>
+        <v>6.69</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>19.95</v>
+        <v>54.38</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>-7.42</v>
+        <v>-4.26</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AFIL</t>
+          <t>DCI</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.52</v>
+        <v>243.75</v>
       </c>
       <c r="C19" t="n">
-        <v>7.89</v>
+        <v>259.9</v>
       </c>
       <c r="D19" t="n">
-        <v>4.92</v>
+        <v>6.63</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>7.89</v>
+        <v>248.6</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>-4.35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AUSOMENT</t>
+          <t>PILITA</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>98.94</v>
+        <v>7.87</v>
       </c>
       <c r="C20" t="n">
-        <v>103.76</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>4.87</v>
+        <v>6.61</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>95.09999999999999</v>
+        <v>7.94</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>-8.35</v>
+        <v>-5.36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STYL</t>
+          <t>HLVLTD</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>238.26</v>
+        <v>7.46</v>
       </c>
       <c r="C21" t="n">
-        <v>249.8</v>
+        <v>7.95</v>
       </c>
       <c r="D21" t="n">
-        <v>4.84</v>
+        <v>6.57</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>252.15</v>
+        <v>7.6</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.9399999999999999</v>
+        <v>-4.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>INSPIRISYS</t>
+          <t>AVTNPL</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>83</v>
+        <v>60.06</v>
       </c>
       <c r="C22" t="n">
-        <v>86.98999999999999</v>
+        <v>64</v>
       </c>
       <c r="D22" t="n">
-        <v>4.81</v>
+        <v>6.56</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>83.7</v>
+        <v>60.78</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>-3.78</v>
+        <v>-5.03</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FELDVR</t>
+          <t>MIDWESTLTD</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.92</v>
+        <v>1084.3</v>
       </c>
       <c r="C23" t="n">
-        <v>3.06</v>
+        <v>1155.3</v>
       </c>
       <c r="D23" t="n">
-        <v>4.79</v>
+        <v>6.55</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>2.98</v>
+        <v>1138.4</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>-2.61</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SHIVAMAUTO</t>
+          <t>ASHIMASYN</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>18.37</v>
+        <v>14.07</v>
       </c>
       <c r="C24" t="n">
-        <v>19.24</v>
+        <v>14.99</v>
       </c>
       <c r="D24" t="n">
-        <v>4.74</v>
+        <v>6.54</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>17.8</v>
+        <v>14.25</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>-7.48</v>
+        <v>-4.94</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RADIOCITY</t>
+          <t>RAMANEWS</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.91</v>
+        <v>34.56</v>
       </c>
       <c r="C25" t="n">
-        <v>6.19</v>
+        <v>36.8</v>
       </c>
       <c r="D25" t="n">
-        <v>4.74</v>
+        <v>6.48</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>5.8</v>
+        <v>35.41</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>-6.3</v>
+        <v>-3.78</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GOLDSTAR</t>
+          <t>VGL</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>9.5</v>
+        <v>61.08</v>
       </c>
       <c r="C26" t="n">
-        <v>9.949999999999999</v>
+        <v>65</v>
       </c>
       <c r="D26" t="n">
-        <v>4.74</v>
+        <v>6.42</v>
       </c>
       <c r="E26" t="b">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>9.25</v>
+        <v>61.16</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>-7.04</v>
+        <v>-5.91</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>REPL</t>
+          <t>RUDRA</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>82.11</v>
+        <v>16.92</v>
       </c>
       <c r="C27" t="n">
-        <v>85.98999999999999</v>
+        <v>18</v>
       </c>
       <c r="D27" t="n">
-        <v>4.73</v>
+        <v>6.38</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>76.73</v>
+        <v>17.05</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>-10.77</v>
+        <v>-5.28</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BRANDMAN</t>
+          <t>INTENTECH</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>155.65</v>
+        <v>90.72</v>
       </c>
       <c r="C28" t="n">
-        <v>163</v>
+        <v>96.5</v>
       </c>
       <c r="D28" t="n">
-        <v>4.72</v>
+        <v>6.37</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>153</v>
+        <v>92.20999999999999</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>-6.13</v>
+        <v>-4.45</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TECHLABS</t>
+          <t>BASML</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>213.45</v>
+        <v>20.18</v>
       </c>
       <c r="C29" t="n">
-        <v>223.4</v>
+        <v>21.43</v>
       </c>
       <c r="D29" t="n">
-        <v>4.66</v>
+        <v>6.19</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>218</v>
+        <v>20.82</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>-2.42</v>
+        <v>-2.85</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>VCL</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.93</v>
+        <v>9804</v>
       </c>
       <c r="C30" t="n">
-        <v>2.02</v>
+        <v>10399</v>
       </c>
       <c r="D30" t="n">
-        <v>4.66</v>
+        <v>6.07</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>1.92</v>
+        <v>10245</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>-4.95</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GUJRAFFIA</t>
+          <t>MAXIND</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>39.08</v>
+        <v>143.62</v>
       </c>
       <c r="C31" t="n">
-        <v>40.89</v>
+        <v>152.15</v>
       </c>
       <c r="D31" t="n">
-        <v>4.63</v>
+        <v>5.94</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>40.68</v>
+        <v>146.83</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>-0.51</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SUMIT</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>37.48</v>
+        <v>90.17</v>
       </c>
       <c r="C32" t="n">
-        <v>39.2</v>
+        <v>95.48</v>
       </c>
       <c r="D32" t="n">
-        <v>4.59</v>
+        <v>5.89</v>
       </c>
       <c r="E32" t="b">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>36.75</v>
+        <v>92</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>-6.25</v>
+        <v>-3.64</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>VIJIFIN</t>
+          <t>RILINFRA</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.19</v>
+        <v>32.05</v>
       </c>
       <c r="C33" t="n">
-        <v>2.29</v>
+        <v>33.9</v>
       </c>
       <c r="D33" t="n">
-        <v>4.57</v>
+        <v>5.77</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>2.17</v>
+        <v>33.3</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>-5.24</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ZENITHSTL</t>
+          <t>CHAMUNDA</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>5.59</v>
+        <v>43.4</v>
       </c>
       <c r="C34" t="n">
-        <v>5.84</v>
+        <v>45.9</v>
       </c>
       <c r="D34" t="n">
-        <v>4.47</v>
+        <v>5.76</v>
       </c>
       <c r="E34" t="b">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>5.5</v>
+        <v>45.9</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>-5.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RSYSTEMS</t>
+          <t>DRCSYSTEMS</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>258.5</v>
+        <v>13.23</v>
       </c>
       <c r="C35" t="n">
-        <v>269.9</v>
+        <v>13.99</v>
       </c>
       <c r="D35" t="n">
-        <v>4.41</v>
+        <v>5.74</v>
       </c>
       <c r="E35" t="b">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>287.9</v>
+        <v>13.65</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>6.67</v>
+        <v>-2.43</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AAKASH</t>
+          <t>PRITI</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>9.789999999999999</v>
+        <v>35.4</v>
       </c>
       <c r="C36" t="n">
-        <v>10.2</v>
+        <v>37.4</v>
       </c>
       <c r="D36" t="n">
-        <v>4.19</v>
+        <v>5.65</v>
       </c>
       <c r="E36" t="b">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>10.97</v>
+        <v>36.9</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>7.55</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DCXINDIA</t>
+          <t>CYBERTECH</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>190.98</v>
+        <v>102.29</v>
       </c>
       <c r="C37" t="n">
-        <v>198.97</v>
+        <v>107.99</v>
       </c>
       <c r="D37" t="n">
-        <v>4.18</v>
+        <v>5.57</v>
       </c>
       <c r="E37" t="b">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>195.82</v>
+        <v>104.7</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>-1.58</v>
+        <v>-3.05</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LANCORHOL</t>
+          <t>CINEVISTA</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>22.96</v>
+        <v>15.53</v>
       </c>
       <c r="C38" t="n">
-        <v>23.89</v>
+        <v>16.38</v>
       </c>
       <c r="D38" t="n">
-        <v>4.05</v>
+        <v>5.47</v>
       </c>
       <c r="E38" t="b">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>21.82</v>
+        <v>15.9</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>-8.66</v>
+        <v>-2.93</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>WORTHPERI</t>
+          <t>BHARATGEAR</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>132.69</v>
+        <v>96.25</v>
       </c>
       <c r="C39" t="n">
-        <v>138</v>
+        <v>101.5</v>
       </c>
       <c r="D39" t="n">
-        <v>4</v>
+        <v>5.45</v>
       </c>
       <c r="E39" t="b">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>126.95</v>
+        <v>98.17</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>-8.01</v>
+        <v>-3.28</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MAHASTEEL</t>
+          <t>NITIRAJ</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>830.8</v>
+        <v>218.2</v>
       </c>
       <c r="C40" t="n">
-        <v>863.95</v>
+        <v>229.95</v>
       </c>
       <c r="D40" t="n">
-        <v>3.99</v>
+        <v>5.38</v>
       </c>
       <c r="E40" t="b">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>855.9</v>
+        <v>217.12</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>-0.93</v>
+        <v>-5.58</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TIJARIA</t>
+          <t>ACEINTEG</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4.77</v>
+        <v>16.95</v>
       </c>
       <c r="C41" t="n">
-        <v>4.96</v>
+        <v>17.85</v>
       </c>
       <c r="D41" t="n">
-        <v>3.98</v>
+        <v>5.31</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>4.72</v>
+        <v>17.15</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>-4.84</v>
+        <v>-3.92</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NITIRAJ</t>
+          <t>MUNJALSHOW</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>213.7</v>
+        <v>123.39</v>
       </c>
       <c r="C42" t="n">
-        <v>222</v>
+        <v>129.89</v>
       </c>
       <c r="D42" t="n">
-        <v>3.88</v>
+        <v>5.27</v>
       </c>
       <c r="E42" t="b">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>208.55</v>
+        <v>125.67</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>-6.06</v>
+        <v>-3.25</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SWANDEF</t>
+          <t>FILATFASH</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2022.5</v>
+        <v>0.19</v>
       </c>
       <c r="C43" t="n">
-        <v>2100</v>
+        <v>0.2</v>
       </c>
       <c r="D43" t="n">
-        <v>3.83</v>
+        <v>5.26</v>
       </c>
       <c r="E43" t="b">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>2000</v>
+        <v>0.2</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>-4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>SUMIT</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>484.5</v>
+        <v>34.98</v>
       </c>
       <c r="C44" t="n">
-        <v>503</v>
+        <v>36.8</v>
       </c>
       <c r="D44" t="n">
-        <v>3.82</v>
+        <v>5.2</v>
       </c>
       <c r="E44" t="b">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>472.55</v>
+        <v>34.88</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>-6.05</v>
+        <v>-5.22</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PARASPETRO</t>
+          <t>LATTEYS</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.1</v>
+        <v>19.78</v>
       </c>
       <c r="C45" t="n">
-        <v>2.18</v>
+        <v>20.8</v>
       </c>
       <c r="D45" t="n">
-        <v>3.81</v>
+        <v>5.16</v>
       </c>
       <c r="E45" t="b">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>2.13</v>
+        <v>20.25</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>-2.29</v>
+        <v>-2.64</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S&amp;SPOWER</t>
+          <t>JHS</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>331.05</v>
+        <v>8.56</v>
       </c>
       <c r="C46" t="n">
-        <v>343.25</v>
+        <v>9</v>
       </c>
       <c r="D46" t="n">
-        <v>3.69</v>
+        <v>5.14</v>
       </c>
       <c r="E46" t="b">
         <v>0</v>
       </c>
-      <c r="F46" t="inlineStr"/>
+      <c r="F46" t="n">
+        <v>8.99</v>
+      </c>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="H46" t="n">
+        <v>-0.11</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MADHUCON</t>
+          <t>TARACHAND</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4.39</v>
+        <v>57.08</v>
       </c>
       <c r="C47" t="n">
-        <v>4.55</v>
+        <v>59.99</v>
       </c>
       <c r="D47" t="n">
-        <v>3.64</v>
+        <v>5.1</v>
       </c>
       <c r="E47" t="b">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>4.37</v>
+        <v>59</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>-3.96</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TICL</t>
+          <t>KDL</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>24.61</v>
+        <v>126.1</v>
       </c>
       <c r="C48" t="n">
-        <v>25.5</v>
+        <v>132.4</v>
       </c>
       <c r="D48" t="n">
-        <v>3.62</v>
+        <v>5</v>
       </c>
       <c r="E48" t="b">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>24.4</v>
+        <v>132.4</v>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>-4.31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SELMC</t>
+          <t>S&amp;SPOWER</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>30.39</v>
+        <v>347.6</v>
       </c>
       <c r="C49" t="n">
-        <v>31.49</v>
+        <v>364.95</v>
       </c>
       <c r="D49" t="n">
-        <v>3.62</v>
+        <v>4.99</v>
       </c>
       <c r="E49" t="b">
         <v>0</v>
       </c>
-      <c r="F49" t="n">
-        <v>29.11</v>
-      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
-      <c r="H49" t="n">
-        <v>-7.56</v>
-      </c>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>CURAA</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>278.95</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="C50" t="n">
-        <v>289</v>
+        <v>98.88</v>
       </c>
       <c r="D50" t="n">
-        <v>3.6</v>
+        <v>4.99</v>
       </c>
       <c r="E50" t="b">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>273.85</v>
+        <v>98.88</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>-5.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>VINEETLAB</t>
+          <t>TECHLABS</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>30.4</v>
+        <v>223.9</v>
       </c>
       <c r="C51" t="n">
-        <v>31.49</v>
+        <v>235</v>
       </c>
       <c r="D51" t="n">
-        <v>3.59</v>
+        <v>4.96</v>
       </c>
       <c r="E51" t="b">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>28.83</v>
+        <v>235.05</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>-8.449999999999999</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ASHIMASYN</t>
+          <t>SECMARK</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>14.01</v>
+        <v>109.95</v>
       </c>
       <c r="C52" t="n">
-        <v>14.5</v>
+        <v>115.4</v>
       </c>
       <c r="D52" t="n">
-        <v>3.5</v>
+        <v>4.96</v>
       </c>
       <c r="E52" t="b">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>14.3</v>
+        <v>117.9</v>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>-1.38</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>JWL</t>
+          <t>NEUEON</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>298.6</v>
+        <v>13.76</v>
       </c>
       <c r="C53" t="n">
-        <v>309</v>
+        <v>14.44</v>
       </c>
       <c r="D53" t="n">
-        <v>3.48</v>
+        <v>4.94</v>
       </c>
       <c r="E53" t="b">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>291.4</v>
+        <v>14.44</v>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>-5.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SIGIND</t>
+          <t>AFIL</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>45.45</v>
+        <v>7.89</v>
       </c>
       <c r="C54" t="n">
-        <v>46.98</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="D54" t="n">
-        <v>3.37</v>
+        <v>4.94</v>
       </c>
       <c r="E54" t="b">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>44.55</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>-5.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PRAKASHSTL</t>
+          <t>MALLCOM</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4.15</v>
+        <v>1047</v>
       </c>
       <c r="C55" t="n">
-        <v>4.29</v>
+        <v>1098</v>
       </c>
       <c r="D55" t="n">
-        <v>3.37</v>
+        <v>4.87</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>4.08</v>
+        <v>1065.2</v>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>-4.9</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MODTHREAD</t>
+          <t>VIVIMEDLAB</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>52.06</v>
+        <v>6.79</v>
       </c>
       <c r="C56" t="n">
-        <v>53.62</v>
+        <v>7.12</v>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>4.86</v>
       </c>
       <c r="E56" t="b">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>51.74</v>
+        <v>6.81</v>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>-3.51</v>
+        <v>-4.35</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MAITREYA</t>
+          <t>DGCONTENT</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>219.05</v>
+        <v>24.32</v>
       </c>
       <c r="C57" t="n">
-        <v>225.5</v>
+        <v>25.5</v>
       </c>
       <c r="D57" t="n">
-        <v>2.94</v>
+        <v>4.85</v>
       </c>
       <c r="E57" t="b">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>217.95</v>
+        <v>24.27</v>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>-3.35</v>
+        <v>-4.82</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>HCL-INSYS</t>
+          <t>IMPEXFERRO</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>12.51</v>
+        <v>1.66</v>
       </c>
       <c r="C58" t="n">
-        <v>12.87</v>
+        <v>1.74</v>
       </c>
       <c r="D58" t="n">
-        <v>2.88</v>
+        <v>4.82</v>
       </c>
       <c r="E58" t="b">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>12.32</v>
+        <v>1.68</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>-4.27</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NOIDATOLL</t>
+          <t>MAHAPEXLTD</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3.87</v>
+        <v>107.62</v>
       </c>
       <c r="C59" t="n">
-        <v>3.98</v>
+        <v>112.8</v>
       </c>
       <c r="D59" t="n">
-        <v>2.84</v>
+        <v>4.81</v>
       </c>
       <c r="E59" t="b">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>3.66</v>
+        <v>107.99</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>-8.039999999999999</v>
+        <v>-4.26</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>GVPTECH</t>
+          <t>VIJIFIN</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>6.52</v>
+        <v>2.29</v>
       </c>
       <c r="C60" t="n">
-        <v>6.7</v>
+        <v>2.4</v>
       </c>
       <c r="D60" t="n">
-        <v>2.76</v>
+        <v>4.8</v>
       </c>
       <c r="E60" t="b">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>6.27</v>
+        <v>2.36</v>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>-6.42</v>
+        <v>-1.67</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TREJHARA</t>
+          <t>SANGINITA</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>175.21</v>
+        <v>12.37</v>
       </c>
       <c r="C61" t="n">
-        <v>179.98</v>
+        <v>12.96</v>
       </c>
       <c r="D61" t="n">
-        <v>2.72</v>
+        <v>4.77</v>
       </c>
       <c r="E61" t="b">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>170</v>
+        <v>12.4</v>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>-5.55</v>
+        <v>-4.32</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ABAN</t>
+          <t>EUROTEXIND</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>22.3</v>
+        <v>13.27</v>
       </c>
       <c r="C62" t="n">
-        <v>22.9</v>
+        <v>13.9</v>
       </c>
       <c r="D62" t="n">
-        <v>2.69</v>
+        <v>4.75</v>
       </c>
       <c r="E62" t="b">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>23.41</v>
+        <v>12.62</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>2.23</v>
+        <v>-9.210000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STEL</t>
+          <t>BLBLIMITED</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>524.65</v>
+        <v>17.28</v>
       </c>
       <c r="C63" t="n">
-        <v>538.7</v>
+        <v>18.1</v>
       </c>
       <c r="D63" t="n">
-        <v>2.68</v>
+        <v>4.75</v>
       </c>
       <c r="E63" t="b">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>534.8</v>
+        <v>17.62</v>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>-0.72</v>
+        <v>-2.65</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TVVISION</t>
+          <t>CAPTRUST</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>5.65</v>
+        <v>12.02</v>
       </c>
       <c r="C64" t="n">
-        <v>5.8</v>
+        <v>12.59</v>
       </c>
       <c r="D64" t="n">
-        <v>2.65</v>
+        <v>4.74</v>
       </c>
       <c r="E64" t="b">
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>5.64</v>
+        <v>12.11</v>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>-2.76</v>
+        <v>-3.81</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>VHLTD</t>
+          <t>JAIPURKURT</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>149.09</v>
+        <v>29.55</v>
       </c>
       <c r="C65" t="n">
-        <v>153</v>
+        <v>30.95</v>
       </c>
       <c r="D65" t="n">
-        <v>2.62</v>
+        <v>4.74</v>
       </c>
       <c r="E65" t="b">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>146</v>
+        <v>31.37</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>-4.58</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SIKKO</t>
+          <t>DELAPLEX</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>4.63</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="C66" t="n">
-        <v>4.75</v>
+        <v>102</v>
       </c>
       <c r="D66" t="n">
-        <v>2.59</v>
+        <v>4.72</v>
       </c>
       <c r="E66" t="b">
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>4.56</v>
+        <v>107</v>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>-4</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SAURASHCEM</t>
+          <t>FELDVR</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>62.59</v>
+        <v>2.97</v>
       </c>
       <c r="C67" t="n">
-        <v>64.2</v>
+        <v>3.11</v>
       </c>
       <c r="D67" t="n">
-        <v>2.57</v>
+        <v>4.71</v>
       </c>
       <c r="E67" t="b">
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>60.15</v>
+        <v>2.83</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>-6.31</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>JINDRILL</t>
+          <t>MAHESHWARI</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>542.2</v>
+        <v>42</v>
       </c>
       <c r="C68" t="n">
-        <v>556</v>
+        <v>43.98</v>
       </c>
       <c r="D68" t="n">
-        <v>2.55</v>
+        <v>4.71</v>
       </c>
       <c r="E68" t="b">
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>565.9</v>
+        <v>41.68</v>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>1.78</v>
+        <v>-5.23</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ASIANHOTNR</t>
+          <t>CELEBRITY</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>292.65</v>
+        <v>7.48</v>
       </c>
       <c r="C69" t="n">
-        <v>299.95</v>
+        <v>7.83</v>
       </c>
       <c r="D69" t="n">
-        <v>2.49</v>
+        <v>4.68</v>
       </c>
       <c r="E69" t="b">
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>289.05</v>
+        <v>7.5</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>-3.63</v>
+        <v>-4.21</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ORCHASP</t>
+          <t>PARIN</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2.43</v>
+        <v>687.95</v>
       </c>
       <c r="C70" t="n">
-        <v>2.49</v>
+        <v>720</v>
       </c>
       <c r="D70" t="n">
-        <v>2.47</v>
+        <v>4.66</v>
       </c>
       <c r="E70" t="b">
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>2.33</v>
+        <v>720</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>-6.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>TRACXN</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>413.6</v>
+        <v>33.14</v>
       </c>
       <c r="C71" t="n">
-        <v>423.7</v>
+        <v>34.67</v>
       </c>
       <c r="D71" t="n">
-        <v>2.44</v>
+        <v>4.62</v>
       </c>
       <c r="E71" t="b">
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>408.3</v>
+        <v>33.92</v>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>-3.63</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BLUECOAST</t>
+          <t>RKSWAMY</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>20.93</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="C72" t="n">
-        <v>21.44</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D72" t="n">
-        <v>2.44</v>
+        <v>4.6</v>
       </c>
       <c r="E72" t="b">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>20.5</v>
+        <v>96.92</v>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>-4.38</v>
+        <v>-2.98</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FEL</t>
+          <t>MANOMAY</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.42</v>
+        <v>214</v>
       </c>
       <c r="C73" t="n">
-        <v>0.43</v>
+        <v>223.8</v>
       </c>
       <c r="D73" t="n">
-        <v>2.38</v>
+        <v>4.58</v>
       </c>
       <c r="E73" t="b">
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>0.41</v>
+        <v>217</v>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>-4.65</v>
+        <v>-3.04</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SIGMAADV</t>
+          <t>GATECHDVR</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>160.13</v>
+        <v>0.44</v>
       </c>
       <c r="C74" t="n">
-        <v>163.9</v>
+        <v>0.46</v>
       </c>
       <c r="D74" t="n">
-        <v>2.35</v>
+        <v>4.55</v>
       </c>
       <c r="E74" t="b">
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>154.43</v>
+        <v>0.45</v>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>-5.78</v>
+        <v>-2.17</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DNAMEDIA</t>
+          <t>PRITIKAUTO</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>3.41</v>
+        <v>12.32</v>
       </c>
       <c r="C75" t="n">
-        <v>3.49</v>
+        <v>12.88</v>
       </c>
       <c r="D75" t="n">
-        <v>2.35</v>
+        <v>4.55</v>
       </c>
       <c r="E75" t="b">
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>3.36</v>
+        <v>12.7</v>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>-3.72</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>IITL</t>
+          <t>TCIFINANCE</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>131.93</v>
+        <v>13.68</v>
       </c>
       <c r="C76" t="n">
-        <v>134.93</v>
+        <v>14.3</v>
       </c>
       <c r="D76" t="n">
-        <v>2.27</v>
+        <v>4.53</v>
       </c>
       <c r="E76" t="b">
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>123.48</v>
+        <v>14.09</v>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>-8.49</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>GATECH</t>
+          <t>BHARATSE</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.46</v>
+        <v>170.69</v>
       </c>
       <c r="C77" t="n">
-        <v>0.47</v>
+        <v>178.37</v>
       </c>
       <c r="D77" t="n">
-        <v>2.17</v>
+        <v>4.5</v>
       </c>
       <c r="E77" t="b">
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>0.46</v>
+        <v>175.01</v>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>-2.13</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ZEELEARN</t>
+          <t>MTARTECH</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>5.57</v>
+        <v>3613.2</v>
       </c>
       <c r="C78" t="n">
-        <v>5.69</v>
+        <v>3775.6</v>
       </c>
       <c r="D78" t="n">
-        <v>2.15</v>
+        <v>4.49</v>
       </c>
       <c r="E78" t="b">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>5.4</v>
+        <v>3723.4</v>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>-5.1</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GATECHDVR</t>
+          <t>GUJRAFFIA</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.47</v>
+        <v>39.48</v>
       </c>
       <c r="C79" t="n">
-        <v>0.48</v>
+        <v>41.25</v>
       </c>
       <c r="D79" t="n">
-        <v>2.13</v>
+        <v>4.48</v>
       </c>
       <c r="E79" t="b">
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>0.43</v>
+        <v>39.03</v>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>-10.42</v>
+        <v>-5.38</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AVONMORE</t>
+          <t>CINELINE</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>14.1</v>
+        <v>85.94</v>
       </c>
       <c r="C80" t="n">
-        <v>14.4</v>
+        <v>89.77</v>
       </c>
       <c r="D80" t="n">
-        <v>2.13</v>
+        <v>4.46</v>
       </c>
       <c r="E80" t="b">
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>13.88</v>
+        <v>88</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>-3.61</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BGLOBAL</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2.84</v>
+        <v>174.24</v>
       </c>
       <c r="C81" t="n">
-        <v>2.9</v>
+        <v>182</v>
       </c>
       <c r="D81" t="n">
-        <v>2.11</v>
+        <v>4.45</v>
       </c>
       <c r="E81" t="b">
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>2.92</v>
+        <v>177.77</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>0.6899999999999999</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>RAJMET</t>
+          <t>5PAISA</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3.81</v>
+        <v>296.8</v>
       </c>
       <c r="C82" t="n">
-        <v>3.89</v>
+        <v>310</v>
       </c>
       <c r="D82" t="n">
-        <v>2.1</v>
+        <v>4.45</v>
       </c>
       <c r="E82" t="b">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>3.76</v>
+        <v>302</v>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>-3.34</v>
+        <v>-2.58</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>KAUSHALYA</t>
+          <t>TREJHARA</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>842.4</v>
+        <v>166.58</v>
       </c>
       <c r="C83" t="n">
-        <v>860</v>
+        <v>173.98</v>
       </c>
       <c r="D83" t="n">
-        <v>2.09</v>
+        <v>4.44</v>
       </c>
       <c r="E83" t="b">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>829</v>
+        <v>171.14</v>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>-3.6</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MTEDUCARE</t>
+          <t>GTL</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1.47</v>
+        <v>6.55</v>
       </c>
       <c r="C84" t="n">
-        <v>1.5</v>
+        <v>6.84</v>
       </c>
       <c r="D84" t="n">
-        <v>2.04</v>
+        <v>4.43</v>
       </c>
       <c r="E84" t="b">
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>1.47</v>
+        <v>6.66</v>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>-2</v>
+        <v>-2.63</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ORTEL</t>
+          <t>DCMNVL</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1.48</v>
+        <v>121.36</v>
       </c>
       <c r="C85" t="n">
-        <v>1.51</v>
+        <v>126.7</v>
       </c>
       <c r="D85" t="n">
-        <v>2.03</v>
+        <v>4.4</v>
       </c>
       <c r="E85" t="b">
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>1.5</v>
+        <v>122.99</v>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>-0.66</v>
+        <v>-2.93</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ROML</t>
+          <t>MIRCELECTR</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>44.98</v>
+        <v>23.87</v>
       </c>
       <c r="C86" t="n">
-        <v>45.89</v>
+        <v>24.92</v>
       </c>
       <c r="D86" t="n">
-        <v>2.02</v>
+        <v>4.4</v>
       </c>
       <c r="E86" t="b">
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>44.41</v>
+        <v>24.97</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>-3.23</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DICIND</t>
+          <t>CHEMBONDCH</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>524.45</v>
+        <v>133.95</v>
       </c>
       <c r="C87" t="n">
-        <v>535</v>
+        <v>139.8</v>
       </c>
       <c r="D87" t="n">
-        <v>2.01</v>
+        <v>4.37</v>
       </c>
       <c r="E87" t="b">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>519.7</v>
+        <v>134.01</v>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>-2.86</v>
+        <v>-4.14</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SBGLP</t>
+          <t>TOLINS</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>28.36</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="C88" t="n">
-        <v>28.93</v>
+        <v>102.98</v>
       </c>
       <c r="D88" t="n">
-        <v>2.01</v>
+        <v>4.33</v>
       </c>
       <c r="E88" t="b">
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>27.72</v>
+        <v>100.64</v>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>-4.18</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>TEJASNET</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>749.35</v>
+        <v>426.1</v>
       </c>
       <c r="C89" t="n">
-        <v>764.35</v>
+        <v>444.4</v>
       </c>
       <c r="D89" t="n">
-        <v>2</v>
+        <v>4.29</v>
       </c>
       <c r="E89" t="b">
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>717.15</v>
+        <v>458.95</v>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>-6.18</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>JMA</t>
+          <t>AVROIND</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>84.67</v>
+        <v>127.54</v>
       </c>
       <c r="C90" t="n">
-        <v>86.36</v>
+        <v>132.99</v>
       </c>
       <c r="D90" t="n">
-        <v>2</v>
+        <v>4.27</v>
       </c>
       <c r="E90" t="b">
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>84</v>
+        <v>133.33</v>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>-2.73</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>RAJRILTD</t>
+          <t>INDOAMIN</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>22.84</v>
+        <v>97.44</v>
       </c>
       <c r="C91" t="n">
-        <v>23.29</v>
+        <v>101.6</v>
       </c>
       <c r="D91" t="n">
-        <v>1.97</v>
+        <v>4.27</v>
       </c>
       <c r="E91" t="b">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>22.4</v>
+        <v>100.64</v>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>-3.82</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SMARTLINK</t>
+          <t>SMLT</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>120.14</v>
+        <v>68.48</v>
       </c>
       <c r="C92" t="n">
-        <v>122.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="D92" t="n">
-        <v>1.96</v>
+        <v>4.26</v>
       </c>
       <c r="E92" t="b">
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>117.2</v>
+        <v>70.87</v>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
-        <v>-4.33</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SOLARA</t>
+          <t>KNAGRI</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>459.05</v>
+        <v>178.16</v>
       </c>
       <c r="C93" t="n">
-        <v>467.95</v>
+        <v>185.7</v>
       </c>
       <c r="D93" t="n">
-        <v>1.94</v>
+        <v>4.23</v>
       </c>
       <c r="E93" t="b">
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>444.3</v>
+        <v>182.96</v>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
-        <v>-5.05</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SURANASOL</t>
+          <t>RUBYMILLS</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>22.26</v>
+        <v>205.29</v>
       </c>
       <c r="C94" t="n">
-        <v>22.69</v>
+        <v>213.88</v>
       </c>
       <c r="D94" t="n">
-        <v>1.93</v>
+        <v>4.18</v>
       </c>
       <c r="E94" t="b">
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>21.23</v>
+        <v>208.9</v>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>-6.43</v>
+        <v>-2.33</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SCPL</t>
+          <t>JPOLYINVST</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>325.75</v>
+        <v>1315</v>
       </c>
       <c r="C95" t="n">
-        <v>332</v>
+        <v>1369.7</v>
       </c>
       <c r="D95" t="n">
-        <v>1.92</v>
+        <v>4.16</v>
       </c>
       <c r="E95" t="b">
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>318.9</v>
+        <v>1406.8</v>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>-3.95</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>VIVIDHA</t>
+          <t>VAISHALI</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.52</v>
+        <v>6.51</v>
       </c>
       <c r="C96" t="n">
-        <v>0.53</v>
+        <v>6.78</v>
       </c>
       <c r="D96" t="n">
-        <v>1.92</v>
+        <v>4.15</v>
       </c>
       <c r="E96" t="b">
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>0.54</v>
+        <v>6.58</v>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>1.89</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>GSS</t>
+          <t>MINDACORP</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>13.09</v>
+        <v>497.65</v>
       </c>
       <c r="C97" t="n">
-        <v>13.34</v>
+        <v>518</v>
       </c>
       <c r="D97" t="n">
-        <v>1.91</v>
+        <v>4.09</v>
       </c>
       <c r="E97" t="b">
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>13</v>
+        <v>509.55</v>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>-2.55</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SADBHIN</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>3.18</v>
+        <v>4236.7</v>
       </c>
       <c r="C98" t="n">
-        <v>3.24</v>
+        <v>4410</v>
       </c>
       <c r="D98" t="n">
-        <v>1.89</v>
+        <v>4.09</v>
       </c>
       <c r="E98" t="b">
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>3.17</v>
+        <v>4374</v>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>-2.16</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>VISASTEEL</t>
+          <t>MANGALAM</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>36.2</v>
+        <v>33.87</v>
       </c>
       <c r="C99" t="n">
-        <v>36.88</v>
+        <v>35.25</v>
       </c>
       <c r="D99" t="n">
-        <v>1.88</v>
+        <v>4.07</v>
       </c>
       <c r="E99" t="b">
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>34.8</v>
+        <v>33.1</v>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
-        <v>-5.64</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>RUDRA</t>
+          <t>IZMO</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>17.76</v>
+        <v>711.2</v>
       </c>
       <c r="C100" t="n">
-        <v>18.09</v>
+        <v>740</v>
       </c>
       <c r="D100" t="n">
-        <v>1.86</v>
+        <v>4.05</v>
       </c>
       <c r="E100" t="b">
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>16.98</v>
+        <v>745.8</v>
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>-6.14</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>TPHQ</t>
+          <t>UNIVASTU</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.55</v>
+        <v>61.85</v>
       </c>
       <c r="C101" t="n">
-        <v>0.5600000000000001</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="D101" t="n">
-        <v>1.82</v>
+        <v>4.04</v>
       </c>
       <c r="E101" t="b">
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>0.5600000000000001</v>
+        <v>62.66</v>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>0</v>
+        <v>-2.63</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AMJLAND</t>
+          <t>MCLEODRUSS</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>38.42</v>
+        <v>36.44</v>
       </c>
       <c r="C102" t="n">
-        <v>39.1</v>
+        <v>37.9</v>
       </c>
       <c r="D102" t="n">
-        <v>1.77</v>
+        <v>4.01</v>
       </c>
       <c r="E102" t="b">
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>38.44</v>
+        <v>40.08</v>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>-1.69</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>RKDL</t>
+          <t>KRYSTAL</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>20.55</v>
+        <v>577.05</v>
       </c>
       <c r="C103" t="n">
-        <v>20.9</v>
+        <v>600.05</v>
       </c>
       <c r="D103" t="n">
-        <v>1.7</v>
+        <v>3.99</v>
       </c>
       <c r="E103" t="b">
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>19.48</v>
+        <v>604.7</v>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>-6.79</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DPEL</t>
+          <t>ISFT</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>290.1</v>
+        <v>67.33</v>
       </c>
       <c r="C104" t="n">
-        <v>295</v>
+        <v>70</v>
       </c>
       <c r="D104" t="n">
-        <v>1.69</v>
+        <v>3.97</v>
       </c>
       <c r="E104" t="b">
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>276.25</v>
+        <v>67.72</v>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
-        <v>-6.36</v>
+        <v>-3.26</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MHLXMIRU</t>
+          <t>SUVIDHAA</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>170.07</v>
+        <v>2.78</v>
       </c>
       <c r="C105" t="n">
-        <v>172.9</v>
+        <v>2.89</v>
       </c>
       <c r="D105" t="n">
-        <v>1.66</v>
+        <v>3.96</v>
       </c>
       <c r="E105" t="b">
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>169.99</v>
+        <v>2.81</v>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>-1.68</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>DANGEE</t>
+          <t>REPRO</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>3.02</v>
+        <v>379.8</v>
       </c>
       <c r="C106" t="n">
-        <v>3.07</v>
+        <v>394.85</v>
       </c>
       <c r="D106" t="n">
-        <v>1.66</v>
+        <v>3.96</v>
       </c>
       <c r="E106" t="b">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>3.01</v>
+        <v>382.6</v>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
-        <v>-1.95</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SPCENET</t>
+          <t>GICL</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>4.28</v>
+        <v>44.96</v>
       </c>
       <c r="C107" t="n">
-        <v>4.35</v>
+        <v>46.74</v>
       </c>
       <c r="D107" t="n">
-        <v>1.64</v>
+        <v>3.96</v>
       </c>
       <c r="E107" t="b">
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>4.09</v>
+        <v>45</v>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>-5.98</v>
+        <v>-3.72</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SHAREINDIA</t>
+          <t>KAPSTON</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>131.99</v>
+        <v>291.5</v>
       </c>
       <c r="C108" t="n">
-        <v>134.01</v>
+        <v>303</v>
       </c>
       <c r="D108" t="n">
-        <v>1.53</v>
+        <v>3.95</v>
       </c>
       <c r="E108" t="b">
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>127.15</v>
+        <v>285.3</v>
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
-        <v>-5.12</v>
+        <v>-5.84</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>KOHINOOR</t>
+          <t>ASPINWALL</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>25.61</v>
+        <v>209.77</v>
       </c>
       <c r="C109" t="n">
-        <v>26</v>
+        <v>218</v>
       </c>
       <c r="D109" t="n">
-        <v>1.52</v>
+        <v>3.92</v>
       </c>
       <c r="E109" t="b">
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>24.89</v>
+        <v>209.27</v>
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>-4.27</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>OMINFRAL</t>
+          <t>MOKSH</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>80.29000000000001</v>
+        <v>11.52</v>
       </c>
       <c r="C110" t="n">
-        <v>81.5</v>
+        <v>11.97</v>
       </c>
       <c r="D110" t="n">
-        <v>1.51</v>
+        <v>3.91</v>
       </c>
       <c r="E110" t="b">
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>77.45</v>
+        <v>11.7</v>
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
-        <v>-4.97</v>
+        <v>-2.26</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AIRAN</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>16.01</v>
+        <v>294.4</v>
       </c>
       <c r="C111" t="n">
-        <v>16.25</v>
+        <v>305.9</v>
       </c>
       <c r="D111" t="n">
-        <v>1.5</v>
+        <v>3.91</v>
       </c>
       <c r="E111" t="b">
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>15.55</v>
+        <v>304.6</v>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>-4.31</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>GVKPIL</t>
+          <t>SOUTHWEST</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>2.69</v>
+        <v>197.23</v>
       </c>
       <c r="C112" t="n">
-        <v>2.73</v>
+        <v>204.9</v>
       </c>
       <c r="D112" t="n">
-        <v>1.49</v>
+        <v>3.89</v>
       </c>
       <c r="E112" t="b">
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>2.64</v>
+        <v>199</v>
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
-        <v>-3.3</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>NELCAST</t>
+          <t>SAMBHV</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>114.59</v>
+        <v>89.52</v>
       </c>
       <c r="C113" t="n">
-        <v>116.3</v>
+        <v>93</v>
       </c>
       <c r="D113" t="n">
-        <v>1.49</v>
+        <v>3.89</v>
       </c>
       <c r="E113" t="b">
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>111.67</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>-3.98</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MBLINFRA</t>
+          <t>ANTGRAPHIC</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>25.61</v>
+        <v>0.78</v>
       </c>
       <c r="C114" t="n">
-        <v>25.99</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D114" t="n">
-        <v>1.48</v>
+        <v>3.85</v>
       </c>
       <c r="E114" t="b">
         <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>24.6</v>
+        <v>0.79</v>
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
-        <v>-5.35</v>
+        <v>-2.47</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>KRITINUT</t>
+          <t>BAGFILMS</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>65.05</v>
+        <v>4.94</v>
       </c>
       <c r="C115" t="n">
-        <v>66</v>
+        <v>5.13</v>
       </c>
       <c r="D115" t="n">
-        <v>1.46</v>
+        <v>3.85</v>
       </c>
       <c r="E115" t="b">
         <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>61.5</v>
+        <v>5.13</v>
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>-6.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SURANAT&amp;P</t>
+          <t>WILLAMAGOR</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>17.24</v>
+        <v>26</v>
       </c>
       <c r="C116" t="n">
-        <v>17.49</v>
+        <v>27</v>
       </c>
       <c r="D116" t="n">
-        <v>1.45</v>
+        <v>3.85</v>
       </c>
       <c r="E116" t="b">
         <v>0</v>
       </c>
-      <c r="F116" t="inlineStr"/>
+      <c r="F116" t="n">
+        <v>26.75</v>
+      </c>
       <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
+      <c r="H116" t="n">
+        <v>-0.93</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>COUNCODOS</t>
+          <t>VIVIDHA</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>4.91</v>
+        <v>0.52</v>
       </c>
       <c r="C117" t="n">
-        <v>4.98</v>
+        <v>0.54</v>
       </c>
       <c r="D117" t="n">
-        <v>1.43</v>
+        <v>3.85</v>
       </c>
       <c r="E117" t="b">
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>4.9</v>
+        <v>0.52</v>
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>-1.61</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>HINDCOMPOS</t>
+          <t>TREL</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>414.05</v>
+        <v>24.03</v>
       </c>
       <c r="C118" t="n">
-        <v>419.9</v>
+        <v>24.95</v>
       </c>
       <c r="D118" t="n">
-        <v>1.41</v>
+        <v>3.83</v>
       </c>
       <c r="E118" t="b">
         <v>0</v>
       </c>
       <c r="F118" t="n">
-        <v>403.95</v>
+        <v>25.05</v>
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
-        <v>-3.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>KDL</t>
+          <t>PLAZACABLE</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>120.1</v>
+        <v>35.52</v>
       </c>
       <c r="C119" t="n">
-        <v>121.7</v>
+        <v>36.88</v>
       </c>
       <c r="D119" t="n">
-        <v>1.33</v>
+        <v>3.83</v>
       </c>
       <c r="E119" t="b">
         <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>122.5</v>
+        <v>35.32</v>
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
-        <v>0.66</v>
+        <v>-4.23</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SPLPETRO</t>
+          <t>STYL</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>669.2</v>
+        <v>260.07</v>
       </c>
       <c r="C120" t="n">
-        <v>678</v>
+        <v>269.99</v>
       </c>
       <c r="D120" t="n">
-        <v>1.32</v>
+        <v>3.81</v>
       </c>
       <c r="E120" t="b">
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>662.4</v>
+        <v>267.4</v>
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
-        <v>-2.3</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>DRONE</t>
+          <t>SILGO</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>47.35</v>
+        <v>71.3</v>
       </c>
       <c r="C121" t="n">
-        <v>47.95</v>
+        <v>74</v>
       </c>
       <c r="D121" t="n">
-        <v>1.27</v>
+        <v>3.79</v>
       </c>
       <c r="E121" t="b">
         <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>46.25</v>
+        <v>76.5</v>
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
-        <v>-3.55</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>RSSOFTWARE</t>
+          <t>RANASUG</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>32.49</v>
+        <v>11.9</v>
       </c>
       <c r="C122" t="n">
-        <v>32.9</v>
+        <v>12.35</v>
       </c>
       <c r="D122" t="n">
-        <v>1.26</v>
+        <v>3.78</v>
       </c>
       <c r="E122" t="b">
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>31.82</v>
+        <v>12.11</v>
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
-        <v>-3.28</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>AXITA</t>
+          <t>CONSOFINVT</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>8.85</v>
+        <v>227.36</v>
       </c>
       <c r="C123" t="n">
-        <v>8.960000000000001</v>
+        <v>235.95</v>
       </c>
       <c r="D123" t="n">
-        <v>1.24</v>
+        <v>3.78</v>
       </c>
       <c r="E123" t="b">
         <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>8.65</v>
+        <v>227.01</v>
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>-3.46</v>
+        <v>-3.79</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CHENNPETRO</t>
+          <t>PRABHA</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1007.5</v>
+        <v>151.78</v>
       </c>
       <c r="C124" t="n">
-        <v>1020</v>
+        <v>157.5</v>
       </c>
       <c r="D124" t="n">
-        <v>1.24</v>
+        <v>3.77</v>
       </c>
       <c r="E124" t="b">
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>948.85</v>
+        <v>151</v>
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
-        <v>-6.98</v>
+        <v>-4.13</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ANTGRAPHIC</t>
+          <t>SUVEN</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.8100000000000001</v>
+        <v>135.88</v>
       </c>
       <c r="C125" t="n">
-        <v>0.82</v>
+        <v>140.99</v>
       </c>
       <c r="D125" t="n">
-        <v>1.23</v>
+        <v>3.76</v>
       </c>
       <c r="E125" t="b">
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>0.79</v>
+        <v>137.89</v>
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>-3.66</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>UNITEDPOLY</t>
+          <t>KARMAENG</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>25.5</v>
+        <v>37.3</v>
       </c>
       <c r="C126" t="n">
-        <v>25.8</v>
+        <v>38.7</v>
       </c>
       <c r="D126" t="n">
-        <v>1.18</v>
+        <v>3.75</v>
       </c>
       <c r="E126" t="b">
         <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>24.9</v>
+        <v>38.8</v>
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
-        <v>-3.49</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>INDUSINVIT</t>
+          <t>MURUDCERA</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>123.21</v>
+        <v>30.65</v>
       </c>
       <c r="C127" t="n">
-        <v>124.67</v>
+        <v>31.8</v>
       </c>
       <c r="D127" t="n">
-        <v>1.18</v>
+        <v>3.75</v>
       </c>
       <c r="E127" t="b">
         <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>121.78</v>
+        <v>31.6</v>
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
-        <v>-2.32</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SUMEETINDS</t>
+          <t>VALIANTLAB</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>30.64</v>
+        <v>55.77</v>
       </c>
       <c r="C128" t="n">
-        <v>31</v>
+        <v>57.85</v>
       </c>
       <c r="D128" t="n">
-        <v>1.17</v>
+        <v>3.73</v>
       </c>
       <c r="E128" t="b">
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>29.61</v>
+        <v>55.01</v>
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
-        <v>-4.48</v>
+        <v>-4.91</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>LASA</t>
+          <t>HMAAGRO</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>7.89</v>
+        <v>24.11</v>
       </c>
       <c r="C129" t="n">
-        <v>7.98</v>
+        <v>25</v>
       </c>
       <c r="D129" t="n">
-        <v>1.14</v>
+        <v>3.69</v>
       </c>
       <c r="E129" t="b">
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>7.74</v>
+        <v>24.45</v>
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
-        <v>-3.01</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ALPHAGEO</t>
+          <t>KRITINUT</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>202.75</v>
+        <v>61.63</v>
       </c>
       <c r="C130" t="n">
-        <v>205</v>
+        <v>63.9</v>
       </c>
       <c r="D130" t="n">
-        <v>1.11</v>
+        <v>3.68</v>
       </c>
       <c r="E130" t="b">
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>208</v>
+        <v>61.85</v>
       </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
-        <v>1.46</v>
+        <v>-3.21</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>EFACTOR</t>
+          <t>SAHYADRI</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>225.5</v>
+        <v>234.4</v>
       </c>
       <c r="C131" t="n">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="D131" t="n">
-        <v>1.11</v>
+        <v>3.67</v>
       </c>
       <c r="E131" t="b">
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>220</v>
+        <v>238.55</v>
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
-        <v>-3.51</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ASMS</t>
+          <t>NAGAFERT</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>9.02</v>
+        <v>4.1</v>
       </c>
       <c r="C132" t="n">
-        <v>9.119999999999999</v>
+        <v>4.25</v>
       </c>
       <c r="D132" t="n">
-        <v>1.11</v>
+        <v>3.66</v>
       </c>
       <c r="E132" t="b">
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>8.76</v>
+        <v>4.25</v>
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
-        <v>-3.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ISHANCH</t>
+          <t>GKENERGY</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>57.79</v>
+        <v>100.4</v>
       </c>
       <c r="C133" t="n">
-        <v>58.4</v>
+        <v>104.05</v>
       </c>
       <c r="D133" t="n">
-        <v>1.06</v>
+        <v>3.64</v>
       </c>
       <c r="E133" t="b">
         <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>56.99</v>
+        <v>102.69</v>
       </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
-        <v>-2.41</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ASIANENE</t>
+          <t>ABAN</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>285.5</v>
+        <v>23.41</v>
       </c>
       <c r="C134" t="n">
-        <v>288.5</v>
+        <v>24.26</v>
       </c>
       <c r="D134" t="n">
-        <v>1.05</v>
+        <v>3.63</v>
       </c>
       <c r="E134" t="b">
         <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>273.55</v>
+        <v>24.58</v>
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
-        <v>-5.18</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SETCO</t>
+          <t>RKDL</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>18.24</v>
+        <v>18.63</v>
       </c>
       <c r="C135" t="n">
-        <v>18.43</v>
+        <v>19.3</v>
       </c>
       <c r="D135" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="E135" t="b">
         <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>17.45</v>
+        <v>19.15</v>
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
-        <v>-5.32</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>OSWALSEEDS</t>
+          <t>GINNIFILA</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>12.62</v>
+        <v>33.05</v>
       </c>
       <c r="C136" t="n">
-        <v>12.75</v>
+        <v>34.24</v>
       </c>
       <c r="D136" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="E136" t="b">
         <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>12.58</v>
+        <v>34.04</v>
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
-        <v>-1.33</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>RUSHIL</t>
+          <t>RHFL</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>16.47</v>
+        <v>2.24</v>
       </c>
       <c r="C137" t="n">
-        <v>16.64</v>
+        <v>2.32</v>
       </c>
       <c r="D137" t="n">
-        <v>1.03</v>
+        <v>3.57</v>
       </c>
       <c r="E137" t="b">
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>16.2</v>
+        <v>2.35</v>
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
-        <v>-2.64</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>BONLON</t>
+          <t>NACLIND</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>38.6</v>
+        <v>117.81</v>
       </c>
       <c r="C138" t="n">
-        <v>38.99</v>
+        <v>121.99</v>
       </c>
       <c r="D138" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="E138" t="b">
         <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>37.97</v>
+        <v>119.8</v>
       </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
-        <v>-2.62</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>TRIGYN</t>
+          <t>VMM</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>48.51</v>
+        <v>108.65</v>
       </c>
       <c r="C139" t="n">
-        <v>49</v>
+        <v>112.5</v>
       </c>
       <c r="D139" t="n">
-        <v>1.01</v>
+        <v>3.54</v>
       </c>
       <c r="E139" t="b">
         <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>46.71</v>
+        <v>110.27</v>
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
-        <v>-4.67</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>KRITIKA</t>
+          <t>FOODSIN</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>5.99</v>
+        <v>51.48</v>
       </c>
       <c r="C140" t="n">
-        <v>6.05</v>
+        <v>53.3</v>
       </c>
       <c r="D140" t="n">
-        <v>1</v>
+        <v>3.54</v>
       </c>
       <c r="E140" t="b">
         <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>6.25</v>
+        <v>53.89</v>
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
-        <v>3.31</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>KAYTEX</t>
+          <t>MOSCHIP</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>84.05</v>
+        <v>168.08</v>
       </c>
       <c r="C141" t="n">
-        <v>84.84999999999999</v>
+        <v>174.02</v>
       </c>
       <c r="D141" t="n">
-        <v>0.95</v>
+        <v>3.53</v>
       </c>
       <c r="E141" t="b">
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>81</v>
+        <v>170.9</v>
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
-        <v>-4.54</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>OILCOUNTUB</t>
+          <t>SWELECTES</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>46.81</v>
+        <v>496.45</v>
       </c>
       <c r="C142" t="n">
-        <v>47.25</v>
+        <v>513.95</v>
       </c>
       <c r="D142" t="n">
-        <v>0.9399999999999999</v>
+        <v>3.53</v>
       </c>
       <c r="E142" t="b">
         <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>47</v>
+        <v>505.5</v>
       </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
-        <v>-0.53</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>LXCHEM</t>
+          <t>RCOM</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>113.72</v>
+        <v>0.85</v>
       </c>
       <c r="C143" t="n">
-        <v>114.78</v>
+        <v>0.88</v>
       </c>
       <c r="D143" t="n">
-        <v>0.93</v>
+        <v>3.53</v>
       </c>
       <c r="E143" t="b">
         <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>112.52</v>
+        <v>0.89</v>
       </c>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
-        <v>-1.97</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>CAPTRUST</t>
+          <t>JKTYRE</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>11.9</v>
+        <v>425.1</v>
       </c>
       <c r="C144" t="n">
-        <v>12.01</v>
+        <v>440</v>
       </c>
       <c r="D144" t="n">
-        <v>0.92</v>
+        <v>3.51</v>
       </c>
       <c r="E144" t="b">
         <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>12.3</v>
+        <v>436.3</v>
       </c>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
-        <v>2.41</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>NAGAFERT</t>
+          <t>HMVL</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>4.34</v>
+        <v>60.75</v>
       </c>
       <c r="C145" t="n">
-        <v>4.38</v>
+        <v>62.88</v>
       </c>
       <c r="D145" t="n">
-        <v>0.92</v>
+        <v>3.51</v>
       </c>
       <c r="E145" t="b">
         <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>4.19</v>
+        <v>62</v>
       </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
-        <v>-4.34</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>MAXIND</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>148.64</v>
+        <v>1082.1</v>
       </c>
       <c r="C146" t="n">
-        <v>150</v>
+        <v>1120</v>
       </c>
       <c r="D146" t="n">
-        <v>0.91</v>
+        <v>3.5</v>
       </c>
       <c r="E146" t="b">
         <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>142.96</v>
+        <v>1114.8</v>
       </c>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
-        <v>-4.69</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MIDWESTLTD</t>
+          <t>TRIVENI</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>1126.7</v>
+        <v>374.65</v>
       </c>
       <c r="C147" t="n">
-        <v>1136.9</v>
+        <v>387.75</v>
       </c>
       <c r="D147" t="n">
-        <v>0.91</v>
+        <v>3.5</v>
       </c>
       <c r="E147" t="b">
         <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>1076</v>
+        <v>368.4</v>
       </c>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
-        <v>-5.36</v>
+        <v>-4.99</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ANANTAM</t>
+          <t>SOLEX</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>102.97</v>
+        <v>840.9</v>
       </c>
       <c r="C148" t="n">
-        <v>103.9</v>
+        <v>870.35</v>
       </c>
       <c r="D148" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="E148" t="b">
         <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>102.22</v>
+        <v>880.1</v>
       </c>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
-        <v>-1.62</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>VAISHALI</t>
+          <t>ORIENTTECH</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>6.74</v>
+        <v>258.95</v>
       </c>
       <c r="C149" t="n">
-        <v>6.8</v>
+        <v>268</v>
       </c>
       <c r="D149" t="n">
-        <v>0.89</v>
+        <v>3.49</v>
       </c>
       <c r="E149" t="b">
         <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>6.55</v>
+        <v>263.55</v>
       </c>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
-        <v>-3.68</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>INA</t>
+          <t>ENCOMPAS</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>96.15000000000001</v>
+        <v>270.55</v>
       </c>
       <c r="C150" t="n">
-        <v>97</v>
+        <v>280</v>
       </c>
       <c r="D150" t="n">
-        <v>0.88</v>
+        <v>3.49</v>
       </c>
       <c r="E150" t="b">
         <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>95.20999999999999</v>
+        <v>280</v>
       </c>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
-        <v>-1.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>UMAEXPORTS</t>
+          <t>ORIENTBELL</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>22.8</v>
+        <v>280.25</v>
       </c>
       <c r="C151" t="n">
-        <v>23</v>
+        <v>290</v>
       </c>
       <c r="D151" t="n">
-        <v>0.88</v>
+        <v>3.48</v>
       </c>
       <c r="E151" t="b">
         <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>22.77</v>
+        <v>281.15</v>
       </c>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
-        <v>-1</v>
+        <v>-3.05</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>GLOBALVECT</t>
+          <t>ORIENTPPR</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>156.69</v>
+        <v>16.66</v>
       </c>
       <c r="C152" t="n">
-        <v>158</v>
+        <v>17.24</v>
       </c>
       <c r="D152" t="n">
-        <v>0.84</v>
+        <v>3.48</v>
       </c>
       <c r="E152" t="b">
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>155.63</v>
+        <v>16.95</v>
       </c>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="n">
-        <v>-1.5</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ANSALAPI</t>
+          <t>KHANDSE</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>3.87</v>
+        <v>17.87</v>
       </c>
       <c r="C153" t="n">
-        <v>3.9</v>
+        <v>18.49</v>
       </c>
       <c r="D153" t="n">
-        <v>0.78</v>
+        <v>3.47</v>
       </c>
       <c r="E153" t="b">
         <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>3.8</v>
+        <v>18.29</v>
       </c>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="n">
-        <v>-2.56</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>MRPL</t>
+          <t>MODTHREAD</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>206.55</v>
+        <v>52.19</v>
       </c>
       <c r="C154" t="n">
-        <v>208.1</v>
+        <v>54</v>
       </c>
       <c r="D154" t="n">
-        <v>0.75</v>
+        <v>3.47</v>
       </c>
       <c r="E154" t="b">
         <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>191.04</v>
+        <v>51.87</v>
       </c>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="n">
-        <v>-8.199999999999999</v>
+        <v>-3.94</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>BALPHARMA</t>
+          <t>TBZ</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>72.47</v>
+        <v>130.5</v>
       </c>
       <c r="C155" t="n">
-        <v>73</v>
+        <v>135</v>
       </c>
       <c r="D155" t="n">
-        <v>0.73</v>
+        <v>3.45</v>
       </c>
       <c r="E155" t="b">
         <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>68.01000000000001</v>
+        <v>133.33</v>
       </c>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="n">
-        <v>-6.84</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>DEEPINDS</t>
+          <t>MITTAL</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>337.7</v>
+        <v>0.88</v>
       </c>
       <c r="C156" t="n">
-        <v>340</v>
+        <v>0.91</v>
       </c>
       <c r="D156" t="n">
-        <v>0.68</v>
+        <v>3.41</v>
       </c>
       <c r="E156" t="b">
         <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>354</v>
+        <v>0.88</v>
       </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="n">
-        <v>4.12</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>VIRINCHI</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>2471.9</v>
+        <v>18.85</v>
       </c>
       <c r="C157" t="n">
-        <v>2488.4</v>
+        <v>19.49</v>
       </c>
       <c r="D157" t="n">
-        <v>0.67</v>
+        <v>3.4</v>
       </c>
       <c r="E157" t="b">
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>2367.3</v>
+        <v>19.21</v>
       </c>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="n">
-        <v>-4.87</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>SOLARINDS</t>
+          <t>AKI</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>15152</v>
+        <v>4.72</v>
       </c>
       <c r="C158" t="n">
-        <v>15250</v>
+        <v>4.88</v>
       </c>
       <c r="D158" t="n">
-        <v>0.65</v>
+        <v>3.39</v>
       </c>
       <c r="E158" t="b">
         <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>14748</v>
+        <v>4.94</v>
       </c>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="n">
-        <v>-3.29</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ALANKIT</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>7.95</v>
+        <v>1605.5</v>
       </c>
       <c r="C159" t="n">
-        <v>8</v>
+        <v>1660</v>
       </c>
       <c r="D159" t="n">
-        <v>0.63</v>
+        <v>3.39</v>
       </c>
       <c r="E159" t="b">
         <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>7.72</v>
+        <v>1617.1</v>
       </c>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="n">
-        <v>-3.5</v>
+        <v>-2.58</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>GFLLIMITED</t>
+          <t>RAMASTEEL</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>43.03</v>
+        <v>5.92</v>
       </c>
       <c r="C160" t="n">
-        <v>43.3</v>
+        <v>6.12</v>
       </c>
       <c r="D160" t="n">
-        <v>0.63</v>
+        <v>3.38</v>
       </c>
       <c r="E160" t="b">
         <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>41.62</v>
+        <v>6</v>
       </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="n">
-        <v>-3.88</v>
+        <v>-1.96</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>VINDHYATEL</t>
+          <t>INDOWIND</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>1003.8</v>
+        <v>8.94</v>
       </c>
       <c r="C161" t="n">
-        <v>1009.9</v>
+        <v>9.24</v>
       </c>
       <c r="D161" t="n">
-        <v>0.61</v>
+        <v>3.36</v>
       </c>
       <c r="E161" t="b">
         <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>998</v>
+        <v>8.92</v>
       </c>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="n">
-        <v>-1.18</v>
+        <v>-3.46</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>CONFIPET</t>
+          <t>BAIDFIN</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>29.73</v>
+        <v>11.07</v>
       </c>
       <c r="C162" t="n">
-        <v>29.91</v>
+        <v>11.44</v>
       </c>
       <c r="D162" t="n">
-        <v>0.61</v>
+        <v>3.34</v>
       </c>
       <c r="E162" t="b">
         <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>28.74</v>
+        <v>11.01</v>
       </c>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="n">
-        <v>-3.91</v>
+        <v>-3.76</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>SURYODAY</t>
+          <t>COASTCORP</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>129.25</v>
+        <v>42.6</v>
       </c>
       <c r="C163" t="n">
-        <v>130</v>
+        <v>44</v>
       </c>
       <c r="D163" t="n">
-        <v>0.58</v>
+        <v>3.29</v>
       </c>
       <c r="E163" t="b">
         <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>129.11</v>
+        <v>45.34</v>
       </c>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="n">
-        <v>-0.68</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>GULFPETRO</t>
+          <t>FIBERWEB</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>31.04</v>
+        <v>37.45</v>
       </c>
       <c r="C164" t="n">
-        <v>31.2</v>
+        <v>38.68</v>
       </c>
       <c r="D164" t="n">
-        <v>0.52</v>
+        <v>3.28</v>
       </c>
       <c r="E164" t="b">
         <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>30.85</v>
+        <v>36.71</v>
       </c>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="n">
-        <v>-1.12</v>
+        <v>-5.09</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ONWARDTEC</t>
+          <t>ORIENTCER</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>250.2</v>
+        <v>35.83</v>
       </c>
       <c r="C165" t="n">
-        <v>251.5</v>
+        <v>37</v>
       </c>
       <c r="D165" t="n">
-        <v>0.52</v>
+        <v>3.27</v>
       </c>
       <c r="E165" t="b">
         <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>240.25</v>
+        <v>36.79</v>
       </c>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="n">
-        <v>-4.47</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SHREYANIND</t>
+          <t>SOLARWORLD</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>150.12</v>
+        <v>163.19</v>
       </c>
       <c r="C166" t="n">
-        <v>150.9</v>
+        <v>168.53</v>
       </c>
       <c r="D166" t="n">
-        <v>0.52</v>
+        <v>3.27</v>
       </c>
       <c r="E166" t="b">
         <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>148.75</v>
+        <v>166.57</v>
       </c>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="n">
-        <v>-1.42</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>LEMERITE</t>
+          <t>VASWANI</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>443.9</v>
+        <v>54.24</v>
       </c>
       <c r="C167" t="n">
-        <v>446.15</v>
+        <v>56</v>
       </c>
       <c r="D167" t="n">
-        <v>0.51</v>
+        <v>3.24</v>
       </c>
       <c r="E167" t="b">
         <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>443.65</v>
+        <v>54.6</v>
       </c>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CSLFINANCE</t>
+          <t>ROLEXRINGS</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>246.7</v>
+        <v>118.31</v>
       </c>
       <c r="C168" t="n">
-        <v>247.95</v>
+        <v>122.13</v>
       </c>
       <c r="D168" t="n">
-        <v>0.51</v>
+        <v>3.23</v>
       </c>
       <c r="E168" t="b">
         <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>244.9</v>
+        <v>120.1</v>
       </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="n">
-        <v>-1.23</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>VENUSREM</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>704.85</v>
+        <v>918.8</v>
       </c>
       <c r="C169" t="n">
-        <v>708.35</v>
+        <v>948.2</v>
       </c>
       <c r="D169" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="E169" t="b">
         <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>690</v>
+        <v>961.25</v>
       </c>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="n">
-        <v>-2.59</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ROSSELLIND</t>
+          <t>TBOTEK</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>46.17</v>
+        <v>1190</v>
       </c>
       <c r="C170" t="n">
-        <v>46.4</v>
+        <v>1228</v>
       </c>
       <c r="D170" t="n">
-        <v>0.5</v>
+        <v>3.19</v>
       </c>
       <c r="E170" t="b">
         <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>45.27</v>
+        <v>1185.4</v>
       </c>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="n">
-        <v>-2.44</v>
+        <v>-3.47</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SMCGLOBAL</t>
+          <t>TECHD</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>71.73999999999999</v>
+        <v>439.9</v>
       </c>
       <c r="C171" t="n">
-        <v>72.09999999999999</v>
+        <v>453.95</v>
       </c>
       <c r="D171" t="n">
-        <v>0.5</v>
+        <v>3.19</v>
       </c>
       <c r="E171" t="b">
         <v>0</v>
       </c>
       <c r="F171" t="n">
-        <v>68.5</v>
+        <v>464.5</v>
       </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="n">
-        <v>-4.99</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>KHAITANLTD</t>
+          <t>BSL</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>95.83</v>
+        <v>126.95</v>
       </c>
       <c r="C172" t="n">
-        <v>96.3</v>
+        <v>131</v>
       </c>
       <c r="D172" t="n">
-        <v>0.49</v>
+        <v>3.19</v>
       </c>
       <c r="E172" t="b">
         <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>91.05</v>
+        <v>129.75</v>
       </c>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="n">
-        <v>-5.45</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>FOODSIN</t>
+          <t>AIMTRON</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>52.59</v>
+        <v>754</v>
       </c>
       <c r="C173" t="n">
-        <v>52.85</v>
+        <v>777.9</v>
       </c>
       <c r="D173" t="n">
-        <v>0.49</v>
+        <v>3.17</v>
       </c>
       <c r="E173" t="b">
         <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>51.58</v>
+        <v>771.8</v>
       </c>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="n">
-        <v>-2.4</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>EMAMIREAL</t>
+          <t>MRPL</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>61.23</v>
+        <v>190.03</v>
       </c>
       <c r="C174" t="n">
-        <v>61.53</v>
+        <v>196</v>
       </c>
       <c r="D174" t="n">
-        <v>0.49</v>
+        <v>3.14</v>
       </c>
       <c r="E174" t="b">
         <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>61.22</v>
+        <v>190.75</v>
       </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="n">
-        <v>-0.5</v>
+        <v>-2.68</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>SINDHUTRAD</t>
+          <t>PLASTIBLEN</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>25.12</v>
+        <v>135.65</v>
       </c>
       <c r="C175" t="n">
-        <v>25.24</v>
+        <v>139.9</v>
       </c>
       <c r="D175" t="n">
-        <v>0.48</v>
+        <v>3.13</v>
       </c>
       <c r="E175" t="b">
         <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>24.08</v>
+        <v>139</v>
       </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="n">
-        <v>-4.6</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SOLEX</t>
+          <t>HCL-INSYS</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>869.25</v>
+        <v>12.21</v>
       </c>
       <c r="C176" t="n">
-        <v>873.45</v>
+        <v>12.59</v>
       </c>
       <c r="D176" t="n">
-        <v>0.48</v>
+        <v>3.11</v>
       </c>
       <c r="E176" t="b">
         <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>843.25</v>
+        <v>12.41</v>
       </c>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="n">
-        <v>-3.46</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SILLYMONKS</t>
+          <t>BCONCEPTS</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>17.41</v>
+        <v>237.65</v>
       </c>
       <c r="C177" t="n">
-        <v>17.49</v>
+        <v>245</v>
       </c>
       <c r="D177" t="n">
-        <v>0.46</v>
+        <v>3.09</v>
       </c>
       <c r="E177" t="b">
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>16.65</v>
+        <v>242</v>
       </c>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="n">
-        <v>-4.8</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>PUSHPA</t>
+          <t>CCAVENUE</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>88.59999999999999</v>
+        <v>14.94</v>
       </c>
       <c r="C178" t="n">
-        <v>89</v>
+        <v>15.4</v>
       </c>
       <c r="D178" t="n">
-        <v>0.45</v>
+        <v>3.08</v>
       </c>
       <c r="E178" t="b">
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>81.15000000000001</v>
+        <v>15.04</v>
       </c>
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="n">
-        <v>-8.82</v>
+        <v>-2.34</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>INDOWIND</t>
+          <t>KROSS</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>8.949999999999999</v>
+        <v>183.6</v>
       </c>
       <c r="C179" t="n">
-        <v>8.99</v>
+        <v>189.23</v>
       </c>
       <c r="D179" t="n">
-        <v>0.45</v>
+        <v>3.07</v>
       </c>
       <c r="E179" t="b">
         <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>8.75</v>
+        <v>190.54</v>
       </c>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="n">
-        <v>-2.67</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>PRAXIS</t>
+          <t>EDELWEISS</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>6.62</v>
+        <v>105.66</v>
       </c>
       <c r="C180" t="n">
-        <v>6.65</v>
+        <v>108.9</v>
       </c>
       <c r="D180" t="n">
-        <v>0.45</v>
+        <v>3.07</v>
       </c>
       <c r="E180" t="b">
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>6.4</v>
+        <v>106.68</v>
       </c>
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="n">
-        <v>-3.76</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SESHAPAPER</t>
+          <t>AWHCL</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>259.55</v>
+        <v>456.25</v>
       </c>
       <c r="C181" t="n">
-        <v>260.7</v>
+        <v>470.25</v>
       </c>
       <c r="D181" t="n">
-        <v>0.44</v>
+        <v>3.07</v>
       </c>
       <c r="E181" t="b">
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>257.05</v>
+        <v>465</v>
       </c>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="n">
-        <v>-1.4</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>HESTERBIO</t>
+          <t>ABINFRA</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>1474.1</v>
+        <v>17.27</v>
       </c>
       <c r="C182" t="n">
-        <v>1480.1</v>
+        <v>17.8</v>
       </c>
       <c r="D182" t="n">
-        <v>0.41</v>
+        <v>3.07</v>
       </c>
       <c r="E182" t="b">
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>1445.6</v>
+        <v>17.42</v>
       </c>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="n">
-        <v>-2.33</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>RVHL</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>38.99</v>
+        <v>3768.6</v>
       </c>
       <c r="C183" t="n">
-        <v>39.15</v>
+        <v>3884</v>
       </c>
       <c r="D183" t="n">
-        <v>0.41</v>
+        <v>3.06</v>
       </c>
       <c r="E183" t="b">
         <v>0</v>
       </c>
-      <c r="F183" t="n">
-        <v>38.43</v>
-      </c>
+      <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr"/>
-      <c r="H183" t="n">
-        <v>-1.84</v>
-      </c>
+      <c r="H183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ALPA</t>
+          <t>SILINV</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>63.45</v>
+        <v>405.6</v>
       </c>
       <c r="C184" t="n">
-        <v>63.7</v>
+        <v>418</v>
       </c>
       <c r="D184" t="n">
-        <v>0.39</v>
+        <v>3.06</v>
       </c>
       <c r="E184" t="b">
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>61.65</v>
+        <v>403.05</v>
       </c>
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="n">
-        <v>-3.22</v>
+        <v>-3.58</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>DOLPHIN</t>
+          <t>EBGNG</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>444.3</v>
+        <v>339.65</v>
       </c>
       <c r="C185" t="n">
-        <v>446</v>
+        <v>350</v>
       </c>
       <c r="D185" t="n">
-        <v>0.38</v>
+        <v>3.05</v>
       </c>
       <c r="E185" t="b">
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>440.5</v>
+        <v>356.6</v>
       </c>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="n">
-        <v>-1.23</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>TEXMOPIPES</t>
+          <t>JAMNAAUTO</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>43.69</v>
+        <v>122.28</v>
       </c>
       <c r="C186" t="n">
-        <v>43.85</v>
+        <v>126</v>
       </c>
       <c r="D186" t="n">
-        <v>0.37</v>
+        <v>3.04</v>
       </c>
       <c r="E186" t="b">
         <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>41.93</v>
+        <v>124.51</v>
       </c>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="n">
-        <v>-4.38</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ASHOKAMET</t>
+          <t>ESCORTS</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>14.03</v>
+        <v>3203.4</v>
       </c>
       <c r="C187" t="n">
-        <v>14.08</v>
+        <v>3300</v>
       </c>
       <c r="D187" t="n">
-        <v>0.36</v>
+        <v>3.02</v>
       </c>
       <c r="E187" t="b">
         <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>14.16</v>
+        <v>3295.4</v>
       </c>
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="n">
-        <v>0.57</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>PTL</t>
+          <t>JPASSOCIAT</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>38.12</v>
+        <v>2.32</v>
       </c>
       <c r="C188" t="n">
-        <v>38.25</v>
+        <v>2.39</v>
       </c>
       <c r="D188" t="n">
-        <v>0.34</v>
+        <v>3.02</v>
       </c>
       <c r="E188" t="b">
         <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>37.12</v>
+        <v>2.38</v>
       </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="n">
-        <v>-2.95</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>DUCON</t>
+          <t>KITEX</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>3.04</v>
+        <v>164.06</v>
       </c>
       <c r="C189" t="n">
-        <v>3.05</v>
+        <v>169</v>
       </c>
       <c r="D189" t="n">
-        <v>0.33</v>
+        <v>3.01</v>
       </c>
       <c r="E189" t="b">
         <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>2.95</v>
+        <v>168.99</v>
       </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="n">
-        <v>-3.28</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>HINDPETRO</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>468.45</v>
+        <v>384.55</v>
       </c>
       <c r="C190" t="n">
-        <v>470</v>
+        <v>396</v>
       </c>
       <c r="D190" t="n">
-        <v>0.33</v>
+        <v>2.98</v>
       </c>
       <c r="E190" t="b">
         <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>451.1</v>
+        <v>384.75</v>
       </c>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="n">
-        <v>-4.02</v>
+        <v>-2.84</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>IFBAGRO</t>
+          <t>SANSERA</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>767.2</v>
+        <v>2096.8</v>
       </c>
       <c r="C191" t="n">
-        <v>769.7</v>
+        <v>2159</v>
       </c>
       <c r="D191" t="n">
-        <v>0.33</v>
+        <v>2.97</v>
       </c>
       <c r="E191" t="b">
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>728.85</v>
+        <v>2135</v>
       </c>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="n">
-        <v>-5.31</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>CENTRUM</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>22.47</v>
+        <v>1837.8</v>
       </c>
       <c r="C192" t="n">
-        <v>22.54</v>
+        <v>1892.4</v>
       </c>
       <c r="D192" t="n">
-        <v>0.31</v>
+        <v>2.97</v>
       </c>
       <c r="E192" t="b">
         <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>21.47</v>
+        <v>1888</v>
       </c>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="n">
-        <v>-4.75</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>KAMATHOTEL</t>
+          <t>AGARIND</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>183.91</v>
+        <v>456.45</v>
       </c>
       <c r="C193" t="n">
-        <v>184.47</v>
+        <v>470</v>
       </c>
       <c r="D193" t="n">
-        <v>0.3</v>
+        <v>2.97</v>
       </c>
       <c r="E193" t="b">
         <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>180.45</v>
+        <v>449.25</v>
       </c>
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="n">
-        <v>-2.18</v>
+        <v>-4.41</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>BAJAJINDEF</t>
+          <t>TIL</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>229.69</v>
+        <v>192.29</v>
       </c>
       <c r="C194" t="n">
-        <v>230.37</v>
+        <v>197.99</v>
       </c>
       <c r="D194" t="n">
-        <v>0.3</v>
+        <v>2.96</v>
       </c>
       <c r="E194" t="b">
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>219.7</v>
+        <v>198.46</v>
       </c>
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="n">
-        <v>-4.63</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>KIRLOSENG</t>
+          <t>SITINET</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>1510.5</v>
+        <v>0.34</v>
       </c>
       <c r="C195" t="n">
-        <v>1515</v>
+        <v>0.35</v>
       </c>
       <c r="D195" t="n">
-        <v>0.3</v>
+        <v>2.94</v>
       </c>
       <c r="E195" t="b">
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>1474.6</v>
+        <v>0.34</v>
       </c>
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="n">
-        <v>-2.67</v>
+        <v>-2.86</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>UNIDT</t>
+          <t>CHANDAN</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>179.85</v>
+        <v>250.65</v>
       </c>
       <c r="C196" t="n">
-        <v>180.38</v>
+        <v>258</v>
       </c>
       <c r="D196" t="n">
-        <v>0.29</v>
+        <v>2.93</v>
       </c>
       <c r="E196" t="b">
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>183.72</v>
+        <v>254.8</v>
       </c>
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="n">
-        <v>1.85</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>GGBL</t>
+          <t>PROSTARM</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>283.2</v>
+        <v>127.27</v>
       </c>
       <c r="C197" t="n">
-        <v>284</v>
+        <v>131</v>
       </c>
       <c r="D197" t="n">
-        <v>0.28</v>
+        <v>2.93</v>
       </c>
       <c r="E197" t="b">
         <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>274.9</v>
+        <v>130.25</v>
       </c>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="n">
-        <v>-3.2</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>LIBERTSHOE</t>
+          <t>REMSONSIND</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>224.4</v>
+        <v>104.84</v>
       </c>
       <c r="C198" t="n">
-        <v>225</v>
+        <v>107.9</v>
       </c>
       <c r="D198" t="n">
-        <v>0.27</v>
+        <v>2.92</v>
       </c>
       <c r="E198" t="b">
         <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>219.26</v>
+        <v>105.28</v>
       </c>
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="n">
-        <v>-2.55</v>
+        <v>-2.43</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>BRNL</t>
+          <t>SIGNATURE</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>18.4</v>
+        <v>874.55</v>
       </c>
       <c r="C199" t="n">
-        <v>18.45</v>
+        <v>900</v>
       </c>
       <c r="D199" t="n">
-        <v>0.27</v>
+        <v>2.91</v>
       </c>
       <c r="E199" t="b">
         <v>0</v>
       </c>
       <c r="F199" t="n">
-        <v>18</v>
+        <v>881.4</v>
       </c>
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="n">
-        <v>-2.44</v>
+        <v>-2.07</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SAGCEM</t>
+          <t>VISHWARAJ</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>186</v>
+        <v>5.15</v>
       </c>
       <c r="C200" t="n">
-        <v>186.49</v>
+        <v>5.3</v>
       </c>
       <c r="D200" t="n">
-        <v>0.26</v>
+        <v>2.91</v>
       </c>
       <c r="E200" t="b">
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>179.11</v>
+        <v>5.25</v>
       </c>
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="n">
-        <v>-3.96</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>MANAKSTEEL</t>
+          <t>HITECHCORP</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>56.96</v>
+        <v>118.55</v>
       </c>
       <c r="C201" t="n">
-        <v>57.1</v>
+        <v>122</v>
       </c>
       <c r="D201" t="n">
-        <v>0.25</v>
+        <v>2.91</v>
       </c>
       <c r="E201" t="b">
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>54.52</v>
+        <v>119.41</v>
       </c>
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="n">
-        <v>-4.52</v>
+        <v>-2.12</v>
       </c>
     </row>
   </sheetData>

--- a/data/trending_momentum_stocks.xlsx
+++ b/data/trending_momentum_stocks.xlsx
@@ -461,1267 +461,1271 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HILTON-RE2</t>
+          <t>SIGMA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2</v>
+        <v>39.22</v>
       </c>
       <c r="C2" t="n">
-        <v>0.23</v>
+        <v>47</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>19.84</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.16</v>
+        <v>40.51</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>-30.43</v>
+        <v>-13.81</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3PLAND</t>
+          <t>MMEL</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30.31</v>
+        <v>25.65</v>
       </c>
       <c r="C3" t="n">
-        <v>33.99</v>
+        <v>28.9</v>
       </c>
       <c r="D3" t="n">
-        <v>12.14</v>
+        <v>12.67</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>30.85</v>
+        <v>26.4</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>-9.24</v>
+        <v>-8.65</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SUPERSPIN</t>
+          <t>VGL</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.22</v>
+        <v>61.19</v>
       </c>
       <c r="C4" t="n">
-        <v>5.8</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>11.11</v>
+        <v>12.6</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>5.67</v>
+        <v>63.47</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>-2.24</v>
+        <v>-7.88</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CROWN</t>
+          <t>TECILCHEM</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>117.54</v>
+        <v>12.9</v>
       </c>
       <c r="C5" t="n">
-        <v>128.2</v>
+        <v>14.45</v>
       </c>
       <c r="D5" t="n">
-        <v>9.07</v>
+        <v>12.02</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>120.98</v>
+        <v>12.99</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>-5.63</v>
+        <v>-10.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SECURKLOUD</t>
+          <t>WILLAMAGOR</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.05</v>
+        <v>25.8</v>
       </c>
       <c r="C6" t="n">
-        <v>21.8</v>
+        <v>28.7</v>
       </c>
       <c r="D6" t="n">
-        <v>8.73</v>
+        <v>11.24</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>21.69</v>
+        <v>28.55</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>-0.5</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>INFOMEDIA</t>
+          <t>MFML</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.24</v>
+        <v>22.5</v>
       </c>
       <c r="C7" t="n">
-        <v>5.69</v>
+        <v>24.99</v>
       </c>
       <c r="D7" t="n">
-        <v>8.59</v>
+        <v>11.07</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>5.07</v>
+        <v>23.44</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>-10.9</v>
+        <v>-6.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GEECEE</t>
+          <t>DCMFINSERV</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>260.8</v>
+        <v>4.69</v>
       </c>
       <c r="C8" t="n">
-        <v>283</v>
+        <v>5.19</v>
       </c>
       <c r="D8" t="n">
-        <v>8.51</v>
+        <v>10.66</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>286.35</v>
+        <v>5.62</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>1.18</v>
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AKSHARCHEM</t>
+          <t>UNIINFO</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>191.16</v>
+        <v>12.44</v>
       </c>
       <c r="C9" t="n">
-        <v>207.3</v>
+        <v>13.75</v>
       </c>
       <c r="D9" t="n">
-        <v>8.44</v>
+        <v>10.53</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>193.24</v>
+        <v>12.8</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>-6.78</v>
+        <v>-6.91</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RSYSTEMS</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>298.1</v>
+        <v>141.55</v>
       </c>
       <c r="C10" t="n">
-        <v>322.65</v>
+        <v>155</v>
       </c>
       <c r="D10" t="n">
-        <v>8.24</v>
+        <v>9.5</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>332.55</v>
+        <v>161.1</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>3.07</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NOIDATOLL</t>
+          <t>SEMAC</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.61</v>
+        <v>212.42</v>
       </c>
       <c r="C11" t="n">
-        <v>3.9</v>
+        <v>231.99</v>
       </c>
       <c r="D11" t="n">
-        <v>8.029999999999999</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>3.63</v>
+        <v>225</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>-6.92</v>
+        <v>-3.01</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PALASHSECU</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>86.22</v>
+        <v>489.95</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>533.85</v>
       </c>
       <c r="D12" t="n">
-        <v>7.86</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>89.09999999999999</v>
+        <v>569.4</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>-4.19</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NECCLTD</t>
+          <t>AMBICAAGAR</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>23.54</v>
       </c>
       <c r="C13" t="n">
-        <v>13.99</v>
+        <v>25.5</v>
       </c>
       <c r="D13" t="n">
-        <v>7.62</v>
+        <v>8.33</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>14.14</v>
+        <v>24.39</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>1.07</v>
+        <v>-4.35</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ARVSMART</t>
+          <t>SECURKLOUD</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>501.35</v>
+        <v>21.94</v>
       </c>
       <c r="C14" t="n">
-        <v>538.5</v>
+        <v>23.73</v>
       </c>
       <c r="D14" t="n">
-        <v>7.41</v>
+        <v>8.16</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>569</v>
+        <v>22.25</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>5.66</v>
+        <v>-6.24</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BIOFILCHEM</t>
+          <t>GROBTEA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30.1</v>
+        <v>861.2</v>
       </c>
       <c r="C15" t="n">
-        <v>32.25</v>
+        <v>930</v>
       </c>
       <c r="D15" t="n">
-        <v>7.14</v>
+        <v>7.99</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>30.97</v>
+        <v>871</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>-3.97</v>
+        <v>-6.34</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JAGSNPHARM</t>
+          <t>WABAG</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>168.27</v>
+        <v>1198.3</v>
       </c>
       <c r="C16" t="n">
-        <v>180</v>
+        <v>1290</v>
       </c>
       <c r="D16" t="n">
-        <v>6.97</v>
+        <v>7.65</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>185.43</v>
+        <v>1281.5</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>3.02</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MEDICO</t>
+          <t>PIGL</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>40.25</v>
+        <v>100.78</v>
       </c>
       <c r="C17" t="n">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="D17" t="n">
-        <v>6.83</v>
+        <v>7.16</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>40.92</v>
+        <v>102.34</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>-4.84</v>
+        <v>-5.24</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MITCON</t>
+          <t>CEINSYS</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>53.24</v>
+        <v>871.35</v>
       </c>
       <c r="C18" t="n">
-        <v>56.8</v>
+        <v>931.95</v>
       </c>
       <c r="D18" t="n">
-        <v>6.69</v>
+        <v>6.95</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>54.38</v>
+        <v>991.25</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>-4.26</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DCI</t>
+          <t>DHARAN</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>243.75</v>
+        <v>0.15</v>
       </c>
       <c r="C19" t="n">
-        <v>259.9</v>
+        <v>0.16</v>
       </c>
       <c r="D19" t="n">
-        <v>6.63</v>
+        <v>6.67</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>248.6</v>
+        <v>0.16</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>-4.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PILITA</t>
+          <t>PRINCEPIPE</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7.87</v>
+        <v>248.55</v>
       </c>
       <c r="C20" t="n">
-        <v>8.390000000000001</v>
+        <v>265</v>
       </c>
       <c r="D20" t="n">
-        <v>6.61</v>
+        <v>6.62</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>7.94</v>
+        <v>267.8</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>-5.36</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HLVLTD</t>
+          <t>OSWALPUMPS</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7.46</v>
+        <v>300.9</v>
       </c>
       <c r="C21" t="n">
-        <v>7.95</v>
+        <v>320</v>
       </c>
       <c r="D21" t="n">
-        <v>6.57</v>
+        <v>6.35</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>7.6</v>
+        <v>330.95</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>-4.4</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AVTNPL</t>
+          <t>ELECTCAST</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>60.06</v>
+        <v>63.02</v>
       </c>
       <c r="C22" t="n">
-        <v>64</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>6.56</v>
+        <v>6.33</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>60.78</v>
+        <v>75.62</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>-5.03</v>
+        <v>12.85</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MIDWESTLTD</t>
+          <t>UMAEXPORTS</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1084.3</v>
+        <v>22.64</v>
       </c>
       <c r="C23" t="n">
-        <v>1155.3</v>
+        <v>23.99</v>
       </c>
       <c r="D23" t="n">
-        <v>6.55</v>
+        <v>5.96</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>1138.4</v>
+        <v>22.99</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>-1.46</v>
+        <v>-4.17</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ASHIMASYN</t>
+          <t>ICDSLTD</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>14.07</v>
+        <v>37.86</v>
       </c>
       <c r="C24" t="n">
-        <v>14.99</v>
+        <v>40</v>
       </c>
       <c r="D24" t="n">
-        <v>6.54</v>
+        <v>5.65</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>14.25</v>
+        <v>39.59</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>-4.94</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RAMANEWS</t>
+          <t>DENTA</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>34.56</v>
+        <v>227.2</v>
       </c>
       <c r="C25" t="n">
-        <v>36.8</v>
+        <v>240</v>
       </c>
       <c r="D25" t="n">
-        <v>6.48</v>
+        <v>5.63</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>35.41</v>
+        <v>272.6</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>-3.78</v>
+        <v>13.58</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>VGL</t>
+          <t>GTECJAINX</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>61.08</v>
+        <v>20.11</v>
       </c>
       <c r="C26" t="n">
-        <v>65</v>
+        <v>21.22</v>
       </c>
       <c r="D26" t="n">
-        <v>6.42</v>
+        <v>5.52</v>
       </c>
       <c r="E26" t="b">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>61.16</v>
+        <v>21.18</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>-5.91</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>RUDRA</t>
+          <t>DELTAMAGNT</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>16.92</v>
+        <v>56.8</v>
       </c>
       <c r="C27" t="n">
-        <v>18</v>
+        <v>59.9</v>
       </c>
       <c r="D27" t="n">
-        <v>6.38</v>
+        <v>5.46</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>17.05</v>
+        <v>59.47</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>-5.28</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>INTENTECH</t>
+          <t>FACT</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>90.72</v>
+        <v>794.5</v>
       </c>
       <c r="C28" t="n">
-        <v>96.5</v>
+        <v>837</v>
       </c>
       <c r="D28" t="n">
-        <v>6.37</v>
+        <v>5.35</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>92.20999999999999</v>
+        <v>854</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>-4.45</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BASML</t>
+          <t>MAGNUM</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>20.18</v>
+        <v>18.86</v>
       </c>
       <c r="C29" t="n">
-        <v>21.43</v>
+        <v>19.85</v>
       </c>
       <c r="D29" t="n">
-        <v>6.19</v>
+        <v>5.25</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>20.82</v>
+        <v>19.47</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>-2.85</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>COASTCORP</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>9804</v>
+        <v>43.42</v>
       </c>
       <c r="C30" t="n">
-        <v>10399</v>
+        <v>45.7</v>
       </c>
       <c r="D30" t="n">
-        <v>6.07</v>
+        <v>5.25</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>10245</v>
+        <v>43.29</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>-1.48</v>
+        <v>-5.27</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MAXIND</t>
+          <t>JASH</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>143.62</v>
+        <v>361.1</v>
       </c>
       <c r="C31" t="n">
-        <v>152.15</v>
+        <v>380</v>
       </c>
       <c r="D31" t="n">
-        <v>5.94</v>
+        <v>5.23</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>146.83</v>
+        <v>384.05</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>-3.5</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>MHLXMIRU</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>90.17</v>
+        <v>164.44</v>
       </c>
       <c r="C32" t="n">
-        <v>95.48</v>
+        <v>173</v>
       </c>
       <c r="D32" t="n">
-        <v>5.89</v>
+        <v>5.21</v>
       </c>
       <c r="E32" t="b">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>92</v>
+        <v>165.05</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>-3.64</v>
+        <v>-4.6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>RILINFRA</t>
+          <t>SRD</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32.05</v>
+        <v>51.29</v>
       </c>
       <c r="C33" t="n">
-        <v>33.9</v>
+        <v>53.95</v>
       </c>
       <c r="D33" t="n">
-        <v>5.77</v>
+        <v>5.19</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>33.3</v>
+        <v>50.59</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>-1.77</v>
+        <v>-6.23</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CHAMUNDA</t>
+          <t>EMSLIMITED</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>43.4</v>
+        <v>259.5</v>
       </c>
       <c r="C34" t="n">
-        <v>45.9</v>
+        <v>272.95</v>
       </c>
       <c r="D34" t="n">
-        <v>5.76</v>
+        <v>5.18</v>
       </c>
       <c r="E34" t="b">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>45.9</v>
+        <v>311.4</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>14.09</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DRCSYSTEMS</t>
+          <t>IONEXCHANG</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>13.23</v>
+        <v>345.8</v>
       </c>
       <c r="C35" t="n">
-        <v>13.99</v>
+        <v>363.6</v>
       </c>
       <c r="D35" t="n">
-        <v>5.74</v>
+        <v>5.15</v>
       </c>
       <c r="E35" t="b">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>13.65</v>
+        <v>383.15</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>-2.43</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PRITI</t>
+          <t>SANWARIA</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>35.4</v>
+        <v>0.2</v>
       </c>
       <c r="C36" t="n">
-        <v>37.4</v>
+        <v>0.21</v>
       </c>
       <c r="D36" t="n">
-        <v>5.65</v>
+        <v>5</v>
       </c>
       <c r="E36" t="b">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>36.9</v>
+        <v>0.21</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>-1.34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CYBERTECH</t>
+          <t>TECHLABS</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>102.29</v>
+        <v>235.05</v>
       </c>
       <c r="C37" t="n">
-        <v>107.99</v>
+        <v>246.8</v>
       </c>
       <c r="D37" t="n">
-        <v>5.57</v>
+        <v>5</v>
       </c>
       <c r="E37" t="b">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>104.7</v>
+        <v>246.8</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>-3.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CINEVISTA</t>
+          <t>CURAA</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>15.53</v>
+        <v>98.88</v>
       </c>
       <c r="C38" t="n">
-        <v>16.38</v>
+        <v>103.82</v>
       </c>
       <c r="D38" t="n">
-        <v>5.47</v>
+        <v>5</v>
       </c>
       <c r="E38" t="b">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>15.9</v>
+        <v>103.82</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>-2.93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BHARATGEAR</t>
+          <t>FILATFASH</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>96.25</v>
+        <v>0.2</v>
       </c>
       <c r="C39" t="n">
-        <v>101.5</v>
+        <v>0.21</v>
       </c>
       <c r="D39" t="n">
-        <v>5.45</v>
+        <v>5</v>
       </c>
       <c r="E39" t="b">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>98.17</v>
+        <v>0.21</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>-3.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NITIRAJ</t>
+          <t>GAUDIUMIVF</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>218.2</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>229.95</v>
+        <v>81.12</v>
       </c>
       <c r="D40" t="n">
-        <v>5.38</v>
+        <v>5</v>
       </c>
       <c r="E40" t="b">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>217.12</v>
+        <v>81.12</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>-5.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ACEINTEG</t>
+          <t>SACHEEROME</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>16.95</v>
+        <v>379.5</v>
       </c>
       <c r="C41" t="n">
-        <v>17.85</v>
+        <v>398.45</v>
       </c>
       <c r="D41" t="n">
-        <v>5.31</v>
+        <v>4.99</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>17.15</v>
+        <v>390</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>-3.92</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MUNJALSHOW</t>
+          <t>KDL</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>123.39</v>
+        <v>132.4</v>
       </c>
       <c r="C42" t="n">
-        <v>129.89</v>
+        <v>139</v>
       </c>
       <c r="D42" t="n">
-        <v>5.27</v>
+        <v>4.98</v>
       </c>
       <c r="E42" t="b">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>125.67</v>
+        <v>139</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>-3.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FILATFASH</t>
+          <t>AFIL</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.19</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="C43" t="n">
-        <v>0.2</v>
+        <v>8.69</v>
       </c>
       <c r="D43" t="n">
-        <v>5.26</v>
+        <v>4.95</v>
       </c>
       <c r="E43" t="b">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2</v>
+        <v>8.4</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>-3.34</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SUMIT</t>
+          <t>MANILAM</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>34.98</v>
+        <v>55.7</v>
       </c>
       <c r="C44" t="n">
-        <v>36.8</v>
+        <v>58.45</v>
       </c>
       <c r="D44" t="n">
-        <v>5.2</v>
+        <v>4.94</v>
       </c>
       <c r="E44" t="b">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>34.88</v>
+        <v>58.45</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>-5.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LATTEYS</t>
+          <t>ROTO</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>19.78</v>
+        <v>54.38</v>
       </c>
       <c r="C45" t="n">
-        <v>20.8</v>
+        <v>57</v>
       </c>
       <c r="D45" t="n">
-        <v>5.16</v>
+        <v>4.82</v>
       </c>
       <c r="E45" t="b">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>20.25</v>
+        <v>61.91</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>-2.64</v>
+        <v>8.609999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>JHS</t>
+          <t>PRITI</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>8.56</v>
+        <v>35.5</v>
       </c>
       <c r="C46" t="n">
-        <v>9</v>
+        <v>37.2</v>
       </c>
       <c r="D46" t="n">
-        <v>5.14</v>
+        <v>4.79</v>
       </c>
       <c r="E46" t="b">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>8.99</v>
+        <v>36.99</v>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>-0.11</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TARACHAND</t>
+          <t>PRAXIS</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>57.08</v>
+        <v>6.74</v>
       </c>
       <c r="C47" t="n">
-        <v>59.99</v>
+        <v>7.06</v>
       </c>
       <c r="D47" t="n">
-        <v>5.1</v>
+        <v>4.75</v>
       </c>
       <c r="E47" t="b">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>59</v>
+        <v>6.85</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>-1.65</v>
+        <v>-2.97</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>KDL</t>
+          <t>AIROLAM</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>126.1</v>
+        <v>87.81</v>
       </c>
       <c r="C48" t="n">
-        <v>132.4</v>
+        <v>91.94</v>
       </c>
       <c r="D48" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="E48" t="b">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>132.4</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>-2.76</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S&amp;SPOWER</t>
+          <t>ATLASCYCLE</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>347.6</v>
+        <v>82.91</v>
       </c>
       <c r="C49" t="n">
-        <v>364.95</v>
+        <v>86.8</v>
       </c>
       <c r="D49" t="n">
-        <v>4.99</v>
+        <v>4.69</v>
       </c>
       <c r="E49" t="b">
         <v>0</v>
       </c>
-      <c r="F49" t="inlineStr"/>
+      <c r="F49" t="n">
+        <v>85.89</v>
+      </c>
       <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="H49" t="n">
+        <v>-1.05</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CURAA</t>
+          <t>RHFL</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>94.18000000000001</v>
+        <v>2.35</v>
       </c>
       <c r="C50" t="n">
-        <v>98.88</v>
+        <v>2.46</v>
       </c>
       <c r="D50" t="n">
-        <v>4.99</v>
+        <v>4.68</v>
       </c>
       <c r="E50" t="b">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>98.88</v>
+        <v>2.46</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
@@ -1731,3923 +1735,3923 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TECHLABS</t>
+          <t>TFL</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>223.9</v>
+        <v>12.9</v>
       </c>
       <c r="C51" t="n">
-        <v>235</v>
+        <v>13.5</v>
       </c>
       <c r="D51" t="n">
-        <v>4.96</v>
+        <v>4.65</v>
       </c>
       <c r="E51" t="b">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>235.05</v>
+        <v>13.4</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>0.02</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SECMARK</t>
+          <t>POLYSIL</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>109.95</v>
+        <v>191.1</v>
       </c>
       <c r="C52" t="n">
-        <v>115.4</v>
+        <v>199.95</v>
       </c>
       <c r="D52" t="n">
-        <v>4.96</v>
+        <v>4.63</v>
       </c>
       <c r="E52" t="b">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>117.9</v>
+        <v>197.9</v>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>2.17</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NEUEON</t>
+          <t>REPRO</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>13.76</v>
+        <v>381.45</v>
       </c>
       <c r="C53" t="n">
-        <v>14.44</v>
+        <v>399</v>
       </c>
       <c r="D53" t="n">
-        <v>4.94</v>
+        <v>4.6</v>
       </c>
       <c r="E53" t="b">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>14.44</v>
+        <v>384.85</v>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>-3.55</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AFIL</t>
+          <t>KOTYARK</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>7.89</v>
+        <v>310.7</v>
       </c>
       <c r="C54" t="n">
-        <v>8.279999999999999</v>
+        <v>325</v>
       </c>
       <c r="D54" t="n">
-        <v>4.94</v>
+        <v>4.6</v>
       </c>
       <c r="E54" t="b">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>8.279999999999999</v>
+        <v>325.05</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MALLCOM</t>
+          <t>HGINFRA</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1047</v>
+        <v>490.55</v>
       </c>
       <c r="C55" t="n">
-        <v>1098</v>
+        <v>513</v>
       </c>
       <c r="D55" t="n">
-        <v>4.87</v>
+        <v>4.58</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>1065.2</v>
+        <v>552.3</v>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>-2.99</v>
+        <v>7.66</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>VIVIMEDLAB</t>
+          <t>MANOMAY</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>6.79</v>
+        <v>218.05</v>
       </c>
       <c r="C56" t="n">
-        <v>7.12</v>
+        <v>228</v>
       </c>
       <c r="D56" t="n">
-        <v>4.86</v>
+        <v>4.56</v>
       </c>
       <c r="E56" t="b">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>6.81</v>
+        <v>224</v>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>-4.35</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DGCONTENT</t>
+          <t>INDIANHUME</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>24.32</v>
+        <v>317.4</v>
       </c>
       <c r="C57" t="n">
-        <v>25.5</v>
+        <v>331.85</v>
       </c>
       <c r="D57" t="n">
-        <v>4.85</v>
+        <v>4.55</v>
       </c>
       <c r="E57" t="b">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>24.27</v>
+        <v>364</v>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>-4.82</v>
+        <v>9.69</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>IMPEXFERRO</t>
+          <t>AURIGROW</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1.66</v>
+        <v>0.22</v>
       </c>
       <c r="C58" t="n">
-        <v>1.74</v>
+        <v>0.23</v>
       </c>
       <c r="D58" t="n">
-        <v>4.82</v>
+        <v>4.55</v>
       </c>
       <c r="E58" t="b">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>1.68</v>
+        <v>0.23</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>-3.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MAHAPEXLTD</t>
+          <t>JPASSOCIAT</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>107.62</v>
+        <v>2.43</v>
       </c>
       <c r="C59" t="n">
-        <v>112.8</v>
+        <v>2.54</v>
       </c>
       <c r="D59" t="n">
-        <v>4.81</v>
+        <v>4.53</v>
       </c>
       <c r="E59" t="b">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>107.99</v>
+        <v>2.55</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>-4.26</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>VIJIFIN</t>
+          <t>PAVNAIND</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2.29</v>
+        <v>18.66</v>
       </c>
       <c r="C60" t="n">
-        <v>2.4</v>
+        <v>19.5</v>
       </c>
       <c r="D60" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="E60" t="b">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>2.36</v>
+        <v>19.5</v>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>-1.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SANGINITA</t>
+          <t>RCOM</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>12.37</v>
+        <v>0.89</v>
       </c>
       <c r="C61" t="n">
-        <v>12.96</v>
+        <v>0.93</v>
       </c>
       <c r="D61" t="n">
-        <v>4.77</v>
+        <v>4.49</v>
       </c>
       <c r="E61" t="b">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>12.4</v>
+        <v>0.93</v>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>-4.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EUROTEXIND</t>
+          <t>NEPTUNE</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>13.27</v>
+        <v>210.25</v>
       </c>
       <c r="C62" t="n">
-        <v>13.9</v>
+        <v>219.7</v>
       </c>
       <c r="D62" t="n">
-        <v>4.75</v>
+        <v>4.49</v>
       </c>
       <c r="E62" t="b">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>12.62</v>
+        <v>220</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>-9.210000000000001</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BLBLIMITED</t>
+          <t>TRUST</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>17.28</v>
+        <v>32.5</v>
       </c>
       <c r="C63" t="n">
-        <v>18.1</v>
+        <v>33.95</v>
       </c>
       <c r="D63" t="n">
-        <v>4.75</v>
+        <v>4.46</v>
       </c>
       <c r="E63" t="b">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>17.62</v>
+        <v>32.05</v>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>-2.65</v>
+        <v>-5.6</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CAPTRUST</t>
+          <t>DIGISPICE</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>12.02</v>
+        <v>17.7</v>
       </c>
       <c r="C64" t="n">
-        <v>12.59</v>
+        <v>18.49</v>
       </c>
       <c r="D64" t="n">
-        <v>4.74</v>
+        <v>4.46</v>
       </c>
       <c r="E64" t="b">
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>12.11</v>
+        <v>18</v>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>-3.81</v>
+        <v>-2.65</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>JAIPURKURT</t>
+          <t>TCIFINANCE</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>29.55</v>
+        <v>14.13</v>
       </c>
       <c r="C65" t="n">
-        <v>30.95</v>
+        <v>14.75</v>
       </c>
       <c r="D65" t="n">
-        <v>4.74</v>
+        <v>4.39</v>
       </c>
       <c r="E65" t="b">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>31.37</v>
+        <v>14.83</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>1.36</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DELAPLEX</t>
+          <t>SPMLINFRA</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>97.40000000000001</v>
+        <v>161.9</v>
       </c>
       <c r="C66" t="n">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="D66" t="n">
-        <v>4.72</v>
+        <v>4.39</v>
       </c>
       <c r="E66" t="b">
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>107</v>
+        <v>187.99</v>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>4.9</v>
+        <v>11.24</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FELDVR</t>
+          <t>MOTOGENFIN</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2.97</v>
+        <v>19.84</v>
       </c>
       <c r="C67" t="n">
-        <v>3.11</v>
+        <v>20.7</v>
       </c>
       <c r="D67" t="n">
-        <v>4.71</v>
+        <v>4.33</v>
       </c>
       <c r="E67" t="b">
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>2.83</v>
+        <v>20.6</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>-9</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MAHESHWARI</t>
+          <t>VPRPL</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>42</v>
+        <v>38.58</v>
       </c>
       <c r="C68" t="n">
-        <v>43.98</v>
+        <v>40.24</v>
       </c>
       <c r="D68" t="n">
-        <v>4.71</v>
+        <v>4.3</v>
       </c>
       <c r="E68" t="b">
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>41.68</v>
+        <v>42.29</v>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>-5.23</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CELEBRITY</t>
+          <t>VILAS</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>7.48</v>
+        <v>348.05</v>
       </c>
       <c r="C69" t="n">
-        <v>7.83</v>
+        <v>363</v>
       </c>
       <c r="D69" t="n">
-        <v>4.68</v>
+        <v>4.3</v>
       </c>
       <c r="E69" t="b">
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>7.5</v>
+        <v>355</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>-4.21</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PARIN</t>
+          <t>BVCL</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>687.95</v>
+        <v>39.6</v>
       </c>
       <c r="C70" t="n">
-        <v>720</v>
+        <v>41.25</v>
       </c>
       <c r="D70" t="n">
-        <v>4.66</v>
+        <v>4.17</v>
       </c>
       <c r="E70" t="b">
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>720</v>
+        <v>40.4</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TRACXN</t>
+          <t>ORCHASP</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>33.14</v>
+        <v>2.2</v>
       </c>
       <c r="C71" t="n">
-        <v>34.67</v>
+        <v>2.29</v>
       </c>
       <c r="D71" t="n">
-        <v>4.62</v>
+        <v>4.09</v>
       </c>
       <c r="E71" t="b">
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>33.92</v>
+        <v>2.24</v>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>-2.16</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>RKSWAMY</t>
+          <t>SHANTI</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>95.51000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="C72" t="n">
-        <v>99.90000000000001</v>
+        <v>6.66</v>
       </c>
       <c r="D72" t="n">
-        <v>4.6</v>
+        <v>4.06</v>
       </c>
       <c r="E72" t="b">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>96.92</v>
+        <v>6.41</v>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>-2.98</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MANOMAY</t>
+          <t>PPSL</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>214</v>
+        <v>6.2</v>
       </c>
       <c r="C73" t="n">
-        <v>223.8</v>
+        <v>6.45</v>
       </c>
       <c r="D73" t="n">
-        <v>4.58</v>
+        <v>4.03</v>
       </c>
       <c r="E73" t="b">
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>217</v>
+        <v>6.4</v>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>-3.04</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>GATECHDVR</t>
+          <t>KRONOX</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.44</v>
+        <v>114.39</v>
       </c>
       <c r="C74" t="n">
-        <v>0.46</v>
+        <v>118.95</v>
       </c>
       <c r="D74" t="n">
-        <v>4.55</v>
+        <v>3.99</v>
       </c>
       <c r="E74" t="b">
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>0.45</v>
+        <v>114.18</v>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>-2.17</v>
+        <v>-4.01</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PRITIKAUTO</t>
+          <t>SANCO</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>12.32</v>
+        <v>2.27</v>
       </c>
       <c r="C75" t="n">
-        <v>12.88</v>
+        <v>2.36</v>
       </c>
       <c r="D75" t="n">
-        <v>4.55</v>
+        <v>3.96</v>
       </c>
       <c r="E75" t="b">
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>12.7</v>
+        <v>2.36</v>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>-1.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TCIFINANCE</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>13.68</v>
+        <v>7.07</v>
       </c>
       <c r="C76" t="n">
-        <v>14.3</v>
+        <v>7.35</v>
       </c>
       <c r="D76" t="n">
-        <v>4.53</v>
+        <v>3.96</v>
       </c>
       <c r="E76" t="b">
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>14.09</v>
+        <v>7.2</v>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>-1.47</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BHARATSE</t>
+          <t>KSOLVES</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>170.69</v>
+        <v>287.05</v>
       </c>
       <c r="C77" t="n">
-        <v>178.37</v>
+        <v>298.4</v>
       </c>
       <c r="D77" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="E77" t="b">
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>175.01</v>
+        <v>291.15</v>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>-1.88</v>
+        <v>-2.43</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>KARMAENG</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>3613.2</v>
+        <v>37.52</v>
       </c>
       <c r="C78" t="n">
-        <v>3775.6</v>
+        <v>39</v>
       </c>
       <c r="D78" t="n">
-        <v>4.49</v>
+        <v>3.94</v>
       </c>
       <c r="E78" t="b">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>3723.4</v>
+        <v>38.1</v>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>-1.38</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GUJRAFFIA</t>
+          <t>PEARLPOLY</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>39.48</v>
+        <v>17.71</v>
       </c>
       <c r="C79" t="n">
-        <v>41.25</v>
+        <v>18.4</v>
       </c>
       <c r="D79" t="n">
-        <v>4.48</v>
+        <v>3.9</v>
       </c>
       <c r="E79" t="b">
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>39.03</v>
+        <v>17.75</v>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>-5.38</v>
+        <v>-3.53</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CINELINE</t>
+          <t>CCCL</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>85.94</v>
+        <v>15.66</v>
       </c>
       <c r="C80" t="n">
-        <v>89.77</v>
+        <v>16.27</v>
       </c>
       <c r="D80" t="n">
-        <v>4.46</v>
+        <v>3.9</v>
       </c>
       <c r="E80" t="b">
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>88</v>
+        <v>15.9</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>-1.97</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>AKG</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>174.24</v>
+        <v>10.71</v>
       </c>
       <c r="C81" t="n">
-        <v>182</v>
+        <v>11.12</v>
       </c>
       <c r="D81" t="n">
-        <v>4.45</v>
+        <v>3.83</v>
       </c>
       <c r="E81" t="b">
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>177.77</v>
+        <v>10.89</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>-2.32</v>
+        <v>-2.07</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5PAISA</t>
+          <t>FRESHARA</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>296.8</v>
+        <v>186.3</v>
       </c>
       <c r="C82" t="n">
-        <v>310</v>
+        <v>193.4</v>
       </c>
       <c r="D82" t="n">
-        <v>4.45</v>
+        <v>3.81</v>
       </c>
       <c r="E82" t="b">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>302</v>
+        <v>187.4</v>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>-2.58</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>TREJHARA</t>
+          <t>WEWIN</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>166.58</v>
+        <v>41.42</v>
       </c>
       <c r="C83" t="n">
-        <v>173.98</v>
+        <v>42.99</v>
       </c>
       <c r="D83" t="n">
-        <v>4.44</v>
+        <v>3.79</v>
       </c>
       <c r="E83" t="b">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>171.14</v>
+        <v>41.99</v>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>-1.63</v>
+        <v>-2.33</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>GTL</t>
+          <t>EBGNG</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>6.55</v>
+        <v>356.6</v>
       </c>
       <c r="C84" t="n">
-        <v>6.84</v>
+        <v>370</v>
       </c>
       <c r="D84" t="n">
-        <v>4.43</v>
+        <v>3.76</v>
       </c>
       <c r="E84" t="b">
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>6.66</v>
+        <v>374.4</v>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>-2.63</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DCMNVL</t>
+          <t>OMINFRAL</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>121.36</v>
+        <v>81.75</v>
       </c>
       <c r="C85" t="n">
-        <v>126.7</v>
+        <v>84.8</v>
       </c>
       <c r="D85" t="n">
-        <v>4.4</v>
+        <v>3.73</v>
       </c>
       <c r="E85" t="b">
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>122.99</v>
+        <v>88.63</v>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>-2.93</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MIRCELECTR</t>
+          <t>EXCEL</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>23.87</v>
+        <v>1.08</v>
       </c>
       <c r="C86" t="n">
-        <v>24.92</v>
+        <v>1.12</v>
       </c>
       <c r="D86" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="E86" t="b">
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>24.97</v>
+        <v>1.17</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>0.2</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CHEMBONDCH</t>
+          <t>AVONMORE</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>133.95</v>
+        <v>13.72</v>
       </c>
       <c r="C87" t="n">
-        <v>139.8</v>
+        <v>14.22</v>
       </c>
       <c r="D87" t="n">
-        <v>4.37</v>
+        <v>3.64</v>
       </c>
       <c r="E87" t="b">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>134.01</v>
+        <v>14.11</v>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>-4.14</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>TOLINS</t>
+          <t>VINEETLAB</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>98.70999999999999</v>
+        <v>29.92</v>
       </c>
       <c r="C88" t="n">
-        <v>102.98</v>
+        <v>31</v>
       </c>
       <c r="D88" t="n">
-        <v>4.33</v>
+        <v>3.61</v>
       </c>
       <c r="E88" t="b">
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>100.64</v>
+        <v>30.37</v>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>-2.27</v>
+        <v>-2.03</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>TEJASNET</t>
+          <t>JISLDVREQS</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>426.1</v>
+        <v>20.5</v>
       </c>
       <c r="C89" t="n">
-        <v>444.4</v>
+        <v>21.24</v>
       </c>
       <c r="D89" t="n">
-        <v>4.29</v>
+        <v>3.61</v>
       </c>
       <c r="E89" t="b">
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>458.95</v>
+        <v>22.85</v>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>3.27</v>
+        <v>7.58</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AVROIND</t>
+          <t>NIRAJ</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>127.54</v>
+        <v>27.5</v>
       </c>
       <c r="C90" t="n">
-        <v>132.99</v>
+        <v>28.49</v>
       </c>
       <c r="D90" t="n">
-        <v>4.27</v>
+        <v>3.6</v>
       </c>
       <c r="E90" t="b">
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>133.33</v>
+        <v>28.26</v>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>0.26</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>INDOAMIN</t>
+          <t>HARRMALAYA</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>97.44</v>
+        <v>181.47</v>
       </c>
       <c r="C91" t="n">
-        <v>101.6</v>
+        <v>188</v>
       </c>
       <c r="D91" t="n">
-        <v>4.27</v>
+        <v>3.6</v>
       </c>
       <c r="E91" t="b">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>100.64</v>
+        <v>184.03</v>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SMLT</t>
+          <t>LFIC</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>68.48</v>
+        <v>130.31</v>
       </c>
       <c r="C92" t="n">
-        <v>71.40000000000001</v>
+        <v>134.99</v>
       </c>
       <c r="D92" t="n">
-        <v>4.26</v>
+        <v>3.59</v>
       </c>
       <c r="E92" t="b">
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>70.87</v>
+        <v>134.75</v>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
-        <v>-0.74</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>KNAGRI</t>
+          <t>IL&amp;FSTRANS</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>178.16</v>
+        <v>2.28</v>
       </c>
       <c r="C93" t="n">
-        <v>185.7</v>
+        <v>2.36</v>
       </c>
       <c r="D93" t="n">
-        <v>4.23</v>
+        <v>3.51</v>
       </c>
       <c r="E93" t="b">
         <v>0</v>
       </c>
-      <c r="F93" t="n">
-        <v>182.96</v>
-      </c>
+      <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
-      <c r="H93" t="n">
-        <v>-1.48</v>
-      </c>
+      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>RUBYMILLS</t>
+          <t>DAMODARIND</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>205.29</v>
+        <v>24.06</v>
       </c>
       <c r="C94" t="n">
-        <v>213.88</v>
+        <v>24.9</v>
       </c>
       <c r="D94" t="n">
-        <v>4.18</v>
+        <v>3.49</v>
       </c>
       <c r="E94" t="b">
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>208.9</v>
+        <v>24.19</v>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>-2.33</v>
+        <v>-2.85</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>JPOLYINVST</t>
+          <t>CYBERTECH</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1315</v>
+        <v>105.14</v>
       </c>
       <c r="C95" t="n">
-        <v>1369.7</v>
+        <v>108.8</v>
       </c>
       <c r="D95" t="n">
-        <v>4.16</v>
+        <v>3.48</v>
       </c>
       <c r="E95" t="b">
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>1406.8</v>
+        <v>107.92</v>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>2.71</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>VAISHALI</t>
+          <t>NAGAFERT</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>6.51</v>
+        <v>4.32</v>
       </c>
       <c r="C96" t="n">
-        <v>6.78</v>
+        <v>4.47</v>
       </c>
       <c r="D96" t="n">
-        <v>4.15</v>
+        <v>3.47</v>
       </c>
       <c r="E96" t="b">
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>6.58</v>
+        <v>4.41</v>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>-2.95</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MINDACORP</t>
+          <t>JAIPURKURT</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>497.65</v>
+        <v>30.93</v>
       </c>
       <c r="C97" t="n">
-        <v>518</v>
+        <v>32</v>
       </c>
       <c r="D97" t="n">
-        <v>4.09</v>
+        <v>3.46</v>
       </c>
       <c r="E97" t="b">
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>509.55</v>
+        <v>31.35</v>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>-1.63</v>
+        <v>-2.03</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>KRITINUT</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>4236.7</v>
+        <v>63.03</v>
       </c>
       <c r="C98" t="n">
-        <v>4410</v>
+        <v>65.2</v>
       </c>
       <c r="D98" t="n">
-        <v>4.09</v>
+        <v>3.44</v>
       </c>
       <c r="E98" t="b">
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>4374</v>
+        <v>65.28</v>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>-0.82</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MANGALAM</t>
+          <t>ZODIAC</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>33.87</v>
+        <v>232.05</v>
       </c>
       <c r="C99" t="n">
-        <v>35.25</v>
+        <v>240</v>
       </c>
       <c r="D99" t="n">
-        <v>4.07</v>
+        <v>3.43</v>
       </c>
       <c r="E99" t="b">
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>33.1</v>
+        <v>235.98</v>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
-        <v>-6.1</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>IZMO</t>
+          <t>VSTL</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>711.2</v>
+        <v>107.35</v>
       </c>
       <c r="C100" t="n">
-        <v>740</v>
+        <v>111</v>
       </c>
       <c r="D100" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="E100" t="b">
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>745.8</v>
+        <v>108.96</v>
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>0.78</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>UNIVASTU</t>
+          <t>BAIDFIN</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>61.85</v>
+        <v>11.08</v>
       </c>
       <c r="C101" t="n">
-        <v>64.34999999999999</v>
+        <v>11.45</v>
       </c>
       <c r="D101" t="n">
-        <v>4.04</v>
+        <v>3.34</v>
       </c>
       <c r="E101" t="b">
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>62.66</v>
+        <v>11.21</v>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>-2.63</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MCLEODRUSS</t>
+          <t>PREMIER</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>36.44</v>
+        <v>2.99</v>
       </c>
       <c r="C102" t="n">
-        <v>37.9</v>
+        <v>3.09</v>
       </c>
       <c r="D102" t="n">
-        <v>4.01</v>
+        <v>3.34</v>
       </c>
       <c r="E102" t="b">
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>40.08</v>
+        <v>2.99</v>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>5.75</v>
+        <v>-3.24</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>KRYSTAL</t>
+          <t>SHEKHAWATI</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>577.05</v>
+        <v>11.99</v>
       </c>
       <c r="C103" t="n">
-        <v>600.05</v>
+        <v>12.39</v>
       </c>
       <c r="D103" t="n">
-        <v>3.99</v>
+        <v>3.34</v>
       </c>
       <c r="E103" t="b">
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>604.7</v>
+        <v>12.33</v>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>0.77</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ISFT</t>
+          <t>AURUM</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>67.33</v>
+        <v>168.43</v>
       </c>
       <c r="C104" t="n">
-        <v>70</v>
+        <v>173.99</v>
       </c>
       <c r="D104" t="n">
-        <v>3.97</v>
+        <v>3.3</v>
       </c>
       <c r="E104" t="b">
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>67.72</v>
+        <v>169.59</v>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
-        <v>-3.26</v>
+        <v>-2.53</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SUVIDHAA</t>
+          <t>TAC</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>2.78</v>
+        <v>452.4</v>
       </c>
       <c r="C105" t="n">
-        <v>2.89</v>
+        <v>467.1</v>
       </c>
       <c r="D105" t="n">
-        <v>3.96</v>
+        <v>3.25</v>
       </c>
       <c r="E105" t="b">
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>2.81</v>
+        <v>476</v>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>-2.77</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>REPRO</t>
+          <t>FOODSIN</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>379.8</v>
+        <v>59.96</v>
       </c>
       <c r="C106" t="n">
-        <v>394.85</v>
+        <v>61.9</v>
       </c>
       <c r="D106" t="n">
-        <v>3.96</v>
+        <v>3.24</v>
       </c>
       <c r="E106" t="b">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>382.6</v>
+        <v>59.2</v>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
-        <v>-3.1</v>
+        <v>-4.36</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>GICL</t>
+          <t>JAIBALAJI</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>44.96</v>
+        <v>61.03</v>
       </c>
       <c r="C107" t="n">
-        <v>46.74</v>
+        <v>63</v>
       </c>
       <c r="D107" t="n">
-        <v>3.96</v>
+        <v>3.23</v>
       </c>
       <c r="E107" t="b">
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>-3.72</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>KAPSTON</t>
+          <t>RELCHEMQ</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>291.5</v>
+        <v>112.03</v>
       </c>
       <c r="C108" t="n">
-        <v>303</v>
+        <v>115.65</v>
       </c>
       <c r="D108" t="n">
-        <v>3.95</v>
+        <v>3.23</v>
       </c>
       <c r="E108" t="b">
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>285.3</v>
+        <v>115.37</v>
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
-        <v>-5.84</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ASPINWALL</t>
+          <t>SADBHAV</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>209.77</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="C109" t="n">
-        <v>218</v>
+        <v>9</v>
       </c>
       <c r="D109" t="n">
-        <v>3.92</v>
+        <v>3.21</v>
       </c>
       <c r="E109" t="b">
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>209.27</v>
+        <v>9.15</v>
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>-4</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MOKSH</t>
+          <t>KAPSTON</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>11.52</v>
+        <v>283.9</v>
       </c>
       <c r="C110" t="n">
-        <v>11.97</v>
+        <v>293</v>
       </c>
       <c r="D110" t="n">
-        <v>3.91</v>
+        <v>3.21</v>
       </c>
       <c r="E110" t="b">
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>11.7</v>
+        <v>285</v>
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
-        <v>-2.26</v>
+        <v>-2.73</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>APS</t>
+          <t>TTKPRESTIG</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>294.4</v>
+        <v>484.5</v>
       </c>
       <c r="C111" t="n">
-        <v>305.9</v>
+        <v>499.95</v>
       </c>
       <c r="D111" t="n">
-        <v>3.91</v>
+        <v>3.19</v>
       </c>
       <c r="E111" t="b">
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>304.6</v>
+        <v>525.15</v>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>-0.42</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SOUTHWEST</t>
+          <t>OCCLLTD</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>197.23</v>
+        <v>85.2</v>
       </c>
       <c r="C112" t="n">
-        <v>204.9</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D112" t="n">
-        <v>3.89</v>
+        <v>3.17</v>
       </c>
       <c r="E112" t="b">
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>199</v>
+        <v>85.7</v>
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
-        <v>-2.88</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SAMBHV</t>
+          <t>JINDALSAW</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>89.52</v>
+        <v>165.85</v>
       </c>
       <c r="C113" t="n">
-        <v>93</v>
+        <v>171</v>
       </c>
       <c r="D113" t="n">
-        <v>3.89</v>
+        <v>3.11</v>
       </c>
       <c r="E113" t="b">
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>92.40000000000001</v>
+        <v>188.08</v>
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>-0.65</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ANTGRAPHIC</t>
+          <t>RKSWAMY</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.78</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="C114" t="n">
-        <v>0.8100000000000001</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="D114" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="E114" t="b">
         <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>0.79</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
-        <v>-2.47</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BAGFILMS</t>
+          <t>JHS</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>4.94</v>
+        <v>9.06</v>
       </c>
       <c r="C115" t="n">
-        <v>5.13</v>
+        <v>9.34</v>
       </c>
       <c r="D115" t="n">
-        <v>3.85</v>
+        <v>3.09</v>
       </c>
       <c r="E115" t="b">
         <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>5.13</v>
+        <v>9.52</v>
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>WILLAMAGOR</t>
+          <t>HMAAGRO</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>26</v>
+        <v>24.64</v>
       </c>
       <c r="C116" t="n">
-        <v>27</v>
+        <v>25.4</v>
       </c>
       <c r="D116" t="n">
-        <v>3.85</v>
+        <v>3.08</v>
       </c>
       <c r="E116" t="b">
         <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>26.75</v>
+        <v>24.8</v>
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
-        <v>-0.93</v>
+        <v>-2.36</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>VIVIDHA</t>
+          <t>SITINET</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.52</v>
+        <v>0.33</v>
       </c>
       <c r="C117" t="n">
-        <v>0.54</v>
+        <v>0.34</v>
       </c>
       <c r="D117" t="n">
-        <v>3.85</v>
+        <v>3.03</v>
       </c>
       <c r="E117" t="b">
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>0.52</v>
+        <v>0.34</v>
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>-3.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>TREL</t>
+          <t>AAKASH</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>24.03</v>
+        <v>10.92</v>
       </c>
       <c r="C118" t="n">
-        <v>24.95</v>
+        <v>11.25</v>
       </c>
       <c r="D118" t="n">
-        <v>3.83</v>
+        <v>3.02</v>
       </c>
       <c r="E118" t="b">
         <v>0</v>
       </c>
       <c r="F118" t="n">
-        <v>25.05</v>
+        <v>10.51</v>
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
-        <v>0.4</v>
+        <v>-6.58</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>PLAZACABLE</t>
+          <t>ASHIMASYN</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>35.52</v>
+        <v>14.05</v>
       </c>
       <c r="C119" t="n">
-        <v>36.88</v>
+        <v>14.47</v>
       </c>
       <c r="D119" t="n">
-        <v>3.83</v>
+        <v>2.99</v>
       </c>
       <c r="E119" t="b">
         <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>35.32</v>
+        <v>14.35</v>
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
-        <v>-4.23</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STYL</t>
+          <t>SAURASHCEM</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>260.07</v>
+        <v>62.13</v>
       </c>
       <c r="C120" t="n">
-        <v>269.99</v>
+        <v>63.98</v>
       </c>
       <c r="D120" t="n">
-        <v>3.81</v>
+        <v>2.98</v>
       </c>
       <c r="E120" t="b">
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>267.4</v>
+        <v>62.93</v>
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
-        <v>-0.96</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SILGO</t>
+          <t>BAGFILMS</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>71.3</v>
+        <v>5.03</v>
       </c>
       <c r="C121" t="n">
-        <v>74</v>
+        <v>5.18</v>
       </c>
       <c r="D121" t="n">
-        <v>3.79</v>
+        <v>2.98</v>
       </c>
       <c r="E121" t="b">
         <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>76.5</v>
+        <v>5.07</v>
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
-        <v>3.38</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>RANASUG</t>
+          <t>MADHAV</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>11.9</v>
+        <v>36.76</v>
       </c>
       <c r="C122" t="n">
-        <v>12.35</v>
+        <v>37.85</v>
       </c>
       <c r="D122" t="n">
-        <v>3.78</v>
+        <v>2.97</v>
       </c>
       <c r="E122" t="b">
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>12.11</v>
+        <v>36.61</v>
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
-        <v>-1.94</v>
+        <v>-3.28</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CONSOFINVT</t>
+          <t>MONEYBOXX</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>227.36</v>
+        <v>68.95</v>
       </c>
       <c r="C123" t="n">
-        <v>235.95</v>
+        <v>71</v>
       </c>
       <c r="D123" t="n">
-        <v>3.78</v>
+        <v>2.97</v>
       </c>
       <c r="E123" t="b">
         <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>227.01</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>-3.79</v>
+        <v>-4.92</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>PRABHA</t>
+          <t>UNITEDPOLY</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>151.78</v>
+        <v>26.22</v>
       </c>
       <c r="C124" t="n">
-        <v>157.5</v>
+        <v>27</v>
       </c>
       <c r="D124" t="n">
-        <v>3.77</v>
+        <v>2.97</v>
       </c>
       <c r="E124" t="b">
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>151</v>
+        <v>27.53</v>
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
-        <v>-4.13</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SUVEN</t>
+          <t>PATINTLOG</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>135.88</v>
+        <v>10.15</v>
       </c>
       <c r="C125" t="n">
-        <v>140.99</v>
+        <v>10.45</v>
       </c>
       <c r="D125" t="n">
-        <v>3.76</v>
+        <v>2.96</v>
       </c>
       <c r="E125" t="b">
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>137.89</v>
+        <v>10.18</v>
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>-2.2</v>
+        <v>-2.58</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>KARMAENG</t>
+          <t>RADIOCITY</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>37.3</v>
+        <v>5.78</v>
       </c>
       <c r="C126" t="n">
-        <v>38.7</v>
+        <v>5.95</v>
       </c>
       <c r="D126" t="n">
-        <v>3.75</v>
+        <v>2.94</v>
       </c>
       <c r="E126" t="b">
         <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>38.8</v>
+        <v>5.8</v>
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
-        <v>0.26</v>
+        <v>-2.52</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MURUDCERA</t>
+          <t>BASML</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>30.65</v>
+        <v>20.78</v>
       </c>
       <c r="C127" t="n">
-        <v>31.8</v>
+        <v>21.39</v>
       </c>
       <c r="D127" t="n">
-        <v>3.75</v>
+        <v>2.94</v>
       </c>
       <c r="E127" t="b">
         <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>31.6</v>
+        <v>20.99</v>
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
-        <v>-0.63</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>VALIANTLAB</t>
+          <t>ABAN</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>55.77</v>
+        <v>24.58</v>
       </c>
       <c r="C128" t="n">
-        <v>57.85</v>
+        <v>25.3</v>
       </c>
       <c r="D128" t="n">
-        <v>3.73</v>
+        <v>2.93</v>
       </c>
       <c r="E128" t="b">
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>55.01</v>
+        <v>25.8</v>
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
-        <v>-4.91</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>HMAAGRO</t>
+          <t>EMKAY</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>24.11</v>
+        <v>220.57</v>
       </c>
       <c r="C129" t="n">
-        <v>25</v>
+        <v>227</v>
       </c>
       <c r="D129" t="n">
-        <v>3.69</v>
+        <v>2.92</v>
       </c>
       <c r="E129" t="b">
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>24.45</v>
+        <v>226.52</v>
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
-        <v>-2.2</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>KRITINUT</t>
+          <t>HLVLTD</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>61.63</v>
+        <v>7.6</v>
       </c>
       <c r="C130" t="n">
-        <v>63.9</v>
+        <v>7.82</v>
       </c>
       <c r="D130" t="n">
-        <v>3.68</v>
+        <v>2.89</v>
       </c>
       <c r="E130" t="b">
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>61.85</v>
+        <v>7.79</v>
       </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
-        <v>-3.21</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SAHYADRI</t>
+          <t>STYLEBAAZA</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>234.4</v>
+        <v>275.15</v>
       </c>
       <c r="C131" t="n">
-        <v>243</v>
+        <v>283</v>
       </c>
       <c r="D131" t="n">
-        <v>3.67</v>
+        <v>2.85</v>
       </c>
       <c r="E131" t="b">
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>238.55</v>
+        <v>282.35</v>
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
-        <v>-1.83</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>NAGAFERT</t>
+          <t>PARASPETRO</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>4.1</v>
+        <v>2.13</v>
       </c>
       <c r="C132" t="n">
-        <v>4.25</v>
+        <v>2.19</v>
       </c>
       <c r="D132" t="n">
-        <v>3.66</v>
+        <v>2.82</v>
       </c>
       <c r="E132" t="b">
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>4.25</v>
+        <v>2.13</v>
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
-        <v>0</v>
+        <v>-2.74</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>GKENERGY</t>
+          <t>SUMEETINDS</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>100.4</v>
+        <v>30.06</v>
       </c>
       <c r="C133" t="n">
-        <v>104.05</v>
+        <v>30.9</v>
       </c>
       <c r="D133" t="n">
-        <v>3.64</v>
+        <v>2.79</v>
       </c>
       <c r="E133" t="b">
         <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>102.69</v>
+        <v>30.02</v>
       </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
-        <v>-1.31</v>
+        <v>-2.85</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ABAN</t>
+          <t>GULFPETRO</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>23.41</v>
+        <v>30.95</v>
       </c>
       <c r="C134" t="n">
-        <v>24.26</v>
+        <v>31.8</v>
       </c>
       <c r="D134" t="n">
-        <v>3.63</v>
+        <v>2.75</v>
       </c>
       <c r="E134" t="b">
         <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>24.58</v>
+        <v>31.14</v>
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
-        <v>1.32</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>RKDL</t>
+          <t>AARVI</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>18.63</v>
+        <v>132.8</v>
       </c>
       <c r="C135" t="n">
-        <v>19.3</v>
+        <v>136.4</v>
       </c>
       <c r="D135" t="n">
-        <v>3.6</v>
+        <v>2.71</v>
       </c>
       <c r="E135" t="b">
         <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>19.15</v>
+        <v>132.21</v>
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
-        <v>-0.78</v>
+        <v>-3.07</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>GINNIFILA</t>
+          <t>THEMISMED</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>33.05</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="C136" t="n">
-        <v>34.24</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="D136" t="n">
-        <v>3.6</v>
+        <v>2.68</v>
       </c>
       <c r="E136" t="b">
         <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>34.04</v>
+        <v>83.78</v>
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
-        <v>-0.58</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>RHFL</t>
+          <t>TEXMOPIPES</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>2.24</v>
+        <v>42.15</v>
       </c>
       <c r="C137" t="n">
-        <v>2.32</v>
+        <v>43.28</v>
       </c>
       <c r="D137" t="n">
-        <v>3.57</v>
+        <v>2.68</v>
       </c>
       <c r="E137" t="b">
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>2.35</v>
+        <v>45.2</v>
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
-        <v>1.29</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>NACLIND</t>
+          <t>TREL</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>117.81</v>
+        <v>24.6</v>
       </c>
       <c r="C138" t="n">
-        <v>121.99</v>
+        <v>25.25</v>
       </c>
       <c r="D138" t="n">
-        <v>3.55</v>
+        <v>2.64</v>
       </c>
       <c r="E138" t="b">
         <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>119.8</v>
+        <v>24.44</v>
       </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
-        <v>-1.8</v>
+        <v>-3.21</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>VMM</t>
+          <t>RUBFILA</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>108.65</v>
+        <v>63.33</v>
       </c>
       <c r="C139" t="n">
-        <v>112.5</v>
+        <v>65</v>
       </c>
       <c r="D139" t="n">
-        <v>3.54</v>
+        <v>2.64</v>
       </c>
       <c r="E139" t="b">
         <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>110.27</v>
+        <v>64.77</v>
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
-        <v>-1.98</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>FOODSIN</t>
+          <t>YASHO</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>51.48</v>
+        <v>1393</v>
       </c>
       <c r="C140" t="n">
-        <v>53.3</v>
+        <v>1429.8</v>
       </c>
       <c r="D140" t="n">
-        <v>3.54</v>
+        <v>2.64</v>
       </c>
       <c r="E140" t="b">
         <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>53.89</v>
+        <v>1415.7</v>
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
-        <v>1.11</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>MOSCHIP</t>
+          <t>BOROLTD</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>168.08</v>
+        <v>253.25</v>
       </c>
       <c r="C141" t="n">
-        <v>174.02</v>
+        <v>259.92</v>
       </c>
       <c r="D141" t="n">
-        <v>3.53</v>
+        <v>2.63</v>
       </c>
       <c r="E141" t="b">
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>170.9</v>
+        <v>260.59</v>
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
-        <v>-1.79</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>SWELECTES</t>
+          <t>TOKYOPLAST</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>496.45</v>
+        <v>74.64</v>
       </c>
       <c r="C142" t="n">
-        <v>513.95</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="D142" t="n">
-        <v>3.53</v>
+        <v>2.63</v>
       </c>
       <c r="E142" t="b">
         <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>505.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
-        <v>-1.64</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>RCOM</t>
+          <t>AVG</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.85</v>
+        <v>135.85</v>
       </c>
       <c r="C143" t="n">
-        <v>0.88</v>
+        <v>139.4</v>
       </c>
       <c r="D143" t="n">
-        <v>3.53</v>
+        <v>2.61</v>
       </c>
       <c r="E143" t="b">
         <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>0.89</v>
+        <v>134.89</v>
       </c>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
-        <v>1.14</v>
+        <v>-3.24</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>JKTYRE</t>
+          <t>STEL</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>425.1</v>
+        <v>501.85</v>
       </c>
       <c r="C144" t="n">
-        <v>440</v>
+        <v>514.95</v>
       </c>
       <c r="D144" t="n">
-        <v>3.51</v>
+        <v>2.61</v>
       </c>
       <c r="E144" t="b">
         <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>436.3</v>
+        <v>497.4</v>
       </c>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
-        <v>-0.84</v>
+        <v>-3.41</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>HMVL</t>
+          <t>ISFT</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>60.75</v>
+        <v>69.02</v>
       </c>
       <c r="C145" t="n">
-        <v>62.88</v>
+        <v>70.8</v>
       </c>
       <c r="D145" t="n">
-        <v>3.51</v>
+        <v>2.58</v>
       </c>
       <c r="E145" t="b">
         <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>62</v>
+        <v>74.61</v>
       </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
-        <v>-1.4</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>CNL</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>1082.1</v>
+        <v>631.8</v>
       </c>
       <c r="C146" t="n">
-        <v>1120</v>
+        <v>648</v>
       </c>
       <c r="D146" t="n">
-        <v>3.5</v>
+        <v>2.56</v>
       </c>
       <c r="E146" t="b">
         <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>1114.8</v>
+        <v>637.95</v>
       </c>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
-        <v>-0.46</v>
+        <v>-1.55</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>TRIVENI</t>
+          <t>SETUINFRA</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>374.65</v>
+        <v>0.39</v>
       </c>
       <c r="C147" t="n">
-        <v>387.75</v>
+        <v>0.4</v>
       </c>
       <c r="D147" t="n">
-        <v>3.5</v>
+        <v>2.56</v>
       </c>
       <c r="E147" t="b">
         <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>368.4</v>
+        <v>0.38</v>
       </c>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
-        <v>-4.99</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SOLEX</t>
+          <t>AKSHAR</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>840.9</v>
+        <v>0.4</v>
       </c>
       <c r="C148" t="n">
-        <v>870.35</v>
+        <v>0.41</v>
       </c>
       <c r="D148" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="E148" t="b">
         <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>880.1</v>
+        <v>0.41</v>
       </c>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ORIENTTECH</t>
+          <t>LORDSCHLO</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>258.95</v>
+        <v>123.82</v>
       </c>
       <c r="C149" t="n">
-        <v>268</v>
+        <v>126.91</v>
       </c>
       <c r="D149" t="n">
-        <v>3.49</v>
+        <v>2.5</v>
       </c>
       <c r="E149" t="b">
         <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>263.55</v>
+        <v>124.66</v>
       </c>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
-        <v>-1.66</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ENCOMPAS</t>
+          <t>WAAREERTL</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>270.55</v>
+        <v>797.25</v>
       </c>
       <c r="C150" t="n">
-        <v>280</v>
+        <v>817.1</v>
       </c>
       <c r="D150" t="n">
-        <v>3.49</v>
+        <v>2.49</v>
       </c>
       <c r="E150" t="b">
         <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>280</v>
+        <v>830.1</v>
       </c>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ORIENTBELL</t>
+          <t>BALKRISHNA</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>280.25</v>
+        <v>12.88</v>
       </c>
       <c r="C151" t="n">
-        <v>290</v>
+        <v>13.2</v>
       </c>
       <c r="D151" t="n">
-        <v>3.48</v>
+        <v>2.48</v>
       </c>
       <c r="E151" t="b">
         <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>281.15</v>
+        <v>12.81</v>
       </c>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
-        <v>-3.05</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ORIENTPPR</t>
+          <t>RAMKY</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>16.66</v>
+        <v>458.7</v>
       </c>
       <c r="C152" t="n">
-        <v>17.24</v>
+        <v>470</v>
       </c>
       <c r="D152" t="n">
-        <v>3.48</v>
+        <v>2.46</v>
       </c>
       <c r="E152" t="b">
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>16.95</v>
+        <v>464.35</v>
       </c>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="n">
-        <v>-1.68</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>KHANDSE</t>
+          <t>MARKOLINES</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>17.87</v>
+        <v>152.96</v>
       </c>
       <c r="C153" t="n">
-        <v>18.49</v>
+        <v>156.7</v>
       </c>
       <c r="D153" t="n">
-        <v>3.47</v>
+        <v>2.45</v>
       </c>
       <c r="E153" t="b">
         <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>18.29</v>
+        <v>155.89</v>
       </c>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="n">
-        <v>-1.08</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>MODTHREAD</t>
+          <t>AKI</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>52.19</v>
+        <v>4.92</v>
       </c>
       <c r="C154" t="n">
-        <v>54</v>
+        <v>5.04</v>
       </c>
       <c r="D154" t="n">
-        <v>3.47</v>
+        <v>2.44</v>
       </c>
       <c r="E154" t="b">
         <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>51.87</v>
+        <v>4.97</v>
       </c>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="n">
-        <v>-3.94</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>TBZ</t>
+          <t>AHLADA</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>130.5</v>
+        <v>40.47</v>
       </c>
       <c r="C155" t="n">
-        <v>135</v>
+        <v>41.44</v>
       </c>
       <c r="D155" t="n">
-        <v>3.45</v>
+        <v>2.4</v>
       </c>
       <c r="E155" t="b">
         <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>133.33</v>
+        <v>43.75</v>
       </c>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="n">
-        <v>-1.24</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>MITTAL</t>
+          <t>TARSONS</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.88</v>
+        <v>194.34</v>
       </c>
       <c r="C156" t="n">
-        <v>0.91</v>
+        <v>199</v>
       </c>
       <c r="D156" t="n">
-        <v>3.41</v>
+        <v>2.4</v>
       </c>
       <c r="E156" t="b">
         <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>0.88</v>
+        <v>197.59</v>
       </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="n">
-        <v>-3.3</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>VIRINCHI</t>
+          <t>COMSYN</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>18.85</v>
+        <v>154.83</v>
       </c>
       <c r="C157" t="n">
-        <v>19.49</v>
+        <v>158.5</v>
       </c>
       <c r="D157" t="n">
-        <v>3.4</v>
+        <v>2.37</v>
       </c>
       <c r="E157" t="b">
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>19.21</v>
+        <v>155.61</v>
       </c>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="n">
-        <v>-1.44</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>AKI</t>
+          <t>FINPIPE</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>4.72</v>
+        <v>185.35</v>
       </c>
       <c r="C158" t="n">
-        <v>4.88</v>
+        <v>189.72</v>
       </c>
       <c r="D158" t="n">
-        <v>3.39</v>
+        <v>2.36</v>
       </c>
       <c r="E158" t="b">
         <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>4.94</v>
+        <v>190.48</v>
       </c>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="n">
-        <v>1.23</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>GKENERGY</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>1605.5</v>
+        <v>105.42</v>
       </c>
       <c r="C159" t="n">
-        <v>1660</v>
+        <v>107.9</v>
       </c>
       <c r="D159" t="n">
-        <v>3.39</v>
+        <v>2.35</v>
       </c>
       <c r="E159" t="b">
         <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>1617.1</v>
+        <v>110.69</v>
       </c>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="n">
-        <v>-2.58</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>RAMASTEEL</t>
+          <t>BHARATSE</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>5.92</v>
+        <v>175.88</v>
       </c>
       <c r="C160" t="n">
-        <v>6.12</v>
+        <v>180</v>
       </c>
       <c r="D160" t="n">
-        <v>3.38</v>
+        <v>2.34</v>
       </c>
       <c r="E160" t="b">
         <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>6</v>
+        <v>176.1</v>
       </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="n">
-        <v>-1.96</v>
+        <v>-2.17</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>INDOWIND</t>
+          <t>VIKASECO</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>8.94</v>
+        <v>1.29</v>
       </c>
       <c r="C161" t="n">
-        <v>9.24</v>
+        <v>1.32</v>
       </c>
       <c r="D161" t="n">
-        <v>3.36</v>
+        <v>2.33</v>
       </c>
       <c r="E161" t="b">
         <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>8.92</v>
+        <v>1.31</v>
       </c>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="n">
-        <v>-3.46</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>BAIDFIN</t>
+          <t>MITTAL</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>11.07</v>
+        <v>0.86</v>
       </c>
       <c r="C162" t="n">
-        <v>11.44</v>
+        <v>0.88</v>
       </c>
       <c r="D162" t="n">
-        <v>3.34</v>
+        <v>2.33</v>
       </c>
       <c r="E162" t="b">
         <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>11.01</v>
+        <v>0.86</v>
       </c>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="n">
-        <v>-3.76</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>COASTCORP</t>
+          <t>ESSENTIA</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>42.6</v>
+        <v>1.3</v>
       </c>
       <c r="C163" t="n">
-        <v>44</v>
+        <v>1.33</v>
       </c>
       <c r="D163" t="n">
-        <v>3.29</v>
+        <v>2.31</v>
       </c>
       <c r="E163" t="b">
         <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>45.34</v>
+        <v>1.32</v>
       </c>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="n">
-        <v>3.05</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>FIBERWEB</t>
+          <t>PYRAMID</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>37.45</v>
+        <v>148.89</v>
       </c>
       <c r="C164" t="n">
-        <v>38.68</v>
+        <v>152.3</v>
       </c>
       <c r="D164" t="n">
-        <v>3.28</v>
+        <v>2.29</v>
       </c>
       <c r="E164" t="b">
         <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>36.71</v>
+        <v>149.17</v>
       </c>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="n">
-        <v>-5.09</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ORIENTCER</t>
+          <t>MIRCELECTR</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>35.83</v>
+        <v>24.92</v>
       </c>
       <c r="C165" t="n">
-        <v>37</v>
+        <v>25.49</v>
       </c>
       <c r="D165" t="n">
-        <v>3.27</v>
+        <v>2.29</v>
       </c>
       <c r="E165" t="b">
         <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>36.79</v>
+        <v>25.79</v>
       </c>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="n">
-        <v>-0.57</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SOLARWORLD</t>
+          <t>JAYKAY</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>163.19</v>
+        <v>139.62</v>
       </c>
       <c r="C166" t="n">
-        <v>168.53</v>
+        <v>142.8</v>
       </c>
       <c r="D166" t="n">
-        <v>3.27</v>
+        <v>2.28</v>
       </c>
       <c r="E166" t="b">
         <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>166.57</v>
+        <v>138.21</v>
       </c>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="n">
-        <v>-1.16</v>
+        <v>-3.21</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>VASWANI</t>
+          <t>RUCHIRA</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>54.24</v>
+        <v>103.44</v>
       </c>
       <c r="C167" t="n">
-        <v>56</v>
+        <v>105.8</v>
       </c>
       <c r="D167" t="n">
-        <v>3.24</v>
+        <v>2.28</v>
       </c>
       <c r="E167" t="b">
         <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>54.6</v>
+        <v>104.42</v>
       </c>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="n">
-        <v>-2.5</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ROLEXRINGS</t>
+          <t>GINNIFILA</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>118.31</v>
+        <v>32.76</v>
       </c>
       <c r="C168" t="n">
-        <v>122.13</v>
+        <v>33.5</v>
       </c>
       <c r="D168" t="n">
-        <v>3.23</v>
+        <v>2.26</v>
       </c>
       <c r="E168" t="b">
         <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>120.1</v>
+        <v>35.98</v>
       </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="n">
-        <v>-1.66</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>KEYFINSERV</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>918.8</v>
+        <v>266.1</v>
       </c>
       <c r="C169" t="n">
-        <v>948.2</v>
+        <v>272</v>
       </c>
       <c r="D169" t="n">
-        <v>3.2</v>
+        <v>2.22</v>
       </c>
       <c r="E169" t="b">
         <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>961.25</v>
+        <v>271.5</v>
       </c>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="n">
-        <v>1.38</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>TBOTEK</t>
+          <t>GATECHDVR</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>1190</v>
+        <v>0.45</v>
       </c>
       <c r="C170" t="n">
-        <v>1228</v>
+        <v>0.46</v>
       </c>
       <c r="D170" t="n">
-        <v>3.19</v>
+        <v>2.22</v>
       </c>
       <c r="E170" t="b">
         <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>1185.4</v>
+        <v>0.46</v>
       </c>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="n">
-        <v>-3.47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>TECHD</t>
+          <t>KANANIIND</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>439.9</v>
+        <v>1.36</v>
       </c>
       <c r="C171" t="n">
-        <v>453.95</v>
+        <v>1.39</v>
       </c>
       <c r="D171" t="n">
-        <v>3.19</v>
+        <v>2.21</v>
       </c>
       <c r="E171" t="b">
         <v>0</v>
       </c>
       <c r="F171" t="n">
-        <v>464.5</v>
+        <v>1.35</v>
       </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="n">
-        <v>2.32</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>BSL</t>
+          <t>WANBURY</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>126.95</v>
+        <v>243.45</v>
       </c>
       <c r="C172" t="n">
-        <v>131</v>
+        <v>248.8</v>
       </c>
       <c r="D172" t="n">
-        <v>3.19</v>
+        <v>2.2</v>
       </c>
       <c r="E172" t="b">
         <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>129.75</v>
+        <v>244.15</v>
       </c>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="n">
-        <v>-0.95</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>AIMTRON</t>
+          <t>HITECH</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>754</v>
+        <v>79.16</v>
       </c>
       <c r="C173" t="n">
-        <v>777.9</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="D173" t="n">
-        <v>3.17</v>
+        <v>2.2</v>
       </c>
       <c r="E173" t="b">
         <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>771.8</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="n">
-        <v>-0.78</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>MRPL</t>
+          <t>RBZJEWEL</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>190.03</v>
+        <v>120.84</v>
       </c>
       <c r="C174" t="n">
-        <v>196</v>
+        <v>123.49</v>
       </c>
       <c r="D174" t="n">
-        <v>3.14</v>
+        <v>2.19</v>
       </c>
       <c r="E174" t="b">
         <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>190.75</v>
+        <v>120.69</v>
       </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="n">
-        <v>-2.68</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>PLASTIBLEN</t>
+          <t>VARDMNPOLY</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>135.65</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="C175" t="n">
-        <v>139.9</v>
+        <v>8.98</v>
       </c>
       <c r="D175" t="n">
-        <v>3.13</v>
+        <v>2.16</v>
       </c>
       <c r="E175" t="b">
         <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>139</v>
+        <v>8.84</v>
       </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="n">
-        <v>-0.64</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>HCL-INSYS</t>
+          <t>YAAP</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>12.21</v>
+        <v>141.75</v>
       </c>
       <c r="C176" t="n">
-        <v>12.59</v>
+        <v>144.8</v>
       </c>
       <c r="D176" t="n">
-        <v>3.11</v>
+        <v>2.15</v>
       </c>
       <c r="E176" t="b">
         <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>12.41</v>
+        <v>148.8</v>
       </c>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="n">
-        <v>-1.43</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>BCONCEPTS</t>
+          <t>OILCOUNTUB</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>237.65</v>
+        <v>46.01</v>
       </c>
       <c r="C177" t="n">
-        <v>245</v>
+        <v>46.99</v>
       </c>
       <c r="D177" t="n">
-        <v>3.09</v>
+        <v>2.13</v>
       </c>
       <c r="E177" t="b">
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>242</v>
+        <v>46.3</v>
       </c>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="n">
-        <v>-1.22</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>CCAVENUE</t>
+          <t>UFO</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>14.94</v>
+        <v>67.08</v>
       </c>
       <c r="C178" t="n">
-        <v>15.4</v>
+        <v>68.5</v>
       </c>
       <c r="D178" t="n">
-        <v>3.08</v>
+        <v>2.12</v>
       </c>
       <c r="E178" t="b">
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>15.04</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="n">
-        <v>-2.34</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>KROSS</t>
+          <t>DIFFNKG</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>183.6</v>
+        <v>263.15</v>
       </c>
       <c r="C179" t="n">
-        <v>189.23</v>
+        <v>268.7</v>
       </c>
       <c r="D179" t="n">
-        <v>3.07</v>
+        <v>2.11</v>
       </c>
       <c r="E179" t="b">
         <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>190.54</v>
+        <v>267.4</v>
       </c>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>EDELWEISS</t>
+          <t>DRONE</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>105.66</v>
+        <v>45.1</v>
       </c>
       <c r="C180" t="n">
-        <v>108.9</v>
+        <v>46.05</v>
       </c>
       <c r="D180" t="n">
-        <v>3.07</v>
+        <v>2.11</v>
       </c>
       <c r="E180" t="b">
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>106.68</v>
+        <v>47.3</v>
       </c>
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="n">
-        <v>-2.04</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>AWHCL</t>
+          <t>ISHANCH</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>456.25</v>
+        <v>59.55</v>
       </c>
       <c r="C181" t="n">
-        <v>470.25</v>
+        <v>60.8</v>
       </c>
       <c r="D181" t="n">
-        <v>3.07</v>
+        <v>2.1</v>
       </c>
       <c r="E181" t="b">
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>465</v>
+        <v>59.5</v>
       </c>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="n">
-        <v>-1.12</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ABINFRA</t>
+          <t>AKASH</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>17.27</v>
+        <v>24.24</v>
       </c>
       <c r="C182" t="n">
-        <v>17.8</v>
+        <v>24.75</v>
       </c>
       <c r="D182" t="n">
-        <v>3.07</v>
+        <v>2.1</v>
       </c>
       <c r="E182" t="b">
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>17.42</v>
+        <v>24.6</v>
       </c>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="n">
-        <v>-2.13</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>GVT&amp;D</t>
+          <t>DNAMEDIA</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>3768.6</v>
+        <v>3.33</v>
       </c>
       <c r="C183" t="n">
-        <v>3884</v>
+        <v>3.4</v>
       </c>
       <c r="D183" t="n">
-        <v>3.06</v>
+        <v>2.1</v>
       </c>
       <c r="E183" t="b">
         <v>0</v>
       </c>
-      <c r="F183" t="inlineStr"/>
+      <c r="F183" t="n">
+        <v>3.38</v>
+      </c>
       <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
+      <c r="H183" t="n">
+        <v>-0.59</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>SILINV</t>
+          <t>KSB</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>405.6</v>
+        <v>761.25</v>
       </c>
       <c r="C184" t="n">
-        <v>418</v>
+        <v>777</v>
       </c>
       <c r="D184" t="n">
-        <v>3.06</v>
+        <v>2.07</v>
       </c>
       <c r="E184" t="b">
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>403.05</v>
+        <v>776.55</v>
       </c>
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="n">
-        <v>-3.58</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>EBGNG</t>
+          <t>JINDRILL</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>339.65</v>
+        <v>542.2</v>
       </c>
       <c r="C185" t="n">
-        <v>350</v>
+        <v>553.35</v>
       </c>
       <c r="D185" t="n">
-        <v>3.05</v>
+        <v>2.06</v>
       </c>
       <c r="E185" t="b">
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>356.6</v>
+        <v>538.45</v>
       </c>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="n">
-        <v>1.89</v>
+        <v>-2.69</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>JAMNAAUTO</t>
+          <t>3IINFOLTD</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>122.28</v>
+        <v>13.13</v>
       </c>
       <c r="C186" t="n">
-        <v>126</v>
+        <v>13.4</v>
       </c>
       <c r="D186" t="n">
-        <v>3.04</v>
+        <v>2.06</v>
       </c>
       <c r="E186" t="b">
         <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>124.51</v>
+        <v>13.56</v>
       </c>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="n">
-        <v>-1.18</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ESCORTS</t>
+          <t>GATECH</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>3203.4</v>
+        <v>0.49</v>
       </c>
       <c r="C187" t="n">
-        <v>3300</v>
+        <v>0.5</v>
       </c>
       <c r="D187" t="n">
-        <v>3.02</v>
+        <v>2.04</v>
       </c>
       <c r="E187" t="b">
         <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>3295.4</v>
+        <v>0.48</v>
       </c>
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="n">
-        <v>-0.14</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>JPASSOCIAT</t>
+          <t>KNAGRI</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>2.32</v>
+        <v>184.24</v>
       </c>
       <c r="C188" t="n">
-        <v>2.39</v>
+        <v>188</v>
       </c>
       <c r="D188" t="n">
-        <v>3.02</v>
+        <v>2.04</v>
       </c>
       <c r="E188" t="b">
         <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>2.38</v>
+        <v>187.78</v>
       </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="n">
-        <v>-0.42</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>KITEX</t>
+          <t>PRIMO</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>164.06</v>
+        <v>17.29</v>
       </c>
       <c r="C189" t="n">
-        <v>169</v>
+        <v>17.64</v>
       </c>
       <c r="D189" t="n">
-        <v>3.01</v>
+        <v>2.02</v>
       </c>
       <c r="E189" t="b">
         <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>168.99</v>
+        <v>17.76</v>
       </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="n">
-        <v>-0.01</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>HINDPETRO</t>
+          <t>ESAFSFB</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>384.55</v>
+        <v>25.19</v>
       </c>
       <c r="C190" t="n">
-        <v>396</v>
+        <v>25.7</v>
       </c>
       <c r="D190" t="n">
-        <v>2.98</v>
+        <v>2.02</v>
       </c>
       <c r="E190" t="b">
         <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>384.75</v>
+        <v>25.55</v>
       </c>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="n">
-        <v>-2.84</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>NDL</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>2096.8</v>
+        <v>2.48</v>
       </c>
       <c r="C191" t="n">
-        <v>2159</v>
+        <v>2.53</v>
       </c>
       <c r="D191" t="n">
-        <v>2.97</v>
+        <v>2.02</v>
       </c>
       <c r="E191" t="b">
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>2135</v>
+        <v>2.55</v>
       </c>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="n">
-        <v>-1.11</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>BELLACASA</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>1837.8</v>
+        <v>262.4</v>
       </c>
       <c r="C192" t="n">
-        <v>1892.4</v>
+        <v>267.7</v>
       </c>
       <c r="D192" t="n">
-        <v>2.97</v>
+        <v>2.02</v>
       </c>
       <c r="E192" t="b">
         <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>1888</v>
+        <v>264.8</v>
       </c>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="n">
-        <v>-0.23</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>AGARIND</t>
+          <t>HINDCON</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>456.45</v>
+        <v>18.91</v>
       </c>
       <c r="C193" t="n">
-        <v>470</v>
+        <v>19.29</v>
       </c>
       <c r="D193" t="n">
-        <v>2.97</v>
+        <v>2.01</v>
       </c>
       <c r="E193" t="b">
         <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>449.25</v>
+        <v>20.05</v>
       </c>
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="n">
-        <v>-4.41</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>TIL</t>
+          <t>ODIGMA</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>192.29</v>
+        <v>23.87</v>
       </c>
       <c r="C194" t="n">
-        <v>197.99</v>
+        <v>24.35</v>
       </c>
       <c r="D194" t="n">
-        <v>2.96</v>
+        <v>2.01</v>
       </c>
       <c r="E194" t="b">
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>198.46</v>
+        <v>24.2</v>
       </c>
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="n">
-        <v>0.24</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SITINET</t>
+          <t>TEJASNET</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.34</v>
+        <v>464.4</v>
       </c>
       <c r="C195" t="n">
-        <v>0.35</v>
+        <v>473.7</v>
       </c>
       <c r="D195" t="n">
-        <v>2.94</v>
+        <v>2</v>
       </c>
       <c r="E195" t="b">
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>0.34</v>
+        <v>479.25</v>
       </c>
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="n">
-        <v>-2.86</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>CHANDAN</t>
+          <t>MOLDTECH</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>250.65</v>
+        <v>129.87</v>
       </c>
       <c r="C196" t="n">
-        <v>258</v>
+        <v>132.47</v>
       </c>
       <c r="D196" t="n">
-        <v>2.93</v>
+        <v>2</v>
       </c>
       <c r="E196" t="b">
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>254.8</v>
+        <v>134.68</v>
       </c>
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="n">
-        <v>-1.24</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>PROSTARM</t>
+          <t>GRMOVER</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>127.27</v>
+        <v>156.38</v>
       </c>
       <c r="C197" t="n">
-        <v>131</v>
+        <v>159.5</v>
       </c>
       <c r="D197" t="n">
-        <v>2.93</v>
+        <v>2</v>
       </c>
       <c r="E197" t="b">
         <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>130.25</v>
+        <v>158.66</v>
       </c>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="n">
-        <v>-0.57</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>REMSONSIND</t>
+          <t>GLOBAL</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>104.84</v>
+        <v>107.61</v>
       </c>
       <c r="C198" t="n">
-        <v>107.9</v>
+        <v>109.76</v>
       </c>
       <c r="D198" t="n">
-        <v>2.92</v>
+        <v>2</v>
       </c>
       <c r="E198" t="b">
         <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>105.28</v>
+        <v>107.96</v>
       </c>
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="n">
-        <v>-2.43</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SIGNATURE</t>
+          <t>UNIVASTU</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>874.55</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="C199" t="n">
-        <v>900</v>
+        <v>66.48</v>
       </c>
       <c r="D199" t="n">
-        <v>2.91</v>
+        <v>1.99</v>
       </c>
       <c r="E199" t="b">
         <v>0</v>
       </c>
       <c r="F199" t="n">
-        <v>881.4</v>
+        <v>65</v>
       </c>
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="n">
-        <v>-2.07</v>
+        <v>-2.23</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>VISHWARAJ</t>
+          <t>BANCOINDIA</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>5.15</v>
+        <v>571.3</v>
       </c>
       <c r="C200" t="n">
-        <v>5.3</v>
+        <v>582.6</v>
       </c>
       <c r="D200" t="n">
-        <v>2.91</v>
+        <v>1.98</v>
       </c>
       <c r="E200" t="b">
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>5.25</v>
+        <v>577.4</v>
       </c>
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>HITECHCORP</t>
+          <t>ASTRON</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>118.55</v>
+        <v>4.04</v>
       </c>
       <c r="C201" t="n">
-        <v>122</v>
+        <v>4.12</v>
       </c>
       <c r="D201" t="n">
-        <v>2.91</v>
+        <v>1.98</v>
       </c>
       <c r="E201" t="b">
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>119.41</v>
+        <v>4.13</v>
       </c>
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="n">
-        <v>-2.12</v>
+        <v>0.24</v>
       </c>
     </row>
   </sheetData>

--- a/data/trending_momentum_stocks.xlsx
+++ b/data/trending_momentum_stocks.xlsx
@@ -461,933 +461,933 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SIGMA</t>
+          <t>SHANTI</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.22</v>
+        <v>6.32</v>
       </c>
       <c r="C2" t="n">
-        <v>47</v>
+        <v>7.3</v>
       </c>
       <c r="D2" t="n">
-        <v>19.84</v>
+        <v>15.51</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>40.51</v>
+        <v>6.56</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>-13.81</v>
+        <v>-10.14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MMEL</t>
+          <t>UMESLTD</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25.65</v>
+        <v>4.99</v>
       </c>
       <c r="C3" t="n">
-        <v>28.9</v>
+        <v>5.7</v>
       </c>
       <c r="D3" t="n">
-        <v>12.67</v>
+        <v>14.23</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>26.4</v>
+        <v>5.98</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>-8.65</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VGL</t>
+          <t>DCMFINSERV</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>61.19</v>
+        <v>5.62</v>
       </c>
       <c r="C4" t="n">
-        <v>68.90000000000001</v>
+        <v>6.24</v>
       </c>
       <c r="D4" t="n">
-        <v>12.6</v>
+        <v>11.03</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>63.47</v>
+        <v>6.74</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>-7.88</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TECILCHEM</t>
+          <t>LPDC</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12.9</v>
+        <v>5.86</v>
       </c>
       <c r="C5" t="n">
-        <v>14.45</v>
+        <v>6.45</v>
       </c>
       <c r="D5" t="n">
-        <v>12.02</v>
+        <v>10.07</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>12.99</v>
+        <v>5.76</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>-10.1</v>
+        <v>-10.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WILLAMAGOR</t>
+          <t>CYBERMEDIA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25.8</v>
+        <v>13.94</v>
       </c>
       <c r="C6" t="n">
-        <v>28.7</v>
+        <v>15.33</v>
       </c>
       <c r="D6" t="n">
-        <v>11.24</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>28.55</v>
+        <v>13.69</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>-0.52</v>
+        <v>-10.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MFML</t>
+          <t>TTKPRESTIG</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22.5</v>
+        <v>535.45</v>
       </c>
       <c r="C7" t="n">
-        <v>24.99</v>
+        <v>585</v>
       </c>
       <c r="D7" t="n">
-        <v>11.07</v>
+        <v>9.25</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>23.44</v>
+        <v>568</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>-6.2</v>
+        <v>-2.91</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DCMFINSERV</t>
+          <t>SATKARTAR</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.69</v>
+        <v>161.2</v>
       </c>
       <c r="C8" t="n">
-        <v>5.19</v>
+        <v>175.95</v>
       </c>
       <c r="D8" t="n">
-        <v>10.66</v>
+        <v>9.15</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>5.62</v>
+        <v>167</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>8.289999999999999</v>
+        <v>-5.09</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UNIINFO</t>
+          <t>BIOPOL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12.44</v>
+        <v>101</v>
       </c>
       <c r="C9" t="n">
-        <v>13.75</v>
+        <v>109.9</v>
       </c>
       <c r="D9" t="n">
-        <v>10.53</v>
+        <v>8.81</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>12.8</v>
+        <v>101</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>-6.91</v>
+        <v>-8.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>OSWALAGRO</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>141.55</v>
+        <v>43.61</v>
       </c>
       <c r="C10" t="n">
-        <v>155</v>
+        <v>46.99</v>
       </c>
       <c r="D10" t="n">
-        <v>9.5</v>
+        <v>7.75</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>161.1</v>
+        <v>43.23</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>3.94</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SEMAC</t>
+          <t>RVHL</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>212.42</v>
+        <v>38.37</v>
       </c>
       <c r="C11" t="n">
-        <v>231.99</v>
+        <v>41.27</v>
       </c>
       <c r="D11" t="n">
-        <v>9.210000000000001</v>
+        <v>7.56</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>225</v>
+        <v>38.01</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>-3.01</v>
+        <v>-7.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>URAVIDEF</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>489.95</v>
+        <v>133.57</v>
       </c>
       <c r="C12" t="n">
-        <v>533.85</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>8.960000000000001</v>
+        <v>7.06</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>569.4</v>
+        <v>133.35</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>6.66</v>
+        <v>-6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AMBICAAGAR</t>
+          <t>INFOMEDIA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23.54</v>
+        <v>5.04</v>
       </c>
       <c r="C13" t="n">
-        <v>25.5</v>
+        <v>5.39</v>
       </c>
       <c r="D13" t="n">
-        <v>8.33</v>
+        <v>6.94</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>24.39</v>
+        <v>5.19</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>-4.35</v>
+        <v>-3.71</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SECURKLOUD</t>
+          <t>DHARAN</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21.94</v>
+        <v>0.15</v>
       </c>
       <c r="C14" t="n">
-        <v>23.73</v>
+        <v>0.16</v>
       </c>
       <c r="D14" t="n">
-        <v>8.16</v>
+        <v>6.67</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>22.25</v>
+        <v>0.16</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>-6.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GROBTEA</t>
+          <t>UNIINFO</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>861.2</v>
+        <v>10.77</v>
       </c>
       <c r="C15" t="n">
-        <v>930</v>
+        <v>11.48</v>
       </c>
       <c r="D15" t="n">
-        <v>7.99</v>
+        <v>6.59</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>871</v>
+        <v>11.69</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>-6.34</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WABAG</t>
+          <t>VINNY</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1198.3</v>
+        <v>1.11</v>
       </c>
       <c r="C16" t="n">
-        <v>1290</v>
+        <v>1.18</v>
       </c>
       <c r="D16" t="n">
-        <v>7.65</v>
+        <v>6.31</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1281.5</v>
+        <v>1.15</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>-0.66</v>
+        <v>-2.54</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PIGL</t>
+          <t>MAHAPEXLTD</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>100.78</v>
+        <v>107.57</v>
       </c>
       <c r="C17" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D17" t="n">
-        <v>7.16</v>
+        <v>5.98</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>102.34</v>
+        <v>113</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>-5.24</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CEINSYS</t>
+          <t>NGLFINE</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>871.35</v>
+        <v>2431</v>
       </c>
       <c r="C18" t="n">
-        <v>931.95</v>
+        <v>2575</v>
       </c>
       <c r="D18" t="n">
-        <v>6.95</v>
+        <v>5.92</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>991.25</v>
+        <v>2337.8</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>6.36</v>
+        <v>-9.210000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DHARAN</t>
+          <t>SRD</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.15</v>
+        <v>50.07</v>
       </c>
       <c r="C19" t="n">
-        <v>0.16</v>
+        <v>52.99</v>
       </c>
       <c r="D19" t="n">
-        <v>6.67</v>
+        <v>5.83</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.16</v>
+        <v>49.64</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>-6.32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PRINCEPIPE</t>
+          <t>CROWN</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>248.55</v>
+        <v>120.96</v>
       </c>
       <c r="C20" t="n">
-        <v>265</v>
+        <v>127.85</v>
       </c>
       <c r="D20" t="n">
-        <v>6.62</v>
+        <v>5.7</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>267.8</v>
+        <v>119.55</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>1.06</v>
+        <v>-6.49</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OSWALPUMPS</t>
+          <t>GLOBECIVIL</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>300.9</v>
+        <v>46.5</v>
       </c>
       <c r="C21" t="n">
-        <v>320</v>
+        <v>48.95</v>
       </c>
       <c r="D21" t="n">
-        <v>6.35</v>
+        <v>5.27</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>330.95</v>
+        <v>46.16</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>3.42</v>
+        <v>-5.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ELECTCAST</t>
+          <t>FILATFASH</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>63.02</v>
+        <v>0.19</v>
       </c>
       <c r="C22" t="n">
-        <v>67.01000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D22" t="n">
-        <v>6.33</v>
+        <v>5.26</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>75.62</v>
+        <v>0.19</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>12.85</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>UMAEXPORTS</t>
+          <t>SANGINITA</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>22.64</v>
+        <v>13.6</v>
       </c>
       <c r="C23" t="n">
-        <v>23.99</v>
+        <v>14.28</v>
       </c>
       <c r="D23" t="n">
-        <v>5.96</v>
+        <v>5</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>22.99</v>
+        <v>14.28</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>-4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ICDSLTD</t>
+          <t>SEJALLTD</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>37.86</v>
+        <v>524.65</v>
       </c>
       <c r="C24" t="n">
-        <v>40</v>
+        <v>550.85</v>
       </c>
       <c r="D24" t="n">
-        <v>5.65</v>
+        <v>4.99</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>39.59</v>
+        <v>526.9</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>-1.02</v>
+        <v>-4.35</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DENTA</t>
+          <t>GJL</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>227.2</v>
+        <v>206.45</v>
       </c>
       <c r="C25" t="n">
-        <v>240</v>
+        <v>216.75</v>
       </c>
       <c r="D25" t="n">
-        <v>5.63</v>
+        <v>4.99</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>272.6</v>
+        <v>216.75</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>13.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GTECJAINX</t>
+          <t>ACETEC</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>20.11</v>
+        <v>129.6</v>
       </c>
       <c r="C26" t="n">
-        <v>21.22</v>
+        <v>136.05</v>
       </c>
       <c r="D26" t="n">
-        <v>5.52</v>
+        <v>4.98</v>
       </c>
       <c r="E26" t="b">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>21.18</v>
+        <v>136.05</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>-0.19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DELTAMAGNT</t>
+          <t>TCIFINANCE</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>56.8</v>
+        <v>14.83</v>
       </c>
       <c r="C27" t="n">
-        <v>59.9</v>
+        <v>15.55</v>
       </c>
       <c r="D27" t="n">
-        <v>5.46</v>
+        <v>4.86</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>59.47</v>
+        <v>14.31</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>-0.72</v>
+        <v>-7.97</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FACT</t>
+          <t>LCCINFOTEC</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>794.5</v>
+        <v>5.17</v>
       </c>
       <c r="C28" t="n">
-        <v>837</v>
+        <v>5.42</v>
       </c>
       <c r="D28" t="n">
-        <v>5.35</v>
+        <v>4.84</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>854</v>
+        <v>5.42</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MAGNUM</t>
+          <t>VASCONEQ</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>18.86</v>
+        <v>34.23</v>
       </c>
       <c r="C29" t="n">
-        <v>19.85</v>
+        <v>35.88</v>
       </c>
       <c r="D29" t="n">
-        <v>5.25</v>
+        <v>4.82</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>19.47</v>
+        <v>34.4</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>-1.91</v>
+        <v>-4.12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>COASTCORP</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>43.42</v>
+        <v>566.9</v>
       </c>
       <c r="C30" t="n">
-        <v>45.7</v>
+        <v>594</v>
       </c>
       <c r="D30" t="n">
-        <v>5.25</v>
+        <v>4.78</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>43.29</v>
+        <v>612.3</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>-5.27</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>JASH</t>
+          <t>SANWARIA</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>361.1</v>
+        <v>0.21</v>
       </c>
       <c r="C31" t="n">
-        <v>380</v>
+        <v>0.22</v>
       </c>
       <c r="D31" t="n">
-        <v>5.23</v>
+        <v>4.76</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>384.05</v>
+        <v>0.22</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MHLXMIRU</t>
+          <t>BSL</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>164.44</v>
+        <v>126.6</v>
       </c>
       <c r="C32" t="n">
-        <v>173</v>
+        <v>132.6</v>
       </c>
       <c r="D32" t="n">
-        <v>5.21</v>
+        <v>4.74</v>
       </c>
       <c r="E32" t="b">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>165.05</v>
+        <v>125.1</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>-4.6</v>
+        <v>-5.66</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SRD</t>
+          <t>KRIDHANINF</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>51.29</v>
+        <v>2.77</v>
       </c>
       <c r="C33" t="n">
-        <v>53.95</v>
+        <v>2.9</v>
       </c>
       <c r="D33" t="n">
-        <v>5.19</v>
+        <v>4.69</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>50.59</v>
+        <v>2.79</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>-6.23</v>
+        <v>-3.79</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>EMSLIMITED</t>
+          <t>TCPLPACK</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>259.5</v>
+        <v>2441</v>
       </c>
       <c r="C34" t="n">
-        <v>272.95</v>
+        <v>2555</v>
       </c>
       <c r="D34" t="n">
-        <v>5.18</v>
+        <v>4.67</v>
       </c>
       <c r="E34" t="b">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>311.4</v>
+        <v>2547</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>14.09</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>IONEXCHANG</t>
+          <t>SAMPANN</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>345.8</v>
+        <v>27.59</v>
       </c>
       <c r="C35" t="n">
-        <v>363.6</v>
+        <v>28.87</v>
       </c>
       <c r="D35" t="n">
-        <v>5.15</v>
+        <v>4.64</v>
       </c>
       <c r="E35" t="b">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>383.15</v>
+        <v>28.49</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>5.38</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SANWARIA</t>
+          <t>SURAJLTD</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.2</v>
+        <v>229.54</v>
       </c>
       <c r="C36" t="n">
-        <v>0.21</v>
+        <v>239.99</v>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="E36" t="b">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0.21</v>
+        <v>238</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TECHLABS</t>
+          <t>SADHNANIQ</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>235.05</v>
+        <v>1.54</v>
       </c>
       <c r="C37" t="n">
-        <v>246.8</v>
+        <v>1.61</v>
       </c>
       <c r="D37" t="n">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="E37" t="b">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>246.8</v>
+        <v>1.61</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
@@ -1397,127 +1397,127 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CURAA</t>
+          <t>BLUECOAST</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>98.88</v>
+        <v>20.72</v>
       </c>
       <c r="C38" t="n">
-        <v>103.82</v>
+        <v>21.66</v>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>4.54</v>
       </c>
       <c r="E38" t="b">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>103.82</v>
+        <v>21.42</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FILATFASH</t>
+          <t>SIMBHALS</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.2</v>
+        <v>8.4</v>
       </c>
       <c r="C39" t="n">
-        <v>0.21</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>5</v>
+        <v>4.52</v>
       </c>
       <c r="E39" t="b">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0.21</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>-6.49</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GAUDIUMIVF</t>
+          <t>KNAGRI</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>77.26000000000001</v>
+        <v>179.95</v>
       </c>
       <c r="C40" t="n">
-        <v>81.12</v>
+        <v>188</v>
       </c>
       <c r="D40" t="n">
-        <v>5</v>
+        <v>4.47</v>
       </c>
       <c r="E40" t="b">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>81.12</v>
+        <v>179.47</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>-4.54</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SACHEEROME</t>
+          <t>VINEETLAB</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>379.5</v>
+        <v>30.31</v>
       </c>
       <c r="C41" t="n">
-        <v>398.45</v>
+        <v>31.65</v>
       </c>
       <c r="D41" t="n">
-        <v>4.99</v>
+        <v>4.42</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>390</v>
+        <v>31.4</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>-2.12</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KDL</t>
+          <t>AURIGROW</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>132.4</v>
+        <v>0.23</v>
       </c>
       <c r="C42" t="n">
-        <v>139</v>
+        <v>0.24</v>
       </c>
       <c r="D42" t="n">
-        <v>4.98</v>
+        <v>4.35</v>
       </c>
       <c r="E42" t="b">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>139</v>
+        <v>0.24</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
@@ -1527,3321 +1527,3325 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AFIL</t>
+          <t>SUNDRMBRAK</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>8.279999999999999</v>
+        <v>566.15</v>
       </c>
       <c r="C43" t="n">
-        <v>8.69</v>
+        <v>590</v>
       </c>
       <c r="D43" t="n">
-        <v>4.95</v>
+        <v>4.21</v>
       </c>
       <c r="E43" t="b">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>8.4</v>
+        <v>567</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>-3.34</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MANILAM</t>
+          <t>GENCON</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>55.7</v>
+        <v>43.5</v>
       </c>
       <c r="C44" t="n">
-        <v>58.45</v>
+        <v>45.3</v>
       </c>
       <c r="D44" t="n">
-        <v>4.94</v>
+        <v>4.14</v>
       </c>
       <c r="E44" t="b">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>58.45</v>
+        <v>43.6</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ROTO</t>
+          <t>GINNIFILA</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>54.38</v>
+        <v>35.83</v>
       </c>
       <c r="C45" t="n">
-        <v>57</v>
+        <v>37.3</v>
       </c>
       <c r="D45" t="n">
-        <v>4.82</v>
+        <v>4.1</v>
       </c>
       <c r="E45" t="b">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>61.91</v>
+        <v>34.86</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>8.609999999999999</v>
+        <v>-6.54</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PRITI</t>
+          <t>FMNL</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>35.5</v>
+        <v>8.42</v>
       </c>
       <c r="C46" t="n">
-        <v>37.2</v>
+        <v>8.76</v>
       </c>
       <c r="D46" t="n">
-        <v>4.79</v>
+        <v>4.04</v>
       </c>
       <c r="E46" t="b">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>36.99</v>
+        <v>8.35</v>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-4.68</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PRAXIS</t>
+          <t>PRITI</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>6.74</v>
+        <v>36.81</v>
       </c>
       <c r="C47" t="n">
-        <v>7.06</v>
+        <v>38.29</v>
       </c>
       <c r="D47" t="n">
-        <v>4.75</v>
+        <v>4.02</v>
       </c>
       <c r="E47" t="b">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>6.85</v>
+        <v>37.13</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>-2.97</v>
+        <v>-3.03</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AIROLAM</t>
+          <t>GSS</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>87.81</v>
+        <v>12.31</v>
       </c>
       <c r="C48" t="n">
-        <v>91.94</v>
+        <v>12.8</v>
       </c>
       <c r="D48" t="n">
-        <v>4.7</v>
+        <v>3.98</v>
       </c>
       <c r="E48" t="b">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>89.40000000000001</v>
+        <v>12.26</v>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>-2.76</v>
+        <v>-4.22</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ATLASCYCLE</t>
+          <t>DRCSYSTEMS</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>82.91</v>
+        <v>13.27</v>
       </c>
       <c r="C49" t="n">
-        <v>86.8</v>
+        <v>13.79</v>
       </c>
       <c r="D49" t="n">
-        <v>4.69</v>
+        <v>3.92</v>
       </c>
       <c r="E49" t="b">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>85.89</v>
+        <v>13.1</v>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>-1.05</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>RHFL</t>
+          <t>GICL</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2.35</v>
+        <v>44.61</v>
       </c>
       <c r="C50" t="n">
-        <v>2.46</v>
+        <v>46.35</v>
       </c>
       <c r="D50" t="n">
-        <v>4.68</v>
+        <v>3.9</v>
       </c>
       <c r="E50" t="b">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>2.46</v>
+        <v>44.85</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>-3.24</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TFL</t>
+          <t>ABINFRA</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>12.9</v>
+        <v>17.61</v>
       </c>
       <c r="C51" t="n">
-        <v>13.5</v>
+        <v>18.29</v>
       </c>
       <c r="D51" t="n">
-        <v>4.65</v>
+        <v>3.86</v>
       </c>
       <c r="E51" t="b">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>13.4</v>
+        <v>17.32</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>-0.74</v>
+        <v>-5.3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>POLYSIL</t>
+          <t>STOVEKRAFT</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>191.1</v>
+        <v>544.95</v>
       </c>
       <c r="C52" t="n">
-        <v>199.95</v>
+        <v>565.9</v>
       </c>
       <c r="D52" t="n">
-        <v>4.63</v>
+        <v>3.84</v>
       </c>
       <c r="E52" t="b">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>197.9</v>
+        <v>549</v>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>-1.03</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>REPRO</t>
+          <t>JAIPURKURT</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>381.45</v>
+        <v>29.77</v>
       </c>
       <c r="C53" t="n">
-        <v>399</v>
+        <v>30.9</v>
       </c>
       <c r="D53" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="E53" t="b">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>384.85</v>
+        <v>30.25</v>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>-3.55</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>KOTYARK</t>
+          <t>TIJARIA</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>310.7</v>
+        <v>4.87</v>
       </c>
       <c r="C54" t="n">
-        <v>325</v>
+        <v>5.05</v>
       </c>
       <c r="D54" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="E54" t="b">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>325.05</v>
+        <v>4.99</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>0.02</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>HGINFRA</t>
+          <t>VIVIDHA</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>490.55</v>
+        <v>0.54</v>
       </c>
       <c r="C55" t="n">
-        <v>513</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D55" t="n">
-        <v>4.58</v>
+        <v>3.7</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>552.3</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>7.66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MANOMAY</t>
+          <t>MKPL</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>218.05</v>
+        <v>4.9</v>
       </c>
       <c r="C56" t="n">
-        <v>228</v>
+        <v>5.08</v>
       </c>
       <c r="D56" t="n">
-        <v>4.56</v>
+        <v>3.67</v>
       </c>
       <c r="E56" t="b">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>224</v>
+        <v>5.22</v>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>-1.75</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>INDIANHUME</t>
+          <t>KEC</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>317.4</v>
+        <v>547.75</v>
       </c>
       <c r="C57" t="n">
-        <v>331.85</v>
+        <v>567.25</v>
       </c>
       <c r="D57" t="n">
-        <v>4.55</v>
+        <v>3.56</v>
       </c>
       <c r="E57" t="b">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>364</v>
+        <v>539</v>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>9.69</v>
+        <v>-4.98</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AURIGROW</t>
+          <t>IGCL</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.22</v>
+        <v>63.18</v>
       </c>
       <c r="C58" t="n">
-        <v>0.23</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D58" t="n">
-        <v>4.55</v>
+        <v>3.51</v>
       </c>
       <c r="E58" t="b">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>0.23</v>
+        <v>62.48</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>-4.46</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>JPASSOCIAT</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2.43</v>
+        <v>569.2</v>
       </c>
       <c r="C59" t="n">
-        <v>2.54</v>
+        <v>589</v>
       </c>
       <c r="D59" t="n">
-        <v>4.53</v>
+        <v>3.48</v>
       </c>
       <c r="E59" t="b">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>2.55</v>
+        <v>582</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>0.39</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PAVNAIND</t>
+          <t>GREENCHEF</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>18.66</v>
+        <v>50.1</v>
       </c>
       <c r="C60" t="n">
-        <v>19.5</v>
+        <v>51.8</v>
       </c>
       <c r="D60" t="n">
-        <v>4.5</v>
+        <v>3.39</v>
       </c>
       <c r="E60" t="b">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>19.5</v>
+        <v>52.05</v>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>RCOM</t>
+          <t>GOLDTECH</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.89</v>
+        <v>38.45</v>
       </c>
       <c r="C61" t="n">
-        <v>0.93</v>
+        <v>39.75</v>
       </c>
       <c r="D61" t="n">
-        <v>4.49</v>
+        <v>3.38</v>
       </c>
       <c r="E61" t="b">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0.93</v>
+        <v>39.03</v>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>-1.81</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>NEPTUNE</t>
+          <t>INTENTECH</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>210.25</v>
+        <v>91.41</v>
       </c>
       <c r="C62" t="n">
-        <v>219.7</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="D62" t="n">
-        <v>4.49</v>
+        <v>3.37</v>
       </c>
       <c r="E62" t="b">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>220</v>
+        <v>91.12</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>0.14</v>
+        <v>-3.57</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>SURANASOL</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>32.5</v>
+        <v>20.8</v>
       </c>
       <c r="C63" t="n">
-        <v>33.95</v>
+        <v>21.5</v>
       </c>
       <c r="D63" t="n">
-        <v>4.46</v>
+        <v>3.37</v>
       </c>
       <c r="E63" t="b">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>32.05</v>
+        <v>21.1</v>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>-5.6</v>
+        <v>-1.86</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DIGISPICE</t>
+          <t>LOVABLE</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>17.7</v>
+        <v>68.7</v>
       </c>
       <c r="C64" t="n">
-        <v>18.49</v>
+        <v>71</v>
       </c>
       <c r="D64" t="n">
-        <v>4.46</v>
+        <v>3.35</v>
       </c>
       <c r="E64" t="b">
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>-2.65</v>
+        <v>-5.63</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TCIFINANCE</t>
+          <t>CTE</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>14.13</v>
+        <v>27.03</v>
       </c>
       <c r="C65" t="n">
-        <v>14.75</v>
+        <v>27.93</v>
       </c>
       <c r="D65" t="n">
-        <v>4.39</v>
+        <v>3.33</v>
       </c>
       <c r="E65" t="b">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>14.83</v>
+        <v>27.45</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>0.54</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SPMLINFRA</t>
+          <t>BASML</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>161.9</v>
+        <v>20.7</v>
       </c>
       <c r="C66" t="n">
-        <v>169</v>
+        <v>21.38</v>
       </c>
       <c r="D66" t="n">
-        <v>4.39</v>
+        <v>3.29</v>
       </c>
       <c r="E66" t="b">
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>187.99</v>
+        <v>20.33</v>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>11.24</v>
+        <v>-4.91</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MOTOGENFIN</t>
+          <t>OMNI</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>19.84</v>
+        <v>208.95</v>
       </c>
       <c r="C67" t="n">
-        <v>20.7</v>
+        <v>215.8</v>
       </c>
       <c r="D67" t="n">
-        <v>4.33</v>
+        <v>3.28</v>
       </c>
       <c r="E67" t="b">
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>20.6</v>
+        <v>213.33</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>-0.48</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>VPRPL</t>
+          <t>RHFL</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>38.58</v>
+        <v>2.46</v>
       </c>
       <c r="C68" t="n">
-        <v>40.24</v>
+        <v>2.54</v>
       </c>
       <c r="D68" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="E68" t="b">
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>42.29</v>
+        <v>2.58</v>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>5.09</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>VILAS</t>
+          <t>RCOM</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>348.05</v>
+        <v>0.93</v>
       </c>
       <c r="C69" t="n">
-        <v>363</v>
+        <v>0.96</v>
       </c>
       <c r="D69" t="n">
-        <v>4.3</v>
+        <v>3.23</v>
       </c>
       <c r="E69" t="b">
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>355</v>
+        <v>0.97</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>-2.2</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BVCL</t>
+          <t>VIJIFIN</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>39.6</v>
+        <v>2.51</v>
       </c>
       <c r="C70" t="n">
-        <v>41.25</v>
+        <v>2.59</v>
       </c>
       <c r="D70" t="n">
-        <v>4.17</v>
+        <v>3.19</v>
       </c>
       <c r="E70" t="b">
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>40.4</v>
+        <v>2.63</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>-2.06</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ORCHASP</t>
+          <t>SUNDARAM</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2.2</v>
+        <v>1.26</v>
       </c>
       <c r="C71" t="n">
-        <v>2.29</v>
+        <v>1.3</v>
       </c>
       <c r="D71" t="n">
-        <v>4.09</v>
+        <v>3.17</v>
       </c>
       <c r="E71" t="b">
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>2.24</v>
+        <v>1.3</v>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>-2.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SHANTI</t>
+          <t>ANKITMETAL</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>6.4</v>
+        <v>1.6</v>
       </c>
       <c r="C72" t="n">
-        <v>6.66</v>
+        <v>1.65</v>
       </c>
       <c r="D72" t="n">
-        <v>4.06</v>
+        <v>3.12</v>
       </c>
       <c r="E72" t="b">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>6.41</v>
+        <v>1.67</v>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>-3.75</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PPSL</t>
+          <t>CSLFINANCE</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>6.2</v>
+        <v>255.15</v>
       </c>
       <c r="C73" t="n">
-        <v>6.45</v>
+        <v>263</v>
       </c>
       <c r="D73" t="n">
-        <v>4.03</v>
+        <v>3.08</v>
       </c>
       <c r="E73" t="b">
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>6.4</v>
+        <v>251.65</v>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>-0.78</v>
+        <v>-4.32</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>KRONOX</t>
+          <t>VAISHALI</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>114.39</v>
+        <v>6.5</v>
       </c>
       <c r="C74" t="n">
-        <v>118.95</v>
+        <v>6.7</v>
       </c>
       <c r="D74" t="n">
-        <v>3.99</v>
+        <v>3.08</v>
       </c>
       <c r="E74" t="b">
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>114.18</v>
+        <v>6.51</v>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>-4.01</v>
+        <v>-2.84</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SANCO</t>
+          <t>AAKASH</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2.27</v>
+        <v>10.68</v>
       </c>
       <c r="C75" t="n">
-        <v>2.36</v>
+        <v>11</v>
       </c>
       <c r="D75" t="n">
-        <v>3.96</v>
+        <v>3</v>
       </c>
       <c r="E75" t="b">
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>2.36</v>
+        <v>10.27</v>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>-6.64</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>XTGLOBAL</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>7.07</v>
+        <v>33.97</v>
       </c>
       <c r="C76" t="n">
-        <v>7.35</v>
+        <v>34.99</v>
       </c>
       <c r="D76" t="n">
-        <v>3.96</v>
+        <v>3</v>
       </c>
       <c r="E76" t="b">
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>7.2</v>
+        <v>34.49</v>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>-2.04</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>KSOLVES</t>
+          <t>GSLSU</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>287.05</v>
+        <v>73.31</v>
       </c>
       <c r="C77" t="n">
-        <v>298.4</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="D77" t="n">
-        <v>3.95</v>
+        <v>2.97</v>
       </c>
       <c r="E77" t="b">
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>291.15</v>
+        <v>72.48</v>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>-2.43</v>
+        <v>-3.99</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>KARMAENG</t>
+          <t>SITINET</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>37.52</v>
+        <v>0.34</v>
       </c>
       <c r="C78" t="n">
-        <v>39</v>
+        <v>0.35</v>
       </c>
       <c r="D78" t="n">
-        <v>3.94</v>
+        <v>2.94</v>
       </c>
       <c r="E78" t="b">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>38.1</v>
+        <v>0.35</v>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>-2.31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PEARLPOLY</t>
+          <t>VIJAYPD</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>17.71</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C79" t="n">
-        <v>18.4</v>
+        <v>74</v>
       </c>
       <c r="D79" t="n">
-        <v>3.9</v>
+        <v>2.92</v>
       </c>
       <c r="E79" t="b">
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>17.75</v>
+        <v>70</v>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>-3.53</v>
+        <v>-5.41</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CCCL</t>
+          <t>IMPEXFERRO</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>15.66</v>
+        <v>1.72</v>
       </c>
       <c r="C80" t="n">
-        <v>16.27</v>
+        <v>1.77</v>
       </c>
       <c r="D80" t="n">
-        <v>3.9</v>
+        <v>2.91</v>
       </c>
       <c r="E80" t="b">
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>15.9</v>
+        <v>1.71</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>-2.27</v>
+        <v>-3.39</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AKG</t>
+          <t>GANGAFORGE</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>10.71</v>
+        <v>2.85</v>
       </c>
       <c r="C81" t="n">
-        <v>11.12</v>
+        <v>2.93</v>
       </c>
       <c r="D81" t="n">
-        <v>3.83</v>
+        <v>2.81</v>
       </c>
       <c r="E81" t="b">
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>10.89</v>
+        <v>2.87</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>-2.07</v>
+        <v>-2.05</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>FRESHARA</t>
+          <t>NECLIFE</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>186.3</v>
+        <v>11.42</v>
       </c>
       <c r="C82" t="n">
-        <v>193.4</v>
+        <v>11.74</v>
       </c>
       <c r="D82" t="n">
-        <v>3.81</v>
+        <v>2.8</v>
       </c>
       <c r="E82" t="b">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>187.4</v>
+        <v>11.41</v>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>-3.1</v>
+        <v>-2.81</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>WEWIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>41.42</v>
+        <v>23.25</v>
       </c>
       <c r="C83" t="n">
-        <v>42.99</v>
+        <v>23.9</v>
       </c>
       <c r="D83" t="n">
-        <v>3.79</v>
+        <v>2.8</v>
       </c>
       <c r="E83" t="b">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>41.99</v>
+        <v>23.39</v>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>-2.33</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EBGNG</t>
+          <t>ADL</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>356.6</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="C84" t="n">
-        <v>370</v>
+        <v>74.95</v>
       </c>
       <c r="D84" t="n">
-        <v>3.76</v>
+        <v>2.69</v>
       </c>
       <c r="E84" t="b">
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>374.4</v>
+        <v>67.12</v>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>1.19</v>
+        <v>-10.45</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>OMINFRAL</t>
+          <t>FLAIR</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>81.75</v>
+        <v>302.1</v>
       </c>
       <c r="C85" t="n">
-        <v>84.8</v>
+        <v>310.15</v>
       </c>
       <c r="D85" t="n">
-        <v>3.73</v>
+        <v>2.66</v>
       </c>
       <c r="E85" t="b">
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>88.63</v>
+        <v>299.1</v>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>4.52</v>
+        <v>-3.56</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EXCEL</t>
+          <t>BRNL</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1.08</v>
+        <v>18.49</v>
       </c>
       <c r="C86" t="n">
-        <v>1.12</v>
+        <v>18.98</v>
       </c>
       <c r="D86" t="n">
-        <v>3.7</v>
+        <v>2.65</v>
       </c>
       <c r="E86" t="b">
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>1.17</v>
+        <v>18.45</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>4.46</v>
+        <v>-2.79</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AVONMORE</t>
+          <t>WABAG</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>13.72</v>
+        <v>1251.9</v>
       </c>
       <c r="C87" t="n">
-        <v>14.22</v>
+        <v>1285.1</v>
       </c>
       <c r="D87" t="n">
-        <v>3.64</v>
+        <v>2.65</v>
       </c>
       <c r="E87" t="b">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>14.11</v>
+        <v>1257.1</v>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>-0.77</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>VINEETLAB</t>
+          <t>SHYAMDHANI</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>29.92</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="C88" t="n">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="D88" t="n">
-        <v>3.61</v>
+        <v>2.64</v>
       </c>
       <c r="E88" t="b">
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>30.37</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>-2.03</v>
+        <v>-4.03</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>JISLDVREQS</t>
+          <t>SBGLP</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>20.5</v>
+        <v>27.47</v>
       </c>
       <c r="C89" t="n">
-        <v>21.24</v>
+        <v>28.19</v>
       </c>
       <c r="D89" t="n">
-        <v>3.61</v>
+        <v>2.62</v>
       </c>
       <c r="E89" t="b">
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>22.85</v>
+        <v>27.3</v>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>7.58</v>
+        <v>-3.16</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>NIRAJ</t>
+          <t>SETUINFRA</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>27.5</v>
+        <v>0.39</v>
       </c>
       <c r="C90" t="n">
-        <v>28.49</v>
+        <v>0.4</v>
       </c>
       <c r="D90" t="n">
-        <v>3.6</v>
+        <v>2.56</v>
       </c>
       <c r="E90" t="b">
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>28.26</v>
+        <v>0.39</v>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>HARRMALAYA</t>
+          <t>DUCON</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>181.47</v>
+        <v>3.14</v>
       </c>
       <c r="C91" t="n">
-        <v>188</v>
+        <v>3.22</v>
       </c>
       <c r="D91" t="n">
-        <v>3.6</v>
+        <v>2.55</v>
       </c>
       <c r="E91" t="b">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>184.03</v>
+        <v>3.1</v>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>-2.11</v>
+        <v>-3.73</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>LFIC</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>130.31</v>
+        <v>60.28</v>
       </c>
       <c r="C92" t="n">
-        <v>134.99</v>
+        <v>61.8</v>
       </c>
       <c r="D92" t="n">
-        <v>3.59</v>
+        <v>2.52</v>
       </c>
       <c r="E92" t="b">
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>134.75</v>
+        <v>60.39</v>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
-        <v>-0.18</v>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>IL&amp;FSTRANS</t>
+          <t>BUTTERFLY</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>2.28</v>
+        <v>694.5</v>
       </c>
       <c r="C93" t="n">
-        <v>2.36</v>
+        <v>712</v>
       </c>
       <c r="D93" t="n">
-        <v>3.51</v>
+        <v>2.52</v>
       </c>
       <c r="E93" t="b">
         <v>0</v>
       </c>
-      <c r="F93" t="inlineStr"/>
+      <c r="F93" t="n">
+        <v>719.8</v>
+      </c>
       <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="H93" t="n">
+        <v>1.1</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DAMODARIND</t>
+          <t>HINDOILEXP</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>24.06</v>
+        <v>147.32</v>
       </c>
       <c r="C94" t="n">
-        <v>24.9</v>
+        <v>151</v>
       </c>
       <c r="D94" t="n">
-        <v>3.49</v>
+        <v>2.5</v>
       </c>
       <c r="E94" t="b">
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>24.19</v>
+        <v>152.36</v>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>-2.85</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CYBERTECH</t>
+          <t>SHRENIK</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>105.14</v>
+        <v>0.4</v>
       </c>
       <c r="C95" t="n">
-        <v>108.8</v>
+        <v>0.41</v>
       </c>
       <c r="D95" t="n">
-        <v>3.48</v>
+        <v>2.5</v>
       </c>
       <c r="E95" t="b">
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>107.92</v>
+        <v>0.41</v>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>NAGAFERT</t>
+          <t>MODTHREAD</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>4.32</v>
+        <v>54.27</v>
       </c>
       <c r="C96" t="n">
-        <v>4.47</v>
+        <v>55.62</v>
       </c>
       <c r="D96" t="n">
-        <v>3.47</v>
+        <v>2.49</v>
       </c>
       <c r="E96" t="b">
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>4.41</v>
+        <v>54</v>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>-1.34</v>
+        <v>-2.91</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>JAIPURKURT</t>
+          <t>CEREBRAINT</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>30.93</v>
+        <v>4.41</v>
       </c>
       <c r="C97" t="n">
-        <v>32</v>
+        <v>4.52</v>
       </c>
       <c r="D97" t="n">
-        <v>3.46</v>
+        <v>2.49</v>
       </c>
       <c r="E97" t="b">
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>31.35</v>
+        <v>4.37</v>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>-2.03</v>
+        <v>-3.32</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>KRITINUT</t>
+          <t>SGMART</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>63.03</v>
+        <v>446.7</v>
       </c>
       <c r="C98" t="n">
-        <v>65.2</v>
+        <v>457.8</v>
       </c>
       <c r="D98" t="n">
-        <v>3.44</v>
+        <v>2.48</v>
       </c>
       <c r="E98" t="b">
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>65.28</v>
+        <v>438.5</v>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>0.12</v>
+        <v>-4.22</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ZODIAC</t>
+          <t>SSDL</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>232.05</v>
+        <v>60.53</v>
       </c>
       <c r="C99" t="n">
-        <v>240</v>
+        <v>61.99</v>
       </c>
       <c r="D99" t="n">
-        <v>3.43</v>
+        <v>2.41</v>
       </c>
       <c r="E99" t="b">
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>235.98</v>
+        <v>60.76</v>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
-        <v>-1.68</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>VSTL</t>
+          <t>NAGAFERT</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>107.35</v>
+        <v>4.18</v>
       </c>
       <c r="C100" t="n">
-        <v>111</v>
+        <v>4.28</v>
       </c>
       <c r="D100" t="n">
-        <v>3.4</v>
+        <v>2.39</v>
       </c>
       <c r="E100" t="b">
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>108.96</v>
+        <v>4.24</v>
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>-1.84</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BAIDFIN</t>
+          <t>NRL</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>11.08</v>
+        <v>50.79</v>
       </c>
       <c r="C101" t="n">
-        <v>11.45</v>
+        <v>51.97</v>
       </c>
       <c r="D101" t="n">
-        <v>3.34</v>
+        <v>2.32</v>
       </c>
       <c r="E101" t="b">
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>11.21</v>
+        <v>51.31</v>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>-2.1</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PREMIER</t>
+          <t>SPCENET</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>2.99</v>
+        <v>3.91</v>
       </c>
       <c r="C102" t="n">
-        <v>3.09</v>
+        <v>4</v>
       </c>
       <c r="D102" t="n">
-        <v>3.34</v>
+        <v>2.3</v>
       </c>
       <c r="E102" t="b">
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>2.99</v>
+        <v>3.9</v>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>-3.24</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SHEKHAWATI</t>
+          <t>PEARLPOLY</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>11.99</v>
+        <v>17.11</v>
       </c>
       <c r="C103" t="n">
-        <v>12.39</v>
+        <v>17.5</v>
       </c>
       <c r="D103" t="n">
-        <v>3.34</v>
+        <v>2.28</v>
       </c>
       <c r="E103" t="b">
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>12.33</v>
+        <v>17.15</v>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>-0.48</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AURUM</t>
+          <t>GATECHDVR</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>168.43</v>
+        <v>0.44</v>
       </c>
       <c r="C104" t="n">
-        <v>173.99</v>
+        <v>0.45</v>
       </c>
       <c r="D104" t="n">
-        <v>3.3</v>
+        <v>2.27</v>
       </c>
       <c r="E104" t="b">
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>169.59</v>
+        <v>0.45</v>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
-        <v>-2.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>TAC</t>
+          <t>ODIGMA</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>452.4</v>
+        <v>23.67</v>
       </c>
       <c r="C105" t="n">
-        <v>467.1</v>
+        <v>24.2</v>
       </c>
       <c r="D105" t="n">
-        <v>3.25</v>
+        <v>2.24</v>
       </c>
       <c r="E105" t="b">
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>476</v>
+        <v>22.99</v>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>1.91</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>FOODSIN</t>
+          <t>ARCHIES</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>59.96</v>
+        <v>13.94</v>
       </c>
       <c r="C106" t="n">
-        <v>61.9</v>
+        <v>14.25</v>
       </c>
       <c r="D106" t="n">
-        <v>3.24</v>
+        <v>2.22</v>
       </c>
       <c r="E106" t="b">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>59.2</v>
+        <v>13.99</v>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
-        <v>-4.36</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>JAIBALAJI</t>
+          <t>INDTERRAIN</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>61.03</v>
+        <v>29.53</v>
       </c>
       <c r="C107" t="n">
-        <v>63</v>
+        <v>30.18</v>
       </c>
       <c r="D107" t="n">
-        <v>3.23</v>
+        <v>2.2</v>
       </c>
       <c r="E107" t="b">
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>69</v>
+        <v>29.5</v>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>9.52</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>RELCHEMQ</t>
+          <t>KAUSHALYA</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>112.03</v>
+        <v>825.95</v>
       </c>
       <c r="C108" t="n">
-        <v>115.65</v>
+        <v>844</v>
       </c>
       <c r="D108" t="n">
-        <v>3.23</v>
+        <v>2.19</v>
       </c>
       <c r="E108" t="b">
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>115.37</v>
+        <v>839.4</v>
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
-        <v>-0.24</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SADBHAV</t>
+          <t>SAURASHCEM</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>8.720000000000001</v>
+        <v>62.44</v>
       </c>
       <c r="C109" t="n">
-        <v>9</v>
+        <v>63.8</v>
       </c>
       <c r="D109" t="n">
-        <v>3.21</v>
+        <v>2.18</v>
       </c>
       <c r="E109" t="b">
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>9.15</v>
+        <v>61.66</v>
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>1.67</v>
+        <v>-3.35</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>KAPSTON</t>
+          <t>KSOLVES</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>283.9</v>
+        <v>288.55</v>
       </c>
       <c r="C110" t="n">
-        <v>293</v>
+        <v>294.8</v>
       </c>
       <c r="D110" t="n">
-        <v>3.21</v>
+        <v>2.17</v>
       </c>
       <c r="E110" t="b">
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
-        <v>-2.73</v>
+        <v>-4.34</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>TTKPRESTIG</t>
+          <t>VARROC</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>484.5</v>
+        <v>494.35</v>
       </c>
       <c r="C111" t="n">
-        <v>499.95</v>
+        <v>504.9</v>
       </c>
       <c r="D111" t="n">
-        <v>3.19</v>
+        <v>2.13</v>
       </c>
       <c r="E111" t="b">
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>525.15</v>
+        <v>482.55</v>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>5.04</v>
+        <v>-4.43</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>OCCLLTD</t>
+          <t>GNA</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>85.2</v>
+        <v>421.1</v>
       </c>
       <c r="C112" t="n">
-        <v>87.90000000000001</v>
+        <v>430</v>
       </c>
       <c r="D112" t="n">
-        <v>3.17</v>
+        <v>2.11</v>
       </c>
       <c r="E112" t="b">
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>85.7</v>
+        <v>411.05</v>
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
-        <v>-2.5</v>
+        <v>-4.41</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>JINDALSAW</t>
+          <t>ZENITHSTL</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>165.85</v>
+        <v>5.68</v>
       </c>
       <c r="C113" t="n">
-        <v>171</v>
+        <v>5.8</v>
       </c>
       <c r="D113" t="n">
-        <v>3.11</v>
+        <v>2.11</v>
       </c>
       <c r="E113" t="b">
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>188.08</v>
+        <v>5.46</v>
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>9.99</v>
+        <v>-5.86</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>RKSWAMY</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>96.93000000000001</v>
+        <v>153.08</v>
       </c>
       <c r="C114" t="n">
-        <v>99.93000000000001</v>
+        <v>156.28</v>
       </c>
       <c r="D114" t="n">
-        <v>3.1</v>
+        <v>2.09</v>
       </c>
       <c r="E114" t="b">
         <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>99.34999999999999</v>
+        <v>166.78</v>
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
-        <v>-0.58</v>
+        <v>6.72</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>JHS</t>
+          <t>GATECH</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>9.06</v>
+        <v>0.48</v>
       </c>
       <c r="C115" t="n">
-        <v>9.34</v>
+        <v>0.49</v>
       </c>
       <c r="D115" t="n">
-        <v>3.09</v>
+        <v>2.08</v>
       </c>
       <c r="E115" t="b">
         <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>9.52</v>
+        <v>0.48</v>
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>1.93</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>HMAAGRO</t>
+          <t>KEYFINSERV</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>24.64</v>
+        <v>266</v>
       </c>
       <c r="C116" t="n">
-        <v>25.4</v>
+        <v>271.5</v>
       </c>
       <c r="D116" t="n">
-        <v>3.08</v>
+        <v>2.07</v>
       </c>
       <c r="E116" t="b">
         <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>24.8</v>
+        <v>268.55</v>
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
-        <v>-2.36</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SITINET</t>
+          <t>DICIND</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.33</v>
+        <v>524.1</v>
       </c>
       <c r="C117" t="n">
-        <v>0.34</v>
+        <v>534.9</v>
       </c>
       <c r="D117" t="n">
-        <v>3.03</v>
+        <v>2.06</v>
       </c>
       <c r="E117" t="b">
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>0.34</v>
+        <v>534</v>
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>AAKASH</t>
+          <t>AXITA</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>10.92</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="C118" t="n">
-        <v>11.25</v>
+        <v>8.98</v>
       </c>
       <c r="D118" t="n">
-        <v>3.02</v>
+        <v>2.05</v>
       </c>
       <c r="E118" t="b">
         <v>0</v>
       </c>
       <c r="F118" t="n">
-        <v>10.51</v>
+        <v>8.9</v>
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
-        <v>-6.58</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ASHIMASYN</t>
+          <t>RADAAN</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>14.05</v>
+        <v>2.94</v>
       </c>
       <c r="C119" t="n">
-        <v>14.47</v>
+        <v>3</v>
       </c>
       <c r="D119" t="n">
-        <v>2.99</v>
+        <v>2.04</v>
       </c>
       <c r="E119" t="b">
         <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>14.35</v>
+        <v>2.98</v>
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
-        <v>-0.83</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SAURASHCEM</t>
+          <t>TREEHOUSE</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>62.13</v>
+        <v>7.86</v>
       </c>
       <c r="C120" t="n">
-        <v>63.98</v>
+        <v>8.02</v>
       </c>
       <c r="D120" t="n">
-        <v>2.98</v>
+        <v>2.04</v>
       </c>
       <c r="E120" t="b">
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>62.93</v>
+        <v>7.81</v>
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
-        <v>-1.64</v>
+        <v>-2.62</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>BAGFILMS</t>
+          <t>SAKHTISUG</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>5.03</v>
+        <v>15.18</v>
       </c>
       <c r="C121" t="n">
-        <v>5.18</v>
+        <v>15.49</v>
       </c>
       <c r="D121" t="n">
-        <v>2.98</v>
+        <v>2.04</v>
       </c>
       <c r="E121" t="b">
         <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>5.07</v>
+        <v>15.26</v>
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
-        <v>-2.12</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MADHAV</t>
+          <t>VHLTD</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>36.76</v>
+        <v>146.47</v>
       </c>
       <c r="C122" t="n">
-        <v>37.85</v>
+        <v>149.45</v>
       </c>
       <c r="D122" t="n">
-        <v>2.97</v>
+        <v>2.03</v>
       </c>
       <c r="E122" t="b">
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>36.61</v>
+        <v>146</v>
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
-        <v>-3.28</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MONEYBOXX</t>
+          <t>C2C</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>68.95</v>
+        <v>324.25</v>
       </c>
       <c r="C123" t="n">
-        <v>71</v>
+        <v>330.8</v>
       </c>
       <c r="D123" t="n">
-        <v>2.97</v>
+        <v>2.02</v>
       </c>
       <c r="E123" t="b">
         <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>67.51000000000001</v>
+        <v>372.95</v>
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>-4.92</v>
+        <v>12.74</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>UNITEDPOLY</t>
+          <t>ATALREAL</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>26.22</v>
+        <v>23.42</v>
       </c>
       <c r="C124" t="n">
-        <v>27</v>
+        <v>23.89</v>
       </c>
       <c r="D124" t="n">
-        <v>2.97</v>
+        <v>2.01</v>
       </c>
       <c r="E124" t="b">
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>27.53</v>
+        <v>22.88</v>
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
-        <v>1.96</v>
+        <v>-4.23</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>PATINTLOG</t>
+          <t>RSSOFTWARE</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>10.15</v>
+        <v>27.94</v>
       </c>
       <c r="C125" t="n">
-        <v>10.45</v>
+        <v>28.5</v>
       </c>
       <c r="D125" t="n">
-        <v>2.96</v>
+        <v>2</v>
       </c>
       <c r="E125" t="b">
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>10.18</v>
+        <v>28.56</v>
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>-2.58</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>RADIOCITY</t>
+          <t>JINDALSAW</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>5.78</v>
+        <v>198.04</v>
       </c>
       <c r="C126" t="n">
-        <v>5.95</v>
+        <v>202</v>
       </c>
       <c r="D126" t="n">
-        <v>2.94</v>
+        <v>2</v>
       </c>
       <c r="E126" t="b">
         <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>5.8</v>
+        <v>192.4</v>
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
-        <v>-2.52</v>
+        <v>-4.75</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BASML</t>
+          <t>LAGNAM</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>20.78</v>
+        <v>68.86</v>
       </c>
       <c r="C127" t="n">
-        <v>21.39</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="D127" t="n">
-        <v>2.94</v>
+        <v>2</v>
       </c>
       <c r="E127" t="b">
         <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>20.99</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
-        <v>-1.87</v>
+        <v>-2.69</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ABAN</t>
+          <t>HYBRIDFIN</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>24.58</v>
+        <v>16.98</v>
       </c>
       <c r="C128" t="n">
-        <v>25.3</v>
+        <v>17.32</v>
       </c>
       <c r="D128" t="n">
-        <v>2.93</v>
+        <v>2</v>
       </c>
       <c r="E128" t="b">
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>25.8</v>
+        <v>16.72</v>
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
-        <v>1.98</v>
+        <v>-3.46</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>EMKAY</t>
+          <t>SOUTHWEST</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>220.57</v>
+        <v>209.52</v>
       </c>
       <c r="C129" t="n">
-        <v>227</v>
+        <v>213.72</v>
       </c>
       <c r="D129" t="n">
-        <v>2.92</v>
+        <v>2</v>
       </c>
       <c r="E129" t="b">
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>226.52</v>
+        <v>203.4</v>
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
-        <v>-0.21</v>
+        <v>-4.83</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>HLVLTD</t>
+          <t>SUTLEJTEX</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>7.6</v>
+        <v>31.71</v>
       </c>
       <c r="C130" t="n">
-        <v>7.82</v>
+        <v>32.34</v>
       </c>
       <c r="D130" t="n">
-        <v>2.89</v>
+        <v>1.99</v>
       </c>
       <c r="E130" t="b">
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>7.79</v>
+        <v>31.18</v>
       </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
-        <v>-0.38</v>
+        <v>-3.59</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>STYLEBAAZA</t>
+          <t>TICL</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>275.15</v>
+        <v>25.99</v>
       </c>
       <c r="C131" t="n">
-        <v>283</v>
+        <v>26.5</v>
       </c>
       <c r="D131" t="n">
-        <v>2.85</v>
+        <v>1.96</v>
       </c>
       <c r="E131" t="b">
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>282.35</v>
+        <v>25.98</v>
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
-        <v>-0.23</v>
+        <v>-1.96</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>PARASPETRO</t>
+          <t>GVPTECH</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>2.13</v>
+        <v>6.23</v>
       </c>
       <c r="C132" t="n">
-        <v>2.19</v>
+        <v>6.35</v>
       </c>
       <c r="D132" t="n">
-        <v>2.82</v>
+        <v>1.93</v>
       </c>
       <c r="E132" t="b">
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>2.13</v>
+        <v>6.1</v>
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
-        <v>-2.74</v>
+        <v>-3.94</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SUMEETINDS</t>
+          <t>DENTALKART</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>30.06</v>
+        <v>402.3</v>
       </c>
       <c r="C133" t="n">
-        <v>30.9</v>
+        <v>409.95</v>
       </c>
       <c r="D133" t="n">
-        <v>2.79</v>
+        <v>1.9</v>
       </c>
       <c r="E133" t="b">
         <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>30.02</v>
+        <v>400.1</v>
       </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
-        <v>-2.85</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>GULFPETRO</t>
+          <t>TPHQ</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>30.95</v>
+        <v>0.53</v>
       </c>
       <c r="C134" t="n">
-        <v>31.8</v>
+        <v>0.54</v>
       </c>
       <c r="D134" t="n">
-        <v>2.75</v>
+        <v>1.89</v>
       </c>
       <c r="E134" t="b">
         <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>31.14</v>
+        <v>0.55</v>
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
-        <v>-2.08</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>AARVI</t>
+          <t>MAGNUM</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>132.8</v>
+        <v>19.62</v>
       </c>
       <c r="C135" t="n">
-        <v>136.4</v>
+        <v>19.99</v>
       </c>
       <c r="D135" t="n">
-        <v>2.71</v>
+        <v>1.89</v>
       </c>
       <c r="E135" t="b">
         <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>132.21</v>
+        <v>19.32</v>
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
-        <v>-3.07</v>
+        <v>-3.35</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>THEMISMED</t>
+          <t>AIRAN</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>81.70999999999999</v>
+        <v>15.92</v>
       </c>
       <c r="C136" t="n">
-        <v>83.90000000000001</v>
+        <v>16.22</v>
       </c>
       <c r="D136" t="n">
-        <v>2.68</v>
+        <v>1.88</v>
       </c>
       <c r="E136" t="b">
         <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>83.78</v>
+        <v>15.97</v>
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
-        <v>-0.14</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>TEXMOPIPES</t>
+          <t>SHAH</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>42.15</v>
+        <v>4.8</v>
       </c>
       <c r="C137" t="n">
-        <v>43.28</v>
+        <v>4.89</v>
       </c>
       <c r="D137" t="n">
-        <v>2.68</v>
+        <v>1.87</v>
       </c>
       <c r="E137" t="b">
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>45.2</v>
+        <v>4.82</v>
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
-        <v>4.44</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>TREL</t>
+          <t>PASHUPATI</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>24.6</v>
+        <v>990</v>
       </c>
       <c r="C138" t="n">
-        <v>25.25</v>
+        <v>1008</v>
       </c>
       <c r="D138" t="n">
-        <v>2.64</v>
+        <v>1.82</v>
       </c>
       <c r="E138" t="b">
         <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>24.44</v>
+        <v>996.25</v>
       </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
-        <v>-3.21</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>RUBFILA</t>
+          <t>ASMS</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>63.33</v>
+        <v>8.82</v>
       </c>
       <c r="C139" t="n">
-        <v>65</v>
+        <v>8.98</v>
       </c>
       <c r="D139" t="n">
-        <v>2.64</v>
+        <v>1.81</v>
       </c>
       <c r="E139" t="b">
         <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>64.77</v>
+        <v>8.84</v>
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
-        <v>-0.35</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>YASHO</t>
+          <t>ELECTCAST</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1393</v>
+        <v>75.62</v>
       </c>
       <c r="C140" t="n">
-        <v>1429.8</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="D140" t="n">
-        <v>2.64</v>
+        <v>1.81</v>
       </c>
       <c r="E140" t="b">
         <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>1415.7</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
-        <v>-0.99</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BOROLTD</t>
+          <t>MCLOUD</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>253.25</v>
+        <v>23.36</v>
       </c>
       <c r="C141" t="n">
-        <v>259.92</v>
+        <v>23.78</v>
       </c>
       <c r="D141" t="n">
-        <v>2.63</v>
+        <v>1.8</v>
       </c>
       <c r="E141" t="b">
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>260.59</v>
+        <v>22.86</v>
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
-        <v>0.26</v>
+        <v>-3.87</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>TOKYOPLAST</t>
+          <t>BAGFILMS</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>74.64</v>
+        <v>5</v>
       </c>
       <c r="C142" t="n">
-        <v>76.59999999999999</v>
+        <v>5.09</v>
       </c>
       <c r="D142" t="n">
-        <v>2.63</v>
+        <v>1.8</v>
       </c>
       <c r="E142" t="b">
         <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>75.40000000000001</v>
+        <v>5</v>
       </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
-        <v>-1.57</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>AVG</t>
+          <t>NIRMAN</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>135.85</v>
+        <v>50</v>
       </c>
       <c r="C143" t="n">
-        <v>139.4</v>
+        <v>50.9</v>
       </c>
       <c r="D143" t="n">
-        <v>2.61</v>
+        <v>1.8</v>
       </c>
       <c r="E143" t="b">
         <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>134.89</v>
+        <v>49.55</v>
       </c>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
-        <v>-3.24</v>
+        <v>-2.65</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>STEL</t>
+          <t>JMA</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>501.85</v>
+        <v>84.48</v>
       </c>
       <c r="C144" t="n">
-        <v>514.95</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="D144" t="n">
-        <v>2.61</v>
+        <v>1.79</v>
       </c>
       <c r="E144" t="b">
         <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>497.4</v>
+        <v>85.62</v>
       </c>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
-        <v>-3.41</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ISFT</t>
+          <t>AKASH</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>69.02</v>
+        <v>24.56</v>
       </c>
       <c r="C145" t="n">
-        <v>70.8</v>
+        <v>25</v>
       </c>
       <c r="D145" t="n">
-        <v>2.58</v>
+        <v>1.79</v>
       </c>
       <c r="E145" t="b">
         <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>74.61</v>
+        <v>24.95</v>
       </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
-        <v>5.38</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CNL</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>631.8</v>
+        <v>190.58</v>
       </c>
       <c r="C146" t="n">
-        <v>648</v>
+        <v>194</v>
       </c>
       <c r="D146" t="n">
-        <v>2.56</v>
+        <v>1.79</v>
       </c>
       <c r="E146" t="b">
         <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>637.95</v>
+        <v>199.3</v>
       </c>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
-        <v>-1.55</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>SETUINFRA</t>
+          <t>ATAM</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.39</v>
+        <v>62.82</v>
       </c>
       <c r="C147" t="n">
-        <v>0.4</v>
+        <v>63.93</v>
       </c>
       <c r="D147" t="n">
-        <v>2.56</v>
+        <v>1.77</v>
       </c>
       <c r="E147" t="b">
         <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>0.38</v>
+        <v>62</v>
       </c>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
-        <v>-5</v>
+        <v>-3.02</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>AKSHAR</t>
+          <t>EMSLIMITED</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.4</v>
+        <v>311.4</v>
       </c>
       <c r="C148" t="n">
-        <v>0.41</v>
+        <v>316.85</v>
       </c>
       <c r="D148" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="E148" t="b">
         <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>0.41</v>
+        <v>303.7</v>
       </c>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
-        <v>0</v>
+        <v>-4.15</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>LORDSCHLO</t>
+          <t>MOTOGENFIN</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>123.82</v>
+        <v>20.1</v>
       </c>
       <c r="C149" t="n">
-        <v>126.91</v>
+        <v>20.45</v>
       </c>
       <c r="D149" t="n">
-        <v>2.5</v>
+        <v>1.74</v>
       </c>
       <c r="E149" t="b">
         <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>124.66</v>
+        <v>20.1</v>
       </c>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
-        <v>-1.77</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>WAAREERTL</t>
+          <t>SAHAJSOLAR</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>797.25</v>
+        <v>110</v>
       </c>
       <c r="C150" t="n">
-        <v>817.1</v>
+        <v>111.9</v>
       </c>
       <c r="D150" t="n">
-        <v>2.49</v>
+        <v>1.73</v>
       </c>
       <c r="E150" t="b">
         <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>830.1</v>
+        <v>110.2</v>
       </c>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
-        <v>1.59</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>BALKRISHNA</t>
+          <t>BLAL</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>12.88</v>
+        <v>176.75</v>
       </c>
       <c r="C151" t="n">
-        <v>13.2</v>
+        <v>179.8</v>
       </c>
       <c r="D151" t="n">
-        <v>2.48</v>
+        <v>1.73</v>
       </c>
       <c r="E151" t="b">
         <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>12.81</v>
+        <v>176.63</v>
       </c>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
-        <v>-2.95</v>
+        <v>-1.76</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>RAMKY</t>
+          <t>BVCL</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>458.7</v>
+        <v>39.72</v>
       </c>
       <c r="C152" t="n">
-        <v>470</v>
+        <v>40.4</v>
       </c>
       <c r="D152" t="n">
-        <v>2.46</v>
+        <v>1.71</v>
       </c>
       <c r="E152" t="b">
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>464.35</v>
+        <v>40.1</v>
       </c>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="n">
-        <v>-1.2</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>MARKOLINES</t>
+          <t>MIRCELECTR</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>152.96</v>
+        <v>25.17</v>
       </c>
       <c r="C153" t="n">
-        <v>156.7</v>
+        <v>25.6</v>
       </c>
       <c r="D153" t="n">
-        <v>2.45</v>
+        <v>1.71</v>
       </c>
       <c r="E153" t="b">
         <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>155.89</v>
+        <v>24.78</v>
       </c>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="n">
-        <v>-0.52</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>AKI</t>
+          <t>FLEXITUFF</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>4.92</v>
+        <v>7.01</v>
       </c>
       <c r="C154" t="n">
-        <v>5.04</v>
+        <v>7.13</v>
       </c>
       <c r="D154" t="n">
-        <v>2.44</v>
+        <v>1.71</v>
       </c>
       <c r="E154" t="b">
         <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>4.97</v>
+        <v>7.05</v>
       </c>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="n">
-        <v>-1.39</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>AHLADA</t>
+          <t>RELIABLE</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>40.47</v>
+        <v>119.96</v>
       </c>
       <c r="C155" t="n">
-        <v>41.44</v>
+        <v>122</v>
       </c>
       <c r="D155" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="E155" t="b">
         <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>43.75</v>
+        <v>120.75</v>
       </c>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="n">
-        <v>5.57</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>TARSONS</t>
+          <t>SUPERSPIN</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>194.34</v>
+        <v>5.3</v>
       </c>
       <c r="C156" t="n">
-        <v>199</v>
+        <v>5.39</v>
       </c>
       <c r="D156" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="E156" t="b">
         <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>197.59</v>
+        <v>5.1</v>
       </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="n">
-        <v>-0.71</v>
+        <v>-5.38</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>COMSYN</t>
+          <t>PRAKASHSTL</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>154.83</v>
+        <v>4.17</v>
       </c>
       <c r="C157" t="n">
-        <v>158.5</v>
+        <v>4.24</v>
       </c>
       <c r="D157" t="n">
-        <v>2.37</v>
+        <v>1.68</v>
       </c>
       <c r="E157" t="b">
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>155.61</v>
+        <v>4.13</v>
       </c>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="n">
-        <v>-1.82</v>
+        <v>-2.59</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>FINPIPE</t>
+          <t>PRITIKAUTO</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>185.35</v>
+        <v>12.48</v>
       </c>
       <c r="C158" t="n">
-        <v>189.72</v>
+        <v>12.69</v>
       </c>
       <c r="D158" t="n">
-        <v>2.36</v>
+        <v>1.68</v>
       </c>
       <c r="E158" t="b">
         <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>190.48</v>
+        <v>12.3</v>
       </c>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="n">
-        <v>0.4</v>
+        <v>-3.07</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>GKENERGY</t>
+          <t>RELCHEMQ</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>105.42</v>
+        <v>113</v>
       </c>
       <c r="C159" t="n">
-        <v>107.9</v>
+        <v>114.88</v>
       </c>
       <c r="D159" t="n">
-        <v>2.35</v>
+        <v>1.66</v>
       </c>
       <c r="E159" t="b">
         <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>110.69</v>
+        <v>112.62</v>
       </c>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="n">
-        <v>2.59</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>BHARATSE</t>
+          <t>TPLPLASTEH</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>175.88</v>
+        <v>61.98</v>
       </c>
       <c r="C160" t="n">
-        <v>180</v>
+        <v>63</v>
       </c>
       <c r="D160" t="n">
-        <v>2.34</v>
+        <v>1.65</v>
       </c>
       <c r="E160" t="b">
         <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>176.1</v>
+        <v>61.7</v>
       </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="n">
-        <v>-2.17</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>VIKASECO</t>
+          <t>JINDRILL</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>1.29</v>
+        <v>531.25</v>
       </c>
       <c r="C161" t="n">
-        <v>1.32</v>
+        <v>540</v>
       </c>
       <c r="D161" t="n">
-        <v>2.33</v>
+        <v>1.65</v>
       </c>
       <c r="E161" t="b">
         <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>1.31</v>
+        <v>524.3</v>
       </c>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="n">
-        <v>-0.76</v>
+        <v>-2.91</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>MITTAL</t>
+          <t>MTNL</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.86</v>
+        <v>26.06</v>
       </c>
       <c r="C162" t="n">
-        <v>0.88</v>
+        <v>26.49</v>
       </c>
       <c r="D162" t="n">
-        <v>2.33</v>
+        <v>1.65</v>
       </c>
       <c r="E162" t="b">
         <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>0.86</v>
+        <v>25.56</v>
       </c>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="n">
-        <v>-2.27</v>
+        <v>-3.51</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ESSENTIA</t>
+          <t>5PAISA</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>1.3</v>
+        <v>304</v>
       </c>
       <c r="C163" t="n">
-        <v>1.33</v>
+        <v>309</v>
       </c>
       <c r="D163" t="n">
-        <v>2.31</v>
+        <v>1.64</v>
       </c>
       <c r="E163" t="b">
         <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>1.32</v>
+        <v>301.3</v>
       </c>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="n">
-        <v>-0.75</v>
+        <v>-2.49</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>PYRAMID</t>
+          <t>ROTO</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>148.89</v>
+        <v>60.97</v>
       </c>
       <c r="C164" t="n">
-        <v>152.3</v>
+        <v>61.97</v>
       </c>
       <c r="D164" t="n">
-        <v>2.29</v>
+        <v>1.64</v>
       </c>
       <c r="E164" t="b">
         <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>149.17</v>
+        <v>60.65</v>
       </c>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="n">
-        <v>-2.06</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>MIRCELECTR</t>
+          <t>MEDICO</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>24.92</v>
+        <v>40.84</v>
       </c>
       <c r="C165" t="n">
-        <v>25.49</v>
+        <v>41.5</v>
       </c>
       <c r="D165" t="n">
-        <v>2.29</v>
+        <v>1.62</v>
       </c>
       <c r="E165" t="b">
         <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>25.79</v>
+        <v>40.2</v>
       </c>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="n">
-        <v>1.18</v>
+        <v>-3.13</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>JAYKAY</t>
+          <t>PAUSHAKLTD</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>139.62</v>
+        <v>418.25</v>
       </c>
       <c r="C166" t="n">
-        <v>142.8</v>
+        <v>425</v>
       </c>
       <c r="D166" t="n">
-        <v>2.28</v>
+        <v>1.61</v>
       </c>
       <c r="E166" t="b">
         <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>138.21</v>
+        <v>420.45</v>
       </c>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="n">
-        <v>-3.21</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>RUCHIRA</t>
+          <t>KILITCH</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>103.44</v>
+        <v>317.9</v>
       </c>
       <c r="C167" t="n">
-        <v>105.8</v>
+        <v>323</v>
       </c>
       <c r="D167" t="n">
-        <v>2.28</v>
+        <v>1.6</v>
       </c>
       <c r="E167" t="b">
         <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>104.42</v>
+        <v>319.2</v>
       </c>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="n">
-        <v>-1.3</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>GINNIFILA</t>
+          <t>NDL</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>32.76</v>
+        <v>2.52</v>
       </c>
       <c r="C168" t="n">
-        <v>33.5</v>
+        <v>2.56</v>
       </c>
       <c r="D168" t="n">
-        <v>2.26</v>
+        <v>1.59</v>
       </c>
       <c r="E168" t="b">
         <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>35.98</v>
+        <v>2.47</v>
       </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="n">
-        <v>7.4</v>
+        <v>-3.52</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>KEYFINSERV</t>
+          <t>SAILIFE</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>266.1</v>
+        <v>1014</v>
       </c>
       <c r="C169" t="n">
-        <v>272</v>
+        <v>1030.05</v>
       </c>
       <c r="D169" t="n">
-        <v>2.22</v>
+        <v>1.58</v>
       </c>
       <c r="E169" t="b">
         <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>271.5</v>
+        <v>993.8</v>
       </c>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="n">
-        <v>-0.18</v>
+        <v>-3.52</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>GATECHDVR</t>
+          <t>ASIANENE</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.45</v>
+        <v>280.65</v>
       </c>
       <c r="C170" t="n">
-        <v>0.46</v>
+        <v>285</v>
       </c>
       <c r="D170" t="n">
-        <v>2.22</v>
+        <v>1.55</v>
       </c>
       <c r="E170" t="b">
         <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>0.46</v>
+        <v>285</v>
       </c>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="n">
@@ -4851,807 +4855,803 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>KANANIIND</t>
+          <t>GLOBE</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>1.36</v>
+        <v>2.59</v>
       </c>
       <c r="C171" t="n">
-        <v>1.39</v>
+        <v>2.63</v>
       </c>
       <c r="D171" t="n">
-        <v>2.21</v>
+        <v>1.54</v>
       </c>
       <c r="E171" t="b">
         <v>0</v>
       </c>
       <c r="F171" t="n">
-        <v>1.35</v>
+        <v>2.55</v>
       </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="n">
-        <v>-2.88</v>
+        <v>-3.04</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>WANBURY</t>
+          <t>UNITEDPOLY</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>243.45</v>
+        <v>27.53</v>
       </c>
       <c r="C172" t="n">
-        <v>248.8</v>
+        <v>27.95</v>
       </c>
       <c r="D172" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="E172" t="b">
         <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>244.15</v>
+        <v>26.94</v>
       </c>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="n">
-        <v>-1.87</v>
+        <v>-3.61</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>HITECH</t>
+          <t>SOLEX</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>79.16</v>
+        <v>879.35</v>
       </c>
       <c r="C173" t="n">
-        <v>80.90000000000001</v>
+        <v>892.55</v>
       </c>
       <c r="D173" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="E173" t="b">
         <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>83.76000000000001</v>
+        <v>860</v>
       </c>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="n">
-        <v>3.54</v>
+        <v>-3.65</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>RBZJEWEL</t>
+          <t>SURANAT&amp;P</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>120.84</v>
+        <v>17.05</v>
       </c>
       <c r="C174" t="n">
-        <v>123.49</v>
+        <v>17.3</v>
       </c>
       <c r="D174" t="n">
-        <v>2.19</v>
+        <v>1.47</v>
       </c>
       <c r="E174" t="b">
         <v>0</v>
       </c>
-      <c r="F174" t="n">
-        <v>120.69</v>
-      </c>
+      <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr"/>
-      <c r="H174" t="n">
-        <v>-2.27</v>
-      </c>
+      <c r="H174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>VARDMNPOLY</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>8.789999999999999</v>
+        <v>397.75</v>
       </c>
       <c r="C175" t="n">
-        <v>8.98</v>
+        <v>403.5</v>
       </c>
       <c r="D175" t="n">
-        <v>2.16</v>
+        <v>1.45</v>
       </c>
       <c r="E175" t="b">
         <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>8.84</v>
+        <v>393.6</v>
       </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="n">
-        <v>-1.56</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>YAAP</t>
+          <t>ONESOURCE</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>141.75</v>
+        <v>1473.6</v>
       </c>
       <c r="C176" t="n">
-        <v>144.8</v>
+        <v>1494.9</v>
       </c>
       <c r="D176" t="n">
-        <v>2.15</v>
+        <v>1.45</v>
       </c>
       <c r="E176" t="b">
         <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>148.8</v>
+        <v>1436</v>
       </c>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="n">
-        <v>2.76</v>
+        <v>-3.94</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>OILCOUNTUB</t>
+          <t>GUJGASLTD</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>46.01</v>
+        <v>391</v>
       </c>
       <c r="C177" t="n">
-        <v>46.99</v>
+        <v>396.6</v>
       </c>
       <c r="D177" t="n">
-        <v>2.13</v>
+        <v>1.43</v>
       </c>
       <c r="E177" t="b">
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>46.3</v>
+        <v>399</v>
       </c>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="n">
-        <v>-1.47</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>UFO</t>
+          <t>LINC</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>67.08</v>
+        <v>102.46</v>
       </c>
       <c r="C178" t="n">
-        <v>68.5</v>
+        <v>103.9</v>
       </c>
       <c r="D178" t="n">
-        <v>2.12</v>
+        <v>1.41</v>
       </c>
       <c r="E178" t="b">
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>67.51000000000001</v>
+        <v>102.74</v>
       </c>
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="n">
-        <v>-1.45</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>DIFFNKG</t>
+          <t>JHS</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>263.15</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="C179" t="n">
-        <v>268.7</v>
+        <v>9.49</v>
       </c>
       <c r="D179" t="n">
-        <v>2.11</v>
+        <v>1.39</v>
       </c>
       <c r="E179" t="b">
         <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>267.4</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="n">
-        <v>-0.48</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>DRONE</t>
+          <t>BANKA</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>45.1</v>
+        <v>51.77</v>
       </c>
       <c r="C180" t="n">
-        <v>46.05</v>
+        <v>52.49</v>
       </c>
       <c r="D180" t="n">
-        <v>2.11</v>
+        <v>1.39</v>
       </c>
       <c r="E180" t="b">
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>47.3</v>
+        <v>51.5</v>
       </c>
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="n">
-        <v>2.71</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ISHANCH</t>
+          <t>SUPREME</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>59.55</v>
+        <v>55.14</v>
       </c>
       <c r="C181" t="n">
-        <v>60.8</v>
+        <v>55.9</v>
       </c>
       <c r="D181" t="n">
-        <v>2.1</v>
+        <v>1.38</v>
       </c>
       <c r="E181" t="b">
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>59.5</v>
+        <v>50.85</v>
       </c>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="n">
-        <v>-2.14</v>
+        <v>-9.029999999999999</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>AKASH</t>
+          <t>NILAINFRA</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>24.24</v>
+        <v>7.39</v>
       </c>
       <c r="C182" t="n">
-        <v>24.75</v>
+        <v>7.49</v>
       </c>
       <c r="D182" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="E182" t="b">
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>24.6</v>
+        <v>7.32</v>
       </c>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="n">
-        <v>-0.61</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>DNAMEDIA</t>
+          <t>TNTELE</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>3.33</v>
+        <v>8.93</v>
       </c>
       <c r="C183" t="n">
-        <v>3.4</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="D183" t="n">
-        <v>2.1</v>
+        <v>1.34</v>
       </c>
       <c r="E183" t="b">
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>3.38</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="n">
-        <v>-0.59</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>KSB</t>
+          <t>SONAMLTD</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>761.25</v>
+        <v>55.25</v>
       </c>
       <c r="C184" t="n">
-        <v>777</v>
+        <v>55.98</v>
       </c>
       <c r="D184" t="n">
-        <v>2.07</v>
+        <v>1.32</v>
       </c>
       <c r="E184" t="b">
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>776.55</v>
+        <v>58.65</v>
       </c>
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="n">
-        <v>-0.06</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>JINDRILL</t>
+          <t>JUSTDIAL</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>542.2</v>
+        <v>535.35</v>
       </c>
       <c r="C185" t="n">
-        <v>553.35</v>
+        <v>542.35</v>
       </c>
       <c r="D185" t="n">
-        <v>2.06</v>
+        <v>1.31</v>
       </c>
       <c r="E185" t="b">
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>538.45</v>
+        <v>519.3</v>
       </c>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="n">
-        <v>-2.69</v>
+        <v>-4.25</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>3IINFOLTD</t>
+          <t>VENUSREM</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>13.13</v>
+        <v>861.7</v>
       </c>
       <c r="C186" t="n">
-        <v>13.4</v>
+        <v>872.95</v>
       </c>
       <c r="D186" t="n">
-        <v>2.06</v>
+        <v>1.31</v>
       </c>
       <c r="E186" t="b">
         <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>13.56</v>
+        <v>918.9</v>
       </c>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="n">
-        <v>1.19</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>GATECH</t>
+          <t>INDOTHAI</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.49</v>
+        <v>261.6</v>
       </c>
       <c r="C187" t="n">
-        <v>0.5</v>
+        <v>265</v>
       </c>
       <c r="D187" t="n">
-        <v>2.04</v>
+        <v>1.3</v>
       </c>
       <c r="E187" t="b">
         <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>0.48</v>
+        <v>258.05</v>
       </c>
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="n">
-        <v>-4</v>
+        <v>-2.62</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>KNAGRI</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>184.24</v>
+        <v>380.15</v>
       </c>
       <c r="C188" t="n">
-        <v>188</v>
+        <v>385</v>
       </c>
       <c r="D188" t="n">
-        <v>2.04</v>
+        <v>1.28</v>
       </c>
       <c r="E188" t="b">
         <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>187.78</v>
+        <v>387.75</v>
       </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="n">
-        <v>-0.12</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>PRIMO</t>
+          <t>GKENERGY</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>17.29</v>
+        <v>110.58</v>
       </c>
       <c r="C189" t="n">
-        <v>17.64</v>
+        <v>112</v>
       </c>
       <c r="D189" t="n">
-        <v>2.02</v>
+        <v>1.28</v>
       </c>
       <c r="E189" t="b">
         <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>17.76</v>
+        <v>109.07</v>
       </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="n">
-        <v>0.68</v>
+        <v>-2.62</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ESAFSFB</t>
+          <t>XELPMOC</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>25.19</v>
+        <v>116.91</v>
       </c>
       <c r="C190" t="n">
-        <v>25.7</v>
+        <v>118.4</v>
       </c>
       <c r="D190" t="n">
-        <v>2.02</v>
+        <v>1.27</v>
       </c>
       <c r="E190" t="b">
         <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>25.55</v>
+        <v>115</v>
       </c>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="n">
-        <v>-0.58</v>
+        <v>-2.87</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>NDL</t>
+          <t>BAJAJINDEF</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>2.48</v>
+        <v>238.66</v>
       </c>
       <c r="C191" t="n">
-        <v>2.53</v>
+        <v>241.65</v>
       </c>
       <c r="D191" t="n">
-        <v>2.02</v>
+        <v>1.25</v>
       </c>
       <c r="E191" t="b">
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>2.55</v>
+        <v>256.4</v>
       </c>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="n">
-        <v>0.79</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>BELLACASA</t>
+          <t>ACCURACY</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>262.4</v>
+        <v>4</v>
       </c>
       <c r="C192" t="n">
-        <v>267.7</v>
+        <v>4.05</v>
       </c>
       <c r="D192" t="n">
-        <v>2.02</v>
+        <v>1.25</v>
       </c>
       <c r="E192" t="b">
         <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>264.8</v>
+        <v>4</v>
       </c>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="n">
-        <v>-1.08</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>HINDCON</t>
+          <t>SERVOTECH</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>18.91</v>
+        <v>68.16</v>
       </c>
       <c r="C193" t="n">
-        <v>19.29</v>
+        <v>69</v>
       </c>
       <c r="D193" t="n">
-        <v>2.01</v>
+        <v>1.23</v>
       </c>
       <c r="E193" t="b">
         <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>20.05</v>
+        <v>69.75</v>
       </c>
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="n">
-        <v>3.94</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ODIGMA</t>
+          <t>RUDRA</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>23.87</v>
+        <v>17.28</v>
       </c>
       <c r="C194" t="n">
-        <v>24.35</v>
+        <v>17.49</v>
       </c>
       <c r="D194" t="n">
-        <v>2.01</v>
+        <v>1.22</v>
       </c>
       <c r="E194" t="b">
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>24.2</v>
+        <v>17.4</v>
       </c>
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="n">
-        <v>-0.62</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>TEJASNET</t>
+          <t>CYBERTECH</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>464.4</v>
+        <v>106.7</v>
       </c>
       <c r="C195" t="n">
-        <v>473.7</v>
+        <v>108</v>
       </c>
       <c r="D195" t="n">
-        <v>2</v>
+        <v>1.22</v>
       </c>
       <c r="E195" t="b">
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>479.25</v>
+        <v>102.55</v>
       </c>
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="n">
-        <v>1.17</v>
+        <v>-5.05</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>MOLDTECH</t>
+          <t>ORBTEXP</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>129.87</v>
+        <v>162.82</v>
       </c>
       <c r="C196" t="n">
-        <v>132.47</v>
+        <v>164.8</v>
       </c>
       <c r="D196" t="n">
-        <v>2</v>
+        <v>1.22</v>
       </c>
       <c r="E196" t="b">
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>134.68</v>
+        <v>161.9</v>
       </c>
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="n">
-        <v>1.67</v>
+        <v>-1.76</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>GRMOVER</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>156.38</v>
+        <v>721.55</v>
       </c>
       <c r="C197" t="n">
-        <v>159.5</v>
+        <v>730.25</v>
       </c>
       <c r="D197" t="n">
-        <v>2</v>
+        <v>1.21</v>
       </c>
       <c r="E197" t="b">
         <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>158.66</v>
+        <v>709.4</v>
       </c>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="n">
-        <v>-0.53</v>
+        <v>-2.86</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>GLOBAL</t>
+          <t>SUMIT</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>107.61</v>
+        <v>33.4</v>
       </c>
       <c r="C198" t="n">
-        <v>109.76</v>
+        <v>33.8</v>
       </c>
       <c r="D198" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="E198" t="b">
         <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>107.96</v>
+        <v>33.89</v>
       </c>
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="n">
-        <v>-1.64</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>UNIVASTU</t>
+          <t>HEIDELBERG</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>65.18000000000001</v>
+        <v>157.13</v>
       </c>
       <c r="C199" t="n">
-        <v>66.48</v>
+        <v>159</v>
       </c>
       <c r="D199" t="n">
-        <v>1.99</v>
+        <v>1.19</v>
       </c>
       <c r="E199" t="b">
         <v>0</v>
       </c>
       <c r="F199" t="n">
-        <v>65</v>
+        <v>157.09</v>
       </c>
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="n">
-        <v>-2.23</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>BANCOINDIA</t>
+          <t>TEXMOPIPES</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>571.3</v>
+        <v>44.47</v>
       </c>
       <c r="C200" t="n">
-        <v>582.6</v>
+        <v>45</v>
       </c>
       <c r="D200" t="n">
-        <v>1.98</v>
+        <v>1.19</v>
       </c>
       <c r="E200" t="b">
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>577.4</v>
+        <v>44.53</v>
       </c>
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="n">
-        <v>-0.89</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ASTRON</t>
+          <t>ORIENTBELL</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>4.04</v>
+        <v>256.45</v>
       </c>
       <c r="C201" t="n">
-        <v>4.12</v>
+        <v>259.5</v>
       </c>
       <c r="D201" t="n">
-        <v>1.98</v>
+        <v>1.19</v>
       </c>
       <c r="E201" t="b">
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>4.13</v>
+        <v>267</v>
       </c>
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="n">
-        <v>0.24</v>
+        <v>2.89</v>
       </c>
     </row>
   </sheetData>

--- a/data/trending_momentum_stocks.xlsx
+++ b/data/trending_momentum_stocks.xlsx
@@ -461,335 +461,335 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SHANTI</t>
+          <t>BHANDA-RE2</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.32</v>
+        <v>0.02</v>
       </c>
       <c r="C2" t="n">
-        <v>7.3</v>
+        <v>0.03</v>
       </c>
       <c r="D2" t="n">
-        <v>15.51</v>
+        <v>50</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>6.56</v>
+        <v>0.02</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>-10.14</v>
+        <v>-33.33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>UMESLTD</t>
+          <t>ICDSLTD</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.99</v>
+        <v>45.37</v>
       </c>
       <c r="C3" t="n">
-        <v>5.7</v>
+        <v>50</v>
       </c>
       <c r="D3" t="n">
-        <v>14.23</v>
+        <v>10.2</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>5.98</v>
+        <v>54.44</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>4.91</v>
+        <v>8.880000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DCMFINSERV</t>
+          <t>KANDARP</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.62</v>
+        <v>140</v>
       </c>
       <c r="C4" t="n">
-        <v>6.24</v>
+        <v>152.8</v>
       </c>
       <c r="D4" t="n">
-        <v>11.03</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>6.74</v>
+        <v>132.5</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>8.01</v>
+        <v>-13.29</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LPDC</t>
+          <t>DCMFINSERV</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.86</v>
+        <v>6.74</v>
       </c>
       <c r="C5" t="n">
-        <v>6.45</v>
+        <v>7.26</v>
       </c>
       <c r="D5" t="n">
-        <v>10.07</v>
+        <v>7.72</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>5.76</v>
+        <v>7.41</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>-10.7</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CYBERMEDIA</t>
+          <t>REGAAL</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13.94</v>
+        <v>87.69</v>
       </c>
       <c r="C6" t="n">
-        <v>15.33</v>
+        <v>94</v>
       </c>
       <c r="D6" t="n">
-        <v>9.970000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>13.69</v>
+        <v>86</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>-10.7</v>
+        <v>-8.51</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TTKPRESTIG</t>
+          <t>DHARAN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>535.45</v>
+        <v>0.14</v>
       </c>
       <c r="C7" t="n">
-        <v>585</v>
+        <v>0.15</v>
       </c>
       <c r="D7" t="n">
-        <v>9.25</v>
+        <v>7.14</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>568</v>
+        <v>0.15</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>-2.91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SATKARTAR</t>
+          <t>UMESLTD</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>161.2</v>
+        <v>5.98</v>
       </c>
       <c r="C8" t="n">
-        <v>175.95</v>
+        <v>6.4</v>
       </c>
       <c r="D8" t="n">
-        <v>9.15</v>
+        <v>7.02</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>167</v>
+        <v>6.25</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>-5.09</v>
+        <v>-2.34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BIOPOL</t>
+          <t>GSS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>101</v>
+        <v>11.98</v>
       </c>
       <c r="C9" t="n">
-        <v>109.9</v>
+        <v>12.78</v>
       </c>
       <c r="D9" t="n">
-        <v>8.81</v>
+        <v>6.68</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>101</v>
+        <v>11.91</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>-8.1</v>
+        <v>-6.81</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OSWALAGRO</t>
+          <t>MAHAPEXLTD</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>43.61</v>
+        <v>115.39</v>
       </c>
       <c r="C10" t="n">
-        <v>46.99</v>
+        <v>123</v>
       </c>
       <c r="D10" t="n">
-        <v>7.75</v>
+        <v>6.6</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>43.23</v>
+        <v>118.98</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>-8</v>
+        <v>-3.27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RVHL</t>
+          <t>INFOMEDIA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>38.37</v>
+        <v>5.15</v>
       </c>
       <c r="C11" t="n">
-        <v>41.27</v>
+        <v>5.48</v>
       </c>
       <c r="D11" t="n">
-        <v>7.56</v>
+        <v>6.41</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>38.01</v>
+        <v>5.15</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>-7.9</v>
+        <v>-6.02</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>URAVIDEF</t>
+          <t>LFIC</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>133.57</v>
+        <v>125.92</v>
       </c>
       <c r="C12" t="n">
-        <v>143</v>
+        <v>133.5</v>
       </c>
       <c r="D12" t="n">
-        <v>7.06</v>
+        <v>6.02</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>133.35</v>
+        <v>127.99</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>-6.75</v>
+        <v>-4.13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>INFOMEDIA</t>
+          <t>TOUCHWOOD</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.04</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="C13" t="n">
-        <v>5.39</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>6.94</v>
+        <v>5.78</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>5.19</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>-3.71</v>
+        <v>-6.39</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DHARAN</t>
+          <t>FILATFASH</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="C14" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="D14" t="n">
-        <v>6.67</v>
+        <v>5.56</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
@@ -799,283 +799,283 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UNIINFO</t>
+          <t>GJL</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10.77</v>
+        <v>216.75</v>
       </c>
       <c r="C15" t="n">
-        <v>11.48</v>
+        <v>227.55</v>
       </c>
       <c r="D15" t="n">
-        <v>6.59</v>
+        <v>4.98</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>11.69</v>
+        <v>227.55</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VINNY</t>
+          <t>SANGINITA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.11</v>
+        <v>14.28</v>
       </c>
       <c r="C16" t="n">
-        <v>1.18</v>
+        <v>14.99</v>
       </c>
       <c r="D16" t="n">
-        <v>6.31</v>
+        <v>4.97</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.15</v>
+        <v>14.99</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>-2.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MAHAPEXLTD</t>
+          <t>SADHNANIQ</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>107.57</v>
+        <v>1.61</v>
       </c>
       <c r="C17" t="n">
-        <v>114</v>
+        <v>1.69</v>
       </c>
       <c r="D17" t="n">
-        <v>5.98</v>
+        <v>4.97</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>113</v>
+        <v>1.69</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>-0.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NGLFINE</t>
+          <t>MORARJEE</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2431</v>
+        <v>6.66</v>
       </c>
       <c r="C18" t="n">
-        <v>2575</v>
+        <v>6.99</v>
       </c>
       <c r="D18" t="n">
-        <v>5.92</v>
+        <v>4.95</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>2337.8</v>
+        <v>6.99</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>-9.210000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SRD</t>
+          <t>VIJIFIN</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>50.07</v>
+        <v>2.63</v>
       </c>
       <c r="C19" t="n">
-        <v>52.99</v>
+        <v>2.76</v>
       </c>
       <c r="D19" t="n">
-        <v>5.83</v>
+        <v>4.94</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>49.64</v>
+        <v>2.76</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>-6.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CROWN</t>
+          <t>ONELIFECAP</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>120.96</v>
+        <v>15.22</v>
       </c>
       <c r="C20" t="n">
-        <v>127.85</v>
+        <v>15.95</v>
       </c>
       <c r="D20" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>119.55</v>
+        <v>15.83</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>-6.49</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GLOBECIVIL</t>
+          <t>GSLSU</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>46.5</v>
+        <v>70.19</v>
       </c>
       <c r="C21" t="n">
-        <v>48.95</v>
+        <v>73.5</v>
       </c>
       <c r="D21" t="n">
-        <v>5.27</v>
+        <v>4.72</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>46.16</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>-5.7</v>
+        <v>-8.300000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FILATFASH</t>
+          <t>SHAHALLOYS</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.19</v>
+        <v>61.95</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2</v>
+        <v>64.8</v>
       </c>
       <c r="D22" t="n">
-        <v>5.26</v>
+        <v>4.6</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.19</v>
+        <v>59.82</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>-5</v>
+        <v>-7.69</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SANGINITA</t>
+          <t>SAMBHAAV</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13.6</v>
+        <v>6.41</v>
       </c>
       <c r="C23" t="n">
-        <v>14.28</v>
+        <v>6.7</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>4.52</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>14.28</v>
+        <v>6.29</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>-6.12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SEJALLTD</t>
+          <t>JPASSOCIAT</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>524.65</v>
+        <v>2.67</v>
       </c>
       <c r="C24" t="n">
-        <v>550.85</v>
+        <v>2.79</v>
       </c>
       <c r="D24" t="n">
-        <v>4.99</v>
+        <v>4.49</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>526.9</v>
+        <v>2.8</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>-4.35</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GJL</t>
+          <t>REXPRO</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>206.45</v>
+        <v>43</v>
       </c>
       <c r="C25" t="n">
-        <v>216.75</v>
+        <v>44.9</v>
       </c>
       <c r="D25" t="n">
-        <v>4.99</v>
+        <v>4.42</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>216.75</v>
+        <v>44.9</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
@@ -1085,153 +1085,153 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ACETEC</t>
+          <t>CONFIPET</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>129.6</v>
+        <v>35.45</v>
       </c>
       <c r="C26" t="n">
-        <v>136.05</v>
+        <v>37</v>
       </c>
       <c r="D26" t="n">
-        <v>4.98</v>
+        <v>4.37</v>
       </c>
       <c r="E26" t="b">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>136.05</v>
+        <v>37.03</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TCIFINANCE</t>
+          <t>PILITA</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>14.83</v>
+        <v>7.81</v>
       </c>
       <c r="C27" t="n">
-        <v>15.55</v>
+        <v>8.15</v>
       </c>
       <c r="D27" t="n">
-        <v>4.86</v>
+        <v>4.35</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>14.31</v>
+        <v>7.86</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>-7.97</v>
+        <v>-3.56</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LCCINFOTEC</t>
+          <t>RAJTV</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5.17</v>
+        <v>39.18</v>
       </c>
       <c r="C28" t="n">
-        <v>5.42</v>
+        <v>40.85</v>
       </c>
       <c r="D28" t="n">
-        <v>4.84</v>
+        <v>4.26</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>5.42</v>
+        <v>38.8</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>-5.02</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>VASCONEQ</t>
+          <t>JHS</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>34.23</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>35.88</v>
+        <v>9.35</v>
       </c>
       <c r="D29" t="n">
-        <v>4.82</v>
+        <v>4.24</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>34.4</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>-4.12</v>
+        <v>-5.24</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>HEADSUP</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>566.9</v>
+        <v>7.13</v>
       </c>
       <c r="C30" t="n">
-        <v>594</v>
+        <v>7.43</v>
       </c>
       <c r="D30" t="n">
-        <v>4.78</v>
+        <v>4.21</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>612.3</v>
+        <v>7.22</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>3.08</v>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SANWARIA</t>
+          <t>AURIGROW</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="C31" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="D31" t="n">
-        <v>4.76</v>
+        <v>4.17</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
@@ -1241,1219 +1241,1219 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BSL</t>
+          <t>THEJO</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>126.6</v>
+        <v>1651.3</v>
       </c>
       <c r="C32" t="n">
-        <v>132.6</v>
+        <v>1720</v>
       </c>
       <c r="D32" t="n">
-        <v>4.74</v>
+        <v>4.16</v>
       </c>
       <c r="E32" t="b">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>125.1</v>
+        <v>1620</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>-5.66</v>
+        <v>-5.81</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>KRIDHANINF</t>
+          <t>FMNL</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.77</v>
+        <v>8.26</v>
       </c>
       <c r="C33" t="n">
-        <v>2.9</v>
+        <v>8.6</v>
       </c>
       <c r="D33" t="n">
-        <v>4.69</v>
+        <v>4.12</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>2.79</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>-3.79</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TCPLPACK</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2441</v>
+        <v>110.48</v>
       </c>
       <c r="C34" t="n">
-        <v>2555</v>
+        <v>114.9</v>
       </c>
       <c r="D34" t="n">
-        <v>4.67</v>
+        <v>4</v>
       </c>
       <c r="E34" t="b">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>2547</v>
+        <v>109.8</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>-0.31</v>
+        <v>-4.44</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SAMPANN</t>
+          <t>BALKRISHNA</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>27.59</v>
+        <v>14.77</v>
       </c>
       <c r="C35" t="n">
-        <v>28.87</v>
+        <v>15.35</v>
       </c>
       <c r="D35" t="n">
-        <v>4.64</v>
+        <v>3.93</v>
       </c>
       <c r="E35" t="b">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>28.49</v>
+        <v>15.2</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>-1.32</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SURAJLTD</t>
+          <t>DEVX</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>229.54</v>
+        <v>37.52</v>
       </c>
       <c r="C36" t="n">
-        <v>239.99</v>
+        <v>38.99</v>
       </c>
       <c r="D36" t="n">
-        <v>4.55</v>
+        <v>3.92</v>
       </c>
       <c r="E36" t="b">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>238</v>
+        <v>36.61</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>-0.83</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SADHNANIQ</t>
+          <t>JUNIPER</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.54</v>
+        <v>204.35</v>
       </c>
       <c r="C37" t="n">
-        <v>1.61</v>
+        <v>212.34</v>
       </c>
       <c r="D37" t="n">
-        <v>4.55</v>
+        <v>3.91</v>
       </c>
       <c r="E37" t="b">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>1.61</v>
+        <v>201.31</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>-5.19</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BLUECOAST</t>
+          <t>BALAJEE</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>20.72</v>
+        <v>26.37</v>
       </c>
       <c r="C38" t="n">
-        <v>21.66</v>
+        <v>27.4</v>
       </c>
       <c r="D38" t="n">
-        <v>4.54</v>
+        <v>3.91</v>
       </c>
       <c r="E38" t="b">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>21.42</v>
+        <v>25.8</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>-1.11</v>
+        <v>-5.84</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SIMBHALS</t>
+          <t>KALPATARU</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>8.4</v>
+        <v>299.5</v>
       </c>
       <c r="C39" t="n">
-        <v>8.779999999999999</v>
+        <v>311.05</v>
       </c>
       <c r="D39" t="n">
-        <v>4.52</v>
+        <v>3.86</v>
       </c>
       <c r="E39" t="b">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>8.210000000000001</v>
+        <v>324.35</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>-6.49</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>KNAGRI</t>
+          <t>PREMIER</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>179.95</v>
+        <v>2.89</v>
       </c>
       <c r="C40" t="n">
-        <v>188</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>4.47</v>
+        <v>3.81</v>
       </c>
       <c r="E40" t="b">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>179.47</v>
+        <v>3</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>-4.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>VINEETLAB</t>
+          <t>ANTGRAPHIC</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>30.31</v>
+        <v>0.79</v>
       </c>
       <c r="C41" t="n">
-        <v>31.65</v>
+        <v>0.82</v>
       </c>
       <c r="D41" t="n">
-        <v>4.42</v>
+        <v>3.8</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>31.4</v>
+        <v>0.79</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>-0.79</v>
+        <v>-3.66</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AURIGROW</t>
+          <t>HMAAGRO</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.23</v>
+        <v>24.77</v>
       </c>
       <c r="C42" t="n">
-        <v>0.24</v>
+        <v>25.65</v>
       </c>
       <c r="D42" t="n">
-        <v>4.35</v>
+        <v>3.55</v>
       </c>
       <c r="E42" t="b">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0.24</v>
+        <v>24.41</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>-4.83</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SUNDRMBRAK</t>
+          <t>RHFL</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>566.15</v>
+        <v>2.58</v>
       </c>
       <c r="C43" t="n">
-        <v>590</v>
+        <v>2.67</v>
       </c>
       <c r="D43" t="n">
-        <v>4.21</v>
+        <v>3.49</v>
       </c>
       <c r="E43" t="b">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>567</v>
+        <v>2.7</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>-3.9</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GENCON</t>
+          <t>VIVIDHA</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>43.5</v>
+        <v>0.6</v>
       </c>
       <c r="C44" t="n">
-        <v>45.3</v>
+        <v>0.62</v>
       </c>
       <c r="D44" t="n">
-        <v>4.14</v>
+        <v>3.33</v>
       </c>
       <c r="E44" t="b">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>43.6</v>
+        <v>0.62</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>-3.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GINNIFILA</t>
+          <t>VIVIMEDLAB</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>35.83</v>
+        <v>6.96</v>
       </c>
       <c r="C45" t="n">
-        <v>37.3</v>
+        <v>7.19</v>
       </c>
       <c r="D45" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="E45" t="b">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>34.86</v>
+        <v>6.93</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>-6.54</v>
+        <v>-3.62</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FMNL</t>
+          <t>ZEEMEDIA</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>8.42</v>
+        <v>7.89</v>
       </c>
       <c r="C46" t="n">
-        <v>8.76</v>
+        <v>8.15</v>
       </c>
       <c r="D46" t="n">
-        <v>4.04</v>
+        <v>3.3</v>
       </c>
       <c r="E46" t="b">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>8.35</v>
+        <v>7.91</v>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>-4.68</v>
+        <v>-2.94</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PRITI</t>
+          <t>NKIND</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>36.81</v>
+        <v>63.54</v>
       </c>
       <c r="C47" t="n">
-        <v>38.29</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>4.02</v>
+        <v>3.24</v>
       </c>
       <c r="E47" t="b">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>37.13</v>
+        <v>63</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>-3.03</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GSS</t>
+          <t>FLFL</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>12.31</v>
+        <v>1.27</v>
       </c>
       <c r="C48" t="n">
-        <v>12.8</v>
+        <v>1.31</v>
       </c>
       <c r="D48" t="n">
-        <v>3.98</v>
+        <v>3.15</v>
       </c>
       <c r="E48" t="b">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>12.26</v>
+        <v>1.28</v>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>-4.22</v>
+        <v>-2.29</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DRCSYSTEMS</t>
+          <t>RCOM</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>13.27</v>
+        <v>0.97</v>
       </c>
       <c r="C49" t="n">
-        <v>13.79</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>3.92</v>
+        <v>3.09</v>
       </c>
       <c r="E49" t="b">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>13.1</v>
+        <v>1.01</v>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GICL</t>
+          <t>NECLIFE</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>44.61</v>
+        <v>11.33</v>
       </c>
       <c r="C50" t="n">
-        <v>46.35</v>
+        <v>11.68</v>
       </c>
       <c r="D50" t="n">
-        <v>3.9</v>
+        <v>3.09</v>
       </c>
       <c r="E50" t="b">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>44.85</v>
+        <v>11.37</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>-3.24</v>
+        <v>-2.65</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ABINFRA</t>
+          <t>GINNIFILA</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>17.61</v>
+        <v>37.34</v>
       </c>
       <c r="C51" t="n">
-        <v>18.29</v>
+        <v>38.49</v>
       </c>
       <c r="D51" t="n">
-        <v>3.86</v>
+        <v>3.08</v>
       </c>
       <c r="E51" t="b">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>17.32</v>
+        <v>36.6</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>-5.3</v>
+        <v>-4.91</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STOVEKRAFT</t>
+          <t>VINEETLAB</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>544.95</v>
+        <v>30.04</v>
       </c>
       <c r="C52" t="n">
-        <v>565.9</v>
+        <v>30.95</v>
       </c>
       <c r="D52" t="n">
-        <v>3.84</v>
+        <v>3.03</v>
       </c>
       <c r="E52" t="b">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>549</v>
+        <v>30.33</v>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>-2.99</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>JAIPURKURT</t>
+          <t>FROG</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>29.77</v>
+        <v>135.6</v>
       </c>
       <c r="C53" t="n">
-        <v>30.9</v>
+        <v>139.7</v>
       </c>
       <c r="D53" t="n">
-        <v>3.8</v>
+        <v>3.02</v>
       </c>
       <c r="E53" t="b">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>30.25</v>
+        <v>134.05</v>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>-2.1</v>
+        <v>-4.04</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TIJARIA</t>
+          <t>SIGMA</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4.87</v>
+        <v>42.47</v>
       </c>
       <c r="C54" t="n">
-        <v>5.05</v>
+        <v>43.75</v>
       </c>
       <c r="D54" t="n">
-        <v>3.7</v>
+        <v>3.01</v>
       </c>
       <c r="E54" t="b">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>4.99</v>
+        <v>40.98</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>-1.19</v>
+        <v>-6.33</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>VIVIDHA</t>
+          <t>NAVKARURB</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="C55" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="D55" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>-6.8</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MKPL</t>
+          <t>SOFTTECH</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4.9</v>
+        <v>259.4</v>
       </c>
       <c r="C56" t="n">
-        <v>5.08</v>
+        <v>267.1</v>
       </c>
       <c r="D56" t="n">
-        <v>3.67</v>
+        <v>2.97</v>
       </c>
       <c r="E56" t="b">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>5.22</v>
+        <v>262.15</v>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>2.76</v>
+        <v>-1.85</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>KEC</t>
+          <t>KNAGRI</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>547.75</v>
+        <v>179.66</v>
       </c>
       <c r="C57" t="n">
-        <v>567.25</v>
+        <v>185</v>
       </c>
       <c r="D57" t="n">
-        <v>3.56</v>
+        <v>2.97</v>
       </c>
       <c r="E57" t="b">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>539</v>
+        <v>177.18</v>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>-4.98</v>
+        <v>-4.23</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>IGCL</t>
+          <t>TREJHARA</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>63.18</v>
+        <v>160.09</v>
       </c>
       <c r="C58" t="n">
-        <v>65.40000000000001</v>
+        <v>164.8</v>
       </c>
       <c r="D58" t="n">
-        <v>3.51</v>
+        <v>2.94</v>
       </c>
       <c r="E58" t="b">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>62.48</v>
+        <v>164</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>-4.46</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>SITINET</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>569.2</v>
+        <v>0.34</v>
       </c>
       <c r="C59" t="n">
-        <v>589</v>
+        <v>0.35</v>
       </c>
       <c r="D59" t="n">
-        <v>3.48</v>
+        <v>2.94</v>
       </c>
       <c r="E59" t="b">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>582</v>
+        <v>0.35</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>-1.19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>GREENCHEF</t>
+          <t>LAXMICOT</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>50.1</v>
+        <v>13.04</v>
       </c>
       <c r="C60" t="n">
-        <v>51.8</v>
+        <v>13.42</v>
       </c>
       <c r="D60" t="n">
-        <v>3.39</v>
+        <v>2.91</v>
       </c>
       <c r="E60" t="b">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>52.05</v>
+        <v>13</v>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>0.48</v>
+        <v>-3.13</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>GOLDTECH</t>
+          <t>TTKPRESTIG</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>38.45</v>
+        <v>578.3</v>
       </c>
       <c r="C61" t="n">
-        <v>39.75</v>
+        <v>595</v>
       </c>
       <c r="D61" t="n">
-        <v>3.38</v>
+        <v>2.89</v>
       </c>
       <c r="E61" t="b">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>39.03</v>
+        <v>582.35</v>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>-1.81</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>INTENTECH</t>
+          <t>HAVISHA</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>91.41</v>
+        <v>1.39</v>
       </c>
       <c r="C62" t="n">
-        <v>94.48999999999999</v>
+        <v>1.43</v>
       </c>
       <c r="D62" t="n">
-        <v>3.37</v>
+        <v>2.88</v>
       </c>
       <c r="E62" t="b">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>91.12</v>
+        <v>1.44</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>-3.57</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SURANASOL</t>
+          <t>XTGLOBAL</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>20.8</v>
+        <v>34.02</v>
       </c>
       <c r="C63" t="n">
-        <v>21.5</v>
+        <v>35</v>
       </c>
       <c r="D63" t="n">
-        <v>3.37</v>
+        <v>2.88</v>
       </c>
       <c r="E63" t="b">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>21.1</v>
+        <v>34.27</v>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>-1.86</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>LOVABLE</t>
+          <t>VGL</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>68.7</v>
+        <v>60.28</v>
       </c>
       <c r="C64" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="D64" t="n">
-        <v>3.35</v>
+        <v>2.85</v>
       </c>
       <c r="E64" t="b">
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>67</v>
+        <v>60.53</v>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>-5.63</v>
+        <v>-2.37</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CTE</t>
+          <t>LOVABLE</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>27.03</v>
+        <v>68.38</v>
       </c>
       <c r="C65" t="n">
-        <v>27.93</v>
+        <v>70.3</v>
       </c>
       <c r="D65" t="n">
-        <v>3.33</v>
+        <v>2.81</v>
       </c>
       <c r="E65" t="b">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>27.45</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>-1.72</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BASML</t>
+          <t>PRAXIS</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>20.7</v>
+        <v>6.57</v>
       </c>
       <c r="C66" t="n">
-        <v>21.38</v>
+        <v>6.75</v>
       </c>
       <c r="D66" t="n">
-        <v>3.29</v>
+        <v>2.74</v>
       </c>
       <c r="E66" t="b">
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>20.33</v>
+        <v>6.55</v>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>-4.91</v>
+        <v>-2.96</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>OMNI</t>
+          <t>NIBL</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>208.95</v>
+        <v>30.65</v>
       </c>
       <c r="C67" t="n">
-        <v>215.8</v>
+        <v>31.49</v>
       </c>
       <c r="D67" t="n">
-        <v>3.28</v>
+        <v>2.74</v>
       </c>
       <c r="E67" t="b">
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>213.33</v>
+        <v>30.36</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>-1.14</v>
+        <v>-3.59</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>RHFL</t>
+          <t>ROSSELLIND</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2.46</v>
+        <v>45.76</v>
       </c>
       <c r="C68" t="n">
-        <v>2.54</v>
+        <v>47</v>
       </c>
       <c r="D68" t="n">
-        <v>3.25</v>
+        <v>2.71</v>
       </c>
       <c r="E68" t="b">
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>2.58</v>
+        <v>44.79</v>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>1.57</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>RCOM</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.93</v>
+        <v>607.6</v>
       </c>
       <c r="C69" t="n">
-        <v>0.96</v>
+        <v>624</v>
       </c>
       <c r="D69" t="n">
-        <v>3.23</v>
+        <v>2.7</v>
       </c>
       <c r="E69" t="b">
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>0.97</v>
+        <v>612.8</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>1.04</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>VIJIFIN</t>
+          <t>PATINTLOG</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2.51</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="C70" t="n">
-        <v>2.59</v>
+        <v>9.9</v>
       </c>
       <c r="D70" t="n">
-        <v>3.19</v>
+        <v>2.7</v>
       </c>
       <c r="E70" t="b">
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>2.63</v>
+        <v>9.73</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>1.54</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SUNDARAM</t>
+          <t>ALANKIT</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1.26</v>
+        <v>7.87</v>
       </c>
       <c r="C71" t="n">
-        <v>1.3</v>
+        <v>8.08</v>
       </c>
       <c r="D71" t="n">
-        <v>3.17</v>
+        <v>2.67</v>
       </c>
       <c r="E71" t="b">
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>1.3</v>
+        <v>7.85</v>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>-2.85</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ANKITMETAL</t>
+          <t>SUNDRMBRAK</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1.6</v>
+        <v>571.75</v>
       </c>
       <c r="C72" t="n">
-        <v>1.65</v>
+        <v>587</v>
       </c>
       <c r="D72" t="n">
-        <v>3.12</v>
+        <v>2.67</v>
       </c>
       <c r="E72" t="b">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>1.67</v>
+        <v>563.4</v>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>1.21</v>
+        <v>-4.02</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CSLFINANCE</t>
+          <t>CAPTRUST</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>255.15</v>
+        <v>11.59</v>
       </c>
       <c r="C73" t="n">
-        <v>263</v>
+        <v>11.9</v>
       </c>
       <c r="D73" t="n">
-        <v>3.08</v>
+        <v>2.67</v>
       </c>
       <c r="E73" t="b">
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>251.65</v>
+        <v>11.5</v>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>-4.32</v>
+        <v>-3.36</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>VAISHALI</t>
+          <t>PIGL</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>6.5</v>
+        <v>101.32</v>
       </c>
       <c r="C74" t="n">
-        <v>6.7</v>
+        <v>104</v>
       </c>
       <c r="D74" t="n">
-        <v>3.08</v>
+        <v>2.65</v>
       </c>
       <c r="E74" t="b">
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>6.51</v>
+        <v>101.16</v>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>-2.84</v>
+        <v>-2.73</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AAKASH</t>
+          <t>GOLDTECH</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>10.68</v>
+        <v>37.71</v>
       </c>
       <c r="C75" t="n">
-        <v>11</v>
+        <v>38.7</v>
       </c>
       <c r="D75" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="E75" t="b">
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>10.27</v>
+        <v>37.79</v>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>-6.64</v>
+        <v>-2.35</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>XTGLOBAL</t>
+          <t>ENERGYDEV</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>33.97</v>
+        <v>15.1</v>
       </c>
       <c r="C76" t="n">
-        <v>34.99</v>
+        <v>15.49</v>
       </c>
       <c r="D76" t="n">
-        <v>3</v>
+        <v>2.58</v>
       </c>
       <c r="E76" t="b">
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>34.49</v>
+        <v>15.27</v>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>-1.43</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>GSLSU</t>
+          <t>SETUINFRA</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>73.31</v>
+        <v>0.39</v>
       </c>
       <c r="C77" t="n">
-        <v>75.48999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="D77" t="n">
-        <v>2.97</v>
+        <v>2.56</v>
       </c>
       <c r="E77" t="b">
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>72.48</v>
+        <v>0.4</v>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>-3.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SITINET</t>
+          <t>AKSHAR</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="C78" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="D78" t="n">
-        <v>2.94</v>
+        <v>2.56</v>
       </c>
       <c r="E78" t="b">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
@@ -2463,3195 +2463,3195 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>VIJAYPD</t>
+          <t>ATLANTAA</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>71.90000000000001</v>
+        <v>36.76</v>
       </c>
       <c r="C79" t="n">
-        <v>74</v>
+        <v>37.7</v>
       </c>
       <c r="D79" t="n">
-        <v>2.92</v>
+        <v>2.56</v>
       </c>
       <c r="E79" t="b">
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>70</v>
+        <v>36.71</v>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>-5.41</v>
+        <v>-2.63</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>IMPEXFERRO</t>
+          <t>TOKYOPLAST</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1.72</v>
+        <v>74.98</v>
       </c>
       <c r="C80" t="n">
-        <v>1.77</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="D80" t="n">
-        <v>2.91</v>
+        <v>2.56</v>
       </c>
       <c r="E80" t="b">
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>1.71</v>
+        <v>73.55</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>-3.39</v>
+        <v>-4.36</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>GANGAFORGE</t>
+          <t>C2C</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2.85</v>
+        <v>389.1</v>
       </c>
       <c r="C81" t="n">
-        <v>2.93</v>
+        <v>398.85</v>
       </c>
       <c r="D81" t="n">
-        <v>2.81</v>
+        <v>2.51</v>
       </c>
       <c r="E81" t="b">
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>2.87</v>
+        <v>390.5</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>-2.05</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>NECLIFE</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>11.42</v>
+        <v>88.88</v>
       </c>
       <c r="C82" t="n">
-        <v>11.74</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D82" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="E82" t="b">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>11.41</v>
+        <v>88.88</v>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>-2.81</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>KOHINOOR</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>23.25</v>
+        <v>24.4</v>
       </c>
       <c r="C83" t="n">
-        <v>23.9</v>
+        <v>25</v>
       </c>
       <c r="D83" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="E83" t="b">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>23.39</v>
+        <v>23.97</v>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>-2.13</v>
+        <v>-4.12</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ADL</t>
+          <t>OILCOUNTUB</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>72.98999999999999</v>
+        <v>44.89</v>
       </c>
       <c r="C84" t="n">
-        <v>74.95</v>
+        <v>45.99</v>
       </c>
       <c r="D84" t="n">
-        <v>2.69</v>
+        <v>2.45</v>
       </c>
       <c r="E84" t="b">
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>67.12</v>
+        <v>44.68</v>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>-10.45</v>
+        <v>-2.85</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>FLAIR</t>
+          <t>VILAS</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>302.1</v>
+        <v>377.85</v>
       </c>
       <c r="C85" t="n">
-        <v>310.15</v>
+        <v>387</v>
       </c>
       <c r="D85" t="n">
-        <v>2.66</v>
+        <v>2.42</v>
       </c>
       <c r="E85" t="b">
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>299.1</v>
+        <v>373</v>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>-3.56</v>
+        <v>-3.62</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BRNL</t>
+          <t>SWANDEF</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>18.49</v>
+        <v>2280.6</v>
       </c>
       <c r="C86" t="n">
-        <v>18.98</v>
+        <v>2335</v>
       </c>
       <c r="D86" t="n">
-        <v>2.65</v>
+        <v>2.39</v>
       </c>
       <c r="E86" t="b">
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>18.45</v>
+        <v>2394.6</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>-2.79</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>WABAG</t>
+          <t>PAVNAIND</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1251.9</v>
+        <v>18.95</v>
       </c>
       <c r="C87" t="n">
-        <v>1285.1</v>
+        <v>19.4</v>
       </c>
       <c r="D87" t="n">
-        <v>2.65</v>
+        <v>2.37</v>
       </c>
       <c r="E87" t="b">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>1257.1</v>
+        <v>19.01</v>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>-2.18</v>
+        <v>-2.01</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SHYAMDHANI</t>
+          <t>KPIGREEN</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>70.15000000000001</v>
+        <v>394.7</v>
       </c>
       <c r="C88" t="n">
-        <v>72</v>
+        <v>404.05</v>
       </c>
       <c r="D88" t="n">
-        <v>2.64</v>
+        <v>2.37</v>
       </c>
       <c r="E88" t="b">
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>69.09999999999999</v>
+        <v>400.4</v>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>-4.03</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SBGLP</t>
+          <t>FISCHER</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>27.47</v>
+        <v>35.15</v>
       </c>
       <c r="C89" t="n">
-        <v>28.19</v>
+        <v>35.98</v>
       </c>
       <c r="D89" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="E89" t="b">
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>27.3</v>
+        <v>34.25</v>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>-3.16</v>
+        <v>-4.81</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SETUINFRA</t>
+          <t>MWL</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.39</v>
+        <v>273.4</v>
       </c>
       <c r="C90" t="n">
-        <v>0.4</v>
+        <v>279.8</v>
       </c>
       <c r="D90" t="n">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="E90" t="b">
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>0.39</v>
+        <v>274.55</v>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>-2.5</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DUCON</t>
+          <t>DAMODARIND</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>3.14</v>
+        <v>23.93</v>
       </c>
       <c r="C91" t="n">
-        <v>3.22</v>
+        <v>24.49</v>
       </c>
       <c r="D91" t="n">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="E91" t="b">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>3.1</v>
+        <v>24.29</v>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>-3.73</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>BSL</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>60.28</v>
+        <v>125.56</v>
       </c>
       <c r="C92" t="n">
-        <v>61.8</v>
+        <v>128.5</v>
       </c>
       <c r="D92" t="n">
-        <v>2.52</v>
+        <v>2.34</v>
       </c>
       <c r="E92" t="b">
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>60.39</v>
+        <v>126.7</v>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
-        <v>-2.28</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BUTTERFLY</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>694.5</v>
+        <v>237.4</v>
       </c>
       <c r="C93" t="n">
-        <v>712</v>
+        <v>242.9</v>
       </c>
       <c r="D93" t="n">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="E93" t="b">
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>719.8</v>
+        <v>236</v>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
-        <v>1.1</v>
+        <v>-2.84</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>HINDOILEXP</t>
+          <t>DSFCL</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>147.32</v>
+        <v>25.12</v>
       </c>
       <c r="C94" t="n">
-        <v>151</v>
+        <v>25.7</v>
       </c>
       <c r="D94" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="E94" t="b">
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>152.36</v>
+        <v>24.71</v>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>0.9</v>
+        <v>-3.85</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SHRENIK</t>
+          <t>HARRMALAYA</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.4</v>
+        <v>181.98</v>
       </c>
       <c r="C95" t="n">
-        <v>0.41</v>
+        <v>186</v>
       </c>
       <c r="D95" t="n">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="E95" t="b">
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>0.41</v>
+        <v>181.99</v>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MODTHREAD</t>
+          <t>BIOFILCHEM</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>54.27</v>
+        <v>30.63</v>
       </c>
       <c r="C96" t="n">
-        <v>55.62</v>
+        <v>31.3</v>
       </c>
       <c r="D96" t="n">
-        <v>2.49</v>
+        <v>2.19</v>
       </c>
       <c r="E96" t="b">
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>54</v>
+        <v>30.84</v>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>-2.91</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CEREBRAINT</t>
+          <t>URAVIDEF</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>4.41</v>
+        <v>130.07</v>
       </c>
       <c r="C97" t="n">
-        <v>4.52</v>
+        <v>132.9</v>
       </c>
       <c r="D97" t="n">
-        <v>2.49</v>
+        <v>2.18</v>
       </c>
       <c r="E97" t="b">
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>4.37</v>
+        <v>128.41</v>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>-3.32</v>
+        <v>-3.38</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SGMART</t>
+          <t>TAKE</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>446.7</v>
+        <v>41.71</v>
       </c>
       <c r="C98" t="n">
-        <v>457.8</v>
+        <v>42.6</v>
       </c>
       <c r="D98" t="n">
-        <v>2.48</v>
+        <v>2.13</v>
       </c>
       <c r="E98" t="b">
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>438.5</v>
+        <v>42.22</v>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>-4.22</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SSDL</t>
+          <t>SRD</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>60.53</v>
+        <v>51.62</v>
       </c>
       <c r="C99" t="n">
-        <v>61.99</v>
+        <v>52.7</v>
       </c>
       <c r="D99" t="n">
-        <v>2.41</v>
+        <v>2.09</v>
       </c>
       <c r="E99" t="b">
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>60.76</v>
+        <v>51.35</v>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
-        <v>-1.98</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>NAGAFERT</t>
+          <t>PHANTOMFX</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>4.18</v>
+        <v>185.65</v>
       </c>
       <c r="C100" t="n">
-        <v>4.28</v>
+        <v>189.5</v>
       </c>
       <c r="D100" t="n">
-        <v>2.39</v>
+        <v>2.07</v>
       </c>
       <c r="E100" t="b">
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>4.24</v>
+        <v>187.1</v>
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>-0.93</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>NRL</t>
+          <t>VARDMNPOLY</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>50.79</v>
+        <v>8.25</v>
       </c>
       <c r="C101" t="n">
-        <v>51.97</v>
+        <v>8.42</v>
       </c>
       <c r="D101" t="n">
-        <v>2.32</v>
+        <v>2.06</v>
       </c>
       <c r="E101" t="b">
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>51.31</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>-1.27</v>
+        <v>-2.61</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SPCENET</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>3.91</v>
+        <v>74.47</v>
       </c>
       <c r="C102" t="n">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="D102" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="E102" t="b">
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>3.9</v>
+        <v>74.06</v>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>-2.5</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PEARLPOLY</t>
+          <t>JAIPURKURT</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>17.11</v>
+        <v>30.27</v>
       </c>
       <c r="C103" t="n">
-        <v>17.5</v>
+        <v>30.89</v>
       </c>
       <c r="D103" t="n">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="E103" t="b">
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>17.15</v>
+        <v>29.98</v>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>-2</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>GATECHDVR</t>
+          <t>GULFPETRO</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.44</v>
+        <v>31.47</v>
       </c>
       <c r="C104" t="n">
-        <v>0.45</v>
+        <v>32.1</v>
       </c>
       <c r="D104" t="n">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="E104" t="b">
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>0.45</v>
+        <v>31.4</v>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ODIGMA</t>
+          <t>GAUDIUMIVF</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>23.67</v>
+        <v>80.87</v>
       </c>
       <c r="C105" t="n">
-        <v>24.2</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="D105" t="n">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="E105" t="b">
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>22.99</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>-5</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ARCHIES</t>
+          <t>MOKSH</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>13.94</v>
+        <v>11.5</v>
       </c>
       <c r="C106" t="n">
-        <v>14.25</v>
+        <v>11.73</v>
       </c>
       <c r="D106" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="E106" t="b">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>13.99</v>
+        <v>11.69</v>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
-        <v>-1.82</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>INDTERRAIN</t>
+          <t>AHLADA</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>29.53</v>
+        <v>41.03</v>
       </c>
       <c r="C107" t="n">
-        <v>30.18</v>
+        <v>41.85</v>
       </c>
       <c r="D107" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="E107" t="b">
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>29.5</v>
+        <v>40.8</v>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>-2.25</v>
+        <v>-2.51</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>KAUSHALYA</t>
+          <t>GOLDENTOBC</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>825.95</v>
+        <v>27.45</v>
       </c>
       <c r="C108" t="n">
-        <v>844</v>
+        <v>28</v>
       </c>
       <c r="D108" t="n">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="E108" t="b">
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>839.4</v>
+        <v>27</v>
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
-        <v>-0.55</v>
+        <v>-3.57</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SAURASHCEM</t>
+          <t>SEYAIND</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>62.44</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="C109" t="n">
-        <v>63.8</v>
+        <v>9.23</v>
       </c>
       <c r="D109" t="n">
-        <v>2.18</v>
+        <v>1.99</v>
       </c>
       <c r="E109" t="b">
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>61.66</v>
+        <v>9.23</v>
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>-3.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>KSOLVES</t>
+          <t>INVENTURE</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>288.55</v>
+        <v>1.02</v>
       </c>
       <c r="C110" t="n">
-        <v>294.8</v>
+        <v>1.04</v>
       </c>
       <c r="D110" t="n">
-        <v>2.17</v>
+        <v>1.96</v>
       </c>
       <c r="E110" t="b">
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>282</v>
+        <v>1.03</v>
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
-        <v>-4.34</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>VARROC</t>
+          <t>21STCENMGM</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>494.35</v>
+        <v>33.64</v>
       </c>
       <c r="C111" t="n">
-        <v>504.9</v>
+        <v>34.3</v>
       </c>
       <c r="D111" t="n">
-        <v>2.13</v>
+        <v>1.96</v>
       </c>
       <c r="E111" t="b">
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>482.55</v>
+        <v>34.2</v>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>-4.43</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>GNA</t>
+          <t>IFCI</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>421.1</v>
+        <v>53.95</v>
       </c>
       <c r="C112" t="n">
-        <v>430</v>
+        <v>55</v>
       </c>
       <c r="D112" t="n">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="E112" t="b">
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>411.05</v>
+        <v>56.75</v>
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
-        <v>-4.41</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ZENITHSTL</t>
+          <t>IZMO</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>5.68</v>
+        <v>734.2</v>
       </c>
       <c r="C113" t="n">
-        <v>5.8</v>
+        <v>748.5</v>
       </c>
       <c r="D113" t="n">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="E113" t="b">
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>5.46</v>
+        <v>723.95</v>
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>-5.86</v>
+        <v>-3.28</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>MAGNUM</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>153.08</v>
+        <v>19.57</v>
       </c>
       <c r="C114" t="n">
-        <v>156.28</v>
+        <v>19.95</v>
       </c>
       <c r="D114" t="n">
-        <v>2.09</v>
+        <v>1.94</v>
       </c>
       <c r="E114" t="b">
         <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>166.78</v>
+        <v>19.29</v>
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
-        <v>6.72</v>
+        <v>-3.31</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>GATECH</t>
+          <t>GRAVITA</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.48</v>
+        <v>1503.2</v>
       </c>
       <c r="C115" t="n">
-        <v>0.49</v>
+        <v>1532</v>
       </c>
       <c r="D115" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="E115" t="b">
         <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>0.48</v>
+        <v>1454.2</v>
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>-2.04</v>
+        <v>-5.08</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>KEYFINSERV</t>
+          <t>AKSHOPTFBR</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>266</v>
+        <v>4.73</v>
       </c>
       <c r="C116" t="n">
-        <v>271.5</v>
+        <v>4.82</v>
       </c>
       <c r="D116" t="n">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="E116" t="b">
         <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>268.55</v>
+        <v>4.54</v>
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
-        <v>-1.09</v>
+        <v>-5.81</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DICIND</t>
+          <t>GOKUL</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>524.1</v>
+        <v>41.22</v>
       </c>
       <c r="C117" t="n">
-        <v>534.9</v>
+        <v>42</v>
       </c>
       <c r="D117" t="n">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="E117" t="b">
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>534</v>
+        <v>41.98</v>
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>-0.17</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>AXITA</t>
+          <t>PASHUPATI</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>8.800000000000001</v>
+        <v>996.1</v>
       </c>
       <c r="C118" t="n">
-        <v>8.98</v>
+        <v>1014.8</v>
       </c>
       <c r="D118" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="E118" t="b">
         <v>0</v>
       </c>
       <c r="F118" t="n">
-        <v>8.9</v>
+        <v>994.7</v>
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
-        <v>-0.89</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>RADAAN</t>
+          <t>GEEKAYWIRE</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>2.94</v>
+        <v>20.89</v>
       </c>
       <c r="C119" t="n">
-        <v>3</v>
+        <v>21.28</v>
       </c>
       <c r="D119" t="n">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="E119" t="b">
         <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>2.98</v>
+        <v>20.5</v>
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
-        <v>-0.67</v>
+        <v>-3.67</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>TREEHOUSE</t>
+          <t>RPPL</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>7.86</v>
+        <v>15.51</v>
       </c>
       <c r="C120" t="n">
-        <v>8.02</v>
+        <v>15.8</v>
       </c>
       <c r="D120" t="n">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="E120" t="b">
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>7.81</v>
+        <v>15.42</v>
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
-        <v>-2.62</v>
+        <v>-2.41</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SAKHTISUG</t>
+          <t>HILTON</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>15.18</v>
+        <v>16.78</v>
       </c>
       <c r="C121" t="n">
-        <v>15.49</v>
+        <v>17.09</v>
       </c>
       <c r="D121" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="E121" t="b">
         <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>15.26</v>
+        <v>16.79</v>
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
-        <v>-1.48</v>
+        <v>-1.76</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>VHLTD</t>
+          <t>PVP</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>146.47</v>
+        <v>24.94</v>
       </c>
       <c r="C122" t="n">
-        <v>149.45</v>
+        <v>25.4</v>
       </c>
       <c r="D122" t="n">
-        <v>2.03</v>
+        <v>1.84</v>
       </c>
       <c r="E122" t="b">
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>146</v>
+        <v>23.82</v>
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
-        <v>-2.31</v>
+        <v>-6.22</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>C2C</t>
+          <t>VHLTD</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>324.25</v>
+        <v>144.94</v>
       </c>
       <c r="C123" t="n">
-        <v>330.8</v>
+        <v>147.6</v>
       </c>
       <c r="D123" t="n">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="E123" t="b">
         <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>372.95</v>
+        <v>142.8</v>
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>12.74</v>
+        <v>-3.25</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ATALREAL</t>
+          <t>HARIOMPIPE</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>23.42</v>
+        <v>324.15</v>
       </c>
       <c r="C124" t="n">
-        <v>23.89</v>
+        <v>329.95</v>
       </c>
       <c r="D124" t="n">
-        <v>2.01</v>
+        <v>1.79</v>
       </c>
       <c r="E124" t="b">
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>22.88</v>
+        <v>320.95</v>
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
-        <v>-4.23</v>
+        <v>-2.73</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>RSSOFTWARE</t>
+          <t>FLYSBS</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>27.94</v>
+        <v>401.75</v>
       </c>
       <c r="C125" t="n">
-        <v>28.5</v>
+        <v>408.95</v>
       </c>
       <c r="D125" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="E125" t="b">
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>28.56</v>
+        <v>395</v>
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>0.21</v>
+        <v>-3.41</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>JINDALSAW</t>
+          <t>TEXMOPIPES</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>198.04</v>
+        <v>45.49</v>
       </c>
       <c r="C126" t="n">
-        <v>202</v>
+        <v>46.3</v>
       </c>
       <c r="D126" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="E126" t="b">
         <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>192.4</v>
+        <v>44.5</v>
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
-        <v>-4.75</v>
+        <v>-3.89</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>LAGNAM</t>
+          <t>PEARLPOLY</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>68.86</v>
+        <v>17.42</v>
       </c>
       <c r="C127" t="n">
-        <v>70.23999999999999</v>
+        <v>17.73</v>
       </c>
       <c r="D127" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="E127" t="b">
         <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>68.34999999999999</v>
+        <v>17.45</v>
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
-        <v>-2.69</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>HYBRIDFIN</t>
+          <t>DBEIL</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>16.98</v>
+        <v>71.64</v>
       </c>
       <c r="C128" t="n">
-        <v>17.32</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D128" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="E128" t="b">
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>16.72</v>
+        <v>70.55</v>
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
-        <v>-3.46</v>
+        <v>-3.22</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SOUTHWEST</t>
+          <t>3IINFOLTD</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>209.52</v>
+        <v>13.14</v>
       </c>
       <c r="C129" t="n">
-        <v>213.72</v>
+        <v>13.37</v>
       </c>
       <c r="D129" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="E129" t="b">
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>203.4</v>
+        <v>13.03</v>
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
-        <v>-4.83</v>
+        <v>-2.54</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SUTLEJTEX</t>
+          <t>NECCLTD</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>31.71</v>
+        <v>13.76</v>
       </c>
       <c r="C130" t="n">
-        <v>32.34</v>
+        <v>14</v>
       </c>
       <c r="D130" t="n">
-        <v>1.99</v>
+        <v>1.74</v>
       </c>
       <c r="E130" t="b">
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>31.18</v>
+        <v>13.86</v>
       </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
-        <v>-3.59</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>TICL</t>
+          <t>KARMAENG</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>25.99</v>
+        <v>40.3</v>
       </c>
       <c r="C131" t="n">
-        <v>26.5</v>
+        <v>40.99</v>
       </c>
       <c r="D131" t="n">
-        <v>1.96</v>
+        <v>1.71</v>
       </c>
       <c r="E131" t="b">
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>25.98</v>
+        <v>38.3</v>
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
-        <v>-1.96</v>
+        <v>-6.56</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>GVPTECH</t>
+          <t>RUCHINFRA</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>6.23</v>
+        <v>5.37</v>
       </c>
       <c r="C132" t="n">
-        <v>6.35</v>
+        <v>5.46</v>
       </c>
       <c r="D132" t="n">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="E132" t="b">
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>6.1</v>
+        <v>5.27</v>
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
-        <v>-3.94</v>
+        <v>-3.48</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>DENTALKART</t>
+          <t>GFLLIMITED</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>402.3</v>
+        <v>46.15</v>
       </c>
       <c r="C133" t="n">
-        <v>409.95</v>
+        <v>46.92</v>
       </c>
       <c r="D133" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="E133" t="b">
         <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>400.1</v>
+        <v>44.73</v>
       </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
-        <v>-2.4</v>
+        <v>-4.67</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>TPHQ</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.53</v>
+        <v>303.6</v>
       </c>
       <c r="C134" t="n">
-        <v>0.54</v>
+        <v>308.65</v>
       </c>
       <c r="D134" t="n">
-        <v>1.89</v>
+        <v>1.66</v>
       </c>
       <c r="E134" t="b">
         <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>0.55</v>
+        <v>303.6</v>
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
-        <v>1.85</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MAGNUM</t>
+          <t>TIRUPATIFL</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>19.62</v>
+        <v>44.07</v>
       </c>
       <c r="C135" t="n">
-        <v>19.99</v>
+        <v>44.8</v>
       </c>
       <c r="D135" t="n">
-        <v>1.89</v>
+        <v>1.66</v>
       </c>
       <c r="E135" t="b">
         <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>19.32</v>
+        <v>44.36</v>
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
-        <v>-3.35</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>AIRAN</t>
+          <t>HINDOILEXP</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>15.92</v>
+        <v>147.44</v>
       </c>
       <c r="C136" t="n">
-        <v>16.22</v>
+        <v>149.89</v>
       </c>
       <c r="D136" t="n">
-        <v>1.88</v>
+        <v>1.66</v>
       </c>
       <c r="E136" t="b">
         <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>15.97</v>
+        <v>143.65</v>
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
-        <v>-1.54</v>
+        <v>-4.16</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SHAH</t>
+          <t>ZODIAC</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>4.8</v>
+        <v>242.41</v>
       </c>
       <c r="C137" t="n">
-        <v>4.89</v>
+        <v>246.37</v>
       </c>
       <c r="D137" t="n">
-        <v>1.87</v>
+        <v>1.63</v>
       </c>
       <c r="E137" t="b">
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>4.82</v>
+        <v>238.94</v>
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
-        <v>-1.43</v>
+        <v>-3.02</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>PASHUPATI</t>
+          <t>SMARTEN</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>990</v>
+        <v>58.3</v>
       </c>
       <c r="C138" t="n">
-        <v>1008</v>
+        <v>59.25</v>
       </c>
       <c r="D138" t="n">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="E138" t="b">
         <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>996.25</v>
+        <v>57.05</v>
       </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
-        <v>-1.17</v>
+        <v>-3.71</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ASMS</t>
+          <t>CEREBRAINT</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>8.82</v>
+        <v>4.37</v>
       </c>
       <c r="C139" t="n">
-        <v>8.98</v>
+        <v>4.44</v>
       </c>
       <c r="D139" t="n">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="E139" t="b">
         <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>8.84</v>
+        <v>4.3</v>
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
-        <v>-1.56</v>
+        <v>-3.15</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ELECTCAST</t>
+          <t>GLOBALVECT</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>75.62</v>
+        <v>163.42</v>
       </c>
       <c r="C140" t="n">
-        <v>76.98999999999999</v>
+        <v>166</v>
       </c>
       <c r="D140" t="n">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="E140" t="b">
         <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>77.06999999999999</v>
+        <v>160.5</v>
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
-        <v>0.1</v>
+        <v>-3.31</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>MCLOUD</t>
+          <t>ANUP</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>23.36</v>
+        <v>1556.6</v>
       </c>
       <c r="C141" t="n">
-        <v>23.78</v>
+        <v>1581</v>
       </c>
       <c r="D141" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="E141" t="b">
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>22.86</v>
+        <v>1585.4</v>
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
-        <v>-3.87</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BAGFILMS</t>
+          <t>SHEKHAWATI</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>5</v>
+        <v>12.7</v>
       </c>
       <c r="C142" t="n">
-        <v>5.09</v>
+        <v>12.9</v>
       </c>
       <c r="D142" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="E142" t="b">
         <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>5</v>
+        <v>12.64</v>
       </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
-        <v>-1.77</v>
+        <v>-2.02</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>NIRMAN</t>
+          <t>THOMASCOTT</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>50</v>
+        <v>257.9</v>
       </c>
       <c r="C143" t="n">
-        <v>50.9</v>
+        <v>261.85</v>
       </c>
       <c r="D143" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="E143" t="b">
         <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>49.55</v>
+        <v>255.05</v>
       </c>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
-        <v>-2.65</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>JMA</t>
+          <t>ODIGMA</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>84.48</v>
+        <v>22.89</v>
       </c>
       <c r="C144" t="n">
-        <v>85.98999999999999</v>
+        <v>23.24</v>
       </c>
       <c r="D144" t="n">
-        <v>1.79</v>
+        <v>1.53</v>
       </c>
       <c r="E144" t="b">
         <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>85.62</v>
+        <v>22.31</v>
       </c>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
-        <v>-0.43</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>AKASH</t>
+          <t>GREENPOWER</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>24.56</v>
+        <v>9.85</v>
       </c>
       <c r="C145" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D145" t="n">
-        <v>1.79</v>
+        <v>1.52</v>
       </c>
       <c r="E145" t="b">
         <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>24.95</v>
+        <v>10.01</v>
       </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>NELCO</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>190.58</v>
+        <v>594.35</v>
       </c>
       <c r="C146" t="n">
-        <v>194</v>
+        <v>603.3</v>
       </c>
       <c r="D146" t="n">
-        <v>1.79</v>
+        <v>1.51</v>
       </c>
       <c r="E146" t="b">
         <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>199.3</v>
+        <v>581.2</v>
       </c>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
-        <v>2.73</v>
+        <v>-3.66</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ATAM</t>
+          <t>EXCELSOFT</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>62.82</v>
+        <v>78.45</v>
       </c>
       <c r="C147" t="n">
-        <v>63.93</v>
+        <v>79.63</v>
       </c>
       <c r="D147" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="E147" t="b">
         <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>62</v>
+        <v>79.79000000000001</v>
       </c>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
-        <v>-3.02</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>EMSLIMITED</t>
+          <t>WELINV</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>311.4</v>
+        <v>1325.6</v>
       </c>
       <c r="C148" t="n">
-        <v>316.85</v>
+        <v>1345.4</v>
       </c>
       <c r="D148" t="n">
-        <v>1.75</v>
+        <v>1.49</v>
       </c>
       <c r="E148" t="b">
         <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>303.7</v>
+        <v>1339.4</v>
       </c>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
-        <v>-4.15</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>MOTOGENFIN</t>
+          <t>SHYAMCENT</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>20.1</v>
+        <v>4.77</v>
       </c>
       <c r="C149" t="n">
-        <v>20.45</v>
+        <v>4.84</v>
       </c>
       <c r="D149" t="n">
-        <v>1.74</v>
+        <v>1.47</v>
       </c>
       <c r="E149" t="b">
         <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>20.1</v>
+        <v>4.7</v>
       </c>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
-        <v>-1.71</v>
+        <v>-2.89</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SAHAJSOLAR</t>
+          <t>HAPPSTMNDS</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>110</v>
+        <v>409.05</v>
       </c>
       <c r="C150" t="n">
-        <v>111.9</v>
+        <v>415</v>
       </c>
       <c r="D150" t="n">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
       <c r="E150" t="b">
         <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>110.2</v>
+        <v>399.45</v>
       </c>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
-        <v>-1.52</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>BLAL</t>
+          <t>SEPC</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>176.75</v>
+        <v>6.23</v>
       </c>
       <c r="C151" t="n">
-        <v>179.8</v>
+        <v>6.32</v>
       </c>
       <c r="D151" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="E151" t="b">
         <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>176.63</v>
+        <v>5.7</v>
       </c>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
-        <v>-1.76</v>
+        <v>-9.81</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>BVCL</t>
+          <t>STANLEY</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>39.72</v>
+        <v>158.71</v>
       </c>
       <c r="C152" t="n">
-        <v>40.4</v>
+        <v>160.99</v>
       </c>
       <c r="D152" t="n">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="E152" t="b">
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>40.1</v>
+        <v>153.51</v>
       </c>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="n">
-        <v>-0.74</v>
+        <v>-4.65</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>MIRCELECTR</t>
+          <t>SURANAT&amp;P</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>25.17</v>
+        <v>17.15</v>
       </c>
       <c r="C153" t="n">
-        <v>25.6</v>
+        <v>17.39</v>
       </c>
       <c r="D153" t="n">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="E153" t="b">
         <v>0</v>
       </c>
-      <c r="F153" t="n">
-        <v>24.78</v>
-      </c>
+      <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr"/>
-      <c r="H153" t="n">
-        <v>-3.2</v>
-      </c>
+      <c r="H153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>FLEXITUFF</t>
+          <t>VIPCLOTHNG</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>7.01</v>
+        <v>18.89</v>
       </c>
       <c r="C154" t="n">
-        <v>7.13</v>
+        <v>19.15</v>
       </c>
       <c r="D154" t="n">
-        <v>1.71</v>
+        <v>1.38</v>
       </c>
       <c r="E154" t="b">
         <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>7.05</v>
+        <v>18.53</v>
       </c>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="n">
-        <v>-1.12</v>
+        <v>-3.24</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>RELIABLE</t>
+          <t>ALPHAGEO</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>119.96</v>
+        <v>196.78</v>
       </c>
       <c r="C155" t="n">
-        <v>122</v>
+        <v>199.5</v>
       </c>
       <c r="D155" t="n">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="E155" t="b">
         <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>120.75</v>
+        <v>192.11</v>
       </c>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="n">
-        <v>-1.02</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SUPERSPIN</t>
+          <t>INDOTECH</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>5.3</v>
+        <v>1375.4</v>
       </c>
       <c r="C156" t="n">
-        <v>5.39</v>
+        <v>1394.2</v>
       </c>
       <c r="D156" t="n">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="E156" t="b">
         <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>5.1</v>
+        <v>1330</v>
       </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="n">
-        <v>-5.38</v>
+        <v>-4.6</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>PRAKASHSTL</t>
+          <t>NAHARSPING</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>4.17</v>
+        <v>194.95</v>
       </c>
       <c r="C157" t="n">
-        <v>4.24</v>
+        <v>197.6</v>
       </c>
       <c r="D157" t="n">
-        <v>1.68</v>
+        <v>1.36</v>
       </c>
       <c r="E157" t="b">
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>4.13</v>
+        <v>190</v>
       </c>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="n">
-        <v>-2.59</v>
+        <v>-3.85</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>PRITIKAUTO</t>
+          <t>SHREYANIND</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>12.48</v>
+        <v>148.89</v>
       </c>
       <c r="C158" t="n">
-        <v>12.69</v>
+        <v>150.9</v>
       </c>
       <c r="D158" t="n">
-        <v>1.68</v>
+        <v>1.35</v>
       </c>
       <c r="E158" t="b">
         <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>12.3</v>
+        <v>150.7</v>
       </c>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="n">
-        <v>-3.07</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>RELCHEMQ</t>
+          <t>EUREKAFORB</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>113</v>
+        <v>445.2</v>
       </c>
       <c r="C159" t="n">
-        <v>114.88</v>
+        <v>451.15</v>
       </c>
       <c r="D159" t="n">
-        <v>1.66</v>
+        <v>1.34</v>
       </c>
       <c r="E159" t="b">
         <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>112.62</v>
+        <v>442.6</v>
       </c>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="n">
-        <v>-1.97</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>TPLPLASTEH</t>
+          <t>TARACHAND</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>61.98</v>
+        <v>60.2</v>
       </c>
       <c r="C160" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D160" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="E160" t="b">
         <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>61.7</v>
+        <v>59.65</v>
       </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="n">
-        <v>-2.06</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>JINDRILL</t>
+          <t>IGCL</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>531.25</v>
+        <v>63.66</v>
       </c>
       <c r="C161" t="n">
-        <v>540</v>
+        <v>64.5</v>
       </c>
       <c r="D161" t="n">
-        <v>1.65</v>
+        <v>1.32</v>
       </c>
       <c r="E161" t="b">
         <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>524.3</v>
+        <v>62.38</v>
       </c>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="n">
-        <v>-2.91</v>
+        <v>-3.29</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>MTNL</t>
+          <t>AIRAN</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>26.06</v>
+        <v>16.03</v>
       </c>
       <c r="C162" t="n">
-        <v>26.49</v>
+        <v>16.24</v>
       </c>
       <c r="D162" t="n">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
       <c r="E162" t="b">
         <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>25.56</v>
+        <v>15.87</v>
       </c>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="n">
-        <v>-3.51</v>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>5PAISA</t>
+          <t>GENUSPAPER</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>304</v>
+        <v>11.77</v>
       </c>
       <c r="C163" t="n">
-        <v>309</v>
+        <v>11.92</v>
       </c>
       <c r="D163" t="n">
-        <v>1.64</v>
+        <v>1.27</v>
       </c>
       <c r="E163" t="b">
         <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>301.3</v>
+        <v>11.82</v>
       </c>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="n">
-        <v>-2.49</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ROTO</t>
+          <t>ALLCARGO</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>60.97</v>
+        <v>7.9</v>
       </c>
       <c r="C164" t="n">
-        <v>61.97</v>
+        <v>8</v>
       </c>
       <c r="D164" t="n">
-        <v>1.64</v>
+        <v>1.27</v>
       </c>
       <c r="E164" t="b">
         <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>60.65</v>
+        <v>7.77</v>
       </c>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="n">
-        <v>-2.13</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>MEDICO</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>40.84</v>
+        <v>149.11</v>
       </c>
       <c r="C165" t="n">
-        <v>41.5</v>
+        <v>151</v>
       </c>
       <c r="D165" t="n">
-        <v>1.62</v>
+        <v>1.27</v>
       </c>
       <c r="E165" t="b">
         <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>40.2</v>
+        <v>149.64</v>
       </c>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="n">
-        <v>-3.13</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>PAUSHAKLTD</t>
+          <t>VISHWARAJ</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>418.25</v>
+        <v>5.56</v>
       </c>
       <c r="C166" t="n">
-        <v>425</v>
+        <v>5.63</v>
       </c>
       <c r="D166" t="n">
-        <v>1.61</v>
+        <v>1.26</v>
       </c>
       <c r="E166" t="b">
         <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>420.45</v>
+        <v>5.42</v>
       </c>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="n">
-        <v>-1.07</v>
+        <v>-3.73</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>KILITCH</t>
+          <t>KRITINUT</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>317.9</v>
+        <v>64.13</v>
       </c>
       <c r="C167" t="n">
-        <v>323</v>
+        <v>64.94</v>
       </c>
       <c r="D167" t="n">
-        <v>1.6</v>
+        <v>1.26</v>
       </c>
       <c r="E167" t="b">
         <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>319.2</v>
+        <v>63.94</v>
       </c>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="n">
-        <v>-1.18</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>NDL</t>
+          <t>SAKUMA</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>2.52</v>
+        <v>1.6</v>
       </c>
       <c r="C168" t="n">
-        <v>2.56</v>
+        <v>1.62</v>
       </c>
       <c r="D168" t="n">
-        <v>1.59</v>
+        <v>1.25</v>
       </c>
       <c r="E168" t="b">
         <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>2.47</v>
+        <v>1.6</v>
       </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="n">
-        <v>-3.52</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SAILIFE</t>
+          <t>VARDHACRLC</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>1014</v>
+        <v>33.87</v>
       </c>
       <c r="C169" t="n">
-        <v>1030.05</v>
+        <v>34.29</v>
       </c>
       <c r="D169" t="n">
-        <v>1.58</v>
+        <v>1.24</v>
       </c>
       <c r="E169" t="b">
         <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>993.8</v>
+        <v>34.17</v>
       </c>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="n">
-        <v>-3.52</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ASIANENE</t>
+          <t>HTMEDIA</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>280.65</v>
+        <v>21.34</v>
       </c>
       <c r="C170" t="n">
-        <v>285</v>
+        <v>21.6</v>
       </c>
       <c r="D170" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="E170" t="b">
         <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>285</v>
+        <v>21</v>
       </c>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="n">
-        <v>0</v>
+        <v>-2.78</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>GLOBE</t>
+          <t>ACMESOLAR</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>2.59</v>
+        <v>240.08</v>
       </c>
       <c r="C171" t="n">
-        <v>2.63</v>
+        <v>243</v>
       </c>
       <c r="D171" t="n">
-        <v>1.54</v>
+        <v>1.22</v>
       </c>
       <c r="E171" t="b">
         <v>0</v>
       </c>
       <c r="F171" t="n">
-        <v>2.55</v>
+        <v>257.82</v>
       </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="n">
-        <v>-3.04</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>UNITEDPOLY</t>
+          <t>JAGSNPHARM</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>27.53</v>
+        <v>189.61</v>
       </c>
       <c r="C172" t="n">
-        <v>27.95</v>
+        <v>191.9</v>
       </c>
       <c r="D172" t="n">
-        <v>1.53</v>
+        <v>1.21</v>
       </c>
       <c r="E172" t="b">
         <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>26.94</v>
+        <v>190.29</v>
       </c>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="n">
-        <v>-3.61</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>SOLEX</t>
+          <t>CHOICEIN</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>879.35</v>
+        <v>645.25</v>
       </c>
       <c r="C173" t="n">
-        <v>892.55</v>
+        <v>653</v>
       </c>
       <c r="D173" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="E173" t="b">
         <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>860</v>
+        <v>638.4</v>
       </c>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="n">
-        <v>-3.65</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>SURANAT&amp;P</t>
+          <t>MAHSCOOTER</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>17.05</v>
+        <v>12816</v>
       </c>
       <c r="C174" t="n">
-        <v>17.3</v>
+        <v>12970</v>
       </c>
       <c r="D174" t="n">
-        <v>1.47</v>
+        <v>1.2</v>
       </c>
       <c r="E174" t="b">
         <v>0</v>
       </c>
-      <c r="F174" t="inlineStr"/>
+      <c r="F174" t="n">
+        <v>12737</v>
+      </c>
       <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr"/>
+      <c r="H174" t="n">
+        <v>-1.8</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>NDL</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>397.75</v>
+        <v>2.49</v>
       </c>
       <c r="C175" t="n">
-        <v>403.5</v>
+        <v>2.52</v>
       </c>
       <c r="D175" t="n">
-        <v>1.45</v>
+        <v>1.2</v>
       </c>
       <c r="E175" t="b">
         <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>393.6</v>
+        <v>2.44</v>
       </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="n">
-        <v>-2.45</v>
+        <v>-3.17</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ONESOURCE</t>
+          <t>STEELCITY</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>1473.6</v>
+        <v>82.02</v>
       </c>
       <c r="C176" t="n">
-        <v>1494.9</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="D176" t="n">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="E176" t="b">
         <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>1436</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="n">
-        <v>-3.94</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>GUJGASLTD</t>
+          <t>TARC</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>391</v>
+        <v>131.36</v>
       </c>
       <c r="C177" t="n">
-        <v>396.6</v>
+        <v>132.9</v>
       </c>
       <c r="D177" t="n">
-        <v>1.43</v>
+        <v>1.17</v>
       </c>
       <c r="E177" t="b">
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>399</v>
+        <v>129.73</v>
       </c>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="n">
-        <v>0.61</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>LINC</t>
+          <t>FLAIR</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>102.46</v>
+        <v>298.2</v>
       </c>
       <c r="C178" t="n">
-        <v>103.9</v>
+        <v>301.7</v>
       </c>
       <c r="D178" t="n">
-        <v>1.41</v>
+        <v>1.17</v>
       </c>
       <c r="E178" t="b">
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>102.74</v>
+        <v>293.45</v>
       </c>
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="n">
-        <v>-1.12</v>
+        <v>-2.73</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>JHS</t>
+          <t>INTLCONV</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>9.359999999999999</v>
+        <v>75.27</v>
       </c>
       <c r="C179" t="n">
-        <v>9.49</v>
+        <v>76.14</v>
       </c>
       <c r="D179" t="n">
-        <v>1.39</v>
+        <v>1.16</v>
       </c>
       <c r="E179" t="b">
         <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>9.289999999999999</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="n">
-        <v>-2.11</v>
+        <v>-1.55</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>BANKA</t>
+          <t>SEJALLTD</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>51.77</v>
+        <v>538.75</v>
       </c>
       <c r="C180" t="n">
-        <v>52.49</v>
+        <v>544.95</v>
       </c>
       <c r="D180" t="n">
-        <v>1.39</v>
+        <v>1.15</v>
       </c>
       <c r="E180" t="b">
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>51.5</v>
+        <v>525.15</v>
       </c>
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="n">
-        <v>-1.89</v>
+        <v>-3.63</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SUPREME</t>
+          <t>BHARATCOAL</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>55.14</v>
+        <v>35.81</v>
       </c>
       <c r="C181" t="n">
-        <v>55.9</v>
+        <v>36.22</v>
       </c>
       <c r="D181" t="n">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="E181" t="b">
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>50.85</v>
+        <v>36.08</v>
       </c>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="n">
-        <v>-9.029999999999999</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>NILAINFRA</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>7.39</v>
+        <v>1911.4</v>
       </c>
       <c r="C182" t="n">
-        <v>7.49</v>
+        <v>1933</v>
       </c>
       <c r="D182" t="n">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="E182" t="b">
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>7.32</v>
+        <v>1917.5</v>
       </c>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="n">
-        <v>-2.27</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>TNTELE</t>
+          <t>RUSHIL</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>8.93</v>
+        <v>16.21</v>
       </c>
       <c r="C183" t="n">
-        <v>9.050000000000001</v>
+        <v>16.39</v>
       </c>
       <c r="D183" t="n">
-        <v>1.34</v>
+        <v>1.11</v>
       </c>
       <c r="E183" t="b">
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>8.960000000000001</v>
+        <v>15.75</v>
       </c>
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="n">
-        <v>-0.99</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>SONAMLTD</t>
+          <t>ALKALI</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>55.25</v>
+        <v>60.33</v>
       </c>
       <c r="C184" t="n">
-        <v>55.98</v>
+        <v>61</v>
       </c>
       <c r="D184" t="n">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="E184" t="b">
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>58.65</v>
+        <v>57.05</v>
       </c>
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="n">
-        <v>4.77</v>
+        <v>-6.48</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>JUSTDIAL</t>
+          <t>CROWN</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>535.35</v>
+        <v>118.79</v>
       </c>
       <c r="C185" t="n">
-        <v>542.35</v>
+        <v>120.1</v>
       </c>
       <c r="D185" t="n">
-        <v>1.31</v>
+        <v>1.1</v>
       </c>
       <c r="E185" t="b">
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>519.3</v>
+        <v>119.55</v>
       </c>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="n">
-        <v>-4.25</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>VENUSREM</t>
+          <t>PLAZACABLE</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>861.7</v>
+        <v>35.61</v>
       </c>
       <c r="C186" t="n">
-        <v>872.95</v>
+        <v>36</v>
       </c>
       <c r="D186" t="n">
-        <v>1.31</v>
+        <v>1.1</v>
       </c>
       <c r="E186" t="b">
         <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>918.9</v>
+        <v>35.98</v>
       </c>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="n">
-        <v>5.26</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>INDOTHAI</t>
+          <t>BASILIC</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>261.6</v>
+        <v>206.45</v>
       </c>
       <c r="C187" t="n">
-        <v>265</v>
+        <v>208.7</v>
       </c>
       <c r="D187" t="n">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="E187" t="b">
         <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>258.05</v>
+        <v>202.35</v>
       </c>
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="n">
-        <v>-2.62</v>
+        <v>-3.04</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>SEDEMAC</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>380.15</v>
+        <v>1441.3</v>
       </c>
       <c r="C188" t="n">
-        <v>385</v>
+        <v>1457</v>
       </c>
       <c r="D188" t="n">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="E188" t="b">
         <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>387.75</v>
+        <v>1464</v>
       </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="n">
-        <v>0.71</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>GKENERGY</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>110.58</v>
+        <v>200.84</v>
       </c>
       <c r="C189" t="n">
-        <v>112</v>
+        <v>203</v>
       </c>
       <c r="D189" t="n">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="E189" t="b">
         <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>109.07</v>
+        <v>185.76</v>
       </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="n">
-        <v>-2.62</v>
+        <v>-8.49</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>XELPMOC</t>
+          <t>MUKANDLTD</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>116.91</v>
+        <v>120.72</v>
       </c>
       <c r="C190" t="n">
-        <v>118.4</v>
+        <v>122</v>
       </c>
       <c r="D190" t="n">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="E190" t="b">
         <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>115</v>
+        <v>120.98</v>
       </c>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="n">
-        <v>-2.87</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>BAJAJINDEF</t>
+          <t>ORIENTCER</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>238.66</v>
+        <v>38.05</v>
       </c>
       <c r="C191" t="n">
-        <v>241.65</v>
+        <v>38.45</v>
       </c>
       <c r="D191" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="E191" t="b">
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>256.4</v>
+        <v>37.02</v>
       </c>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="n">
-        <v>6.1</v>
+        <v>-3.72</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ACCURACY</t>
+          <t>DANGEE</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>4</v>
+        <v>2.86</v>
       </c>
       <c r="C192" t="n">
-        <v>4.05</v>
+        <v>2.89</v>
       </c>
       <c r="D192" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="E192" t="b">
         <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="n">
-        <v>-1.23</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SERVOTECH</t>
+          <t>SHAH</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>68.16</v>
+        <v>4.82</v>
       </c>
       <c r="C193" t="n">
-        <v>69</v>
+        <v>4.87</v>
       </c>
       <c r="D193" t="n">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="E193" t="b">
         <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>69.75</v>
+        <v>4.83</v>
       </c>
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="n">
-        <v>1.09</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>RUDRA</t>
+          <t>DPSCLTD</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>17.28</v>
+        <v>8.66</v>
       </c>
       <c r="C194" t="n">
-        <v>17.49</v>
+        <v>8.75</v>
       </c>
       <c r="D194" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="E194" t="b">
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>17.4</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="n">
-        <v>-0.51</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>CYBERTECH</t>
+          <t>ZENITHEXPO</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>106.7</v>
+        <v>193.2</v>
       </c>
       <c r="C195" t="n">
-        <v>108</v>
+        <v>195.2</v>
       </c>
       <c r="D195" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="E195" t="b">
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>102.55</v>
+        <v>196</v>
       </c>
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="n">
-        <v>-5.05</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ORBTEXP</t>
+          <t>SPCENET</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>162.82</v>
+        <v>3.9</v>
       </c>
       <c r="C196" t="n">
-        <v>164.8</v>
+        <v>3.94</v>
       </c>
       <c r="D196" t="n">
-        <v>1.22</v>
+        <v>1.03</v>
       </c>
       <c r="E196" t="b">
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>161.9</v>
+        <v>3.77</v>
       </c>
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="n">
-        <v>-1.76</v>
+        <v>-4.31</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>KAPSTON</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>721.55</v>
+        <v>277.15</v>
       </c>
       <c r="C197" t="n">
-        <v>730.25</v>
+        <v>280</v>
       </c>
       <c r="D197" t="n">
-        <v>1.21</v>
+        <v>1.03</v>
       </c>
       <c r="E197" t="b">
         <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>709.4</v>
+        <v>276.85</v>
       </c>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="n">
-        <v>-2.86</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SUMIT</t>
+          <t>MAHICKRA</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>33.4</v>
+        <v>206</v>
       </c>
       <c r="C198" t="n">
-        <v>33.8</v>
+        <v>208.1</v>
       </c>
       <c r="D198" t="n">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="E198" t="b">
         <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>33.89</v>
+        <v>208.1</v>
       </c>
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>HEIDELBERG</t>
+          <t>JISLJALEQS</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>157.13</v>
+        <v>34.38</v>
       </c>
       <c r="C199" t="n">
-        <v>159</v>
+        <v>34.73</v>
       </c>
       <c r="D199" t="n">
-        <v>1.19</v>
+        <v>1.02</v>
       </c>
       <c r="E199" t="b">
         <v>0</v>
       </c>
       <c r="F199" t="n">
-        <v>157.09</v>
+        <v>32.98</v>
       </c>
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="n">
-        <v>-1.2</v>
+        <v>-5.04</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>TEXMOPIPES</t>
+          <t>KOKUYOCMLN</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>44.47</v>
+        <v>78.11</v>
       </c>
       <c r="C200" t="n">
-        <v>45</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="D200" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="E200" t="b">
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>44.53</v>
+        <v>77.3</v>
       </c>
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="n">
-        <v>-1.04</v>
+        <v>-2.03</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ORIENTBELL</t>
+          <t>DAMCAPITAL</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>256.45</v>
+        <v>131.12</v>
       </c>
       <c r="C201" t="n">
-        <v>259.5</v>
+        <v>132.43</v>
       </c>
       <c r="D201" t="n">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="E201" t="b">
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>267</v>
+        <v>127.71</v>
       </c>
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="n">
-        <v>2.89</v>
+        <v>-3.56</v>
       </c>
     </row>
   </sheetData>

--- a/data/trending_momentum_stocks.xlsx
+++ b/data/trending_momentum_stocks.xlsx
@@ -487,2779 +487,2779 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ICDSLTD</t>
+          <t>CREATIVEYE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.37</v>
+        <v>6.65</v>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>7.89</v>
       </c>
       <c r="D3" t="n">
-        <v>10.2</v>
+        <v>18.65</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>54.44</v>
+        <v>6.88</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>8.880000000000001</v>
+        <v>-12.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KANDARP</t>
+          <t>UMAEXPORTS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>140</v>
+        <v>24.28</v>
       </c>
       <c r="C4" t="n">
-        <v>152.8</v>
+        <v>28.79</v>
       </c>
       <c r="D4" t="n">
-        <v>9.140000000000001</v>
+        <v>18.57</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>132.5</v>
+        <v>25.35</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>-13.29</v>
+        <v>-11.95</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DCMFINSERV</t>
+          <t>CENTRUM</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.74</v>
+        <v>22.84</v>
       </c>
       <c r="C5" t="n">
-        <v>7.26</v>
+        <v>27</v>
       </c>
       <c r="D5" t="n">
-        <v>7.72</v>
+        <v>18.21</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>7.41</v>
+        <v>23.25</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>2.07</v>
+        <v>-13.89</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>REGAAL</t>
+          <t>ICDSLTD</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>87.69</v>
+        <v>54.44</v>
       </c>
       <c r="C6" t="n">
-        <v>94</v>
+        <v>59.88</v>
       </c>
       <c r="D6" t="n">
-        <v>7.2</v>
+        <v>9.99</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>86</v>
+        <v>51.98</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>-8.51</v>
+        <v>-13.19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DHARAN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.14</v>
+        <v>6.19</v>
       </c>
       <c r="C7" t="n">
-        <v>0.15</v>
+        <v>6.8</v>
       </c>
       <c r="D7" t="n">
-        <v>7.14</v>
+        <v>9.85</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.15</v>
+        <v>6.09</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-10.44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UMESLTD</t>
+          <t>DCMFINSERV</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.98</v>
+        <v>7.41</v>
       </c>
       <c r="C8" t="n">
-        <v>6.4</v>
+        <v>8.09</v>
       </c>
       <c r="D8" t="n">
-        <v>7.02</v>
+        <v>9.18</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>6.25</v>
+        <v>8.15</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>-2.34</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GSS</t>
+          <t>SUPREME</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11.98</v>
+        <v>50.55</v>
       </c>
       <c r="C9" t="n">
-        <v>12.78</v>
+        <v>54.8</v>
       </c>
       <c r="D9" t="n">
-        <v>6.68</v>
+        <v>8.41</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>11.91</v>
+        <v>49.32</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>-6.81</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MAHAPEXLTD</t>
+          <t>AKI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>115.39</v>
+        <v>4.36</v>
       </c>
       <c r="C10" t="n">
-        <v>123</v>
+        <v>4.7</v>
       </c>
       <c r="D10" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>118.98</v>
+        <v>4.95</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>-3.27</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>INFOMEDIA</t>
+          <t>SECURKLOUD</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.15</v>
+        <v>21.08</v>
       </c>
       <c r="C11" t="n">
-        <v>5.48</v>
+        <v>22.7</v>
       </c>
       <c r="D11" t="n">
-        <v>6.41</v>
+        <v>7.69</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>5.15</v>
+        <v>21.03</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>-6.02</v>
+        <v>-7.36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LFIC</t>
+          <t>TOUCHWOOD</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>125.92</v>
+        <v>72.63</v>
       </c>
       <c r="C12" t="n">
-        <v>133.5</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>6.02</v>
+        <v>7.38</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>127.99</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>-4.13</v>
+        <v>-8.949999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TOUCHWOOD</t>
+          <t>SHANTI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>70.90000000000001</v>
+        <v>6.52</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>5.78</v>
+        <v>7.36</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>70.20999999999999</v>
+        <v>6.41</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>-6.39</v>
+        <v>-8.43</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FILATFASH</t>
+          <t>BAJEL</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.18</v>
+        <v>139.96</v>
       </c>
       <c r="C14" t="n">
-        <v>0.19</v>
+        <v>149.9</v>
       </c>
       <c r="D14" t="n">
-        <v>5.56</v>
+        <v>7.1</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.19</v>
+        <v>151.79</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GJL</t>
+          <t>MKPL</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>216.75</v>
+        <v>4.73</v>
       </c>
       <c r="C15" t="n">
-        <v>227.55</v>
+        <v>5.05</v>
       </c>
       <c r="D15" t="n">
-        <v>4.98</v>
+        <v>6.77</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>227.55</v>
+        <v>5.02</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SANGINITA</t>
+          <t>ALKALI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14.28</v>
+        <v>57.19</v>
       </c>
       <c r="C16" t="n">
-        <v>14.99</v>
+        <v>60.99</v>
       </c>
       <c r="D16" t="n">
-        <v>4.97</v>
+        <v>6.64</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>14.99</v>
+        <v>59.48</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SADHNANIQ</t>
+          <t>COMPUSOFT</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.61</v>
+        <v>15.2</v>
       </c>
       <c r="C17" t="n">
-        <v>1.69</v>
+        <v>16.2</v>
       </c>
       <c r="D17" t="n">
-        <v>4.97</v>
+        <v>6.58</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.69</v>
+        <v>14.27</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-11.91</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MORARJEE</t>
+          <t>HCG-RE</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6.66</v>
+        <v>28.2</v>
       </c>
       <c r="C18" t="n">
-        <v>6.99</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>4.95</v>
+        <v>6.38</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>6.99</v>
+        <v>22.35</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-25.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>VIJIFIN</t>
+          <t>GSS</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.63</v>
+        <v>11.86</v>
       </c>
       <c r="C19" t="n">
-        <v>2.76</v>
+        <v>12.6</v>
       </c>
       <c r="D19" t="n">
-        <v>4.94</v>
+        <v>6.24</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>2.76</v>
+        <v>11.36</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>-9.84</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ONELIFECAP</t>
+          <t>SAHYADRI</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>15.22</v>
+        <v>221.3</v>
       </c>
       <c r="C20" t="n">
-        <v>15.95</v>
+        <v>235</v>
       </c>
       <c r="D20" t="n">
-        <v>4.8</v>
+        <v>6.19</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>15.83</v>
+        <v>221.2</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>-0.75</v>
+        <v>-5.87</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GSLSU</t>
+          <t>LEMERITE</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>70.19</v>
+        <v>439.6</v>
       </c>
       <c r="C21" t="n">
-        <v>73.5</v>
+        <v>466</v>
       </c>
       <c r="D21" t="n">
-        <v>4.72</v>
+        <v>6.01</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>67.40000000000001</v>
+        <v>442</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>-8.300000000000001</v>
+        <v>-5.15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SHAHALLOYS</t>
+          <t>SUMIT</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>61.95</v>
+        <v>38.51</v>
       </c>
       <c r="C22" t="n">
-        <v>64.8</v>
+        <v>40.82</v>
       </c>
       <c r="D22" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>59.82</v>
+        <v>37.33</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>-7.69</v>
+        <v>-8.550000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SAMBHAAV</t>
+          <t>TFL</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6.41</v>
+        <v>12.33</v>
       </c>
       <c r="C23" t="n">
-        <v>6.7</v>
+        <v>13.06</v>
       </c>
       <c r="D23" t="n">
-        <v>4.52</v>
+        <v>5.92</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>6.29</v>
+        <v>12.16</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>-6.12</v>
+        <v>-6.89</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JPASSOCIAT</t>
+          <t>ADROITINFO</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.67</v>
+        <v>9.42</v>
       </c>
       <c r="C24" t="n">
-        <v>2.79</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>4.49</v>
+        <v>5.73</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>2.8</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>0.36</v>
+        <v>-8.43</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>REXPRO</t>
+          <t>AEPL</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>43</v>
+        <v>17.54</v>
       </c>
       <c r="C25" t="n">
-        <v>44.9</v>
+        <v>18.54</v>
       </c>
       <c r="D25" t="n">
-        <v>4.42</v>
+        <v>5.7</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>44.9</v>
+        <v>17.61</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>-5.02</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CONFIPET</t>
+          <t>ODIGMA</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>35.45</v>
+        <v>22.48</v>
       </c>
       <c r="C26" t="n">
-        <v>37</v>
+        <v>23.74</v>
       </c>
       <c r="D26" t="n">
-        <v>4.37</v>
+        <v>5.6</v>
       </c>
       <c r="E26" t="b">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>37.03</v>
+        <v>22.01</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>0.08</v>
+        <v>-7.29</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PILITA</t>
+          <t>LAMBODHARA</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.81</v>
+        <v>94.72</v>
       </c>
       <c r="C27" t="n">
-        <v>8.15</v>
+        <v>100</v>
       </c>
       <c r="D27" t="n">
-        <v>4.35</v>
+        <v>5.57</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>7.86</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>-3.56</v>
+        <v>-6.01</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>RAJTV</t>
+          <t>FILATFASH</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>39.18</v>
+        <v>0.18</v>
       </c>
       <c r="C28" t="n">
-        <v>40.85</v>
+        <v>0.19</v>
       </c>
       <c r="D28" t="n">
-        <v>4.26</v>
+        <v>5.56</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>38.8</v>
+        <v>0.19</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>-5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>JHS</t>
+          <t>CPCAP</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>8.970000000000001</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="C29" t="n">
-        <v>9.35</v>
+        <v>88.89</v>
       </c>
       <c r="D29" t="n">
-        <v>4.24</v>
+        <v>5.42</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>8.859999999999999</v>
+        <v>83.05</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>-5.24</v>
+        <v>-6.57</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>HEADSUP</t>
+          <t>KEEPLEARN</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7.13</v>
+        <v>1.87</v>
       </c>
       <c r="C30" t="n">
-        <v>7.43</v>
+        <v>1.97</v>
       </c>
       <c r="D30" t="n">
-        <v>4.21</v>
+        <v>5.35</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>7.22</v>
+        <v>1.91</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>-2.83</v>
+        <v>-3.05</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AURIGROW</t>
+          <t>URBAN</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.24</v>
+        <v>125.25</v>
       </c>
       <c r="C31" t="n">
-        <v>0.25</v>
+        <v>131.95</v>
       </c>
       <c r="D31" t="n">
-        <v>4.17</v>
+        <v>5.35</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0.25</v>
+        <v>125.5</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>-4.89</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>THEJO</t>
+          <t>SUPERHOUSE</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1651.3</v>
+        <v>142.58</v>
       </c>
       <c r="C32" t="n">
-        <v>1720</v>
+        <v>149.9</v>
       </c>
       <c r="D32" t="n">
-        <v>4.16</v>
+        <v>5.13</v>
       </c>
       <c r="E32" t="b">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>1620</v>
+        <v>141.11</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>-5.81</v>
+        <v>-5.86</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FMNL</t>
+          <t>MACPOWER</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>8.26</v>
+        <v>903.05</v>
       </c>
       <c r="C33" t="n">
-        <v>8.6</v>
+        <v>948.8</v>
       </c>
       <c r="D33" t="n">
-        <v>4.12</v>
+        <v>5.07</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>8.390000000000001</v>
+        <v>881.25</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>-2.44</v>
+        <v>-7.12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>GAYAPROJ</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>110.48</v>
+        <v>12.7</v>
       </c>
       <c r="C34" t="n">
-        <v>114.9</v>
+        <v>13.33</v>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>4.96</v>
       </c>
       <c r="E34" t="b">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>109.8</v>
+        <v>13.33</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>-4.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BALKRISHNA</t>
+          <t>RCOM</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>14.77</v>
+        <v>1.01</v>
       </c>
       <c r="C35" t="n">
-        <v>15.35</v>
+        <v>1.06</v>
       </c>
       <c r="D35" t="n">
-        <v>3.93</v>
+        <v>4.95</v>
       </c>
       <c r="E35" t="b">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>15.2</v>
+        <v>0.96</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>-0.98</v>
+        <v>-9.43</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DEVX</t>
+          <t>VIVIDHA</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>37.52</v>
+        <v>0.61</v>
       </c>
       <c r="C36" t="n">
-        <v>38.99</v>
+        <v>0.64</v>
       </c>
       <c r="D36" t="n">
-        <v>3.92</v>
+        <v>4.92</v>
       </c>
       <c r="E36" t="b">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>36.61</v>
+        <v>0.6</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>-6.1</v>
+        <v>-6.25</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>JUNIPER</t>
+          <t>ONELIFECAP</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>204.35</v>
+        <v>15.14</v>
       </c>
       <c r="C37" t="n">
-        <v>212.34</v>
+        <v>15.88</v>
       </c>
       <c r="D37" t="n">
-        <v>3.91</v>
+        <v>4.89</v>
       </c>
       <c r="E37" t="b">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>201.31</v>
+        <v>15.4</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>-5.19</v>
+        <v>-3.02</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BALAJEE</t>
+          <t>LIBERTSHOE</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>26.37</v>
+        <v>262.47</v>
       </c>
       <c r="C38" t="n">
-        <v>27.4</v>
+        <v>275</v>
       </c>
       <c r="D38" t="n">
-        <v>3.91</v>
+        <v>4.77</v>
       </c>
       <c r="E38" t="b">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>25.8</v>
+        <v>263.06</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>-5.84</v>
+        <v>-4.34</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>KALPATARU</t>
+          <t>DHRUV</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>299.5</v>
+        <v>29.88</v>
       </c>
       <c r="C39" t="n">
-        <v>311.05</v>
+        <v>31.3</v>
       </c>
       <c r="D39" t="n">
-        <v>3.86</v>
+        <v>4.75</v>
       </c>
       <c r="E39" t="b">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>324.35</v>
+        <v>29.92</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>4.28</v>
+        <v>-4.41</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PREMIER</t>
+          <t>EQUIPPP</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.89</v>
+        <v>16.48</v>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>17.26</v>
       </c>
       <c r="D40" t="n">
-        <v>3.81</v>
+        <v>4.73</v>
       </c>
       <c r="E40" t="b">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>3</v>
+        <v>17.3</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ANTGRAPHIC</t>
+          <t>VIJIFIN</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.79</v>
+        <v>2.76</v>
       </c>
       <c r="C41" t="n">
-        <v>0.82</v>
+        <v>2.89</v>
       </c>
       <c r="D41" t="n">
-        <v>3.8</v>
+        <v>4.71</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0.79</v>
+        <v>2.89</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>-3.66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HMAAGRO</t>
+          <t>SILLYMONKS</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>24.77</v>
+        <v>16</v>
       </c>
       <c r="C42" t="n">
-        <v>25.65</v>
+        <v>16.75</v>
       </c>
       <c r="D42" t="n">
-        <v>3.55</v>
+        <v>4.69</v>
       </c>
       <c r="E42" t="b">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>24.41</v>
+        <v>16.68</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>-4.83</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>RHFL</t>
+          <t>CELEBRITY</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.58</v>
+        <v>7.52</v>
       </c>
       <c r="C43" t="n">
-        <v>2.67</v>
+        <v>7.87</v>
       </c>
       <c r="D43" t="n">
-        <v>3.49</v>
+        <v>4.65</v>
       </c>
       <c r="E43" t="b">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>2.7</v>
+        <v>7.56</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>1.12</v>
+        <v>-3.94</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>VIVIDHA</t>
+          <t>LIKHITHA</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6</v>
+        <v>141.84</v>
       </c>
       <c r="C44" t="n">
-        <v>0.62</v>
+        <v>148.4</v>
       </c>
       <c r="D44" t="n">
-        <v>3.33</v>
+        <v>4.62</v>
       </c>
       <c r="E44" t="b">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.62</v>
+        <v>139.37</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>-6.08</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>VIVIMEDLAB</t>
+          <t>AVROIND</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>6.96</v>
+        <v>130.85</v>
       </c>
       <c r="C45" t="n">
-        <v>7.19</v>
+        <v>136.9</v>
       </c>
       <c r="D45" t="n">
-        <v>3.3</v>
+        <v>4.62</v>
       </c>
       <c r="E45" t="b">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>6.93</v>
+        <v>137.39</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>-3.62</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ZEEMEDIA</t>
+          <t>VAISHALI</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>7.89</v>
+        <v>6.12</v>
       </c>
       <c r="C46" t="n">
-        <v>8.15</v>
+        <v>6.4</v>
       </c>
       <c r="D46" t="n">
-        <v>3.3</v>
+        <v>4.58</v>
       </c>
       <c r="E46" t="b">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>7.91</v>
+        <v>6.07</v>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>-2.94</v>
+        <v>-5.16</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NKIND</t>
+          <t>ORTEL</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>63.54</v>
+        <v>1.54</v>
       </c>
       <c r="C47" t="n">
-        <v>65.59999999999999</v>
+        <v>1.61</v>
       </c>
       <c r="D47" t="n">
-        <v>3.24</v>
+        <v>4.55</v>
       </c>
       <c r="E47" t="b">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>63</v>
+        <v>1.61</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>-3.96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FLFL</t>
+          <t>ADVANCE</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1.27</v>
+        <v>98.22</v>
       </c>
       <c r="C48" t="n">
-        <v>1.31</v>
+        <v>102.6</v>
       </c>
       <c r="D48" t="n">
-        <v>3.15</v>
+        <v>4.46</v>
       </c>
       <c r="E48" t="b">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>1.28</v>
+        <v>99.47</v>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>-2.29</v>
+        <v>-3.05</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>RCOM</t>
+          <t>RAMKY</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.97</v>
+        <v>479.7</v>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>501</v>
       </c>
       <c r="D49" t="n">
-        <v>3.09</v>
+        <v>4.44</v>
       </c>
       <c r="E49" t="b">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>1.01</v>
+        <v>464.85</v>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>-7.22</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NECLIFE</t>
+          <t>SANWARIA</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>11.33</v>
+        <v>0.23</v>
       </c>
       <c r="C50" t="n">
-        <v>11.68</v>
+        <v>0.24</v>
       </c>
       <c r="D50" t="n">
-        <v>3.09</v>
+        <v>4.35</v>
       </c>
       <c r="E50" t="b">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>11.37</v>
+        <v>0.24</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>-2.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GINNIFILA</t>
+          <t>GATECH</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>37.34</v>
+        <v>0.46</v>
       </c>
       <c r="C51" t="n">
-        <v>38.49</v>
+        <v>0.48</v>
       </c>
       <c r="D51" t="n">
-        <v>3.08</v>
+        <v>4.35</v>
       </c>
       <c r="E51" t="b">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>36.6</v>
+        <v>0.46</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>-4.91</v>
+        <v>-4.17</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>VINEETLAB</t>
+          <t>SONAMLTD</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>30.04</v>
+        <v>56.52</v>
       </c>
       <c r="C52" t="n">
-        <v>30.95</v>
+        <v>58.96</v>
       </c>
       <c r="D52" t="n">
-        <v>3.03</v>
+        <v>4.32</v>
       </c>
       <c r="E52" t="b">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>30.33</v>
+        <v>56.14</v>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>-2</v>
+        <v>-4.78</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FROG</t>
+          <t>VERTOZ</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>135.6</v>
+        <v>36.19</v>
       </c>
       <c r="C53" t="n">
-        <v>139.7</v>
+        <v>37.7</v>
       </c>
       <c r="D53" t="n">
-        <v>3.02</v>
+        <v>4.17</v>
       </c>
       <c r="E53" t="b">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>134.05</v>
+        <v>34.85</v>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>-4.04</v>
+        <v>-7.56</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SIGMA</t>
+          <t>MAXIND</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>42.47</v>
+        <v>145.94</v>
       </c>
       <c r="C54" t="n">
-        <v>43.75</v>
+        <v>152</v>
       </c>
       <c r="D54" t="n">
-        <v>3.01</v>
+        <v>4.15</v>
       </c>
       <c r="E54" t="b">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>40.98</v>
+        <v>140.5</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>-6.33</v>
+        <v>-7.57</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NAVKARURB</t>
+          <t>VISHWARAJ</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>5.38</v>
       </c>
       <c r="C55" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>4.09</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0.96</v>
+        <v>5.1</v>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>-6.8</v>
+        <v>-8.93</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SOFTTECH</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>259.4</v>
+        <v>593.6</v>
       </c>
       <c r="C56" t="n">
-        <v>267.1</v>
+        <v>617.8</v>
       </c>
       <c r="D56" t="n">
-        <v>2.97</v>
+        <v>4.08</v>
       </c>
       <c r="E56" t="b">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>262.15</v>
+        <v>578.05</v>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>-1.85</v>
+        <v>-6.43</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>KNAGRI</t>
+          <t>MOS</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>179.66</v>
+        <v>13.5</v>
       </c>
       <c r="C57" t="n">
-        <v>185</v>
+        <v>14.05</v>
       </c>
       <c r="D57" t="n">
-        <v>2.97</v>
+        <v>4.07</v>
       </c>
       <c r="E57" t="b">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>177.18</v>
+        <v>13.9</v>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>-4.23</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TREJHARA</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>160.09</v>
+        <v>565.9</v>
       </c>
       <c r="C58" t="n">
-        <v>164.8</v>
+        <v>588.95</v>
       </c>
       <c r="D58" t="n">
-        <v>2.94</v>
+        <v>4.07</v>
       </c>
       <c r="E58" t="b">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>164</v>
+        <v>537.6</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>-0.49</v>
+        <v>-8.720000000000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SITINET</t>
+          <t>TEJASNET</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.34</v>
+        <v>424.45</v>
       </c>
       <c r="C59" t="n">
-        <v>0.35</v>
+        <v>441.65</v>
       </c>
       <c r="D59" t="n">
-        <v>2.94</v>
+        <v>4.05</v>
       </c>
       <c r="E59" t="b">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0.35</v>
+        <v>441</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>LAXMICOT</t>
+          <t>TVVISION</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>13.04</v>
+        <v>5.47</v>
       </c>
       <c r="C60" t="n">
-        <v>13.42</v>
+        <v>5.69</v>
       </c>
       <c r="D60" t="n">
-        <v>2.91</v>
+        <v>4.02</v>
       </c>
       <c r="E60" t="b">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>13</v>
+        <v>5.26</v>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>-3.13</v>
+        <v>-7.56</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TTKPRESTIG</t>
+          <t>AURIGROW</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>578.3</v>
+        <v>0.25</v>
       </c>
       <c r="C61" t="n">
-        <v>595</v>
+        <v>0.26</v>
       </c>
       <c r="D61" t="n">
-        <v>2.89</v>
+        <v>4</v>
       </c>
       <c r="E61" t="b">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>582.35</v>
+        <v>0.26</v>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>-2.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>HAVISHA</t>
+          <t>BANKA</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1.39</v>
+        <v>48.04</v>
       </c>
       <c r="C62" t="n">
-        <v>1.43</v>
+        <v>49.95</v>
       </c>
       <c r="D62" t="n">
-        <v>2.88</v>
+        <v>3.98</v>
       </c>
       <c r="E62" t="b">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>1.44</v>
+        <v>46.99</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>0.7</v>
+        <v>-5.93</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>XTGLOBAL</t>
+          <t>SUMEETINDS</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>34.02</v>
+        <v>28.86</v>
       </c>
       <c r="C63" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D63" t="n">
-        <v>2.88</v>
+        <v>3.95</v>
       </c>
       <c r="E63" t="b">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>34.27</v>
+        <v>29.61</v>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>-2.09</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>VGL</t>
+          <t>SWANDEF</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>60.28</v>
+        <v>2394.6</v>
       </c>
       <c r="C64" t="n">
-        <v>62</v>
+        <v>2489</v>
       </c>
       <c r="D64" t="n">
-        <v>2.85</v>
+        <v>3.94</v>
       </c>
       <c r="E64" t="b">
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>60.53</v>
+        <v>2350</v>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>-2.37</v>
+        <v>-5.58</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>LOVABLE</t>
+          <t>SANGINITA</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>68.38</v>
+        <v>14.99</v>
       </c>
       <c r="C65" t="n">
-        <v>70.3</v>
+        <v>15.57</v>
       </c>
       <c r="D65" t="n">
-        <v>2.81</v>
+        <v>3.87</v>
       </c>
       <c r="E65" t="b">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>69.98999999999999</v>
+        <v>15.73</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>-0.44</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PRAXIS</t>
+          <t>JAIPURKURT</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>6.57</v>
+        <v>29.67</v>
       </c>
       <c r="C66" t="n">
-        <v>6.75</v>
+        <v>30.8</v>
       </c>
       <c r="D66" t="n">
-        <v>2.74</v>
+        <v>3.81</v>
       </c>
       <c r="E66" t="b">
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>6.55</v>
+        <v>29.71</v>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>-2.96</v>
+        <v>-3.54</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>NIBL</t>
+          <t>NOIDATOLL</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>30.65</v>
+        <v>3.42</v>
       </c>
       <c r="C67" t="n">
-        <v>31.49</v>
+        <v>3.55</v>
       </c>
       <c r="D67" t="n">
-        <v>2.74</v>
+        <v>3.8</v>
       </c>
       <c r="E67" t="b">
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>30.36</v>
+        <v>3.47</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>-3.59</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ROSSELLIND</t>
+          <t>SHREERAMA</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>45.76</v>
+        <v>46.07</v>
       </c>
       <c r="C68" t="n">
-        <v>47</v>
+        <v>47.8</v>
       </c>
       <c r="D68" t="n">
-        <v>2.71</v>
+        <v>3.76</v>
       </c>
       <c r="E68" t="b">
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>44.79</v>
+        <v>45.05</v>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>-4.7</v>
+        <v>-5.75</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>ANTGRAPHIC</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>607.6</v>
+        <v>0.8</v>
       </c>
       <c r="C69" t="n">
-        <v>624</v>
+        <v>0.83</v>
       </c>
       <c r="D69" t="n">
-        <v>2.7</v>
+        <v>3.75</v>
       </c>
       <c r="E69" t="b">
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>612.8</v>
+        <v>0.8</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>-1.79</v>
+        <v>-3.61</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PATINTLOG</t>
+          <t>JETFREIGHT</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>9.640000000000001</v>
+        <v>18.34</v>
       </c>
       <c r="C70" t="n">
-        <v>9.9</v>
+        <v>19</v>
       </c>
       <c r="D70" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="E70" t="b">
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>9.73</v>
+        <v>17.8</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>-1.72</v>
+        <v>-6.32</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ALANKIT</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>7.87</v>
+        <v>955.85</v>
       </c>
       <c r="C71" t="n">
-        <v>8.08</v>
+        <v>990</v>
       </c>
       <c r="D71" t="n">
-        <v>2.67</v>
+        <v>3.57</v>
       </c>
       <c r="E71" t="b">
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>7.85</v>
+        <v>946</v>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>-2.85</v>
+        <v>-4.44</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SUNDRMBRAK</t>
+          <t>SURAJEST</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>571.75</v>
+        <v>204.95</v>
       </c>
       <c r="C72" t="n">
-        <v>587</v>
+        <v>212.14</v>
       </c>
       <c r="D72" t="n">
-        <v>2.67</v>
+        <v>3.51</v>
       </c>
       <c r="E72" t="b">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>563.4</v>
+        <v>203.19</v>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>-4.02</v>
+        <v>-4.22</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CAPTRUST</t>
+          <t>URAVIDEF</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>11.59</v>
+        <v>128.51</v>
       </c>
       <c r="C73" t="n">
-        <v>11.9</v>
+        <v>133</v>
       </c>
       <c r="D73" t="n">
-        <v>2.67</v>
+        <v>3.49</v>
       </c>
       <c r="E73" t="b">
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>11.5</v>
+        <v>126.26</v>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>-3.36</v>
+        <v>-5.07</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PIGL</t>
+          <t>WABAG</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>101.32</v>
+        <v>1227.6</v>
       </c>
       <c r="C74" t="n">
-        <v>104</v>
+        <v>1270</v>
       </c>
       <c r="D74" t="n">
-        <v>2.65</v>
+        <v>3.45</v>
       </c>
       <c r="E74" t="b">
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>101.16</v>
+        <v>1223.5</v>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>-2.73</v>
+        <v>-3.66</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>GOLDTECH</t>
+          <t>HARRMALAYA</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>37.71</v>
+        <v>177.66</v>
       </c>
       <c r="C75" t="n">
-        <v>38.7</v>
+        <v>183.7</v>
       </c>
       <c r="D75" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="E75" t="b">
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>37.79</v>
+        <v>172.33</v>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>-2.35</v>
+        <v>-6.19</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ENERGYDEV</t>
+          <t>ZYDUSWELL</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>15.1</v>
+        <v>404.25</v>
       </c>
       <c r="C76" t="n">
-        <v>15.49</v>
+        <v>418</v>
       </c>
       <c r="D76" t="n">
-        <v>2.58</v>
+        <v>3.4</v>
       </c>
       <c r="E76" t="b">
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>15.27</v>
+        <v>415.45</v>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>-1.42</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SETUINFRA</t>
+          <t>VIVIANA</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.39</v>
+        <v>627.7</v>
       </c>
       <c r="C77" t="n">
-        <v>0.4</v>
+        <v>649</v>
       </c>
       <c r="D77" t="n">
-        <v>2.56</v>
+        <v>3.39</v>
       </c>
       <c r="E77" t="b">
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>0.4</v>
+        <v>612</v>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>-5.7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AKSHAR</t>
+          <t>VINNY</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.39</v>
+        <v>1.18</v>
       </c>
       <c r="C78" t="n">
-        <v>0.4</v>
+        <v>1.22</v>
       </c>
       <c r="D78" t="n">
-        <v>2.56</v>
+        <v>3.39</v>
       </c>
       <c r="E78" t="b">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>0.4</v>
+        <v>1.14</v>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>-6.56</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ATLANTAA</t>
+          <t>RADIOCITY</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>36.76</v>
+        <v>5.61</v>
       </c>
       <c r="C79" t="n">
-        <v>37.7</v>
+        <v>5.8</v>
       </c>
       <c r="D79" t="n">
-        <v>2.56</v>
+        <v>3.39</v>
       </c>
       <c r="E79" t="b">
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>36.71</v>
+        <v>5.58</v>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>-2.63</v>
+        <v>-3.79</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>TOKYOPLAST</t>
+          <t>HINDCON</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>74.98</v>
+        <v>18.95</v>
       </c>
       <c r="C80" t="n">
-        <v>76.90000000000001</v>
+        <v>19.59</v>
       </c>
       <c r="D80" t="n">
-        <v>2.56</v>
+        <v>3.38</v>
       </c>
       <c r="E80" t="b">
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>73.55</v>
+        <v>18.5</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>-4.36</v>
+        <v>-5.56</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>C2C</t>
+          <t>ZEELEARN</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>389.1</v>
+        <v>5.36</v>
       </c>
       <c r="C81" t="n">
-        <v>398.85</v>
+        <v>5.54</v>
       </c>
       <c r="D81" t="n">
-        <v>2.51</v>
+        <v>3.36</v>
       </c>
       <c r="E81" t="b">
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>390.5</v>
+        <v>5.4</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>-2.09</v>
+        <v>-2.53</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>SUPREMEPWR</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>88.88</v>
+        <v>153.4</v>
       </c>
       <c r="C82" t="n">
-        <v>91.09999999999999</v>
+        <v>158.5</v>
       </c>
       <c r="D82" t="n">
-        <v>2.5</v>
+        <v>3.32</v>
       </c>
       <c r="E82" t="b">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>88.88</v>
+        <v>155</v>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>-2.44</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>KOHINOOR</t>
+          <t>PRITI</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>24.4</v>
+        <v>36.29</v>
       </c>
       <c r="C83" t="n">
-        <v>25</v>
+        <v>37.49</v>
       </c>
       <c r="D83" t="n">
-        <v>2.46</v>
+        <v>3.31</v>
       </c>
       <c r="E83" t="b">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>23.97</v>
+        <v>34.68</v>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>-4.12</v>
+        <v>-7.5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>OILCOUNTUB</t>
+          <t>NOVAAGRI</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>44.89</v>
+        <v>27.1</v>
       </c>
       <c r="C84" t="n">
-        <v>45.99</v>
+        <v>27.98</v>
       </c>
       <c r="D84" t="n">
-        <v>2.45</v>
+        <v>3.25</v>
       </c>
       <c r="E84" t="b">
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>44.68</v>
+        <v>26.66</v>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>-2.85</v>
+        <v>-4.72</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>VILAS</t>
+          <t>NEXTMEDIA</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>377.85</v>
+        <v>5</v>
       </c>
       <c r="C85" t="n">
-        <v>387</v>
+        <v>5.16</v>
       </c>
       <c r="D85" t="n">
-        <v>2.42</v>
+        <v>3.2</v>
       </c>
       <c r="E85" t="b">
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>373</v>
+        <v>4.83</v>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>-3.62</v>
+        <v>-6.4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SWANDEF</t>
+          <t>GOKUL</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2280.6</v>
+        <v>40.7</v>
       </c>
       <c r="C86" t="n">
-        <v>2335</v>
+        <v>42</v>
       </c>
       <c r="D86" t="n">
-        <v>2.39</v>
+        <v>3.19</v>
       </c>
       <c r="E86" t="b">
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>2394.6</v>
+        <v>40.05</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>2.55</v>
+        <v>-4.64</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PAVNAIND</t>
+          <t>ORIENTALTL</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>18.95</v>
+        <v>5.7</v>
       </c>
       <c r="C87" t="n">
-        <v>19.4</v>
+        <v>5.88</v>
       </c>
       <c r="D87" t="n">
-        <v>2.37</v>
+        <v>3.16</v>
       </c>
       <c r="E87" t="b">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>19.01</v>
+        <v>5.63</v>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>-2.01</v>
+        <v>-4.25</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>KPIGREEN</t>
+          <t>MANBA</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>394.7</v>
+        <v>120.2</v>
       </c>
       <c r="C88" t="n">
-        <v>404.05</v>
+        <v>123.99</v>
       </c>
       <c r="D88" t="n">
-        <v>2.37</v>
+        <v>3.15</v>
       </c>
       <c r="E88" t="b">
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>400.4</v>
+        <v>119.52</v>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>-0.9</v>
+        <v>-3.61</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FISCHER</t>
+          <t>ALMONDZ</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>35.15</v>
+        <v>13.95</v>
       </c>
       <c r="C89" t="n">
-        <v>35.98</v>
+        <v>14.39</v>
       </c>
       <c r="D89" t="n">
-        <v>2.36</v>
+        <v>3.15</v>
       </c>
       <c r="E89" t="b">
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>34.25</v>
+        <v>13.69</v>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>-4.81</v>
+        <v>-4.86</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MWL</t>
+          <t>COMMITTED</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>273.4</v>
+        <v>237.45</v>
       </c>
       <c r="C90" t="n">
-        <v>279.8</v>
+        <v>244.9</v>
       </c>
       <c r="D90" t="n">
-        <v>2.34</v>
+        <v>3.14</v>
       </c>
       <c r="E90" t="b">
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>274.55</v>
+        <v>249.3</v>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>-1.88</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DAMODARIND</t>
+          <t>ANMOL</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>23.93</v>
+        <v>10.86</v>
       </c>
       <c r="C91" t="n">
-        <v>24.49</v>
+        <v>11.2</v>
       </c>
       <c r="D91" t="n">
-        <v>2.34</v>
+        <v>3.13</v>
       </c>
       <c r="E91" t="b">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>24.29</v>
+        <v>10.82</v>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>-0.82</v>
+        <v>-3.39</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BSL</t>
+          <t>GVPTECH</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>125.56</v>
+        <v>5.81</v>
       </c>
       <c r="C92" t="n">
-        <v>128.5</v>
+        <v>5.99</v>
       </c>
       <c r="D92" t="n">
-        <v>2.34</v>
+        <v>3.1</v>
       </c>
       <c r="E92" t="b">
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>126.7</v>
+        <v>6.1</v>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
-        <v>-1.4</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>DAMODARIND</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>237.4</v>
+        <v>24.01</v>
       </c>
       <c r="C93" t="n">
-        <v>242.9</v>
+        <v>24.75</v>
       </c>
       <c r="D93" t="n">
-        <v>2.32</v>
+        <v>3.08</v>
       </c>
       <c r="E93" t="b">
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>236</v>
+        <v>23.99</v>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
-        <v>-2.84</v>
+        <v>-3.07</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DSFCL</t>
+          <t>BHARATSE</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>25.12</v>
+        <v>158.87</v>
       </c>
       <c r="C94" t="n">
-        <v>25.7</v>
+        <v>163.75</v>
       </c>
       <c r="D94" t="n">
-        <v>2.31</v>
+        <v>3.07</v>
       </c>
       <c r="E94" t="b">
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>24.71</v>
+        <v>158.68</v>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>-3.85</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>HARRMALAYA</t>
+          <t>GICL</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>181.98</v>
+        <v>43.64</v>
       </c>
       <c r="C95" t="n">
-        <v>186</v>
+        <v>44.94</v>
       </c>
       <c r="D95" t="n">
-        <v>2.21</v>
+        <v>2.98</v>
       </c>
       <c r="E95" t="b">
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>181.99</v>
+        <v>43.92</v>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>-2.16</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BIOFILCHEM</t>
+          <t>OMNI</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>30.63</v>
+        <v>218.54</v>
       </c>
       <c r="C96" t="n">
-        <v>31.3</v>
+        <v>225</v>
       </c>
       <c r="D96" t="n">
-        <v>2.19</v>
+        <v>2.96</v>
       </c>
       <c r="E96" t="b">
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>30.84</v>
+        <v>215.1</v>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>-1.47</v>
+        <v>-4.4</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>URAVIDEF</t>
+          <t>INDOWIND</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>130.07</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="C97" t="n">
-        <v>132.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D97" t="n">
-        <v>2.18</v>
+        <v>2.96</v>
       </c>
       <c r="E97" t="b">
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>128.41</v>
+        <v>8.4</v>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>-3.38</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>TAKE</t>
+          <t>PROSTARM</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>41.71</v>
+        <v>125.31</v>
       </c>
       <c r="C98" t="n">
-        <v>42.6</v>
+        <v>129</v>
       </c>
       <c r="D98" t="n">
-        <v>2.13</v>
+        <v>2.94</v>
       </c>
       <c r="E98" t="b">
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>42.22</v>
+        <v>123.44</v>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>-0.89</v>
+        <v>-4.31</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SRD</t>
+          <t>BESTAGRO</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>51.62</v>
+        <v>14.85</v>
       </c>
       <c r="C99" t="n">
-        <v>52.7</v>
+        <v>15.27</v>
       </c>
       <c r="D99" t="n">
-        <v>2.09</v>
+        <v>2.83</v>
       </c>
       <c r="E99" t="b">
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>51.35</v>
+        <v>14.11</v>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
-        <v>-2.56</v>
+        <v>-7.6</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PHANTOMFX</t>
+          <t>IVP</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>185.65</v>
+        <v>126.51</v>
       </c>
       <c r="C100" t="n">
-        <v>189.5</v>
+        <v>130</v>
       </c>
       <c r="D100" t="n">
-        <v>2.07</v>
+        <v>2.76</v>
       </c>
       <c r="E100" t="b">
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>187.1</v>
+        <v>127</v>
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>-1.27</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>VARDMNPOLY</t>
+          <t>TCC</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>8.25</v>
+        <v>395.25</v>
       </c>
       <c r="C101" t="n">
-        <v>8.42</v>
+        <v>406</v>
       </c>
       <c r="D101" t="n">
-        <v>2.06</v>
+        <v>2.72</v>
       </c>
       <c r="E101" t="b">
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>8.199999999999999</v>
+        <v>387.15</v>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>-2.61</v>
+        <v>-4.64</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>MANOMAY</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>74.47</v>
+        <v>209.3</v>
       </c>
       <c r="C102" t="n">
-        <v>76</v>
+        <v>215</v>
       </c>
       <c r="D102" t="n">
-        <v>2.05</v>
+        <v>2.72</v>
       </c>
       <c r="E102" t="b">
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>74.06</v>
+        <v>201.65</v>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>-2.55</v>
+        <v>-6.21</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>JAIPURKURT</t>
+          <t>PILITA</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>30.27</v>
+        <v>7.34</v>
       </c>
       <c r="C103" t="n">
-        <v>30.89</v>
+        <v>7.54</v>
       </c>
       <c r="D103" t="n">
-        <v>2.05</v>
+        <v>2.72</v>
       </c>
       <c r="E103" t="b">
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>29.98</v>
+        <v>7.18</v>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>-2.95</v>
+        <v>-4.77</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>GULFPETRO</t>
+          <t>DPEL</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>31.47</v>
+        <v>297</v>
       </c>
       <c r="C104" t="n">
-        <v>32.1</v>
+        <v>305.05</v>
       </c>
       <c r="D104" t="n">
-        <v>2</v>
+        <v>2.71</v>
       </c>
       <c r="E104" t="b">
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>31.4</v>
+        <v>309.75</v>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
-        <v>-2.18</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>GAUDIUMIVF</t>
+          <t>RELCHEMQ</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>80.87</v>
+        <v>112.42</v>
       </c>
       <c r="C105" t="n">
-        <v>82.48999999999999</v>
+        <v>115.45</v>
       </c>
       <c r="D105" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="E105" t="b">
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>81.65000000000001</v>
+        <v>112.5</v>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>-1.02</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MOKSH</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>11.5</v>
+        <v>13.38</v>
       </c>
       <c r="C106" t="n">
-        <v>11.73</v>
+        <v>13.74</v>
       </c>
       <c r="D106" t="n">
-        <v>2</v>
+        <v>2.69</v>
       </c>
       <c r="E106" t="b">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>11.69</v>
+        <v>13.27</v>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
-        <v>-0.34</v>
+        <v>-3.42</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AHLADA</t>
+          <t>EMKAY</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>41.03</v>
+        <v>210.37</v>
       </c>
       <c r="C107" t="n">
-        <v>41.85</v>
+        <v>215.99</v>
       </c>
       <c r="D107" t="n">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="E107" t="b">
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>40.8</v>
+        <v>214.63</v>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>-2.51</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>GOLDENTOBC</t>
+          <t>REDINGTON</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>27.45</v>
+        <v>234.55</v>
       </c>
       <c r="C108" t="n">
-        <v>28</v>
+        <v>240.75</v>
       </c>
       <c r="D108" t="n">
-        <v>2</v>
+        <v>2.64</v>
       </c>
       <c r="E108" t="b">
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>27</v>
+        <v>228.5</v>
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
-        <v>-3.57</v>
+        <v>-5.09</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SEYAIND</t>
+          <t>AKSHAR</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>9.050000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="C109" t="n">
-        <v>9.23</v>
+        <v>0.39</v>
       </c>
       <c r="D109" t="n">
-        <v>1.99</v>
+        <v>2.63</v>
       </c>
       <c r="E109" t="b">
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>9.23</v>
+        <v>0.39</v>
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
@@ -3269,2389 +3269,2393 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>INVENTURE</t>
+          <t>SHYAMCENT</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1.02</v>
+        <v>4.62</v>
       </c>
       <c r="C110" t="n">
-        <v>1.04</v>
+        <v>4.74</v>
       </c>
       <c r="D110" t="n">
-        <v>1.96</v>
+        <v>2.6</v>
       </c>
       <c r="E110" t="b">
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>1.03</v>
+        <v>4.55</v>
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
-        <v>-0.96</v>
+        <v>-4.01</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>21STCENMGM</t>
+          <t>KEYFINSERV</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>33.64</v>
+        <v>253.45</v>
       </c>
       <c r="C111" t="n">
-        <v>34.3</v>
+        <v>260</v>
       </c>
       <c r="D111" t="n">
-        <v>1.96</v>
+        <v>2.58</v>
       </c>
       <c r="E111" t="b">
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>34.2</v>
+        <v>252</v>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>-0.29</v>
+        <v>-3.08</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>IFCI</t>
+          <t>PRAXIS</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>53.95</v>
+        <v>6.25</v>
       </c>
       <c r="C112" t="n">
-        <v>55</v>
+        <v>6.41</v>
       </c>
       <c r="D112" t="n">
-        <v>1.95</v>
+        <v>2.56</v>
       </c>
       <c r="E112" t="b">
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>56.75</v>
+        <v>6.29</v>
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
-        <v>3.18</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>IZMO</t>
+          <t>COMPINFO</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>734.2</v>
+        <v>1.17</v>
       </c>
       <c r="C113" t="n">
-        <v>748.5</v>
+        <v>1.2</v>
       </c>
       <c r="D113" t="n">
-        <v>1.95</v>
+        <v>2.56</v>
       </c>
       <c r="E113" t="b">
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>723.95</v>
+        <v>1.21</v>
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>-3.28</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MAGNUM</t>
+          <t>SETUINFRA</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>19.57</v>
+        <v>0.39</v>
       </c>
       <c r="C114" t="n">
-        <v>19.95</v>
+        <v>0.4</v>
       </c>
       <c r="D114" t="n">
-        <v>1.94</v>
+        <v>2.56</v>
       </c>
       <c r="E114" t="b">
         <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>19.29</v>
+        <v>0.38</v>
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
-        <v>-3.31</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>GRAVITA</t>
+          <t>ARCHIDPLY</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1503.2</v>
+        <v>73.14</v>
       </c>
       <c r="C115" t="n">
-        <v>1532</v>
+        <v>75</v>
       </c>
       <c r="D115" t="n">
-        <v>1.92</v>
+        <v>2.54</v>
       </c>
       <c r="E115" t="b">
         <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>1454.2</v>
+        <v>71</v>
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>-5.08</v>
+        <v>-5.33</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>AKSHOPTFBR</t>
+          <t>INDTERRAIN</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>4.73</v>
+        <v>28.43</v>
       </c>
       <c r="C116" t="n">
-        <v>4.82</v>
+        <v>29.15</v>
       </c>
       <c r="D116" t="n">
-        <v>1.9</v>
+        <v>2.53</v>
       </c>
       <c r="E116" t="b">
         <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>4.54</v>
+        <v>28.1</v>
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
-        <v>-5.81</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>GOKUL</t>
+          <t>PIGL</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>41.22</v>
+        <v>99.47</v>
       </c>
       <c r="C117" t="n">
-        <v>42</v>
+        <v>101.99</v>
       </c>
       <c r="D117" t="n">
-        <v>1.89</v>
+        <v>2.53</v>
       </c>
       <c r="E117" t="b">
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>41.98</v>
+        <v>97.66</v>
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>-0.05</v>
+        <v>-4.25</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>PASHUPATI</t>
+          <t>ONWARDTEC</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>996.1</v>
+        <v>235.35</v>
       </c>
       <c r="C118" t="n">
-        <v>1014.8</v>
+        <v>241.3</v>
       </c>
       <c r="D118" t="n">
-        <v>1.88</v>
+        <v>2.53</v>
       </c>
       <c r="E118" t="b">
         <v>0</v>
       </c>
       <c r="F118" t="n">
-        <v>994.7</v>
+        <v>227.15</v>
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
-        <v>-1.98</v>
+        <v>-5.86</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>GEEKAYWIRE</t>
+          <t>SOUTHWEST</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>20.89</v>
+        <v>193.06</v>
       </c>
       <c r="C119" t="n">
-        <v>21.28</v>
+        <v>197.9</v>
       </c>
       <c r="D119" t="n">
-        <v>1.87</v>
+        <v>2.51</v>
       </c>
       <c r="E119" t="b">
         <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>20.5</v>
+        <v>191.48</v>
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
-        <v>-3.67</v>
+        <v>-3.24</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>RPPL</t>
+          <t>TICL</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>15.51</v>
+        <v>26.28</v>
       </c>
       <c r="C120" t="n">
-        <v>15.8</v>
+        <v>26.94</v>
       </c>
       <c r="D120" t="n">
-        <v>1.87</v>
+        <v>2.51</v>
       </c>
       <c r="E120" t="b">
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>15.42</v>
+        <v>25.39</v>
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
-        <v>-2.41</v>
+        <v>-5.75</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>HILTON</t>
+          <t>MCLEODRUSS</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>16.78</v>
+        <v>37.07</v>
       </c>
       <c r="C121" t="n">
-        <v>17.09</v>
+        <v>38</v>
       </c>
       <c r="D121" t="n">
-        <v>1.85</v>
+        <v>2.51</v>
       </c>
       <c r="E121" t="b">
         <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>16.79</v>
+        <v>35.62</v>
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
-        <v>-1.76</v>
+        <v>-6.26</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>PVP</t>
+          <t>SMARTLINK</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>24.94</v>
+        <v>118.54</v>
       </c>
       <c r="C122" t="n">
-        <v>25.4</v>
+        <v>121.5</v>
       </c>
       <c r="D122" t="n">
-        <v>1.84</v>
+        <v>2.5</v>
       </c>
       <c r="E122" t="b">
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>23.82</v>
+        <v>119.96</v>
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
-        <v>-6.22</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>VHLTD</t>
+          <t>SJLOGISTIC</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>144.94</v>
+        <v>262.4</v>
       </c>
       <c r="C123" t="n">
-        <v>147.6</v>
+        <v>268.95</v>
       </c>
       <c r="D123" t="n">
-        <v>1.84</v>
+        <v>2.5</v>
       </c>
       <c r="E123" t="b">
         <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>142.8</v>
+        <v>261.6</v>
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>-3.25</v>
+        <v>-2.73</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>HARIOMPIPE</t>
+          <t>RKDL</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>324.15</v>
+        <v>19.31</v>
       </c>
       <c r="C124" t="n">
-        <v>329.95</v>
+        <v>19.79</v>
       </c>
       <c r="D124" t="n">
-        <v>1.79</v>
+        <v>2.49</v>
       </c>
       <c r="E124" t="b">
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>320.95</v>
+        <v>18.5</v>
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
-        <v>-2.73</v>
+        <v>-6.52</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>FLYSBS</t>
+          <t>INDOTHAI</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>401.75</v>
+        <v>250.2</v>
       </c>
       <c r="C125" t="n">
-        <v>408.95</v>
+        <v>256.4</v>
       </c>
       <c r="D125" t="n">
-        <v>1.79</v>
+        <v>2.48</v>
       </c>
       <c r="E125" t="b">
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>395</v>
+        <v>250.15</v>
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>-3.41</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>TEXMOPIPES</t>
+          <t>BALAXI</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>45.49</v>
+        <v>18.65</v>
       </c>
       <c r="C126" t="n">
-        <v>46.3</v>
+        <v>19.11</v>
       </c>
       <c r="D126" t="n">
-        <v>1.78</v>
+        <v>2.47</v>
       </c>
       <c r="E126" t="b">
         <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>44.5</v>
+        <v>17.79</v>
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
-        <v>-3.89</v>
+        <v>-6.91</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>PEARLPOLY</t>
+          <t>FLEXITUFF</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>17.42</v>
+        <v>6.9</v>
       </c>
       <c r="C127" t="n">
-        <v>17.73</v>
+        <v>7.07</v>
       </c>
       <c r="D127" t="n">
-        <v>1.78</v>
+        <v>2.46</v>
       </c>
       <c r="E127" t="b">
         <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>17.45</v>
+        <v>6.99</v>
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
-        <v>-1.58</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>DBEIL</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>71.64</v>
+        <v>6.16</v>
       </c>
       <c r="C128" t="n">
-        <v>72.90000000000001</v>
+        <v>6.31</v>
       </c>
       <c r="D128" t="n">
-        <v>1.76</v>
+        <v>2.44</v>
       </c>
       <c r="E128" t="b">
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>70.55</v>
+        <v>6.29</v>
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
-        <v>-3.22</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>3IINFOLTD</t>
+          <t>ABINFRA</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>13.14</v>
+        <v>16.87</v>
       </c>
       <c r="C129" t="n">
-        <v>13.37</v>
+        <v>17.28</v>
       </c>
       <c r="D129" t="n">
-        <v>1.75</v>
+        <v>2.43</v>
       </c>
       <c r="E129" t="b">
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>13.03</v>
+        <v>16.95</v>
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
-        <v>-2.54</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>NECCLTD</t>
+          <t>BALPHARMA</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>13.76</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="C130" t="n">
-        <v>14</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D130" t="n">
-        <v>1.74</v>
+        <v>2.4</v>
       </c>
       <c r="E130" t="b">
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>13.86</v>
+        <v>67.8</v>
       </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
-        <v>-1</v>
+        <v>-4.37</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>KARMAENG</t>
+          <t>RPEL</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>40.3</v>
+        <v>649.5</v>
       </c>
       <c r="C131" t="n">
-        <v>40.99</v>
+        <v>664.95</v>
       </c>
       <c r="D131" t="n">
-        <v>1.71</v>
+        <v>2.38</v>
       </c>
       <c r="E131" t="b">
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>38.3</v>
+        <v>643.25</v>
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
-        <v>-6.56</v>
+        <v>-3.26</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>RUCHINFRA</t>
+          <t>KRITI</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>5.37</v>
+        <v>81.66</v>
       </c>
       <c r="C132" t="n">
-        <v>5.46</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D132" t="n">
-        <v>1.68</v>
+        <v>2.38</v>
       </c>
       <c r="E132" t="b">
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>5.27</v>
+        <v>79</v>
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
-        <v>-3.48</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>GFLLIMITED</t>
+          <t>SILGO</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>46.15</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="C133" t="n">
-        <v>46.92</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="D133" t="n">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="E133" t="b">
         <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>44.73</v>
+        <v>70.98</v>
       </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
-        <v>-4.67</v>
+        <v>-2.75</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>BIRLAMONEY</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>303.6</v>
+        <v>115.93</v>
       </c>
       <c r="C134" t="n">
-        <v>308.65</v>
+        <v>118.68</v>
       </c>
       <c r="D134" t="n">
-        <v>1.66</v>
+        <v>2.37</v>
       </c>
       <c r="E134" t="b">
         <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>303.6</v>
+        <v>113.46</v>
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
-        <v>-1.64</v>
+        <v>-4.4</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>TIRUPATIFL</t>
+          <t>SADHNANIQ</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>44.07</v>
+        <v>1.69</v>
       </c>
       <c r="C135" t="n">
-        <v>44.8</v>
+        <v>1.73</v>
       </c>
       <c r="D135" t="n">
-        <v>1.66</v>
+        <v>2.37</v>
       </c>
       <c r="E135" t="b">
         <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>44.36</v>
+        <v>1.77</v>
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
-        <v>-0.98</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>HINDOILEXP</t>
+          <t>DPSCLTD</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>147.44</v>
+        <v>8.44</v>
       </c>
       <c r="C136" t="n">
-        <v>149.89</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="D136" t="n">
-        <v>1.66</v>
+        <v>2.37</v>
       </c>
       <c r="E136" t="b">
         <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>143.65</v>
+        <v>8.31</v>
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
-        <v>-4.16</v>
+        <v>-3.82</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ZODIAC</t>
+          <t>TREEHOUSE</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>242.41</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="C137" t="n">
-        <v>246.37</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D137" t="n">
-        <v>1.63</v>
+        <v>2.34</v>
       </c>
       <c r="E137" t="b">
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>238.94</v>
+        <v>8.07</v>
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
-        <v>-3.02</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>SMARTEN</t>
+          <t>GATECHDVR</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>58.3</v>
+        <v>0.43</v>
       </c>
       <c r="C138" t="n">
-        <v>59.25</v>
+        <v>0.44</v>
       </c>
       <c r="D138" t="n">
-        <v>1.63</v>
+        <v>2.33</v>
       </c>
       <c r="E138" t="b">
         <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>57.05</v>
+        <v>0.43</v>
       </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
-        <v>-3.71</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>CEREBRAINT</t>
+          <t>BBTCL</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>4.37</v>
+        <v>170.04</v>
       </c>
       <c r="C139" t="n">
-        <v>4.44</v>
+        <v>174</v>
       </c>
       <c r="D139" t="n">
-        <v>1.6</v>
+        <v>2.33</v>
       </c>
       <c r="E139" t="b">
         <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>4.3</v>
+        <v>165</v>
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
-        <v>-3.15</v>
+        <v>-5.17</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>GLOBALVECT</t>
+          <t>MURUDCERA</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>163.42</v>
+        <v>29.32</v>
       </c>
       <c r="C140" t="n">
-        <v>166</v>
+        <v>30</v>
       </c>
       <c r="D140" t="n">
-        <v>1.58</v>
+        <v>2.32</v>
       </c>
       <c r="E140" t="b">
         <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>160.5</v>
+        <v>29.39</v>
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
-        <v>-3.31</v>
+        <v>-2.03</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ANUP</t>
+          <t>OBSCP</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1556.6</v>
+        <v>293.25</v>
       </c>
       <c r="C141" t="n">
-        <v>1581</v>
+        <v>300</v>
       </c>
       <c r="D141" t="n">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="E141" t="b">
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>1585.4</v>
+        <v>288.75</v>
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
-        <v>0.28</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>SHEKHAWATI</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>12.7</v>
+        <v>146.57</v>
       </c>
       <c r="C142" t="n">
-        <v>12.9</v>
+        <v>149.9</v>
       </c>
       <c r="D142" t="n">
-        <v>1.57</v>
+        <v>2.27</v>
       </c>
       <c r="E142" t="b">
         <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>12.64</v>
+        <v>150.89</v>
       </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
-        <v>-2.02</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>THOMASCOTT</t>
+          <t>INDOTECH</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>257.9</v>
+        <v>1318.8</v>
       </c>
       <c r="C143" t="n">
-        <v>261.85</v>
+        <v>1348.8</v>
       </c>
       <c r="D143" t="n">
-        <v>1.53</v>
+        <v>2.27</v>
       </c>
       <c r="E143" t="b">
         <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>255.05</v>
+        <v>1268.9</v>
       </c>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
-        <v>-2.6</v>
+        <v>-5.92</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ODIGMA</t>
+          <t>KHADIM</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>22.89</v>
+        <v>101.13</v>
       </c>
       <c r="C144" t="n">
-        <v>23.24</v>
+        <v>103.4</v>
       </c>
       <c r="D144" t="n">
-        <v>1.53</v>
+        <v>2.24</v>
       </c>
       <c r="E144" t="b">
         <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>22.31</v>
+        <v>98.5</v>
       </c>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
-        <v>-4</v>
+        <v>-4.74</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>GREENPOWER</t>
+          <t>RSSOFTWARE</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>9.85</v>
+        <v>27.87</v>
       </c>
       <c r="C145" t="n">
-        <v>10</v>
+        <v>28.49</v>
       </c>
       <c r="D145" t="n">
-        <v>1.52</v>
+        <v>2.22</v>
       </c>
       <c r="E145" t="b">
         <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>10.01</v>
+        <v>26.91</v>
       </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
-        <v>0.1</v>
+        <v>-5.55</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>NELCO</t>
+          <t>SUVIDHAA</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>594.35</v>
+        <v>2.7</v>
       </c>
       <c r="C146" t="n">
-        <v>603.3</v>
+        <v>2.76</v>
       </c>
       <c r="D146" t="n">
-        <v>1.51</v>
+        <v>2.22</v>
       </c>
       <c r="E146" t="b">
         <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>581.2</v>
+        <v>2.7</v>
       </c>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
-        <v>-3.66</v>
+        <v>-2.17</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>EXCELSOFT</t>
+          <t>UMIYA-MRO</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>78.45</v>
+        <v>79.75</v>
       </c>
       <c r="C147" t="n">
-        <v>79.63</v>
+        <v>81.5</v>
       </c>
       <c r="D147" t="n">
-        <v>1.5</v>
+        <v>2.19</v>
       </c>
       <c r="E147" t="b">
         <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>79.79000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
-        <v>0.2</v>
+        <v>-5.64</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>WELINV</t>
+          <t>AARTISURF</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>1325.6</v>
+        <v>364.55</v>
       </c>
       <c r="C148" t="n">
-        <v>1345.4</v>
+        <v>372.5</v>
       </c>
       <c r="D148" t="n">
-        <v>1.49</v>
+        <v>2.18</v>
       </c>
       <c r="E148" t="b">
         <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>1339.4</v>
+        <v>354.95</v>
       </c>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
-        <v>-0.45</v>
+        <v>-4.71</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SHYAMCENT</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>4.77</v>
+        <v>110.5</v>
       </c>
       <c r="C149" t="n">
-        <v>4.84</v>
+        <v>112.9</v>
       </c>
       <c r="D149" t="n">
-        <v>1.47</v>
+        <v>2.17</v>
       </c>
       <c r="E149" t="b">
         <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>4.7</v>
+        <v>105</v>
       </c>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
-        <v>-2.89</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>HAPPSTMNDS</t>
+          <t>AVONMORE</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>409.05</v>
+        <v>11.65</v>
       </c>
       <c r="C150" t="n">
-        <v>415</v>
+        <v>11.9</v>
       </c>
       <c r="D150" t="n">
-        <v>1.45</v>
+        <v>2.15</v>
       </c>
       <c r="E150" t="b">
         <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>399.45</v>
+        <v>12.16</v>
       </c>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
-        <v>-3.75</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SEPC</t>
+          <t>UMESLTD</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>6.23</v>
+        <v>6.51</v>
       </c>
       <c r="C151" t="n">
-        <v>6.32</v>
+        <v>6.65</v>
       </c>
       <c r="D151" t="n">
-        <v>1.44</v>
+        <v>2.15</v>
       </c>
       <c r="E151" t="b">
         <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
-        <v>-9.81</v>
+        <v>-3.76</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>STANLEY</t>
+          <t>NAVKARURB</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>158.71</v>
+        <v>0.95</v>
       </c>
       <c r="C152" t="n">
-        <v>160.99</v>
+        <v>0.97</v>
       </c>
       <c r="D152" t="n">
-        <v>1.44</v>
+        <v>2.11</v>
       </c>
       <c r="E152" t="b">
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>153.51</v>
+        <v>0.97</v>
       </c>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="n">
-        <v>-4.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SURANAT&amp;P</t>
+          <t>BGLOBAL</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>17.15</v>
+        <v>2.84</v>
       </c>
       <c r="C153" t="n">
-        <v>17.39</v>
+        <v>2.9</v>
       </c>
       <c r="D153" t="n">
-        <v>1.4</v>
+        <v>2.11</v>
       </c>
       <c r="E153" t="b">
         <v>0</v>
       </c>
-      <c r="F153" t="inlineStr"/>
+      <c r="F153" t="n">
+        <v>2.83</v>
+      </c>
       <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr"/>
+      <c r="H153" t="n">
+        <v>-2.41</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>VIPCLOTHNG</t>
+          <t>LOTUSEYE</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>18.89</v>
+        <v>103.53</v>
       </c>
       <c r="C154" t="n">
-        <v>19.15</v>
+        <v>105.69</v>
       </c>
       <c r="D154" t="n">
-        <v>1.38</v>
+        <v>2.09</v>
       </c>
       <c r="E154" t="b">
         <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>18.53</v>
+        <v>103.5</v>
       </c>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="n">
-        <v>-3.24</v>
+        <v>-2.07</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ALPHAGEO</t>
+          <t>INDIASHLTR</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>196.78</v>
+        <v>689.65</v>
       </c>
       <c r="C155" t="n">
-        <v>199.5</v>
+        <v>704</v>
       </c>
       <c r="D155" t="n">
-        <v>1.38</v>
+        <v>2.08</v>
       </c>
       <c r="E155" t="b">
         <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>192.11</v>
+        <v>697.8</v>
       </c>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="n">
-        <v>-3.7</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>INDOTECH</t>
+          <t>GOPAL</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>1375.4</v>
+        <v>269.4</v>
       </c>
       <c r="C156" t="n">
-        <v>1394.2</v>
+        <v>275</v>
       </c>
       <c r="D156" t="n">
-        <v>1.37</v>
+        <v>2.08</v>
       </c>
       <c r="E156" t="b">
         <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>1330</v>
+        <v>268.05</v>
       </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="n">
-        <v>-4.6</v>
+        <v>-2.53</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>NAHARSPING</t>
+          <t>GFLLIMITED</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>194.95</v>
+        <v>43.99</v>
       </c>
       <c r="C157" t="n">
-        <v>197.6</v>
+        <v>44.9</v>
       </c>
       <c r="D157" t="n">
-        <v>1.36</v>
+        <v>2.07</v>
       </c>
       <c r="E157" t="b">
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>190</v>
+        <v>42.7</v>
       </c>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="n">
-        <v>-3.85</v>
+        <v>-4.9</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>SHREYANIND</t>
+          <t>INA</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>148.89</v>
+        <v>95.23</v>
       </c>
       <c r="C158" t="n">
-        <v>150.9</v>
+        <v>97.2</v>
       </c>
       <c r="D158" t="n">
-        <v>1.35</v>
+        <v>2.07</v>
       </c>
       <c r="E158" t="b">
         <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>150.7</v>
+        <v>94.27</v>
       </c>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="n">
-        <v>-0.13</v>
+        <v>-3.01</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>EUREKAFORB</t>
+          <t>PARSVNATH</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>445.2</v>
+        <v>6.76</v>
       </c>
       <c r="C159" t="n">
-        <v>451.15</v>
+        <v>6.9</v>
       </c>
       <c r="D159" t="n">
-        <v>1.34</v>
+        <v>2.07</v>
       </c>
       <c r="E159" t="b">
         <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>442.6</v>
+        <v>6.56</v>
       </c>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="n">
-        <v>-1.9</v>
+        <v>-4.93</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>TARACHAND</t>
+          <t>BTML</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>60.2</v>
+        <v>7.27</v>
       </c>
       <c r="C160" t="n">
-        <v>61</v>
+        <v>7.42</v>
       </c>
       <c r="D160" t="n">
-        <v>1.33</v>
+        <v>2.06</v>
       </c>
       <c r="E160" t="b">
         <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>59.65</v>
+        <v>6.77</v>
       </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="n">
-        <v>-2.21</v>
+        <v>-8.76</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>IGCL</t>
+          <t>MAHEPC</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>63.66</v>
+        <v>112.01</v>
       </c>
       <c r="C161" t="n">
-        <v>64.5</v>
+        <v>114.3</v>
       </c>
       <c r="D161" t="n">
-        <v>1.32</v>
+        <v>2.04</v>
       </c>
       <c r="E161" t="b">
         <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>62.38</v>
+        <v>108.95</v>
       </c>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="n">
-        <v>-3.29</v>
+        <v>-4.68</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>AIRAN</t>
+          <t>SUPREMEENG</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>16.03</v>
+        <v>0.98</v>
       </c>
       <c r="C162" t="n">
-        <v>16.24</v>
+        <v>1</v>
       </c>
       <c r="D162" t="n">
-        <v>1.31</v>
+        <v>2.04</v>
       </c>
       <c r="E162" t="b">
         <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>15.87</v>
+        <v>0.99</v>
       </c>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="n">
-        <v>-2.28</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>GENUSPAPER</t>
+          <t>WSI</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>11.77</v>
+        <v>63.69</v>
       </c>
       <c r="C163" t="n">
-        <v>11.92</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="D163" t="n">
-        <v>1.27</v>
+        <v>2.04</v>
       </c>
       <c r="E163" t="b">
         <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>11.82</v>
+        <v>61.46</v>
       </c>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="n">
-        <v>-0.84</v>
+        <v>-5.43</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ALLCARGO</t>
+          <t>FCSSOFT</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>7.9</v>
+        <v>1.48</v>
       </c>
       <c r="C164" t="n">
-        <v>8</v>
+        <v>1.51</v>
       </c>
       <c r="D164" t="n">
-        <v>1.27</v>
+        <v>2.03</v>
       </c>
       <c r="E164" t="b">
         <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>7.77</v>
+        <v>1.44</v>
       </c>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="n">
-        <v>-2.88</v>
+        <v>-4.64</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>SRD</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>149.11</v>
+        <v>51.16</v>
       </c>
       <c r="C165" t="n">
-        <v>151</v>
+        <v>52.2</v>
       </c>
       <c r="D165" t="n">
-        <v>1.27</v>
+        <v>2.03</v>
       </c>
       <c r="E165" t="b">
         <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>149.64</v>
+        <v>49.35</v>
       </c>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="n">
-        <v>-0.9</v>
+        <v>-5.46</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>VISHWARAJ</t>
+          <t>DMCC</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>5.56</v>
+        <v>211.74</v>
       </c>
       <c r="C166" t="n">
-        <v>5.63</v>
+        <v>216</v>
       </c>
       <c r="D166" t="n">
-        <v>1.26</v>
+        <v>2.01</v>
       </c>
       <c r="E166" t="b">
         <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>5.42</v>
+        <v>214.24</v>
       </c>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="n">
-        <v>-3.73</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>KRITINUT</t>
+          <t>SIKKO</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>64.13</v>
+        <v>4.5</v>
       </c>
       <c r="C167" t="n">
-        <v>64.94</v>
+        <v>4.59</v>
       </c>
       <c r="D167" t="n">
-        <v>1.26</v>
+        <v>2</v>
       </c>
       <c r="E167" t="b">
         <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>63.94</v>
+        <v>4.37</v>
       </c>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="n">
-        <v>-1.54</v>
+        <v>-4.79</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SAKUMA</t>
+          <t>DEEDEV</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>1.6</v>
+        <v>297.3</v>
       </c>
       <c r="C168" t="n">
-        <v>1.62</v>
+        <v>303.25</v>
       </c>
       <c r="D168" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="E168" t="b">
         <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>1.6</v>
+        <v>290</v>
       </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="n">
-        <v>-1.23</v>
+        <v>-4.37</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>VARDHACRLC</t>
+          <t>VISASTEEL</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>33.87</v>
+        <v>34.19</v>
       </c>
       <c r="C169" t="n">
-        <v>34.29</v>
+        <v>34.87</v>
       </c>
       <c r="D169" t="n">
-        <v>1.24</v>
+        <v>1.99</v>
       </c>
       <c r="E169" t="b">
         <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>34.17</v>
+        <v>34</v>
       </c>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="n">
-        <v>-0.35</v>
+        <v>-2.49</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>HTMEDIA</t>
+          <t>ORIENTCER</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>21.34</v>
+        <v>35.66</v>
       </c>
       <c r="C170" t="n">
-        <v>21.6</v>
+        <v>36.37</v>
       </c>
       <c r="D170" t="n">
-        <v>1.22</v>
+        <v>1.99</v>
       </c>
       <c r="E170" t="b">
         <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>21</v>
+        <v>35.18</v>
       </c>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="n">
-        <v>-2.78</v>
+        <v>-3.27</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ACMESOLAR</t>
+          <t>MODTHREAD</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>240.08</v>
+        <v>53.33</v>
       </c>
       <c r="C171" t="n">
-        <v>243</v>
+        <v>54.39</v>
       </c>
       <c r="D171" t="n">
-        <v>1.22</v>
+        <v>1.99</v>
       </c>
       <c r="E171" t="b">
         <v>0</v>
       </c>
       <c r="F171" t="n">
-        <v>257.82</v>
+        <v>49</v>
       </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="n">
-        <v>6.1</v>
+        <v>-9.91</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>JAGSNPHARM</t>
+          <t>PAVNAIND</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>189.61</v>
+        <v>18.1</v>
       </c>
       <c r="C172" t="n">
-        <v>191.9</v>
+        <v>18.46</v>
       </c>
       <c r="D172" t="n">
-        <v>1.21</v>
+        <v>1.99</v>
       </c>
       <c r="E172" t="b">
         <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>190.29</v>
+        <v>17.95</v>
       </c>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="n">
-        <v>-0.84</v>
+        <v>-2.76</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>CHOICEIN</t>
+          <t>CMNL</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>645.25</v>
+        <v>98</v>
       </c>
       <c r="C173" t="n">
-        <v>653</v>
+        <v>99.95</v>
       </c>
       <c r="D173" t="n">
-        <v>1.2</v>
+        <v>1.99</v>
       </c>
       <c r="E173" t="b">
         <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>638.4</v>
+        <v>95</v>
       </c>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="n">
-        <v>-2.24</v>
+        <v>-4.95</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>MAHSCOOTER</t>
+          <t>OSWALSEEDS</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>12816</v>
+        <v>11.76</v>
       </c>
       <c r="C174" t="n">
-        <v>12970</v>
+        <v>11.99</v>
       </c>
       <c r="D174" t="n">
-        <v>1.2</v>
+        <v>1.96</v>
       </c>
       <c r="E174" t="b">
         <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>12737</v>
+        <v>11.42</v>
       </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="n">
-        <v>-1.8</v>
+        <v>-4.75</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>NDL</t>
+          <t>ESAFSFB</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>2.49</v>
+        <v>24.22</v>
       </c>
       <c r="C175" t="n">
-        <v>2.52</v>
+        <v>24.69</v>
       </c>
       <c r="D175" t="n">
-        <v>1.2</v>
+        <v>1.94</v>
       </c>
       <c r="E175" t="b">
         <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>2.44</v>
+        <v>23.81</v>
       </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="n">
-        <v>-3.17</v>
+        <v>-3.56</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>STEELCITY</t>
+          <t>STYL</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>82.02</v>
+        <v>250.08</v>
       </c>
       <c r="C176" t="n">
-        <v>82.98999999999999</v>
+        <v>254.9</v>
       </c>
       <c r="D176" t="n">
-        <v>1.18</v>
+        <v>1.93</v>
       </c>
       <c r="E176" t="b">
         <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>81.43000000000001</v>
+        <v>250.8</v>
       </c>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="n">
-        <v>-1.88</v>
+        <v>-1.61</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>TARC</t>
+          <t>NATHBIOGEN</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>131.36</v>
+        <v>142.28</v>
       </c>
       <c r="C177" t="n">
-        <v>132.9</v>
+        <v>145</v>
       </c>
       <c r="D177" t="n">
-        <v>1.17</v>
+        <v>1.91</v>
       </c>
       <c r="E177" t="b">
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>129.73</v>
+        <v>139.06</v>
       </c>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="n">
-        <v>-2.39</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>FLAIR</t>
+          <t>KAPSTON</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>298.2</v>
+        <v>270.35</v>
       </c>
       <c r="C178" t="n">
-        <v>301.7</v>
+        <v>275.5</v>
       </c>
       <c r="D178" t="n">
-        <v>1.17</v>
+        <v>1.9</v>
       </c>
       <c r="E178" t="b">
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>293.45</v>
+        <v>272</v>
       </c>
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="n">
-        <v>-2.73</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>INTLCONV</t>
+          <t>SAKUMA</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>75.27</v>
+        <v>1.58</v>
       </c>
       <c r="C179" t="n">
-        <v>76.14</v>
+        <v>1.61</v>
       </c>
       <c r="D179" t="n">
-        <v>1.16</v>
+        <v>1.9</v>
       </c>
       <c r="E179" t="b">
         <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>74.95999999999999</v>
+        <v>1.55</v>
       </c>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="n">
-        <v>-1.55</v>
+        <v>-3.73</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SEJALLTD</t>
+          <t>SVPGLOB</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>538.75</v>
+        <v>2.65</v>
       </c>
       <c r="C180" t="n">
-        <v>544.95</v>
+        <v>2.7</v>
       </c>
       <c r="D180" t="n">
-        <v>1.15</v>
+        <v>1.89</v>
       </c>
       <c r="E180" t="b">
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>525.15</v>
+        <v>2.65</v>
       </c>
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="n">
-        <v>-3.63</v>
+        <v>-1.85</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>BHARATCOAL</t>
+          <t>NTPCGREEN</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>35.81</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="C181" t="n">
-        <v>36.22</v>
+        <v>100</v>
       </c>
       <c r="D181" t="n">
-        <v>1.14</v>
+        <v>1.88</v>
       </c>
       <c r="E181" t="b">
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>36.08</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="n">
-        <v>-0.39</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>EXCEL</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>1911.4</v>
+        <v>1.07</v>
       </c>
       <c r="C182" t="n">
-        <v>1933</v>
+        <v>1.09</v>
       </c>
       <c r="D182" t="n">
-        <v>1.13</v>
+        <v>1.87</v>
       </c>
       <c r="E182" t="b">
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>1917.5</v>
+        <v>1.03</v>
       </c>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="n">
-        <v>-0.8</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>RUSHIL</t>
+          <t>NAHARINDUS</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>16.21</v>
+        <v>88.84</v>
       </c>
       <c r="C183" t="n">
-        <v>16.39</v>
+        <v>90.5</v>
       </c>
       <c r="D183" t="n">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="E183" t="b">
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>15.75</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="n">
-        <v>-3.9</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ALKALI</t>
+          <t>MONEYBOXX</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>60.33</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="C184" t="n">
-        <v>61</v>
+        <v>65.69</v>
       </c>
       <c r="D184" t="n">
-        <v>1.11</v>
+        <v>1.86</v>
       </c>
       <c r="E184" t="b">
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>57.05</v>
+        <v>63.29</v>
       </c>
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="n">
-        <v>-6.48</v>
+        <v>-3.65</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>CROWN</t>
+          <t>TEXMOPIPES</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>118.79</v>
+        <v>42.95</v>
       </c>
       <c r="C185" t="n">
-        <v>120.1</v>
+        <v>43.75</v>
       </c>
       <c r="D185" t="n">
-        <v>1.1</v>
+        <v>1.86</v>
       </c>
       <c r="E185" t="b">
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>119.55</v>
+        <v>41.97</v>
       </c>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="n">
-        <v>-0.46</v>
+        <v>-4.07</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>PLAZACABLE</t>
+          <t>NILAINFRA</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>35.61</v>
+        <v>7.12</v>
       </c>
       <c r="C186" t="n">
-        <v>36</v>
+        <v>7.25</v>
       </c>
       <c r="D186" t="n">
-        <v>1.1</v>
+        <v>1.83</v>
       </c>
       <c r="E186" t="b">
         <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>35.98</v>
+        <v>6.86</v>
       </c>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="n">
-        <v>-0.06</v>
+        <v>-5.38</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>BASILIC</t>
+          <t>DTIL</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>206.45</v>
+        <v>127.66</v>
       </c>
       <c r="C187" t="n">
-        <v>208.7</v>
+        <v>130</v>
       </c>
       <c r="D187" t="n">
-        <v>1.09</v>
+        <v>1.83</v>
       </c>
       <c r="E187" t="b">
         <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>202.35</v>
+        <v>127</v>
       </c>
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="n">
-        <v>-3.04</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SEDEMAC</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>1441.3</v>
+        <v>304.45</v>
       </c>
       <c r="C188" t="n">
-        <v>1457</v>
+        <v>310</v>
       </c>
       <c r="D188" t="n">
-        <v>1.09</v>
+        <v>1.82</v>
       </c>
       <c r="E188" t="b">
         <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>1464</v>
+        <v>298.1</v>
       </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="n">
-        <v>0.48</v>
+        <v>-3.84</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>SYSTMTXC</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>200.84</v>
+        <v>63.69</v>
       </c>
       <c r="C189" t="n">
-        <v>203</v>
+        <v>64.84</v>
       </c>
       <c r="D189" t="n">
-        <v>1.08</v>
+        <v>1.81</v>
       </c>
       <c r="E189" t="b">
         <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>185.76</v>
+        <v>62.03</v>
       </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="n">
-        <v>-8.49</v>
+        <v>-4.33</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>MUKANDLTD</t>
+          <t>KNAGRI</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>120.72</v>
+        <v>178.8</v>
       </c>
       <c r="C190" t="n">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="D190" t="n">
-        <v>1.06</v>
+        <v>1.79</v>
       </c>
       <c r="E190" t="b">
         <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>120.98</v>
+        <v>175.66</v>
       </c>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="n">
-        <v>-0.84</v>
+        <v>-3.48</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ORIENTCER</t>
+          <t>ORIENTELEC</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>38.05</v>
+        <v>169.8</v>
       </c>
       <c r="C191" t="n">
-        <v>38.45</v>
+        <v>172.78</v>
       </c>
       <c r="D191" t="n">
-        <v>1.05</v>
+        <v>1.76</v>
       </c>
       <c r="E191" t="b">
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>37.02</v>
+        <v>167.32</v>
       </c>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="n">
-        <v>-3.72</v>
+        <v>-3.16</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>DANGEE</t>
+          <t>VHLTD</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>2.86</v>
+        <v>139.56</v>
       </c>
       <c r="C192" t="n">
-        <v>2.89</v>
+        <v>142</v>
       </c>
       <c r="D192" t="n">
-        <v>1.05</v>
+        <v>1.75</v>
       </c>
       <c r="E192" t="b">
         <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>2.88</v>
+        <v>139.9</v>
       </c>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="n">
-        <v>-0.35</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SHAH</t>
+          <t>COASTCORP</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>4.82</v>
+        <v>43.64</v>
       </c>
       <c r="C193" t="n">
-        <v>4.87</v>
+        <v>44.4</v>
       </c>
       <c r="D193" t="n">
-        <v>1.04</v>
+        <v>1.74</v>
       </c>
       <c r="E193" t="b">
         <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>4.83</v>
+        <v>44.98</v>
       </c>
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="n">
-        <v>-0.82</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>DPSCLTD</t>
+          <t>SCHAND</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>8.66</v>
+        <v>146.49</v>
       </c>
       <c r="C194" t="n">
-        <v>8.75</v>
+        <v>148.99</v>
       </c>
       <c r="D194" t="n">
-        <v>1.04</v>
+        <v>1.71</v>
       </c>
       <c r="E194" t="b">
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>8.609999999999999</v>
+        <v>140.83</v>
       </c>
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="n">
-        <v>-1.6</v>
+        <v>-5.48</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ZENITHEXPO</t>
+          <t>AEQUS</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>193.2</v>
+        <v>116.8</v>
       </c>
       <c r="C195" t="n">
-        <v>195.2</v>
+        <v>118.8</v>
       </c>
       <c r="D195" t="n">
-        <v>1.04</v>
+        <v>1.71</v>
       </c>
       <c r="E195" t="b">
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>196</v>
+        <v>114.53</v>
       </c>
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="n">
-        <v>0.41</v>
+        <v>-3.59</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SPCENET</t>
+          <t>SHAH</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>3.9</v>
+        <v>4.72</v>
       </c>
       <c r="C196" t="n">
-        <v>3.94</v>
+        <v>4.8</v>
       </c>
       <c r="D196" t="n">
-        <v>1.03</v>
+        <v>1.69</v>
       </c>
       <c r="E196" t="b">
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>3.77</v>
+        <v>4.73</v>
       </c>
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="n">
-        <v>-4.31</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>KAPSTON</t>
+          <t>NILASPACES</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>277.15</v>
+        <v>13.07</v>
       </c>
       <c r="C197" t="n">
-        <v>280</v>
+        <v>13.29</v>
       </c>
       <c r="D197" t="n">
-        <v>1.03</v>
+        <v>1.68</v>
       </c>
       <c r="E197" t="b">
         <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>276.85</v>
+        <v>13.04</v>
       </c>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="n">
-        <v>-1.12</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>MAHICKRA</t>
+          <t>PASHUPATI</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>206</v>
+        <v>988.45</v>
       </c>
       <c r="C198" t="n">
-        <v>208.1</v>
+        <v>1005</v>
       </c>
       <c r="D198" t="n">
-        <v>1.02</v>
+        <v>1.67</v>
       </c>
       <c r="E198" t="b">
         <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>208.1</v>
+        <v>988.35</v>
       </c>
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="n">
-        <v>0</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>JISLJALEQS</t>
+          <t>SEDEMAC</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>34.38</v>
+        <v>1465.5</v>
       </c>
       <c r="C199" t="n">
-        <v>34.73</v>
+        <v>1490</v>
       </c>
       <c r="D199" t="n">
-        <v>1.02</v>
+        <v>1.67</v>
       </c>
       <c r="E199" t="b">
         <v>0</v>
       </c>
       <c r="F199" t="n">
-        <v>32.98</v>
+        <v>1456.5</v>
       </c>
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="n">
-        <v>-5.04</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>KOKUYOCMLN</t>
+          <t>ALANKIT</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>78.11</v>
+        <v>7.85</v>
       </c>
       <c r="C200" t="n">
-        <v>78.90000000000001</v>
+        <v>7.98</v>
       </c>
       <c r="D200" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="E200" t="b">
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>77.3</v>
+        <v>7.7</v>
       </c>
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="n">
-        <v>-2.03</v>
+        <v>-3.51</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>DAMCAPITAL</t>
+          <t>WINSOME</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>131.12</v>
+        <v>1.81</v>
       </c>
       <c r="C201" t="n">
-        <v>132.43</v>
+        <v>1.84</v>
       </c>
       <c r="D201" t="n">
-        <v>1</v>
+        <v>1.66</v>
       </c>
       <c r="E201" t="b">
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>127.71</v>
+        <v>1.78</v>
       </c>
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="n">
-        <v>-3.56</v>
+        <v>-3.26</v>
       </c>
     </row>
   </sheetData>

--- a/data/trending_momentum_stocks.xlsx
+++ b/data/trending_momentum_stocks.xlsx
@@ -461,1548 +461,1548 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BHANDA-RE2</t>
+          <t>RADAAN</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02</v>
+        <v>2.71</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03</v>
+        <v>3.03</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>11.81</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02</v>
+        <v>2.81</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>-33.33</v>
+        <v>-7.26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CREATIVEYE</t>
+          <t>RAJMET</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.65</v>
+        <v>3.44</v>
       </c>
       <c r="C3" t="n">
-        <v>7.89</v>
+        <v>3.79</v>
       </c>
       <c r="D3" t="n">
-        <v>18.65</v>
+        <v>10.17</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>6.88</v>
+        <v>3.57</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>-12.8</v>
+        <v>-5.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>UMAEXPORTS</t>
+          <t>CCHHL</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24.28</v>
+        <v>11.74</v>
       </c>
       <c r="C4" t="n">
-        <v>28.79</v>
+        <v>12.8</v>
       </c>
       <c r="D4" t="n">
-        <v>18.57</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>25.35</v>
+        <v>11.75</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>-11.95</v>
+        <v>-8.199999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CENTRUM</t>
+          <t>PRITI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.84</v>
+        <v>34.26</v>
       </c>
       <c r="C5" t="n">
-        <v>27</v>
+        <v>37.35</v>
       </c>
       <c r="D5" t="n">
-        <v>18.21</v>
+        <v>9.02</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>23.25</v>
+        <v>36.99</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>-13.89</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ICDSLTD</t>
+          <t>RADIOCITY</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>54.44</v>
+        <v>5.48</v>
       </c>
       <c r="C6" t="n">
-        <v>59.88</v>
+        <v>5.96</v>
       </c>
       <c r="D6" t="n">
-        <v>9.99</v>
+        <v>8.76</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>51.98</v>
+        <v>5.47</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>-13.19</v>
+        <v>-8.220000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>SPCENET</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.19</v>
+        <v>3.86</v>
       </c>
       <c r="C7" t="n">
-        <v>6.8</v>
+        <v>4.19</v>
       </c>
       <c r="D7" t="n">
-        <v>9.85</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>6.09</v>
+        <v>4.24</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>-10.44</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DCMFINSERV</t>
+          <t>MITTAL</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.41</v>
+        <v>0.71</v>
       </c>
       <c r="C8" t="n">
-        <v>8.09</v>
+        <v>0.77</v>
       </c>
       <c r="D8" t="n">
-        <v>9.18</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>8.15</v>
+        <v>0.85</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>0.74</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SUPREME</t>
+          <t>MODTHREAD</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50.55</v>
+        <v>48.01</v>
       </c>
       <c r="C9" t="n">
-        <v>54.8</v>
+        <v>51.99</v>
       </c>
       <c r="D9" t="n">
-        <v>8.41</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>49.32</v>
+        <v>50.49</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>-10</v>
+        <v>-2.89</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AKI</t>
+          <t>SHREYANIND</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.36</v>
+        <v>138.53</v>
       </c>
       <c r="C10" t="n">
-        <v>4.7</v>
+        <v>149.85</v>
       </c>
       <c r="D10" t="n">
-        <v>7.8</v>
+        <v>8.17</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>4.95</v>
+        <v>139.48</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>5.32</v>
+        <v>-6.92</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SECURKLOUD</t>
+          <t>SPLIL</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.08</v>
+        <v>24.33</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7</v>
+        <v>26.3</v>
       </c>
       <c r="D11" t="n">
-        <v>7.69</v>
+        <v>8.1</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>21.03</v>
+        <v>24.87</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>-7.36</v>
+        <v>-5.44</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TOUCHWOOD</t>
+          <t>SHEKHAWATI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>72.63</v>
+        <v>11.98</v>
       </c>
       <c r="C12" t="n">
-        <v>77.98999999999999</v>
+        <v>12.9</v>
       </c>
       <c r="D12" t="n">
-        <v>7.38</v>
+        <v>7.68</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>71.01000000000001</v>
+        <v>12.59</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>-8.949999999999999</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SHANTI</t>
+          <t>AMNPLST</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6.52</v>
+        <v>147.81</v>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>159</v>
       </c>
       <c r="D13" t="n">
-        <v>7.36</v>
+        <v>7.57</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>6.41</v>
+        <v>152.5</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>-8.43</v>
+        <v>-4.09</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BAJEL</t>
+          <t>SHANTI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>139.96</v>
+        <v>6.42</v>
       </c>
       <c r="C14" t="n">
-        <v>149.9</v>
+        <v>6.9</v>
       </c>
       <c r="D14" t="n">
-        <v>7.1</v>
+        <v>7.48</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>151.79</v>
+        <v>6.49</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>1.26</v>
+        <v>-5.94</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MKPL</t>
+          <t>SIGIND</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.73</v>
+        <v>44.24</v>
       </c>
       <c r="C15" t="n">
-        <v>5.05</v>
+        <v>47.5</v>
       </c>
       <c r="D15" t="n">
-        <v>6.77</v>
+        <v>7.37</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>5.02</v>
+        <v>44.5</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>-0.59</v>
+        <v>-6.32</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ALKALI</t>
+          <t>DPEL</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>57.19</v>
+        <v>326.7</v>
       </c>
       <c r="C16" t="n">
-        <v>60.99</v>
+        <v>349.95</v>
       </c>
       <c r="D16" t="n">
-        <v>6.64</v>
+        <v>7.12</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>59.48</v>
+        <v>359.35</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>-2.48</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>COMPUSOFT</t>
+          <t>PNC</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15.2</v>
+        <v>20.12</v>
       </c>
       <c r="C17" t="n">
-        <v>16.2</v>
+        <v>21.4</v>
       </c>
       <c r="D17" t="n">
-        <v>6.58</v>
+        <v>6.36</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>14.27</v>
+        <v>20.01</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>-11.91</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HCG-RE</t>
+          <t>PRIMO</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>28.2</v>
+        <v>17.96</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>19.1</v>
       </c>
       <c r="D18" t="n">
-        <v>6.38</v>
+        <v>6.35</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>22.35</v>
+        <v>18.2</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>-25.5</v>
+        <v>-4.71</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GSS</t>
+          <t>DIGIKORE</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>11.86</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>12.6</v>
+        <v>86.45</v>
       </c>
       <c r="D19" t="n">
-        <v>6.24</v>
+        <v>6.27</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>11.36</v>
+        <v>84.95</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>-9.84</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SAHYADRI</t>
+          <t>WELINV</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>221.3</v>
+        <v>1308.5</v>
       </c>
       <c r="C20" t="n">
-        <v>235</v>
+        <v>1390</v>
       </c>
       <c r="D20" t="n">
-        <v>6.19</v>
+        <v>6.23</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>221.2</v>
+        <v>1280.4</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>-5.87</v>
+        <v>-7.88</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LEMERITE</t>
+          <t>SUPERSPIN</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>439.6</v>
+        <v>4.23</v>
       </c>
       <c r="C21" t="n">
-        <v>466</v>
+        <v>4.49</v>
       </c>
       <c r="D21" t="n">
-        <v>6.01</v>
+        <v>6.15</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>442</v>
+        <v>4.12</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>-5.15</v>
+        <v>-8.24</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SUMIT</t>
+          <t>MKPL</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>38.51</v>
+        <v>5.01</v>
       </c>
       <c r="C22" t="n">
-        <v>40.82</v>
+        <v>5.3</v>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>5.79</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>37.33</v>
+        <v>5.07</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>-8.550000000000001</v>
+        <v>-4.34</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TFL</t>
+          <t>ITI</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>12.33</v>
+        <v>277.15</v>
       </c>
       <c r="C23" t="n">
-        <v>13.06</v>
+        <v>293.15</v>
       </c>
       <c r="D23" t="n">
-        <v>5.92</v>
+        <v>5.77</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>12.16</v>
+        <v>282.05</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>-6.89</v>
+        <v>-3.79</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ADROITINFO</t>
+          <t>TOKYOPLAST</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9.42</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="C24" t="n">
-        <v>9.960000000000001</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>5.73</v>
+        <v>5.64</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>9.119999999999999</v>
+        <v>72</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>-8.43</v>
+        <v>-2.69</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AEPL</t>
+          <t>SUTLEJTEX</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>17.54</v>
+        <v>29.36</v>
       </c>
       <c r="C25" t="n">
-        <v>18.54</v>
+        <v>31</v>
       </c>
       <c r="D25" t="n">
-        <v>5.7</v>
+        <v>5.59</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>17.61</v>
+        <v>30.05</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>-5.02</v>
+        <v>-3.06</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ODIGMA</t>
+          <t>COASTCORP</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>22.48</v>
+        <v>45.94</v>
       </c>
       <c r="C26" t="n">
-        <v>23.74</v>
+        <v>48.5</v>
       </c>
       <c r="D26" t="n">
-        <v>5.6</v>
+        <v>5.57</v>
       </c>
       <c r="E26" t="b">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>22.01</v>
+        <v>46.24</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>-7.29</v>
+        <v>-4.66</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LAMBODHARA</t>
+          <t>CPEDU</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>94.72</v>
+        <v>167.67</v>
       </c>
       <c r="C27" t="n">
-        <v>100</v>
+        <v>176.9</v>
       </c>
       <c r="D27" t="n">
-        <v>5.57</v>
+        <v>5.5</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>93.98999999999999</v>
+        <v>171.32</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>-6.01</v>
+        <v>-3.15</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FILATFASH</t>
+          <t>SUPREME</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.18</v>
+        <v>52.76</v>
       </c>
       <c r="C28" t="n">
-        <v>0.19</v>
+        <v>55.6</v>
       </c>
       <c r="D28" t="n">
-        <v>5.56</v>
+        <v>5.38</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.19</v>
+        <v>51.65</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>-7.1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CPCAP</t>
+          <t>SEMAC</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>84.31999999999999</v>
+        <v>236.27</v>
       </c>
       <c r="C29" t="n">
-        <v>88.89</v>
+        <v>248.96</v>
       </c>
       <c r="D29" t="n">
-        <v>5.42</v>
+        <v>5.37</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>83.05</v>
+        <v>240</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>-6.57</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>KEEPLEARN</t>
+          <t>MUNJALSHOW</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.87</v>
+        <v>119.7</v>
       </c>
       <c r="C30" t="n">
-        <v>1.97</v>
+        <v>125.8</v>
       </c>
       <c r="D30" t="n">
-        <v>5.35</v>
+        <v>5.1</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>1.91</v>
+        <v>119.81</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>-3.05</v>
+        <v>-4.76</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>URBAN</t>
+          <t>JETFREIGHT</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>125.25</v>
+        <v>17.99</v>
       </c>
       <c r="C31" t="n">
-        <v>131.95</v>
+        <v>18.9</v>
       </c>
       <c r="D31" t="n">
-        <v>5.35</v>
+        <v>5.06</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>125.5</v>
+        <v>18.48</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>-4.89</v>
+        <v>-2.22</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SUPERHOUSE</t>
+          <t>SETUINFRA</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>142.58</v>
+        <v>0.4</v>
       </c>
       <c r="C32" t="n">
-        <v>149.9</v>
+        <v>0.42</v>
       </c>
       <c r="D32" t="n">
-        <v>5.13</v>
+        <v>5</v>
       </c>
       <c r="E32" t="b">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>141.11</v>
+        <v>0.41</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>-5.86</v>
+        <v>-2.38</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MACPOWER</t>
+          <t>GJL</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>903.05</v>
+        <v>238.9</v>
       </c>
       <c r="C33" t="n">
-        <v>948.8</v>
+        <v>250.8</v>
       </c>
       <c r="D33" t="n">
-        <v>5.07</v>
+        <v>4.98</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>881.25</v>
+        <v>250.8</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>-7.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GAYAPROJ</t>
+          <t>POWERMECH</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>12.7</v>
+        <v>1876.5</v>
       </c>
       <c r="C34" t="n">
-        <v>13.33</v>
+        <v>1969.9</v>
       </c>
       <c r="D34" t="n">
-        <v>4.96</v>
+        <v>4.98</v>
       </c>
       <c r="E34" t="b">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>13.33</v>
+        <v>1930</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>-2.03</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RCOM</t>
+          <t>TCIFINANCE</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.01</v>
+        <v>13.55</v>
       </c>
       <c r="C35" t="n">
-        <v>1.06</v>
+        <v>14.22</v>
       </c>
       <c r="D35" t="n">
-        <v>4.95</v>
+        <v>4.94</v>
       </c>
       <c r="E35" t="b">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0.96</v>
+        <v>13.3</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>-9.43</v>
+        <v>-6.47</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>VIVIDHA</t>
+          <t>BAFNAPH</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.61</v>
+        <v>104.11</v>
       </c>
       <c r="C36" t="n">
-        <v>0.64</v>
+        <v>109.25</v>
       </c>
       <c r="D36" t="n">
-        <v>4.92</v>
+        <v>4.94</v>
       </c>
       <c r="E36" t="b">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6</v>
+        <v>109.31</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>-6.25</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ONELIFECAP</t>
+          <t>OILCOUNTUB</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>15.14</v>
+        <v>36.97</v>
       </c>
       <c r="C37" t="n">
-        <v>15.88</v>
+        <v>38.79</v>
       </c>
       <c r="D37" t="n">
-        <v>4.89</v>
+        <v>4.92</v>
       </c>
       <c r="E37" t="b">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>15.4</v>
+        <v>44.36</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>-3.02</v>
+        <v>14.36</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LIBERTSHOE</t>
+          <t>VISHWARAJ</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>262.47</v>
+        <v>5.08</v>
       </c>
       <c r="C38" t="n">
-        <v>275</v>
+        <v>5.33</v>
       </c>
       <c r="D38" t="n">
-        <v>4.77</v>
+        <v>4.92</v>
       </c>
       <c r="E38" t="b">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>263.06</v>
+        <v>5.21</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>-4.34</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DHRUV</t>
+          <t>SIGMA</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>29.88</v>
+        <v>40.03</v>
       </c>
       <c r="C39" t="n">
-        <v>31.3</v>
+        <v>41.98</v>
       </c>
       <c r="D39" t="n">
-        <v>4.75</v>
+        <v>4.87</v>
       </c>
       <c r="E39" t="b">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>29.92</v>
+        <v>40.01</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>-4.41</v>
+        <v>-4.69</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>EQUIPPP</t>
+          <t>VIJIFIN</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>16.48</v>
+        <v>2.89</v>
       </c>
       <c r="C40" t="n">
-        <v>17.26</v>
+        <v>3.03</v>
       </c>
       <c r="D40" t="n">
-        <v>4.73</v>
+        <v>4.84</v>
       </c>
       <c r="E40" t="b">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>17.3</v>
+        <v>3.03</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>VIJIFIN</t>
+          <t>DCMFINSERV</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.76</v>
+        <v>8.15</v>
       </c>
       <c r="C41" t="n">
-        <v>2.89</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>4.71</v>
+        <v>4.79</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>2.89</v>
+        <v>7.75</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>-9.25</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SILLYMONKS</t>
+          <t>SANCO</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>16</v>
+        <v>2.3</v>
       </c>
       <c r="C42" t="n">
-        <v>16.75</v>
+        <v>2.41</v>
       </c>
       <c r="D42" t="n">
-        <v>4.69</v>
+        <v>4.78</v>
       </c>
       <c r="E42" t="b">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>16.68</v>
+        <v>2.39</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>-0.42</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CELEBRITY</t>
+          <t>OMKARCHEM</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7.52</v>
+        <v>3.82</v>
       </c>
       <c r="C43" t="n">
-        <v>7.87</v>
+        <v>4</v>
       </c>
       <c r="D43" t="n">
-        <v>4.65</v>
+        <v>4.71</v>
       </c>
       <c r="E43" t="b">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>7.56</v>
+        <v>3.95</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>-3.94</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LIKHITHA</t>
+          <t>AMJLAND</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>141.84</v>
+        <v>36.28</v>
       </c>
       <c r="C44" t="n">
-        <v>148.4</v>
+        <v>37.98</v>
       </c>
       <c r="D44" t="n">
-        <v>4.62</v>
+        <v>4.69</v>
       </c>
       <c r="E44" t="b">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>139.37</v>
+        <v>36.69</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>-6.08</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AVROIND</t>
+          <t>KOTARISUG</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>130.85</v>
+        <v>23.36</v>
       </c>
       <c r="C45" t="n">
-        <v>136.9</v>
+        <v>24.45</v>
       </c>
       <c r="D45" t="n">
-        <v>4.62</v>
+        <v>4.67</v>
       </c>
       <c r="E45" t="b">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>137.39</v>
+        <v>23.7</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>0.36</v>
+        <v>-3.07</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>VAISHALI</t>
+          <t>ODIGMA</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>6.12</v>
+        <v>21.98</v>
       </c>
       <c r="C46" t="n">
-        <v>6.4</v>
+        <v>23</v>
       </c>
       <c r="D46" t="n">
-        <v>4.58</v>
+        <v>4.64</v>
       </c>
       <c r="E46" t="b">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>6.07</v>
+        <v>22.9</v>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>-5.16</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ORTEL</t>
+          <t>GEEKAYWIRE</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1.54</v>
+        <v>20.3</v>
       </c>
       <c r="C47" t="n">
-        <v>1.61</v>
+        <v>21.24</v>
       </c>
       <c r="D47" t="n">
-        <v>4.55</v>
+        <v>4.63</v>
       </c>
       <c r="E47" t="b">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>1.61</v>
+        <v>20.56</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ADVANCE</t>
+          <t>UMAEXPORTS</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>98.22</v>
+        <v>22.42</v>
       </c>
       <c r="C48" t="n">
-        <v>102.6</v>
+        <v>23.45</v>
       </c>
       <c r="D48" t="n">
-        <v>4.46</v>
+        <v>4.59</v>
       </c>
       <c r="E48" t="b">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>99.47</v>
+        <v>22.7</v>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>-3.05</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>RAMKY</t>
+          <t>GINNIFILA</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>479.7</v>
+        <v>35.35</v>
       </c>
       <c r="C49" t="n">
-        <v>501</v>
+        <v>36.97</v>
       </c>
       <c r="D49" t="n">
-        <v>4.44</v>
+        <v>4.58</v>
       </c>
       <c r="E49" t="b">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>464.85</v>
+        <v>36.09</v>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>-7.22</v>
+        <v>-2.38</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SANWARIA</t>
+          <t>BAJEL</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.23</v>
+        <v>167.95</v>
       </c>
       <c r="C50" t="n">
-        <v>0.24</v>
+        <v>175.59</v>
       </c>
       <c r="D50" t="n">
-        <v>4.35</v>
+        <v>4.55</v>
       </c>
       <c r="E50" t="b">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0.24</v>
+        <v>173.66</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GATECH</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.46</v>
+        <v>596.9</v>
       </c>
       <c r="C51" t="n">
-        <v>0.48</v>
+        <v>624</v>
       </c>
       <c r="D51" t="n">
-        <v>4.35</v>
+        <v>4.54</v>
       </c>
       <c r="E51" t="b">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>0.46</v>
+        <v>601.9</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>-4.17</v>
+        <v>-3.54</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SONAMLTD</t>
+          <t>GPTINFRA</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>56.52</v>
+        <v>99.41</v>
       </c>
       <c r="C52" t="n">
-        <v>58.96</v>
+        <v>103.87</v>
       </c>
       <c r="D52" t="n">
-        <v>4.32</v>
+        <v>4.49</v>
       </c>
       <c r="E52" t="b">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>56.14</v>
+        <v>101.78</v>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>-4.78</v>
+        <v>-2.01</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>VERTOZ</t>
+          <t>KALPATARU</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>36.19</v>
+        <v>295.7</v>
       </c>
       <c r="C53" t="n">
-        <v>37.7</v>
+        <v>308.7</v>
       </c>
       <c r="D53" t="n">
-        <v>4.17</v>
+        <v>4.4</v>
       </c>
       <c r="E53" t="b">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>34.85</v>
+        <v>308.45</v>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>-7.56</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MAXIND</t>
+          <t>RAJSREESUG</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>145.94</v>
+        <v>25.88</v>
       </c>
       <c r="C54" t="n">
-        <v>152</v>
+        <v>27</v>
       </c>
       <c r="D54" t="n">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="E54" t="b">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>140.5</v>
+        <v>27.36</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>-7.57</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>VISHWARAJ</t>
+          <t>TARMAT</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>5.38</v>
+        <v>50.7</v>
       </c>
       <c r="C55" t="n">
-        <v>5.6</v>
+        <v>52.88</v>
       </c>
       <c r="D55" t="n">
-        <v>4.09</v>
+        <v>4.3</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>5.1</v>
+        <v>51.41</v>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>-8.93</v>
+        <v>-2.78</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>NINSYS</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>593.6</v>
+        <v>296.55</v>
       </c>
       <c r="C56" t="n">
-        <v>617.8</v>
+        <v>308.95</v>
       </c>
       <c r="D56" t="n">
-        <v>4.08</v>
+        <v>4.18</v>
       </c>
       <c r="E56" t="b">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>578.05</v>
+        <v>302.55</v>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>-6.43</v>
+        <v>-2.07</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MOS</t>
+          <t>KAMOPAINTS</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>13.5</v>
+        <v>4.31</v>
       </c>
       <c r="C57" t="n">
-        <v>14.05</v>
+        <v>4.49</v>
       </c>
       <c r="D57" t="n">
-        <v>4.07</v>
+        <v>4.18</v>
       </c>
       <c r="E57" t="b">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>13.9</v>
+        <v>4.28</v>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>-1.07</v>
+        <v>-4.68</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>DELPHIFX</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>565.9</v>
+        <v>9.84</v>
       </c>
       <c r="C58" t="n">
-        <v>588.95</v>
+        <v>10.25</v>
       </c>
       <c r="D58" t="n">
-        <v>4.07</v>
+        <v>4.17</v>
       </c>
       <c r="E58" t="b">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>537.6</v>
+        <v>10.1</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>-8.720000000000001</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TEJASNET</t>
+          <t>BEARDSELL</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>424.45</v>
+        <v>22.8</v>
       </c>
       <c r="C59" t="n">
-        <v>441.65</v>
+        <v>23.75</v>
       </c>
       <c r="D59" t="n">
-        <v>4.05</v>
+        <v>4.17</v>
       </c>
       <c r="E59" t="b">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>441</v>
+        <v>23.2</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>-0.15</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TVVISION</t>
+          <t>SANWARIA</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>5.47</v>
+        <v>0.24</v>
       </c>
       <c r="C60" t="n">
-        <v>5.69</v>
+        <v>0.25</v>
       </c>
       <c r="D60" t="n">
-        <v>4.02</v>
+        <v>4.17</v>
       </c>
       <c r="E60" t="b">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>5.26</v>
+        <v>0.25</v>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>-7.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AURIGROW</t>
+          <t>JPPOWER</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.25</v>
+        <v>13.5</v>
       </c>
       <c r="C61" t="n">
-        <v>0.26</v>
+        <v>14.04</v>
       </c>
       <c r="D61" t="n">
         <v>4</v>
@@ -2011,1896 +2011,1896 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0.26</v>
+        <v>13.43</v>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>-4.34</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BANKA</t>
+          <t>JARO</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>48.04</v>
+        <v>462.5</v>
       </c>
       <c r="C62" t="n">
-        <v>49.95</v>
+        <v>481</v>
       </c>
       <c r="D62" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="E62" t="b">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>46.99</v>
+        <v>478.4</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>-5.93</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SUMEETINDS</t>
+          <t>PILITA</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>28.86</v>
+        <v>7.25</v>
       </c>
       <c r="C63" t="n">
-        <v>30</v>
+        <v>7.54</v>
       </c>
       <c r="D63" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="E63" t="b">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>29.61</v>
+        <v>7.43</v>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>-1.3</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SWANDEF</t>
+          <t>KANPRPLA</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2394.6</v>
+        <v>156.77</v>
       </c>
       <c r="C64" t="n">
-        <v>2489</v>
+        <v>163</v>
       </c>
       <c r="D64" t="n">
-        <v>3.94</v>
+        <v>3.97</v>
       </c>
       <c r="E64" t="b">
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>2350</v>
+        <v>161.51</v>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>-5.58</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SANGINITA</t>
+          <t>ACL</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>14.99</v>
+        <v>50.99</v>
       </c>
       <c r="C65" t="n">
-        <v>15.57</v>
+        <v>53</v>
       </c>
       <c r="D65" t="n">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="E65" t="b">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>15.73</v>
+        <v>53.77</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>1.03</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>JAIPURKURT</t>
+          <t>ELGIRUBCO</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>29.67</v>
+        <v>37.25</v>
       </c>
       <c r="C66" t="n">
-        <v>30.8</v>
+        <v>38.7</v>
       </c>
       <c r="D66" t="n">
-        <v>3.81</v>
+        <v>3.89</v>
       </c>
       <c r="E66" t="b">
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>29.71</v>
+        <v>37.78</v>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>-3.54</v>
+        <v>-2.38</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>NOIDATOLL</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>3.42</v>
+        <v>13.7</v>
       </c>
       <c r="C67" t="n">
-        <v>3.55</v>
+        <v>14.23</v>
       </c>
       <c r="D67" t="n">
-        <v>3.8</v>
+        <v>3.87</v>
       </c>
       <c r="E67" t="b">
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>3.47</v>
+        <v>13.58</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>-2.25</v>
+        <v>-4.57</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SHREERAMA</t>
+          <t>AURIGROW</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>46.07</v>
+        <v>0.26</v>
       </c>
       <c r="C68" t="n">
-        <v>47.8</v>
+        <v>0.27</v>
       </c>
       <c r="D68" t="n">
-        <v>3.76</v>
+        <v>3.85</v>
       </c>
       <c r="E68" t="b">
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>45.05</v>
+        <v>0.27</v>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>-5.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ANTGRAPHIC</t>
+          <t>INTENTECH</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.8</v>
+        <v>86.19</v>
       </c>
       <c r="C69" t="n">
-        <v>0.83</v>
+        <v>89.5</v>
       </c>
       <c r="D69" t="n">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="E69" t="b">
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>0.8</v>
+        <v>85.39</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>-3.61</v>
+        <v>-4.59</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>JETFREIGHT</t>
+          <t>HAPPSTMNDS</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>18.34</v>
+        <v>377.35</v>
       </c>
       <c r="C70" t="n">
-        <v>19</v>
+        <v>391.8</v>
       </c>
       <c r="D70" t="n">
-        <v>3.6</v>
+        <v>3.83</v>
       </c>
       <c r="E70" t="b">
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>17.8</v>
+        <v>377.45</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>-6.32</v>
+        <v>-3.66</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>GENCON</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>955.85</v>
+        <v>44.17</v>
       </c>
       <c r="C71" t="n">
-        <v>990</v>
+        <v>45.85</v>
       </c>
       <c r="D71" t="n">
-        <v>3.57</v>
+        <v>3.8</v>
       </c>
       <c r="E71" t="b">
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>946</v>
+        <v>44</v>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>-4.44</v>
+        <v>-4.03</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SURAJEST</t>
+          <t>SHYAMCENT</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>204.95</v>
+        <v>4.48</v>
       </c>
       <c r="C72" t="n">
-        <v>212.14</v>
+        <v>4.65</v>
       </c>
       <c r="D72" t="n">
-        <v>3.51</v>
+        <v>3.79</v>
       </c>
       <c r="E72" t="b">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>203.19</v>
+        <v>4.51</v>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>-4.22</v>
+        <v>-3.01</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>URAVIDEF</t>
+          <t>ALANKIT</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>128.51</v>
+        <v>7.65</v>
       </c>
       <c r="C73" t="n">
-        <v>133</v>
+        <v>7.94</v>
       </c>
       <c r="D73" t="n">
-        <v>3.49</v>
+        <v>3.79</v>
       </c>
       <c r="E73" t="b">
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>126.26</v>
+        <v>7.74</v>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>-5.07</v>
+        <v>-2.52</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>WABAG</t>
+          <t>GANGABATH</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1227.6</v>
+        <v>22.1</v>
       </c>
       <c r="C74" t="n">
-        <v>1270</v>
+        <v>22.9</v>
       </c>
       <c r="D74" t="n">
-        <v>3.45</v>
+        <v>3.62</v>
       </c>
       <c r="E74" t="b">
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>1223.5</v>
+        <v>23.95</v>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>-3.66</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>HARRMALAYA</t>
+          <t>VINNY</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>177.66</v>
+        <v>1.12</v>
       </c>
       <c r="C75" t="n">
-        <v>183.7</v>
+        <v>1.16</v>
       </c>
       <c r="D75" t="n">
-        <v>3.4</v>
+        <v>3.57</v>
       </c>
       <c r="E75" t="b">
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>172.33</v>
+        <v>1.15</v>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>-6.19</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ZYDUSWELL</t>
+          <t>KOTHARIPRO</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>404.25</v>
+        <v>62.96</v>
       </c>
       <c r="C76" t="n">
-        <v>418</v>
+        <v>65.2</v>
       </c>
       <c r="D76" t="n">
-        <v>3.4</v>
+        <v>3.56</v>
       </c>
       <c r="E76" t="b">
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>415.45</v>
+        <v>63.63</v>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>-0.61</v>
+        <v>-2.41</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>VIVIANA</t>
+          <t>HINDCON</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>627.7</v>
+        <v>18.35</v>
       </c>
       <c r="C77" t="n">
-        <v>649</v>
+        <v>19</v>
       </c>
       <c r="D77" t="n">
-        <v>3.39</v>
+        <v>3.54</v>
       </c>
       <c r="E77" t="b">
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>612</v>
+        <v>18.59</v>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>-5.7</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>VINNY</t>
+          <t>LOTUSEYE</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1.18</v>
+        <v>107.18</v>
       </c>
       <c r="C78" t="n">
-        <v>1.22</v>
+        <v>110.94</v>
       </c>
       <c r="D78" t="n">
-        <v>3.39</v>
+        <v>3.51</v>
       </c>
       <c r="E78" t="b">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>1.14</v>
+        <v>106.66</v>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>-6.56</v>
+        <v>-3.86</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>RADIOCITY</t>
+          <t>KDL</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>5.61</v>
+        <v>118.9</v>
       </c>
       <c r="C79" t="n">
-        <v>5.8</v>
+        <v>123</v>
       </c>
       <c r="D79" t="n">
-        <v>3.39</v>
+        <v>3.45</v>
       </c>
       <c r="E79" t="b">
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>5.58</v>
+        <v>124.8</v>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>-3.79</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>HINDCON</t>
+          <t>BROOKS</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>18.95</v>
+        <v>57.03</v>
       </c>
       <c r="C80" t="n">
-        <v>19.59</v>
+        <v>58.98</v>
       </c>
       <c r="D80" t="n">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="E80" t="b">
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>18.5</v>
+        <v>56.38</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>-5.56</v>
+        <v>-4.41</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ZEELEARN</t>
+          <t>ROML</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>5.36</v>
+        <v>43.52</v>
       </c>
       <c r="C81" t="n">
-        <v>5.54</v>
+        <v>45</v>
       </c>
       <c r="D81" t="n">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="E81" t="b">
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>5.4</v>
+        <v>44.4</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>-2.53</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SUPREMEPWR</t>
+          <t>PRAKASHSTL</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>153.4</v>
+        <v>4.13</v>
       </c>
       <c r="C82" t="n">
-        <v>158.5</v>
+        <v>4.27</v>
       </c>
       <c r="D82" t="n">
-        <v>3.32</v>
+        <v>3.39</v>
       </c>
       <c r="E82" t="b">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>155</v>
+        <v>4.12</v>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>-2.21</v>
+        <v>-3.51</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PRITI</t>
+          <t>BOHRAIND</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>36.29</v>
+        <v>16.92</v>
       </c>
       <c r="C83" t="n">
-        <v>37.49</v>
+        <v>17.49</v>
       </c>
       <c r="D83" t="n">
-        <v>3.31</v>
+        <v>3.37</v>
       </c>
       <c r="E83" t="b">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>34.68</v>
+        <v>16.5</v>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>-7.5</v>
+        <v>-5.66</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>NOVAAGRI</t>
+          <t>MOKSH</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>27.1</v>
+        <v>11.08</v>
       </c>
       <c r="C84" t="n">
-        <v>27.98</v>
+        <v>11.45</v>
       </c>
       <c r="D84" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="E84" t="b">
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>26.66</v>
+        <v>10.98</v>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>-4.72</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>NEXTMEDIA</t>
+          <t>VHLTD</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>5</v>
+        <v>139.86</v>
       </c>
       <c r="C85" t="n">
-        <v>5.16</v>
+        <v>144.5</v>
       </c>
       <c r="D85" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="E85" t="b">
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>4.83</v>
+        <v>139.25</v>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>-6.4</v>
+        <v>-3.63</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>GOKUL</t>
+          <t>AARON</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>40.7</v>
+        <v>140.27</v>
       </c>
       <c r="C86" t="n">
-        <v>42</v>
+        <v>144.9</v>
       </c>
       <c r="D86" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="E86" t="b">
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>40.05</v>
+        <v>141.06</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>-4.64</v>
+        <v>-2.65</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ORIENTALTL</t>
+          <t>GALAPREC</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>5.7</v>
+        <v>745.2</v>
       </c>
       <c r="C87" t="n">
-        <v>5.88</v>
+        <v>769.8</v>
       </c>
       <c r="D87" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="E87" t="b">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>5.63</v>
+        <v>742</v>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>-4.25</v>
+        <v>-3.61</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MANBA</t>
+          <t>PANACHE</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>120.2</v>
+        <v>298.3</v>
       </c>
       <c r="C88" t="n">
-        <v>123.99</v>
+        <v>308</v>
       </c>
       <c r="D88" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="E88" t="b">
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>119.52</v>
+        <v>309.5</v>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>-3.61</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ALMONDZ</t>
+          <t>ALKALI</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>13.95</v>
+        <v>57.72</v>
       </c>
       <c r="C89" t="n">
-        <v>14.39</v>
+        <v>59.59</v>
       </c>
       <c r="D89" t="n">
-        <v>3.15</v>
+        <v>3.24</v>
       </c>
       <c r="E89" t="b">
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>13.69</v>
+        <v>57.25</v>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>-4.86</v>
+        <v>-3.93</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>COMMITTED</t>
+          <t>SEJALLTD</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>237.45</v>
+        <v>503.75</v>
       </c>
       <c r="C90" t="n">
-        <v>244.9</v>
+        <v>519.95</v>
       </c>
       <c r="D90" t="n">
-        <v>3.14</v>
+        <v>3.22</v>
       </c>
       <c r="E90" t="b">
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>249.3</v>
+        <v>498.9</v>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>1.8</v>
+        <v>-4.05</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ANMOL</t>
+          <t>PATINTLOG</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>10.86</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="C91" t="n">
-        <v>11.2</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="D91" t="n">
-        <v>3.13</v>
+        <v>3.22</v>
       </c>
       <c r="E91" t="b">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>10.82</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>-3.39</v>
+        <v>-5.93</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>GVPTECH</t>
+          <t>SYNCOMF</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>5.81</v>
+        <v>11.82</v>
       </c>
       <c r="C92" t="n">
-        <v>5.99</v>
+        <v>12.2</v>
       </c>
       <c r="D92" t="n">
-        <v>3.1</v>
+        <v>3.21</v>
       </c>
       <c r="E92" t="b">
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>6.1</v>
+        <v>11.9</v>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
-        <v>1.84</v>
+        <v>-2.46</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DAMODARIND</t>
+          <t>MGEL</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>24.01</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="C93" t="n">
-        <v>24.75</v>
+        <v>10.2</v>
       </c>
       <c r="D93" t="n">
-        <v>3.08</v>
+        <v>3.13</v>
       </c>
       <c r="E93" t="b">
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>23.99</v>
+        <v>10.12</v>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
-        <v>-3.07</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BHARATSE</t>
+          <t>HEXATRADEX</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>158.87</v>
+        <v>160.02</v>
       </c>
       <c r="C94" t="n">
-        <v>163.75</v>
+        <v>165</v>
       </c>
       <c r="D94" t="n">
-        <v>3.07</v>
+        <v>3.11</v>
       </c>
       <c r="E94" t="b">
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>158.68</v>
+        <v>161.5</v>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>-3.1</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>GICL</t>
+          <t>FLFL</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>43.64</v>
+        <v>1.29</v>
       </c>
       <c r="C95" t="n">
-        <v>44.94</v>
+        <v>1.33</v>
       </c>
       <c r="D95" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="E95" t="b">
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>43.92</v>
+        <v>1.33</v>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>-2.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>OMNI</t>
+          <t>AIRAN</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>218.54</v>
+        <v>15.43</v>
       </c>
       <c r="C96" t="n">
-        <v>225</v>
+        <v>15.9</v>
       </c>
       <c r="D96" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="E96" t="b">
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>215.1</v>
+        <v>15.55</v>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>-4.4</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>INDOWIND</t>
+          <t>LOVABLE</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>8.449999999999999</v>
+        <v>66.48</v>
       </c>
       <c r="C97" t="n">
-        <v>8.699999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="D97" t="n">
-        <v>2.96</v>
+        <v>3.04</v>
       </c>
       <c r="E97" t="b">
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>8.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>-3.45</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PROSTARM</t>
+          <t>LIBAS</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>125.31</v>
+        <v>10.58</v>
       </c>
       <c r="C98" t="n">
-        <v>129</v>
+        <v>10.9</v>
       </c>
       <c r="D98" t="n">
-        <v>2.94</v>
+        <v>3.02</v>
       </c>
       <c r="E98" t="b">
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>123.44</v>
+        <v>10</v>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>-4.31</v>
+        <v>-8.26</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BESTAGRO</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>14.85</v>
+        <v>533.05</v>
       </c>
       <c r="C99" t="n">
-        <v>15.27</v>
+        <v>549</v>
       </c>
       <c r="D99" t="n">
-        <v>2.83</v>
+        <v>2.99</v>
       </c>
       <c r="E99" t="b">
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>14.11</v>
+        <v>525.3</v>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
-        <v>-7.6</v>
+        <v>-4.32</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>IVP</t>
+          <t>SADHAV</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>126.51</v>
+        <v>95.2</v>
       </c>
       <c r="C100" t="n">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="D100" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="E100" t="b">
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>-2.31</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>TCC</t>
+          <t>ZODIACLOTH</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>395.25</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="C101" t="n">
-        <v>406</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="D101" t="n">
-        <v>2.72</v>
+        <v>2.94</v>
       </c>
       <c r="E101" t="b">
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>387.15</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>-4.64</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MANOMAY</t>
+          <t>GSLSU</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>209.3</v>
+        <v>64.12</v>
       </c>
       <c r="C102" t="n">
-        <v>215</v>
+        <v>66</v>
       </c>
       <c r="D102" t="n">
-        <v>2.72</v>
+        <v>2.93</v>
       </c>
       <c r="E102" t="b">
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>201.65</v>
+        <v>62.57</v>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>-6.21</v>
+        <v>-5.2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PILITA</t>
+          <t>RELCHEMQ</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>7.34</v>
+        <v>112.15</v>
       </c>
       <c r="C103" t="n">
-        <v>7.54</v>
+        <v>115.44</v>
       </c>
       <c r="D103" t="n">
-        <v>2.72</v>
+        <v>2.93</v>
       </c>
       <c r="E103" t="b">
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>7.18</v>
+        <v>111.5</v>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>-4.77</v>
+        <v>-3.41</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DPEL</t>
+          <t>ZENITHSTL</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>297</v>
+        <v>5.19</v>
       </c>
       <c r="C104" t="n">
-        <v>305.05</v>
+        <v>5.34</v>
       </c>
       <c r="D104" t="n">
-        <v>2.71</v>
+        <v>2.89</v>
       </c>
       <c r="E104" t="b">
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>309.75</v>
+        <v>5.22</v>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
-        <v>1.54</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>RELCHEMQ</t>
+          <t>BRNL</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>112.42</v>
+        <v>17.5</v>
       </c>
       <c r="C105" t="n">
-        <v>115.45</v>
+        <v>18</v>
       </c>
       <c r="D105" t="n">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="E105" t="b">
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>112.5</v>
+        <v>17.42</v>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>-2.56</v>
+        <v>-3.22</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>SAURASHCEM</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>13.38</v>
+        <v>58.34</v>
       </c>
       <c r="C106" t="n">
-        <v>13.74</v>
+        <v>60</v>
       </c>
       <c r="D106" t="n">
-        <v>2.69</v>
+        <v>2.85</v>
       </c>
       <c r="E106" t="b">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>13.27</v>
+        <v>59.34</v>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
-        <v>-3.42</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>EMKAY</t>
+          <t>ASHIMASYN</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>210.37</v>
+        <v>14.35</v>
       </c>
       <c r="C107" t="n">
-        <v>215.99</v>
+        <v>14.75</v>
       </c>
       <c r="D107" t="n">
-        <v>2.67</v>
+        <v>2.79</v>
       </c>
       <c r="E107" t="b">
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>214.63</v>
+        <v>14.26</v>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>-0.63</v>
+        <v>-3.32</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>REDINGTON</t>
+          <t>CYIENTDLM</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>234.55</v>
+        <v>300.6</v>
       </c>
       <c r="C108" t="n">
-        <v>240.75</v>
+        <v>309</v>
       </c>
       <c r="D108" t="n">
-        <v>2.64</v>
+        <v>2.79</v>
       </c>
       <c r="E108" t="b">
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>228.5</v>
+        <v>333.75</v>
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
-        <v>-5.09</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AKSHAR</t>
+          <t>DCM</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.38</v>
+        <v>58.39</v>
       </c>
       <c r="C109" t="n">
-        <v>0.39</v>
+        <v>60</v>
       </c>
       <c r="D109" t="n">
-        <v>2.63</v>
+        <v>2.76</v>
       </c>
       <c r="E109" t="b">
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>0.39</v>
+        <v>58.52</v>
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>0</v>
+        <v>-2.47</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SHYAMCENT</t>
+          <t>ANMOL</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>4.62</v>
+        <v>10.6</v>
       </c>
       <c r="C110" t="n">
-        <v>4.74</v>
+        <v>10.89</v>
       </c>
       <c r="D110" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="E110" t="b">
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>4.55</v>
+        <v>10.52</v>
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
-        <v>-4.01</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>KEYFINSERV</t>
+          <t>AIMTRON</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>253.45</v>
+        <v>743.4</v>
       </c>
       <c r="C111" t="n">
-        <v>260</v>
+        <v>763.7</v>
       </c>
       <c r="D111" t="n">
-        <v>2.58</v>
+        <v>2.73</v>
       </c>
       <c r="E111" t="b">
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>252</v>
+        <v>780.55</v>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>-3.08</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>PRAXIS</t>
+          <t>VIVIANA</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>6.25</v>
+        <v>621.15</v>
       </c>
       <c r="C112" t="n">
-        <v>6.41</v>
+        <v>637.9</v>
       </c>
       <c r="D112" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="E112" t="b">
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>6.29</v>
+        <v>633</v>
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
-        <v>-1.87</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>COMPINFO</t>
+          <t>RELIABLE</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1.17</v>
+        <v>111.99</v>
       </c>
       <c r="C113" t="n">
-        <v>1.2</v>
+        <v>115</v>
       </c>
       <c r="D113" t="n">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="E113" t="b">
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>1.21</v>
+        <v>112.79</v>
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>0.83</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SETUINFRA</t>
+          <t>KAPSTON</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.39</v>
+        <v>271.75</v>
       </c>
       <c r="C114" t="n">
-        <v>0.4</v>
+        <v>279</v>
       </c>
       <c r="D114" t="n">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="E114" t="b">
         <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>0.38</v>
+        <v>271.3</v>
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
-        <v>-5</v>
+        <v>-2.76</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ARCHIDPLY</t>
+          <t>ASIANHOTNR</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>73.14</v>
+        <v>297.15</v>
       </c>
       <c r="C115" t="n">
-        <v>75</v>
+        <v>305</v>
       </c>
       <c r="D115" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="E115" t="b">
         <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>71</v>
+        <v>295.05</v>
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>-5.33</v>
+        <v>-3.26</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>INDTERRAIN</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>28.43</v>
+        <v>6528.5</v>
       </c>
       <c r="C116" t="n">
-        <v>29.15</v>
+        <v>6701</v>
       </c>
       <c r="D116" t="n">
-        <v>2.53</v>
+        <v>2.64</v>
       </c>
       <c r="E116" t="b">
         <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>28.1</v>
+        <v>6625.5</v>
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
-        <v>-3.6</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>PIGL</t>
+          <t>LORDSCHLO</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>99.47</v>
+        <v>116.92</v>
       </c>
       <c r="C117" t="n">
-        <v>101.99</v>
+        <v>120</v>
       </c>
       <c r="D117" t="n">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="E117" t="b">
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>97.66</v>
+        <v>121.53</v>
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>-4.25</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ONWARDTEC</t>
+          <t>KOHINOOR</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>235.35</v>
+        <v>22.9</v>
       </c>
       <c r="C118" t="n">
-        <v>241.3</v>
+        <v>23.5</v>
       </c>
       <c r="D118" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="E118" t="b">
         <v>0</v>
       </c>
       <c r="F118" t="n">
-        <v>227.15</v>
+        <v>22.6</v>
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
-        <v>-5.86</v>
+        <v>-3.83</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SOUTHWEST</t>
+          <t>TIGERLOGS</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>193.06</v>
+        <v>26.18</v>
       </c>
       <c r="C119" t="n">
-        <v>197.9</v>
+        <v>26.85</v>
       </c>
       <c r="D119" t="n">
-        <v>2.51</v>
+        <v>2.56</v>
       </c>
       <c r="E119" t="b">
         <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>191.48</v>
+        <v>26.25</v>
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
-        <v>-3.24</v>
+        <v>-2.23</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>TICL</t>
+          <t>DISHTV</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>26.28</v>
+        <v>2.34</v>
       </c>
       <c r="C120" t="n">
-        <v>26.94</v>
+        <v>2.4</v>
       </c>
       <c r="D120" t="n">
-        <v>2.51</v>
+        <v>2.56</v>
       </c>
       <c r="E120" t="b">
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>25.39</v>
+        <v>2.2</v>
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
-        <v>-5.75</v>
+        <v>-8.33</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MCLEODRUSS</t>
+          <t>MOLDTECH</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>37.07</v>
+        <v>123.47</v>
       </c>
       <c r="C121" t="n">
-        <v>38</v>
+        <v>126.6</v>
       </c>
       <c r="D121" t="n">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="E121" t="b">
         <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>35.62</v>
+        <v>123.17</v>
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
-        <v>-6.26</v>
+        <v>-2.71</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SMARTLINK</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>118.54</v>
+        <v>127.56</v>
       </c>
       <c r="C122" t="n">
-        <v>121.5</v>
+        <v>130.8</v>
       </c>
       <c r="D122" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="E122" t="b">
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>119.96</v>
+        <v>126.66</v>
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
-        <v>-1.27</v>
+        <v>-3.17</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SJLOGISTIC</t>
+          <t>HAPPYFORGE</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>262.4</v>
+        <v>1264</v>
       </c>
       <c r="C123" t="n">
-        <v>268.95</v>
+        <v>1296</v>
       </c>
       <c r="D123" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="E123" t="b">
         <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>261.6</v>
+        <v>1277.1</v>
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>-2.73</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>RKDL</t>
+          <t>RKEC</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>19.31</v>
+        <v>35.99</v>
       </c>
       <c r="C124" t="n">
-        <v>19.79</v>
+        <v>36.9</v>
       </c>
       <c r="D124" t="n">
-        <v>2.49</v>
+        <v>2.53</v>
       </c>
       <c r="E124" t="b">
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>18.5</v>
+        <v>35.71</v>
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
-        <v>-6.52</v>
+        <v>-3.22</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>INDOTHAI</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>250.2</v>
+        <v>86.81</v>
       </c>
       <c r="C125" t="n">
-        <v>256.4</v>
+        <v>88.98999999999999</v>
       </c>
       <c r="D125" t="n">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="E125" t="b">
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>250.15</v>
+        <v>88.98999999999999</v>
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>-2.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BALAXI</t>
+          <t>FEL</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>18.65</v>
+        <v>0.4</v>
       </c>
       <c r="C126" t="n">
-        <v>19.11</v>
+        <v>0.41</v>
       </c>
       <c r="D126" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="E126" t="b">
         <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>17.79</v>
+        <v>0.4</v>
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
-        <v>-6.91</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>FLEXITUFF</t>
+          <t>SHRENIK</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>6.9</v>
+        <v>0.4</v>
       </c>
       <c r="C127" t="n">
-        <v>7.07</v>
+        <v>0.41</v>
       </c>
       <c r="D127" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="E127" t="b">
         <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>6.99</v>
+        <v>0.41</v>
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>NRL</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>6.16</v>
+        <v>51.57</v>
       </c>
       <c r="C128" t="n">
-        <v>6.31</v>
+        <v>52.85</v>
       </c>
       <c r="D128" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="E128" t="b">
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>6.29</v>
+        <v>50.9</v>
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
-        <v>-0.32</v>
+        <v>-3.69</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ABINFRA</t>
+          <t>PLAZACABLE</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>16.87</v>
+        <v>34.29</v>
       </c>
       <c r="C129" t="n">
-        <v>17.28</v>
+        <v>35.14</v>
       </c>
       <c r="D129" t="n">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="E129" t="b">
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>16.95</v>
+        <v>34.41</v>
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
-        <v>-1.91</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BALPHARMA</t>
+          <t>UCAL</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>69.23999999999999</v>
+        <v>97.29000000000001</v>
       </c>
       <c r="C130" t="n">
-        <v>70.90000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="D130" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="E130" t="b">
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>67.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
-        <v>-4.37</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>RPEL</t>
+          <t>HILINFRA</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>649.5</v>
+        <v>49.14</v>
       </c>
       <c r="C131" t="n">
-        <v>664.95</v>
+        <v>50.36</v>
       </c>
       <c r="D131" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="E131" t="b">
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>643.25</v>
+        <v>49</v>
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
-        <v>-3.26</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>KRITI</t>
+          <t>SOUTHWEST</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>81.66</v>
+        <v>183.47</v>
       </c>
       <c r="C132" t="n">
-        <v>83.59999999999999</v>
+        <v>188</v>
       </c>
       <c r="D132" t="n">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="E132" t="b">
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>79</v>
+        <v>189.97</v>
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
-        <v>-5.5</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SILGO</t>
+          <t>CORDSCABLE</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>71.29000000000001</v>
+        <v>146.14</v>
       </c>
       <c r="C133" t="n">
-        <v>72.98999999999999</v>
+        <v>149.6</v>
       </c>
       <c r="D133" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="E133" t="b">
         <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>70.98</v>
+        <v>146.45</v>
       </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
-        <v>-2.75</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>BIRLAMONEY</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>115.93</v>
+        <v>105.6</v>
       </c>
       <c r="C134" t="n">
-        <v>118.68</v>
+        <v>108.1</v>
       </c>
       <c r="D134" t="n">
         <v>2.37</v>
@@ -3909,76 +3909,76 @@
         <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>113.46</v>
+        <v>104.6</v>
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
-        <v>-4.4</v>
+        <v>-3.24</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SADHNANIQ</t>
+          <t>TARACHAND</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>1.69</v>
+        <v>57.59</v>
       </c>
       <c r="C135" t="n">
-        <v>1.73</v>
+        <v>58.95</v>
       </c>
       <c r="D135" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="E135" t="b">
         <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>1.77</v>
+        <v>57.82</v>
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
-        <v>2.31</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>DPSCLTD</t>
+          <t>DAMODARIND</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>8.44</v>
+        <v>23.43</v>
       </c>
       <c r="C136" t="n">
-        <v>8.640000000000001</v>
+        <v>23.98</v>
       </c>
       <c r="D136" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="E136" t="b">
         <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>8.31</v>
+        <v>23.4</v>
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
-        <v>-3.82</v>
+        <v>-2.42</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>TREEHOUSE</t>
+          <t>TIL</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>8.109999999999999</v>
+        <v>196.39</v>
       </c>
       <c r="C137" t="n">
-        <v>8.300000000000001</v>
+        <v>200.99</v>
       </c>
       <c r="D137" t="n">
         <v>2.34</v>
@@ -3987,24 +3987,24 @@
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>8.07</v>
+        <v>191.75</v>
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
-        <v>-2.77</v>
+        <v>-4.6</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>GATECHDVR</t>
+          <t>KMEW</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.43</v>
+        <v>1538.8</v>
       </c>
       <c r="C138" t="n">
-        <v>0.44</v>
+        <v>1574.7</v>
       </c>
       <c r="D138" t="n">
         <v>2.33</v>
@@ -4013,102 +4013,102 @@
         <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>0.43</v>
+        <v>1526.8</v>
       </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
-        <v>-2.27</v>
+        <v>-3.04</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>BBTCL</t>
+          <t>AMDIND</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>170.04</v>
+        <v>35.19</v>
       </c>
       <c r="C139" t="n">
-        <v>174</v>
+        <v>36</v>
       </c>
       <c r="D139" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="E139" t="b">
         <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>165</v>
+        <v>35.36</v>
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
-        <v>-5.17</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>MURUDCERA</t>
+          <t>ABINFRA</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>29.32</v>
+        <v>17.01</v>
       </c>
       <c r="C140" t="n">
-        <v>30</v>
+        <v>17.4</v>
       </c>
       <c r="D140" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="E140" t="b">
         <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>29.39</v>
+        <v>17.16</v>
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
-        <v>-2.03</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>OBSCP</t>
+          <t>ASTRON</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>293.25</v>
+        <v>3.95</v>
       </c>
       <c r="C141" t="n">
-        <v>300</v>
+        <v>4.04</v>
       </c>
       <c r="D141" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="E141" t="b">
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>288.75</v>
+        <v>3.94</v>
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
-        <v>-3.75</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>SUNDARAM</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>146.57</v>
+        <v>1.32</v>
       </c>
       <c r="C142" t="n">
-        <v>149.9</v>
+        <v>1.35</v>
       </c>
       <c r="D142" t="n">
         <v>2.27</v>
@@ -4117,24 +4117,24 @@
         <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>150.89</v>
+        <v>1.29</v>
       </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
-        <v>0.66</v>
+        <v>-4.44</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>INDOTECH</t>
+          <t>DIFFNKG</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1318.8</v>
+        <v>239.75</v>
       </c>
       <c r="C143" t="n">
-        <v>1348.8</v>
+        <v>245.2</v>
       </c>
       <c r="D143" t="n">
         <v>2.27</v>
@@ -4143,241 +4143,241 @@
         <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>1268.9</v>
+        <v>240.75</v>
       </c>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
-        <v>-5.92</v>
+        <v>-1.81</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>KHADIM</t>
+          <t>EIHAHOTELS</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>101.13</v>
+        <v>302</v>
       </c>
       <c r="C144" t="n">
-        <v>103.4</v>
+        <v>308.8</v>
       </c>
       <c r="D144" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="E144" t="b">
         <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>98.5</v>
+        <v>301.2</v>
       </c>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
-        <v>-4.74</v>
+        <v>-2.46</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>RSSOFTWARE</t>
+          <t>CEINSYS</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>27.87</v>
+        <v>938.45</v>
       </c>
       <c r="C145" t="n">
-        <v>28.49</v>
+        <v>959.6</v>
       </c>
       <c r="D145" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="E145" t="b">
         <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>26.91</v>
+        <v>945.5</v>
       </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
-        <v>-5.55</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SUVIDHAA</t>
+          <t>KANANIIND</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>2.7</v>
+        <v>1.34</v>
       </c>
       <c r="C146" t="n">
-        <v>2.76</v>
+        <v>1.37</v>
       </c>
       <c r="D146" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="E146" t="b">
         <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>2.7</v>
+        <v>1.36</v>
       </c>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
-        <v>-2.17</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>UMIYA-MRO</t>
+          <t>NDLVENTURE</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>79.75</v>
+        <v>113.48</v>
       </c>
       <c r="C147" t="n">
-        <v>81.5</v>
+        <v>116</v>
       </c>
       <c r="D147" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="E147" t="b">
         <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>76.90000000000001</v>
+        <v>112.48</v>
       </c>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
-        <v>-5.64</v>
+        <v>-3.03</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>AARTISURF</t>
+          <t>ISFT</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>364.55</v>
+        <v>65.55</v>
       </c>
       <c r="C148" t="n">
-        <v>372.5</v>
+        <v>67</v>
       </c>
       <c r="D148" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="E148" t="b">
         <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>354.95</v>
+        <v>68</v>
       </c>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
-        <v>-4.71</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>PACEDIGITK</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>110.5</v>
+        <v>163.9</v>
       </c>
       <c r="C149" t="n">
-        <v>112.9</v>
+        <v>167.5</v>
       </c>
       <c r="D149" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="E149" t="b">
         <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>105</v>
+        <v>169.82</v>
       </c>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
-        <v>-7</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>AVONMORE</t>
+          <t>DPABHUSHAN</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>11.65</v>
+        <v>977.5</v>
       </c>
       <c r="C150" t="n">
-        <v>11.9</v>
+        <v>999</v>
       </c>
       <c r="D150" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="E150" t="b">
         <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>12.16</v>
+        <v>972.3</v>
       </c>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
-        <v>2.18</v>
+        <v>-2.67</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>UMESLTD</t>
+          <t>NGIL</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>6.51</v>
+        <v>25.25</v>
       </c>
       <c r="C151" t="n">
-        <v>6.65</v>
+        <v>25.8</v>
       </c>
       <c r="D151" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="E151" t="b">
         <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>6.4</v>
+        <v>25.48</v>
       </c>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
-        <v>-3.76</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>NAVKARURB</t>
+          <t>GATECH</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.95</v>
+        <v>0.46</v>
       </c>
       <c r="C152" t="n">
-        <v>0.97</v>
+        <v>0.47</v>
       </c>
       <c r="D152" t="n">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="E152" t="b">
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>0.97</v>
+        <v>0.47</v>
       </c>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="n">
@@ -4387,1275 +4387,1275 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BGLOBAL</t>
+          <t>PRECOT</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>2.84</v>
+        <v>484.55</v>
       </c>
       <c r="C153" t="n">
-        <v>2.9</v>
+        <v>495</v>
       </c>
       <c r="D153" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="E153" t="b">
         <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>2.83</v>
+        <v>490.8</v>
       </c>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="n">
-        <v>-2.41</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>LOTUSEYE</t>
+          <t>MANBA</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>103.53</v>
+        <v>123.34</v>
       </c>
       <c r="C154" t="n">
-        <v>105.69</v>
+        <v>126</v>
       </c>
       <c r="D154" t="n">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="E154" t="b">
         <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>103.5</v>
+        <v>120.3</v>
       </c>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="n">
-        <v>-2.07</v>
+        <v>-4.52</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>INDIASHLTR</t>
+          <t>ASAL</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>689.65</v>
+        <v>410.95</v>
       </c>
       <c r="C155" t="n">
-        <v>704</v>
+        <v>419.8</v>
       </c>
       <c r="D155" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="E155" t="b">
         <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>697.8</v>
+        <v>417.75</v>
       </c>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="n">
-        <v>-0.88</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>GOPAL</t>
+          <t>BALAXI</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>269.4</v>
+        <v>17.67</v>
       </c>
       <c r="C156" t="n">
-        <v>275</v>
+        <v>18.05</v>
       </c>
       <c r="D156" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="E156" t="b">
         <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>268.05</v>
+        <v>18.18</v>
       </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="n">
-        <v>-2.53</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>GFLLIMITED</t>
+          <t>INDOWIND</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>43.99</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="C157" t="n">
-        <v>44.9</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="D157" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="E157" t="b">
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>42.7</v>
+        <v>8.31</v>
       </c>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="n">
-        <v>-4.9</v>
+        <v>-2.69</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>INA</t>
+          <t>TNTELE</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>95.23</v>
+        <v>8.42</v>
       </c>
       <c r="C158" t="n">
-        <v>97.2</v>
+        <v>8.6</v>
       </c>
       <c r="D158" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="E158" t="b">
         <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>94.27</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="n">
-        <v>-3.01</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>BORANA</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>6.76</v>
+        <v>369.1</v>
       </c>
       <c r="C159" t="n">
-        <v>6.9</v>
+        <v>376.95</v>
       </c>
       <c r="D159" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="E159" t="b">
         <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>6.56</v>
+        <v>374.75</v>
       </c>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="n">
-        <v>-4.93</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>BTML</t>
+          <t>GOLDENTOBC</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>7.27</v>
+        <v>28.69</v>
       </c>
       <c r="C160" t="n">
-        <v>7.42</v>
+        <v>29.3</v>
       </c>
       <c r="D160" t="n">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="E160" t="b">
         <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>6.77</v>
+        <v>28.68</v>
       </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="n">
-        <v>-8.76</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>MAHEPC</t>
+          <t>PREMEXPLN</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>112.01</v>
+        <v>431.85</v>
       </c>
       <c r="C161" t="n">
-        <v>114.3</v>
+        <v>441</v>
       </c>
       <c r="D161" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="E161" t="b">
         <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>108.95</v>
+        <v>443</v>
       </c>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="n">
-        <v>-4.68</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>SUPREMEENG</t>
+          <t>SBC</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.98</v>
+        <v>31.34</v>
       </c>
       <c r="C162" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="D162" t="n">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="E162" t="b">
         <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>0.99</v>
+        <v>31.77</v>
       </c>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="n">
-        <v>-1</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>WSI</t>
+          <t>VISAKAIND</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>63.69</v>
+        <v>56.8</v>
       </c>
       <c r="C163" t="n">
-        <v>64.98999999999999</v>
+        <v>58</v>
       </c>
       <c r="D163" t="n">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="E163" t="b">
         <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>61.46</v>
+        <v>56.82</v>
       </c>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="n">
-        <v>-5.43</v>
+        <v>-2.03</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>FCSSOFT</t>
+          <t>FISCHER</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>1.48</v>
+        <v>33.2</v>
       </c>
       <c r="C164" t="n">
-        <v>1.51</v>
+        <v>33.9</v>
       </c>
       <c r="D164" t="n">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="E164" t="b">
         <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>1.44</v>
+        <v>33.91</v>
       </c>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="n">
-        <v>-4.64</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SRD</t>
+          <t>SURANASOL</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>51.16</v>
+        <v>21.29</v>
       </c>
       <c r="C165" t="n">
-        <v>52.2</v>
+        <v>21.74</v>
       </c>
       <c r="D165" t="n">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="E165" t="b">
         <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>49.35</v>
+        <v>21.37</v>
       </c>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="n">
-        <v>-5.46</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>DMCC</t>
+          <t>STALLION</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>211.74</v>
+        <v>113.42</v>
       </c>
       <c r="C166" t="n">
-        <v>216</v>
+        <v>115.8</v>
       </c>
       <c r="D166" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="E166" t="b">
         <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>214.24</v>
+        <v>118.3</v>
       </c>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="n">
-        <v>-0.8100000000000001</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SIKKO</t>
+          <t>UTIAMC</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>4.5</v>
+        <v>959.85</v>
       </c>
       <c r="C167" t="n">
-        <v>4.59</v>
+        <v>980</v>
       </c>
       <c r="D167" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="E167" t="b">
         <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>4.37</v>
+        <v>972.25</v>
       </c>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="n">
-        <v>-4.79</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>DEEDEV</t>
+          <t>AKSHOPTFBR</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>297.3</v>
+        <v>4.28</v>
       </c>
       <c r="C168" t="n">
-        <v>303.25</v>
+        <v>4.37</v>
       </c>
       <c r="D168" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="E168" t="b">
         <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>290</v>
+        <v>4.58</v>
       </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="n">
-        <v>-4.37</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>VISASTEEL</t>
+          <t>TFL</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>34.19</v>
+        <v>11.95</v>
       </c>
       <c r="C169" t="n">
-        <v>34.87</v>
+        <v>12.2</v>
       </c>
       <c r="D169" t="n">
-        <v>1.99</v>
+        <v>2.09</v>
       </c>
       <c r="E169" t="b">
         <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>34</v>
+        <v>13.36</v>
       </c>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="n">
-        <v>-2.49</v>
+        <v>9.51</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ORIENTCER</t>
+          <t>AFIL</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>35.66</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="C170" t="n">
-        <v>36.37</v>
+        <v>8.31</v>
       </c>
       <c r="D170" t="n">
-        <v>1.99</v>
+        <v>2.09</v>
       </c>
       <c r="E170" t="b">
         <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>35.18</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="n">
-        <v>-3.27</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>MODTHREAD</t>
+          <t>NAVKARURB</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>53.33</v>
+        <v>0.96</v>
       </c>
       <c r="C171" t="n">
-        <v>54.39</v>
+        <v>0.98</v>
       </c>
       <c r="D171" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="E171" t="b">
         <v>0</v>
       </c>
       <c r="F171" t="n">
-        <v>49</v>
+        <v>0.96</v>
       </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="n">
-        <v>-9.91</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>PAVNAIND</t>
+          <t>VMARCIND</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>18.1</v>
+        <v>682.8</v>
       </c>
       <c r="C172" t="n">
-        <v>18.46</v>
+        <v>697</v>
       </c>
       <c r="D172" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="E172" t="b">
         <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>17.95</v>
+        <v>680.6</v>
       </c>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="n">
-        <v>-2.76</v>
+        <v>-2.35</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>CMNL</t>
+          <t>GOLDTECH</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>98</v>
+        <v>38.49</v>
       </c>
       <c r="C173" t="n">
-        <v>99.95</v>
+        <v>39.29</v>
       </c>
       <c r="D173" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="E173" t="b">
         <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>95</v>
+        <v>39.66</v>
       </c>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="n">
-        <v>-4.95</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>OSWALSEEDS</t>
+          <t>MODINATUR</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>11.76</v>
+        <v>285.15</v>
       </c>
       <c r="C174" t="n">
-        <v>11.99</v>
+        <v>291</v>
       </c>
       <c r="D174" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="E174" t="b">
         <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>11.42</v>
+        <v>298.5</v>
       </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="n">
-        <v>-4.75</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ESAFSFB</t>
+          <t>ENERGYDEV</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>24.22</v>
+        <v>15.09</v>
       </c>
       <c r="C175" t="n">
-        <v>24.69</v>
+        <v>15.4</v>
       </c>
       <c r="D175" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="E175" t="b">
         <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>23.81</v>
+        <v>15.01</v>
       </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="n">
-        <v>-3.56</v>
+        <v>-2.53</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>STYL</t>
+          <t>PASHUPATI</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>250.08</v>
+        <v>990</v>
       </c>
       <c r="C176" t="n">
-        <v>254.9</v>
+        <v>1010</v>
       </c>
       <c r="D176" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="E176" t="b">
         <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>250.8</v>
+        <v>998</v>
       </c>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="n">
-        <v>-1.61</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>NATHBIOGEN</t>
+          <t>GANESHIN</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>142.28</v>
+        <v>84.2</v>
       </c>
       <c r="C177" t="n">
-        <v>145</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="D177" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="E177" t="b">
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>139.06</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="n">
-        <v>-4.1</v>
+        <v>-2.33</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>KAPSTON</t>
+          <t>AVROIND</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>270.35</v>
+        <v>137.36</v>
       </c>
       <c r="C178" t="n">
-        <v>275.5</v>
+        <v>140.14</v>
       </c>
       <c r="D178" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="E178" t="b">
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>272</v>
+        <v>136.51</v>
       </c>
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="n">
-        <v>-1.27</v>
+        <v>-2.59</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SAKUMA</t>
+          <t>IRMENERGY</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>1.58</v>
+        <v>200.56</v>
       </c>
       <c r="C179" t="n">
-        <v>1.61</v>
+        <v>204.6</v>
       </c>
       <c r="D179" t="n">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="E179" t="b">
         <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>1.55</v>
+        <v>201.28</v>
       </c>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="n">
-        <v>-3.73</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SVPGLOB</t>
+          <t>APEX</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>2.65</v>
+        <v>328.4</v>
       </c>
       <c r="C180" t="n">
-        <v>2.7</v>
+        <v>335</v>
       </c>
       <c r="D180" t="n">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="E180" t="b">
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>2.65</v>
+        <v>331.5</v>
       </c>
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="n">
-        <v>-1.85</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>NTPCGREEN</t>
+          <t>HPAL</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>98.15000000000001</v>
+        <v>31.01</v>
       </c>
       <c r="C181" t="n">
-        <v>100</v>
+        <v>31.63</v>
       </c>
       <c r="D181" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="E181" t="b">
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>94.90000000000001</v>
+        <v>31.62</v>
       </c>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="n">
-        <v>-5.1</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>EXCEL</t>
+          <t>UTTAMSUGAR</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>1.07</v>
+        <v>189.9</v>
       </c>
       <c r="C182" t="n">
-        <v>1.09</v>
+        <v>193.7</v>
       </c>
       <c r="D182" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="E182" t="b">
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>1.03</v>
+        <v>193</v>
       </c>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="n">
-        <v>-5.5</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>NAHARINDUS</t>
+          <t>RAMRAT</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>88.84</v>
+        <v>299.65</v>
       </c>
       <c r="C183" t="n">
-        <v>90.5</v>
+        <v>305.65</v>
       </c>
       <c r="D183" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="E183" t="b">
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>89.54000000000001</v>
+        <v>298</v>
       </c>
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="n">
-        <v>-1.06</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>MONEYBOXX</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>64.48999999999999</v>
+        <v>669.95</v>
       </c>
       <c r="C184" t="n">
-        <v>65.69</v>
+        <v>683.3</v>
       </c>
       <c r="D184" t="n">
-        <v>1.86</v>
+        <v>1.99</v>
       </c>
       <c r="E184" t="b">
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>63.29</v>
+        <v>675.85</v>
       </c>
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="n">
-        <v>-3.65</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>TEXMOPIPES</t>
+          <t>RAJRILTD</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>42.95</v>
+        <v>21.17</v>
       </c>
       <c r="C185" t="n">
-        <v>43.75</v>
+        <v>21.59</v>
       </c>
       <c r="D185" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="E185" t="b">
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>41.97</v>
+        <v>21.28</v>
       </c>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="n">
-        <v>-4.07</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>NILAINFRA</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>7.12</v>
+        <v>360.9</v>
       </c>
       <c r="C186" t="n">
-        <v>7.25</v>
+        <v>368</v>
       </c>
       <c r="D186" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="E186" t="b">
         <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>6.86</v>
+        <v>368.85</v>
       </c>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="n">
-        <v>-5.38</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>DTIL</t>
+          <t>JAYSREETEA</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>127.66</v>
+        <v>87.52</v>
       </c>
       <c r="C187" t="n">
-        <v>130</v>
+        <v>89.23999999999999</v>
       </c>
       <c r="D187" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="E187" t="b">
         <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>127</v>
+        <v>89.3</v>
       </c>
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="n">
-        <v>-2.31</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>APS</t>
+          <t>BHARATWIRE</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>304.45</v>
+        <v>153.97</v>
       </c>
       <c r="C188" t="n">
-        <v>310</v>
+        <v>157</v>
       </c>
       <c r="D188" t="n">
-        <v>1.82</v>
+        <v>1.97</v>
       </c>
       <c r="E188" t="b">
         <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>298.1</v>
+        <v>154.68</v>
       </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="n">
-        <v>-3.84</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>SYSTMTXC</t>
+          <t>EXXARO</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>63.69</v>
+        <v>6.61</v>
       </c>
       <c r="C189" t="n">
-        <v>64.84</v>
+        <v>6.74</v>
       </c>
       <c r="D189" t="n">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="E189" t="b">
         <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>62.03</v>
+        <v>6.68</v>
       </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="n">
-        <v>-4.33</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>KNAGRI</t>
+          <t>ALMONDZ</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>178.8</v>
+        <v>13.73</v>
       </c>
       <c r="C190" t="n">
-        <v>182</v>
+        <v>14</v>
       </c>
       <c r="D190" t="n">
-        <v>1.79</v>
+        <v>1.97</v>
       </c>
       <c r="E190" t="b">
         <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>175.66</v>
+        <v>14.3</v>
       </c>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="n">
-        <v>-3.48</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ORIENTELEC</t>
+          <t>SUPREMEENG</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>169.8</v>
+        <v>1.02</v>
       </c>
       <c r="C191" t="n">
-        <v>172.78</v>
+        <v>1.04</v>
       </c>
       <c r="D191" t="n">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="E191" t="b">
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>167.32</v>
+        <v>1.07</v>
       </c>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="n">
-        <v>-3.16</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>VHLTD</t>
+          <t>ATLANTAELE</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>139.56</v>
+        <v>979.75</v>
       </c>
       <c r="C192" t="n">
-        <v>142</v>
+        <v>999</v>
       </c>
       <c r="D192" t="n">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="E192" t="b">
         <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>139.9</v>
+        <v>991.55</v>
       </c>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="n">
-        <v>-1.48</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>COASTCORP</t>
+          <t>UNITEDPOLY</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>43.64</v>
+        <v>25.01</v>
       </c>
       <c r="C193" t="n">
-        <v>44.4</v>
+        <v>25.5</v>
       </c>
       <c r="D193" t="n">
-        <v>1.74</v>
+        <v>1.96</v>
       </c>
       <c r="E193" t="b">
         <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>44.98</v>
+        <v>25.98</v>
       </c>
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="n">
-        <v>1.31</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SCHAND</t>
+          <t>SAKUMA</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>146.49</v>
+        <v>1.53</v>
       </c>
       <c r="C194" t="n">
-        <v>148.99</v>
+        <v>1.56</v>
       </c>
       <c r="D194" t="n">
-        <v>1.71</v>
+        <v>1.96</v>
       </c>
       <c r="E194" t="b">
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>140.83</v>
+        <v>1.53</v>
       </c>
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="n">
-        <v>-5.48</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>AEQUS</t>
+          <t>FIEMIND</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>116.8</v>
+        <v>2005</v>
       </c>
       <c r="C195" t="n">
-        <v>118.8</v>
+        <v>2044</v>
       </c>
       <c r="D195" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="E195" t="b">
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>114.53</v>
+        <v>1995.6</v>
       </c>
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="n">
-        <v>-3.59</v>
+        <v>-2.37</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SHAH</t>
+          <t>TEJASNET</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>4.72</v>
+        <v>446.85</v>
       </c>
       <c r="C196" t="n">
-        <v>4.8</v>
+        <v>455.5</v>
       </c>
       <c r="D196" t="n">
-        <v>1.69</v>
+        <v>1.94</v>
       </c>
       <c r="E196" t="b">
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>4.73</v>
+        <v>437.65</v>
       </c>
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="n">
-        <v>-1.46</v>
+        <v>-3.92</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>NILASPACES</t>
+          <t>KRITINUT</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>13.07</v>
+        <v>61.76</v>
       </c>
       <c r="C197" t="n">
-        <v>13.29</v>
+        <v>62.95</v>
       </c>
       <c r="D197" t="n">
-        <v>1.68</v>
+        <v>1.93</v>
       </c>
       <c r="E197" t="b">
         <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>13.04</v>
+        <v>62.27</v>
       </c>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="n">
-        <v>-1.88</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>PASHUPATI</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>988.45</v>
+        <v>713.2</v>
       </c>
       <c r="C198" t="n">
-        <v>1005</v>
+        <v>726.95</v>
       </c>
       <c r="D198" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="E198" t="b">
         <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>988.35</v>
+        <v>714.55</v>
       </c>
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="n">
-        <v>-1.66</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SEDEMAC</t>
+          <t>KRITIKA</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>1465.5</v>
+        <v>5.18</v>
       </c>
       <c r="C199" t="n">
-        <v>1490</v>
+        <v>5.28</v>
       </c>
       <c r="D199" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="E199" t="b">
         <v>0</v>
       </c>
       <c r="F199" t="n">
-        <v>1456.5</v>
+        <v>5.48</v>
       </c>
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="n">
-        <v>-2.25</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ALANKIT</t>
+          <t>JSWINFRA</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>7.85</v>
+        <v>250.4</v>
       </c>
       <c r="C200" t="n">
-        <v>7.98</v>
+        <v>255.2</v>
       </c>
       <c r="D200" t="n">
-        <v>1.66</v>
+        <v>1.92</v>
       </c>
       <c r="E200" t="b">
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>7.7</v>
+        <v>255.15</v>
       </c>
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="n">
-        <v>-3.51</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>WINSOME</t>
+          <t>SVPGLOB</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>1.81</v>
+        <v>2.63</v>
       </c>
       <c r="C201" t="n">
-        <v>1.84</v>
+        <v>2.68</v>
       </c>
       <c r="D201" t="n">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="E201" t="b">
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>1.78</v>
+        <v>2.55</v>
       </c>
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="n">
-        <v>-3.26</v>
+        <v>-4.85</v>
       </c>
     </row>
   </sheetData>

--- a/data/trending_momentum_stocks.xlsx
+++ b/data/trending_momentum_stocks.xlsx
@@ -461,3923 +461,3923 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RADAAN</t>
+          <t>MITTAL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.71</v>
+        <v>0.85</v>
       </c>
       <c r="C2" t="n">
-        <v>3.03</v>
+        <v>0.99</v>
       </c>
       <c r="D2" t="n">
-        <v>11.81</v>
+        <v>16.47</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>2.81</v>
+        <v>0.98</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>-7.26</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RAJMET</t>
+          <t>INSPIRE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.44</v>
+        <v>9.65</v>
       </c>
       <c r="C3" t="n">
-        <v>3.79</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>10.17</v>
+        <v>13.99</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3.57</v>
+        <v>10.95</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>-5.8</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CCHHL</t>
+          <t>VINEETLAB</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.74</v>
+        <v>29.01</v>
       </c>
       <c r="C4" t="n">
-        <v>12.8</v>
+        <v>32</v>
       </c>
       <c r="D4" t="n">
-        <v>9.029999999999999</v>
+        <v>10.31</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>11.75</v>
+        <v>29.97</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>-8.199999999999999</v>
+        <v>-6.34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PRITI</t>
+          <t>VICTORYEV</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34.26</v>
+        <v>14.3</v>
       </c>
       <c r="C5" t="n">
-        <v>37.35</v>
+        <v>15.75</v>
       </c>
       <c r="D5" t="n">
-        <v>9.02</v>
+        <v>10.14</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>36.99</v>
+        <v>15</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>-0.96</v>
+        <v>-4.76</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RADIOCITY</t>
+          <t>CYBERMEDIA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.48</v>
+        <v>13.1</v>
       </c>
       <c r="C6" t="n">
-        <v>5.96</v>
+        <v>14.35</v>
       </c>
       <c r="D6" t="n">
-        <v>8.76</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>5.47</v>
+        <v>13.51</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>-8.220000000000001</v>
+        <v>-5.85</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SPCENET</t>
+          <t>ENSER</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.86</v>
+        <v>11.6</v>
       </c>
       <c r="C7" t="n">
-        <v>4.19</v>
+        <v>12.65</v>
       </c>
       <c r="D7" t="n">
-        <v>8.550000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>4.24</v>
+        <v>11.3</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>1.19</v>
+        <v>-10.67</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MITTAL</t>
+          <t>DELTIC</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.71</v>
+        <v>36</v>
       </c>
       <c r="C8" t="n">
-        <v>0.77</v>
+        <v>39</v>
       </c>
       <c r="D8" t="n">
-        <v>8.449999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.85</v>
+        <v>36.1</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>10.39</v>
+        <v>-7.44</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MODTHREAD</t>
+          <t>DPEL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>48.01</v>
+        <v>359.35</v>
       </c>
       <c r="C9" t="n">
-        <v>51.99</v>
+        <v>387</v>
       </c>
       <c r="D9" t="n">
-        <v>8.289999999999999</v>
+        <v>7.69</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>50.49</v>
+        <v>392.5</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>-2.89</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SHREYANIND</t>
+          <t>LASA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>138.53</v>
+        <v>7.3</v>
       </c>
       <c r="C10" t="n">
-        <v>149.85</v>
+        <v>7.8</v>
       </c>
       <c r="D10" t="n">
-        <v>8.17</v>
+        <v>6.85</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>139.48</v>
+        <v>7.47</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>-6.92</v>
+        <v>-4.23</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SPLIL</t>
+          <t>ICDSLTD</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24.33</v>
+        <v>47.14</v>
       </c>
       <c r="C11" t="n">
-        <v>26.3</v>
+        <v>50.2</v>
       </c>
       <c r="D11" t="n">
-        <v>8.1</v>
+        <v>6.49</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>24.87</v>
+        <v>47.28</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>-5.44</v>
+        <v>-5.82</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SHEKHAWATI</t>
+          <t>DCMSIL</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11.98</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>12.9</v>
+        <v>89</v>
       </c>
       <c r="D12" t="n">
-        <v>7.68</v>
+        <v>5.65</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>12.59</v>
+        <v>86.28</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>-2.4</v>
+        <v>-3.06</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AMNPLST</t>
+          <t>PAVNAIND</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>147.81</v>
+        <v>18.02</v>
       </c>
       <c r="C13" t="n">
-        <v>159</v>
+        <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>7.57</v>
+        <v>5.44</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>152.5</v>
+        <v>18.12</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>-4.09</v>
+        <v>-4.63</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SHANTI</t>
+          <t>SILGO</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.42</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="C14" t="n">
-        <v>6.9</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>7.48</v>
+        <v>5.42</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>6.49</v>
+        <v>72.75</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>-5.94</v>
+        <v>-6.73</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SIGIND</t>
+          <t>CTE</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>44.24</v>
+        <v>24.42</v>
       </c>
       <c r="C15" t="n">
-        <v>47.5</v>
+        <v>25.7</v>
       </c>
       <c r="D15" t="n">
-        <v>7.37</v>
+        <v>5.24</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>44.5</v>
+        <v>24.67</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>-6.32</v>
+        <v>-4.01</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DPEL</t>
+          <t>EUROTEXIND</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>326.7</v>
+        <v>12.5</v>
       </c>
       <c r="C16" t="n">
-        <v>349.95</v>
+        <v>13.12</v>
       </c>
       <c r="D16" t="n">
-        <v>7.12</v>
+        <v>4.96</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>359.35</v>
+        <v>12.58</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>2.69</v>
+        <v>-4.12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PNC</t>
+          <t>VIJIFIN</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20.12</v>
+        <v>3.03</v>
       </c>
       <c r="C17" t="n">
-        <v>21.4</v>
+        <v>3.18</v>
       </c>
       <c r="D17" t="n">
-        <v>6.36</v>
+        <v>4.95</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>20.01</v>
+        <v>3.18</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>-6.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PRIMO</t>
+          <t>BONLON</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17.96</v>
+        <v>37.99</v>
       </c>
       <c r="C18" t="n">
-        <v>19.1</v>
+        <v>39.85</v>
       </c>
       <c r="D18" t="n">
-        <v>6.35</v>
+        <v>4.9</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>18.2</v>
+        <v>39.7</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>-4.71</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DIGIKORE</t>
+          <t>SIDDHICOTS</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>81.34999999999999</v>
+        <v>28.05</v>
       </c>
       <c r="C19" t="n">
-        <v>86.45</v>
+        <v>29.4</v>
       </c>
       <c r="D19" t="n">
-        <v>6.27</v>
+        <v>4.81</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>84.95</v>
+        <v>29.2</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>-1.74</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>WELINV</t>
+          <t>BMETRICS</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1308.5</v>
+        <v>40.9</v>
       </c>
       <c r="C20" t="n">
-        <v>1390</v>
+        <v>42.85</v>
       </c>
       <c r="D20" t="n">
-        <v>6.23</v>
+        <v>4.77</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1280.4</v>
+        <v>42.5</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>-7.88</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SUPERSPIN</t>
+          <t>HBSL</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4.23</v>
+        <v>48.97</v>
       </c>
       <c r="C21" t="n">
-        <v>4.49</v>
+        <v>51.3</v>
       </c>
       <c r="D21" t="n">
-        <v>6.15</v>
+        <v>4.76</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>4.12</v>
+        <v>48.52</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>-8.24</v>
+        <v>-5.42</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MKPL</t>
+          <t>COOLCAPS</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5.01</v>
+        <v>23.4</v>
       </c>
       <c r="C22" t="n">
-        <v>5.3</v>
+        <v>24.5</v>
       </c>
       <c r="D22" t="n">
-        <v>5.79</v>
+        <v>4.7</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>5.07</v>
+        <v>24.55</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>-4.34</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ITI</t>
+          <t>GUJRAFFIA</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>277.15</v>
+        <v>36.48</v>
       </c>
       <c r="C23" t="n">
-        <v>293.15</v>
+        <v>38.19</v>
       </c>
       <c r="D23" t="n">
-        <v>5.77</v>
+        <v>4.69</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>282.05</v>
+        <v>37.92</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>-3.79</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TOKYOPLAST</t>
+          <t>SUPREMEENG</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>70.04000000000001</v>
+        <v>1.07</v>
       </c>
       <c r="C24" t="n">
-        <v>73.98999999999999</v>
+        <v>1.12</v>
       </c>
       <c r="D24" t="n">
-        <v>5.64</v>
+        <v>4.67</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>72</v>
+        <v>1.12</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>-2.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SUTLEJTEX</t>
+          <t>ORIENTLTD</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>29.36</v>
+        <v>59.68</v>
       </c>
       <c r="C25" t="n">
-        <v>31</v>
+        <v>62.4</v>
       </c>
       <c r="D25" t="n">
-        <v>5.59</v>
+        <v>4.56</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>30.05</v>
+        <v>62.89</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>-3.06</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>COASTCORP</t>
+          <t>DELTAMAGNT</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>45.94</v>
+        <v>55</v>
       </c>
       <c r="C26" t="n">
-        <v>48.5</v>
+        <v>57.5</v>
       </c>
       <c r="D26" t="n">
-        <v>5.57</v>
+        <v>4.55</v>
       </c>
       <c r="E26" t="b">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>46.24</v>
+        <v>56.16</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>-4.66</v>
+        <v>-2.33</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CPEDU</t>
+          <t>GOLDENTOBC</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>167.67</v>
+        <v>27.51</v>
       </c>
       <c r="C27" t="n">
-        <v>176.9</v>
+        <v>28.75</v>
       </c>
       <c r="D27" t="n">
-        <v>5.5</v>
+        <v>4.51</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>171.32</v>
+        <v>26.23</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>-3.15</v>
+        <v>-8.77</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SUPREME</t>
+          <t>JPPOWER</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>52.76</v>
+        <v>13.98</v>
       </c>
       <c r="C28" t="n">
-        <v>55.6</v>
+        <v>14.6</v>
       </c>
       <c r="D28" t="n">
-        <v>5.38</v>
+        <v>4.43</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>51.65</v>
+        <v>15.04</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>-7.1</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SEMAC</t>
+          <t>HEXT</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>236.27</v>
+        <v>407</v>
       </c>
       <c r="C29" t="n">
-        <v>248.96</v>
+        <v>425</v>
       </c>
       <c r="D29" t="n">
-        <v>5.37</v>
+        <v>4.42</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>240</v>
+        <v>422.55</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>-3.6</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MUNJALSHOW</t>
+          <t>EQUIPPP</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>119.7</v>
+        <v>18.16</v>
       </c>
       <c r="C30" t="n">
-        <v>125.8</v>
+        <v>18.96</v>
       </c>
       <c r="D30" t="n">
-        <v>5.1</v>
+        <v>4.41</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>119.81</v>
+        <v>18.55</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>-4.76</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>JETFREIGHT</t>
+          <t>CANARYS</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>17.99</v>
+        <v>20.4</v>
       </c>
       <c r="C31" t="n">
-        <v>18.9</v>
+        <v>21.3</v>
       </c>
       <c r="D31" t="n">
-        <v>5.06</v>
+        <v>4.41</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>18.48</v>
+        <v>20.5</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>-2.22</v>
+        <v>-3.76</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SETUINFRA</t>
+          <t>KEEPLEARN</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.4</v>
+        <v>1.85</v>
       </c>
       <c r="C32" t="n">
-        <v>0.42</v>
+        <v>1.93</v>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>4.32</v>
       </c>
       <c r="E32" t="b">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0.41</v>
+        <v>1.84</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>-2.38</v>
+        <v>-4.66</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GJL</t>
+          <t>BAFNAPH</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>238.9</v>
+        <v>109.31</v>
       </c>
       <c r="C33" t="n">
-        <v>250.8</v>
+        <v>113.99</v>
       </c>
       <c r="D33" t="n">
-        <v>4.98</v>
+        <v>4.28</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>250.8</v>
+        <v>114.77</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>POWERMECH</t>
+          <t>ENERGYDEV</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1876.5</v>
+        <v>14.63</v>
       </c>
       <c r="C34" t="n">
-        <v>1969.9</v>
+        <v>15.25</v>
       </c>
       <c r="D34" t="n">
-        <v>4.98</v>
+        <v>4.24</v>
       </c>
       <c r="E34" t="b">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>1930</v>
+        <v>14.67</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>-2.03</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TCIFINANCE</t>
+          <t>DEVIT</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>13.55</v>
+        <v>28.73</v>
       </c>
       <c r="C35" t="n">
-        <v>14.22</v>
+        <v>29.9</v>
       </c>
       <c r="D35" t="n">
-        <v>4.94</v>
+        <v>4.07</v>
       </c>
       <c r="E35" t="b">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>13.3</v>
+        <v>29.21</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>-6.47</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BAFNAPH</t>
+          <t>AIRAN</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>104.11</v>
+        <v>15.28</v>
       </c>
       <c r="C36" t="n">
-        <v>109.25</v>
+        <v>15.89</v>
       </c>
       <c r="D36" t="n">
-        <v>4.94</v>
+        <v>3.99</v>
       </c>
       <c r="E36" t="b">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>109.31</v>
+        <v>15.5</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>0.05</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>OILCOUNTUB</t>
+          <t>AKG</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>36.97</v>
+        <v>10.8</v>
       </c>
       <c r="C37" t="n">
-        <v>38.79</v>
+        <v>11.23</v>
       </c>
       <c r="D37" t="n">
-        <v>4.92</v>
+        <v>3.98</v>
       </c>
       <c r="E37" t="b">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>44.36</v>
+        <v>10.92</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>14.36</v>
+        <v>-2.76</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>VISHWARAJ</t>
+          <t>NOIDATOLL</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5.08</v>
+        <v>3.52</v>
       </c>
       <c r="C38" t="n">
-        <v>5.33</v>
+        <v>3.66</v>
       </c>
       <c r="D38" t="n">
-        <v>4.92</v>
+        <v>3.98</v>
       </c>
       <c r="E38" t="b">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>5.21</v>
+        <v>3.65</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>-2.25</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SIGMA</t>
+          <t>PIGL</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>40.03</v>
+        <v>95.3</v>
       </c>
       <c r="C39" t="n">
-        <v>41.98</v>
+        <v>98.98999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>4.87</v>
+        <v>3.87</v>
       </c>
       <c r="E39" t="b">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>40.01</v>
+        <v>101.44</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>-4.69</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>VIJIFIN</t>
+          <t>MAGNUM</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.89</v>
+        <v>18.8</v>
       </c>
       <c r="C40" t="n">
-        <v>3.03</v>
+        <v>19.5</v>
       </c>
       <c r="D40" t="n">
-        <v>4.84</v>
+        <v>3.72</v>
       </c>
       <c r="E40" t="b">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>3.03</v>
+        <v>18.99</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>-2.62</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DCMFINSERV</t>
+          <t>AURIGROW</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>8.15</v>
+        <v>0.27</v>
       </c>
       <c r="C41" t="n">
-        <v>8.539999999999999</v>
+        <v>0.28</v>
       </c>
       <c r="D41" t="n">
-        <v>4.79</v>
+        <v>3.7</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>7.75</v>
+        <v>0.28</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>-9.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SANCO</t>
+          <t>EXXARO</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.3</v>
+        <v>6.61</v>
       </c>
       <c r="C42" t="n">
-        <v>2.41</v>
+        <v>6.85</v>
       </c>
       <c r="D42" t="n">
-        <v>4.78</v>
+        <v>3.63</v>
       </c>
       <c r="E42" t="b">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>2.39</v>
+        <v>6.94</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>-0.83</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>OMKARCHEM</t>
+          <t>RKEC</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3.82</v>
+        <v>35.31</v>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
+        <v>36.57</v>
       </c>
       <c r="D43" t="n">
-        <v>4.71</v>
+        <v>3.57</v>
       </c>
       <c r="E43" t="b">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>3.95</v>
+        <v>36.32</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>-1.25</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AMJLAND</t>
+          <t>PALASHSECU</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>36.28</v>
+        <v>85.38</v>
       </c>
       <c r="C44" t="n">
-        <v>37.98</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>4.69</v>
+        <v>3.54</v>
       </c>
       <c r="E44" t="b">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>36.69</v>
+        <v>87.48999999999999</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>-3.4</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>KOTARISUG</t>
+          <t>ANIKINDS</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>23.36</v>
+        <v>39.15</v>
       </c>
       <c r="C45" t="n">
-        <v>24.45</v>
+        <v>40.5</v>
       </c>
       <c r="D45" t="n">
-        <v>4.67</v>
+        <v>3.45</v>
       </c>
       <c r="E45" t="b">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>23.7</v>
+        <v>39.46</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>-3.07</v>
+        <v>-2.57</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ODIGMA</t>
+          <t>VERTOZ</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>21.98</v>
+        <v>34.8</v>
       </c>
       <c r="C46" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D46" t="n">
-        <v>4.64</v>
+        <v>3.45</v>
       </c>
       <c r="E46" t="b">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>22.9</v>
+        <v>36.38</v>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>-0.43</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GEEKAYWIRE</t>
+          <t>GFLLIMITED</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>20.3</v>
+        <v>43.36</v>
       </c>
       <c r="C47" t="n">
-        <v>21.24</v>
+        <v>44.8</v>
       </c>
       <c r="D47" t="n">
-        <v>4.63</v>
+        <v>3.32</v>
       </c>
       <c r="E47" t="b">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>20.56</v>
+        <v>44.37</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>-3.2</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>UMAEXPORTS</t>
+          <t>VITAL</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>22.42</v>
+        <v>39.45</v>
       </c>
       <c r="C48" t="n">
-        <v>23.45</v>
+        <v>40.75</v>
       </c>
       <c r="D48" t="n">
-        <v>4.59</v>
+        <v>3.3</v>
       </c>
       <c r="E48" t="b">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>22.7</v>
+        <v>40</v>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>-3.2</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>GINNIFILA</t>
+          <t>RUCHINFRA</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>35.35</v>
+        <v>4.87</v>
       </c>
       <c r="C49" t="n">
-        <v>36.97</v>
+        <v>5.03</v>
       </c>
       <c r="D49" t="n">
-        <v>4.58</v>
+        <v>3.29</v>
       </c>
       <c r="E49" t="b">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>36.09</v>
+        <v>4.98</v>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>-2.38</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BAJEL</t>
+          <t>ORIENTALTL</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>167.95</v>
+        <v>5.23</v>
       </c>
       <c r="C50" t="n">
-        <v>175.59</v>
+        <v>5.4</v>
       </c>
       <c r="D50" t="n">
-        <v>4.55</v>
+        <v>3.25</v>
       </c>
       <c r="E50" t="b">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>173.66</v>
+        <v>5.36</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>-1.1</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>BAGFILMS</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>596.9</v>
+        <v>4.34</v>
       </c>
       <c r="C51" t="n">
-        <v>624</v>
+        <v>4.48</v>
       </c>
       <c r="D51" t="n">
-        <v>4.54</v>
+        <v>3.23</v>
       </c>
       <c r="E51" t="b">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>601.9</v>
+        <v>4.49</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>-3.54</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GPTINFRA</t>
+          <t>GSS</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>99.41</v>
+        <v>11.13</v>
       </c>
       <c r="C52" t="n">
-        <v>103.87</v>
+        <v>11.49</v>
       </c>
       <c r="D52" t="n">
-        <v>4.49</v>
+        <v>3.23</v>
       </c>
       <c r="E52" t="b">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>101.78</v>
+        <v>11.14</v>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>-2.01</v>
+        <v>-3.05</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>KALPATARU</t>
+          <t>NEPHROCARE</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>295.7</v>
+        <v>66.8</v>
       </c>
       <c r="C53" t="n">
-        <v>308.7</v>
+        <v>68.95</v>
       </c>
       <c r="D53" t="n">
-        <v>4.4</v>
+        <v>3.22</v>
       </c>
       <c r="E53" t="b">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>308.45</v>
+        <v>68</v>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>-0.08</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>RAJSREESUG</t>
+          <t>IMPEXFERRO</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>25.88</v>
+        <v>1.56</v>
       </c>
       <c r="C54" t="n">
-        <v>27</v>
+        <v>1.61</v>
       </c>
       <c r="D54" t="n">
-        <v>4.33</v>
+        <v>3.21</v>
       </c>
       <c r="E54" t="b">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>27.36</v>
+        <v>1.58</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>1.33</v>
+        <v>-1.86</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TARMAT</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>50.7</v>
+        <v>106.6</v>
       </c>
       <c r="C55" t="n">
-        <v>52.88</v>
+        <v>110</v>
       </c>
       <c r="D55" t="n">
-        <v>4.3</v>
+        <v>3.19</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>51.41</v>
+        <v>111.9</v>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>-2.78</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>NINSYS</t>
+          <t>ALLCARGO</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>296.55</v>
+        <v>7.84</v>
       </c>
       <c r="C56" t="n">
-        <v>308.95</v>
+        <v>8.09</v>
       </c>
       <c r="D56" t="n">
-        <v>4.18</v>
+        <v>3.19</v>
       </c>
       <c r="E56" t="b">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>302.55</v>
+        <v>8.24</v>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>-2.07</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>KAMOPAINTS</t>
+          <t>VGL</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4.31</v>
+        <v>59.12</v>
       </c>
       <c r="C57" t="n">
-        <v>4.49</v>
+        <v>61</v>
       </c>
       <c r="D57" t="n">
-        <v>4.18</v>
+        <v>3.18</v>
       </c>
       <c r="E57" t="b">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>4.28</v>
+        <v>59.4</v>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>-4.68</v>
+        <v>-2.62</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DELPHIFX</t>
+          <t>HAVISHA</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>9.84</v>
+        <v>1.26</v>
       </c>
       <c r="C58" t="n">
-        <v>10.25</v>
+        <v>1.3</v>
       </c>
       <c r="D58" t="n">
-        <v>4.17</v>
+        <v>3.17</v>
       </c>
       <c r="E58" t="b">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>10.1</v>
+        <v>1.24</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>-1.46</v>
+        <v>-4.62</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BEARDSELL</t>
+          <t>XTGLOBAL</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>22.8</v>
+        <v>30.26</v>
       </c>
       <c r="C59" t="n">
-        <v>23.75</v>
+        <v>31.21</v>
       </c>
       <c r="D59" t="n">
-        <v>4.17</v>
+        <v>3.14</v>
       </c>
       <c r="E59" t="b">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>23.2</v>
+        <v>30.65</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>-2.32</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SANWARIA</t>
+          <t>KKJEWELS</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.24</v>
+        <v>95</v>
       </c>
       <c r="C60" t="n">
-        <v>0.25</v>
+        <v>97.95</v>
       </c>
       <c r="D60" t="n">
-        <v>4.17</v>
+        <v>3.11</v>
       </c>
       <c r="E60" t="b">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>0.25</v>
+        <v>95.5</v>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>JPPOWER</t>
+          <t>FISCHER</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>13.5</v>
+        <v>34.86</v>
       </c>
       <c r="C61" t="n">
-        <v>14.04</v>
+        <v>35.94</v>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="E61" t="b">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>13.43</v>
+        <v>36.6</v>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>-4.34</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>JARO</t>
+          <t>RNFI</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>462.5</v>
+        <v>247.25</v>
       </c>
       <c r="C62" t="n">
-        <v>481</v>
+        <v>254.9</v>
       </c>
       <c r="D62" t="n">
-        <v>4</v>
+        <v>3.09</v>
       </c>
       <c r="E62" t="b">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>478.4</v>
+        <v>253</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>-0.54</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PILITA</t>
+          <t>SIGMA</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>7.25</v>
+        <v>39.77</v>
       </c>
       <c r="C63" t="n">
-        <v>7.54</v>
+        <v>40.99</v>
       </c>
       <c r="D63" t="n">
-        <v>4</v>
+        <v>3.07</v>
       </c>
       <c r="E63" t="b">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>7.43</v>
+        <v>40.61</v>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>-1.46</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>KANPRPLA</t>
+          <t>SITINET</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>156.77</v>
+        <v>0.33</v>
       </c>
       <c r="C64" t="n">
-        <v>163</v>
+        <v>0.34</v>
       </c>
       <c r="D64" t="n">
-        <v>3.97</v>
+        <v>3.03</v>
       </c>
       <c r="E64" t="b">
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>161.51</v>
+        <v>0.33</v>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>-0.91</v>
+        <v>-2.94</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ACL</t>
+          <t>APCL</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>50.99</v>
+        <v>112.59</v>
       </c>
       <c r="C65" t="n">
-        <v>53</v>
+        <v>116</v>
       </c>
       <c r="D65" t="n">
-        <v>3.94</v>
+        <v>3.03</v>
       </c>
       <c r="E65" t="b">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>53.77</v>
+        <v>116.09</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>1.45</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ELGIRUBCO</t>
+          <t>BYKE</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>37.25</v>
+        <v>33.01</v>
       </c>
       <c r="C66" t="n">
-        <v>38.7</v>
+        <v>34</v>
       </c>
       <c r="D66" t="n">
-        <v>3.89</v>
+        <v>3</v>
       </c>
       <c r="E66" t="b">
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>37.78</v>
+        <v>33.4</v>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>-2.38</v>
+        <v>-1.76</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>RAJSREESUG</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>13.7</v>
+        <v>26.9</v>
       </c>
       <c r="C67" t="n">
-        <v>14.23</v>
+        <v>27.7</v>
       </c>
       <c r="D67" t="n">
-        <v>3.87</v>
+        <v>2.97</v>
       </c>
       <c r="E67" t="b">
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>13.58</v>
+        <v>27.64</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>-4.57</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AURIGROW</t>
+          <t>SIKKO</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.26</v>
+        <v>4.56</v>
       </c>
       <c r="C68" t="n">
-        <v>0.27</v>
+        <v>4.69</v>
       </c>
       <c r="D68" t="n">
-        <v>3.85</v>
+        <v>2.85</v>
       </c>
       <c r="E68" t="b">
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>0.27</v>
+        <v>4.66</v>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>INTENTECH</t>
+          <t>NATHBIOGEN</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>86.19</v>
+        <v>140.41</v>
       </c>
       <c r="C69" t="n">
-        <v>89.5</v>
+        <v>144.4</v>
       </c>
       <c r="D69" t="n">
-        <v>3.84</v>
+        <v>2.84</v>
       </c>
       <c r="E69" t="b">
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>85.39</v>
+        <v>143</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>-4.59</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>HAPPSTMNDS</t>
+          <t>GVPTECH</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>377.35</v>
+        <v>5.74</v>
       </c>
       <c r="C70" t="n">
-        <v>391.8</v>
+        <v>5.9</v>
       </c>
       <c r="D70" t="n">
-        <v>3.83</v>
+        <v>2.79</v>
       </c>
       <c r="E70" t="b">
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>377.45</v>
+        <v>5.8</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>-3.66</v>
+        <v>-1.69</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>GENCON</t>
+          <t>SELMC</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>44.17</v>
+        <v>29.07</v>
       </c>
       <c r="C71" t="n">
-        <v>45.85</v>
+        <v>29.88</v>
       </c>
       <c r="D71" t="n">
-        <v>3.8</v>
+        <v>2.79</v>
       </c>
       <c r="E71" t="b">
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>44</v>
+        <v>29.16</v>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>-4.03</v>
+        <v>-2.41</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SHYAMCENT</t>
+          <t>SOMANYCERA</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>4.48</v>
+        <v>362.95</v>
       </c>
       <c r="C72" t="n">
-        <v>4.65</v>
+        <v>373</v>
       </c>
       <c r="D72" t="n">
-        <v>3.79</v>
+        <v>2.77</v>
       </c>
       <c r="E72" t="b">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>4.51</v>
+        <v>383.35</v>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>-3.01</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ALANKIT</t>
+          <t>NEXTMEDIA</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>7.65</v>
+        <v>5.06</v>
       </c>
       <c r="C73" t="n">
-        <v>7.94</v>
+        <v>5.2</v>
       </c>
       <c r="D73" t="n">
-        <v>3.79</v>
+        <v>2.77</v>
       </c>
       <c r="E73" t="b">
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>7.74</v>
+        <v>4.93</v>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>-2.52</v>
+        <v>-5.19</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>GANGABATH</t>
+          <t>CROWN</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>22.1</v>
+        <v>118.73</v>
       </c>
       <c r="C74" t="n">
-        <v>22.9</v>
+        <v>122</v>
       </c>
       <c r="D74" t="n">
-        <v>3.62</v>
+        <v>2.75</v>
       </c>
       <c r="E74" t="b">
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>23.95</v>
+        <v>119.2</v>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>4.59</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>VINNY</t>
+          <t>DELPHIFX</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1.12</v>
+        <v>10.31</v>
       </c>
       <c r="C75" t="n">
-        <v>1.16</v>
+        <v>10.59</v>
       </c>
       <c r="D75" t="n">
-        <v>3.57</v>
+        <v>2.72</v>
       </c>
       <c r="E75" t="b">
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>1.15</v>
+        <v>10.44</v>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>-0.86</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>KOTHARIPRO</t>
+          <t>AEPL</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>62.96</v>
+        <v>17.62</v>
       </c>
       <c r="C76" t="n">
-        <v>65.2</v>
+        <v>18.1</v>
       </c>
       <c r="D76" t="n">
-        <v>3.56</v>
+        <v>2.72</v>
       </c>
       <c r="E76" t="b">
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>63.63</v>
+        <v>17.95</v>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>-2.41</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>HINDCON</t>
+          <t>CLEANMAX</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>18.35</v>
+        <v>890.7</v>
       </c>
       <c r="C77" t="n">
-        <v>19</v>
+        <v>914.9</v>
       </c>
       <c r="D77" t="n">
-        <v>3.54</v>
+        <v>2.72</v>
       </c>
       <c r="E77" t="b">
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>18.59</v>
+        <v>883</v>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>-2.16</v>
+        <v>-3.49</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>LOTUSEYE</t>
+          <t>SHIVAMAUTO</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>107.18</v>
+        <v>15.48</v>
       </c>
       <c r="C78" t="n">
-        <v>110.94</v>
+        <v>15.9</v>
       </c>
       <c r="D78" t="n">
-        <v>3.51</v>
+        <v>2.71</v>
       </c>
       <c r="E78" t="b">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>106.66</v>
+        <v>15.99</v>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>-3.86</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>KDL</t>
+          <t>TARACHAND</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>118.9</v>
+        <v>57.27</v>
       </c>
       <c r="C79" t="n">
-        <v>123</v>
+        <v>58.8</v>
       </c>
       <c r="D79" t="n">
-        <v>3.45</v>
+        <v>2.67</v>
       </c>
       <c r="E79" t="b">
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>124.8</v>
+        <v>57.99</v>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>1.46</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BROOKS</t>
+          <t>SUTLEJTEX</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>57.03</v>
+        <v>29.22</v>
       </c>
       <c r="C80" t="n">
-        <v>58.98</v>
+        <v>30</v>
       </c>
       <c r="D80" t="n">
-        <v>3.42</v>
+        <v>2.67</v>
       </c>
       <c r="E80" t="b">
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>56.38</v>
+        <v>29.49</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>-4.41</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ROML</t>
+          <t>VALIANTORG</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>43.52</v>
+        <v>197.64</v>
       </c>
       <c r="C81" t="n">
-        <v>45</v>
+        <v>202.9</v>
       </c>
       <c r="D81" t="n">
-        <v>3.4</v>
+        <v>2.66</v>
       </c>
       <c r="E81" t="b">
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>44.4</v>
+        <v>237.16</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>-1.33</v>
+        <v>16.89</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PRAKASHSTL</t>
+          <t>BLAL</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>4.13</v>
+        <v>167.55</v>
       </c>
       <c r="C82" t="n">
-        <v>4.27</v>
+        <v>172</v>
       </c>
       <c r="D82" t="n">
-        <v>3.39</v>
+        <v>2.66</v>
       </c>
       <c r="E82" t="b">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>4.12</v>
+        <v>169.52</v>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>-3.51</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BOHRAIND</t>
+          <t>NDL</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>16.92</v>
+        <v>2.26</v>
       </c>
       <c r="C83" t="n">
-        <v>17.49</v>
+        <v>2.32</v>
       </c>
       <c r="D83" t="n">
-        <v>3.37</v>
+        <v>2.65</v>
       </c>
       <c r="E83" t="b">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>16.5</v>
+        <v>2.26</v>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>-5.66</v>
+        <v>-2.59</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MOKSH</t>
+          <t>COMPUSOFT</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>11.08</v>
+        <v>13.74</v>
       </c>
       <c r="C84" t="n">
-        <v>11.45</v>
+        <v>14.1</v>
       </c>
       <c r="D84" t="n">
-        <v>3.34</v>
+        <v>2.62</v>
       </c>
       <c r="E84" t="b">
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>10.98</v>
+        <v>13.83</v>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>-4.1</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>VHLTD</t>
+          <t>SHREERAMA</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>139.86</v>
+        <v>45.93</v>
       </c>
       <c r="C85" t="n">
-        <v>144.5</v>
+        <v>47.1</v>
       </c>
       <c r="D85" t="n">
-        <v>3.32</v>
+        <v>2.55</v>
       </c>
       <c r="E85" t="b">
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>139.25</v>
+        <v>48.26</v>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>-3.63</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AARON</t>
+          <t>GTECJAINX</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>140.27</v>
+        <v>19.21</v>
       </c>
       <c r="C86" t="n">
-        <v>144.9</v>
+        <v>19.7</v>
       </c>
       <c r="D86" t="n">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="E86" t="b">
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>141.06</v>
+        <v>19.09</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>-2.65</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>GALAPREC</t>
+          <t>LOKESHMACH</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>745.2</v>
+        <v>199.8</v>
       </c>
       <c r="C87" t="n">
-        <v>769.8</v>
+        <v>204.9</v>
       </c>
       <c r="D87" t="n">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="E87" t="b">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>742</v>
+        <v>206.3</v>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>-3.61</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PANACHE</t>
+          <t>RVHL</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>298.3</v>
+        <v>36.18</v>
       </c>
       <c r="C88" t="n">
-        <v>308</v>
+        <v>37.1</v>
       </c>
       <c r="D88" t="n">
-        <v>3.25</v>
+        <v>2.54</v>
       </c>
       <c r="E88" t="b">
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>309.5</v>
+        <v>37.29</v>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ALKALI</t>
+          <t>BTML</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>57.72</v>
+        <v>6.73</v>
       </c>
       <c r="C89" t="n">
-        <v>59.59</v>
+        <v>6.9</v>
       </c>
       <c r="D89" t="n">
-        <v>3.24</v>
+        <v>2.53</v>
       </c>
       <c r="E89" t="b">
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>57.25</v>
+        <v>6.8</v>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>-3.93</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SEJALLTD</t>
+          <t>URBANCO</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>503.75</v>
+        <v>110.11</v>
       </c>
       <c r="C90" t="n">
-        <v>519.95</v>
+        <v>112.9</v>
       </c>
       <c r="D90" t="n">
-        <v>3.22</v>
+        <v>2.53</v>
       </c>
       <c r="E90" t="b">
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>498.9</v>
+        <v>124.89</v>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>-4.05</v>
+        <v>10.62</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PATINTLOG</t>
+          <t>DSFCL</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>9.640000000000001</v>
+        <v>22.91</v>
       </c>
       <c r="C91" t="n">
-        <v>9.949999999999999</v>
+        <v>23.49</v>
       </c>
       <c r="D91" t="n">
-        <v>3.22</v>
+        <v>2.53</v>
       </c>
       <c r="E91" t="b">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>9.359999999999999</v>
+        <v>23.99</v>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>-5.93</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SYNCOMF</t>
+          <t>ADL</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>11.82</v>
+        <v>68.38</v>
       </c>
       <c r="C92" t="n">
-        <v>12.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="D92" t="n">
-        <v>3.21</v>
+        <v>2.52</v>
       </c>
       <c r="E92" t="b">
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>11.9</v>
+        <v>68</v>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
-        <v>-2.46</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MGEL</t>
+          <t>FEL</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>9.890000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="C93" t="n">
-        <v>10.2</v>
+        <v>0.41</v>
       </c>
       <c r="D93" t="n">
-        <v>3.13</v>
+        <v>2.5</v>
       </c>
       <c r="E93" t="b">
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>10.12</v>
+        <v>0.41</v>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
-        <v>-0.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>HEXATRADEX</t>
+          <t>ATLASCYCLE</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>160.02</v>
+        <v>83.42</v>
       </c>
       <c r="C94" t="n">
-        <v>165</v>
+        <v>85.5</v>
       </c>
       <c r="D94" t="n">
-        <v>3.11</v>
+        <v>2.49</v>
       </c>
       <c r="E94" t="b">
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>161.5</v>
+        <v>84</v>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>-2.12</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FLFL</t>
+          <t>ALKALI</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1.29</v>
+        <v>56.69</v>
       </c>
       <c r="C95" t="n">
-        <v>1.33</v>
+        <v>58.1</v>
       </c>
       <c r="D95" t="n">
-        <v>3.1</v>
+        <v>2.49</v>
       </c>
       <c r="E95" t="b">
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>1.33</v>
+        <v>57.21</v>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AIRAN</t>
+          <t>DCI</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>15.43</v>
+        <v>257.2</v>
       </c>
       <c r="C96" t="n">
-        <v>15.9</v>
+        <v>263.6</v>
       </c>
       <c r="D96" t="n">
-        <v>3.05</v>
+        <v>2.49</v>
       </c>
       <c r="E96" t="b">
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>15.55</v>
+        <v>265.8</v>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>-2.2</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>LOVABLE</t>
+          <t>DPWIRES</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>66.48</v>
+        <v>138.57</v>
       </c>
       <c r="C97" t="n">
-        <v>68.5</v>
+        <v>142</v>
       </c>
       <c r="D97" t="n">
-        <v>3.04</v>
+        <v>2.48</v>
       </c>
       <c r="E97" t="b">
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>67.59999999999999</v>
+        <v>143.08</v>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>-1.31</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>LIBAS</t>
+          <t>GEECEE</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>10.58</v>
+        <v>251.95</v>
       </c>
       <c r="C98" t="n">
-        <v>10.9</v>
+        <v>258.2</v>
       </c>
       <c r="D98" t="n">
-        <v>3.02</v>
+        <v>2.48</v>
       </c>
       <c r="E98" t="b">
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>10</v>
+        <v>256.05</v>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>-8.26</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>BIRLAMONEY</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>533.05</v>
+        <v>115.33</v>
       </c>
       <c r="C99" t="n">
-        <v>549</v>
+        <v>118.19</v>
       </c>
       <c r="D99" t="n">
-        <v>2.99</v>
+        <v>2.48</v>
       </c>
       <c r="E99" t="b">
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>525.3</v>
+        <v>118.25</v>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
-        <v>-4.32</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SADHAV</t>
+          <t>CEIGALL</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>95.2</v>
+        <v>279</v>
       </c>
       <c r="C100" t="n">
-        <v>98</v>
+        <v>285.9</v>
       </c>
       <c r="D100" t="n">
-        <v>2.94</v>
+        <v>2.47</v>
       </c>
       <c r="E100" t="b">
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>96</v>
+        <v>281.85</v>
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>-2.04</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ZODIACLOTH</t>
+          <t>UMIYA-MRO</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>67.98999999999999</v>
+        <v>79.06</v>
       </c>
       <c r="C101" t="n">
-        <v>69.98999999999999</v>
+        <v>81</v>
       </c>
       <c r="D101" t="n">
-        <v>2.94</v>
+        <v>2.45</v>
       </c>
       <c r="E101" t="b">
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>68.40000000000001</v>
+        <v>81</v>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>-2.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>GSLSU</t>
+          <t>SHRENIK</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>64.12</v>
+        <v>0.41</v>
       </c>
       <c r="C102" t="n">
-        <v>66</v>
+        <v>0.42</v>
       </c>
       <c r="D102" t="n">
-        <v>2.93</v>
+        <v>2.44</v>
       </c>
       <c r="E102" t="b">
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>62.57</v>
+        <v>0.41</v>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>-5.2</v>
+        <v>-2.38</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>RELCHEMQ</t>
+          <t>KOHINOOR</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>112.15</v>
+        <v>22.44</v>
       </c>
       <c r="C103" t="n">
-        <v>115.44</v>
+        <v>22.98</v>
       </c>
       <c r="D103" t="n">
-        <v>2.93</v>
+        <v>2.41</v>
       </c>
       <c r="E103" t="b">
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>111.5</v>
+        <v>22.77</v>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>-3.41</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ZENITHSTL</t>
+          <t>NARMADA</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>5.19</v>
+        <v>33.18</v>
       </c>
       <c r="C104" t="n">
-        <v>5.34</v>
+        <v>33.98</v>
       </c>
       <c r="D104" t="n">
-        <v>2.89</v>
+        <v>2.41</v>
       </c>
       <c r="E104" t="b">
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>5.22</v>
+        <v>33.82</v>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
-        <v>-2.25</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>BRNL</t>
+          <t>AKI</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>17.5</v>
+        <v>4.58</v>
       </c>
       <c r="C105" t="n">
-        <v>18</v>
+        <v>4.69</v>
       </c>
       <c r="D105" t="n">
-        <v>2.86</v>
+        <v>2.4</v>
       </c>
       <c r="E105" t="b">
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>17.42</v>
+        <v>5.07</v>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>-3.22</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SAURASHCEM</t>
+          <t>URAVIDEF</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>58.34</v>
+        <v>128.91</v>
       </c>
       <c r="C106" t="n">
-        <v>60</v>
+        <v>132</v>
       </c>
       <c r="D106" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="E106" t="b">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>59.34</v>
+        <v>128.14</v>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
-        <v>-1.1</v>
+        <v>-2.92</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ASHIMASYN</t>
+          <t>DUCON</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>14.35</v>
+        <v>2.93</v>
       </c>
       <c r="C107" t="n">
-        <v>14.75</v>
+        <v>3</v>
       </c>
       <c r="D107" t="n">
-        <v>2.79</v>
+        <v>2.39</v>
       </c>
       <c r="E107" t="b">
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>14.26</v>
+        <v>3.01</v>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>-3.32</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CYIENTDLM</t>
+          <t>SAMPANN</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>300.6</v>
+        <v>29.3</v>
       </c>
       <c r="C108" t="n">
-        <v>309</v>
+        <v>30</v>
       </c>
       <c r="D108" t="n">
-        <v>2.79</v>
+        <v>2.39</v>
       </c>
       <c r="E108" t="b">
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>333.75</v>
+        <v>29.73</v>
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
-        <v>8.01</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>DCM</t>
+          <t>SHEKHAWATI</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>58.39</v>
+        <v>11.82</v>
       </c>
       <c r="C109" t="n">
-        <v>60</v>
+        <v>12.1</v>
       </c>
       <c r="D109" t="n">
-        <v>2.76</v>
+        <v>2.37</v>
       </c>
       <c r="E109" t="b">
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>58.52</v>
+        <v>11.6</v>
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>-2.47</v>
+        <v>-4.13</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ANMOL</t>
+          <t>ZODIAC</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>10.6</v>
+        <v>235.49</v>
       </c>
       <c r="C110" t="n">
-        <v>10.89</v>
+        <v>241</v>
       </c>
       <c r="D110" t="n">
-        <v>2.74</v>
+        <v>2.34</v>
       </c>
       <c r="E110" t="b">
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>10.52</v>
+        <v>241.3</v>
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
-        <v>-3.4</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AIMTRON</t>
+          <t>SVPGLOB</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>743.4</v>
+        <v>2.58</v>
       </c>
       <c r="C111" t="n">
-        <v>763.7</v>
+        <v>2.64</v>
       </c>
       <c r="D111" t="n">
-        <v>2.73</v>
+        <v>2.33</v>
       </c>
       <c r="E111" t="b">
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>780.55</v>
+        <v>2.63</v>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>2.21</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>VIVIANA</t>
+          <t>SUPREMEPWR</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>621.15</v>
+        <v>163.2</v>
       </c>
       <c r="C112" t="n">
-        <v>637.9</v>
+        <v>167</v>
       </c>
       <c r="D112" t="n">
-        <v>2.7</v>
+        <v>2.33</v>
       </c>
       <c r="E112" t="b">
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>633</v>
+        <v>173</v>
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
-        <v>-0.77</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>RELIABLE</t>
+          <t>PILITA</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>111.99</v>
+        <v>7.33</v>
       </c>
       <c r="C113" t="n">
-        <v>115</v>
+        <v>7.5</v>
       </c>
       <c r="D113" t="n">
-        <v>2.69</v>
+        <v>2.32</v>
       </c>
       <c r="E113" t="b">
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>112.79</v>
+        <v>7.55</v>
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>-1.92</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>KAPSTON</t>
+          <t>FMNL</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>271.75</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="C114" t="n">
-        <v>279</v>
+        <v>8.4</v>
       </c>
       <c r="D114" t="n">
-        <v>2.67</v>
+        <v>2.31</v>
       </c>
       <c r="E114" t="b">
         <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>271.3</v>
+        <v>8.19</v>
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
-        <v>-2.76</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ASIANHOTNR</t>
+          <t>GAYAHWS</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>297.15</v>
+        <v>2.16</v>
       </c>
       <c r="C115" t="n">
-        <v>305</v>
+        <v>2.21</v>
       </c>
       <c r="D115" t="n">
-        <v>2.64</v>
+        <v>2.31</v>
       </c>
       <c r="E115" t="b">
         <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>295.05</v>
+        <v>2.22</v>
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>-3.26</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>UNITEDTEA</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>6528.5</v>
+        <v>521.95</v>
       </c>
       <c r="C116" t="n">
-        <v>6701</v>
+        <v>534</v>
       </c>
       <c r="D116" t="n">
-        <v>2.64</v>
+        <v>2.31</v>
       </c>
       <c r="E116" t="b">
         <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>6625.5</v>
+        <v>545.95</v>
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
-        <v>-1.13</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>LORDSCHLO</t>
+          <t>IGCL</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>116.92</v>
+        <v>57.84</v>
       </c>
       <c r="C117" t="n">
-        <v>120</v>
+        <v>59.17</v>
       </c>
       <c r="D117" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="E117" t="b">
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>121.53</v>
+        <v>59.51</v>
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>1.28</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>KOHINOOR</t>
+          <t>SHREEJISPG</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>22.9</v>
+        <v>364.65</v>
       </c>
       <c r="C118" t="n">
-        <v>23.5</v>
+        <v>373</v>
       </c>
       <c r="D118" t="n">
-        <v>2.62</v>
+        <v>2.29</v>
       </c>
       <c r="E118" t="b">
         <v>0</v>
       </c>
       <c r="F118" t="n">
-        <v>22.6</v>
+        <v>370.75</v>
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
-        <v>-3.83</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>TIGERLOGS</t>
+          <t>GOKUL</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>26.18</v>
+        <v>40.57</v>
       </c>
       <c r="C119" t="n">
-        <v>26.85</v>
+        <v>41.5</v>
       </c>
       <c r="D119" t="n">
-        <v>2.56</v>
+        <v>2.29</v>
       </c>
       <c r="E119" t="b">
         <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>26.25</v>
+        <v>42.14</v>
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
-        <v>-2.23</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>DISHTV</t>
+          <t>ASHIMASYN</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>2.34</v>
+        <v>13.98</v>
       </c>
       <c r="C120" t="n">
-        <v>2.4</v>
+        <v>14.3</v>
       </c>
       <c r="D120" t="n">
-        <v>2.56</v>
+        <v>2.29</v>
       </c>
       <c r="E120" t="b">
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>2.2</v>
+        <v>14.19</v>
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
-        <v>-8.33</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MOLDTECH</t>
+          <t>SAGARDEEP</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>123.47</v>
+        <v>22.48</v>
       </c>
       <c r="C121" t="n">
-        <v>126.6</v>
+        <v>22.99</v>
       </c>
       <c r="D121" t="n">
-        <v>2.54</v>
+        <v>2.27</v>
       </c>
       <c r="E121" t="b">
         <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>123.17</v>
+        <v>23.49</v>
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
-        <v>-2.71</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>LIBAS</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>127.56</v>
+        <v>10.36</v>
       </c>
       <c r="C122" t="n">
-        <v>130.8</v>
+        <v>10.59</v>
       </c>
       <c r="D122" t="n">
-        <v>2.54</v>
+        <v>2.22</v>
       </c>
       <c r="E122" t="b">
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>126.66</v>
+        <v>10.15</v>
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
-        <v>-3.17</v>
+        <v>-4.15</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>HAPPYFORGE</t>
+          <t>VENUSREM</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>1264</v>
+        <v>914.9</v>
       </c>
       <c r="C123" t="n">
-        <v>1296</v>
+        <v>935</v>
       </c>
       <c r="D123" t="n">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="E123" t="b">
         <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>1277.1</v>
+        <v>916.55</v>
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>-1.46</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>RKEC</t>
+          <t>UNIVASTU</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>35.99</v>
+        <v>64</v>
       </c>
       <c r="C124" t="n">
-        <v>36.9</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D124" t="n">
-        <v>2.53</v>
+        <v>2.19</v>
       </c>
       <c r="E124" t="b">
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>35.71</v>
+        <v>64.75</v>
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
-        <v>-3.22</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>PASHUPATI</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>86.81</v>
+        <v>983.5</v>
       </c>
       <c r="C125" t="n">
-        <v>88.98999999999999</v>
+        <v>1005</v>
       </c>
       <c r="D125" t="n">
-        <v>2.51</v>
+        <v>2.19</v>
       </c>
       <c r="E125" t="b">
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>88.98999999999999</v>
+        <v>993.3</v>
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>0</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>FEL</t>
+          <t>GOKULAGRO</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.4</v>
+        <v>191</v>
       </c>
       <c r="C126" t="n">
-        <v>0.41</v>
+        <v>195.15</v>
       </c>
       <c r="D126" t="n">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="E126" t="b">
         <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>0.4</v>
+        <v>195.71</v>
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
-        <v>-2.44</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SHRENIK</t>
+          <t>OMAXAUTO</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.4</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="C127" t="n">
-        <v>0.41</v>
+        <v>97.98</v>
       </c>
       <c r="D127" t="n">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="E127" t="b">
         <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>0.41</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>NRL</t>
+          <t>RPPL</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>51.57</v>
+        <v>15.66</v>
       </c>
       <c r="C128" t="n">
-        <v>52.85</v>
+        <v>16</v>
       </c>
       <c r="D128" t="n">
-        <v>2.48</v>
+        <v>2.17</v>
       </c>
       <c r="E128" t="b">
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>50.9</v>
+        <v>16</v>
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
-        <v>-3.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>PLAZACABLE</t>
+          <t>VAISHALI</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>34.29</v>
+        <v>6.07</v>
       </c>
       <c r="C129" t="n">
-        <v>35.14</v>
+        <v>6.2</v>
       </c>
       <c r="D129" t="n">
-        <v>2.48</v>
+        <v>2.14</v>
       </c>
       <c r="E129" t="b">
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>34.41</v>
+        <v>6.14</v>
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
-        <v>-2.08</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>UCAL</t>
+          <t>HPL</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>97.29000000000001</v>
+        <v>275.15</v>
       </c>
       <c r="C130" t="n">
-        <v>99.7</v>
+        <v>281</v>
       </c>
       <c r="D130" t="n">
-        <v>2.48</v>
+        <v>2.13</v>
       </c>
       <c r="E130" t="b">
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>97.59999999999999</v>
+        <v>291.6</v>
       </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
-        <v>-2.11</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>HILINFRA</t>
+          <t>PEARLPOLY</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>49.14</v>
+        <v>16.63</v>
       </c>
       <c r="C131" t="n">
-        <v>50.36</v>
+        <v>16.98</v>
       </c>
       <c r="D131" t="n">
-        <v>2.48</v>
+        <v>2.1</v>
       </c>
       <c r="E131" t="b">
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>49</v>
+        <v>16.6</v>
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
-        <v>-2.7</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SOUTHWEST</t>
+          <t>JARO</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>183.47</v>
+        <v>471.35</v>
       </c>
       <c r="C132" t="n">
-        <v>188</v>
+        <v>481.25</v>
       </c>
       <c r="D132" t="n">
-        <v>2.47</v>
+        <v>2.1</v>
       </c>
       <c r="E132" t="b">
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>189.97</v>
+        <v>487.3</v>
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
-        <v>1.05</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>CORDSCABLE</t>
+          <t>REGAAL</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>146.14</v>
+        <v>75.64</v>
       </c>
       <c r="C133" t="n">
-        <v>149.6</v>
+        <v>77.23</v>
       </c>
       <c r="D133" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="E133" t="b">
         <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>146.45</v>
+        <v>75.31</v>
       </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
-        <v>-2.11</v>
+        <v>-2.49</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>BORANA</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>105.6</v>
+        <v>375.2</v>
       </c>
       <c r="C134" t="n">
-        <v>108.1</v>
+        <v>382.95</v>
       </c>
       <c r="D134" t="n">
-        <v>2.37</v>
+        <v>2.07</v>
       </c>
       <c r="E134" t="b">
         <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>104.6</v>
+        <v>378</v>
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
-        <v>-3.24</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>TARACHAND</t>
+          <t>BHAGYANGR</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>57.59</v>
+        <v>147.69</v>
       </c>
       <c r="C135" t="n">
-        <v>58.95</v>
+        <v>150.74</v>
       </c>
       <c r="D135" t="n">
-        <v>2.36</v>
+        <v>2.07</v>
       </c>
       <c r="E135" t="b">
         <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>57.82</v>
+        <v>149.99</v>
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
-        <v>-1.92</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>DAMODARIND</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>23.43</v>
+        <v>88.43000000000001</v>
       </c>
       <c r="C136" t="n">
-        <v>23.98</v>
+        <v>90.25</v>
       </c>
       <c r="D136" t="n">
-        <v>2.35</v>
+        <v>2.06</v>
       </c>
       <c r="E136" t="b">
         <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>23.4</v>
+        <v>92</v>
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
-        <v>-2.42</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>TIL</t>
+          <t>RPPINFRA</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>196.39</v>
+        <v>70.76000000000001</v>
       </c>
       <c r="C137" t="n">
-        <v>200.99</v>
+        <v>72.2</v>
       </c>
       <c r="D137" t="n">
-        <v>2.34</v>
+        <v>2.04</v>
       </c>
       <c r="E137" t="b">
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>191.75</v>
+        <v>71.94</v>
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
-        <v>-4.6</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>KMEW</t>
+          <t>PATINTLOG</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>1538.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="C138" t="n">
-        <v>1574.7</v>
+        <v>9.49</v>
       </c>
       <c r="D138" t="n">
-        <v>2.33</v>
+        <v>2.04</v>
       </c>
       <c r="E138" t="b">
         <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>1526.8</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
-        <v>-3.04</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>AMDIND</t>
+          <t>NIRMAN</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>35.19</v>
+        <v>46.6</v>
       </c>
       <c r="C139" t="n">
-        <v>36</v>
+        <v>47.55</v>
       </c>
       <c r="D139" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="E139" t="b">
         <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>35.36</v>
+        <v>47</v>
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
-        <v>-1.78</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ABINFRA</t>
+          <t>TVSELECT</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>17.01</v>
+        <v>395</v>
       </c>
       <c r="C140" t="n">
-        <v>17.4</v>
+        <v>403</v>
       </c>
       <c r="D140" t="n">
-        <v>2.29</v>
+        <v>2.03</v>
       </c>
       <c r="E140" t="b">
         <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>17.16</v>
+        <v>416.75</v>
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
-        <v>-1.38</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ASTRON</t>
+          <t>EBGNG</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>3.95</v>
+        <v>376.4</v>
       </c>
       <c r="C141" t="n">
-        <v>4.04</v>
+        <v>384</v>
       </c>
       <c r="D141" t="n">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="E141" t="b">
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>3.94</v>
+        <v>382.5</v>
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
-        <v>-2.48</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>SUNDARAM</t>
+          <t>LAMBODHARA</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>1.32</v>
+        <v>92.53</v>
       </c>
       <c r="C142" t="n">
-        <v>1.35</v>
+        <v>94.39</v>
       </c>
       <c r="D142" t="n">
-        <v>2.27</v>
+        <v>2.01</v>
       </c>
       <c r="E142" t="b">
         <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>1.29</v>
+        <v>103.75</v>
       </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
-        <v>-4.44</v>
+        <v>9.92</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>DIFFNKG</t>
+          <t>CREATIVEYE</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>239.75</v>
+        <v>6.47</v>
       </c>
       <c r="C143" t="n">
-        <v>245.2</v>
+        <v>6.6</v>
       </c>
       <c r="D143" t="n">
-        <v>2.27</v>
+        <v>2.01</v>
       </c>
       <c r="E143" t="b">
         <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>240.75</v>
+        <v>6.61</v>
       </c>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
-        <v>-1.81</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>EIHAHOTELS</t>
+          <t>ALGOQUANT</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>302</v>
+        <v>55</v>
       </c>
       <c r="C144" t="n">
-        <v>308.8</v>
+        <v>56.1</v>
       </c>
       <c r="D144" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="E144" t="b">
         <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>301.2</v>
+        <v>56.87</v>
       </c>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
-        <v>-2.46</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CEINSYS</t>
+          <t>MASON</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>938.45</v>
+        <v>145</v>
       </c>
       <c r="C145" t="n">
-        <v>959.6</v>
+        <v>147.9</v>
       </c>
       <c r="D145" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="E145" t="b">
         <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>945.5</v>
+        <v>147.9</v>
       </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
-        <v>-1.47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>KANANIIND</t>
+          <t>NATCAPSUQ</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>1.34</v>
+        <v>151.28</v>
       </c>
       <c r="C146" t="n">
-        <v>1.37</v>
+        <v>154.3</v>
       </c>
       <c r="D146" t="n">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="E146" t="b">
         <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>1.36</v>
+        <v>154.3</v>
       </c>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
-        <v>-0.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>NDLVENTURE</t>
+          <t>PRITIKAUTO</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>113.48</v>
+        <v>11.49</v>
       </c>
       <c r="C147" t="n">
-        <v>116</v>
+        <v>11.72</v>
       </c>
       <c r="D147" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="E147" t="b">
         <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>112.48</v>
+        <v>12.02</v>
       </c>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
-        <v>-3.03</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ISFT</t>
+          <t>HEXATRADEX</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>65.55</v>
+        <v>160.05</v>
       </c>
       <c r="C148" t="n">
-        <v>67</v>
+        <v>163.25</v>
       </c>
       <c r="D148" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="E148" t="b">
         <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>68</v>
+        <v>162.94</v>
       </c>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
-        <v>1.49</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>PACEDIGITK</t>
+          <t>ACCURACY</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>163.9</v>
+        <v>4</v>
       </c>
       <c r="C149" t="n">
-        <v>167.5</v>
+        <v>4.08</v>
       </c>
       <c r="D149" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="E149" t="b">
         <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>169.82</v>
+        <v>4</v>
       </c>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
-        <v>1.39</v>
+        <v>-1.96</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>DPABHUSHAN</t>
+          <t>PLAZACABLE</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>977.5</v>
+        <v>33.82</v>
       </c>
       <c r="C150" t="n">
-        <v>999</v>
+        <v>34.49</v>
       </c>
       <c r="D150" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="E150" t="b">
         <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>972.3</v>
+        <v>34.22</v>
       </c>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
-        <v>-2.67</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>NGIL</t>
+          <t>MEGATHERM</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>25.25</v>
+        <v>194.1</v>
       </c>
       <c r="C151" t="n">
-        <v>25.8</v>
+        <v>197.95</v>
       </c>
       <c r="D151" t="n">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="E151" t="b">
         <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>25.48</v>
+        <v>193.2</v>
       </c>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
-        <v>-1.24</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>GATECH</t>
+          <t>SEYAIND</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.46</v>
+        <v>9.59</v>
       </c>
       <c r="C152" t="n">
-        <v>0.47</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="D152" t="n">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="E152" t="b">
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>0.47</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="n">
@@ -4387,1275 +4387,1275 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>PRECOT</t>
+          <t>FLAIR</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>484.55</v>
+        <v>302.8</v>
       </c>
       <c r="C153" t="n">
-        <v>495</v>
+        <v>308.8</v>
       </c>
       <c r="D153" t="n">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="E153" t="b">
         <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>490.8</v>
+        <v>315.2</v>
       </c>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="n">
-        <v>-0.85</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>MANBA</t>
+          <t>BROOKS</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>123.34</v>
+        <v>55.4</v>
       </c>
       <c r="C154" t="n">
-        <v>126</v>
+        <v>56.49</v>
       </c>
       <c r="D154" t="n">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="E154" t="b">
         <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>120.3</v>
+        <v>57</v>
       </c>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="n">
-        <v>-4.52</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ASAL</t>
+          <t>RKSWAMY</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>410.95</v>
+        <v>89.14</v>
       </c>
       <c r="C155" t="n">
-        <v>419.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D155" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="E155" t="b">
         <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>417.75</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="n">
-        <v>-0.49</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>BALAXI</t>
+          <t>SECMARK</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>17.67</v>
+        <v>108.18</v>
       </c>
       <c r="C156" t="n">
-        <v>18.05</v>
+        <v>110.3</v>
       </c>
       <c r="D156" t="n">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="E156" t="b">
         <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>18.18</v>
+        <v>111</v>
       </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="n">
-        <v>0.72</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>INDOWIND</t>
+          <t>GOLDTECH</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>8.359999999999999</v>
+        <v>39.82</v>
       </c>
       <c r="C157" t="n">
-        <v>8.539999999999999</v>
+        <v>40.6</v>
       </c>
       <c r="D157" t="n">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="E157" t="b">
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>8.31</v>
+        <v>40.62</v>
       </c>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="n">
-        <v>-2.69</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>TNTELE</t>
+          <t>TPHQ</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>8.42</v>
+        <v>0.51</v>
       </c>
       <c r="C158" t="n">
-        <v>8.6</v>
+        <v>0.52</v>
       </c>
       <c r="D158" t="n">
-        <v>2.14</v>
+        <v>1.96</v>
       </c>
       <c r="E158" t="b">
         <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>8.539999999999999</v>
+        <v>0.52</v>
       </c>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="n">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>BORANA</t>
+          <t>SEMAC</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>369.1</v>
+        <v>259.89</v>
       </c>
       <c r="C159" t="n">
-        <v>376.95</v>
+        <v>264.95</v>
       </c>
       <c r="D159" t="n">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="E159" t="b">
         <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>374.75</v>
+        <v>281.8</v>
       </c>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="n">
-        <v>-0.58</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>GOLDENTOBC</t>
+          <t>EMMBI</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>28.69</v>
+        <v>79.06</v>
       </c>
       <c r="C160" t="n">
-        <v>29.3</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D160" t="n">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="E160" t="b">
         <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>28.68</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="n">
-        <v>-2.12</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>PREMEXPLN</t>
+          <t>ARFIN</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>431.85</v>
+        <v>76.42</v>
       </c>
       <c r="C161" t="n">
-        <v>441</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="D161" t="n">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="E161" t="b">
         <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>443</v>
+        <v>74.75</v>
       </c>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="n">
-        <v>0.45</v>
+        <v>-4.04</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>SBC</t>
+          <t>SHAH</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>31.34</v>
+        <v>4.69</v>
       </c>
       <c r="C162" t="n">
-        <v>32</v>
+        <v>4.78</v>
       </c>
       <c r="D162" t="n">
-        <v>2.11</v>
+        <v>1.92</v>
       </c>
       <c r="E162" t="b">
         <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>31.77</v>
+        <v>4.77</v>
       </c>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="n">
-        <v>-0.72</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>VISAKAIND</t>
+          <t>SHANTI</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>56.8</v>
+        <v>6.32</v>
       </c>
       <c r="C163" t="n">
-        <v>58</v>
+        <v>6.44</v>
       </c>
       <c r="D163" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="E163" t="b">
         <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>56.82</v>
+        <v>6.49</v>
       </c>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="n">
-        <v>-2.03</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>FISCHER</t>
+          <t>PANSARI</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>33.2</v>
+        <v>265.15</v>
       </c>
       <c r="C164" t="n">
-        <v>33.9</v>
+        <v>270.15</v>
       </c>
       <c r="D164" t="n">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="E164" t="b">
         <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>33.91</v>
+        <v>266</v>
       </c>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="n">
-        <v>0.03</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SURANASOL</t>
+          <t>KUANTUM</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>21.29</v>
+        <v>76.06</v>
       </c>
       <c r="C165" t="n">
-        <v>21.74</v>
+        <v>77.48</v>
       </c>
       <c r="D165" t="n">
-        <v>2.11</v>
+        <v>1.87</v>
       </c>
       <c r="E165" t="b">
         <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>21.37</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="n">
-        <v>-1.7</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>STALLION</t>
+          <t>ASMS</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>113.42</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="C166" t="n">
-        <v>115.8</v>
+        <v>8.27</v>
       </c>
       <c r="D166" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="E166" t="b">
         <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>118.3</v>
+        <v>8.5</v>
       </c>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="n">
-        <v>2.16</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>UTIAMC</t>
+          <t>ZIMLAB</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>959.85</v>
+        <v>70.19</v>
       </c>
       <c r="C167" t="n">
-        <v>980</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="D167" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="E167" t="b">
         <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>972.25</v>
+        <v>69.66</v>
       </c>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="n">
-        <v>-0.79</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>AKSHOPTFBR</t>
+          <t>CRAMC</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>4.28</v>
+        <v>234.2</v>
       </c>
       <c r="C168" t="n">
-        <v>4.37</v>
+        <v>238.5</v>
       </c>
       <c r="D168" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="E168" t="b">
         <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>4.58</v>
+        <v>238.2</v>
       </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="n">
-        <v>4.81</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>TFL</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>11.95</v>
+        <v>1026.6</v>
       </c>
       <c r="C169" t="n">
-        <v>12.2</v>
+        <v>1045.5</v>
       </c>
       <c r="D169" t="n">
-        <v>2.09</v>
+        <v>1.84</v>
       </c>
       <c r="E169" t="b">
         <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>13.36</v>
+        <v>1084.2</v>
       </c>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="n">
-        <v>9.51</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>AFIL</t>
+          <t>DGCONTENT</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>8.140000000000001</v>
+        <v>23.08</v>
       </c>
       <c r="C170" t="n">
-        <v>8.31</v>
+        <v>23.5</v>
       </c>
       <c r="D170" t="n">
-        <v>2.09</v>
+        <v>1.82</v>
       </c>
       <c r="E170" t="b">
         <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>8.539999999999999</v>
+        <v>23.2</v>
       </c>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="n">
-        <v>2.77</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>NAVKARURB</t>
+          <t>ZENITHSTL</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.96</v>
+        <v>5.02</v>
       </c>
       <c r="C171" t="n">
-        <v>0.98</v>
+        <v>5.11</v>
       </c>
       <c r="D171" t="n">
-        <v>2.08</v>
+        <v>1.79</v>
       </c>
       <c r="E171" t="b">
         <v>0</v>
       </c>
       <c r="F171" t="n">
-        <v>0.96</v>
+        <v>5.01</v>
       </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="n">
-        <v>-2.04</v>
+        <v>-1.96</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>VMARCIND</t>
+          <t>VIVIDHA</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>682.8</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C172" t="n">
-        <v>697</v>
+        <v>0.57</v>
       </c>
       <c r="D172" t="n">
-        <v>2.08</v>
+        <v>1.79</v>
       </c>
       <c r="E172" t="b">
         <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>680.6</v>
+        <v>0.59</v>
       </c>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="n">
-        <v>-2.35</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>GOLDTECH</t>
+          <t>PARSVNATH</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>38.49</v>
+        <v>6.78</v>
       </c>
       <c r="C173" t="n">
-        <v>39.29</v>
+        <v>6.9</v>
       </c>
       <c r="D173" t="n">
-        <v>2.08</v>
+        <v>1.77</v>
       </c>
       <c r="E173" t="b">
         <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>39.66</v>
+        <v>6.81</v>
       </c>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="n">
-        <v>0.9399999999999999</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>MODINATUR</t>
+          <t>VIRINCHI</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>285.15</v>
+        <v>16.95</v>
       </c>
       <c r="C174" t="n">
-        <v>291</v>
+        <v>17.25</v>
       </c>
       <c r="D174" t="n">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="E174" t="b">
         <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>298.5</v>
+        <v>17.11</v>
       </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="n">
-        <v>2.58</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ENERGYDEV</t>
+          <t>AXISCADES</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>15.09</v>
+        <v>1384.5</v>
       </c>
       <c r="C175" t="n">
-        <v>15.4</v>
+        <v>1408.8</v>
       </c>
       <c r="D175" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="E175" t="b">
         <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>15.01</v>
+        <v>1453.7</v>
       </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="n">
-        <v>-2.53</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>PASHUPATI</t>
+          <t>THELEELA</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>990</v>
+        <v>407.85</v>
       </c>
       <c r="C176" t="n">
-        <v>1010</v>
+        <v>415</v>
       </c>
       <c r="D176" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="E176" t="b">
         <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>998</v>
+        <v>411.65</v>
       </c>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="n">
-        <v>-1.19</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>GANESHIN</t>
+          <t>MAHAPEXLTD</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>84.2</v>
+        <v>117.76</v>
       </c>
       <c r="C177" t="n">
-        <v>85.90000000000001</v>
+        <v>119.8</v>
       </c>
       <c r="D177" t="n">
-        <v>2.02</v>
+        <v>1.73</v>
       </c>
       <c r="E177" t="b">
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>83.90000000000001</v>
+        <v>118.92</v>
       </c>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="n">
-        <v>-2.33</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>AVROIND</t>
+          <t>GMBREW</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>137.36</v>
+        <v>963.35</v>
       </c>
       <c r="C178" t="n">
-        <v>140.14</v>
+        <v>980</v>
       </c>
       <c r="D178" t="n">
-        <v>2.02</v>
+        <v>1.73</v>
       </c>
       <c r="E178" t="b">
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>136.51</v>
+        <v>1029</v>
       </c>
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="n">
-        <v>-2.59</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>IRMENERGY</t>
+          <t>TINNARUBR</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>200.56</v>
+        <v>628.2</v>
       </c>
       <c r="C179" t="n">
-        <v>204.6</v>
+        <v>639</v>
       </c>
       <c r="D179" t="n">
-        <v>2.01</v>
+        <v>1.72</v>
       </c>
       <c r="E179" t="b">
         <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>201.28</v>
+        <v>630</v>
       </c>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="n">
-        <v>-1.62</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>APEX</t>
+          <t>MODIS</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>328.4</v>
+        <v>304.5</v>
       </c>
       <c r="C180" t="n">
-        <v>335</v>
+        <v>309.7</v>
       </c>
       <c r="D180" t="n">
-        <v>2.01</v>
+        <v>1.71</v>
       </c>
       <c r="E180" t="b">
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>331.5</v>
+        <v>315.1</v>
       </c>
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="n">
-        <v>-1.04</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>HPAL</t>
+          <t>VARDMNPOLY</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>31.01</v>
+        <v>7.62</v>
       </c>
       <c r="C181" t="n">
-        <v>31.63</v>
+        <v>7.75</v>
       </c>
       <c r="D181" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="E181" t="b">
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>31.62</v>
+        <v>7.64</v>
       </c>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="n">
-        <v>-0.03</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>UTTAMSUGAR</t>
+          <t>LPDC</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>189.9</v>
+        <v>5.89</v>
       </c>
       <c r="C182" t="n">
-        <v>193.7</v>
+        <v>5.99</v>
       </c>
       <c r="D182" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="E182" t="b">
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>193</v>
+        <v>5.99</v>
       </c>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="n">
-        <v>-0.36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>RAMRAT</t>
+          <t>SICALLOG</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>299.65</v>
+        <v>65.87</v>
       </c>
       <c r="C183" t="n">
-        <v>305.65</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="D183" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="E183" t="b">
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>298</v>
+        <v>63.5</v>
       </c>
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="n">
-        <v>-2.5</v>
+        <v>-5.21</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>HCL-INSYS</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>669.95</v>
+        <v>11.79</v>
       </c>
       <c r="C184" t="n">
-        <v>683.3</v>
+        <v>11.99</v>
       </c>
       <c r="D184" t="n">
-        <v>1.99</v>
+        <v>1.7</v>
       </c>
       <c r="E184" t="b">
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>675.85</v>
+        <v>11.97</v>
       </c>
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="n">
-        <v>-1.09</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>RAJRILTD</t>
+          <t>RHETAN</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>21.17</v>
+        <v>24.83</v>
       </c>
       <c r="C185" t="n">
-        <v>21.59</v>
+        <v>25.25</v>
       </c>
       <c r="D185" t="n">
-        <v>1.98</v>
+        <v>1.69</v>
       </c>
       <c r="E185" t="b">
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>21.28</v>
+        <v>25.03</v>
       </c>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="n">
-        <v>-1.44</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>COASTCORP</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>360.9</v>
+        <v>46.22</v>
       </c>
       <c r="C186" t="n">
-        <v>368</v>
+        <v>47</v>
       </c>
       <c r="D186" t="n">
-        <v>1.97</v>
+        <v>1.69</v>
       </c>
       <c r="E186" t="b">
         <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>368.85</v>
+        <v>46.16</v>
       </c>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="n">
-        <v>0.23</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>JAYSREETEA</t>
+          <t>BALAXI</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>87.52</v>
+        <v>17.7</v>
       </c>
       <c r="C187" t="n">
-        <v>89.23999999999999</v>
+        <v>18</v>
       </c>
       <c r="D187" t="n">
-        <v>1.97</v>
+        <v>1.69</v>
       </c>
       <c r="E187" t="b">
         <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>89.3</v>
+        <v>18.04</v>
       </c>
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>BHARATWIRE</t>
+          <t>INDIQUBE</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>153.97</v>
+        <v>138.66</v>
       </c>
       <c r="C188" t="n">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="D188" t="n">
-        <v>1.97</v>
+        <v>1.69</v>
       </c>
       <c r="E188" t="b">
         <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>154.68</v>
+        <v>142.42</v>
       </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="n">
-        <v>-1.48</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>EXXARO</t>
+          <t>UNITEDPOLY</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>6.61</v>
+        <v>26.24</v>
       </c>
       <c r="C189" t="n">
-        <v>6.74</v>
+        <v>26.68</v>
       </c>
       <c r="D189" t="n">
-        <v>1.97</v>
+        <v>1.68</v>
       </c>
       <c r="E189" t="b">
         <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>6.68</v>
+        <v>26.85</v>
       </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="n">
-        <v>-0.89</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ALMONDZ</t>
+          <t>OSWALPUMPS</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>13.73</v>
+        <v>302.9</v>
       </c>
       <c r="C190" t="n">
-        <v>14</v>
+        <v>308</v>
       </c>
       <c r="D190" t="n">
-        <v>1.97</v>
+        <v>1.68</v>
       </c>
       <c r="E190" t="b">
         <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>14.3</v>
+        <v>316.6</v>
       </c>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="n">
-        <v>2.14</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>SUPREMEENG</t>
+          <t>BVCL</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>1.02</v>
+        <v>37.2</v>
       </c>
       <c r="C191" t="n">
-        <v>1.04</v>
+        <v>37.82</v>
       </c>
       <c r="D191" t="n">
-        <v>1.96</v>
+        <v>1.67</v>
       </c>
       <c r="E191" t="b">
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>1.07</v>
+        <v>37.65</v>
       </c>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="n">
-        <v>2.88</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ATLANTAELE</t>
+          <t>UTKARSHBNK</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>979.75</v>
+        <v>11.97</v>
       </c>
       <c r="C192" t="n">
-        <v>999</v>
+        <v>12.17</v>
       </c>
       <c r="D192" t="n">
-        <v>1.96</v>
+        <v>1.67</v>
       </c>
       <c r="E192" t="b">
         <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>991.55</v>
+        <v>12.04</v>
       </c>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="n">
-        <v>-0.75</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>UNITEDPOLY</t>
+          <t>TCPLPACK</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>25.01</v>
+        <v>2409.6</v>
       </c>
       <c r="C193" t="n">
-        <v>25.5</v>
+        <v>2449.9</v>
       </c>
       <c r="D193" t="n">
-        <v>1.96</v>
+        <v>1.67</v>
       </c>
       <c r="E193" t="b">
         <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>25.98</v>
+        <v>2442.8</v>
       </c>
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="n">
-        <v>1.88</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SAKUMA</t>
+          <t>GLOBECIVIL</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>1.53</v>
+        <v>42.68</v>
       </c>
       <c r="C194" t="n">
-        <v>1.56</v>
+        <v>43.39</v>
       </c>
       <c r="D194" t="n">
-        <v>1.96</v>
+        <v>1.66</v>
       </c>
       <c r="E194" t="b">
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>1.53</v>
+        <v>43.57</v>
       </c>
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="n">
-        <v>-1.92</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>FIEMIND</t>
+          <t>MAWANASUG</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>2005</v>
+        <v>77.13</v>
       </c>
       <c r="C195" t="n">
-        <v>2044</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="D195" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="E195" t="b">
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>1995.6</v>
+        <v>78.48</v>
       </c>
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="n">
-        <v>-2.37</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>TEJASNET</t>
+          <t>KILITCH</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>446.85</v>
+        <v>319.5</v>
       </c>
       <c r="C196" t="n">
-        <v>455.5</v>
+        <v>324.75</v>
       </c>
       <c r="D196" t="n">
-        <v>1.94</v>
+        <v>1.64</v>
       </c>
       <c r="E196" t="b">
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>437.65</v>
+        <v>318.4</v>
       </c>
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="n">
-        <v>-3.92</v>
+        <v>-1.96</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>KRITINUT</t>
+          <t>IFBAGRO</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>61.76</v>
+        <v>683.3</v>
       </c>
       <c r="C197" t="n">
-        <v>62.95</v>
+        <v>694.5</v>
       </c>
       <c r="D197" t="n">
-        <v>1.93</v>
+        <v>1.64</v>
       </c>
       <c r="E197" t="b">
         <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>62.27</v>
+        <v>711.05</v>
       </c>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="n">
-        <v>-1.08</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>IDBI</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>713.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="C198" t="n">
-        <v>726.95</v>
+        <v>75.31</v>
       </c>
       <c r="D198" t="n">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="E198" t="b">
         <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>714.55</v>
+        <v>75.17</v>
       </c>
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="n">
-        <v>-1.71</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>KRITIKA</t>
+          <t>BIRLACABLE</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>5.18</v>
+        <v>129.73</v>
       </c>
       <c r="C199" t="n">
-        <v>5.28</v>
+        <v>131.84</v>
       </c>
       <c r="D199" t="n">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="E199" t="b">
         <v>0</v>
       </c>
       <c r="F199" t="n">
-        <v>5.48</v>
+        <v>135.01</v>
       </c>
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="n">
-        <v>3.79</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>JSWINFRA</t>
+          <t>AURIONPRO</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>250.4</v>
+        <v>821.2</v>
       </c>
       <c r="C200" t="n">
-        <v>255.2</v>
+        <v>834.5</v>
       </c>
       <c r="D200" t="n">
-        <v>1.92</v>
+        <v>1.62</v>
       </c>
       <c r="E200" t="b">
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>255.15</v>
+        <v>839.35</v>
       </c>
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="n">
-        <v>-0.02</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SVPGLOB</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>2.63</v>
+        <v>1472.1</v>
       </c>
       <c r="C201" t="n">
-        <v>2.68</v>
+        <v>1495.8</v>
       </c>
       <c r="D201" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="E201" t="b">
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>2.55</v>
+        <v>1554.4</v>
       </c>
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="n">
-        <v>-4.85</v>
+        <v>3.92</v>
       </c>
     </row>
   </sheetData>

--- a/data/trending_momentum_stocks.xlsx
+++ b/data/trending_momentum_stocks.xlsx
@@ -461,5201 +461,5197 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MITTAL</t>
+          <t>RADAAN</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.85</v>
+        <v>2.86</v>
       </c>
       <c r="C2" t="n">
-        <v>0.99</v>
+        <v>3.42</v>
       </c>
       <c r="D2" t="n">
-        <v>16.47</v>
+        <v>19.58</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.98</v>
+        <v>2.93</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>-1.01</v>
+        <v>-14.33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>INSPIRE</t>
+          <t>USHAFIN</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.65</v>
+        <v>32.4</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>36.9</v>
       </c>
       <c r="D3" t="n">
-        <v>13.99</v>
+        <v>13.89</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>10.95</v>
+        <v>35</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>-0.45</v>
+        <v>-5.15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VINEETLAB</t>
+          <t>KAYTEX</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29.01</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>78.8</v>
       </c>
       <c r="D4" t="n">
-        <v>10.31</v>
+        <v>10.83</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>29.97</v>
+        <v>73.95</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>-6.34</v>
+        <v>-6.15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VICTORYEV</t>
+          <t>INFOMEDIA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.3</v>
+        <v>4.99</v>
       </c>
       <c r="C5" t="n">
-        <v>15.75</v>
+        <v>5.48</v>
       </c>
       <c r="D5" t="n">
-        <v>10.14</v>
+        <v>9.82</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>4.85</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>-4.76</v>
+        <v>-11.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CYBERMEDIA</t>
+          <t>EMKAYTOOLS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13.1</v>
+        <v>91</v>
       </c>
       <c r="C6" t="n">
-        <v>14.35</v>
+        <v>98</v>
       </c>
       <c r="D6" t="n">
-        <v>9.539999999999999</v>
+        <v>7.69</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>13.51</v>
+        <v>95</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>-5.85</v>
+        <v>-3.06</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ENSER</t>
+          <t>ENCOMPAS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11.6</v>
+        <v>241.75</v>
       </c>
       <c r="C7" t="n">
-        <v>12.65</v>
+        <v>259</v>
       </c>
       <c r="D7" t="n">
-        <v>9.050000000000001</v>
+        <v>7.14</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>11.3</v>
+        <v>253.75</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>-10.67</v>
+        <v>-2.03</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DELTIC</t>
+          <t>VALIANTORG</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>36</v>
+        <v>237.16</v>
       </c>
       <c r="C8" t="n">
-        <v>39</v>
+        <v>250</v>
       </c>
       <c r="D8" t="n">
-        <v>8.33</v>
+        <v>5.41</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>36.1</v>
+        <v>264.56</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>-7.44</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DPEL</t>
+          <t>KORE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>359.35</v>
+        <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>387</v>
+        <v>102.9</v>
       </c>
       <c r="D9" t="n">
-        <v>7.69</v>
+        <v>5</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>392.5</v>
+        <v>102.9</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LASA</t>
+          <t>GJL</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7.3</v>
+        <v>263.3</v>
       </c>
       <c r="C10" t="n">
-        <v>7.8</v>
+        <v>276.45</v>
       </c>
       <c r="D10" t="n">
-        <v>6.85</v>
+        <v>4.99</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>7.47</v>
+        <v>276.45</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>-4.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ICDSLTD</t>
+          <t>TIJARIA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>47.14</v>
+        <v>4.62</v>
       </c>
       <c r="C11" t="n">
-        <v>50.2</v>
+        <v>4.85</v>
       </c>
       <c r="D11" t="n">
-        <v>6.49</v>
+        <v>4.98</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>47.28</v>
+        <v>4.41</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>-5.82</v>
+        <v>-9.07</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DCMSIL</t>
+          <t>DPEL</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>84.23999999999999</v>
+        <v>391.55</v>
       </c>
       <c r="C12" t="n">
-        <v>89</v>
+        <v>411</v>
       </c>
       <c r="D12" t="n">
-        <v>5.65</v>
+        <v>4.97</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>86.28</v>
+        <v>392</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>-3.06</v>
+        <v>-4.62</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PAVNAIND</t>
+          <t>UMESLTD</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18.02</v>
+        <v>6.48</v>
       </c>
       <c r="C13" t="n">
-        <v>19</v>
+        <v>6.8</v>
       </c>
       <c r="D13" t="n">
-        <v>5.44</v>
+        <v>4.94</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>18.12</v>
+        <v>6.17</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>-4.63</v>
+        <v>-9.26</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SILGO</t>
+          <t>APSISAERO</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>73.98999999999999</v>
+        <v>160.65</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>168.5</v>
       </c>
       <c r="D14" t="n">
-        <v>5.42</v>
+        <v>4.89</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>72.75</v>
+        <v>168.65</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>-6.73</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CTE</t>
+          <t>VHLTD</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24.42</v>
+        <v>140</v>
       </c>
       <c r="C15" t="n">
-        <v>25.7</v>
+        <v>146.8</v>
       </c>
       <c r="D15" t="n">
-        <v>5.24</v>
+        <v>4.86</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>24.67</v>
+        <v>138.6</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>-4.01</v>
+        <v>-5.59</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EUROTEXIND</t>
+          <t>BLUECOAST</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12.5</v>
+        <v>19.66</v>
       </c>
       <c r="C16" t="n">
-        <v>13.12</v>
+        <v>20.59</v>
       </c>
       <c r="D16" t="n">
-        <v>4.96</v>
+        <v>4.73</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>12.58</v>
+        <v>20.49</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>-4.12</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>VIJIFIN</t>
+          <t>ORTEL</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.03</v>
+        <v>1.76</v>
       </c>
       <c r="C17" t="n">
-        <v>3.18</v>
+        <v>1.84</v>
       </c>
       <c r="D17" t="n">
-        <v>4.95</v>
+        <v>4.55</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>3.18</v>
+        <v>1.8</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-2.17</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BONLON</t>
+          <t>BAFNAPH</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>37.99</v>
+        <v>114.77</v>
       </c>
       <c r="C18" t="n">
-        <v>39.85</v>
+        <v>119.99</v>
       </c>
       <c r="D18" t="n">
-        <v>4.9</v>
+        <v>4.55</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>39.7</v>
+        <v>120.5</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>-0.38</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SIDDHICOTS</t>
+          <t>CAPTRUST</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>28.05</v>
+        <v>11.72</v>
       </c>
       <c r="C19" t="n">
-        <v>29.4</v>
+        <v>12.24</v>
       </c>
       <c r="D19" t="n">
-        <v>4.81</v>
+        <v>4.44</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>29.2</v>
+        <v>11.9</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>-0.68</v>
+        <v>-2.78</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BMETRICS</t>
+          <t>COOLCAPS</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>40.9</v>
+        <v>23.85</v>
       </c>
       <c r="C20" t="n">
-        <v>42.85</v>
+        <v>24.9</v>
       </c>
       <c r="D20" t="n">
-        <v>4.77</v>
+        <v>4.4</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>42.5</v>
+        <v>24.4</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>-0.82</v>
+        <v>-2.01</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HBSL</t>
+          <t>EXXARO</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>48.97</v>
+        <v>6.9</v>
       </c>
       <c r="C21" t="n">
-        <v>51.3</v>
+        <v>7.2</v>
       </c>
       <c r="D21" t="n">
-        <v>4.76</v>
+        <v>4.35</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>48.52</v>
+        <v>6.94</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>-5.42</v>
+        <v>-3.61</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COOLCAPS</t>
+          <t>OPTIVALUE</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>23.4</v>
+        <v>80.45</v>
       </c>
       <c r="C22" t="n">
-        <v>24.5</v>
+        <v>83.95</v>
       </c>
       <c r="D22" t="n">
-        <v>4.7</v>
+        <v>4.35</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>24.55</v>
+        <v>80.5</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.2</v>
+        <v>-4.11</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GUJRAFFIA</t>
+          <t>MITTAL</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>36.48</v>
+        <v>0.96</v>
       </c>
       <c r="C23" t="n">
-        <v>38.19</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>4.69</v>
+        <v>4.17</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>37.92</v>
+        <v>1.03</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>-0.71</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SUPREMEENG</t>
+          <t>VCL</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.07</v>
+        <v>1.44</v>
       </c>
       <c r="C24" t="n">
-        <v>1.12</v>
+        <v>1.5</v>
       </c>
       <c r="D24" t="n">
-        <v>4.67</v>
+        <v>4.17</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>1.12</v>
+        <v>1.49</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORIENTLTD</t>
+          <t>TREEHOUSE</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>59.68</v>
+        <v>8.4</v>
       </c>
       <c r="C25" t="n">
-        <v>62.4</v>
+        <v>8.74</v>
       </c>
       <c r="D25" t="n">
-        <v>4.56</v>
+        <v>4.05</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>62.89</v>
+        <v>8.5</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>0.79</v>
+        <v>-2.75</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DELTAMAGNT</t>
+          <t>SUPERSPIN</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>55</v>
+        <v>4.52</v>
       </c>
       <c r="C26" t="n">
-        <v>57.5</v>
+        <v>4.7</v>
       </c>
       <c r="D26" t="n">
-        <v>4.55</v>
+        <v>3.98</v>
       </c>
       <c r="E26" t="b">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>56.16</v>
+        <v>4.36</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>-2.33</v>
+        <v>-7.23</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GOLDENTOBC</t>
+          <t>PURPLEUTED</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27.51</v>
+        <v>284.15</v>
       </c>
       <c r="C27" t="n">
-        <v>28.75</v>
+        <v>295.4</v>
       </c>
       <c r="D27" t="n">
-        <v>4.51</v>
+        <v>3.96</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>26.23</v>
+        <v>280</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>-8.77</v>
+        <v>-5.21</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>JPPOWER</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>13.98</v>
+        <v>515.65</v>
       </c>
       <c r="C28" t="n">
-        <v>14.6</v>
+        <v>535.65</v>
       </c>
       <c r="D28" t="n">
-        <v>4.43</v>
+        <v>3.88</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>15.04</v>
+        <v>560.75</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>3.01</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>HEXT</t>
+          <t>GOLDENTOBC</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>407</v>
+        <v>27.64</v>
       </c>
       <c r="C29" t="n">
-        <v>425</v>
+        <v>28.65</v>
       </c>
       <c r="D29" t="n">
-        <v>4.42</v>
+        <v>3.65</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>422.55</v>
+        <v>28.47</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>-0.58</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EQUIPPP</t>
+          <t>PYRAMID</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>18.16</v>
+        <v>143.35</v>
       </c>
       <c r="C30" t="n">
-        <v>18.96</v>
+        <v>148.5</v>
       </c>
       <c r="D30" t="n">
-        <v>4.41</v>
+        <v>3.59</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>18.55</v>
+        <v>148.01</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>-2.16</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CANARYS</t>
+          <t>AURIGROW</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>20.4</v>
+        <v>0.28</v>
       </c>
       <c r="C31" t="n">
-        <v>21.3</v>
+        <v>0.29</v>
       </c>
       <c r="D31" t="n">
-        <v>4.41</v>
+        <v>3.57</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>20.5</v>
+        <v>0.29</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>-3.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>KEEPLEARN</t>
+          <t>DCMNVL</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.85</v>
+        <v>111.36</v>
       </c>
       <c r="C32" t="n">
-        <v>1.93</v>
+        <v>115.3</v>
       </c>
       <c r="D32" t="n">
-        <v>4.32</v>
+        <v>3.54</v>
       </c>
       <c r="E32" t="b">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>1.84</v>
+        <v>111</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>-4.66</v>
+        <v>-3.73</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BAFNAPH</t>
+          <t>UMAEXPORTS</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>109.31</v>
+        <v>22.21</v>
       </c>
       <c r="C33" t="n">
-        <v>113.99</v>
+        <v>22.99</v>
       </c>
       <c r="D33" t="n">
-        <v>4.28</v>
+        <v>3.51</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>114.77</v>
+        <v>22.38</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>0.68</v>
+        <v>-2.65</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ENERGYDEV</t>
+          <t>SIGMAADV</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>14.63</v>
+        <v>159.06</v>
       </c>
       <c r="C34" t="n">
-        <v>15.25</v>
+        <v>164.63</v>
       </c>
       <c r="D34" t="n">
-        <v>4.24</v>
+        <v>3.5</v>
       </c>
       <c r="E34" t="b">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>14.67</v>
+        <v>167.01</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>-3.8</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DEVIT</t>
+          <t>DGCONTENT</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>28.73</v>
+        <v>23.87</v>
       </c>
       <c r="C35" t="n">
-        <v>29.9</v>
+        <v>24.7</v>
       </c>
       <c r="D35" t="n">
-        <v>4.07</v>
+        <v>3.48</v>
       </c>
       <c r="E35" t="b">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>29.21</v>
+        <v>24.5</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>-2.31</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AIRAN</t>
+          <t>SHIVAMILLS</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>15.28</v>
+        <v>54.16</v>
       </c>
       <c r="C36" t="n">
-        <v>15.89</v>
+        <v>56</v>
       </c>
       <c r="D36" t="n">
-        <v>3.99</v>
+        <v>3.4</v>
       </c>
       <c r="E36" t="b">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>15.5</v>
+        <v>55.44</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>-2.45</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AKG</t>
+          <t>SHANTI</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10.8</v>
+        <v>6.27</v>
       </c>
       <c r="C37" t="n">
-        <v>11.23</v>
+        <v>6.48</v>
       </c>
       <c r="D37" t="n">
-        <v>3.98</v>
+        <v>3.35</v>
       </c>
       <c r="E37" t="b">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>10.92</v>
+        <v>6.37</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>-2.76</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NOIDATOLL</t>
+          <t>SITINET</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3.52</v>
+        <v>0.33</v>
       </c>
       <c r="C38" t="n">
-        <v>3.66</v>
+        <v>0.34</v>
       </c>
       <c r="D38" t="n">
-        <v>3.98</v>
+        <v>3.03</v>
       </c>
       <c r="E38" t="b">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>3.65</v>
+        <v>0.32</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>-0.27</v>
+        <v>-5.88</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PIGL</t>
+          <t>ZODIACLOTH</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>95.3</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="C39" t="n">
-        <v>98.98999999999999</v>
+        <v>70.39</v>
       </c>
       <c r="D39" t="n">
-        <v>3.87</v>
+        <v>2.98</v>
       </c>
       <c r="E39" t="b">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>101.44</v>
+        <v>68.98</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>2.47</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MAGNUM</t>
+          <t>GEEKAYWIRE</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>18.8</v>
+        <v>20.99</v>
       </c>
       <c r="C40" t="n">
-        <v>19.5</v>
+        <v>21.6</v>
       </c>
       <c r="D40" t="n">
-        <v>3.72</v>
+        <v>2.91</v>
       </c>
       <c r="E40" t="b">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>18.99</v>
+        <v>21.3</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>-2.62</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AURIGROW</t>
+          <t>GRINFRA</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.27</v>
+        <v>925.05</v>
       </c>
       <c r="C41" t="n">
-        <v>0.28</v>
+        <v>951.2</v>
       </c>
       <c r="D41" t="n">
-        <v>3.7</v>
+        <v>2.83</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0.28</v>
+        <v>918</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>-3.49</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>EXXARO</t>
+          <t>ASTRON</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>6.61</v>
+        <v>3.93</v>
       </c>
       <c r="C42" t="n">
-        <v>6.85</v>
+        <v>4.04</v>
       </c>
       <c r="D42" t="n">
-        <v>3.63</v>
+        <v>2.8</v>
       </c>
       <c r="E42" t="b">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>6.94</v>
+        <v>3.92</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>1.31</v>
+        <v>-2.97</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>RKEC</t>
+          <t>RUCHINFRA</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>35.31</v>
+        <v>5.05</v>
       </c>
       <c r="C43" t="n">
-        <v>36.57</v>
+        <v>5.19</v>
       </c>
       <c r="D43" t="n">
-        <v>3.57</v>
+        <v>2.77</v>
       </c>
       <c r="E43" t="b">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>36.32</v>
+        <v>5.15</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>-0.68</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PALASHSECU</t>
+          <t>SHYAMDHANI</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>85.38</v>
+        <v>62.25</v>
       </c>
       <c r="C44" t="n">
-        <v>88.40000000000001</v>
+        <v>63.95</v>
       </c>
       <c r="D44" t="n">
-        <v>3.54</v>
+        <v>2.73</v>
       </c>
       <c r="E44" t="b">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>87.48999999999999</v>
+        <v>60.35</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>-1.03</v>
+        <v>-5.63</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ANIKINDS</t>
+          <t>KEEPLEARN</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>39.15</v>
+        <v>1.84</v>
       </c>
       <c r="C45" t="n">
-        <v>40.5</v>
+        <v>1.89</v>
       </c>
       <c r="D45" t="n">
-        <v>3.45</v>
+        <v>2.72</v>
       </c>
       <c r="E45" t="b">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>39.46</v>
+        <v>1.88</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>-2.57</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>VERTOZ</t>
+          <t>DNAMEDIA</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>34.8</v>
+        <v>3.39</v>
       </c>
       <c r="C46" t="n">
-        <v>36</v>
+        <v>3.48</v>
       </c>
       <c r="D46" t="n">
-        <v>3.45</v>
+        <v>2.65</v>
       </c>
       <c r="E46" t="b">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>36.38</v>
+        <v>3.43</v>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>1.06</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GFLLIMITED</t>
+          <t>RVHL</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>43.36</v>
+        <v>36.16</v>
       </c>
       <c r="C47" t="n">
-        <v>44.8</v>
+        <v>37.1</v>
       </c>
       <c r="D47" t="n">
-        <v>3.32</v>
+        <v>2.6</v>
       </c>
       <c r="E47" t="b">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>44.37</v>
+        <v>36.69</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>-0.96</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>VITAL</t>
+          <t>PAVNAIND</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>39.45</v>
+        <v>18.13</v>
       </c>
       <c r="C48" t="n">
-        <v>40.75</v>
+        <v>18.6</v>
       </c>
       <c r="D48" t="n">
-        <v>3.3</v>
+        <v>2.59</v>
       </c>
       <c r="E48" t="b">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>40</v>
+        <v>18.18</v>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>-1.84</v>
+        <v>-2.26</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>RUCHINFRA</t>
+          <t>SETUINFRA</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4.87</v>
+        <v>0.39</v>
       </c>
       <c r="C49" t="n">
-        <v>5.03</v>
+        <v>0.4</v>
       </c>
       <c r="D49" t="n">
-        <v>3.29</v>
+        <v>2.56</v>
       </c>
       <c r="E49" t="b">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>4.98</v>
+        <v>0.39</v>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>-0.99</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ORIENTALTL</t>
+          <t>OSWALSEEDS</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>5.23</v>
+        <v>11.7</v>
       </c>
       <c r="C50" t="n">
-        <v>5.4</v>
+        <v>12</v>
       </c>
       <c r="D50" t="n">
-        <v>3.25</v>
+        <v>2.56</v>
       </c>
       <c r="E50" t="b">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>5.36</v>
+        <v>11.42</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>-0.74</v>
+        <v>-4.83</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BAGFILMS</t>
+          <t>ARIHANTSUP</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4.34</v>
+        <v>221.25</v>
       </c>
       <c r="C51" t="n">
-        <v>4.48</v>
+        <v>226.9</v>
       </c>
       <c r="D51" t="n">
-        <v>3.23</v>
+        <v>2.55</v>
       </c>
       <c r="E51" t="b">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>4.49</v>
+        <v>219.5</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>0.22</v>
+        <v>-3.26</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GSS</t>
+          <t>WEWIN</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>11.13</v>
+        <v>40.96</v>
       </c>
       <c r="C52" t="n">
-        <v>11.49</v>
+        <v>42</v>
       </c>
       <c r="D52" t="n">
-        <v>3.23</v>
+        <v>2.54</v>
       </c>
       <c r="E52" t="b">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>11.14</v>
+        <v>39.78</v>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>-3.05</v>
+        <v>-5.29</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NEPHROCARE</t>
+          <t>ANTGRAPHIC</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>66.8</v>
+        <v>0.8</v>
       </c>
       <c r="C53" t="n">
-        <v>68.95</v>
+        <v>0.82</v>
       </c>
       <c r="D53" t="n">
-        <v>3.22</v>
+        <v>2.5</v>
       </c>
       <c r="E53" t="b">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>68</v>
+        <v>0.8</v>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>-1.38</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>IMPEXFERRO</t>
+          <t>VISASTEEL</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1.56</v>
+        <v>32.38</v>
       </c>
       <c r="C54" t="n">
-        <v>1.61</v>
+        <v>33.19</v>
       </c>
       <c r="D54" t="n">
-        <v>3.21</v>
+        <v>2.5</v>
       </c>
       <c r="E54" t="b">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>1.58</v>
+        <v>31.75</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>-1.86</v>
+        <v>-4.34</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>VGL</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>106.6</v>
+        <v>59.71</v>
       </c>
       <c r="C55" t="n">
-        <v>110</v>
+        <v>61.2</v>
       </c>
       <c r="D55" t="n">
-        <v>3.19</v>
+        <v>2.5</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>111.9</v>
+        <v>59.8</v>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>1.73</v>
+        <v>-2.29</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ALLCARGO</t>
+          <t>SMLT</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>7.84</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="C56" t="n">
-        <v>8.09</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="D56" t="n">
-        <v>3.19</v>
+        <v>2.49</v>
       </c>
       <c r="E56" t="b">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>8.24</v>
+        <v>68.83</v>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>1.85</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>VGL</t>
+          <t>IMPEXFERRO</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>59.12</v>
+        <v>1.61</v>
       </c>
       <c r="C57" t="n">
-        <v>61</v>
+        <v>1.65</v>
       </c>
       <c r="D57" t="n">
-        <v>3.18</v>
+        <v>2.48</v>
       </c>
       <c r="E57" t="b">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>59.4</v>
+        <v>1.61</v>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>-2.62</v>
+        <v>-2.42</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>HAVISHA</t>
+          <t>JHS</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1.26</v>
+        <v>8.08</v>
       </c>
       <c r="C58" t="n">
-        <v>1.3</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="D58" t="n">
-        <v>3.17</v>
+        <v>2.48</v>
       </c>
       <c r="E58" t="b">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>1.24</v>
+        <v>8.1</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>-4.62</v>
+        <v>-2.17</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>XTGLOBAL</t>
+          <t>REGENCERAM</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>30.26</v>
+        <v>41.88</v>
       </c>
       <c r="C59" t="n">
-        <v>31.21</v>
+        <v>42.9</v>
       </c>
       <c r="D59" t="n">
-        <v>3.14</v>
+        <v>2.44</v>
       </c>
       <c r="E59" t="b">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>30.65</v>
+        <v>42.9</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>-1.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>KKJEWELS</t>
+          <t>FEL</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>95</v>
+        <v>0.41</v>
       </c>
       <c r="C60" t="n">
-        <v>97.95</v>
+        <v>0.42</v>
       </c>
       <c r="D60" t="n">
-        <v>3.11</v>
+        <v>2.44</v>
       </c>
       <c r="E60" t="b">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>95.5</v>
+        <v>0.42</v>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FISCHER</t>
+          <t>ABCOTS</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>34.86</v>
+        <v>402.4</v>
       </c>
       <c r="C61" t="n">
-        <v>35.94</v>
+        <v>412</v>
       </c>
       <c r="D61" t="n">
-        <v>3.1</v>
+        <v>2.39</v>
       </c>
       <c r="E61" t="b">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>36.6</v>
+        <v>406.4</v>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>1.84</v>
+        <v>-1.36</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>RNFI</t>
+          <t>HAVISHA</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>247.25</v>
+        <v>1.26</v>
       </c>
       <c r="C62" t="n">
-        <v>254.9</v>
+        <v>1.29</v>
       </c>
       <c r="D62" t="n">
-        <v>3.09</v>
+        <v>2.38</v>
       </c>
       <c r="E62" t="b">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>253</v>
+        <v>1.24</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>-0.75</v>
+        <v>-3.88</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SIGMA</t>
+          <t>AERONEU</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>39.77</v>
+        <v>64.28</v>
       </c>
       <c r="C63" t="n">
-        <v>40.99</v>
+        <v>65.8</v>
       </c>
       <c r="D63" t="n">
-        <v>3.07</v>
+        <v>2.36</v>
       </c>
       <c r="E63" t="b">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>40.61</v>
+        <v>64.5</v>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>-0.93</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SITINET</t>
+          <t>CYBERMEDIA</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.33</v>
+        <v>13.67</v>
       </c>
       <c r="C64" t="n">
-        <v>0.34</v>
+        <v>13.99</v>
       </c>
       <c r="D64" t="n">
-        <v>3.03</v>
+        <v>2.34</v>
       </c>
       <c r="E64" t="b">
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>0.33</v>
+        <v>13.56</v>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>-2.94</v>
+        <v>-3.07</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>APCL</t>
+          <t>IFBAGRO</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>112.59</v>
+        <v>717.45</v>
       </c>
       <c r="C65" t="n">
-        <v>116</v>
+        <v>733.95</v>
       </c>
       <c r="D65" t="n">
-        <v>3.03</v>
+        <v>2.3</v>
       </c>
       <c r="E65" t="b">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>116.09</v>
+        <v>729.35</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>0.08</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BYKE</t>
+          <t>PASHUPATI</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>33.01</v>
+        <v>987.65</v>
       </c>
       <c r="C66" t="n">
-        <v>34</v>
+        <v>1010</v>
       </c>
       <c r="D66" t="n">
-        <v>3</v>
+        <v>2.26</v>
       </c>
       <c r="E66" t="b">
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>33.4</v>
+        <v>985.15</v>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>-1.76</v>
+        <v>-2.46</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>RAJSREESUG</t>
+          <t>CELEBRITY</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>26.9</v>
+        <v>7.63</v>
       </c>
       <c r="C67" t="n">
-        <v>27.7</v>
+        <v>7.8</v>
       </c>
       <c r="D67" t="n">
-        <v>2.97</v>
+        <v>2.23</v>
       </c>
       <c r="E67" t="b">
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>27.64</v>
+        <v>7.46</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>-0.22</v>
+        <v>-4.36</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SIKKO</t>
+          <t>OWAIS</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>4.56</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="C68" t="n">
-        <v>4.69</v>
+        <v>99</v>
       </c>
       <c r="D68" t="n">
-        <v>2.85</v>
+        <v>2.17</v>
       </c>
       <c r="E68" t="b">
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>4.66</v>
+        <v>101.7</v>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>-0.64</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>NATHBIOGEN</t>
+          <t>EIFFL</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>140.41</v>
+        <v>231.26</v>
       </c>
       <c r="C69" t="n">
-        <v>144.4</v>
+        <v>236.25</v>
       </c>
       <c r="D69" t="n">
-        <v>2.84</v>
+        <v>2.16</v>
       </c>
       <c r="E69" t="b">
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>143</v>
+        <v>230.61</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>-0.97</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GVPTECH</t>
+          <t>ACEINTEG</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>5.74</v>
+        <v>16.73</v>
       </c>
       <c r="C70" t="n">
-        <v>5.9</v>
+        <v>17.09</v>
       </c>
       <c r="D70" t="n">
-        <v>2.79</v>
+        <v>2.15</v>
       </c>
       <c r="E70" t="b">
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>5.8</v>
+        <v>16.95</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>-1.69</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SELMC</t>
+          <t>MURUDCERA</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>29.07</v>
+        <v>30.07</v>
       </c>
       <c r="C71" t="n">
-        <v>29.88</v>
+        <v>30.7</v>
       </c>
       <c r="D71" t="n">
-        <v>2.79</v>
+        <v>2.1</v>
       </c>
       <c r="E71" t="b">
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>29.16</v>
+        <v>30.1</v>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>-2.41</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SOMANYCERA</t>
+          <t>GULFPETRO</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>362.95</v>
+        <v>29.29</v>
       </c>
       <c r="C72" t="n">
-        <v>373</v>
+        <v>29.9</v>
       </c>
       <c r="D72" t="n">
-        <v>2.77</v>
+        <v>2.08</v>
       </c>
       <c r="E72" t="b">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>383.35</v>
+        <v>28.77</v>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>2.77</v>
+        <v>-3.78</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>NEXTMEDIA</t>
+          <t>CORALFINAC</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>5.06</v>
+        <v>31.33</v>
       </c>
       <c r="C73" t="n">
-        <v>5.2</v>
+        <v>31.98</v>
       </c>
       <c r="D73" t="n">
-        <v>2.77</v>
+        <v>2.07</v>
       </c>
       <c r="E73" t="b">
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>4.93</v>
+        <v>31.85</v>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>-5.19</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CROWN</t>
+          <t>SANCO</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>118.73</v>
+        <v>2.42</v>
       </c>
       <c r="C74" t="n">
-        <v>122</v>
+        <v>2.47</v>
       </c>
       <c r="D74" t="n">
-        <v>2.75</v>
+        <v>2.07</v>
       </c>
       <c r="E74" t="b">
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>119.2</v>
+        <v>2.3</v>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>-2.3</v>
+        <v>-6.88</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DELPHIFX</t>
+          <t>NOIDATOLL</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>10.31</v>
+        <v>3.39</v>
       </c>
       <c r="C75" t="n">
-        <v>10.59</v>
+        <v>3.46</v>
       </c>
       <c r="D75" t="n">
-        <v>2.72</v>
+        <v>2.06</v>
       </c>
       <c r="E75" t="b">
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>10.44</v>
+        <v>3.35</v>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>-1.42</v>
+        <v>-3.18</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AEPL</t>
+          <t>CCHHL</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>17.62</v>
+        <v>12.19</v>
       </c>
       <c r="C76" t="n">
-        <v>18.1</v>
+        <v>12.44</v>
       </c>
       <c r="D76" t="n">
-        <v>2.72</v>
+        <v>2.05</v>
       </c>
       <c r="E76" t="b">
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>17.95</v>
+        <v>11.82</v>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>-0.83</v>
+        <v>-4.98</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CLEANMAX</t>
+          <t>TGBHOTELS</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>890.7</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="C77" t="n">
-        <v>914.9</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="D77" t="n">
-        <v>2.72</v>
+        <v>2.05</v>
       </c>
       <c r="E77" t="b">
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>883</v>
+        <v>8.84</v>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>-3.49</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SHIVAMAUTO</t>
+          <t>SIGMA</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>15.48</v>
+        <v>40.18</v>
       </c>
       <c r="C78" t="n">
-        <v>15.9</v>
+        <v>41</v>
       </c>
       <c r="D78" t="n">
-        <v>2.71</v>
+        <v>2.04</v>
       </c>
       <c r="E78" t="b">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>15.99</v>
+        <v>40.43</v>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>0.57</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>TARACHAND</t>
+          <t>SUTLEJTEX</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>57.27</v>
+        <v>29.4</v>
       </c>
       <c r="C79" t="n">
-        <v>58.8</v>
+        <v>30</v>
       </c>
       <c r="D79" t="n">
-        <v>2.67</v>
+        <v>2.04</v>
       </c>
       <c r="E79" t="b">
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>57.99</v>
+        <v>29.3</v>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>-1.38</v>
+        <v>-2.33</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SUTLEJTEX</t>
+          <t>SURANAT&amp;P</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>29.22</v>
+        <v>17.74</v>
       </c>
       <c r="C80" t="n">
-        <v>30</v>
+        <v>18.1</v>
       </c>
       <c r="D80" t="n">
-        <v>2.67</v>
+        <v>2.03</v>
       </c>
       <c r="E80" t="b">
         <v>0</v>
       </c>
-      <c r="F80" t="n">
-        <v>29.49</v>
-      </c>
+      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
-      <c r="H80" t="n">
-        <v>-1.7</v>
-      </c>
+      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>VALIANTORG</t>
+          <t>HINDCOMPOS</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>197.64</v>
+        <v>387.15</v>
       </c>
       <c r="C81" t="n">
-        <v>202.9</v>
+        <v>395</v>
       </c>
       <c r="D81" t="n">
-        <v>2.66</v>
+        <v>2.03</v>
       </c>
       <c r="E81" t="b">
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>237.16</v>
+        <v>385.5</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>16.89</v>
+        <v>-2.41</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BLAL</t>
+          <t>RUBFILA</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>167.55</v>
+        <v>62.86</v>
       </c>
       <c r="C82" t="n">
-        <v>172</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="D82" t="n">
-        <v>2.66</v>
+        <v>1.97</v>
       </c>
       <c r="E82" t="b">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>169.52</v>
+        <v>61.68</v>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>-1.44</v>
+        <v>-3.78</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>NDL</t>
+          <t>INTENTECH</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2.26</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="C83" t="n">
-        <v>2.32</v>
+        <v>89.8</v>
       </c>
       <c r="D83" t="n">
-        <v>2.65</v>
+        <v>1.96</v>
       </c>
       <c r="E83" t="b">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>2.26</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>-2.59</v>
+        <v>-3.84</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>COMPUSOFT</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>13.74</v>
+        <v>6.67</v>
       </c>
       <c r="C84" t="n">
-        <v>14.1</v>
+        <v>6.8</v>
       </c>
       <c r="D84" t="n">
-        <v>2.62</v>
+        <v>1.95</v>
       </c>
       <c r="E84" t="b">
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>13.83</v>
+        <v>7.29</v>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>-1.91</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SHREERAMA</t>
+          <t>AKI</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>45.93</v>
+        <v>4.65</v>
       </c>
       <c r="C85" t="n">
-        <v>47.1</v>
+        <v>4.74</v>
       </c>
       <c r="D85" t="n">
-        <v>2.55</v>
+        <v>1.94</v>
       </c>
       <c r="E85" t="b">
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>48.26</v>
+        <v>4.61</v>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>2.46</v>
+        <v>-2.74</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>GTECJAINX</t>
+          <t>SPCENET</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>19.21</v>
+        <v>4.15</v>
       </c>
       <c r="C86" t="n">
-        <v>19.7</v>
+        <v>4.23</v>
       </c>
       <c r="D86" t="n">
-        <v>2.55</v>
+        <v>1.93</v>
       </c>
       <c r="E86" t="b">
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>19.09</v>
+        <v>4.2</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>-3.1</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>LOKESHMACH</t>
+          <t>SILGO</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>199.8</v>
+        <v>72.01000000000001</v>
       </c>
       <c r="C87" t="n">
-        <v>204.9</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D87" t="n">
-        <v>2.55</v>
+        <v>1.93</v>
       </c>
       <c r="E87" t="b">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>206.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>0.68</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>RVHL</t>
+          <t>SURANI</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>36.18</v>
+        <v>59.85</v>
       </c>
       <c r="C88" t="n">
-        <v>37.1</v>
+        <v>61</v>
       </c>
       <c r="D88" t="n">
-        <v>2.54</v>
+        <v>1.92</v>
       </c>
       <c r="E88" t="b">
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>37.29</v>
+        <v>71.8</v>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>0.51</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BTML</t>
+          <t>PIONEEREMB</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>6.73</v>
+        <v>25.32</v>
       </c>
       <c r="C89" t="n">
-        <v>6.9</v>
+        <v>25.8</v>
       </c>
       <c r="D89" t="n">
-        <v>2.53</v>
+        <v>1.9</v>
       </c>
       <c r="E89" t="b">
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>6.8</v>
+        <v>24.98</v>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>-1.45</v>
+        <v>-3.18</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>URBANCO</t>
+          <t>MANAKSTEEL</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>110.11</v>
+        <v>53.54</v>
       </c>
       <c r="C90" t="n">
-        <v>112.9</v>
+        <v>54.55</v>
       </c>
       <c r="D90" t="n">
-        <v>2.53</v>
+        <v>1.89</v>
       </c>
       <c r="E90" t="b">
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>124.89</v>
+        <v>53.2</v>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>10.62</v>
+        <v>-2.47</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DSFCL</t>
+          <t>HARDWYN</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>22.91</v>
+        <v>17.95</v>
       </c>
       <c r="C91" t="n">
-        <v>23.49</v>
+        <v>18.29</v>
       </c>
       <c r="D91" t="n">
-        <v>2.53</v>
+        <v>1.89</v>
       </c>
       <c r="E91" t="b">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>23.99</v>
+        <v>17.94</v>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>2.13</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ADL</t>
+          <t>WANBURY</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>68.38</v>
+        <v>249.35</v>
       </c>
       <c r="C92" t="n">
-        <v>70.09999999999999</v>
+        <v>253.95</v>
       </c>
       <c r="D92" t="n">
-        <v>2.52</v>
+        <v>1.84</v>
       </c>
       <c r="E92" t="b">
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>68</v>
+        <v>244</v>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
-        <v>-3</v>
+        <v>-3.92</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FEL</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.4</v>
+        <v>531.2</v>
       </c>
       <c r="C93" t="n">
-        <v>0.41</v>
+        <v>541</v>
       </c>
       <c r="D93" t="n">
-        <v>2.5</v>
+        <v>1.84</v>
       </c>
       <c r="E93" t="b">
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>0.41</v>
+        <v>534.5</v>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ATLASCYCLE</t>
+          <t>XTGLOBAL</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>83.42</v>
+        <v>30.99</v>
       </c>
       <c r="C94" t="n">
-        <v>85.5</v>
+        <v>31.55</v>
       </c>
       <c r="D94" t="n">
-        <v>2.49</v>
+        <v>1.81</v>
       </c>
       <c r="E94" t="b">
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>84</v>
+        <v>30.55</v>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>-1.75</v>
+        <v>-3.17</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ALKALI</t>
+          <t>AXITA</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>56.69</v>
+        <v>8.85</v>
       </c>
       <c r="C95" t="n">
-        <v>58.1</v>
+        <v>9.01</v>
       </c>
       <c r="D95" t="n">
-        <v>2.49</v>
+        <v>1.81</v>
       </c>
       <c r="E95" t="b">
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>57.21</v>
+        <v>8.75</v>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>-1.53</v>
+        <v>-2.89</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DCI</t>
+          <t>GOYALALUM</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>257.2</v>
+        <v>6.12</v>
       </c>
       <c r="C96" t="n">
-        <v>263.6</v>
+        <v>6.23</v>
       </c>
       <c r="D96" t="n">
-        <v>2.49</v>
+        <v>1.8</v>
       </c>
       <c r="E96" t="b">
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>265.8</v>
+        <v>6.15</v>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>0.83</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>DPWIRES</t>
+          <t>NILASPACES</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>138.57</v>
+        <v>12.97</v>
       </c>
       <c r="C97" t="n">
-        <v>142</v>
+        <v>13.2</v>
       </c>
       <c r="D97" t="n">
-        <v>2.48</v>
+        <v>1.77</v>
       </c>
       <c r="E97" t="b">
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>143.08</v>
+        <v>12.8</v>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>0.76</v>
+        <v>-3.03</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>GEECEE</t>
+          <t>REPL</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>251.95</v>
+        <v>72.73</v>
       </c>
       <c r="C98" t="n">
-        <v>258.2</v>
+        <v>74</v>
       </c>
       <c r="D98" t="n">
-        <v>2.48</v>
+        <v>1.75</v>
       </c>
       <c r="E98" t="b">
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>256.05</v>
+        <v>73.29000000000001</v>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>-0.83</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BIRLAMONEY</t>
+          <t>AGSTRA</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>115.33</v>
+        <v>2.93</v>
       </c>
       <c r="C99" t="n">
-        <v>118.19</v>
+        <v>2.98</v>
       </c>
       <c r="D99" t="n">
-        <v>2.48</v>
+        <v>1.71</v>
       </c>
       <c r="E99" t="b">
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>118.25</v>
+        <v>2.9</v>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
-        <v>0.05</v>
+        <v>-2.68</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CEIGALL</t>
+          <t>BESTAGRO</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>279</v>
+        <v>14.73</v>
       </c>
       <c r="C100" t="n">
-        <v>285.9</v>
+        <v>14.98</v>
       </c>
       <c r="D100" t="n">
-        <v>2.47</v>
+        <v>1.7</v>
       </c>
       <c r="E100" t="b">
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>281.85</v>
+        <v>14.53</v>
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>-1.42</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>UMIYA-MRO</t>
+          <t>GSS</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>79.06</v>
+        <v>11.21</v>
       </c>
       <c r="C101" t="n">
-        <v>81</v>
+        <v>11.4</v>
       </c>
       <c r="D101" t="n">
-        <v>2.45</v>
+        <v>1.69</v>
       </c>
       <c r="E101" t="b">
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>81</v>
+        <v>11.15</v>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>0</v>
+        <v>-2.19</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SHRENIK</t>
+          <t>HILTON</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.41</v>
+        <v>16.23</v>
       </c>
       <c r="C102" t="n">
-        <v>0.42</v>
+        <v>16.5</v>
       </c>
       <c r="D102" t="n">
-        <v>2.44</v>
+        <v>1.66</v>
       </c>
       <c r="E102" t="b">
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>0.41</v>
+        <v>16.38</v>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>-2.38</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>KOHINOOR</t>
+          <t>AVONMORE</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>22.44</v>
+        <v>12.89</v>
       </c>
       <c r="C103" t="n">
-        <v>22.98</v>
+        <v>13.1</v>
       </c>
       <c r="D103" t="n">
-        <v>2.41</v>
+        <v>1.63</v>
       </c>
       <c r="E103" t="b">
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>22.77</v>
+        <v>12.8</v>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>-0.91</v>
+        <v>-2.29</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>NARMADA</t>
+          <t>MANAKALUCO</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>33.18</v>
+        <v>25.4</v>
       </c>
       <c r="C104" t="n">
-        <v>33.98</v>
+        <v>25.79</v>
       </c>
       <c r="D104" t="n">
-        <v>2.41</v>
+        <v>1.54</v>
       </c>
       <c r="E104" t="b">
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>33.82</v>
+        <v>24.69</v>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
-        <v>-0.47</v>
+        <v>-4.27</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AKI</t>
+          <t>GVKPIL</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>4.58</v>
+        <v>2.64</v>
       </c>
       <c r="C105" t="n">
-        <v>4.69</v>
+        <v>2.68</v>
       </c>
       <c r="D105" t="n">
-        <v>2.4</v>
+        <v>1.52</v>
       </c>
       <c r="E105" t="b">
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>5.07</v>
+        <v>2.68</v>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>URAVIDEF</t>
+          <t>HESTERBIO</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>128.91</v>
+        <v>1401.5</v>
       </c>
       <c r="C106" t="n">
-        <v>132</v>
+        <v>1422.5</v>
       </c>
       <c r="D106" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="E106" t="b">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>128.14</v>
+        <v>1435</v>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
-        <v>-2.92</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>DUCON</t>
+          <t>PRUDMOULI</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>2.93</v>
+        <v>12.66</v>
       </c>
       <c r="C107" t="n">
-        <v>3</v>
+        <v>12.85</v>
       </c>
       <c r="D107" t="n">
-        <v>2.39</v>
+        <v>1.5</v>
       </c>
       <c r="E107" t="b">
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>3.01</v>
+        <v>12.18</v>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>0.33</v>
+        <v>-5.21</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SAMPANN</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>29.3</v>
+        <v>234.9</v>
       </c>
       <c r="C108" t="n">
-        <v>30</v>
+        <v>238.4</v>
       </c>
       <c r="D108" t="n">
-        <v>2.39</v>
+        <v>1.49</v>
       </c>
       <c r="E108" t="b">
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>29.73</v>
+        <v>236.95</v>
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
-        <v>-0.9</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SHEKHAWATI</t>
+          <t>MGEL</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>11.82</v>
+        <v>10.05</v>
       </c>
       <c r="C109" t="n">
-        <v>12.1</v>
+        <v>10.2</v>
       </c>
       <c r="D109" t="n">
-        <v>2.37</v>
+        <v>1.49</v>
       </c>
       <c r="E109" t="b">
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>11.6</v>
+        <v>10.01</v>
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>-4.13</v>
+        <v>-1.86</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ZODIAC</t>
+          <t>UNIDT</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>235.49</v>
+        <v>162.87</v>
       </c>
       <c r="C110" t="n">
-        <v>241</v>
+        <v>165.3</v>
       </c>
       <c r="D110" t="n">
-        <v>2.34</v>
+        <v>1.49</v>
       </c>
       <c r="E110" t="b">
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>241.3</v>
+        <v>155.45</v>
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
-        <v>0.12</v>
+        <v>-5.96</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SVPGLOB</t>
+          <t>ARCHIDPLY</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>2.58</v>
+        <v>71.45</v>
       </c>
       <c r="C111" t="n">
-        <v>2.64</v>
+        <v>72.5</v>
       </c>
       <c r="D111" t="n">
-        <v>2.33</v>
+        <v>1.47</v>
       </c>
       <c r="E111" t="b">
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>2.63</v>
+        <v>70.77</v>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>-0.38</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SUPREMEPWR</t>
+          <t>MAANALU</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>163.2</v>
+        <v>131.06</v>
       </c>
       <c r="C112" t="n">
-        <v>167</v>
+        <v>132.98</v>
       </c>
       <c r="D112" t="n">
-        <v>2.33</v>
+        <v>1.46</v>
       </c>
       <c r="E112" t="b">
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>173</v>
+        <v>134.5</v>
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
-        <v>3.59</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>PILITA</t>
+          <t>MAHAPEXLTD</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>7.33</v>
+        <v>134.06</v>
       </c>
       <c r="C113" t="n">
-        <v>7.5</v>
+        <v>136</v>
       </c>
       <c r="D113" t="n">
-        <v>2.32</v>
+        <v>1.45</v>
       </c>
       <c r="E113" t="b">
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>7.55</v>
+        <v>132.49</v>
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>0.67</v>
+        <v>-2.58</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>FMNL</t>
+          <t>LAXMICOT</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>8.210000000000001</v>
+        <v>12.52</v>
       </c>
       <c r="C114" t="n">
-        <v>8.4</v>
+        <v>12.7</v>
       </c>
       <c r="D114" t="n">
-        <v>2.31</v>
+        <v>1.44</v>
       </c>
       <c r="E114" t="b">
         <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>8.19</v>
+        <v>12.35</v>
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
-        <v>-2.5</v>
+        <v>-2.76</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>GAYAHWS</t>
+          <t>MTEDUCARE</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>2.16</v>
+        <v>1.39</v>
       </c>
       <c r="C115" t="n">
-        <v>2.21</v>
+        <v>1.41</v>
       </c>
       <c r="D115" t="n">
-        <v>2.31</v>
+        <v>1.44</v>
       </c>
       <c r="E115" t="b">
         <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>2.22</v>
+        <v>1.33</v>
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>0.45</v>
+        <v>-5.67</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>UNITEDTEA</t>
+          <t>RPPINFRA</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>521.95</v>
+        <v>72.70999999999999</v>
       </c>
       <c r="C116" t="n">
-        <v>534</v>
+        <v>73.75</v>
       </c>
       <c r="D116" t="n">
-        <v>2.31</v>
+        <v>1.43</v>
       </c>
       <c r="E116" t="b">
         <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>545.95</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
-        <v>2.24</v>
+        <v>-3.38</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>IGCL</t>
+          <t>GANGAFORGE</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>57.84</v>
+        <v>2.82</v>
       </c>
       <c r="C117" t="n">
-        <v>59.17</v>
+        <v>2.86</v>
       </c>
       <c r="D117" t="n">
-        <v>2.3</v>
+        <v>1.42</v>
       </c>
       <c r="E117" t="b">
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>59.51</v>
+        <v>2.83</v>
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>0.57</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SHREEJISPG</t>
+          <t>RUDRA</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>364.65</v>
+        <v>16.52</v>
       </c>
       <c r="C118" t="n">
-        <v>373</v>
+        <v>16.75</v>
       </c>
       <c r="D118" t="n">
-        <v>2.29</v>
+        <v>1.39</v>
       </c>
       <c r="E118" t="b">
         <v>0</v>
       </c>
       <c r="F118" t="n">
-        <v>370.75</v>
+        <v>16.32</v>
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
-        <v>-0.6</v>
+        <v>-2.57</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>GOKUL</t>
+          <t>ASAHISONG</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>40.57</v>
+        <v>197.3</v>
       </c>
       <c r="C119" t="n">
-        <v>41.5</v>
+        <v>199.89</v>
       </c>
       <c r="D119" t="n">
-        <v>2.29</v>
+        <v>1.31</v>
       </c>
       <c r="E119" t="b">
         <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>42.14</v>
+        <v>196.78</v>
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
-        <v>1.54</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ASHIMASYN</t>
+          <t>LOVABLE</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>13.98</v>
+        <v>67.14</v>
       </c>
       <c r="C120" t="n">
-        <v>14.3</v>
+        <v>68</v>
       </c>
       <c r="D120" t="n">
-        <v>2.29</v>
+        <v>1.28</v>
       </c>
       <c r="E120" t="b">
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>14.19</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
-        <v>-0.77</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SAGARDEEP</t>
+          <t>DJML</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>22.48</v>
+        <v>80.01000000000001</v>
       </c>
       <c r="C121" t="n">
-        <v>22.99</v>
+        <v>81</v>
       </c>
       <c r="D121" t="n">
-        <v>2.27</v>
+        <v>1.24</v>
       </c>
       <c r="E121" t="b">
         <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>23.49</v>
+        <v>80</v>
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
-        <v>2.17</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>LIBAS</t>
+          <t>IMPAL</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>10.36</v>
+        <v>1022.4</v>
       </c>
       <c r="C122" t="n">
-        <v>10.59</v>
+        <v>1035</v>
       </c>
       <c r="D122" t="n">
-        <v>2.22</v>
+        <v>1.23</v>
       </c>
       <c r="E122" t="b">
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>10.15</v>
+        <v>1007.6</v>
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
-        <v>-4.15</v>
+        <v>-2.65</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>VENUSREM</t>
+          <t>GLOBE</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>914.9</v>
+        <v>2.49</v>
       </c>
       <c r="C123" t="n">
-        <v>935</v>
+        <v>2.52</v>
       </c>
       <c r="D123" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="E123" t="b">
         <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>916.55</v>
+        <v>2.46</v>
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>-1.97</v>
+        <v>-2.38</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>UNIVASTU</t>
+          <t>HMAAGRO</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>64</v>
+        <v>23.73</v>
       </c>
       <c r="C124" t="n">
-        <v>65.40000000000001</v>
+        <v>24.01</v>
       </c>
       <c r="D124" t="n">
-        <v>2.19</v>
+        <v>1.18</v>
       </c>
       <c r="E124" t="b">
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>64.75</v>
+        <v>23.43</v>
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
-        <v>-0.99</v>
+        <v>-2.42</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>PASHUPATI</t>
+          <t>MANGALAM</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>983.5</v>
+        <v>30.62</v>
       </c>
       <c r="C125" t="n">
-        <v>1005</v>
+        <v>30.98</v>
       </c>
       <c r="D125" t="n">
-        <v>2.19</v>
+        <v>1.18</v>
       </c>
       <c r="E125" t="b">
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>993.3</v>
+        <v>30.9</v>
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>-1.16</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>GOKULAGRO</t>
+          <t>PARSVNATH</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>191</v>
+        <v>6.81</v>
       </c>
       <c r="C126" t="n">
-        <v>195.15</v>
+        <v>6.89</v>
       </c>
       <c r="D126" t="n">
-        <v>2.17</v>
+        <v>1.17</v>
       </c>
       <c r="E126" t="b">
         <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>195.71</v>
+        <v>6.74</v>
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
-        <v>0.29</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>OMAXAUTO</t>
+          <t>WEL</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>95.90000000000001</v>
+        <v>138.14</v>
       </c>
       <c r="C127" t="n">
-        <v>97.98</v>
+        <v>139.7</v>
       </c>
       <c r="D127" t="n">
-        <v>2.17</v>
+        <v>1.13</v>
       </c>
       <c r="E127" t="b">
         <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>99.98999999999999</v>
+        <v>137.59</v>
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
-        <v>2.05</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>RPPL</t>
+          <t>TOLINS</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>15.66</v>
+        <v>101.85</v>
       </c>
       <c r="C128" t="n">
-        <v>16</v>
+        <v>103</v>
       </c>
       <c r="D128" t="n">
-        <v>2.17</v>
+        <v>1.13</v>
       </c>
       <c r="E128" t="b">
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>16</v>
+        <v>100.53</v>
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
-        <v>0</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>VAISHALI</t>
+          <t>ZEELEARN</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>6.07</v>
+        <v>5.3</v>
       </c>
       <c r="C129" t="n">
-        <v>6.2</v>
+        <v>5.36</v>
       </c>
       <c r="D129" t="n">
-        <v>2.14</v>
+        <v>1.13</v>
       </c>
       <c r="E129" t="b">
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>6.14</v>
+        <v>5.26</v>
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
-        <v>-0.97</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>HPL</t>
+          <t>TTL</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>275.15</v>
+        <v>8.99</v>
       </c>
       <c r="C130" t="n">
-        <v>281</v>
+        <v>9.09</v>
       </c>
       <c r="D130" t="n">
-        <v>2.13</v>
+        <v>1.11</v>
       </c>
       <c r="E130" t="b">
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>291.6</v>
+        <v>9.1</v>
       </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
-        <v>3.77</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>PEARLPOLY</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>16.63</v>
+        <v>255.25</v>
       </c>
       <c r="C131" t="n">
-        <v>16.98</v>
+        <v>258</v>
       </c>
       <c r="D131" t="n">
-        <v>2.1</v>
+        <v>1.08</v>
       </c>
       <c r="E131" t="b">
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>16.6</v>
+        <v>251.75</v>
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
-        <v>-2.24</v>
+        <v>-2.42</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>JARO</t>
+          <t>KANPRPLA</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>471.35</v>
+        <v>183.14</v>
       </c>
       <c r="C132" t="n">
-        <v>481.25</v>
+        <v>185</v>
       </c>
       <c r="D132" t="n">
-        <v>2.1</v>
+        <v>1.02</v>
       </c>
       <c r="E132" t="b">
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>487.3</v>
+        <v>181.75</v>
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
-        <v>1.26</v>
+        <v>-1.76</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>REGAAL</t>
+          <t>WAAREEINDO</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>75.64</v>
+        <v>349.4</v>
       </c>
       <c r="C133" t="n">
-        <v>77.23</v>
+        <v>352.95</v>
       </c>
       <c r="D133" t="n">
-        <v>2.1</v>
+        <v>1.02</v>
       </c>
       <c r="E133" t="b">
         <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>75.31</v>
+        <v>366.85</v>
       </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
-        <v>-2.49</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>BORANA</t>
+          <t>ENERGYDEV</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>375.2</v>
+        <v>15.04</v>
       </c>
       <c r="C134" t="n">
-        <v>382.95</v>
+        <v>15.19</v>
       </c>
       <c r="D134" t="n">
-        <v>2.07</v>
+        <v>1</v>
       </c>
       <c r="E134" t="b">
         <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>378</v>
+        <v>15.44</v>
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
-        <v>-1.29</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BHAGYANGR</t>
+          <t>AMNPLST</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>147.69</v>
+        <v>149.57</v>
       </c>
       <c r="C135" t="n">
-        <v>150.74</v>
+        <v>151</v>
       </c>
       <c r="D135" t="n">
-        <v>2.07</v>
+        <v>0.96</v>
       </c>
       <c r="E135" t="b">
         <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>149.99</v>
+        <v>151.1</v>
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
-        <v>-0.5</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>VIJIFIN</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>88.43000000000001</v>
+        <v>3.18</v>
       </c>
       <c r="C136" t="n">
-        <v>90.25</v>
+        <v>3.21</v>
       </c>
       <c r="D136" t="n">
-        <v>2.06</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E136" t="b">
         <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>92</v>
+        <v>3.03</v>
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
-        <v>1.94</v>
+        <v>-5.61</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>RPPINFRA</t>
+          <t>ENIL</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>70.76000000000001</v>
+        <v>105.91</v>
       </c>
       <c r="C137" t="n">
-        <v>72.2</v>
+        <v>106.9</v>
       </c>
       <c r="D137" t="n">
-        <v>2.04</v>
+        <v>0.93</v>
       </c>
       <c r="E137" t="b">
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>71.94</v>
+        <v>106.04</v>
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
-        <v>-0.36</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>PATINTLOG</t>
+          <t>PRAXIS</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>9.300000000000001</v>
+        <v>6.45</v>
       </c>
       <c r="C138" t="n">
-        <v>9.49</v>
+        <v>6.51</v>
       </c>
       <c r="D138" t="n">
-        <v>2.04</v>
+        <v>0.93</v>
       </c>
       <c r="E138" t="b">
         <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>9.539999999999999</v>
+        <v>6.49</v>
       </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
-        <v>0.53</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>NIRMAN</t>
+          <t>MAWANASUG</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>46.6</v>
+        <v>78.27</v>
       </c>
       <c r="C139" t="n">
-        <v>47.55</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="D139" t="n">
-        <v>2.04</v>
+        <v>0.92</v>
       </c>
       <c r="E139" t="b">
         <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>47</v>
+        <v>78.8</v>
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
-        <v>-1.16</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>TVSELECT</t>
+          <t>AMANTA</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>395</v>
+        <v>97.12</v>
       </c>
       <c r="C140" t="n">
-        <v>403</v>
+        <v>98</v>
       </c>
       <c r="D140" t="n">
-        <v>2.03</v>
+        <v>0.91</v>
       </c>
       <c r="E140" t="b">
         <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>416.75</v>
+        <v>95.86</v>
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
-        <v>3.41</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>EBGNG</t>
+          <t>HINDOILEXP</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>376.4</v>
+        <v>131.18</v>
       </c>
       <c r="C141" t="n">
-        <v>384</v>
+        <v>132.35</v>
       </c>
       <c r="D141" t="n">
-        <v>2.02</v>
+        <v>0.89</v>
       </c>
       <c r="E141" t="b">
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>382.5</v>
+        <v>132.85</v>
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
-        <v>-0.39</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>LAMBODHARA</t>
+          <t>DISHTV</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>92.53</v>
+        <v>2.28</v>
       </c>
       <c r="C142" t="n">
-        <v>94.39</v>
+        <v>2.3</v>
       </c>
       <c r="D142" t="n">
-        <v>2.01</v>
+        <v>0.88</v>
       </c>
       <c r="E142" t="b">
         <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>103.75</v>
+        <v>2.31</v>
       </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
-        <v>9.92</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>CREATIVEYE</t>
+          <t>IVP</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>6.47</v>
+        <v>133.39</v>
       </c>
       <c r="C143" t="n">
-        <v>6.6</v>
+        <v>134.5</v>
       </c>
       <c r="D143" t="n">
-        <v>2.01</v>
+        <v>0.83</v>
       </c>
       <c r="E143" t="b">
         <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>6.61</v>
+        <v>132</v>
       </c>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
-        <v>0.15</v>
+        <v>-1.86</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ALGOQUANT</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>55</v>
+        <v>6.07</v>
       </c>
       <c r="C144" t="n">
-        <v>56.1</v>
+        <v>6.12</v>
       </c>
       <c r="D144" t="n">
-        <v>2</v>
+        <v>0.82</v>
       </c>
       <c r="E144" t="b">
         <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>56.87</v>
+        <v>5.99</v>
       </c>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
-        <v>1.37</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>MASON</t>
+          <t>BALAJEE</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>145</v>
+        <v>25.77</v>
       </c>
       <c r="C145" t="n">
-        <v>147.9</v>
+        <v>25.98</v>
       </c>
       <c r="D145" t="n">
-        <v>2</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E145" t="b">
         <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>147.9</v>
+        <v>25.6</v>
       </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
-        <v>0</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>NATCAPSUQ</t>
+          <t>SASTASUNDR</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>151.28</v>
+        <v>285.6</v>
       </c>
       <c r="C146" t="n">
-        <v>154.3</v>
+        <v>287.9</v>
       </c>
       <c r="D146" t="n">
-        <v>2</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E146" t="b">
         <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>154.3</v>
+        <v>282.75</v>
       </c>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
-        <v>0</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>PRITIKAUTO</t>
+          <t>KOHINOOR</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>11.49</v>
+        <v>23.41</v>
       </c>
       <c r="C147" t="n">
-        <v>11.72</v>
+        <v>23.6</v>
       </c>
       <c r="D147" t="n">
-        <v>2</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E147" t="b">
         <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>12.02</v>
+        <v>22.92</v>
       </c>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
-        <v>2.56</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>HEXATRADEX</t>
+          <t>MEGASTAR</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>160.05</v>
+        <v>251.06</v>
       </c>
       <c r="C148" t="n">
-        <v>163.25</v>
+        <v>252.95</v>
       </c>
       <c r="D148" t="n">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="E148" t="b">
         <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>162.94</v>
+        <v>245.02</v>
       </c>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
-        <v>-0.19</v>
+        <v>-3.14</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ACCURACY</t>
+          <t>KANANIIND</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>4</v>
+        <v>1.38</v>
       </c>
       <c r="C149" t="n">
-        <v>4.08</v>
+        <v>1.39</v>
       </c>
       <c r="D149" t="n">
-        <v>2</v>
+        <v>0.72</v>
       </c>
       <c r="E149" t="b">
         <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>4</v>
+        <v>1.36</v>
       </c>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
-        <v>-1.96</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>PLAZACABLE</t>
+          <t>AEPL</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>33.82</v>
+        <v>18.37</v>
       </c>
       <c r="C150" t="n">
-        <v>34.49</v>
+        <v>18.5</v>
       </c>
       <c r="D150" t="n">
-        <v>1.98</v>
+        <v>0.71</v>
       </c>
       <c r="E150" t="b">
         <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>34.22</v>
+        <v>18</v>
       </c>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
-        <v>-0.78</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>MEGATHERM</t>
+          <t>AVROIND</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>194.1</v>
+        <v>125.95</v>
       </c>
       <c r="C151" t="n">
-        <v>197.95</v>
+        <v>126.8</v>
       </c>
       <c r="D151" t="n">
-        <v>1.98</v>
+        <v>0.67</v>
       </c>
       <c r="E151" t="b">
         <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>193.2</v>
+        <v>120.76</v>
       </c>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
-        <v>-2.4</v>
+        <v>-4.76</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SEYAIND</t>
+          <t>HCL-INSYS</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>9.59</v>
+        <v>11.9</v>
       </c>
       <c r="C152" t="n">
-        <v>9.779999999999999</v>
+        <v>11.98</v>
       </c>
       <c r="D152" t="n">
-        <v>1.98</v>
+        <v>0.67</v>
       </c>
       <c r="E152" t="b">
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>9.779999999999999</v>
+        <v>11.83</v>
       </c>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="n">
-        <v>0</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>FLAIR</t>
+          <t>SUPERHOUSE</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>302.8</v>
+        <v>145.05</v>
       </c>
       <c r="C153" t="n">
-        <v>308.8</v>
+        <v>146</v>
       </c>
       <c r="D153" t="n">
-        <v>1.98</v>
+        <v>0.65</v>
       </c>
       <c r="E153" t="b">
         <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>315.2</v>
+        <v>144.99</v>
       </c>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="n">
-        <v>2.07</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BROOKS</t>
+          <t>AHLUCONT</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>55.4</v>
+        <v>746</v>
       </c>
       <c r="C154" t="n">
-        <v>56.49</v>
+        <v>749.95</v>
       </c>
       <c r="D154" t="n">
-        <v>1.97</v>
+        <v>0.53</v>
       </c>
       <c r="E154" t="b">
         <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>57</v>
+        <v>731</v>
       </c>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="n">
-        <v>0.9</v>
+        <v>-2.53</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>RKSWAMY</t>
+          <t>MOTOGENFIN</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>89.14</v>
+        <v>20.89</v>
       </c>
       <c r="C155" t="n">
-        <v>90.90000000000001</v>
+        <v>21</v>
       </c>
       <c r="D155" t="n">
-        <v>1.97</v>
+        <v>0.53</v>
       </c>
       <c r="E155" t="b">
         <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>90.70999999999999</v>
+        <v>20.8</v>
       </c>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="n">
-        <v>-0.21</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SECMARK</t>
+          <t>KANORICHEM</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>108.18</v>
+        <v>63.07</v>
       </c>
       <c r="C156" t="n">
-        <v>110.3</v>
+        <v>63.4</v>
       </c>
       <c r="D156" t="n">
-        <v>1.96</v>
+        <v>0.52</v>
       </c>
       <c r="E156" t="b">
         <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>111</v>
+        <v>62.03</v>
       </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="n">
-        <v>0.63</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>GOLDTECH</t>
+          <t>EMMBI</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>39.82</v>
+        <v>82.06999999999999</v>
       </c>
       <c r="C157" t="n">
-        <v>40.6</v>
+        <v>82.5</v>
       </c>
       <c r="D157" t="n">
-        <v>1.96</v>
+        <v>0.52</v>
       </c>
       <c r="E157" t="b">
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>40.62</v>
+        <v>81.61</v>
       </c>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="n">
-        <v>0.05</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>TPHQ</t>
+          <t>SEMAC</t>
         </is>
       </c>
       <c r="B158" t="n">
+        <v>283.54</v>
+      </c>
+      <c r="C158" t="n">
+        <v>284.99</v>
+      </c>
+      <c r="D158" t="n">
         <v>0.51</v>
       </c>
-      <c r="C158" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="D158" t="n">
-        <v>1.96</v>
-      </c>
       <c r="E158" t="b">
         <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>0.52</v>
+        <v>279.99</v>
       </c>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="n">
-        <v>0</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>SEMAC</t>
+          <t>FOCUS</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>259.89</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="C159" t="n">
-        <v>264.95</v>
+        <v>68.38</v>
       </c>
       <c r="D159" t="n">
-        <v>1.95</v>
+        <v>0.5</v>
       </c>
       <c r="E159" t="b">
         <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>281.8</v>
+        <v>67.5</v>
       </c>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="n">
-        <v>6.36</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>EMMBI</t>
+          <t>APCL</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>79.06</v>
+        <v>114.58</v>
       </c>
       <c r="C160" t="n">
-        <v>80.59999999999999</v>
+        <v>115.15</v>
       </c>
       <c r="D160" t="n">
-        <v>1.95</v>
+        <v>0.5</v>
       </c>
       <c r="E160" t="b">
         <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>80.43000000000001</v>
+        <v>114.94</v>
       </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="n">
-        <v>-0.21</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ARFIN</t>
+          <t>ONWARDTEC</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>76.42</v>
+        <v>248.3</v>
       </c>
       <c r="C161" t="n">
-        <v>77.90000000000001</v>
+        <v>249.55</v>
       </c>
       <c r="D161" t="n">
-        <v>1.94</v>
+        <v>0.5</v>
       </c>
       <c r="E161" t="b">
         <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>74.75</v>
+        <v>242</v>
       </c>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="n">
-        <v>-4.04</v>
+        <v>-3.03</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>SHAH</t>
+          <t>TTKPRESTIG</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>4.69</v>
+        <v>477.7</v>
       </c>
       <c r="C162" t="n">
-        <v>4.78</v>
+        <v>480.1</v>
       </c>
       <c r="D162" t="n">
-        <v>1.92</v>
+        <v>0.5</v>
       </c>
       <c r="E162" t="b">
         <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>4.77</v>
+        <v>485.85</v>
       </c>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="n">
-        <v>-0.21</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>SHANTI</t>
+          <t>JUBLCPL</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>6.32</v>
+        <v>1706.7</v>
       </c>
       <c r="C163" t="n">
-        <v>6.44</v>
+        <v>1715.2</v>
       </c>
       <c r="D163" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="E163" t="b">
         <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>6.49</v>
+        <v>1673.5</v>
       </c>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="n">
-        <v>0.78</v>
+        <v>-2.43</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>PANSARI</t>
+          <t>BELLACASA</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>265.15</v>
+        <v>269</v>
       </c>
       <c r="C164" t="n">
-        <v>270.15</v>
+        <v>270.35</v>
       </c>
       <c r="D164" t="n">
-        <v>1.89</v>
+        <v>0.5</v>
       </c>
       <c r="E164" t="b">
         <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="n">
-        <v>-1.54</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>KUANTUM</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>76.06</v>
+        <v>1109.4</v>
       </c>
       <c r="C165" t="n">
-        <v>77.48</v>
+        <v>1115</v>
       </c>
       <c r="D165" t="n">
-        <v>1.87</v>
+        <v>0.5</v>
       </c>
       <c r="E165" t="b">
         <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>78.04000000000001</v>
+        <v>1079.4</v>
       </c>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="n">
-        <v>0.72</v>
+        <v>-3.19</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ASMS</t>
+          <t>MCL</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>8.119999999999999</v>
+        <v>62.78</v>
       </c>
       <c r="C166" t="n">
-        <v>8.27</v>
+        <v>63.09</v>
       </c>
       <c r="D166" t="n">
-        <v>1.85</v>
+        <v>0.49</v>
       </c>
       <c r="E166" t="b">
         <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>8.5</v>
+        <v>61.8</v>
       </c>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="n">
-        <v>2.78</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ZIMLAB</t>
+          <t>KMSUGAR</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>70.19</v>
+        <v>25.07</v>
       </c>
       <c r="C167" t="n">
-        <v>71.48999999999999</v>
+        <v>25.19</v>
       </c>
       <c r="D167" t="n">
-        <v>1.85</v>
+        <v>0.48</v>
       </c>
       <c r="E167" t="b">
         <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>69.66</v>
+        <v>25.39</v>
       </c>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="n">
-        <v>-2.56</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CRAMC</t>
+          <t>LGHL</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>234.2</v>
+        <v>269.05</v>
       </c>
       <c r="C168" t="n">
-        <v>238.5</v>
+        <v>270.35</v>
       </c>
       <c r="D168" t="n">
-        <v>1.84</v>
+        <v>0.48</v>
       </c>
       <c r="E168" t="b">
         <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>238.2</v>
+        <v>269.05</v>
       </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="n">
-        <v>-0.13</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>KHAITANLTD</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>1026.6</v>
+        <v>99</v>
       </c>
       <c r="C169" t="n">
-        <v>1045.5</v>
+        <v>99.48</v>
       </c>
       <c r="D169" t="n">
-        <v>1.84</v>
+        <v>0.48</v>
       </c>
       <c r="E169" t="b">
         <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>1084.2</v>
+        <v>95.48</v>
       </c>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="n">
-        <v>3.7</v>
+        <v>-4.02</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>DGCONTENT</t>
+          <t>JETFREIGHT</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>23.08</v>
+        <v>17.75</v>
       </c>
       <c r="C170" t="n">
-        <v>23.5</v>
+        <v>17.83</v>
       </c>
       <c r="D170" t="n">
-        <v>1.82</v>
+        <v>0.45</v>
       </c>
       <c r="E170" t="b">
         <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>23.2</v>
+        <v>17.63</v>
       </c>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="n">
-        <v>-1.28</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ZENITHSTL</t>
+          <t>KABRAEXTRU</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>5.02</v>
+        <v>220.7</v>
       </c>
       <c r="C171" t="n">
-        <v>5.11</v>
+        <v>221.7</v>
       </c>
       <c r="D171" t="n">
-        <v>1.79</v>
+        <v>0.45</v>
       </c>
       <c r="E171" t="b">
         <v>0</v>
       </c>
       <c r="F171" t="n">
-        <v>5.01</v>
+        <v>215.15</v>
       </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="n">
-        <v>-1.96</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>VIVIDHA</t>
+          <t>CALSOFT</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.5600000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="C172" t="n">
-        <v>0.57</v>
+        <v>13.56</v>
       </c>
       <c r="D172" t="n">
-        <v>1.79</v>
+        <v>0.44</v>
       </c>
       <c r="E172" t="b">
         <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>0.59</v>
+        <v>13.48</v>
       </c>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="n">
-        <v>3.51</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>ALMONDZ</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>6.78</v>
+        <v>13.94</v>
       </c>
       <c r="C173" t="n">
-        <v>6.9</v>
+        <v>14</v>
       </c>
       <c r="D173" t="n">
-        <v>1.77</v>
+        <v>0.43</v>
       </c>
       <c r="E173" t="b">
         <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>6.81</v>
+        <v>14.22</v>
       </c>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="n">
-        <v>-1.3</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>VIRINCHI</t>
+          <t>KRIDHANINF</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>16.95</v>
+        <v>2.46</v>
       </c>
       <c r="C174" t="n">
-        <v>17.25</v>
+        <v>2.47</v>
       </c>
       <c r="D174" t="n">
-        <v>1.77</v>
+        <v>0.41</v>
       </c>
       <c r="E174" t="b">
         <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>17.11</v>
+        <v>2.41</v>
       </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-2.43</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>AXISCADES</t>
+          <t>CAPINVIT</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>1384.5</v>
+        <v>68.12</v>
       </c>
       <c r="C175" t="n">
-        <v>1408.8</v>
+        <v>68.39</v>
       </c>
       <c r="D175" t="n">
-        <v>1.76</v>
+        <v>0.4</v>
       </c>
       <c r="E175" t="b">
         <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>1453.7</v>
+        <v>67.76000000000001</v>
       </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="n">
-        <v>3.19</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>THELEELA</t>
+          <t>PLAZACABLE</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>407.85</v>
+        <v>34.65</v>
       </c>
       <c r="C176" t="n">
-        <v>415</v>
+        <v>34.79</v>
       </c>
       <c r="D176" t="n">
-        <v>1.75</v>
+        <v>0.4</v>
       </c>
       <c r="E176" t="b">
         <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>411.65</v>
+        <v>34.35</v>
       </c>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>MAHAPEXLTD</t>
+          <t>GENCON</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>117.76</v>
+        <v>43.78</v>
       </c>
       <c r="C177" t="n">
-        <v>119.8</v>
+        <v>43.95</v>
       </c>
       <c r="D177" t="n">
-        <v>1.73</v>
+        <v>0.39</v>
       </c>
       <c r="E177" t="b">
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>118.92</v>
+        <v>43.84</v>
       </c>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="n">
-        <v>-0.73</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>GMBREW</t>
+          <t>BHANDARI</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>963.35</v>
+        <v>2.57</v>
       </c>
       <c r="C178" t="n">
-        <v>980</v>
+        <v>2.58</v>
       </c>
       <c r="D178" t="n">
-        <v>1.73</v>
+        <v>0.39</v>
       </c>
       <c r="E178" t="b">
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>1029</v>
+        <v>2.57</v>
       </c>
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="n">
-        <v>5</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>TINNARUBR</t>
+          <t>DCI</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>628.2</v>
+        <v>277.4</v>
       </c>
       <c r="C179" t="n">
-        <v>639</v>
+        <v>278.4</v>
       </c>
       <c r="D179" t="n">
-        <v>1.72</v>
+        <v>0.36</v>
       </c>
       <c r="E179" t="b">
         <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>630</v>
+        <v>270.8</v>
       </c>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="n">
-        <v>-1.41</v>
+        <v>-2.73</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>MODIS</t>
+          <t>RSYSTEMS</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>304.5</v>
+        <v>262.65</v>
       </c>
       <c r="C180" t="n">
-        <v>309.7</v>
+        <v>263.6</v>
       </c>
       <c r="D180" t="n">
-        <v>1.71</v>
+        <v>0.36</v>
       </c>
       <c r="E180" t="b">
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>315.1</v>
+        <v>263.3</v>
       </c>
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="n">
-        <v>1.74</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>VARDMNPOLY</t>
+          <t>SOLEX</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>7.62</v>
+        <v>950.5</v>
       </c>
       <c r="C181" t="n">
-        <v>7.75</v>
+        <v>953.95</v>
       </c>
       <c r="D181" t="n">
-        <v>1.71</v>
+        <v>0.36</v>
       </c>
       <c r="E181" t="b">
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>7.64</v>
+        <v>924.35</v>
       </c>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="n">
-        <v>-1.42</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>LPDC</t>
+          <t>RMDRIP</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>5.89</v>
+        <v>38.87</v>
       </c>
       <c r="C182" t="n">
-        <v>5.99</v>
+        <v>39</v>
       </c>
       <c r="D182" t="n">
-        <v>1.7</v>
+        <v>0.33</v>
       </c>
       <c r="E182" t="b">
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>5.99</v>
+        <v>40.81</v>
       </c>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>SICALLOG</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>65.87</v>
+        <v>470.45</v>
       </c>
       <c r="C183" t="n">
-        <v>66.98999999999999</v>
+        <v>471.95</v>
       </c>
       <c r="D183" t="n">
-        <v>1.7</v>
+        <v>0.32</v>
       </c>
       <c r="E183" t="b">
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>63.5</v>
+        <v>478.5</v>
       </c>
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="n">
-        <v>-5.21</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>HCL-INSYS</t>
+          <t>MBLINFRA</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>11.79</v>
+        <v>22.32</v>
       </c>
       <c r="C184" t="n">
-        <v>11.99</v>
+        <v>22.39</v>
       </c>
       <c r="D184" t="n">
-        <v>1.7</v>
+        <v>0.31</v>
       </c>
       <c r="E184" t="b">
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>11.97</v>
+        <v>22.23</v>
       </c>
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="n">
-        <v>-0.17</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>RHETAN</t>
+          <t>FLEXITUFF</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>24.83</v>
+        <v>6.45</v>
       </c>
       <c r="C185" t="n">
-        <v>25.25</v>
+        <v>6.47</v>
       </c>
       <c r="D185" t="n">
-        <v>1.69</v>
+        <v>0.31</v>
       </c>
       <c r="E185" t="b">
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>25.03</v>
+        <v>6.42</v>
       </c>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="n">
-        <v>-0.87</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>COASTCORP</t>
+          <t>ORIENTCER</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>46.22</v>
+        <v>38.19</v>
       </c>
       <c r="C186" t="n">
-        <v>47</v>
+        <v>38.3</v>
       </c>
       <c r="D186" t="n">
-        <v>1.69</v>
+        <v>0.29</v>
       </c>
       <c r="E186" t="b">
         <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>46.16</v>
+        <v>39.4</v>
       </c>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="n">
-        <v>-1.79</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>BALAXI</t>
+          <t>GLOBECIVIL</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>17.7</v>
+        <v>43.23</v>
       </c>
       <c r="C187" t="n">
-        <v>18</v>
+        <v>43.35</v>
       </c>
       <c r="D187" t="n">
-        <v>1.69</v>
+        <v>0.28</v>
       </c>
       <c r="E187" t="b">
         <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>18.04</v>
+        <v>42.95</v>
       </c>
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="n">
-        <v>0.22</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>INDIQUBE</t>
+          <t>MINDTECK</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>138.66</v>
+        <v>183.75</v>
       </c>
       <c r="C188" t="n">
-        <v>141</v>
+        <v>184.25</v>
       </c>
       <c r="D188" t="n">
-        <v>1.69</v>
+        <v>0.27</v>
       </c>
       <c r="E188" t="b">
         <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>142.42</v>
+        <v>179.27</v>
       </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="n">
-        <v>1.01</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>UNITEDPOLY</t>
+          <t>IFGLEXPOR</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>26.24</v>
+        <v>146.32</v>
       </c>
       <c r="C189" t="n">
-        <v>26.68</v>
+        <v>146.7</v>
       </c>
       <c r="D189" t="n">
-        <v>1.68</v>
+        <v>0.26</v>
       </c>
       <c r="E189" t="b">
         <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>26.85</v>
+        <v>144.91</v>
       </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="n">
-        <v>0.64</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>OSWALPUMPS</t>
+          <t>NDLVENTURE</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>302.9</v>
+        <v>114.72</v>
       </c>
       <c r="C190" t="n">
-        <v>308</v>
+        <v>115</v>
       </c>
       <c r="D190" t="n">
-        <v>1.68</v>
+        <v>0.24</v>
       </c>
       <c r="E190" t="b">
         <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>316.6</v>
+        <v>115.57</v>
       </c>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="n">
-        <v>2.79</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>BVCL</t>
+          <t>PNC</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>37.2</v>
+        <v>21.05</v>
       </c>
       <c r="C191" t="n">
-        <v>37.82</v>
+        <v>21.1</v>
       </c>
       <c r="D191" t="n">
-        <v>1.67</v>
+        <v>0.24</v>
       </c>
       <c r="E191" t="b">
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>37.65</v>
+        <v>20.94</v>
       </c>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="n">
-        <v>-0.45</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>UTKARSHBNK</t>
+          <t>GFLLIMITED</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>11.97</v>
+        <v>45.4</v>
       </c>
       <c r="C192" t="n">
-        <v>12.17</v>
+        <v>45.5</v>
       </c>
       <c r="D192" t="n">
-        <v>1.67</v>
+        <v>0.22</v>
       </c>
       <c r="E192" t="b">
         <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>12.04</v>
+        <v>44.45</v>
       </c>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="n">
-        <v>-1.07</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>TCPLPACK</t>
+          <t>SIKKO</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>2409.6</v>
+        <v>4.76</v>
       </c>
       <c r="C193" t="n">
-        <v>2449.9</v>
+        <v>4.77</v>
       </c>
       <c r="D193" t="n">
-        <v>1.67</v>
+        <v>0.21</v>
       </c>
       <c r="E193" t="b">
         <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>2442.8</v>
+        <v>4.74</v>
       </c>
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="n">
-        <v>-0.29</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>GLOBECIVIL</t>
+          <t>SHAH</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>42.68</v>
+        <v>4.77</v>
       </c>
       <c r="C194" t="n">
-        <v>43.39</v>
+        <v>4.78</v>
       </c>
       <c r="D194" t="n">
-        <v>1.66</v>
+        <v>0.21</v>
       </c>
       <c r="E194" t="b">
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>43.57</v>
+        <v>4.73</v>
       </c>
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="n">
-        <v>0.41</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>MAWANASUG</t>
+          <t>HINDCON</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>77.13</v>
+        <v>18.9</v>
       </c>
       <c r="C195" t="n">
-        <v>78.40000000000001</v>
+        <v>18.94</v>
       </c>
       <c r="D195" t="n">
-        <v>1.65</v>
+        <v>0.21</v>
       </c>
       <c r="E195" t="b">
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>78.48</v>
+        <v>18.64</v>
       </c>
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="n">
-        <v>0.1</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>KILITCH</t>
+          <t>RELCHEMQ</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>319.5</v>
+        <v>114.68</v>
       </c>
       <c r="C196" t="n">
-        <v>324.75</v>
+        <v>114.9</v>
       </c>
       <c r="D196" t="n">
-        <v>1.64</v>
+        <v>0.19</v>
       </c>
       <c r="E196" t="b">
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>318.4</v>
+        <v>113.98</v>
       </c>
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="n">
-        <v>-1.96</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>IFBAGRO</t>
+          <t>INDIGRID</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>683.3</v>
+        <v>164.74</v>
       </c>
       <c r="C197" t="n">
-        <v>694.5</v>
+        <v>165</v>
       </c>
       <c r="D197" t="n">
-        <v>1.64</v>
+        <v>0.16</v>
       </c>
       <c r="E197" t="b">
         <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>711.05</v>
+        <v>164.52</v>
       </c>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="n">
-        <v>2.38</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>IDBI</t>
+          <t>BHARATRAS</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>74.09999999999999</v>
+        <v>1338.1</v>
       </c>
       <c r="C198" t="n">
-        <v>75.31</v>
+        <v>1340</v>
       </c>
       <c r="D198" t="n">
-        <v>1.63</v>
+        <v>0.14</v>
       </c>
       <c r="E198" t="b">
         <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>75.17</v>
+        <v>1299.2</v>
       </c>
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="n">
-        <v>-0.19</v>
+        <v>-3.04</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>BIRLACABLE</t>
+          <t>THEJO</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>129.73</v>
+        <v>1583.6</v>
       </c>
       <c r="C199" t="n">
-        <v>131.84</v>
+        <v>1585.8</v>
       </c>
       <c r="D199" t="n">
-        <v>1.63</v>
+        <v>0.14</v>
       </c>
       <c r="E199" t="b">
         <v>0</v>
       </c>
       <c r="F199" t="n">
-        <v>135.01</v>
+        <v>1572</v>
       </c>
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="n">
-        <v>2.4</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>AURIONPRO</t>
+          <t>INTLCONV</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>821.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="C200" t="n">
-        <v>834.5</v>
+        <v>70</v>
       </c>
       <c r="D200" t="n">
-        <v>1.62</v>
+        <v>0.14</v>
       </c>
       <c r="E200" t="b">
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>839.35</v>
+        <v>70.59</v>
       </c>
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="n">
-        <v>0.58</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>BCONCEPTS</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>1472.1</v>
+        <v>231.15</v>
       </c>
       <c r="C201" t="n">
-        <v>1495.8</v>
+        <v>231.45</v>
       </c>
       <c r="D201" t="n">
-        <v>1.61</v>
+        <v>0.13</v>
       </c>
       <c r="E201" t="b">
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>1554.4</v>
+        <v>238</v>
       </c>
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="n">
-        <v>3.92</v>
+        <v>2.83</v>
       </c>
     </row>
   </sheetData>

--- a/data/trending_momentum_stocks.xlsx
+++ b/data/trending_momentum_stocks.xlsx
@@ -461,5197 +461,5193 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RADAAN</t>
+          <t>INDIQUBE</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.86</v>
+        <v>146.39</v>
       </c>
       <c r="C2" t="n">
-        <v>3.42</v>
+        <v>172</v>
       </c>
       <c r="D2" t="n">
-        <v>19.58</v>
+        <v>17.49</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>2.93</v>
+        <v>152.4</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>-14.33</v>
+        <v>-11.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>USHAFIN</t>
+          <t>SINGERIND</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32.4</v>
+        <v>70.42</v>
       </c>
       <c r="C3" t="n">
-        <v>36.9</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>13.89</v>
+        <v>12.6</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>35</v>
+        <v>72.95</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>-5.15</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KAYTEX</t>
+          <t>GVPTECH</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>71.09999999999999</v>
+        <v>6.58</v>
       </c>
       <c r="C4" t="n">
-        <v>78.8</v>
+        <v>7.36</v>
       </c>
       <c r="D4" t="n">
-        <v>10.83</v>
+        <v>11.85</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>73.95</v>
+        <v>7.78</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>-6.15</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>INFOMEDIA</t>
+          <t>FINKURVE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.99</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>5.48</v>
+        <v>72</v>
       </c>
       <c r="D5" t="n">
-        <v>9.82</v>
+        <v>9.76</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>4.85</v>
+        <v>67.5</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>-11.5</v>
+        <v>-6.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EMKAYTOOLS</t>
+          <t>ROSSELLIND</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>91</v>
+        <v>45.74</v>
       </c>
       <c r="C6" t="n">
-        <v>98</v>
+        <v>50.01</v>
       </c>
       <c r="D6" t="n">
-        <v>7.69</v>
+        <v>9.34</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>95</v>
+        <v>46.51</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>-3.06</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ENCOMPAS</t>
+          <t>KEYFINSERV</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>241.75</v>
+        <v>260.7</v>
       </c>
       <c r="C7" t="n">
-        <v>259</v>
+        <v>284.9</v>
       </c>
       <c r="D7" t="n">
-        <v>7.14</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>253.75</v>
+        <v>264.75</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>-2.03</v>
+        <v>-7.07</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VALIANTORG</t>
+          <t>VASWANI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>237.16</v>
+        <v>52.78</v>
       </c>
       <c r="C8" t="n">
-        <v>250</v>
+        <v>57.55</v>
       </c>
       <c r="D8" t="n">
-        <v>5.41</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>264.56</v>
+        <v>53.3</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>5.82</v>
+        <v>-7.38</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KORE</t>
+          <t>RAJTV</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>36.36</v>
       </c>
       <c r="C9" t="n">
-        <v>102.9</v>
+        <v>39.5</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>102.9</v>
+        <v>37.58</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-4.86</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GJL</t>
+          <t>NKIND</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>263.3</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>276.45</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>4.99</v>
+        <v>7.92</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>276.45</v>
+        <v>63</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>-7.34</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TIJARIA</t>
+          <t>VERTOZ</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.62</v>
+        <v>36.16</v>
       </c>
       <c r="C11" t="n">
-        <v>4.85</v>
+        <v>39</v>
       </c>
       <c r="D11" t="n">
-        <v>4.98</v>
+        <v>7.85</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>4.41</v>
+        <v>36.83</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>-9.07</v>
+        <v>-5.56</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DPEL</t>
+          <t>DHARAN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>391.55</v>
+        <v>0.14</v>
       </c>
       <c r="C12" t="n">
-        <v>411</v>
+        <v>0.15</v>
       </c>
       <c r="D12" t="n">
-        <v>4.97</v>
+        <v>7.14</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>392</v>
+        <v>0.15</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>-4.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UMESLTD</t>
+          <t>LATTEYS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6.48</v>
+        <v>19.14</v>
       </c>
       <c r="C13" t="n">
-        <v>6.8</v>
+        <v>20.49</v>
       </c>
       <c r="D13" t="n">
-        <v>4.94</v>
+        <v>7.05</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>6.17</v>
+        <v>19.85</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>-9.26</v>
+        <v>-3.12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>APSISAERO</t>
+          <t>GEECEE</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>160.65</v>
+        <v>254.9</v>
       </c>
       <c r="C14" t="n">
-        <v>168.5</v>
+        <v>271.95</v>
       </c>
       <c r="D14" t="n">
-        <v>4.89</v>
+        <v>6.69</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>168.65</v>
+        <v>258.05</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.09</v>
+        <v>-5.11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VHLTD</t>
+          <t>CELEBRITY</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>140</v>
+        <v>7.18</v>
       </c>
       <c r="C15" t="n">
-        <v>146.8</v>
+        <v>7.66</v>
       </c>
       <c r="D15" t="n">
-        <v>4.86</v>
+        <v>6.69</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>138.6</v>
+        <v>7.53</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>-5.59</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BLUECOAST</t>
+          <t>MANUGRAPH</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19.66</v>
+        <v>12.94</v>
       </c>
       <c r="C16" t="n">
-        <v>20.59</v>
+        <v>13.8</v>
       </c>
       <c r="D16" t="n">
-        <v>4.73</v>
+        <v>6.65</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>20.49</v>
+        <v>13.39</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>-0.49</v>
+        <v>-2.97</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ORTEL</t>
+          <t>SOFTTECH</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.76</v>
+        <v>253.5</v>
       </c>
       <c r="C17" t="n">
-        <v>1.84</v>
+        <v>269.55</v>
       </c>
       <c r="D17" t="n">
-        <v>4.55</v>
+        <v>6.33</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8</v>
+        <v>265.95</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>-2.17</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BAFNAPH</t>
+          <t>RAMASTEEL</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>114.77</v>
+        <v>5.22</v>
       </c>
       <c r="C18" t="n">
-        <v>119.99</v>
+        <v>5.55</v>
       </c>
       <c r="D18" t="n">
-        <v>4.55</v>
+        <v>6.32</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>120.5</v>
+        <v>5.31</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>0.43</v>
+        <v>-4.32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CAPTRUST</t>
+          <t>MADHAV</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>11.72</v>
+        <v>33.41</v>
       </c>
       <c r="C19" t="n">
-        <v>12.24</v>
+        <v>35.5</v>
       </c>
       <c r="D19" t="n">
-        <v>4.44</v>
+        <v>6.26</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>11.9</v>
+        <v>34.41</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>-2.78</v>
+        <v>-3.07</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>COOLCAPS</t>
+          <t>RELIABLE</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>23.85</v>
+        <v>122.14</v>
       </c>
       <c r="C20" t="n">
-        <v>24.9</v>
+        <v>129.75</v>
       </c>
       <c r="D20" t="n">
-        <v>4.4</v>
+        <v>6.23</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>24.4</v>
+        <v>122.26</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>-2.01</v>
+        <v>-5.77</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EXXARO</t>
+          <t>HPAL</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6.9</v>
+        <v>30.67</v>
       </c>
       <c r="C21" t="n">
-        <v>7.2</v>
+        <v>32.58</v>
       </c>
       <c r="D21" t="n">
-        <v>4.35</v>
+        <v>6.23</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>6.94</v>
+        <v>31.33</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>-3.61</v>
+        <v>-3.84</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>OPTIVALUE</t>
+          <t>CCCL</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>80.45</v>
+        <v>14.69</v>
       </c>
       <c r="C22" t="n">
-        <v>83.95</v>
+        <v>15.54</v>
       </c>
       <c r="D22" t="n">
-        <v>4.35</v>
+        <v>5.79</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>80.5</v>
+        <v>14.7</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>-4.11</v>
+        <v>-5.41</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MITTAL</t>
+          <t>OSWALSEEDS</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.96</v>
+        <v>11.58</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>12.25</v>
       </c>
       <c r="D23" t="n">
-        <v>4.17</v>
+        <v>5.79</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>1.03</v>
+        <v>11.66</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>-4.82</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>VCL</t>
+          <t>MONEYBOXX</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.44</v>
+        <v>61.55</v>
       </c>
       <c r="C24" t="n">
-        <v>1.5</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>4.17</v>
+        <v>5.59</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>1.49</v>
+        <v>61.95</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>-0.67</v>
+        <v>-4.68</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TREEHOUSE</t>
+          <t>NRL</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8.4</v>
+        <v>49.5</v>
       </c>
       <c r="C25" t="n">
-        <v>8.74</v>
+        <v>52.18</v>
       </c>
       <c r="D25" t="n">
-        <v>4.05</v>
+        <v>5.41</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>8.5</v>
+        <v>50.9</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>-2.75</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SUPERSPIN</t>
+          <t>INDOWIND</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.52</v>
+        <v>8.75</v>
       </c>
       <c r="C26" t="n">
-        <v>4.7</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>3.98</v>
+        <v>5.37</v>
       </c>
       <c r="E26" t="b">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>4.36</v>
+        <v>8.98</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>-7.23</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PURPLEUTED</t>
+          <t>KRITINUT</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>284.15</v>
+        <v>63.49</v>
       </c>
       <c r="C27" t="n">
-        <v>295.4</v>
+        <v>66.8</v>
       </c>
       <c r="D27" t="n">
-        <v>3.96</v>
+        <v>5.21</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>280</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>-5.21</v>
+        <v>-2.75</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>GLOBALVECT</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>515.65</v>
+        <v>158.64</v>
       </c>
       <c r="C28" t="n">
-        <v>535.65</v>
+        <v>166.9</v>
       </c>
       <c r="D28" t="n">
-        <v>3.88</v>
+        <v>5.21</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>560.75</v>
+        <v>158.2</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>4.69</v>
+        <v>-5.21</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GOLDENTOBC</t>
+          <t>GATECHDVR</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>27.64</v>
+        <v>0.39</v>
       </c>
       <c r="C29" t="n">
-        <v>28.65</v>
+        <v>0.41</v>
       </c>
       <c r="D29" t="n">
-        <v>3.65</v>
+        <v>5.13</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>28.47</v>
+        <v>0.41</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PYRAMID</t>
+          <t>COMPUSOFT</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>143.35</v>
+        <v>13.27</v>
       </c>
       <c r="C30" t="n">
-        <v>148.5</v>
+        <v>13.95</v>
       </c>
       <c r="D30" t="n">
-        <v>3.59</v>
+        <v>5.12</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>148.01</v>
+        <v>13.28</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>-0.33</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AURIGROW</t>
+          <t>UMAEXPORTS</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.28</v>
+        <v>20.94</v>
       </c>
       <c r="C31" t="n">
-        <v>0.29</v>
+        <v>22</v>
       </c>
       <c r="D31" t="n">
-        <v>3.57</v>
+        <v>5.06</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0.29</v>
+        <v>21.86</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DCMNVL</t>
+          <t>RMDRIP</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>111.36</v>
+        <v>40.81</v>
       </c>
       <c r="C32" t="n">
-        <v>115.3</v>
+        <v>42.85</v>
       </c>
       <c r="D32" t="n">
-        <v>3.54</v>
+        <v>5</v>
       </c>
       <c r="E32" t="b">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>111</v>
+        <v>42.85</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>-3.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>UMAEXPORTS</t>
+          <t>WAAREEINDO</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>22.21</v>
+        <v>366.85</v>
       </c>
       <c r="C33" t="n">
-        <v>22.99</v>
+        <v>385.15</v>
       </c>
       <c r="D33" t="n">
-        <v>3.51</v>
+        <v>4.99</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>22.38</v>
+        <v>385.15</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>-2.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SIGMAADV</t>
+          <t>IL&amp;FSENGG</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>159.06</v>
+        <v>23.7</v>
       </c>
       <c r="C34" t="n">
-        <v>164.63</v>
+        <v>24.88</v>
       </c>
       <c r="D34" t="n">
-        <v>3.5</v>
+        <v>4.98</v>
       </c>
       <c r="E34" t="b">
         <v>0</v>
       </c>
-      <c r="F34" t="n">
-        <v>167.01</v>
-      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="n">
-        <v>1.45</v>
-      </c>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DGCONTENT</t>
+          <t>CKKRETAIL</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>23.87</v>
+        <v>125.7</v>
       </c>
       <c r="C35" t="n">
-        <v>24.7</v>
+        <v>131.95</v>
       </c>
       <c r="D35" t="n">
-        <v>3.48</v>
+        <v>4.97</v>
       </c>
       <c r="E35" t="b">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>24.5</v>
+        <v>131.95</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SHIVAMILLS</t>
+          <t>OWAIS</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>54.16</v>
+        <v>101.7</v>
       </c>
       <c r="C36" t="n">
-        <v>56</v>
+        <v>106.75</v>
       </c>
       <c r="D36" t="n">
-        <v>3.4</v>
+        <v>4.97</v>
       </c>
       <c r="E36" t="b">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>55.44</v>
+        <v>106.75</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SHANTI</t>
+          <t>DCMSRIND</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6.27</v>
+        <v>34.18</v>
       </c>
       <c r="C37" t="n">
-        <v>6.48</v>
+        <v>35.88</v>
       </c>
       <c r="D37" t="n">
-        <v>3.35</v>
+        <v>4.97</v>
       </c>
       <c r="E37" t="b">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>6.37</v>
+        <v>36.6</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>-1.7</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SITINET</t>
+          <t>UNIHEALTH</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.33</v>
+        <v>376.55</v>
       </c>
       <c r="C38" t="n">
-        <v>0.34</v>
+        <v>395</v>
       </c>
       <c r="D38" t="n">
-        <v>3.03</v>
+        <v>4.9</v>
       </c>
       <c r="E38" t="b">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.32</v>
+        <v>395.35</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>-5.88</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ZODIACLOTH</t>
+          <t>TECHERA</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>68.34999999999999</v>
+        <v>174.7</v>
       </c>
       <c r="C39" t="n">
-        <v>70.39</v>
+        <v>183.2</v>
       </c>
       <c r="D39" t="n">
-        <v>2.98</v>
+        <v>4.87</v>
       </c>
       <c r="E39" t="b">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>68.98</v>
+        <v>183.4</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>-2</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GEEKAYWIRE</t>
+          <t>PRIZOR</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>20.99</v>
+        <v>371</v>
       </c>
       <c r="C40" t="n">
-        <v>21.6</v>
+        <v>389</v>
       </c>
       <c r="D40" t="n">
-        <v>2.91</v>
+        <v>4.85</v>
       </c>
       <c r="E40" t="b">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>21.3</v>
+        <v>389.55</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>-1.39</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GRINFRA</t>
+          <t>APSISAERO</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>925.05</v>
+        <v>168.65</v>
       </c>
       <c r="C41" t="n">
-        <v>951.2</v>
+        <v>176.7</v>
       </c>
       <c r="D41" t="n">
-        <v>2.83</v>
+        <v>4.77</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>918</v>
+        <v>177.05</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>-3.49</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ASTRON</t>
+          <t>LIBAS</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3.93</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="C42" t="n">
-        <v>4.04</v>
+        <v>10.35</v>
       </c>
       <c r="D42" t="n">
-        <v>2.8</v>
+        <v>4.76</v>
       </c>
       <c r="E42" t="b">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>3.92</v>
+        <v>9.94</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>-2.97</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>RUCHINFRA</t>
+          <t>ORTEL</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>5.05</v>
+        <v>1.68</v>
       </c>
       <c r="C43" t="n">
-        <v>5.19</v>
+        <v>1.76</v>
       </c>
       <c r="D43" t="n">
-        <v>2.77</v>
+        <v>4.76</v>
       </c>
       <c r="E43" t="b">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>5.15</v>
+        <v>1.76</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>-0.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SHYAMDHANI</t>
+          <t>IFGLEXPOR</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>62.25</v>
+        <v>146</v>
       </c>
       <c r="C44" t="n">
-        <v>63.95</v>
+        <v>152.9</v>
       </c>
       <c r="D44" t="n">
-        <v>2.73</v>
+        <v>4.73</v>
       </c>
       <c r="E44" t="b">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>60.35</v>
+        <v>145.02</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>-5.63</v>
+        <v>-5.15</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>KEEPLEARN</t>
+          <t>GOLDSTAR</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.84</v>
+        <v>7.4</v>
       </c>
       <c r="C45" t="n">
-        <v>1.89</v>
+        <v>7.75</v>
       </c>
       <c r="D45" t="n">
-        <v>2.72</v>
+        <v>4.73</v>
       </c>
       <c r="E45" t="b">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>1.88</v>
+        <v>7.7</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>-0.53</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DNAMEDIA</t>
+          <t>ASHWINI</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3.39</v>
+        <v>142.25</v>
       </c>
       <c r="C46" t="n">
-        <v>3.48</v>
+        <v>148.95</v>
       </c>
       <c r="D46" t="n">
-        <v>2.65</v>
+        <v>4.71</v>
       </c>
       <c r="E46" t="b">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>3.43</v>
+        <v>147</v>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>-1.44</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>RVHL</t>
+          <t>SAMBHAAV</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>36.16</v>
+        <v>5.53</v>
       </c>
       <c r="C47" t="n">
-        <v>37.1</v>
+        <v>5.79</v>
       </c>
       <c r="D47" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="E47" t="b">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>36.69</v>
+        <v>5.68</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>-1.11</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PAVNAIND</t>
+          <t>OMKARCHEM</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>18.13</v>
+        <v>3.85</v>
       </c>
       <c r="C48" t="n">
-        <v>18.6</v>
+        <v>4.03</v>
       </c>
       <c r="D48" t="n">
-        <v>2.59</v>
+        <v>4.68</v>
       </c>
       <c r="E48" t="b">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>18.18</v>
+        <v>3.96</v>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>-2.26</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SETUINFRA</t>
+          <t>MEDICAMEQ</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.39</v>
+        <v>261.85</v>
       </c>
       <c r="C49" t="n">
-        <v>0.4</v>
+        <v>274</v>
       </c>
       <c r="D49" t="n">
-        <v>2.56</v>
+        <v>4.64</v>
       </c>
       <c r="E49" t="b">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0.39</v>
+        <v>263.7</v>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>-2.5</v>
+        <v>-3.76</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>OSWALSEEDS</t>
+          <t>INDTERRAIN</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>11.7</v>
+        <v>28</v>
       </c>
       <c r="C50" t="n">
-        <v>12</v>
+        <v>29.3</v>
       </c>
       <c r="D50" t="n">
-        <v>2.56</v>
+        <v>4.64</v>
       </c>
       <c r="E50" t="b">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>11.42</v>
+        <v>28.89</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>-4.83</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ARIHANTSUP</t>
+          <t>TARAPUR</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>221.25</v>
+        <v>25.93</v>
       </c>
       <c r="C51" t="n">
-        <v>226.9</v>
+        <v>27.13</v>
       </c>
       <c r="D51" t="n">
-        <v>2.55</v>
+        <v>4.63</v>
       </c>
       <c r="E51" t="b">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>219.5</v>
+        <v>26.89</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>-3.26</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>WEWIN</t>
+          <t>TRIGYN</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>40.96</v>
+        <v>47.66</v>
       </c>
       <c r="C52" t="n">
-        <v>42</v>
+        <v>49.8</v>
       </c>
       <c r="D52" t="n">
-        <v>2.54</v>
+        <v>4.49</v>
       </c>
       <c r="E52" t="b">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>39.78</v>
+        <v>49.36</v>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>-5.29</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ANTGRAPHIC</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8</v>
+        <v>7.14</v>
       </c>
       <c r="C53" t="n">
-        <v>0.82</v>
+        <v>7.46</v>
       </c>
       <c r="D53" t="n">
-        <v>2.5</v>
+        <v>4.48</v>
       </c>
       <c r="E53" t="b">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0.8</v>
+        <v>7.38</v>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>-2.44</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>VISASTEEL</t>
+          <t>DALMIASUG</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>32.38</v>
+        <v>298.75</v>
       </c>
       <c r="C54" t="n">
-        <v>33.19</v>
+        <v>312.1</v>
       </c>
       <c r="D54" t="n">
-        <v>2.5</v>
+        <v>4.47</v>
       </c>
       <c r="E54" t="b">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>31.75</v>
+        <v>318.3</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>-4.34</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>VGL</t>
+          <t>SRTL</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>59.71</v>
+        <v>48.27</v>
       </c>
       <c r="C55" t="n">
-        <v>61.2</v>
+        <v>50.4</v>
       </c>
       <c r="D55" t="n">
-        <v>2.5</v>
+        <v>4.41</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>59.8</v>
+        <v>49.8</v>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>-2.29</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SMLT</t>
+          <t>TARACHAND</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>68.15000000000001</v>
+        <v>55.5</v>
       </c>
       <c r="C56" t="n">
-        <v>69.84999999999999</v>
+        <v>57.95</v>
       </c>
       <c r="D56" t="n">
-        <v>2.49</v>
+        <v>4.41</v>
       </c>
       <c r="E56" t="b">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>68.83</v>
+        <v>57.41</v>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>-1.46</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>IMPEXFERRO</t>
+          <t>INDORAMA</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1.61</v>
+        <v>31.33</v>
       </c>
       <c r="C57" t="n">
-        <v>1.65</v>
+        <v>32.7</v>
       </c>
       <c r="D57" t="n">
-        <v>2.48</v>
+        <v>4.37</v>
       </c>
       <c r="E57" t="b">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>1.61</v>
+        <v>31.9</v>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>-2.42</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>JHS</t>
+          <t>CENTUM</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>8.08</v>
+        <v>2725.8</v>
       </c>
       <c r="C58" t="n">
-        <v>8.279999999999999</v>
+        <v>2844.3</v>
       </c>
       <c r="D58" t="n">
-        <v>2.48</v>
+        <v>4.35</v>
       </c>
       <c r="E58" t="b">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>8.1</v>
+        <v>2975.1</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>-2.17</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>REGENCERAM</t>
+          <t>AIRAN</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>41.88</v>
+        <v>15.21</v>
       </c>
       <c r="C59" t="n">
-        <v>42.9</v>
+        <v>15.87</v>
       </c>
       <c r="D59" t="n">
-        <v>2.44</v>
+        <v>4.34</v>
       </c>
       <c r="E59" t="b">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>42.9</v>
+        <v>15.29</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>-3.65</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FEL</t>
+          <t>CPEDU</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.41</v>
+        <v>165.36</v>
       </c>
       <c r="C60" t="n">
-        <v>0.42</v>
+        <v>172.4</v>
       </c>
       <c r="D60" t="n">
-        <v>2.44</v>
+        <v>4.26</v>
       </c>
       <c r="E60" t="b">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>0.42</v>
+        <v>168.75</v>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ABCOTS</t>
+          <t>MAGNUM</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>402.4</v>
+        <v>18.37</v>
       </c>
       <c r="C61" t="n">
-        <v>412</v>
+        <v>19.15</v>
       </c>
       <c r="D61" t="n">
-        <v>2.39</v>
+        <v>4.25</v>
       </c>
       <c r="E61" t="b">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>406.4</v>
+        <v>18.86</v>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>-1.36</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>HAVISHA</t>
+          <t>JSWHL</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1.26</v>
+        <v>15976</v>
       </c>
       <c r="C62" t="n">
-        <v>1.29</v>
+        <v>16650</v>
       </c>
       <c r="D62" t="n">
-        <v>2.38</v>
+        <v>4.22</v>
       </c>
       <c r="E62" t="b">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>1.24</v>
+        <v>16026</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>-3.88</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AERONEU</t>
+          <t>PAVNAIND</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>64.28</v>
+        <v>18.08</v>
       </c>
       <c r="C63" t="n">
-        <v>65.8</v>
+        <v>18.84</v>
       </c>
       <c r="D63" t="n">
-        <v>2.36</v>
+        <v>4.2</v>
       </c>
       <c r="E63" t="b">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>64.5</v>
+        <v>18.09</v>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>-1.98</v>
+        <v>-3.98</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CYBERMEDIA</t>
+          <t>NIBL</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>13.67</v>
+        <v>28.59</v>
       </c>
       <c r="C64" t="n">
-        <v>13.99</v>
+        <v>29.78</v>
       </c>
       <c r="D64" t="n">
-        <v>2.34</v>
+        <v>4.16</v>
       </c>
       <c r="E64" t="b">
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>13.56</v>
+        <v>29.35</v>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>-3.07</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>IFBAGRO</t>
+          <t>NIPPOBATRY</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>717.45</v>
+        <v>292.75</v>
       </c>
       <c r="C65" t="n">
-        <v>733.95</v>
+        <v>304.9</v>
       </c>
       <c r="D65" t="n">
-        <v>2.3</v>
+        <v>4.15</v>
       </c>
       <c r="E65" t="b">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>729.35</v>
+        <v>300.1</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>-0.63</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PASHUPATI</t>
+          <t>HINDCOMPOS</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>987.65</v>
+        <v>381.95</v>
       </c>
       <c r="C66" t="n">
-        <v>1010</v>
+        <v>397.8</v>
       </c>
       <c r="D66" t="n">
-        <v>2.26</v>
+        <v>4.15</v>
       </c>
       <c r="E66" t="b">
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>985.15</v>
+        <v>387.7</v>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>-2.46</v>
+        <v>-2.54</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CELEBRITY</t>
+          <t>SIGNPOST</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>7.63</v>
+        <v>236.6</v>
       </c>
       <c r="C67" t="n">
-        <v>7.8</v>
+        <v>246.1</v>
       </c>
       <c r="D67" t="n">
-        <v>2.23</v>
+        <v>4.02</v>
       </c>
       <c r="E67" t="b">
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>7.46</v>
+        <v>237.3</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>-4.36</v>
+        <v>-3.58</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>OWAIS</t>
+          <t>NAGREEKCAP</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>96.90000000000001</v>
+        <v>22.65</v>
       </c>
       <c r="C68" t="n">
-        <v>99</v>
+        <v>23.56</v>
       </c>
       <c r="D68" t="n">
-        <v>2.17</v>
+        <v>4.02</v>
       </c>
       <c r="E68" t="b">
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>101.7</v>
+        <v>23.89</v>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>2.73</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EIFFL</t>
+          <t>MANOMAY</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>231.26</v>
+        <v>201.64</v>
       </c>
       <c r="C69" t="n">
-        <v>236.25</v>
+        <v>209.71</v>
       </c>
       <c r="D69" t="n">
-        <v>2.16</v>
+        <v>4</v>
       </c>
       <c r="E69" t="b">
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>230.61</v>
+        <v>207.36</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>-2.39</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ACEINTEG</t>
+          <t>MFML</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>16.73</v>
+        <v>23.26</v>
       </c>
       <c r="C70" t="n">
-        <v>17.09</v>
+        <v>24.19</v>
       </c>
       <c r="D70" t="n">
-        <v>2.15</v>
+        <v>4</v>
       </c>
       <c r="E70" t="b">
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>16.95</v>
+        <v>23.97</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>-0.82</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MURUDCERA</t>
+          <t>KOTHARIPRO</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>30.07</v>
+        <v>63.39</v>
       </c>
       <c r="C71" t="n">
-        <v>30.7</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D71" t="n">
-        <v>2.1</v>
+        <v>3.96</v>
       </c>
       <c r="E71" t="b">
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>30.1</v>
+        <v>63.98</v>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>-1.95</v>
+        <v>-2.91</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>GULFPETRO</t>
+          <t>RKEC</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>29.29</v>
+        <v>34.31</v>
       </c>
       <c r="C72" t="n">
-        <v>29.9</v>
+        <v>35.64</v>
       </c>
       <c r="D72" t="n">
-        <v>2.08</v>
+        <v>3.88</v>
       </c>
       <c r="E72" t="b">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>28.77</v>
+        <v>34.64</v>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>-3.78</v>
+        <v>-2.81</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CORALFINAC</t>
+          <t>COOLCAPS</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>31.33</v>
+        <v>24.9</v>
       </c>
       <c r="C73" t="n">
-        <v>31.98</v>
+        <v>25.85</v>
       </c>
       <c r="D73" t="n">
-        <v>2.07</v>
+        <v>3.82</v>
       </c>
       <c r="E73" t="b">
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>31.85</v>
+        <v>26.1</v>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>-0.41</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SANCO</t>
+          <t>ASMS</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2.42</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="C74" t="n">
-        <v>2.47</v>
+        <v>8.44</v>
       </c>
       <c r="D74" t="n">
-        <v>2.07</v>
+        <v>3.81</v>
       </c>
       <c r="E74" t="b">
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>2.3</v>
+        <v>8.33</v>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>-6.88</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>NOIDATOLL</t>
+          <t>UNITEDPOLY</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>3.39</v>
+        <v>26.89</v>
       </c>
       <c r="C75" t="n">
-        <v>3.46</v>
+        <v>27.91</v>
       </c>
       <c r="D75" t="n">
-        <v>2.06</v>
+        <v>3.79</v>
       </c>
       <c r="E75" t="b">
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>3.35</v>
+        <v>26.8</v>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>-3.18</v>
+        <v>-3.98</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CCHHL</t>
+          <t>LASA</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>12.19</v>
+        <v>7.4</v>
       </c>
       <c r="C76" t="n">
-        <v>12.44</v>
+        <v>7.68</v>
       </c>
       <c r="D76" t="n">
-        <v>2.05</v>
+        <v>3.78</v>
       </c>
       <c r="E76" t="b">
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>11.82</v>
+        <v>7.39</v>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>-4.98</v>
+        <v>-3.78</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>TGBHOTELS</t>
+          <t>CROWN</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>8.789999999999999</v>
+        <v>115.55</v>
       </c>
       <c r="C77" t="n">
-        <v>8.970000000000001</v>
+        <v>119.89</v>
       </c>
       <c r="D77" t="n">
-        <v>2.05</v>
+        <v>3.76</v>
       </c>
       <c r="E77" t="b">
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>8.84</v>
+        <v>117.74</v>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>-1.45</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SIGMA</t>
+          <t>VIVIMEDLAB</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>40.18</v>
+        <v>6.39</v>
       </c>
       <c r="C78" t="n">
-        <v>41</v>
+        <v>6.63</v>
       </c>
       <c r="D78" t="n">
-        <v>2.04</v>
+        <v>3.76</v>
       </c>
       <c r="E78" t="b">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>40.43</v>
+        <v>6.47</v>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>-1.39</v>
+        <v>-2.41</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SUTLEJTEX</t>
+          <t>SINTERCOM</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>29.4</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="C79" t="n">
-        <v>30</v>
+        <v>79.2</v>
       </c>
       <c r="D79" t="n">
-        <v>2.04</v>
+        <v>3.66</v>
       </c>
       <c r="E79" t="b">
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>29.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>-2.33</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SURANAT&amp;P</t>
+          <t>ROML</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>17.74</v>
+        <v>43.4</v>
       </c>
       <c r="C80" t="n">
-        <v>18.1</v>
+        <v>44.98</v>
       </c>
       <c r="D80" t="n">
-        <v>2.03</v>
+        <v>3.64</v>
       </c>
       <c r="E80" t="b">
         <v>0</v>
       </c>
-      <c r="F80" t="inlineStr"/>
+      <c r="F80" t="n">
+        <v>44.49</v>
+      </c>
       <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="H80" t="n">
+        <v>-1.09</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>HINDCOMPOS</t>
+          <t>SPCENET</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>387.15</v>
+        <v>3.86</v>
       </c>
       <c r="C81" t="n">
-        <v>395</v>
+        <v>4</v>
       </c>
       <c r="D81" t="n">
-        <v>2.03</v>
+        <v>3.63</v>
       </c>
       <c r="E81" t="b">
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>385.5</v>
+        <v>3.94</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>-2.41</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>RUBFILA</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>62.86</v>
+        <v>556.15</v>
       </c>
       <c r="C82" t="n">
-        <v>64.09999999999999</v>
+        <v>576.15</v>
       </c>
       <c r="D82" t="n">
-        <v>1.97</v>
+        <v>3.6</v>
       </c>
       <c r="E82" t="b">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>61.68</v>
+        <v>558.95</v>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>-3.78</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>INTENTECH</t>
+          <t>NOIDATOLL</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>88.06999999999999</v>
+        <v>3.35</v>
       </c>
       <c r="C83" t="n">
-        <v>89.8</v>
+        <v>3.47</v>
       </c>
       <c r="D83" t="n">
-        <v>1.96</v>
+        <v>3.58</v>
       </c>
       <c r="E83" t="b">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>86.34999999999999</v>
+        <v>3.57</v>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>-3.84</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>RPPINFRA</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>6.67</v>
+        <v>68.31</v>
       </c>
       <c r="C84" t="n">
-        <v>6.8</v>
+        <v>70.75</v>
       </c>
       <c r="D84" t="n">
-        <v>1.95</v>
+        <v>3.57</v>
       </c>
       <c r="E84" t="b">
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>7.29</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>7.21</v>
+        <v>-2.57</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AKI</t>
+          <t>VIVIDHA</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>4.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C85" t="n">
-        <v>4.74</v>
+        <v>0.58</v>
       </c>
       <c r="D85" t="n">
-        <v>1.94</v>
+        <v>3.57</v>
       </c>
       <c r="E85" t="b">
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>4.61</v>
+        <v>0.58</v>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>-2.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SPCENET</t>
+          <t>SUVIDHAA</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>4.15</v>
+        <v>2.84</v>
       </c>
       <c r="C86" t="n">
-        <v>4.23</v>
+        <v>2.94</v>
       </c>
       <c r="D86" t="n">
-        <v>1.93</v>
+        <v>3.52</v>
       </c>
       <c r="E86" t="b">
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>4.2</v>
+        <v>2.83</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>-0.71</v>
+        <v>-3.74</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SILGO</t>
+          <t>UJJIVANSFB</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>72.01000000000001</v>
+        <v>52.49</v>
       </c>
       <c r="C87" t="n">
-        <v>73.40000000000001</v>
+        <v>54.33</v>
       </c>
       <c r="D87" t="n">
-        <v>1.93</v>
+        <v>3.51</v>
       </c>
       <c r="E87" t="b">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>71.59999999999999</v>
+        <v>53.99</v>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>-2.45</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SURANI</t>
+          <t>SHEKHAWATI</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>59.85</v>
+        <v>11.69</v>
       </c>
       <c r="C88" t="n">
-        <v>61</v>
+        <v>12.1</v>
       </c>
       <c r="D88" t="n">
-        <v>1.92</v>
+        <v>3.51</v>
       </c>
       <c r="E88" t="b">
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>71.8</v>
+        <v>12.07</v>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>17.7</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PIONEEREMB</t>
+          <t>BAGFILMS</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>25.32</v>
+        <v>4.28</v>
       </c>
       <c r="C89" t="n">
-        <v>25.8</v>
+        <v>4.43</v>
       </c>
       <c r="D89" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="E89" t="b">
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>24.98</v>
+        <v>4.4</v>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>-3.18</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MANAKSTEEL</t>
+          <t>RAJSREESUG</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>53.54</v>
+        <v>27.44</v>
       </c>
       <c r="C90" t="n">
-        <v>54.55</v>
+        <v>28.4</v>
       </c>
       <c r="D90" t="n">
-        <v>1.89</v>
+        <v>3.5</v>
       </c>
       <c r="E90" t="b">
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>53.2</v>
+        <v>29.66</v>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>-2.47</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>HARDWYN</t>
+          <t>JAICORPLTD</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>17.95</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="C91" t="n">
-        <v>18.29</v>
+        <v>101.99</v>
       </c>
       <c r="D91" t="n">
-        <v>1.89</v>
+        <v>3.47</v>
       </c>
       <c r="E91" t="b">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>17.94</v>
+        <v>106.5</v>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>-1.91</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>WANBURY</t>
+          <t>AURIGROW</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>249.35</v>
+        <v>0.29</v>
       </c>
       <c r="C92" t="n">
-        <v>253.95</v>
+        <v>0.3</v>
       </c>
       <c r="D92" t="n">
-        <v>1.84</v>
+        <v>3.45</v>
       </c>
       <c r="E92" t="b">
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>244</v>
+        <v>0.3</v>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
-        <v>-3.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>CHEMBONDCH</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>531.2</v>
+        <v>125.15</v>
       </c>
       <c r="C93" t="n">
-        <v>541</v>
+        <v>129.45</v>
       </c>
       <c r="D93" t="n">
-        <v>1.84</v>
+        <v>3.44</v>
       </c>
       <c r="E93" t="b">
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>534.5</v>
+        <v>129.6</v>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
-        <v>-1.2</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>XTGLOBAL</t>
+          <t>RUCHINFRA</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>30.99</v>
+        <v>4.96</v>
       </c>
       <c r="C94" t="n">
-        <v>31.55</v>
+        <v>5.13</v>
       </c>
       <c r="D94" t="n">
-        <v>1.81</v>
+        <v>3.43</v>
       </c>
       <c r="E94" t="b">
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>30.55</v>
+        <v>5</v>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>-3.17</v>
+        <v>-2.53</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AXITA</t>
+          <t>PARACABLES</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>8.85</v>
+        <v>34.23</v>
       </c>
       <c r="C95" t="n">
-        <v>9.01</v>
+        <v>35.4</v>
       </c>
       <c r="D95" t="n">
-        <v>1.81</v>
+        <v>3.42</v>
       </c>
       <c r="E95" t="b">
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>8.75</v>
+        <v>34.75</v>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>-2.89</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>GOYALALUM</t>
+          <t>DCMNVL</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>6.12</v>
+        <v>110.01</v>
       </c>
       <c r="C96" t="n">
-        <v>6.23</v>
+        <v>113.75</v>
       </c>
       <c r="D96" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="E96" t="b">
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>6.15</v>
+        <v>114.3</v>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>-1.28</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>NILASPACES</t>
+          <t>TARMAT</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>12.97</v>
+        <v>54.07</v>
       </c>
       <c r="C97" t="n">
-        <v>13.2</v>
+        <v>55.9</v>
       </c>
       <c r="D97" t="n">
-        <v>1.77</v>
+        <v>3.38</v>
       </c>
       <c r="E97" t="b">
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>12.8</v>
+        <v>53.12</v>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>-3.03</v>
+        <v>-4.97</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>REPL</t>
+          <t>EQUIPPP</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>72.73</v>
+        <v>18.63</v>
       </c>
       <c r="C98" t="n">
-        <v>74</v>
+        <v>19.25</v>
       </c>
       <c r="D98" t="n">
-        <v>1.75</v>
+        <v>3.33</v>
       </c>
       <c r="E98" t="b">
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>73.29000000000001</v>
+        <v>18.11</v>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>-0.96</v>
+        <v>-5.92</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AGSTRA</t>
+          <t>SCHNEIDER</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>2.93</v>
+        <v>895.2</v>
       </c>
       <c r="C99" t="n">
-        <v>2.98</v>
+        <v>925</v>
       </c>
       <c r="D99" t="n">
-        <v>1.71</v>
+        <v>3.33</v>
       </c>
       <c r="E99" t="b">
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>2.9</v>
+        <v>908.1</v>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
-        <v>-2.68</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BESTAGRO</t>
+          <t>RIIL</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>14.73</v>
+        <v>636.65</v>
       </c>
       <c r="C100" t="n">
-        <v>14.98</v>
+        <v>657.7</v>
       </c>
       <c r="D100" t="n">
-        <v>1.7</v>
+        <v>3.31</v>
       </c>
       <c r="E100" t="b">
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>14.53</v>
+        <v>709.95</v>
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>-3</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>GSS</t>
+          <t>AAKASH</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>11.21</v>
+        <v>9.08</v>
       </c>
       <c r="C101" t="n">
-        <v>11.4</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="D101" t="n">
-        <v>1.69</v>
+        <v>3.3</v>
       </c>
       <c r="E101" t="b">
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>11.15</v>
+        <v>9</v>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>-2.19</v>
+        <v>-4.05</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>HILTON</t>
+          <t>POLYSIL</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>16.23</v>
+        <v>159.7</v>
       </c>
       <c r="C102" t="n">
-        <v>16.5</v>
+        <v>164.95</v>
       </c>
       <c r="D102" t="n">
-        <v>1.66</v>
+        <v>3.29</v>
       </c>
       <c r="E102" t="b">
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>16.38</v>
+        <v>152</v>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>-0.73</v>
+        <v>-7.85</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AVONMORE</t>
+          <t>ELECTCAST</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>12.89</v>
+        <v>71.94</v>
       </c>
       <c r="C103" t="n">
-        <v>13.1</v>
+        <v>74.3</v>
       </c>
       <c r="D103" t="n">
-        <v>1.63</v>
+        <v>3.28</v>
       </c>
       <c r="E103" t="b">
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>12.8</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>-2.29</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MANAKALUCO</t>
+          <t>PRUDMOULI</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>25.4</v>
+        <v>11.53</v>
       </c>
       <c r="C104" t="n">
-        <v>25.79</v>
+        <v>11.9</v>
       </c>
       <c r="D104" t="n">
-        <v>1.54</v>
+        <v>3.21</v>
       </c>
       <c r="E104" t="b">
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>24.69</v>
+        <v>11.73</v>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
-        <v>-4.27</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>GVKPIL</t>
+          <t>SURANI</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>2.64</v>
+        <v>71.75</v>
       </c>
       <c r="C105" t="n">
-        <v>2.68</v>
+        <v>74</v>
       </c>
       <c r="D105" t="n">
-        <v>1.52</v>
+        <v>3.14</v>
       </c>
       <c r="E105" t="b">
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>2.68</v>
+        <v>68.75</v>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>-7.09</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>HESTERBIO</t>
+          <t>MAHEPC</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1401.5</v>
+        <v>113.44</v>
       </c>
       <c r="C106" t="n">
-        <v>1422.5</v>
+        <v>116.99</v>
       </c>
       <c r="D106" t="n">
-        <v>1.5</v>
+        <v>3.13</v>
       </c>
       <c r="E106" t="b">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>1435</v>
+        <v>114.58</v>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
-        <v>0.88</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>PRUDMOULI</t>
+          <t>OSWALAGRO</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>12.66</v>
+        <v>41.42</v>
       </c>
       <c r="C107" t="n">
-        <v>12.85</v>
+        <v>42.7</v>
       </c>
       <c r="D107" t="n">
-        <v>1.5</v>
+        <v>3.09</v>
       </c>
       <c r="E107" t="b">
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>12.18</v>
+        <v>42.56</v>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>-5.21</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>MAHASTEEL</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>234.9</v>
+        <v>925.55</v>
       </c>
       <c r="C108" t="n">
-        <v>238.4</v>
+        <v>953.95</v>
       </c>
       <c r="D108" t="n">
-        <v>1.49</v>
+        <v>3.07</v>
       </c>
       <c r="E108" t="b">
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>236.95</v>
+        <v>901.05</v>
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
-        <v>-0.61</v>
+        <v>-5.55</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MGEL</t>
+          <t>RADAAN</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>10.05</v>
+        <v>2.94</v>
       </c>
       <c r="C109" t="n">
-        <v>10.2</v>
+        <v>3.03</v>
       </c>
       <c r="D109" t="n">
-        <v>1.49</v>
+        <v>3.06</v>
       </c>
       <c r="E109" t="b">
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>10.01</v>
+        <v>2.94</v>
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>-1.86</v>
+        <v>-2.97</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>UNIDT</t>
+          <t>SITINET</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>162.87</v>
+        <v>0.33</v>
       </c>
       <c r="C110" t="n">
-        <v>165.3</v>
+        <v>0.34</v>
       </c>
       <c r="D110" t="n">
-        <v>1.49</v>
+        <v>3.03</v>
       </c>
       <c r="E110" t="b">
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>155.45</v>
+        <v>0.34</v>
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
-        <v>-5.96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ARCHIDPLY</t>
+          <t>BIL</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>71.45</v>
+        <v>699.3</v>
       </c>
       <c r="C111" t="n">
-        <v>72.5</v>
+        <v>720</v>
       </c>
       <c r="D111" t="n">
-        <v>1.47</v>
+        <v>2.96</v>
       </c>
       <c r="E111" t="b">
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>70.77</v>
+        <v>709.7</v>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>-2.39</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MAANALU</t>
+          <t>KCPSUGIND</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>131.06</v>
+        <v>23.31</v>
       </c>
       <c r="C112" t="n">
-        <v>132.98</v>
+        <v>24</v>
       </c>
       <c r="D112" t="n">
-        <v>1.46</v>
+        <v>2.96</v>
       </c>
       <c r="E112" t="b">
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>134.5</v>
+        <v>24.53</v>
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
-        <v>1.14</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MAHAPEXLTD</t>
+          <t>EXCEL</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>134.06</v>
+        <v>1.02</v>
       </c>
       <c r="C113" t="n">
-        <v>136</v>
+        <v>1.05</v>
       </c>
       <c r="D113" t="n">
-        <v>1.45</v>
+        <v>2.94</v>
       </c>
       <c r="E113" t="b">
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>132.49</v>
+        <v>1.02</v>
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>-2.58</v>
+        <v>-2.86</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>LAXMICOT</t>
+          <t>FROG</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>12.52</v>
+        <v>130</v>
       </c>
       <c r="C114" t="n">
-        <v>12.7</v>
+        <v>133.8</v>
       </c>
       <c r="D114" t="n">
-        <v>1.44</v>
+        <v>2.92</v>
       </c>
       <c r="E114" t="b">
         <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>12.35</v>
+        <v>129</v>
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
-        <v>-2.76</v>
+        <v>-3.59</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MTEDUCARE</t>
+          <t>ARMOUR</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1.39</v>
+        <v>22.35</v>
       </c>
       <c r="C115" t="n">
-        <v>1.41</v>
+        <v>23</v>
       </c>
       <c r="D115" t="n">
-        <v>1.44</v>
+        <v>2.91</v>
       </c>
       <c r="E115" t="b">
         <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>1.33</v>
+        <v>23</v>
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>-5.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>RPPINFRA</t>
+          <t>ENERGYDEV</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>72.70999999999999</v>
+        <v>14.91</v>
       </c>
       <c r="C116" t="n">
-        <v>73.75</v>
+        <v>15.34</v>
       </c>
       <c r="D116" t="n">
-        <v>1.43</v>
+        <v>2.88</v>
       </c>
       <c r="E116" t="b">
         <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>71.26000000000001</v>
+        <v>14.88</v>
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
-        <v>-3.38</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>GANGAFORGE</t>
+          <t>BAJAJINDEF</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>2.82</v>
+        <v>230.38</v>
       </c>
       <c r="C117" t="n">
-        <v>2.86</v>
+        <v>236.99</v>
       </c>
       <c r="D117" t="n">
-        <v>1.42</v>
+        <v>2.87</v>
       </c>
       <c r="E117" t="b">
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>2.83</v>
+        <v>233.93</v>
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>-1.05</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>RUDRA</t>
+          <t>GMRP&amp;UI</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>16.52</v>
+        <v>101.1</v>
       </c>
       <c r="C118" t="n">
-        <v>16.75</v>
+        <v>104</v>
       </c>
       <c r="D118" t="n">
-        <v>1.39</v>
+        <v>2.87</v>
       </c>
       <c r="E118" t="b">
         <v>0</v>
       </c>
-      <c r="F118" t="n">
-        <v>16.32</v>
-      </c>
+      <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
-      <c r="H118" t="n">
-        <v>-2.57</v>
-      </c>
+      <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ASAHISONG</t>
+          <t>RUCHIRA</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>197.3</v>
+        <v>99.06</v>
       </c>
       <c r="C119" t="n">
-        <v>199.89</v>
+        <v>101.89</v>
       </c>
       <c r="D119" t="n">
-        <v>1.31</v>
+        <v>2.86</v>
       </c>
       <c r="E119" t="b">
         <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>196.78</v>
+        <v>101.5</v>
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
-        <v>-1.56</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>LOVABLE</t>
+          <t>ASTRON</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>67.14</v>
+        <v>3.87</v>
       </c>
       <c r="C120" t="n">
-        <v>68</v>
+        <v>3.98</v>
       </c>
       <c r="D120" t="n">
-        <v>1.28</v>
+        <v>2.84</v>
       </c>
       <c r="E120" t="b">
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>67.09999999999999</v>
+        <v>3.93</v>
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
-        <v>-1.32</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>DJML</t>
+          <t>TREL</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>80.01000000000001</v>
+        <v>24.16</v>
       </c>
       <c r="C121" t="n">
-        <v>81</v>
+        <v>24.84</v>
       </c>
       <c r="D121" t="n">
-        <v>1.24</v>
+        <v>2.81</v>
       </c>
       <c r="E121" t="b">
         <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>80</v>
+        <v>24.87</v>
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
-        <v>-1.23</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>IMPAL</t>
+          <t>EMSLIMITED</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1022.4</v>
+        <v>290.85</v>
       </c>
       <c r="C122" t="n">
-        <v>1035</v>
+        <v>299</v>
       </c>
       <c r="D122" t="n">
-        <v>1.23</v>
+        <v>2.8</v>
       </c>
       <c r="E122" t="b">
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>1007.6</v>
+        <v>298.8</v>
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
-        <v>-2.65</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>GLOBE</t>
+          <t>EXXARO</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>2.49</v>
+        <v>6.81</v>
       </c>
       <c r="C123" t="n">
-        <v>2.52</v>
+        <v>7</v>
       </c>
       <c r="D123" t="n">
-        <v>1.2</v>
+        <v>2.79</v>
       </c>
       <c r="E123" t="b">
         <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>2.46</v>
+        <v>6.92</v>
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>-2.38</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>HMAAGRO</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>23.73</v>
+        <v>184.86</v>
       </c>
       <c r="C124" t="n">
-        <v>24.01</v>
+        <v>190</v>
       </c>
       <c r="D124" t="n">
-        <v>1.18</v>
+        <v>2.78</v>
       </c>
       <c r="E124" t="b">
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>23.43</v>
+        <v>188.54</v>
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
-        <v>-2.42</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>MANGALAM</t>
+          <t>BYKE</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>30.62</v>
+        <v>32.1</v>
       </c>
       <c r="C125" t="n">
-        <v>30.98</v>
+        <v>32.99</v>
       </c>
       <c r="D125" t="n">
-        <v>1.18</v>
+        <v>2.77</v>
       </c>
       <c r="E125" t="b">
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>30.9</v>
+        <v>32.85</v>
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>-0.26</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>VIPCLOTHNG</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>6.81</v>
+        <v>17.42</v>
       </c>
       <c r="C126" t="n">
-        <v>6.89</v>
+        <v>17.9</v>
       </c>
       <c r="D126" t="n">
-        <v>1.17</v>
+        <v>2.76</v>
       </c>
       <c r="E126" t="b">
         <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>6.74</v>
+        <v>17.69</v>
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
-        <v>-2.18</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>WEL</t>
+          <t>BPL</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>138.14</v>
+        <v>47.2</v>
       </c>
       <c r="C127" t="n">
-        <v>139.7</v>
+        <v>48.5</v>
       </c>
       <c r="D127" t="n">
-        <v>1.13</v>
+        <v>2.75</v>
       </c>
       <c r="E127" t="b">
         <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>137.59</v>
+        <v>48.03</v>
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
-        <v>-1.51</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>TOLINS</t>
+          <t>FORCEMOT</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>101.85</v>
+        <v>20720</v>
       </c>
       <c r="C128" t="n">
-        <v>103</v>
+        <v>21290</v>
       </c>
       <c r="D128" t="n">
-        <v>1.13</v>
+        <v>2.75</v>
       </c>
       <c r="E128" t="b">
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>100.53</v>
+        <v>21395</v>
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
-        <v>-2.4</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ZEELEARN</t>
+          <t>NATCAPSUQ</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>5.3</v>
+        <v>145.52</v>
       </c>
       <c r="C129" t="n">
-        <v>5.36</v>
+        <v>149.5</v>
       </c>
       <c r="D129" t="n">
-        <v>1.13</v>
+        <v>2.74</v>
       </c>
       <c r="E129" t="b">
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>5.26</v>
+        <v>149.25</v>
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
-        <v>-1.87</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>TTL</t>
+          <t>GRPLTD</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>8.99</v>
+        <v>1798</v>
       </c>
       <c r="C130" t="n">
-        <v>9.09</v>
+        <v>1846.8</v>
       </c>
       <c r="D130" t="n">
-        <v>1.11</v>
+        <v>2.71</v>
       </c>
       <c r="E130" t="b">
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>9.1</v>
+        <v>1824.2</v>
       </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
-        <v>0.11</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>TTKHLTCARE</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>255.25</v>
+        <v>816.15</v>
       </c>
       <c r="C131" t="n">
-        <v>258</v>
+        <v>838</v>
       </c>
       <c r="D131" t="n">
-        <v>1.08</v>
+        <v>2.68</v>
       </c>
       <c r="E131" t="b">
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>251.75</v>
+        <v>823.05</v>
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
-        <v>-2.42</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>KANPRPLA</t>
+          <t>GAUDIUMIVF</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>183.14</v>
+        <v>80.55</v>
       </c>
       <c r="C132" t="n">
-        <v>185</v>
+        <v>82.7</v>
       </c>
       <c r="D132" t="n">
-        <v>1.02</v>
+        <v>2.67</v>
       </c>
       <c r="E132" t="b">
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>181.75</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
-        <v>-1.76</v>
+        <v>-4.79</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>WAAREEINDO</t>
+          <t>KOTARISUG</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>349.4</v>
+        <v>23.37</v>
       </c>
       <c r="C133" t="n">
-        <v>352.95</v>
+        <v>23.99</v>
       </c>
       <c r="D133" t="n">
-        <v>1.02</v>
+        <v>2.65</v>
       </c>
       <c r="E133" t="b">
         <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>366.85</v>
+        <v>24.77</v>
       </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
-        <v>3.94</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ENERGYDEV</t>
+          <t>SERVOTECH</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>15.04</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="C134" t="n">
-        <v>15.19</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="D134" t="n">
-        <v>1</v>
+        <v>2.64</v>
       </c>
       <c r="E134" t="b">
         <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>15.44</v>
+        <v>69.88</v>
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
-        <v>1.65</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>AMNPLST</t>
+          <t>WEBELSOLAR</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>149.57</v>
+        <v>62.38</v>
       </c>
       <c r="C135" t="n">
-        <v>151</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="D135" t="n">
-        <v>0.96</v>
+        <v>2.61</v>
       </c>
       <c r="E135" t="b">
         <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>151.1</v>
+        <v>71.83</v>
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
-        <v>0.07000000000000001</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>VIJIFIN</t>
+          <t>DHAMPURSUG</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>3.18</v>
+        <v>120.38</v>
       </c>
       <c r="C136" t="n">
-        <v>3.21</v>
+        <v>123.5</v>
       </c>
       <c r="D136" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.59</v>
       </c>
       <c r="E136" t="b">
         <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>3.03</v>
+        <v>126.93</v>
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
-        <v>-5.61</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ENIL</t>
+          <t>FSL</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>105.91</v>
+        <v>220.22</v>
       </c>
       <c r="C137" t="n">
-        <v>106.9</v>
+        <v>225.9</v>
       </c>
       <c r="D137" t="n">
-        <v>0.93</v>
+        <v>2.58</v>
       </c>
       <c r="E137" t="b">
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>106.04</v>
+        <v>220.25</v>
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
-        <v>-0.8</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>PRAXIS</t>
+          <t>TCIFINANCE</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>6.45</v>
+        <v>13.65</v>
       </c>
       <c r="C138" t="n">
-        <v>6.51</v>
+        <v>14</v>
       </c>
       <c r="D138" t="n">
-        <v>0.93</v>
+        <v>2.56</v>
       </c>
       <c r="E138" t="b">
         <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>6.49</v>
+        <v>13.65</v>
       </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
-        <v>-0.31</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>MAWANASUG</t>
+          <t>BAJAJHIND</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>78.27</v>
+        <v>15.65</v>
       </c>
       <c r="C139" t="n">
-        <v>78.98999999999999</v>
+        <v>16.05</v>
       </c>
       <c r="D139" t="n">
-        <v>0.92</v>
+        <v>2.56</v>
       </c>
       <c r="E139" t="b">
         <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>78.8</v>
+        <v>16.5</v>
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
-        <v>-0.24</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>AMANTA</t>
+          <t>WESTLIFE</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>97.12</v>
+        <v>431.05</v>
       </c>
       <c r="C140" t="n">
-        <v>98</v>
+        <v>442</v>
       </c>
       <c r="D140" t="n">
-        <v>0.91</v>
+        <v>2.54</v>
       </c>
       <c r="E140" t="b">
         <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>95.86</v>
+        <v>433.85</v>
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
-        <v>-2.18</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>HINDOILEXP</t>
+          <t>ZIMLAB</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>131.18</v>
+        <v>66.52</v>
       </c>
       <c r="C141" t="n">
-        <v>132.35</v>
+        <v>68.2</v>
       </c>
       <c r="D141" t="n">
-        <v>0.89</v>
+        <v>2.53</v>
       </c>
       <c r="E141" t="b">
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>132.85</v>
+        <v>66.92</v>
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
-        <v>0.38</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>DISHTV</t>
+          <t>LPDC</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>2.28</v>
+        <v>5.94</v>
       </c>
       <c r="C142" t="n">
-        <v>2.3</v>
+        <v>6.09</v>
       </c>
       <c r="D142" t="n">
-        <v>0.88</v>
+        <v>2.53</v>
       </c>
       <c r="E142" t="b">
         <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>2.31</v>
+        <v>5.83</v>
       </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
-        <v>0.43</v>
+        <v>-4.27</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>IVP</t>
+          <t>LINDEINDIA</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>133.39</v>
+        <v>7011.5</v>
       </c>
       <c r="C143" t="n">
-        <v>134.5</v>
+        <v>7188</v>
       </c>
       <c r="D143" t="n">
-        <v>0.83</v>
+        <v>2.52</v>
       </c>
       <c r="E143" t="b">
         <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>132</v>
+        <v>7150</v>
       </c>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
-        <v>-1.86</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>JAYSREETEA</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>6.07</v>
+        <v>84.76000000000001</v>
       </c>
       <c r="C144" t="n">
-        <v>6.12</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="D144" t="n">
-        <v>0.82</v>
+        <v>2.52</v>
       </c>
       <c r="E144" t="b">
         <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>5.99</v>
+        <v>87.33</v>
       </c>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
-        <v>-2.12</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>BALAJEE</t>
+          <t>HAPPSTMNDS</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>25.77</v>
+        <v>371.65</v>
       </c>
       <c r="C145" t="n">
-        <v>25.98</v>
+        <v>381</v>
       </c>
       <c r="D145" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.52</v>
       </c>
       <c r="E145" t="b">
         <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>25.6</v>
+        <v>395.9</v>
       </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
-        <v>-1.46</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SASTASUNDR</t>
+          <t>MOLDTECH</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>285.6</v>
+        <v>121.84</v>
       </c>
       <c r="C146" t="n">
-        <v>287.9</v>
+        <v>124.9</v>
       </c>
       <c r="D146" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.51</v>
       </c>
       <c r="E146" t="b">
         <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>282.75</v>
+        <v>122.29</v>
       </c>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
-        <v>-1.79</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>KOHINOOR</t>
+          <t>BLUECOAST</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>23.41</v>
+        <v>20</v>
       </c>
       <c r="C147" t="n">
-        <v>23.6</v>
+        <v>20.5</v>
       </c>
       <c r="D147" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="E147" t="b">
         <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>22.92</v>
+        <v>20.49</v>
       </c>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
-        <v>-2.88</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>MEGASTAR</t>
+          <t>FEL</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>251.06</v>
+        <v>0.4</v>
       </c>
       <c r="C148" t="n">
-        <v>252.95</v>
+        <v>0.41</v>
       </c>
       <c r="D148" t="n">
-        <v>0.75</v>
+        <v>2.5</v>
       </c>
       <c r="E148" t="b">
         <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>245.02</v>
+        <v>0.41</v>
       </c>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
-        <v>-3.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>KANANIIND</t>
+          <t>AKSHAR</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>1.38</v>
+        <v>0.4</v>
       </c>
       <c r="C149" t="n">
-        <v>1.39</v>
+        <v>0.41</v>
       </c>
       <c r="D149" t="n">
-        <v>0.72</v>
+        <v>2.5</v>
       </c>
       <c r="E149" t="b">
         <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>1.36</v>
+        <v>0.4</v>
       </c>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
-        <v>-2.16</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>AEPL</t>
+          <t>INFOBEAN</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>18.37</v>
+        <v>136.11</v>
       </c>
       <c r="C150" t="n">
-        <v>18.5</v>
+        <v>139.5</v>
       </c>
       <c r="D150" t="n">
-        <v>0.71</v>
+        <v>2.49</v>
       </c>
       <c r="E150" t="b">
         <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>18</v>
+        <v>137.98</v>
       </c>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
-        <v>-2.7</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>AVROIND</t>
+          <t>ROSSTECH</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>125.95</v>
+        <v>685.35</v>
       </c>
       <c r="C151" t="n">
-        <v>126.8</v>
+        <v>702.4</v>
       </c>
       <c r="D151" t="n">
-        <v>0.67</v>
+        <v>2.49</v>
       </c>
       <c r="E151" t="b">
         <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>120.76</v>
+        <v>713.05</v>
       </c>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
-        <v>-4.76</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>HCL-INSYS</t>
+          <t>IFBAGRO</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>11.9</v>
+        <v>726.95</v>
       </c>
       <c r="C152" t="n">
-        <v>11.98</v>
+        <v>744.95</v>
       </c>
       <c r="D152" t="n">
-        <v>0.67</v>
+        <v>2.48</v>
       </c>
       <c r="E152" t="b">
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>11.83</v>
+        <v>763.25</v>
       </c>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="n">
-        <v>-1.25</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SUPERHOUSE</t>
+          <t>GOACARBON</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>145.05</v>
+        <v>306.3</v>
       </c>
       <c r="C153" t="n">
-        <v>146</v>
+        <v>313.9</v>
       </c>
       <c r="D153" t="n">
-        <v>0.65</v>
+        <v>2.48</v>
       </c>
       <c r="E153" t="b">
         <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>144.99</v>
+        <v>312</v>
       </c>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>AHLUCONT</t>
+          <t>GTPL</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>746</v>
+        <v>58.05</v>
       </c>
       <c r="C154" t="n">
-        <v>749.95</v>
+        <v>59.49</v>
       </c>
       <c r="D154" t="n">
-        <v>0.53</v>
+        <v>2.48</v>
       </c>
       <c r="E154" t="b">
         <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>731</v>
+        <v>58.48</v>
       </c>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="n">
-        <v>-2.53</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>MOTOGENFIN</t>
+          <t>PILITA</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>20.89</v>
+        <v>7.29</v>
       </c>
       <c r="C155" t="n">
-        <v>21</v>
+        <v>7.47</v>
       </c>
       <c r="D155" t="n">
-        <v>0.53</v>
+        <v>2.47</v>
       </c>
       <c r="E155" t="b">
         <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>20.8</v>
+        <v>7.58</v>
       </c>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="n">
-        <v>-0.95</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>KANORICHEM</t>
+          <t>KAMATHOTEL</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>63.07</v>
+        <v>179.57</v>
       </c>
       <c r="C156" t="n">
-        <v>63.4</v>
+        <v>183.99</v>
       </c>
       <c r="D156" t="n">
-        <v>0.52</v>
+        <v>2.46</v>
       </c>
       <c r="E156" t="b">
         <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>62.03</v>
+        <v>182.33</v>
       </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="n">
-        <v>-2.16</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>EMMBI</t>
+          <t>DEVIT</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>82.06999999999999</v>
+        <v>27.82</v>
       </c>
       <c r="C157" t="n">
-        <v>82.5</v>
+        <v>28.5</v>
       </c>
       <c r="D157" t="n">
-        <v>0.52</v>
+        <v>2.44</v>
       </c>
       <c r="E157" t="b">
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>81.61</v>
+        <v>28.45</v>
       </c>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="n">
-        <v>-1.08</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>SEMAC</t>
+          <t>CIFL</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>283.54</v>
+        <v>25.38</v>
       </c>
       <c r="C158" t="n">
-        <v>284.99</v>
+        <v>26</v>
       </c>
       <c r="D158" t="n">
-        <v>0.51</v>
+        <v>2.44</v>
       </c>
       <c r="E158" t="b">
         <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>279.99</v>
+        <v>25.38</v>
       </c>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="n">
-        <v>-1.75</v>
+        <v>-2.38</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>FOCUS</t>
+          <t>MENONBE</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>68.04000000000001</v>
+        <v>117.14</v>
       </c>
       <c r="C159" t="n">
-        <v>68.38</v>
+        <v>120</v>
       </c>
       <c r="D159" t="n">
-        <v>0.5</v>
+        <v>2.44</v>
       </c>
       <c r="E159" t="b">
         <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>67.5</v>
+        <v>119.86</v>
       </c>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="n">
-        <v>-1.29</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>APCL</t>
+          <t>SESHAPAPER</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>114.58</v>
+        <v>259.1</v>
       </c>
       <c r="C160" t="n">
-        <v>115.15</v>
+        <v>265.4</v>
       </c>
       <c r="D160" t="n">
-        <v>0.5</v>
+        <v>2.43</v>
       </c>
       <c r="E160" t="b">
         <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>114.94</v>
+        <v>262.15</v>
       </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="n">
-        <v>-0.18</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ONWARDTEC</t>
+          <t>RADIANTCMS</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>248.3</v>
+        <v>35.15</v>
       </c>
       <c r="C161" t="n">
-        <v>249.55</v>
+        <v>36</v>
       </c>
       <c r="D161" t="n">
-        <v>0.5</v>
+        <v>2.42</v>
       </c>
       <c r="E161" t="b">
         <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>242</v>
+        <v>35.68</v>
       </c>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="n">
-        <v>-3.03</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>TTKPRESTIG</t>
+          <t>IZMO</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>477.7</v>
+        <v>702.05</v>
       </c>
       <c r="C162" t="n">
-        <v>480.1</v>
+        <v>719</v>
       </c>
       <c r="D162" t="n">
-        <v>0.5</v>
+        <v>2.41</v>
       </c>
       <c r="E162" t="b">
         <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>485.85</v>
+        <v>713.5</v>
       </c>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="n">
-        <v>1.2</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>JUBLCPL</t>
+          <t>AURUM</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>1706.7</v>
+        <v>167.02</v>
       </c>
       <c r="C163" t="n">
-        <v>1715.2</v>
+        <v>171</v>
       </c>
       <c r="D163" t="n">
-        <v>0.5</v>
+        <v>2.38</v>
       </c>
       <c r="E163" t="b">
         <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>1673.5</v>
+        <v>169.22</v>
       </c>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="n">
-        <v>-2.43</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>BELLACASA</t>
+          <t>C2C</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>269</v>
+        <v>352.6</v>
       </c>
       <c r="C164" t="n">
-        <v>270.35</v>
+        <v>361</v>
       </c>
       <c r="D164" t="n">
-        <v>0.5</v>
+        <v>2.38</v>
       </c>
       <c r="E164" t="b">
         <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>267</v>
+        <v>363.95</v>
       </c>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="n">
-        <v>-1.24</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>BFUTILITIE</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>1109.4</v>
+        <v>411.5</v>
       </c>
       <c r="C165" t="n">
-        <v>1115</v>
+        <v>421.3</v>
       </c>
       <c r="D165" t="n">
-        <v>0.5</v>
+        <v>2.38</v>
       </c>
       <c r="E165" t="b">
         <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>1079.4</v>
+        <v>425</v>
       </c>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="n">
-        <v>-3.19</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>MCL</t>
+          <t>RVTH</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>62.78</v>
+        <v>625.4</v>
       </c>
       <c r="C166" t="n">
-        <v>63.09</v>
+        <v>640.15</v>
       </c>
       <c r="D166" t="n">
-        <v>0.49</v>
+        <v>2.36</v>
       </c>
       <c r="E166" t="b">
         <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>61.8</v>
+        <v>624.3</v>
       </c>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="n">
-        <v>-2.04</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>KMSUGAR</t>
+          <t>ORIENTALTL</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>25.07</v>
+        <v>5.13</v>
       </c>
       <c r="C167" t="n">
-        <v>25.19</v>
+        <v>5.25</v>
       </c>
       <c r="D167" t="n">
-        <v>0.48</v>
+        <v>2.34</v>
       </c>
       <c r="E167" t="b">
         <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>25.39</v>
+        <v>5.23</v>
       </c>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="n">
-        <v>0.79</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>LGHL</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>269.05</v>
+        <v>2047.4</v>
       </c>
       <c r="C168" t="n">
-        <v>270.35</v>
+        <v>2095</v>
       </c>
       <c r="D168" t="n">
-        <v>0.48</v>
+        <v>2.32</v>
       </c>
       <c r="E168" t="b">
         <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>269.05</v>
+        <v>2084</v>
       </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="n">
-        <v>-0.48</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>KHAITANLTD</t>
+          <t>RAJMET</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>99</v>
+        <v>3.45</v>
       </c>
       <c r="C169" t="n">
-        <v>99.48</v>
+        <v>3.53</v>
       </c>
       <c r="D169" t="n">
-        <v>0.48</v>
+        <v>2.32</v>
       </c>
       <c r="E169" t="b">
         <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>95.48</v>
+        <v>3.51</v>
       </c>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="n">
-        <v>-4.02</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>JETFREIGHT</t>
+          <t>ASALCBR</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>17.75</v>
+        <v>722.3</v>
       </c>
       <c r="C170" t="n">
-        <v>17.83</v>
+        <v>739</v>
       </c>
       <c r="D170" t="n">
-        <v>0.45</v>
+        <v>2.31</v>
       </c>
       <c r="E170" t="b">
         <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>17.63</v>
+        <v>742.95</v>
       </c>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="n">
-        <v>-1.12</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>KABRAEXTRU</t>
+          <t>HCC</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>220.7</v>
+        <v>15.15</v>
       </c>
       <c r="C171" t="n">
-        <v>221.7</v>
+        <v>15.5</v>
       </c>
       <c r="D171" t="n">
-        <v>0.45</v>
+        <v>2.31</v>
       </c>
       <c r="E171" t="b">
         <v>0</v>
       </c>
       <c r="F171" t="n">
-        <v>215.15</v>
+        <v>15.65</v>
       </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="n">
-        <v>-2.95</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>CALSOFT</t>
+          <t>KOHINOOR</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>13.5</v>
+        <v>22.58</v>
       </c>
       <c r="C172" t="n">
-        <v>13.56</v>
+        <v>23.1</v>
       </c>
       <c r="D172" t="n">
-        <v>0.44</v>
+        <v>2.3</v>
       </c>
       <c r="E172" t="b">
         <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>13.48</v>
+        <v>22.73</v>
       </c>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="n">
-        <v>-0.59</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ALMONDZ</t>
+          <t>RCOM</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>13.94</v>
+        <v>0.87</v>
       </c>
       <c r="C173" t="n">
-        <v>14</v>
+        <v>0.89</v>
       </c>
       <c r="D173" t="n">
-        <v>0.43</v>
+        <v>2.3</v>
       </c>
       <c r="E173" t="b">
         <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>14.22</v>
+        <v>0.91</v>
       </c>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>KRIDHANINF</t>
+          <t>GOKULAGRO</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>2.46</v>
+        <v>182.37</v>
       </c>
       <c r="C174" t="n">
-        <v>2.47</v>
+        <v>186.57</v>
       </c>
       <c r="D174" t="n">
-        <v>0.41</v>
+        <v>2.3</v>
       </c>
       <c r="E174" t="b">
         <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>2.41</v>
+        <v>185.21</v>
       </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="n">
-        <v>-2.43</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>CAPINVIT</t>
+          <t>DWARKESH</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>68.12</v>
+        <v>37.65</v>
       </c>
       <c r="C175" t="n">
-        <v>68.39</v>
+        <v>38.51</v>
       </c>
       <c r="D175" t="n">
-        <v>0.4</v>
+        <v>2.28</v>
       </c>
       <c r="E175" t="b">
         <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>67.76000000000001</v>
+        <v>39.6</v>
       </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="n">
-        <v>-0.92</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>PLAZACABLE</t>
+          <t>MSPL</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>34.65</v>
+        <v>29.53</v>
       </c>
       <c r="C176" t="n">
-        <v>34.79</v>
+        <v>30.2</v>
       </c>
       <c r="D176" t="n">
-        <v>0.4</v>
+        <v>2.27</v>
       </c>
       <c r="E176" t="b">
         <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>34.35</v>
+        <v>30.09</v>
       </c>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="n">
-        <v>-1.26</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>GENCON</t>
+          <t>KAKATCEM</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>43.78</v>
+        <v>100.66</v>
       </c>
       <c r="C177" t="n">
-        <v>43.95</v>
+        <v>102.94</v>
       </c>
       <c r="D177" t="n">
-        <v>0.39</v>
+        <v>2.27</v>
       </c>
       <c r="E177" t="b">
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>43.84</v>
+        <v>102</v>
       </c>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="n">
-        <v>-0.25</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>BHANDARI</t>
+          <t>MURUDCERA</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>2.57</v>
+        <v>30.02</v>
       </c>
       <c r="C178" t="n">
-        <v>2.58</v>
+        <v>30.7</v>
       </c>
       <c r="D178" t="n">
-        <v>0.39</v>
+        <v>2.27</v>
       </c>
       <c r="E178" t="b">
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>2.57</v>
+        <v>30.19</v>
       </c>
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="n">
-        <v>-0.39</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>DCI</t>
+          <t>NAHARPOLY</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>277.4</v>
+        <v>236.43</v>
       </c>
       <c r="C179" t="n">
-        <v>278.4</v>
+        <v>241.8</v>
       </c>
       <c r="D179" t="n">
-        <v>0.36</v>
+        <v>2.27</v>
       </c>
       <c r="E179" t="b">
         <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>270.8</v>
+        <v>242.72</v>
       </c>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="n">
-        <v>-2.73</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>RSYSTEMS</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>262.65</v>
+        <v>98.77</v>
       </c>
       <c r="C180" t="n">
-        <v>263.6</v>
+        <v>101</v>
       </c>
       <c r="D180" t="n">
-        <v>0.36</v>
+        <v>2.26</v>
       </c>
       <c r="E180" t="b">
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>263.3</v>
+        <v>102.09</v>
       </c>
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="n">
-        <v>-0.11</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SOLEX</t>
+          <t>SHANTI</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>950.5</v>
+        <v>6.21</v>
       </c>
       <c r="C181" t="n">
-        <v>953.95</v>
+        <v>6.35</v>
       </c>
       <c r="D181" t="n">
-        <v>0.36</v>
+        <v>2.25</v>
       </c>
       <c r="E181" t="b">
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>924.35</v>
+        <v>6.3</v>
       </c>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="n">
-        <v>-3.1</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>RMDRIP</t>
+          <t>LALPATHLAB</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>38.87</v>
+        <v>1325.4</v>
       </c>
       <c r="C182" t="n">
-        <v>39</v>
+        <v>1355</v>
       </c>
       <c r="D182" t="n">
-        <v>0.33</v>
+        <v>2.23</v>
       </c>
       <c r="E182" t="b">
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>40.81</v>
+        <v>1321.1</v>
       </c>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="n">
-        <v>4.64</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>VADILALIND</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>470.45</v>
+        <v>4573.2</v>
       </c>
       <c r="C183" t="n">
-        <v>471.95</v>
+        <v>4675</v>
       </c>
       <c r="D183" t="n">
-        <v>0.32</v>
+        <v>2.23</v>
       </c>
       <c r="E183" t="b">
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>478.5</v>
+        <v>4605.1</v>
       </c>
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="n">
-        <v>1.39</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>MBLINFRA</t>
+          <t>RUDRA</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>22.32</v>
+        <v>16.24</v>
       </c>
       <c r="C184" t="n">
-        <v>22.39</v>
+        <v>16.6</v>
       </c>
       <c r="D184" t="n">
-        <v>0.31</v>
+        <v>2.22</v>
       </c>
       <c r="E184" t="b">
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>22.23</v>
+        <v>16.56</v>
       </c>
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="n">
-        <v>-0.71</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>FLEXITUFF</t>
+          <t>OLAELEC</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>6.45</v>
+        <v>23.48</v>
       </c>
       <c r="C185" t="n">
-        <v>6.47</v>
+        <v>24</v>
       </c>
       <c r="D185" t="n">
-        <v>0.31</v>
+        <v>2.21</v>
       </c>
       <c r="E185" t="b">
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>6.42</v>
+        <v>23.69</v>
       </c>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="n">
-        <v>-0.77</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ORIENTCER</t>
+          <t>SKIPPER</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>38.19</v>
+        <v>351.25</v>
       </c>
       <c r="C186" t="n">
-        <v>38.3</v>
+        <v>358.95</v>
       </c>
       <c r="D186" t="n">
-        <v>0.29</v>
+        <v>2.19</v>
       </c>
       <c r="E186" t="b">
         <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>39.4</v>
+        <v>354.9</v>
       </c>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="n">
-        <v>2.87</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>GLOBECIVIL</t>
+          <t>AVANTIFEED</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>43.23</v>
+        <v>1174.4</v>
       </c>
       <c r="C187" t="n">
-        <v>43.35</v>
+        <v>1200</v>
       </c>
       <c r="D187" t="n">
-        <v>0.28</v>
+        <v>2.18</v>
       </c>
       <c r="E187" t="b">
         <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>42.95</v>
+        <v>1210.6</v>
       </c>
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="n">
-        <v>-0.92</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>MINDTECK</t>
+          <t>GATECH</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>183.75</v>
+        <v>0.46</v>
       </c>
       <c r="C188" t="n">
-        <v>184.25</v>
+        <v>0.47</v>
       </c>
       <c r="D188" t="n">
-        <v>0.27</v>
+        <v>2.17</v>
       </c>
       <c r="E188" t="b">
         <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>179.27</v>
+        <v>0.47</v>
       </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="n">
-        <v>-2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>IFGLEXPOR</t>
+          <t>AAREYDRUGS</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>146.32</v>
+        <v>66.95</v>
       </c>
       <c r="C189" t="n">
-        <v>146.7</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="D189" t="n">
-        <v>0.26</v>
+        <v>2.17</v>
       </c>
       <c r="E189" t="b">
         <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>144.91</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="n">
-        <v>-1.22</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>NDLVENTURE</t>
+          <t>DEEDEV</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>114.72</v>
+        <v>266.1</v>
       </c>
       <c r="C190" t="n">
-        <v>115</v>
+        <v>271.85</v>
       </c>
       <c r="D190" t="n">
-        <v>0.24</v>
+        <v>2.16</v>
       </c>
       <c r="E190" t="b">
         <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>115.57</v>
+        <v>272.8</v>
       </c>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="n">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>PNC</t>
+          <t>SSDL</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>21.05</v>
+        <v>56.53</v>
       </c>
       <c r="C191" t="n">
-        <v>21.1</v>
+        <v>57.75</v>
       </c>
       <c r="D191" t="n">
-        <v>0.24</v>
+        <v>2.16</v>
       </c>
       <c r="E191" t="b">
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>20.94</v>
+        <v>58</v>
       </c>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="n">
-        <v>-0.76</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>GFLLIMITED</t>
+          <t>SARDAEN</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>45.4</v>
+        <v>509.65</v>
       </c>
       <c r="C192" t="n">
-        <v>45.5</v>
+        <v>520.5</v>
       </c>
       <c r="D192" t="n">
-        <v>0.22</v>
+        <v>2.13</v>
       </c>
       <c r="E192" t="b">
         <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>44.45</v>
+        <v>521.5</v>
       </c>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="n">
-        <v>-2.31</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SIKKO</t>
+          <t>JAYAGROGN</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>4.76</v>
+        <v>166.45</v>
       </c>
       <c r="C193" t="n">
-        <v>4.77</v>
+        <v>170</v>
       </c>
       <c r="D193" t="n">
-        <v>0.21</v>
+        <v>2.13</v>
       </c>
       <c r="E193" t="b">
         <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>4.74</v>
+        <v>169.51</v>
       </c>
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="n">
-        <v>-0.63</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SHAH</t>
+          <t>UNIDT</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>4.77</v>
+        <v>152.16</v>
       </c>
       <c r="C194" t="n">
-        <v>4.78</v>
+        <v>155.4</v>
       </c>
       <c r="D194" t="n">
-        <v>0.21</v>
+        <v>2.13</v>
       </c>
       <c r="E194" t="b">
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>4.73</v>
+        <v>156.52</v>
       </c>
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="n">
-        <v>-1.05</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>HINDCON</t>
+          <t>SAGCEM</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>18.9</v>
+        <v>172.24</v>
       </c>
       <c r="C195" t="n">
-        <v>18.94</v>
+        <v>175.88</v>
       </c>
       <c r="D195" t="n">
-        <v>0.21</v>
+        <v>2.11</v>
       </c>
       <c r="E195" t="b">
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>18.64</v>
+        <v>173.39</v>
       </c>
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="n">
-        <v>-1.58</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>RELCHEMQ</t>
+          <t>AVADHSUGAR</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>114.68</v>
+        <v>426.1</v>
       </c>
       <c r="C196" t="n">
-        <v>114.9</v>
+        <v>435.05</v>
       </c>
       <c r="D196" t="n">
-        <v>0.19</v>
+        <v>2.1</v>
       </c>
       <c r="E196" t="b">
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>113.98</v>
+        <v>448.2</v>
       </c>
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="n">
-        <v>-0.8</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>INDIGRID</t>
+          <t>STALLION</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>164.74</v>
+        <v>112.39</v>
       </c>
       <c r="C197" t="n">
-        <v>165</v>
+        <v>114.75</v>
       </c>
       <c r="D197" t="n">
-        <v>0.16</v>
+        <v>2.1</v>
       </c>
       <c r="E197" t="b">
         <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>164.52</v>
+        <v>113.85</v>
       </c>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="n">
-        <v>-0.29</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>BHARATRAS</t>
+          <t>BELRISE</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>1338.1</v>
+        <v>177.27</v>
       </c>
       <c r="C198" t="n">
-        <v>1340</v>
+        <v>181</v>
       </c>
       <c r="D198" t="n">
-        <v>0.14</v>
+        <v>2.1</v>
       </c>
       <c r="E198" t="b">
         <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>1299.2</v>
+        <v>185.74</v>
       </c>
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="n">
-        <v>-3.04</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>THEJO</t>
+          <t>COROMANDEL</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>1583.6</v>
+        <v>1973.7</v>
       </c>
       <c r="C199" t="n">
-        <v>1585.8</v>
+        <v>2015</v>
       </c>
       <c r="D199" t="n">
-        <v>0.14</v>
+        <v>2.09</v>
       </c>
       <c r="E199" t="b">
         <v>0</v>
       </c>
       <c r="F199" t="n">
-        <v>1572</v>
+        <v>1986.1</v>
       </c>
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="n">
-        <v>-0.87</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>INTLCONV</t>
+          <t>RADIOCITY</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>69.90000000000001</v>
+        <v>5.27</v>
       </c>
       <c r="C200" t="n">
-        <v>70</v>
+        <v>5.38</v>
       </c>
       <c r="D200" t="n">
-        <v>0.14</v>
+        <v>2.09</v>
       </c>
       <c r="E200" t="b">
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>70.59</v>
+        <v>5.24</v>
       </c>
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="n">
-        <v>0.84</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>BCONCEPTS</t>
+          <t>BLKASHYAP</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>231.15</v>
+        <v>49.17</v>
       </c>
       <c r="C201" t="n">
-        <v>231.45</v>
+        <v>50.2</v>
       </c>
       <c r="D201" t="n">
-        <v>0.13</v>
+        <v>2.09</v>
       </c>
       <c r="E201" t="b">
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>238</v>
+        <v>50</v>
       </c>
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="n">
-        <v>2.83</v>
+        <v>-0.4</v>
       </c>
     </row>
   </sheetData>

--- a/data/trending_momentum_stocks.xlsx
+++ b/data/trending_momentum_stocks.xlsx
@@ -461,595 +461,595 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>INDIQUBE</t>
+          <t>HGM</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>146.39</v>
+        <v>44.88</v>
       </c>
       <c r="C2" t="n">
-        <v>172</v>
+        <v>49.9</v>
       </c>
       <c r="D2" t="n">
-        <v>17.49</v>
+        <v>11.19</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>152.4</v>
+        <v>53.85</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>-11.4</v>
+        <v>7.92</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SINGERIND</t>
+          <t>TFL</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70.42</v>
+        <v>12.79</v>
       </c>
       <c r="C3" t="n">
-        <v>79.29000000000001</v>
+        <v>13.97</v>
       </c>
       <c r="D3" t="n">
-        <v>12.6</v>
+        <v>9.23</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>72.95</v>
+        <v>12.54</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>-8</v>
+        <v>-10.24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GVPTECH</t>
+          <t>INFOMEDIA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.58</v>
+        <v>4.93</v>
       </c>
       <c r="C4" t="n">
-        <v>7.36</v>
+        <v>5.35</v>
       </c>
       <c r="D4" t="n">
-        <v>11.85</v>
+        <v>8.52</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>7.78</v>
+        <v>4.63</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>5.71</v>
+        <v>-13.46</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FINKURVE</t>
+          <t>TVVISION</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.59999999999999</v>
+        <v>5.26</v>
       </c>
       <c r="C5" t="n">
-        <v>72</v>
+        <v>5.68</v>
       </c>
       <c r="D5" t="n">
-        <v>9.76</v>
+        <v>7.98</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>67.5</v>
+        <v>4.92</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>-6.25</v>
+        <v>-13.38</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ROSSELLIND</t>
+          <t>CYBERMEDIA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45.74</v>
+        <v>13.12</v>
       </c>
       <c r="C6" t="n">
-        <v>50.01</v>
+        <v>14.07</v>
       </c>
       <c r="D6" t="n">
-        <v>9.34</v>
+        <v>7.24</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>46.51</v>
+        <v>13</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>-7</v>
+        <v>-7.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KEYFINSERV</t>
+          <t>DSFCL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>260.7</v>
+        <v>21.96</v>
       </c>
       <c r="C7" t="n">
-        <v>284.9</v>
+        <v>23.48</v>
       </c>
       <c r="D7" t="n">
-        <v>9.279999999999999</v>
+        <v>6.92</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>264.75</v>
+        <v>22.11</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>-7.07</v>
+        <v>-5.83</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VASWANI</t>
+          <t>NAHARCAP</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52.78</v>
+        <v>225.85</v>
       </c>
       <c r="C8" t="n">
-        <v>57.55</v>
+        <v>239</v>
       </c>
       <c r="D8" t="n">
-        <v>9.039999999999999</v>
+        <v>5.82</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>53.3</v>
+        <v>217.69</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>-7.38</v>
+        <v>-8.92</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RAJTV</t>
+          <t>DCXINDIA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36.36</v>
+        <v>163.72</v>
       </c>
       <c r="C9" t="n">
-        <v>39.5</v>
+        <v>173</v>
       </c>
       <c r="D9" t="n">
-        <v>8.640000000000001</v>
+        <v>5.67</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>37.58</v>
+        <v>179.49</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>-4.86</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NKIND</t>
+          <t>ANTGRAPHIC</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>0.77</v>
       </c>
       <c r="C10" t="n">
-        <v>67.98999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>7.92</v>
+        <v>5.19</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>63</v>
+        <v>0.75</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>-7.34</v>
+        <v>-7.41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VERTOZ</t>
+          <t>VADILALIND</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>36.16</v>
+        <v>4531.8</v>
       </c>
       <c r="C11" t="n">
-        <v>39</v>
+        <v>4763.4</v>
       </c>
       <c r="D11" t="n">
-        <v>7.85</v>
+        <v>5.11</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>36.83</v>
+        <v>4367.6</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>-5.56</v>
+        <v>-8.31</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DHARAN</t>
+          <t>NINSYS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.14</v>
+        <v>290.2</v>
       </c>
       <c r="C12" t="n">
-        <v>0.15</v>
+        <v>304.95</v>
       </c>
       <c r="D12" t="n">
-        <v>7.14</v>
+        <v>5.08</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.15</v>
+        <v>292.8</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>-3.98</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LATTEYS</t>
+          <t>APSISAERO</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19.14</v>
+        <v>177.05</v>
       </c>
       <c r="C13" t="n">
-        <v>20.49</v>
+        <v>185.9</v>
       </c>
       <c r="D13" t="n">
-        <v>7.05</v>
+        <v>5</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>19.85</v>
+        <v>185.9</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>-3.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GEECEE</t>
+          <t>DENEERS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>254.9</v>
+        <v>147</v>
       </c>
       <c r="C14" t="n">
-        <v>271.95</v>
+        <v>154.3</v>
       </c>
       <c r="D14" t="n">
-        <v>6.69</v>
+        <v>4.97</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>258.05</v>
+        <v>154.35</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>-5.11</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CELEBRITY</t>
+          <t>PRUDMOULI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.18</v>
+        <v>12.1</v>
       </c>
       <c r="C15" t="n">
-        <v>7.66</v>
+        <v>12.7</v>
       </c>
       <c r="D15" t="n">
-        <v>6.69</v>
+        <v>4.96</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>7.53</v>
+        <v>12.05</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>-1.7</v>
+        <v>-5.12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MANUGRAPH</t>
+          <t>GAYAPROJ</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12.94</v>
+        <v>13.33</v>
       </c>
       <c r="C16" t="n">
-        <v>13.8</v>
+        <v>13.99</v>
       </c>
       <c r="D16" t="n">
-        <v>6.65</v>
+        <v>4.95</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>13.39</v>
+        <v>13.99</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>-2.97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SOFTTECH</t>
+          <t>SAMBHAAV</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>253.5</v>
+        <v>5.71</v>
       </c>
       <c r="C17" t="n">
-        <v>269.55</v>
+        <v>5.99</v>
       </c>
       <c r="D17" t="n">
-        <v>6.33</v>
+        <v>4.9</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>265.95</v>
+        <v>5.66</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>-1.34</v>
+        <v>-5.51</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RAMASTEEL</t>
+          <t>PILITA</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.22</v>
+        <v>7.44</v>
       </c>
       <c r="C18" t="n">
-        <v>5.55</v>
+        <v>7.8</v>
       </c>
       <c r="D18" t="n">
-        <v>6.32</v>
+        <v>4.84</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>5.31</v>
+        <v>7</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>-4.32</v>
+        <v>-10.26</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MADHAV</t>
+          <t>WEWIN</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>33.41</v>
+        <v>42.45</v>
       </c>
       <c r="C19" t="n">
-        <v>35.5</v>
+        <v>44.5</v>
       </c>
       <c r="D19" t="n">
-        <v>6.26</v>
+        <v>4.83</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>34.41</v>
+        <v>40.32</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>-3.07</v>
+        <v>-9.390000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RELIABLE</t>
+          <t>ICDSLTD</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>122.14</v>
+        <v>43.99</v>
       </c>
       <c r="C20" t="n">
-        <v>129.75</v>
+        <v>46.1</v>
       </c>
       <c r="D20" t="n">
-        <v>6.23</v>
+        <v>4.8</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>122.26</v>
+        <v>43.99</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>-5.77</v>
+        <v>-4.58</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HPAL</t>
+          <t>MORARJEE</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>30.67</v>
+        <v>6.3</v>
       </c>
       <c r="C21" t="n">
-        <v>32.58</v>
+        <v>6.6</v>
       </c>
       <c r="D21" t="n">
-        <v>6.23</v>
+        <v>4.76</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>31.33</v>
+        <v>6.54</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>-3.84</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CCCL</t>
+          <t>VITAL</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14.69</v>
+        <v>37.25</v>
       </c>
       <c r="C22" t="n">
-        <v>15.54</v>
+        <v>39</v>
       </c>
       <c r="D22" t="n">
-        <v>5.79</v>
+        <v>4.7</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>14.7</v>
+        <v>36.5</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>-5.41</v>
+        <v>-6.41</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>OSWALSEEDS</t>
+          <t>ANIKINDS</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>11.58</v>
+        <v>37.93</v>
       </c>
       <c r="C23" t="n">
-        <v>12.25</v>
+        <v>39.7</v>
       </c>
       <c r="D23" t="n">
-        <v>5.79</v>
+        <v>4.67</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>11.66</v>
+        <v>37.5</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>-4.82</v>
+        <v>-5.54</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MONEYBOXX</t>
+          <t>AGRITECH</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>61.55</v>
+        <v>105.12</v>
       </c>
       <c r="C24" t="n">
-        <v>64.98999999999999</v>
+        <v>110</v>
       </c>
       <c r="D24" t="n">
-        <v>5.59</v>
+        <v>4.64</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>61.95</v>
+        <v>104.85</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
@@ -1059,205 +1059,205 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NRL</t>
+          <t>COOLCAPS</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>49.5</v>
+        <v>26.1</v>
       </c>
       <c r="C25" t="n">
-        <v>52.18</v>
+        <v>27.3</v>
       </c>
       <c r="D25" t="n">
-        <v>5.41</v>
+        <v>4.6</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>50.9</v>
+        <v>27.4</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>-2.45</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>INDOWIND</t>
+          <t>DRONE</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>8.75</v>
+        <v>45.45</v>
       </c>
       <c r="C26" t="n">
-        <v>9.220000000000001</v>
+        <v>47.5</v>
       </c>
       <c r="D26" t="n">
-        <v>5.37</v>
+        <v>4.51</v>
       </c>
       <c r="E26" t="b">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>8.98</v>
+        <v>44</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>-2.6</v>
+        <v>-7.37</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>KRITINUT</t>
+          <t>TCL</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>63.49</v>
+        <v>86.25</v>
       </c>
       <c r="C27" t="n">
-        <v>66.8</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>5.21</v>
+        <v>4.23</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>64.95999999999999</v>
+        <v>85.3</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>-2.75</v>
+        <v>-5.12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GLOBALVECT</t>
+          <t>SAGARDEEP</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>158.64</v>
+        <v>23.03</v>
       </c>
       <c r="C28" t="n">
-        <v>166.9</v>
+        <v>23.99</v>
       </c>
       <c r="D28" t="n">
-        <v>5.21</v>
+        <v>4.17</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>158.2</v>
+        <v>22.6</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>-5.21</v>
+        <v>-5.79</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GATECHDVR</t>
+          <t>INDUSINVIT</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.39</v>
+        <v>124.27</v>
       </c>
       <c r="C29" t="n">
-        <v>0.41</v>
+        <v>129.4</v>
       </c>
       <c r="D29" t="n">
-        <v>5.13</v>
+        <v>4.13</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0.41</v>
+        <v>124.6</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>-3.71</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>COMPUSOFT</t>
+          <t>VISASTEEL</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>13.27</v>
+        <v>30.06</v>
       </c>
       <c r="C30" t="n">
-        <v>13.95</v>
+        <v>31.3</v>
       </c>
       <c r="D30" t="n">
-        <v>5.12</v>
+        <v>4.13</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>13.28</v>
+        <v>28.99</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>-4.8</v>
+        <v>-7.38</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>UMAEXPORTS</t>
+          <t>BLBLIMITED</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>20.94</v>
+        <v>16.61</v>
       </c>
       <c r="C31" t="n">
-        <v>22</v>
+        <v>17.29</v>
       </c>
       <c r="D31" t="n">
-        <v>5.06</v>
+        <v>4.09</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>21.86</v>
+        <v>16.33</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>-0.64</v>
+        <v>-5.55</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RMDRIP</t>
+          <t>LRRPL</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>40.81</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="C32" t="n">
-        <v>42.85</v>
+        <v>73.75</v>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>4.09</v>
       </c>
       <c r="E32" t="b">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>42.85</v>
+        <v>73.75</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
@@ -1267,4387 +1267,4395 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>WAAREEINDO</t>
+          <t>OMKARCHEM</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>366.85</v>
+        <v>3.93</v>
       </c>
       <c r="C33" t="n">
-        <v>385.15</v>
+        <v>4.09</v>
       </c>
       <c r="D33" t="n">
-        <v>4.99</v>
+        <v>4.07</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>385.15</v>
+        <v>3.9</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>-4.65</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>IL&amp;FSENGG</t>
+          <t>TECILCHEM</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>23.7</v>
+        <v>13</v>
       </c>
       <c r="C34" t="n">
-        <v>24.88</v>
+        <v>13.5</v>
       </c>
       <c r="D34" t="n">
-        <v>4.98</v>
+        <v>3.85</v>
       </c>
       <c r="E34" t="b">
         <v>0</v>
       </c>
-      <c r="F34" t="inlineStr"/>
+      <c r="F34" t="n">
+        <v>12.02</v>
+      </c>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="H34" t="n">
+        <v>-10.96</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CKKRETAIL</t>
+          <t>COMPINFO</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>125.7</v>
+        <v>1.05</v>
       </c>
       <c r="C35" t="n">
-        <v>131.95</v>
+        <v>1.09</v>
       </c>
       <c r="D35" t="n">
-        <v>4.97</v>
+        <v>3.81</v>
       </c>
       <c r="E35" t="b">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>131.95</v>
+        <v>1.06</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>-2.75</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>OWAIS</t>
+          <t>CAPTRUST</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>101.7</v>
+        <v>11.85</v>
       </c>
       <c r="C36" t="n">
-        <v>106.75</v>
+        <v>12.3</v>
       </c>
       <c r="D36" t="n">
-        <v>4.97</v>
+        <v>3.8</v>
       </c>
       <c r="E36" t="b">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>106.75</v>
+        <v>11.7</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>-4.88</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DCMSRIND</t>
+          <t>ASTRON</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>34.18</v>
+        <v>4.04</v>
       </c>
       <c r="C37" t="n">
-        <v>35.88</v>
+        <v>4.19</v>
       </c>
       <c r="D37" t="n">
-        <v>4.97</v>
+        <v>3.71</v>
       </c>
       <c r="E37" t="b">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>36.6</v>
+        <v>3.99</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>2.01</v>
+        <v>-4.77</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>UNIHEALTH</t>
+          <t>ATCENERGY</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>376.55</v>
+        <v>23.05</v>
       </c>
       <c r="C38" t="n">
-        <v>395</v>
+        <v>23.85</v>
       </c>
       <c r="D38" t="n">
-        <v>4.9</v>
+        <v>3.47</v>
       </c>
       <c r="E38" t="b">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>395.35</v>
+        <v>23.4</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>0.09</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TECHERA</t>
+          <t>NAVKARURB</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>174.7</v>
+        <v>0.87</v>
       </c>
       <c r="C39" t="n">
-        <v>183.2</v>
+        <v>0.9</v>
       </c>
       <c r="D39" t="n">
-        <v>4.87</v>
+        <v>3.45</v>
       </c>
       <c r="E39" t="b">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>183.4</v>
+        <v>0.83</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>0.11</v>
+        <v>-7.78</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PRIZOR</t>
+          <t>VSTL</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>371</v>
+        <v>113.12</v>
       </c>
       <c r="C40" t="n">
-        <v>389</v>
+        <v>117</v>
       </c>
       <c r="D40" t="n">
-        <v>4.85</v>
+        <v>3.43</v>
       </c>
       <c r="E40" t="b">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>389.55</v>
+        <v>106.01</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>0.14</v>
+        <v>-9.390000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>APSISAERO</t>
+          <t>SHIVAMILLS</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>168.65</v>
+        <v>52.86</v>
       </c>
       <c r="C41" t="n">
-        <v>176.7</v>
+        <v>54.65</v>
       </c>
       <c r="D41" t="n">
-        <v>4.77</v>
+        <v>3.39</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>177.05</v>
+        <v>52.13</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>0.2</v>
+        <v>-4.61</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>LIBAS</t>
+          <t>MOTOGENFIN</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>9.880000000000001</v>
+        <v>20.09</v>
       </c>
       <c r="C42" t="n">
-        <v>10.35</v>
+        <v>20.77</v>
       </c>
       <c r="D42" t="n">
-        <v>4.76</v>
+        <v>3.38</v>
       </c>
       <c r="E42" t="b">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>9.94</v>
+        <v>20</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>-3.96</v>
+        <v>-3.71</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ORTEL</t>
+          <t>SIKKO</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.68</v>
+        <v>4.74</v>
       </c>
       <c r="C43" t="n">
-        <v>1.76</v>
+        <v>4.9</v>
       </c>
       <c r="D43" t="n">
-        <v>4.76</v>
+        <v>3.38</v>
       </c>
       <c r="E43" t="b">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>1.76</v>
+        <v>4.6</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>-6.12</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>IFGLEXPOR</t>
+          <t>SIGIND</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>146</v>
+        <v>43.24</v>
       </c>
       <c r="C44" t="n">
-        <v>152.9</v>
+        <v>44.69</v>
       </c>
       <c r="D44" t="n">
-        <v>4.73</v>
+        <v>3.35</v>
       </c>
       <c r="E44" t="b">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>145.02</v>
+        <v>41.92</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>-5.15</v>
+        <v>-6.2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GOLDSTAR</t>
+          <t>KHAITANLTD</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>7.4</v>
+        <v>95.69</v>
       </c>
       <c r="C45" t="n">
-        <v>7.75</v>
+        <v>98.89</v>
       </c>
       <c r="D45" t="n">
-        <v>4.73</v>
+        <v>3.34</v>
       </c>
       <c r="E45" t="b">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>7.7</v>
+        <v>94.02</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>-0.65</v>
+        <v>-4.92</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ASHWINI</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>142.25</v>
+        <v>102.58</v>
       </c>
       <c r="C46" t="n">
-        <v>148.95</v>
+        <v>106</v>
       </c>
       <c r="D46" t="n">
-        <v>4.71</v>
+        <v>3.33</v>
       </c>
       <c r="E46" t="b">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>147</v>
+        <v>99.23999999999999</v>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>-1.31</v>
+        <v>-6.38</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SAMBHAAV</t>
+          <t>AURIGROW</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>5.53</v>
+        <v>0.3</v>
       </c>
       <c r="C47" t="n">
-        <v>5.79</v>
+        <v>0.31</v>
       </c>
       <c r="D47" t="n">
-        <v>4.7</v>
+        <v>3.33</v>
       </c>
       <c r="E47" t="b">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>5.68</v>
+        <v>0.29</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>-1.9</v>
+        <v>-6.45</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>OMKARCHEM</t>
+          <t>GSS</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3.85</v>
+        <v>10.99</v>
       </c>
       <c r="C48" t="n">
-        <v>4.03</v>
+        <v>11.35</v>
       </c>
       <c r="D48" t="n">
-        <v>4.68</v>
+        <v>3.28</v>
       </c>
       <c r="E48" t="b">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>3.96</v>
+        <v>10.62</v>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>-1.74</v>
+        <v>-6.43</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MEDICAMEQ</t>
+          <t>MADHAV</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>261.85</v>
+        <v>34.28</v>
       </c>
       <c r="C49" t="n">
-        <v>274</v>
+        <v>35.4</v>
       </c>
       <c r="D49" t="n">
-        <v>4.64</v>
+        <v>3.27</v>
       </c>
       <c r="E49" t="b">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>263.7</v>
+        <v>33.25</v>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>-3.76</v>
+        <v>-6.07</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>INDTERRAIN</t>
+          <t>NKIND</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>28</v>
+        <v>64.89</v>
       </c>
       <c r="C50" t="n">
-        <v>29.3</v>
+        <v>67</v>
       </c>
       <c r="D50" t="n">
-        <v>4.64</v>
+        <v>3.25</v>
       </c>
       <c r="E50" t="b">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>28.89</v>
+        <v>66.5</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>-1.4</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TARAPUR</t>
+          <t>NOIDATOLL</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25.93</v>
+        <v>3.39</v>
       </c>
       <c r="C51" t="n">
-        <v>27.13</v>
+        <v>3.5</v>
       </c>
       <c r="D51" t="n">
-        <v>4.63</v>
+        <v>3.24</v>
       </c>
       <c r="E51" t="b">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>26.89</v>
+        <v>3.36</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>-0.88</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TRIGYN</t>
+          <t>SIGMAADV</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>47.66</v>
+        <v>172.48</v>
       </c>
       <c r="C52" t="n">
-        <v>49.8</v>
+        <v>178</v>
       </c>
       <c r="D52" t="n">
-        <v>4.49</v>
+        <v>3.2</v>
       </c>
       <c r="E52" t="b">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>49.36</v>
+        <v>163.94</v>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>-0.88</v>
+        <v>-7.9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>SITINET</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>7.14</v>
+        <v>0.32</v>
       </c>
       <c r="C53" t="n">
-        <v>7.46</v>
+        <v>0.33</v>
       </c>
       <c r="D53" t="n">
-        <v>4.48</v>
+        <v>3.13</v>
       </c>
       <c r="E53" t="b">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>7.38</v>
+        <v>0.33</v>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>-1.07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DALMIASUG</t>
+          <t>AERONEU</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>298.75</v>
+        <v>66.75</v>
       </c>
       <c r="C54" t="n">
-        <v>312.1</v>
+        <v>68.8</v>
       </c>
       <c r="D54" t="n">
-        <v>4.47</v>
+        <v>3.07</v>
       </c>
       <c r="E54" t="b">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>318.3</v>
+        <v>68</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>1.99</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SRTL</t>
+          <t>TGBHOTELS</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>48.27</v>
+        <v>8.23</v>
       </c>
       <c r="C55" t="n">
-        <v>50.4</v>
+        <v>8.48</v>
       </c>
       <c r="D55" t="n">
-        <v>4.41</v>
+        <v>3.04</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>49.8</v>
+        <v>7.96</v>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>-1.19</v>
+        <v>-6.13</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TARACHAND</t>
+          <t>AEPL</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>55.5</v>
+        <v>16.85</v>
       </c>
       <c r="C56" t="n">
-        <v>57.95</v>
+        <v>17.35</v>
       </c>
       <c r="D56" t="n">
-        <v>4.41</v>
+        <v>2.97</v>
       </c>
       <c r="E56" t="b">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>57.41</v>
+        <v>16.68</v>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>-0.93</v>
+        <v>-3.86</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>INDORAMA</t>
+          <t>SURYALAXMI</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>31.33</v>
+        <v>52.44</v>
       </c>
       <c r="C57" t="n">
-        <v>32.7</v>
+        <v>54</v>
       </c>
       <c r="D57" t="n">
-        <v>4.37</v>
+        <v>2.97</v>
       </c>
       <c r="E57" t="b">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>31.9</v>
+        <v>50.4</v>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>-2.45</v>
+        <v>-6.67</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CENTUM</t>
+          <t>SHIVAMAUTO</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2725.8</v>
+        <v>15.93</v>
       </c>
       <c r="C58" t="n">
-        <v>2844.3</v>
+        <v>16.4</v>
       </c>
       <c r="D58" t="n">
-        <v>4.35</v>
+        <v>2.95</v>
       </c>
       <c r="E58" t="b">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>2975.1</v>
+        <v>15.46</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>4.6</v>
+        <v>-5.73</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AIRAN</t>
+          <t>EFACTOR</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>15.21</v>
+        <v>181.75</v>
       </c>
       <c r="C59" t="n">
-        <v>15.87</v>
+        <v>187</v>
       </c>
       <c r="D59" t="n">
-        <v>4.34</v>
+        <v>2.89</v>
       </c>
       <c r="E59" t="b">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>15.29</v>
+        <v>175</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>-3.65</v>
+        <v>-6.42</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CPEDU</t>
+          <t>ELDEHSG</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>165.36</v>
+        <v>811.65</v>
       </c>
       <c r="C60" t="n">
-        <v>172.4</v>
+        <v>835</v>
       </c>
       <c r="D60" t="n">
-        <v>4.26</v>
+        <v>2.88</v>
       </c>
       <c r="E60" t="b">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>168.75</v>
+        <v>767.05</v>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>-2.12</v>
+        <v>-8.140000000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MAGNUM</t>
+          <t>BSL</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>18.37</v>
+        <v>123.36</v>
       </c>
       <c r="C61" t="n">
-        <v>19.15</v>
+        <v>126.89</v>
       </c>
       <c r="D61" t="n">
-        <v>4.25</v>
+        <v>2.86</v>
       </c>
       <c r="E61" t="b">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>18.86</v>
+        <v>114</v>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>-1.51</v>
+        <v>-10.16</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>JSWHL</t>
+          <t>SIMBHALS</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>15976</v>
+        <v>7.4</v>
       </c>
       <c r="C62" t="n">
-        <v>16650</v>
+        <v>7.61</v>
       </c>
       <c r="D62" t="n">
-        <v>4.22</v>
+        <v>2.84</v>
       </c>
       <c r="E62" t="b">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>16026</v>
+        <v>7.2</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>-3.75</v>
+        <v>-5.39</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PAVNAIND</t>
+          <t>FROG</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>18.08</v>
+        <v>126.35</v>
       </c>
       <c r="C63" t="n">
-        <v>18.84</v>
+        <v>129.9</v>
       </c>
       <c r="D63" t="n">
-        <v>4.2</v>
+        <v>2.81</v>
       </c>
       <c r="E63" t="b">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>18.09</v>
+        <v>124</v>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>-3.98</v>
+        <v>-4.54</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>NIBL</t>
+          <t>SEJALLTD</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>28.59</v>
+        <v>481.75</v>
       </c>
       <c r="C64" t="n">
-        <v>29.78</v>
+        <v>495</v>
       </c>
       <c r="D64" t="n">
-        <v>4.16</v>
+        <v>2.75</v>
       </c>
       <c r="E64" t="b">
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>29.35</v>
+        <v>481</v>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>-1.44</v>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>NIPPOBATRY</t>
+          <t>HEXATRADEX</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>292.75</v>
+        <v>159.66</v>
       </c>
       <c r="C65" t="n">
-        <v>304.9</v>
+        <v>164</v>
       </c>
       <c r="D65" t="n">
-        <v>4.15</v>
+        <v>2.72</v>
       </c>
       <c r="E65" t="b">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>300.1</v>
+        <v>158.3</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>-1.57</v>
+        <v>-3.48</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>HINDCOMPOS</t>
+          <t>SICALLOG</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>381.95</v>
+        <v>64.94</v>
       </c>
       <c r="C66" t="n">
-        <v>397.8</v>
+        <v>66.7</v>
       </c>
       <c r="D66" t="n">
-        <v>4.15</v>
+        <v>2.71</v>
       </c>
       <c r="E66" t="b">
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>387.7</v>
+        <v>63.9</v>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>-2.54</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SIGNPOST</t>
+          <t>RMDRIP</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>236.6</v>
+        <v>42.85</v>
       </c>
       <c r="C67" t="n">
-        <v>246.1</v>
+        <v>44</v>
       </c>
       <c r="D67" t="n">
-        <v>4.02</v>
+        <v>2.68</v>
       </c>
       <c r="E67" t="b">
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>237.3</v>
+        <v>40.71</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>-3.58</v>
+        <v>-7.48</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>NAGREEKCAP</t>
+          <t>AVONMORE</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>22.65</v>
+        <v>12.08</v>
       </c>
       <c r="C68" t="n">
-        <v>23.56</v>
+        <v>12.4</v>
       </c>
       <c r="D68" t="n">
-        <v>4.02</v>
+        <v>2.65</v>
       </c>
       <c r="E68" t="b">
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>23.89</v>
+        <v>11.65</v>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>1.4</v>
+        <v>-6.05</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MANOMAY</t>
+          <t>SETUINFRA</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>201.64</v>
+        <v>0.39</v>
       </c>
       <c r="C69" t="n">
-        <v>209.71</v>
+        <v>0.4</v>
       </c>
       <c r="D69" t="n">
-        <v>4</v>
+        <v>2.56</v>
       </c>
       <c r="E69" t="b">
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>207.36</v>
+        <v>0.4</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>-1.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MFML</t>
+          <t>WAAREEINDO</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>23.26</v>
+        <v>385.15</v>
       </c>
       <c r="C70" t="n">
-        <v>24.19</v>
+        <v>395</v>
       </c>
       <c r="D70" t="n">
-        <v>4</v>
+        <v>2.56</v>
       </c>
       <c r="E70" t="b">
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>23.97</v>
+        <v>404.4</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>-0.91</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>KOTHARIPRO</t>
+          <t>GATECHDVR</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>63.39</v>
+        <v>0.39</v>
       </c>
       <c r="C71" t="n">
-        <v>65.90000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="D71" t="n">
-        <v>3.96</v>
+        <v>2.56</v>
       </c>
       <c r="E71" t="b">
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>63.98</v>
+        <v>0.39</v>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>-2.91</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>RKEC</t>
+          <t>PVP</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>34.31</v>
+        <v>25.1</v>
       </c>
       <c r="C72" t="n">
-        <v>35.64</v>
+        <v>25.73</v>
       </c>
       <c r="D72" t="n">
-        <v>3.88</v>
+        <v>2.51</v>
       </c>
       <c r="E72" t="b">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>34.64</v>
+        <v>25.87</v>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>-2.81</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>COOLCAPS</t>
+          <t>URAVIDEF</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>24.9</v>
+        <v>126.49</v>
       </c>
       <c r="C73" t="n">
-        <v>25.85</v>
+        <v>129.65</v>
       </c>
       <c r="D73" t="n">
-        <v>3.82</v>
+        <v>2.5</v>
       </c>
       <c r="E73" t="b">
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>26.1</v>
+        <v>125.19</v>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>0.97</v>
+        <v>-3.44</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ASMS</t>
+          <t>PANSARI</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>8.130000000000001</v>
+        <v>276.1</v>
       </c>
       <c r="C74" t="n">
-        <v>8.44</v>
+        <v>282.95</v>
       </c>
       <c r="D74" t="n">
-        <v>3.81</v>
+        <v>2.48</v>
       </c>
       <c r="E74" t="b">
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>8.33</v>
+        <v>266</v>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>-1.3</v>
+        <v>-5.99</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>UNITEDPOLY</t>
+          <t>RAJSREESUG</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>26.89</v>
+        <v>28.31</v>
       </c>
       <c r="C75" t="n">
-        <v>27.91</v>
+        <v>29</v>
       </c>
       <c r="D75" t="n">
-        <v>3.79</v>
+        <v>2.44</v>
       </c>
       <c r="E75" t="b">
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>26.8</v>
+        <v>26.71</v>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>-3.98</v>
+        <v>-7.9</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>LASA</t>
+          <t>3IINFOLTD</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>7.4</v>
+        <v>13.82</v>
       </c>
       <c r="C76" t="n">
-        <v>7.68</v>
+        <v>14.15</v>
       </c>
       <c r="D76" t="n">
-        <v>3.78</v>
+        <v>2.39</v>
       </c>
       <c r="E76" t="b">
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>7.39</v>
+        <v>13.29</v>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>-3.78</v>
+        <v>-6.08</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CROWN</t>
+          <t>EQUIPPP</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>115.55</v>
+        <v>17.96</v>
       </c>
       <c r="C77" t="n">
-        <v>119.89</v>
+        <v>18.39</v>
       </c>
       <c r="D77" t="n">
-        <v>3.76</v>
+        <v>2.39</v>
       </c>
       <c r="E77" t="b">
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>117.74</v>
+        <v>17.12</v>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>-1.79</v>
+        <v>-6.91</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>VIVIMEDLAB</t>
+          <t>LASA</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>6.39</v>
+        <v>7.13</v>
       </c>
       <c r="C78" t="n">
-        <v>6.63</v>
+        <v>7.3</v>
       </c>
       <c r="D78" t="n">
-        <v>3.76</v>
+        <v>2.38</v>
       </c>
       <c r="E78" t="b">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>6.47</v>
+        <v>7.15</v>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>-2.41</v>
+        <v>-2.05</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SINTERCOM</t>
+          <t>MASFIN</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>76.40000000000001</v>
+        <v>302.55</v>
       </c>
       <c r="C79" t="n">
-        <v>79.2</v>
+        <v>309.55</v>
       </c>
       <c r="D79" t="n">
-        <v>3.66</v>
+        <v>2.31</v>
       </c>
       <c r="E79" t="b">
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>78.40000000000001</v>
+        <v>287.95</v>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>-1.01</v>
+        <v>-6.98</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ROML</t>
+          <t>GPTINFRA</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>43.4</v>
+        <v>103.62</v>
       </c>
       <c r="C80" t="n">
-        <v>44.98</v>
+        <v>106</v>
       </c>
       <c r="D80" t="n">
-        <v>3.64</v>
+        <v>2.3</v>
       </c>
       <c r="E80" t="b">
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>44.49</v>
+        <v>102.54</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>-1.09</v>
+        <v>-3.26</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SPCENET</t>
+          <t>RCOM</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>3.86</v>
+        <v>0.89</v>
       </c>
       <c r="C81" t="n">
-        <v>4</v>
+        <v>0.91</v>
       </c>
       <c r="D81" t="n">
-        <v>3.63</v>
+        <v>2.25</v>
       </c>
       <c r="E81" t="b">
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>3.94</v>
+        <v>0.87</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>-1.5</v>
+        <v>-4.4</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>DAVANGERE</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>556.15</v>
+        <v>4.05</v>
       </c>
       <c r="C82" t="n">
-        <v>576.15</v>
+        <v>4.14</v>
       </c>
       <c r="D82" t="n">
-        <v>3.6</v>
+        <v>2.22</v>
       </c>
       <c r="E82" t="b">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>558.95</v>
+        <v>3.89</v>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>-2.99</v>
+        <v>-6.04</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>NOIDATOLL</t>
+          <t>KEEPLEARN</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>3.35</v>
+        <v>1.82</v>
       </c>
       <c r="C83" t="n">
-        <v>3.47</v>
+        <v>1.86</v>
       </c>
       <c r="D83" t="n">
-        <v>3.58</v>
+        <v>2.2</v>
       </c>
       <c r="E83" t="b">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>3.57</v>
+        <v>1.8</v>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>2.88</v>
+        <v>-3.23</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>RPPINFRA</t>
+          <t>VAISHALI</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>68.31</v>
+        <v>5.98</v>
       </c>
       <c r="C84" t="n">
-        <v>70.75</v>
+        <v>6.11</v>
       </c>
       <c r="D84" t="n">
-        <v>3.57</v>
+        <v>2.17</v>
       </c>
       <c r="E84" t="b">
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>68.93000000000001</v>
+        <v>5.95</v>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>-2.57</v>
+        <v>-2.62</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>VIVIDHA</t>
+          <t>GATECH</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="C85" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="D85" t="n">
-        <v>3.57</v>
+        <v>2.17</v>
       </c>
       <c r="E85" t="b">
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>0.58</v>
+        <v>0.46</v>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SUVIDHAA</t>
+          <t>GUJALKALI</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2.84</v>
+        <v>538.25</v>
       </c>
       <c r="C86" t="n">
-        <v>2.94</v>
+        <v>549.9</v>
       </c>
       <c r="D86" t="n">
-        <v>3.52</v>
+        <v>2.16</v>
       </c>
       <c r="E86" t="b">
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>2.83</v>
+        <v>561.35</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>-3.74</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>UJJIVANSFB</t>
+          <t>KSHITIJPOL</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>52.49</v>
+        <v>2.33</v>
       </c>
       <c r="C87" t="n">
-        <v>54.33</v>
+        <v>2.38</v>
       </c>
       <c r="D87" t="n">
-        <v>3.51</v>
+        <v>2.15</v>
       </c>
       <c r="E87" t="b">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>53.99</v>
+        <v>2.25</v>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>-0.63</v>
+        <v>-5.46</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SHEKHAWATI</t>
+          <t>AKG</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>11.69</v>
+        <v>10.82</v>
       </c>
       <c r="C88" t="n">
-        <v>12.1</v>
+        <v>11.05</v>
       </c>
       <c r="D88" t="n">
-        <v>3.51</v>
+        <v>2.13</v>
       </c>
       <c r="E88" t="b">
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>12.07</v>
+        <v>10.65</v>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>-0.25</v>
+        <v>-3.62</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BAGFILMS</t>
+          <t>ALANKIT</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>4.28</v>
+        <v>7.54</v>
       </c>
       <c r="C89" t="n">
-        <v>4.43</v>
+        <v>7.7</v>
       </c>
       <c r="D89" t="n">
-        <v>3.5</v>
+        <v>2.12</v>
       </c>
       <c r="E89" t="b">
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>4.4</v>
+        <v>7.21</v>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>-0.68</v>
+        <v>-6.36</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>RAJSREESUG</t>
+          <t>CELEBRITY</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>27.44</v>
+        <v>7.25</v>
       </c>
       <c r="C90" t="n">
-        <v>28.4</v>
+        <v>7.4</v>
       </c>
       <c r="D90" t="n">
-        <v>3.5</v>
+        <v>2.07</v>
       </c>
       <c r="E90" t="b">
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>29.66</v>
+        <v>7.26</v>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>4.44</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>JAICORPLTD</t>
+          <t>JOCIL</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>98.56999999999999</v>
+        <v>110.49</v>
       </c>
       <c r="C91" t="n">
-        <v>101.99</v>
+        <v>112.77</v>
       </c>
       <c r="D91" t="n">
-        <v>3.47</v>
+        <v>2.06</v>
       </c>
       <c r="E91" t="b">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>106.5</v>
+        <v>109</v>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>4.42</v>
+        <v>-3.34</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AURIGROW</t>
+          <t>LATTEYS</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.29</v>
+        <v>19.5</v>
       </c>
       <c r="C92" t="n">
-        <v>0.3</v>
+        <v>19.9</v>
       </c>
       <c r="D92" t="n">
-        <v>3.45</v>
+        <v>2.05</v>
       </c>
       <c r="E92" t="b">
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>0.3</v>
+        <v>19.05</v>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>-4.27</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CHEMBONDCH</t>
+          <t>INTENTECH</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>125.15</v>
+        <v>83.98</v>
       </c>
       <c r="C93" t="n">
-        <v>129.45</v>
+        <v>85.7</v>
       </c>
       <c r="D93" t="n">
-        <v>3.44</v>
+        <v>2.05</v>
       </c>
       <c r="E93" t="b">
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>129.6</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
-        <v>0.12</v>
+        <v>-7.57</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>RUCHINFRA</t>
+          <t>NBIFIN</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>4.96</v>
+        <v>1723.8</v>
       </c>
       <c r="C94" t="n">
-        <v>5.13</v>
+        <v>1759</v>
       </c>
       <c r="D94" t="n">
-        <v>3.43</v>
+        <v>2.04</v>
       </c>
       <c r="E94" t="b">
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>5</v>
+        <v>1715</v>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>-2.53</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PARACABLES</t>
+          <t>MAHAPEXLTD</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>34.23</v>
+        <v>56.45</v>
       </c>
       <c r="C95" t="n">
-        <v>35.4</v>
+        <v>57.6</v>
       </c>
       <c r="D95" t="n">
-        <v>3.42</v>
+        <v>2.04</v>
       </c>
       <c r="E95" t="b">
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>34.75</v>
+        <v>53.25</v>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>-1.84</v>
+        <v>-7.55</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DCMNVL</t>
+          <t>HITECHCORP</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>110.01</v>
+        <v>141.16</v>
       </c>
       <c r="C96" t="n">
-        <v>113.75</v>
+        <v>144</v>
       </c>
       <c r="D96" t="n">
-        <v>3.4</v>
+        <v>2.01</v>
       </c>
       <c r="E96" t="b">
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>114.3</v>
+        <v>136.01</v>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>0.48</v>
+        <v>-5.55</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>TARMAT</t>
+          <t>ROML</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>54.07</v>
+        <v>43.5</v>
       </c>
       <c r="C97" t="n">
-        <v>55.9</v>
+        <v>44.37</v>
       </c>
       <c r="D97" t="n">
-        <v>3.38</v>
+        <v>2</v>
       </c>
       <c r="E97" t="b">
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>53.12</v>
+        <v>43.49</v>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>-4.97</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EQUIPPP</t>
+          <t>MODIRUBBER</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>18.63</v>
+        <v>109.81</v>
       </c>
       <c r="C98" t="n">
-        <v>19.25</v>
+        <v>112</v>
       </c>
       <c r="D98" t="n">
-        <v>3.33</v>
+        <v>1.99</v>
       </c>
       <c r="E98" t="b">
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>18.11</v>
+        <v>110.61</v>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>-5.92</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SCHNEIDER</t>
+          <t>CONFIPET</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>895.2</v>
+        <v>36.28</v>
       </c>
       <c r="C99" t="n">
-        <v>925</v>
+        <v>37</v>
       </c>
       <c r="D99" t="n">
-        <v>3.33</v>
+        <v>1.98</v>
       </c>
       <c r="E99" t="b">
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>908.1</v>
+        <v>35.6</v>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
-        <v>-1.83</v>
+        <v>-3.78</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>RIIL</t>
+          <t>SEYAIND</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>636.65</v>
+        <v>10.15</v>
       </c>
       <c r="C100" t="n">
-        <v>657.7</v>
+        <v>10.35</v>
       </c>
       <c r="D100" t="n">
-        <v>3.31</v>
+        <v>1.97</v>
       </c>
       <c r="E100" t="b">
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>709.95</v>
+        <v>10.35</v>
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>7.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AAKASH</t>
+          <t>DCMSRIND</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>9.08</v>
+        <v>35.32</v>
       </c>
       <c r="C101" t="n">
-        <v>9.380000000000001</v>
+        <v>36</v>
       </c>
       <c r="D101" t="n">
-        <v>3.3</v>
+        <v>1.93</v>
       </c>
       <c r="E101" t="b">
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>-4.05</v>
+        <v>-5.56</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>POLYSIL</t>
+          <t>EXXARO</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>159.7</v>
+        <v>6.84</v>
       </c>
       <c r="C102" t="n">
-        <v>164.95</v>
+        <v>6.97</v>
       </c>
       <c r="D102" t="n">
-        <v>3.29</v>
+        <v>1.9</v>
       </c>
       <c r="E102" t="b">
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>152</v>
+        <v>6.71</v>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>-7.85</v>
+        <v>-3.73</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ELECTCAST</t>
+          <t>DCM</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>71.94</v>
+        <v>61.24</v>
       </c>
       <c r="C103" t="n">
-        <v>74.3</v>
+        <v>62.4</v>
       </c>
       <c r="D103" t="n">
-        <v>3.28</v>
+        <v>1.89</v>
       </c>
       <c r="E103" t="b">
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>73.56999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>-0.98</v>
+        <v>-6.09</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>PRUDMOULI</t>
+          <t>BIOFILCHEM</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>11.53</v>
+        <v>29.93</v>
       </c>
       <c r="C104" t="n">
-        <v>11.9</v>
+        <v>30.49</v>
       </c>
       <c r="D104" t="n">
-        <v>3.21</v>
+        <v>1.87</v>
       </c>
       <c r="E104" t="b">
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>11.73</v>
+        <v>29.2</v>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
-        <v>-1.43</v>
+        <v>-4.23</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SURANI</t>
+          <t>KESORAMIND</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>71.75</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="C105" t="n">
-        <v>74</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D105" t="n">
-        <v>3.14</v>
+        <v>1.86</v>
       </c>
       <c r="E105" t="b">
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>68.75</v>
+        <v>7.79</v>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>-7.09</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MAHEPC</t>
+          <t>RILINFRA</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>113.44</v>
+        <v>37.75</v>
       </c>
       <c r="C106" t="n">
-        <v>116.99</v>
+        <v>38.45</v>
       </c>
       <c r="D106" t="n">
-        <v>3.13</v>
+        <v>1.85</v>
       </c>
       <c r="E106" t="b">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>114.58</v>
+        <v>36</v>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
-        <v>-2.06</v>
+        <v>-6.37</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>OSWALAGRO</t>
+          <t>WEBELSOLAR</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>41.42</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="C107" t="n">
-        <v>42.7</v>
+        <v>76.22</v>
       </c>
       <c r="D107" t="n">
-        <v>3.09</v>
+        <v>1.83</v>
       </c>
       <c r="E107" t="b">
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>42.56</v>
+        <v>72.48999999999999</v>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>-0.33</v>
+        <v>-4.89</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MAHASTEEL</t>
+          <t>PASHUPATI</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>925.55</v>
+        <v>981.1</v>
       </c>
       <c r="C108" t="n">
-        <v>953.95</v>
+        <v>999</v>
       </c>
       <c r="D108" t="n">
-        <v>3.07</v>
+        <v>1.82</v>
       </c>
       <c r="E108" t="b">
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>901.05</v>
+        <v>957.2</v>
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
-        <v>-5.55</v>
+        <v>-4.18</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>RADAAN</t>
+          <t>PAVNAIND</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>2.94</v>
+        <v>18.11</v>
       </c>
       <c r="C109" t="n">
-        <v>3.03</v>
+        <v>18.44</v>
       </c>
       <c r="D109" t="n">
-        <v>3.06</v>
+        <v>1.82</v>
       </c>
       <c r="E109" t="b">
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>2.94</v>
+        <v>17.95</v>
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>-2.97</v>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SITINET</t>
+          <t>VIVIDHA</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.33</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C110" t="n">
-        <v>0.34</v>
+        <v>0.57</v>
       </c>
       <c r="D110" t="n">
-        <v>3.03</v>
+        <v>1.79</v>
       </c>
       <c r="E110" t="b">
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>0.34</v>
+        <v>0.58</v>
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>BIL</t>
+          <t>EIFFL</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>699.3</v>
+        <v>231.92</v>
       </c>
       <c r="C111" t="n">
-        <v>720</v>
+        <v>236</v>
       </c>
       <c r="D111" t="n">
-        <v>2.96</v>
+        <v>1.76</v>
       </c>
       <c r="E111" t="b">
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>709.7</v>
+        <v>229.04</v>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>-1.43</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>KCPSUGIND</t>
+          <t>CALSOFT</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>23.31</v>
+        <v>12.68</v>
       </c>
       <c r="C112" t="n">
-        <v>24</v>
+        <v>12.9</v>
       </c>
       <c r="D112" t="n">
-        <v>2.96</v>
+        <v>1.74</v>
       </c>
       <c r="E112" t="b">
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>24.53</v>
+        <v>12.51</v>
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
-        <v>2.21</v>
+        <v>-3.02</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>EXCEL</t>
+          <t>VGL</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1.02</v>
+        <v>57.38</v>
       </c>
       <c r="C113" t="n">
-        <v>1.05</v>
+        <v>58.38</v>
       </c>
       <c r="D113" t="n">
-        <v>2.94</v>
+        <v>1.74</v>
       </c>
       <c r="E113" t="b">
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>1.02</v>
+        <v>57.39</v>
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>-2.86</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>FROG</t>
+          <t>CNL</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>130</v>
+        <v>578.9</v>
       </c>
       <c r="C114" t="n">
-        <v>133.8</v>
+        <v>589</v>
       </c>
       <c r="D114" t="n">
-        <v>2.92</v>
+        <v>1.74</v>
       </c>
       <c r="E114" t="b">
         <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>129</v>
+        <v>547.85</v>
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
-        <v>-3.59</v>
+        <v>-6.99</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ARMOUR</t>
+          <t>LYKALABS</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>22.35</v>
+        <v>54.95</v>
       </c>
       <c r="C115" t="n">
-        <v>23</v>
+        <v>55.9</v>
       </c>
       <c r="D115" t="n">
-        <v>2.91</v>
+        <v>1.73</v>
       </c>
       <c r="E115" t="b">
         <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>23</v>
+        <v>51.37</v>
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>-8.1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ENERGYDEV</t>
+          <t>KRIDHANINF</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>14.91</v>
+        <v>2.32</v>
       </c>
       <c r="C116" t="n">
-        <v>15.34</v>
+        <v>2.36</v>
       </c>
       <c r="D116" t="n">
-        <v>2.88</v>
+        <v>1.72</v>
       </c>
       <c r="E116" t="b">
         <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>14.88</v>
+        <v>2.34</v>
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
-        <v>-3</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BAJAJINDEF</t>
+          <t>JMA</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>230.38</v>
+        <v>80.56999999999999</v>
       </c>
       <c r="C117" t="n">
-        <v>236.99</v>
+        <v>81.95</v>
       </c>
       <c r="D117" t="n">
-        <v>2.87</v>
+        <v>1.71</v>
       </c>
       <c r="E117" t="b">
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>233.93</v>
+        <v>80.59</v>
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>-1.29</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>GMRP&amp;UI</t>
+          <t>INDOWIND</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>101.1</v>
+        <v>8.83</v>
       </c>
       <c r="C118" t="n">
-        <v>104</v>
+        <v>8.98</v>
       </c>
       <c r="D118" t="n">
-        <v>2.87</v>
+        <v>1.7</v>
       </c>
       <c r="E118" t="b">
         <v>0</v>
       </c>
-      <c r="F118" t="inlineStr"/>
+      <c r="F118" t="n">
+        <v>8.27</v>
+      </c>
       <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
+      <c r="H118" t="n">
+        <v>-7.91</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>RUCHIRA</t>
+          <t>ADROITINFO</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>99.06</v>
+        <v>8.83</v>
       </c>
       <c r="C119" t="n">
-        <v>101.89</v>
+        <v>8.98</v>
       </c>
       <c r="D119" t="n">
-        <v>2.86</v>
+        <v>1.7</v>
       </c>
       <c r="E119" t="b">
         <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>101.5</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
-        <v>-0.38</v>
+        <v>-6.9</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ASTRON</t>
+          <t>VARDMNPOLY</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>3.87</v>
+        <v>7.69</v>
       </c>
       <c r="C120" t="n">
-        <v>3.98</v>
+        <v>7.82</v>
       </c>
       <c r="D120" t="n">
-        <v>2.84</v>
+        <v>1.69</v>
       </c>
       <c r="E120" t="b">
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>3.93</v>
+        <v>7.31</v>
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
-        <v>-1.26</v>
+        <v>-6.52</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>TREL</t>
+          <t>BAIDFIN</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>24.16</v>
+        <v>10.82</v>
       </c>
       <c r="C121" t="n">
-        <v>24.84</v>
+        <v>11</v>
       </c>
       <c r="D121" t="n">
-        <v>2.81</v>
+        <v>1.66</v>
       </c>
       <c r="E121" t="b">
         <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>24.87</v>
+        <v>10.66</v>
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
-        <v>0.12</v>
+        <v>-3.09</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>EMSLIMITED</t>
+          <t>MARKOLINES</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>290.85</v>
+        <v>151.49</v>
       </c>
       <c r="C122" t="n">
-        <v>299</v>
+        <v>154</v>
       </c>
       <c r="D122" t="n">
-        <v>2.8</v>
+        <v>1.66</v>
       </c>
       <c r="E122" t="b">
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>298.8</v>
+        <v>150.09</v>
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-2.54</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>EXXARO</t>
+          <t>SUNDARAM</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>6.81</v>
+        <v>1.21</v>
       </c>
       <c r="C123" t="n">
-        <v>7</v>
+        <v>1.23</v>
       </c>
       <c r="D123" t="n">
-        <v>2.79</v>
+        <v>1.65</v>
       </c>
       <c r="E123" t="b">
         <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>6.92</v>
+        <v>1.19</v>
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>-1.14</v>
+        <v>-3.25</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>UGARSUGAR</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>184.86</v>
+        <v>38.35</v>
       </c>
       <c r="C124" t="n">
-        <v>190</v>
+        <v>38.97</v>
       </c>
       <c r="D124" t="n">
-        <v>2.78</v>
+        <v>1.62</v>
       </c>
       <c r="E124" t="b">
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>188.54</v>
+        <v>35.83</v>
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
-        <v>-0.77</v>
+        <v>-8.06</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BYKE</t>
+          <t>BALPHARMA</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>32.1</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="C125" t="n">
-        <v>32.99</v>
+        <v>68.98</v>
       </c>
       <c r="D125" t="n">
-        <v>2.77</v>
+        <v>1.59</v>
       </c>
       <c r="E125" t="b">
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>32.85</v>
+        <v>66.8</v>
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>-0.42</v>
+        <v>-3.16</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>VIPCLOTHNG</t>
+          <t>KILITCH</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>17.42</v>
+        <v>316.1</v>
       </c>
       <c r="C126" t="n">
-        <v>17.9</v>
+        <v>321</v>
       </c>
       <c r="D126" t="n">
-        <v>2.76</v>
+        <v>1.55</v>
       </c>
       <c r="E126" t="b">
         <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>17.69</v>
+        <v>320.55</v>
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
-        <v>-1.17</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BPL</t>
+          <t>AUSOMENT</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>47.2</v>
+        <v>101.93</v>
       </c>
       <c r="C127" t="n">
-        <v>48.5</v>
+        <v>103.5</v>
       </c>
       <c r="D127" t="n">
-        <v>2.75</v>
+        <v>1.54</v>
       </c>
       <c r="E127" t="b">
         <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>48.03</v>
+        <v>98.28</v>
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
-        <v>-0.97</v>
+        <v>-5.04</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>FORCEMOT</t>
+          <t>NAMOEWASTE</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>20720</v>
+        <v>159</v>
       </c>
       <c r="C128" t="n">
-        <v>21290</v>
+        <v>161.45</v>
       </c>
       <c r="D128" t="n">
-        <v>2.75</v>
+        <v>1.54</v>
       </c>
       <c r="E128" t="b">
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>21395</v>
+        <v>153.05</v>
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
-        <v>0.49</v>
+        <v>-5.2</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>NATCAPSUQ</t>
+          <t>HARDWYN</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>145.52</v>
+        <v>18.81</v>
       </c>
       <c r="C129" t="n">
-        <v>149.5</v>
+        <v>19.1</v>
       </c>
       <c r="D129" t="n">
-        <v>2.74</v>
+        <v>1.54</v>
       </c>
       <c r="E129" t="b">
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>149.25</v>
+        <v>19.5</v>
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
-        <v>-0.17</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>GRPLTD</t>
+          <t>21STCENMGM</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1798</v>
+        <v>31.9</v>
       </c>
       <c r="C130" t="n">
-        <v>1846.8</v>
+        <v>32.39</v>
       </c>
       <c r="D130" t="n">
-        <v>2.71</v>
+        <v>1.54</v>
       </c>
       <c r="E130" t="b">
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>1824.2</v>
+        <v>31.27</v>
       </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
-        <v>-1.22</v>
+        <v>-3.46</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>TTKHLTCARE</t>
+          <t>SVPGLOB</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>816.15</v>
+        <v>2.6</v>
       </c>
       <c r="C131" t="n">
-        <v>838</v>
+        <v>2.64</v>
       </c>
       <c r="D131" t="n">
-        <v>2.68</v>
+        <v>1.54</v>
       </c>
       <c r="E131" t="b">
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>823.05</v>
+        <v>2.62</v>
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
-        <v>-1.78</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>GAUDIUMIVF</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>80.55</v>
+        <v>226.57</v>
       </c>
       <c r="C132" t="n">
-        <v>82.7</v>
+        <v>230</v>
       </c>
       <c r="D132" t="n">
-        <v>2.67</v>
+        <v>1.51</v>
       </c>
       <c r="E132" t="b">
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>78.73999999999999</v>
+        <v>222</v>
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
-        <v>-4.79</v>
+        <v>-3.48</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>KOTARISUG</t>
+          <t>MALLCOM</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>23.37</v>
+        <v>1033.2</v>
       </c>
       <c r="C133" t="n">
-        <v>23.99</v>
+        <v>1048.7</v>
       </c>
       <c r="D133" t="n">
-        <v>2.65</v>
+        <v>1.5</v>
       </c>
       <c r="E133" t="b">
         <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>24.77</v>
+        <v>985</v>
       </c>
 